--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO15" headerRowCount="1">
-  <autoFilter ref="A1:CO15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO42" headerRowCount="1">
+  <autoFilter ref="A1:CO42"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$15)</f>
+        <f>COUNTA('Picks'!$A$2:$A$42)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$42,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$42,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$42,"settled",'Picks'!$V$2:$V$42,"win")+COUNTIFS('Picks'!$U$2:$U$42,"settled",'Picks'!$V$2:$V$42,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$15,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$42,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$42,"&gt;0",'Picks'!$V$2:$V$42,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$42,"&gt;0",'Picks'!$V$2:$V$42,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")/(COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"win")+COUNTIFS('Picks'!$BX$2:$BX$15,"&gt;0",'Picks'!$V$2:$V$15,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$42,"&gt;0",'Picks'!$V$2:$V$42,"win")/(COUNTIFS('Picks'!$BX$2:$BX$42,"&gt;0",'Picks'!$V$2:$V$42,"win")+COUNTIFS('Picks'!$BX$2:$BX$42,"&gt;0",'Picks'!$V$2:$V$42,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$15)/SUM('Picks'!$BX$2:$BX$15),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$42)/SUM('Picks'!$BX$2:$BX$42),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$15)</f>
+        <f>SUM('Picks'!$BY$2:$BY$42)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$15,"&lt;&gt;",'Picks'!$AB$2:$AB$15),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$42,"&lt;&gt;",'Picks'!$AB$2:$AB$42),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$42,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$42,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$15,'Picks'!$AM$2:$AM$15,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$42,'Picks'!$AM$2:$AM$42,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$42,$A14,'Picks'!$U$2:$U$42,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$42,$A14,'Picks'!$U$2:$U$42,"settled",'Picks'!$V$2:$V$42,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$42,$A14,'Picks'!$U$2:$U$42,"settled",'Picks'!$V$2:$V$42,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$42,'Picks'!$H$2:$H$42,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A14,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$42,'Picks'!$H$2:$H$42,$A14,'Picks'!$U$2:$U$42,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$42,$A15,'Picks'!$U$2:$U$42,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$42,$A15,'Picks'!$U$2:$U$42,"settled",'Picks'!$V$2:$V$42,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$42,$A15,'Picks'!$U$2:$U$42,"settled",'Picks'!$V$2:$V$42,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$42,'Picks'!$H$2:$H$42,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A15,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$42,'Picks'!$H$2:$H$42,$A15,'Picks'!$U$2:$U$42,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$42,$A16,'Picks'!$U$2:$U$42,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$42,$A16,'Picks'!$U$2:$U$42,"settled",'Picks'!$V$2:$V$42,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled",'Picks'!$V$2:$V$15,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$42,$A16,'Picks'!$U$2:$U$42,"settled",'Picks'!$V$2:$V$42,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$15,'Picks'!$H$2:$H$15,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$42,'Picks'!$H$2:$H$42,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$15,'Picks'!$H$2:$H$15,$A16,'Picks'!$U$2:$U$15,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$42,'Picks'!$H$2:$H$42,$A16,'Picks'!$U$2:$U$42,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO15"/>
+  <dimension ref="A1:CO42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3310,18 +3310,32 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
+      <c r="AC8" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T01:52:01.459436Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-agc-mel-2026-07-26).</t>
@@ -3493,22 +3507,22 @@
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>8a628c820b574af7</t>
+          <t>d70fc113f3034152</t>
         </is>
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:20.623550Z</t>
+          <t>2026-07-27T10:27:30.866418Z</t>
         </is>
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T08:00:00Z</t>
+          <t>2026-07-27T11:00:00Z</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>60702</t>
+          <t>60732</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -3518,12 +3532,12 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
@@ -3533,7 +3547,7 @@
       </c>
       <c r="I9" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J9" s="25" t="n"/>
@@ -3543,26 +3557,26 @@
         </is>
       </c>
       <c r="L9" s="26" t="n">
-        <v>163</v>
+        <v>-203</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>2.63</v>
+        <v>1.492611</v>
       </c>
       <c r="N9" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.669967</v>
       </c>
       <c r="O9" s="28" t="n">
-        <v>0.607321</v>
+        <v>0.736846</v>
       </c>
       <c r="P9" s="28" t="n"/>
       <c r="Q9" s="28" t="n">
-        <v>0.227093</v>
+        <v>0.06687899999999999</v>
       </c>
       <c r="R9" s="26" t="n">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="S9" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T9" s="24" t="inlineStr">
         <is>
@@ -3571,21 +3585,35 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
+      <c r="AC9" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:27:57.945893Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-cs2-erx-ent-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-astr-nvo-2026-07-27).</t>
         </is>
       </c>
       <c r="AF9" s="31" t="inlineStr">
@@ -3595,7 +3623,7 @@
       </c>
       <c r="AG9" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH9" s="24" t="n"/>
@@ -3626,32 +3654,32 @@
       </c>
       <c r="AP9" s="24" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AQ9" s="24" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AR9" s="24" t="inlineStr">
         <is>
-          <t>Entropy</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AS9" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="AT9" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="AU9" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="AV9" s="24" t="n"/>
@@ -3704,7 +3732,7 @@
       </c>
       <c r="BH9" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:11.610199Z</t>
+          <t>2026-07-27T10:27:02.394501Z</t>
         </is>
       </c>
       <c r="BI9" s="24" t="inlineStr">
@@ -3714,13 +3742,13 @@
       </c>
       <c r="BJ9" s="25" t="n"/>
       <c r="BK9" s="26" t="n">
-        <v>163</v>
+        <v>-203</v>
       </c>
       <c r="BL9" s="27" t="n">
-        <v>2.63</v>
+        <v>1.492611</v>
       </c>
       <c r="BM9" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.669967</v>
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
@@ -3754,12 +3782,12 @@
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>a5378127b8f34b3b</t>
+          <t>a2e4473ba2dc4ac2</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:20.623550Z</t>
+          <t>2026-07-27T10:27:30.866418Z</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -3769,7 +3797,7 @@
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>60732</t>
+          <t>63352</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -3779,12 +3807,12 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="H10" s="24" t="inlineStr">
@@ -3804,23 +3832,23 @@
         </is>
       </c>
       <c r="L10" s="26" t="n">
-        <v>-170</v>
+        <v>-156</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.641026</v>
       </c>
       <c r="N10" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.609375</v>
       </c>
       <c r="O10" s="28" t="n">
-        <v>0.736846</v>
+        <v>0.862507</v>
       </c>
       <c r="P10" s="28" t="n"/>
       <c r="Q10" s="28" t="n">
-        <v>0.107216</v>
+        <v>0.253132</v>
       </c>
       <c r="R10" s="26" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="S10" s="29" t="n">
         <v>2</v>
@@ -3832,21 +3860,35 @@
       </c>
       <c r="U10" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>1.2821</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:27:59.189348Z</t>
+        </is>
+      </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-astr-nvo-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-exruby-erx-2026-07-27).</t>
         </is>
       </c>
       <c r="AF10" s="31" t="inlineStr">
@@ -3887,32 +3929,32 @@
       </c>
       <c r="AP10" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AQ10" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AR10" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AS10" s="24" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AT10" s="24" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AU10" s="24" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AV10" s="24" t="n"/>
@@ -3965,7 +4007,7 @@
       </c>
       <c r="BH10" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:12.664245Z</t>
+          <t>2026-07-27T10:27:03.352513Z</t>
         </is>
       </c>
       <c r="BI10" s="24" t="inlineStr">
@@ -3975,13 +4017,13 @@
       </c>
       <c r="BJ10" s="25" t="n"/>
       <c r="BK10" s="26" t="n">
-        <v>-170</v>
+        <v>-156</v>
       </c>
       <c r="BL10" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.641026</v>
       </c>
       <c r="BM10" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.609375</v>
       </c>
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
@@ -4015,22 +4057,22 @@
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>3c3fb090dd0448b4</t>
+          <t>18433aef54b14feb</t>
         </is>
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:20.623550Z</t>
+          <t>2026-07-27T10:27:30.866418Z</t>
         </is>
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T15:30:00Z</t>
+          <t>2026-07-27T11:00:00Z</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>60764</t>
+          <t>63351</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -4040,12 +4082,12 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Benched gods</t>
         </is>
       </c>
       <c r="G11" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="H11" s="24" t="inlineStr">
@@ -4055,7 +4097,7 @@
       </c>
       <c r="I11" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J11" s="25" t="n"/>
@@ -4065,26 +4107,26 @@
         </is>
       </c>
       <c r="L11" s="26" t="n">
-        <v>-194</v>
+        <v>104</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>1.515464</v>
+        <v>2.04</v>
       </c>
       <c r="N11" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.490196</v>
       </c>
       <c r="O11" s="28" t="n">
-        <v>0.735192</v>
+        <v>0.629085</v>
       </c>
       <c r="P11" s="28" t="n"/>
       <c r="Q11" s="28" t="n">
-        <v>0.07532800000000001</v>
+        <v>0.138889</v>
       </c>
       <c r="R11" s="26" t="n">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="S11" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T11" s="24" t="inlineStr">
         <is>
@@ -4093,21 +4135,35 @@
       </c>
       <c r="U11" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
+      <c r="AC11" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:09:01.989713Z</t>
+        </is>
+      </c>
       <c r="AE11" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-brute-navij-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-cs2-bpl-bge-2026-07-27).</t>
         </is>
       </c>
       <c r="AF11" s="31" t="inlineStr">
@@ -4117,7 +4173,7 @@
       </c>
       <c r="AG11" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH11" s="24" t="n"/>
@@ -4125,7 +4181,7 @@
       <c r="AJ11" s="31" t="n"/>
       <c r="AK11" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL11" s="26" t="n">
@@ -4133,47 +4189,47 @@
       </c>
       <c r="AM11" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN11" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO11" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP11" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Benched gods</t>
         </is>
       </c>
       <c r="AQ11" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Benched gods</t>
         </is>
       </c>
       <c r="AR11" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>Benched gods</t>
         </is>
       </c>
       <c r="AS11" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AT11" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AU11" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AV11" s="24" t="n"/>
@@ -4226,7 +4282,7 @@
       </c>
       <c r="BH11" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:17.438646Z</t>
+          <t>2026-07-27T10:27:03.893606Z</t>
         </is>
       </c>
       <c r="BI11" s="24" t="inlineStr">
@@ -4236,13 +4292,13 @@
       </c>
       <c r="BJ11" s="25" t="n"/>
       <c r="BK11" s="26" t="n">
-        <v>-194</v>
+        <v>104</v>
       </c>
       <c r="BL11" s="27" t="n">
-        <v>1.515464</v>
+        <v>2.04</v>
       </c>
       <c r="BM11" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.490196</v>
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
@@ -4276,22 +4332,22 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>285c42f894b94c28</t>
+          <t>2d614c810b014ac4</t>
         </is>
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:20.623550Z</t>
+          <t>2026-07-27T10:27:30.866418Z</t>
         </is>
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T16:30:00Z</t>
+          <t>2026-07-27T11:00:00Z</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>60788</t>
+          <t>60729</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -4301,12 +4357,12 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="H12" s="24" t="inlineStr">
@@ -4326,26 +4382,26 @@
         </is>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-156</v>
+        <v>-178</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.561798</v>
       </c>
       <c r="N12" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.640288</v>
       </c>
       <c r="O12" s="28" t="n">
-        <v>0.659512</v>
+        <v>0.539211</v>
       </c>
       <c r="P12" s="28" t="n"/>
       <c r="Q12" s="28" t="n">
-        <v>0.050137</v>
+        <v>-0.101077</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="S12" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T12" s="24" t="inlineStr">
         <is>
@@ -4354,21 +4410,35 @@
       </c>
       <c r="U12" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
+      <c r="AC12" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:28:01.359998Z</t>
+        </is>
+      </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-brute-mouzn-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-unity-mta-2026-07-27).</t>
         </is>
       </c>
       <c r="AF12" s="31" t="inlineStr">
@@ -4386,7 +4456,7 @@
       <c r="AJ12" s="31" t="n"/>
       <c r="AK12" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL12" s="26" t="n">
@@ -4394,47 +4464,47 @@
       </c>
       <c r="AM12" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN12" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO12" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP12" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AQ12" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AR12" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AS12" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="AT12" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="AU12" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="AV12" s="24" t="n"/>
@@ -4487,7 +4557,7 @@
       </c>
       <c r="BH12" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:17.953712Z</t>
+          <t>2026-07-27T10:27:04.366441Z</t>
         </is>
       </c>
       <c r="BI12" s="24" t="inlineStr">
@@ -4497,13 +4567,13 @@
       </c>
       <c r="BJ12" s="25" t="n"/>
       <c r="BK12" s="26" t="n">
-        <v>-156</v>
+        <v>-178</v>
       </c>
       <c r="BL12" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.561798</v>
       </c>
       <c r="BM12" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.640288</v>
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
@@ -4537,22 +4607,22 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>7003ea918f9740ec</t>
+          <t>23a1cd38bdc74392</t>
         </is>
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:20.623550Z</t>
+          <t>2026-07-27T10:27:30.866418Z</t>
         </is>
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T17:00:00Z</t>
+          <t>2026-07-27T12:00:00Z</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>60795</t>
+          <t>60736</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -4562,12 +4632,12 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>Falcons Force</t>
+          <t>Atputies</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -4587,26 +4657,26 @@
         </is>
       </c>
       <c r="L13" s="26" t="n">
-        <v>-163</v>
+        <v>150</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.5</v>
       </c>
       <c r="N13" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.4</v>
       </c>
       <c r="O13" s="28" t="n">
-        <v>0.70196</v>
+        <v>0.610293</v>
       </c>
       <c r="P13" s="28" t="n"/>
       <c r="Q13" s="28" t="n">
-        <v>0.082188</v>
+        <v>0.210293</v>
       </c>
       <c r="R13" s="26" t="n">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="S13" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T13" s="24" t="inlineStr">
         <is>
@@ -4615,21 +4685,35 @@
       </c>
       <c r="U13" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y13" s="25" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n"/>
-      <c r="AD13" s="24" t="n"/>
+      <c r="AC13" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:28:02.496927Z</t>
+        </is>
+      </c>
       <c r="AE13" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-bbp-falf-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-nvo-atp-2026-07-27).</t>
         </is>
       </c>
       <c r="AF13" s="31" t="inlineStr">
@@ -4639,7 +4723,7 @@
       </c>
       <c r="AG13" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH13" s="24" t="n"/>
@@ -4670,32 +4754,32 @@
       </c>
       <c r="AP13" s="24" t="inlineStr">
         <is>
-          <t>Falcons Force</t>
+          <t>Atputies</t>
         </is>
       </c>
       <c r="AQ13" s="24" t="inlineStr">
         <is>
-          <t>Falcons Force</t>
+          <t>Atputies</t>
         </is>
       </c>
       <c r="AR13" s="24" t="inlineStr">
         <is>
-          <t>Falcons Force</t>
+          <t>Atputies</t>
         </is>
       </c>
       <c r="AS13" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AT13" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AU13" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AV13" s="24" t="n"/>
@@ -4748,7 +4832,7 @@
       </c>
       <c r="BH13" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:18.459256Z</t>
+          <t>2026-07-27T10:27:05.476395Z</t>
         </is>
       </c>
       <c r="BI13" s="24" t="inlineStr">
@@ -4758,13 +4842,13 @@
       </c>
       <c r="BJ13" s="25" t="n"/>
       <c r="BK13" s="26" t="n">
-        <v>-163</v>
+        <v>150</v>
       </c>
       <c r="BL13" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.5</v>
       </c>
       <c r="BM13" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.4</v>
       </c>
       <c r="BN13" s="28" t="n"/>
       <c r="BO13" s="28" t="n"/>
@@ -4798,22 +4882,22 @@
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>9306e248170c423a</t>
+          <t>d94baaebfbd64a2e</t>
         </is>
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:20.623550Z</t>
+          <t>2026-07-27T13:31:52.156513Z</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T17:00:00Z</t>
+          <t>2026-07-27T14:00:00Z</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>60794</t>
+          <t>63303</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -4823,12 +4907,12 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>HATERS</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="H14" s="24" t="inlineStr">
@@ -4838,7 +4922,7 @@
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J14" s="25" t="n"/>
@@ -4848,26 +4932,26 @@
         </is>
       </c>
       <c r="L14" s="26" t="n">
-        <v>178</v>
+        <v>-163</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>2.78</v>
+        <v>1.613497</v>
       </c>
       <c r="N14" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.619772</v>
       </c>
       <c r="O14" s="28" t="n">
-        <v>0.573171</v>
+        <v>0.652309</v>
       </c>
       <c r="P14" s="28" t="n"/>
       <c r="Q14" s="28" t="n">
-        <v>0.213459</v>
+        <v>0.032537</v>
       </c>
       <c r="R14" s="26" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="S14" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T14" s="24" t="inlineStr">
         <is>
@@ -4876,21 +4960,35 @@
       </c>
       <c r="U14" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V14" s="24" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y14" s="25" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n"/>
-      <c r="AD14" s="24" t="n"/>
+      <c r="AC14" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:32:18.485840Z</t>
+        </is>
+      </c>
       <c r="AE14" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-cs2-rush-hat-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-erx-ica-2026-07-27).</t>
         </is>
       </c>
       <c r="AF14" s="31" t="inlineStr">
@@ -4900,7 +4998,7 @@
       </c>
       <c r="AG14" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH14" s="24" t="n"/>
@@ -4931,32 +5029,32 @@
       </c>
       <c r="AP14" s="24" t="inlineStr">
         <is>
-          <t>HATERS</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AQ14" s="24" t="inlineStr">
         <is>
-          <t>HATERS</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AR14" s="24" t="inlineStr">
         <is>
-          <t>HATERS</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AS14" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AT14" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AU14" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AV14" s="24" t="n"/>
@@ -4974,7 +5072,7 @@
       </c>
       <c r="BA14" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>d55450e581d49c9cac62c08b0f9a47fad2adbce61565b9ce26f93fb0e665f4f9</t>
         </is>
       </c>
       <c r="BB14" s="24" t="inlineStr">
@@ -4989,7 +5087,7 @@
       </c>
       <c r="BD14" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>d55450e581d49c9cac62c08b0f9a47fad2adbce61565b9ce26f93fb0e665f4f9</t>
         </is>
       </c>
       <c r="BE14" s="24" t="inlineStr">
@@ -5009,7 +5107,7 @@
       </c>
       <c r="BH14" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:18.919041Z</t>
+          <t>2026-07-27T13:31:26.771058Z</t>
         </is>
       </c>
       <c r="BI14" s="24" t="inlineStr">
@@ -5019,13 +5117,13 @@
       </c>
       <c r="BJ14" s="25" t="n"/>
       <c r="BK14" s="26" t="n">
-        <v>178</v>
+        <v>-163</v>
       </c>
       <c r="BL14" s="27" t="n">
-        <v>2.78</v>
+        <v>1.613497</v>
       </c>
       <c r="BM14" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.619772</v>
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
@@ -5059,22 +5157,22 @@
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>85066b8a91bc43c9</t>
+          <t>13ca41647d4e4a0d</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:20.623550Z</t>
+          <t>2026-07-27T13:31:52.156513Z</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
         <is>
-          <t>2026-07-27T17:30:00Z</t>
+          <t>2026-07-27T14:00:00Z</t>
         </is>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>60805</t>
+          <t>63354</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -5084,12 +5182,12 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="G15" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>GenOne</t>
         </is>
       </c>
       <c r="H15" s="24" t="inlineStr">
@@ -5099,7 +5197,7 @@
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J15" s="25" t="n"/>
@@ -5109,23 +5207,23 @@
         </is>
       </c>
       <c r="L15" s="26" t="n">
-        <v>-156</v>
+        <v>-133</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.75188</v>
       </c>
       <c r="N15" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.570815</v>
       </c>
       <c r="O15" s="28" t="n">
-        <v>0.55859</v>
+        <v>0.550435</v>
       </c>
       <c r="P15" s="28" t="n"/>
       <c r="Q15" s="28" t="n">
-        <v>-0.050785</v>
+        <v>-0.02038</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S15" s="29" t="n">
         <v>0</v>
@@ -5137,21 +5235,35 @@
       </c>
       <c r="U15" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y15" s="25" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
+      <c r="AC15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:03:36.426866Z</t>
+        </is>
+      </c>
       <c r="AE15" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-navij-mouzn-2026-07-27).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-g1-sparta-2026-07-27).</t>
         </is>
       </c>
       <c r="AF15" s="31" t="inlineStr">
@@ -5192,32 +5304,32 @@
       </c>
       <c r="AP15" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AQ15" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AR15" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AS15" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>GenOne</t>
         </is>
       </c>
       <c r="AT15" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>GenOne</t>
         </is>
       </c>
       <c r="AU15" s="24" t="inlineStr">
         <is>
-          <t>NAVI Junior</t>
+          <t>GenOne</t>
         </is>
       </c>
       <c r="AV15" s="24" t="n"/>
@@ -5235,7 +5347,7 @@
       </c>
       <c r="BA15" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>d55450e581d49c9cac62c08b0f9a47fad2adbce61565b9ce26f93fb0e665f4f9</t>
         </is>
       </c>
       <c r="BB15" s="24" t="inlineStr">
@@ -5250,7 +5362,7 @@
       </c>
       <c r="BD15" s="24" t="inlineStr">
         <is>
-          <t>e9c327ce15d79aaa8ed5032a6fb86929aaa479e14a8bc9a35686411400dd6b91</t>
+          <t>d55450e581d49c9cac62c08b0f9a47fad2adbce61565b9ce26f93fb0e665f4f9</t>
         </is>
       </c>
       <c r="BE15" s="24" t="inlineStr">
@@ -5270,7 +5382,7 @@
       </c>
       <c r="BH15" s="24" t="inlineStr">
         <is>
-          <t>2026-07-26T19:32:19.381755Z</t>
+          <t>2026-07-27T13:31:27.241966Z</t>
         </is>
       </c>
       <c r="BI15" s="24" t="inlineStr">
@@ -5280,13 +5392,13 @@
       </c>
       <c r="BJ15" s="25" t="n"/>
       <c r="BK15" s="26" t="n">
-        <v>-156</v>
+        <v>-133</v>
       </c>
       <c r="BL15" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.75188</v>
       </c>
       <c r="BM15" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.570815</v>
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
@@ -5317,6 +5429,7165 @@
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
     </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>f7d181a644b349e7</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:31:52.156513Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>63353</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>SAW Youngsters</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.563841</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>-0.055931</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:09:05.326701Z</t>
+        </is>
+      </c>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-re-sawy-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>SAW Youngsters</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>SAW Youngsters</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>SAW Youngsters</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>d55450e581d49c9cac62c08b0f9a47fad2adbce61565b9ce26f93fb0e665f4f9</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>d55450e581d49c9cac62c08b0f9a47fad2adbce61565b9ce26f93fb0e665f4f9</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:31:27.716035Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>4897241dec7e4460</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:31:52.156513Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>60748</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.538172</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>-0.102116</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:03:37.717594Z</t>
+        </is>
+      </c>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-bpl-misa-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>d55450e581d49c9cac62c08b0f9a47fad2adbce61565b9ce26f93fb0e665f4f9</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>d55450e581d49c9cac62c08b0f9a47fad2adbce61565b9ce26f93fb0e665f4f9</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:31:28.222165Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>8ff4294220a9430c</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:31:52.156513Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>60788</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Brute</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.658722</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>0.049347</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n">
+        <v>1.2821</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:47:14.211302Z</t>
+        </is>
+      </c>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-brute-mouzn-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>Brute</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>Brute</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>Brute</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>d55450e581d49c9cac62c08b0f9a47fad2adbce61565b9ce26f93fb0e665f4f9</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>d55450e581d49c9cac62c08b0f9a47fad2adbce61565b9ce26f93fb0e665f4f9</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T13:31:31.182868Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>a4054a1c905c46da</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:36:41.723874Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>60795</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Falcons Force</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>Bebop</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.680315</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>0.07094</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>55</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:47:15.379469Z</t>
+        </is>
+      </c>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-bbp-falf-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>Falcons Force</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>Falcons Force</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>Falcons Force</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>Bebop</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>Bebop</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>Bebop</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>6329bd3e425200846e7ff17d6fd62114a73b33dcf85796cbdc7cb776105e39da</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>6329bd3e425200846e7ff17d6fd62114a73b33dcf85796cbdc7cb776105e39da</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:36:23.363578Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>2c1ca287fd514edc</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:36:41.723874Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>63356</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.5595909999999999</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>-0.09075900000000001</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:47:16.601700Z</t>
+        </is>
+      </c>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-cs2-jpu-ica-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>6329bd3e425200846e7ff17d6fd62114a73b33dcf85796cbdc7cb776105e39da</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>6329bd3e425200846e7ff17d6fd62114a73b33dcf85796cbdc7cb776105e39da</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:36:24.394273Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>6538dda149344041</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:36:41.723874Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>60794</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>HATERS</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.506515</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>0.156865</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>98</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:51:48.309540Z</t>
+        </is>
+      </c>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-cs2-rush-hat-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>HATERS</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>HATERS</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>HATERS</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>6329bd3e425200846e7ff17d6fd62114a73b33dcf85796cbdc7cb776105e39da</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>6329bd3e425200846e7ff17d6fd62114a73b33dcf85796cbdc7cb776105e39da</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T16:36:24.863764Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>aa04701e4c294a7f</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:08:18.026663Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:30:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>60805</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.573006</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>-0.056624</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T19:47:18.735287Z</t>
+        </is>
+      </c>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-navij-mouzn-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>131e6b24b579a0abf2eb74dac6edd091b7176b450ac3f8f4f38bd35710b750d7</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>131e6b24b579a0abf2eb74dac6edd091b7176b450ac3f8f4f38bd35710b750d7</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:08:00.705639Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>b880e7fcfba0433e</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:38:10.535886Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T18:15:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>63492</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>aimclub</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.65286</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>0.10331</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>72</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n">
+        <v>1.6393</v>
+      </c>
+      <c r="AD23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T22:51:49.488820Z</t>
+        </is>
+      </c>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-aimc-mel-2026-07-27).</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>mellren</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>aimclub</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>aimclub</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>aimclub</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>867870f5311168845ab98ba889eb7970c88200d6dbd0532dbd8a6a3de3837c1a</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>867870f5311168845ab98ba889eb7970c88200d6dbd0532dbd8a6a3de3837c1a</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:37:55.611264Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n"/>
+      <c r="BY23" s="27" t="n"/>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>d7ae167da1244103</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>63357</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>BET-M 33</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.582559</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>-0.077305</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="26" t="n"/>
+      <c r="X24" s="26" t="n"/>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n"/>
+      <c r="AD24" s="24" t="n"/>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-33-hon-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>BET-M 33</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>BET-M 33</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>BET-M 33</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:39.276046Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n"/>
+      <c r="BY24" s="27" t="n"/>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>c7533602b6d8481c</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>63306</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.710969</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>0.25014</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="26" t="n"/>
+      <c r="X25" s="26" t="n"/>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n"/>
+      <c r="AD25" s="24" t="n"/>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-bpl-enjoy-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:39.784703Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n"/>
+      <c r="BY25" s="27" t="n"/>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>22f0867f90b74019</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>64432</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Noir Verse</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.509533</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>0.159883</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="n"/>
+      <c r="W26" s="26" t="n"/>
+      <c r="X26" s="26" t="n"/>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n"/>
+      <c r="AD26" s="24" t="n"/>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-cs2-nvo-mouzn-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>Noir Verse</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>Noir Verse</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>Noir Verse</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:40.889369Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n"/>
+      <c r="BY26" s="27" t="n"/>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>310d6c4312fd480c</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>64433</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.580775</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>-0.048855</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="n"/>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="26" t="n"/>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n"/>
+      <c r="AD27" s="24" t="n"/>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-astr-navij-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>ASTRAL</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:41.424963Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n"/>
+      <c r="BY27" s="27" t="n"/>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>b248eb6e992643dc</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>63307</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>ex-MANA eSports</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <v>0.628318</v>
+      </c>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="28" t="n">
+        <v>-0.062084</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="n"/>
+      <c r="W28" s="26" t="n"/>
+      <c r="X28" s="26" t="n"/>
+      <c r="Y28" s="25" t="n"/>
+      <c r="Z28" s="26" t="n"/>
+      <c r="AA28" s="28" t="n"/>
+      <c r="AB28" s="28" t="n"/>
+      <c r="AC28" s="30" t="n"/>
+      <c r="AD28" s="24" t="n"/>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-re-exmana-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG28" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH28" s="24" t="n"/>
+      <c r="AI28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="n"/>
+      <c r="AK28" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN28" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO28" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP28" s="24" t="inlineStr">
+        <is>
+          <t>ex-MANA eSports</t>
+        </is>
+      </c>
+      <c r="AQ28" s="24" t="inlineStr">
+        <is>
+          <t>ex-MANA eSports</t>
+        </is>
+      </c>
+      <c r="AR28" s="24" t="inlineStr">
+        <is>
+          <t>ex-MANA eSports</t>
+        </is>
+      </c>
+      <c r="AS28" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AT28" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AU28" s="24" t="inlineStr">
+        <is>
+          <t>Rune Eaters</t>
+        </is>
+      </c>
+      <c r="AV28" s="24" t="n"/>
+      <c r="AW28" s="24" t="n"/>
+      <c r="AX28" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY28" s="24" t="n"/>
+      <c r="AZ28" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB28" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG28" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH28" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:41.919045Z</t>
+        </is>
+      </c>
+      <c r="BI28" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ28" s="25" t="n"/>
+      <c r="BK28" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL28" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM28" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN28" s="28" t="n"/>
+      <c r="BO28" s="28" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
+      <c r="BR28" s="28" t="n"/>
+      <c r="BS28" s="28" t="n"/>
+      <c r="BT28" s="28" t="n"/>
+      <c r="BU28" s="25" t="n"/>
+      <c r="BV28" s="29" t="n"/>
+      <c r="BW28" s="24" t="n"/>
+      <c r="BX28" s="30" t="n"/>
+      <c r="BY28" s="27" t="n"/>
+      <c r="BZ28" s="24" t="n"/>
+      <c r="CA28" s="31" t="n"/>
+      <c r="CB28" s="24" t="n"/>
+      <c r="CC28" s="24" t="n"/>
+      <c r="CD28" s="24" t="n"/>
+      <c r="CE28" s="24" t="n"/>
+      <c r="CF28" s="24" t="n"/>
+      <c r="CG28" s="24" t="n"/>
+      <c r="CH28" s="24" t="n"/>
+      <c r="CI28" s="24" t="n"/>
+      <c r="CJ28" s="24" t="n"/>
+      <c r="CK28" s="24" t="n"/>
+      <c r="CL28" s="24" t="n"/>
+      <c r="CM28" s="24" t="n"/>
+      <c r="CN28" s="24" t="n"/>
+      <c r="CO28" s="24" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>386e4dc745654aff</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>63359</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.589686</v>
+      </c>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n">
+        <v>0.070455</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>55</v>
+      </c>
+      <c r="S29" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="n"/>
+      <c r="W29" s="26" t="n"/>
+      <c r="X29" s="26" t="n"/>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="28" t="n"/>
+      <c r="AC29" s="30" t="n"/>
+      <c r="AD29" s="24" t="n"/>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-btf-g2a-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG29" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="AQ29" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="AR29" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="AS29" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AT29" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AU29" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA29" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB29" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC29" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH29" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:42.419976Z</t>
+        </is>
+      </c>
+      <c r="BI29" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL29" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM29" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN29" s="28" t="n"/>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n"/>
+      <c r="BY29" s="27" t="n"/>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="n"/>
+      <c r="CD29" s="24" t="n"/>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="n"/>
+      <c r="CJ29" s="24" t="n"/>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>8515f4ed46bc404c</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>64367</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Bebop</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <v>0.525641</v>
+      </c>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="28" t="n">
+        <v>0.06481199999999999</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <v>52</v>
+      </c>
+      <c r="S30" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T30" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U30" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="n"/>
+      <c r="W30" s="26" t="n"/>
+      <c r="X30" s="26" t="n"/>
+      <c r="Y30" s="25" t="n"/>
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="28" t="n"/>
+      <c r="AC30" s="30" t="n"/>
+      <c r="AD30" s="24" t="n"/>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-bpl-bbp-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG30" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH30" s="24" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN30" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO30" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP30" s="24" t="inlineStr">
+        <is>
+          <t>Bebop</t>
+        </is>
+      </c>
+      <c r="AQ30" s="24" t="inlineStr">
+        <is>
+          <t>Bebop</t>
+        </is>
+      </c>
+      <c r="AR30" s="24" t="inlineStr">
+        <is>
+          <t>Bebop</t>
+        </is>
+      </c>
+      <c r="AS30" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AT30" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AU30" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AV30" s="24" t="n"/>
+      <c r="AW30" s="24" t="n"/>
+      <c r="AX30" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY30" s="24" t="n"/>
+      <c r="AZ30" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA30" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB30" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC30" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD30" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG30" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH30" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:42.912018Z</t>
+        </is>
+      </c>
+      <c r="BI30" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ30" s="25" t="n"/>
+      <c r="BK30" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL30" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM30" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN30" s="28" t="n"/>
+      <c r="BO30" s="28" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
+      <c r="BR30" s="28" t="n"/>
+      <c r="BS30" s="28" t="n"/>
+      <c r="BT30" s="28" t="n"/>
+      <c r="BU30" s="25" t="n"/>
+      <c r="BV30" s="29" t="n"/>
+      <c r="BW30" s="24" t="n"/>
+      <c r="BX30" s="30" t="n"/>
+      <c r="BY30" s="27" t="n"/>
+      <c r="BZ30" s="24" t="n"/>
+      <c r="CA30" s="31" t="n"/>
+      <c r="CB30" s="24" t="n"/>
+      <c r="CC30" s="24" t="n"/>
+      <c r="CD30" s="24" t="n"/>
+      <c r="CE30" s="24" t="n"/>
+      <c r="CF30" s="24" t="n"/>
+      <c r="CG30" s="24" t="n"/>
+      <c r="CH30" s="24" t="n"/>
+      <c r="CI30" s="24" t="n"/>
+      <c r="CJ30" s="24" t="n"/>
+      <c r="CK30" s="24" t="n"/>
+      <c r="CL30" s="24" t="n"/>
+      <c r="CM30" s="24" t="n"/>
+      <c r="CN30" s="24" t="n"/>
+      <c r="CO30" s="24" t="n"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>e0cf1c2d06654c1f</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>63358</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>Atreides</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <v>0.563287</v>
+      </c>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="28" t="n">
+        <v>-0.056485</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="n"/>
+      <c r="W31" s="26" t="n"/>
+      <c r="X31" s="26" t="n"/>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="26" t="n"/>
+      <c r="AA31" s="28" t="n"/>
+      <c r="AB31" s="28" t="n"/>
+      <c r="AC31" s="30" t="n"/>
+      <c r="AD31" s="24" t="n"/>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-atr-erx-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG31" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="n"/>
+      <c r="AK31" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM31" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP31" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AQ31" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AR31" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AS31" s="24" t="inlineStr">
+        <is>
+          <t>Atreides</t>
+        </is>
+      </c>
+      <c r="AT31" s="24" t="inlineStr">
+        <is>
+          <t>Atreides</t>
+        </is>
+      </c>
+      <c r="AU31" s="24" t="inlineStr">
+        <is>
+          <t>Atreides</t>
+        </is>
+      </c>
+      <c r="AV31" s="24" t="n"/>
+      <c r="AW31" s="24" t="n"/>
+      <c r="AX31" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY31" s="24" t="n"/>
+      <c r="AZ31" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA31" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB31" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC31" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD31" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG31" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH31" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:43.417305Z</t>
+        </is>
+      </c>
+      <c r="BI31" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ31" s="25" t="n"/>
+      <c r="BK31" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL31" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM31" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN31" s="28" t="n"/>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
+      <c r="BR31" s="28" t="n"/>
+      <c r="BS31" s="28" t="n"/>
+      <c r="BT31" s="28" t="n"/>
+      <c r="BU31" s="25" t="n"/>
+      <c r="BV31" s="29" t="n"/>
+      <c r="BW31" s="24" t="n"/>
+      <c r="BX31" s="30" t="n"/>
+      <c r="BY31" s="27" t="n"/>
+      <c r="BZ31" s="24" t="n"/>
+      <c r="CA31" s="31" t="n"/>
+      <c r="CB31" s="24" t="n"/>
+      <c r="CC31" s="24" t="n"/>
+      <c r="CD31" s="24" t="n"/>
+      <c r="CE31" s="24" t="n"/>
+      <c r="CF31" s="24" t="n"/>
+      <c r="CG31" s="24" t="n"/>
+      <c r="CH31" s="24" t="n"/>
+      <c r="CI31" s="24" t="n"/>
+      <c r="CJ31" s="24" t="n"/>
+      <c r="CK31" s="24" t="n"/>
+      <c r="CL31" s="24" t="n"/>
+      <c r="CM31" s="24" t="n"/>
+      <c r="CN31" s="24" t="n"/>
+      <c r="CO31" s="24" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>999ba6d2f5984911</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>63707</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>UNiTY esports</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.6484839999999999</v>
+      </c>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n">
+        <v>0.048484</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>44</v>
+      </c>
+      <c r="S32" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="n"/>
+      <c r="W32" s="26" t="n"/>
+      <c r="X32" s="26" t="n"/>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n"/>
+      <c r="AA32" s="28" t="n"/>
+      <c r="AB32" s="28" t="n"/>
+      <c r="AC32" s="30" t="n"/>
+      <c r="AD32" s="24" t="n"/>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-erx-unity-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG32" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="inlineStr">
+        <is>
+          <t>UNiTY esports</t>
+        </is>
+      </c>
+      <c r="AQ32" s="24" t="inlineStr">
+        <is>
+          <t>UNiTY esports</t>
+        </is>
+      </c>
+      <c r="AR32" s="24" t="inlineStr">
+        <is>
+          <t>UNiTY esports</t>
+        </is>
+      </c>
+      <c r="AS32" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AT32" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AU32" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA32" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB32" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC32" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD32" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG32" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH32" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:43.912117Z</t>
+        </is>
+      </c>
+      <c r="BI32" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM32" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN32" s="28" t="n"/>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
+      <c r="BR32" s="28" t="n"/>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+      <c r="CB32" s="24" t="n"/>
+      <c r="CC32" s="24" t="n"/>
+      <c r="CD32" s="24" t="n"/>
+      <c r="CE32" s="24" t="n"/>
+      <c r="CF32" s="24" t="n"/>
+      <c r="CG32" s="24" t="n"/>
+      <c r="CH32" s="24" t="n"/>
+      <c r="CI32" s="24" t="n"/>
+      <c r="CJ32" s="24" t="n"/>
+      <c r="CK32" s="24" t="n"/>
+      <c r="CL32" s="24" t="n"/>
+      <c r="CM32" s="24" t="n"/>
+      <c r="CN32" s="24" t="n"/>
+      <c r="CO32" s="24" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>7b476b8e853b4e29</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>63360</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <v>0.53791</v>
+      </c>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n">
+        <v>0.057141</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>49</v>
+      </c>
+      <c r="S33" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U33" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="n"/>
+      <c r="W33" s="26" t="n"/>
+      <c r="X33" s="26" t="n"/>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="26" t="n"/>
+      <c r="AA33" s="28" t="n"/>
+      <c r="AB33" s="28" t="n"/>
+      <c r="AC33" s="30" t="n"/>
+      <c r="AD33" s="24" t="n"/>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-btf-jpu-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG33" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="31" t="n"/>
+      <c r="AK33" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN33" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP33" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AQ33" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AR33" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AS33" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AT33" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AU33" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AV33" s="24" t="n"/>
+      <c r="AW33" s="24" t="n"/>
+      <c r="AX33" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY33" s="24" t="n"/>
+      <c r="AZ33" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA33" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB33" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC33" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD33" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG33" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH33" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:45.363088Z</t>
+        </is>
+      </c>
+      <c r="BI33" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ33" s="25" t="n"/>
+      <c r="BK33" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL33" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM33" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN33" s="28" t="n"/>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
+      <c r="BR33" s="28" t="n"/>
+      <c r="BS33" s="28" t="n"/>
+      <c r="BT33" s="28" t="n"/>
+      <c r="BU33" s="25" t="n"/>
+      <c r="BV33" s="29" t="n"/>
+      <c r="BW33" s="24" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
+      <c r="BZ33" s="24" t="n"/>
+      <c r="CA33" s="31" t="n"/>
+      <c r="CB33" s="24" t="n"/>
+      <c r="CC33" s="24" t="n"/>
+      <c r="CD33" s="24" t="n"/>
+      <c r="CE33" s="24" t="n"/>
+      <c r="CF33" s="24" t="n"/>
+      <c r="CG33" s="24" t="n"/>
+      <c r="CH33" s="24" t="n"/>
+      <c r="CI33" s="24" t="n"/>
+      <c r="CJ33" s="24" t="n"/>
+      <c r="CK33" s="24" t="n"/>
+      <c r="CL33" s="24" t="n"/>
+      <c r="CM33" s="24" t="n"/>
+      <c r="CN33" s="24" t="n"/>
+      <c r="CO33" s="24" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>4dedd6963b9c4ebd</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>63362</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <v>0.548241</v>
+      </c>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n">
+        <v>0.107712</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="S34" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U34" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="n"/>
+      <c r="W34" s="26" t="n"/>
+      <c r="X34" s="26" t="n"/>
+      <c r="Y34" s="25" t="n"/>
+      <c r="Z34" s="26" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="30" t="n"/>
+      <c r="AD34" s="24" t="n"/>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-sparta-g2a-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG34" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH34" s="24" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM34" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN34" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO34" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP34" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="AQ34" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="AR34" s="24" t="inlineStr">
+        <is>
+          <t>G2 Ares</t>
+        </is>
+      </c>
+      <c r="AS34" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AT34" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AU34" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AV34" s="24" t="n"/>
+      <c r="AW34" s="24" t="n"/>
+      <c r="AX34" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY34" s="24" t="n"/>
+      <c r="AZ34" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA34" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB34" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC34" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD34" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG34" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH34" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:47.940507Z</t>
+        </is>
+      </c>
+      <c r="BI34" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ34" s="25" t="n"/>
+      <c r="BK34" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL34" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM34" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN34" s="28" t="n"/>
+      <c r="BO34" s="28" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
+      <c r="BR34" s="28" t="n"/>
+      <c r="BS34" s="28" t="n"/>
+      <c r="BT34" s="28" t="n"/>
+      <c r="BU34" s="25" t="n"/>
+      <c r="BV34" s="29" t="n"/>
+      <c r="BW34" s="24" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
+      <c r="BZ34" s="24" t="n"/>
+      <c r="CA34" s="31" t="n"/>
+      <c r="CB34" s="24" t="n"/>
+      <c r="CC34" s="24" t="n"/>
+      <c r="CD34" s="24" t="n"/>
+      <c r="CE34" s="24" t="n"/>
+      <c r="CF34" s="24" t="n"/>
+      <c r="CG34" s="24" t="n"/>
+      <c r="CH34" s="24" t="n"/>
+      <c r="CI34" s="24" t="n"/>
+      <c r="CJ34" s="24" t="n"/>
+      <c r="CK34" s="24" t="n"/>
+      <c r="CL34" s="24" t="n"/>
+      <c r="CM34" s="24" t="n"/>
+      <c r="CN34" s="24" t="n"/>
+      <c r="CO34" s="24" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>b76147fdbe3547e4</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>63363</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>Lavked</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>CYBERSHOKE Prospects</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N35" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="O35" s="28" t="n">
+        <v>0.553566</v>
+      </c>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n">
+        <v>0.084082</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S35" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U35" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V35" s="24" t="n"/>
+      <c r="W35" s="26" t="n"/>
+      <c r="X35" s="26" t="n"/>
+      <c r="Y35" s="25" t="n"/>
+      <c r="Z35" s="26" t="n"/>
+      <c r="AA35" s="28" t="n"/>
+      <c r="AB35" s="28" t="n"/>
+      <c r="AC35" s="30" t="n"/>
+      <c r="AD35" s="24" t="n"/>
+      <c r="AE35" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-cshp-lav-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF35" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG35" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="31" t="n"/>
+      <c r="AJ35" s="31" t="n"/>
+      <c r="AK35" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM35" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN35" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO35" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP35" s="24" t="inlineStr">
+        <is>
+          <t>Lavked</t>
+        </is>
+      </c>
+      <c r="AQ35" s="24" t="inlineStr">
+        <is>
+          <t>Lavked</t>
+        </is>
+      </c>
+      <c r="AR35" s="24" t="inlineStr">
+        <is>
+          <t>Lavked</t>
+        </is>
+      </c>
+      <c r="AS35" s="24" t="inlineStr">
+        <is>
+          <t>CYBERSHOKE Prospects</t>
+        </is>
+      </c>
+      <c r="AT35" s="24" t="inlineStr">
+        <is>
+          <t>CYBERSHOKE Prospects</t>
+        </is>
+      </c>
+      <c r="AU35" s="24" t="inlineStr">
+        <is>
+          <t>CYBERSHOKE Prospects</t>
+        </is>
+      </c>
+      <c r="AV35" s="24" t="n"/>
+      <c r="AW35" s="24" t="n"/>
+      <c r="AX35" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY35" s="24" t="n"/>
+      <c r="AZ35" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA35" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB35" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC35" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD35" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG35" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH35" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:49.411771Z</t>
+        </is>
+      </c>
+      <c r="BI35" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ35" s="25" t="n"/>
+      <c r="BK35" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="BL35" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM35" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="BN35" s="28" t="n"/>
+      <c r="BO35" s="28" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
+      <c r="BR35" s="28" t="n"/>
+      <c r="BS35" s="28" t="n"/>
+      <c r="BT35" s="28" t="n"/>
+      <c r="BU35" s="25" t="n"/>
+      <c r="BV35" s="29" t="n"/>
+      <c r="BW35" s="24" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
+      <c r="BZ35" s="24" t="n"/>
+      <c r="CA35" s="31" t="n"/>
+      <c r="CB35" s="24" t="n"/>
+      <c r="CC35" s="24" t="n"/>
+      <c r="CD35" s="24" t="n"/>
+      <c r="CE35" s="24" t="n"/>
+      <c r="CF35" s="24" t="n"/>
+      <c r="CG35" s="24" t="n"/>
+      <c r="CH35" s="24" t="n"/>
+      <c r="CI35" s="24" t="n"/>
+      <c r="CJ35" s="24" t="n"/>
+      <c r="CK35" s="24" t="n"/>
+      <c r="CL35" s="24" t="n"/>
+      <c r="CM35" s="24" t="n"/>
+      <c r="CN35" s="24" t="n"/>
+      <c r="CO35" s="24" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>e38e6b2beb2f4bef</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>63311</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>UNiTY esports</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <v>0.536588</v>
+      </c>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n">
+        <v>0.166218</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S36" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U36" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="n"/>
+      <c r="W36" s="26" t="n"/>
+      <c r="X36" s="26" t="n"/>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="26" t="n"/>
+      <c r="AA36" s="28" t="n"/>
+      <c r="AB36" s="28" t="n"/>
+      <c r="AC36" s="30" t="n"/>
+      <c r="AD36" s="24" t="n"/>
+      <c r="AE36" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-cs2-lk-unity-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF36" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG36" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="31" t="n"/>
+      <c r="AK36" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN36" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO36" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP36" s="24" t="inlineStr">
+        <is>
+          <t>UNiTY esports</t>
+        </is>
+      </c>
+      <c r="AQ36" s="24" t="inlineStr">
+        <is>
+          <t>UNiTY esports</t>
+        </is>
+      </c>
+      <c r="AR36" s="24" t="inlineStr">
+        <is>
+          <t>UNiTY esports</t>
+        </is>
+      </c>
+      <c r="AS36" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="AT36" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="AU36" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="AV36" s="24" t="n"/>
+      <c r="AW36" s="24" t="n"/>
+      <c r="AX36" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY36" s="24" t="n"/>
+      <c r="AZ36" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA36" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB36" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC36" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD36" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG36" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH36" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:49.932343Z</t>
+        </is>
+      </c>
+      <c r="BI36" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ36" s="25" t="n"/>
+      <c r="BK36" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="BL36" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BM36" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="BN36" s="28" t="n"/>
+      <c r="BO36" s="28" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
+      <c r="BR36" s="28" t="n"/>
+      <c r="BS36" s="28" t="n"/>
+      <c r="BT36" s="28" t="n"/>
+      <c r="BU36" s="25" t="n"/>
+      <c r="BV36" s="29" t="n"/>
+      <c r="BW36" s="24" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
+      <c r="BZ36" s="24" t="n"/>
+      <c r="CA36" s="31" t="n"/>
+      <c r="CB36" s="24" t="n"/>
+      <c r="CC36" s="24" t="n"/>
+      <c r="CD36" s="24" t="n"/>
+      <c r="CE36" s="24" t="n"/>
+      <c r="CF36" s="24" t="n"/>
+      <c r="CG36" s="24" t="n"/>
+      <c r="CH36" s="24" t="n"/>
+      <c r="CI36" s="24" t="n"/>
+      <c r="CJ36" s="24" t="n"/>
+      <c r="CK36" s="24" t="n"/>
+      <c r="CL36" s="24" t="n"/>
+      <c r="CM36" s="24" t="n"/>
+      <c r="CN36" s="24" t="n"/>
+      <c r="CO36" s="24" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>4710a7b97eb84e81</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>64369</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>Falcons Force</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N37" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O37" s="28" t="n">
+        <v>0.5211479999999999</v>
+      </c>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="28" t="n">
+        <v>0.021148</v>
+      </c>
+      <c r="R37" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S37" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U37" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="n"/>
+      <c r="W37" s="26" t="n"/>
+      <c r="X37" s="26" t="n"/>
+      <c r="Y37" s="25" t="n"/>
+      <c r="Z37" s="26" t="n"/>
+      <c r="AA37" s="28" t="n"/>
+      <c r="AB37" s="28" t="n"/>
+      <c r="AC37" s="30" t="n"/>
+      <c r="AD37" s="24" t="n"/>
+      <c r="AE37" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-misa-falf-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF37" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG37" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH37" s="24" t="n"/>
+      <c r="AI37" s="31" t="n"/>
+      <c r="AJ37" s="31" t="n"/>
+      <c r="AK37" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL37" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM37" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN37" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO37" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP37" s="24" t="inlineStr">
+        <is>
+          <t>Falcons Force</t>
+        </is>
+      </c>
+      <c r="AQ37" s="24" t="inlineStr">
+        <is>
+          <t>Falcons Force</t>
+        </is>
+      </c>
+      <c r="AR37" s="24" t="inlineStr">
+        <is>
+          <t>Falcons Force</t>
+        </is>
+      </c>
+      <c r="AS37" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="AT37" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="AU37" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="AV37" s="24" t="n"/>
+      <c r="AW37" s="24" t="n"/>
+      <c r="AX37" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY37" s="24" t="n"/>
+      <c r="AZ37" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA37" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB37" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC37" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD37" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG37" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH37" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:50.504855Z</t>
+        </is>
+      </c>
+      <c r="BI37" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ37" s="25" t="n"/>
+      <c r="BK37" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL37" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM37" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN37" s="28" t="n"/>
+      <c r="BO37" s="28" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
+      <c r="BR37" s="28" t="n"/>
+      <c r="BS37" s="28" t="n"/>
+      <c r="BT37" s="28" t="n"/>
+      <c r="BU37" s="25" t="n"/>
+      <c r="BV37" s="29" t="n"/>
+      <c r="BW37" s="24" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
+      <c r="BZ37" s="24" t="n"/>
+      <c r="CA37" s="31" t="n"/>
+      <c r="CB37" s="24" t="n"/>
+      <c r="CC37" s="24" t="n"/>
+      <c r="CD37" s="24" t="n"/>
+      <c r="CE37" s="24" t="n"/>
+      <c r="CF37" s="24" t="n"/>
+      <c r="CG37" s="24" t="n"/>
+      <c r="CH37" s="24" t="n"/>
+      <c r="CI37" s="24" t="n"/>
+      <c r="CJ37" s="24" t="n"/>
+      <c r="CK37" s="24" t="n"/>
+      <c r="CL37" s="24" t="n"/>
+      <c r="CM37" s="24" t="n"/>
+      <c r="CN37" s="24" t="n"/>
+      <c r="CO37" s="24" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>bbcd2c2ef81f4286</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>61708</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>largadosypelados</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>Bounty Hunters Esports</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N38" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O38" s="28" t="n">
+        <v>0.730996</v>
+      </c>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n">
+        <v>0.250227</v>
+      </c>
+      <c r="R38" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S38" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U38" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="n"/>
+      <c r="W38" s="26" t="n"/>
+      <c r="X38" s="26" t="n"/>
+      <c r="Y38" s="25" t="n"/>
+      <c r="Z38" s="26" t="n"/>
+      <c r="AA38" s="28" t="n"/>
+      <c r="AB38" s="28" t="n"/>
+      <c r="AC38" s="30" t="n"/>
+      <c r="AD38" s="24" t="n"/>
+      <c r="AE38" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-bhe-ldp-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF38" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG38" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH38" s="24" t="n"/>
+      <c r="AI38" s="31" t="n"/>
+      <c r="AJ38" s="31" t="n"/>
+      <c r="AK38" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM38" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN38" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO38" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP38" s="24" t="inlineStr">
+        <is>
+          <t>largadosypelados</t>
+        </is>
+      </c>
+      <c r="AQ38" s="24" t="inlineStr">
+        <is>
+          <t>largadosypelados</t>
+        </is>
+      </c>
+      <c r="AR38" s="24" t="inlineStr">
+        <is>
+          <t>largadosypelados</t>
+        </is>
+      </c>
+      <c r="AS38" s="24" t="inlineStr">
+        <is>
+          <t>Bounty Hunters Esports</t>
+        </is>
+      </c>
+      <c r="AT38" s="24" t="inlineStr">
+        <is>
+          <t>Bounty Hunters Esports</t>
+        </is>
+      </c>
+      <c r="AU38" s="24" t="inlineStr">
+        <is>
+          <t>Bounty Hunters Esports</t>
+        </is>
+      </c>
+      <c r="AV38" s="24" t="n"/>
+      <c r="AW38" s="24" t="n"/>
+      <c r="AX38" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY38" s="24" t="n"/>
+      <c r="AZ38" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA38" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB38" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC38" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD38" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG38" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH38" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:51.025834Z</t>
+        </is>
+      </c>
+      <c r="BI38" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ38" s="25" t="n"/>
+      <c r="BK38" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL38" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM38" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN38" s="28" t="n"/>
+      <c r="BO38" s="28" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
+      <c r="BR38" s="28" t="n"/>
+      <c r="BS38" s="28" t="n"/>
+      <c r="BT38" s="28" t="n"/>
+      <c r="BU38" s="25" t="n"/>
+      <c r="BV38" s="29" t="n"/>
+      <c r="BW38" s="24" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
+      <c r="BZ38" s="24" t="n"/>
+      <c r="CA38" s="31" t="n"/>
+      <c r="CB38" s="24" t="n"/>
+      <c r="CC38" s="24" t="n"/>
+      <c r="CD38" s="24" t="n"/>
+      <c r="CE38" s="24" t="n"/>
+      <c r="CF38" s="24" t="n"/>
+      <c r="CG38" s="24" t="n"/>
+      <c r="CH38" s="24" t="n"/>
+      <c r="CI38" s="24" t="n"/>
+      <c r="CJ38" s="24" t="n"/>
+      <c r="CK38" s="24" t="n"/>
+      <c r="CL38" s="24" t="n"/>
+      <c r="CM38" s="24" t="n"/>
+      <c r="CN38" s="24" t="n"/>
+      <c r="CO38" s="24" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>1ef28cef3128445f</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>62235</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>QUINTESSÊNCIA</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>ALKA GAMING</t>
+        </is>
+      </c>
+      <c r="H39" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J39" s="25" t="n"/>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L39" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M39" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N39" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O39" s="28" t="n">
+        <v>0.690487</v>
+      </c>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="28" t="n">
+        <v>8.500000000000001e-05</v>
+      </c>
+      <c r="R39" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="S39" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U39" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V39" s="24" t="n"/>
+      <c r="W39" s="26" t="n"/>
+      <c r="X39" s="26" t="n"/>
+      <c r="Y39" s="25" t="n"/>
+      <c r="Z39" s="26" t="n"/>
+      <c r="AA39" s="28" t="n"/>
+      <c r="AB39" s="28" t="n"/>
+      <c r="AC39" s="30" t="n"/>
+      <c r="AD39" s="24" t="n"/>
+      <c r="AE39" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-alka-quin-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF39" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG39" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH39" s="24" t="n"/>
+      <c r="AI39" s="31" t="n"/>
+      <c r="AJ39" s="31" t="n"/>
+      <c r="AK39" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL39" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM39" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN39" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO39" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP39" s="24" t="inlineStr">
+        <is>
+          <t>QUINTESSÊNCIA</t>
+        </is>
+      </c>
+      <c r="AQ39" s="24" t="inlineStr">
+        <is>
+          <t>QUINTESSÊNCIA</t>
+        </is>
+      </c>
+      <c r="AR39" s="24" t="inlineStr">
+        <is>
+          <t>QUINTESSÊNCIA</t>
+        </is>
+      </c>
+      <c r="AS39" s="24" t="inlineStr">
+        <is>
+          <t>ALKA GAMING</t>
+        </is>
+      </c>
+      <c r="AT39" s="24" t="inlineStr">
+        <is>
+          <t>ALKA GAMING</t>
+        </is>
+      </c>
+      <c r="AU39" s="24" t="inlineStr">
+        <is>
+          <t>ALKA GAMING</t>
+        </is>
+      </c>
+      <c r="AV39" s="24" t="n"/>
+      <c r="AW39" s="24" t="n"/>
+      <c r="AX39" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY39" s="24" t="n"/>
+      <c r="AZ39" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA39" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB39" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC39" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD39" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG39" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH39" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T01:59:59.872308Z</t>
+        </is>
+      </c>
+      <c r="BI39" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ39" s="25" t="n"/>
+      <c r="BK39" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL39" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM39" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN39" s="28" t="n"/>
+      <c r="BO39" s="28" t="n"/>
+      <c r="BP39" s="25" t="n"/>
+      <c r="BQ39" s="27" t="n"/>
+      <c r="BR39" s="28" t="n"/>
+      <c r="BS39" s="28" t="n"/>
+      <c r="BT39" s="28" t="n"/>
+      <c r="BU39" s="25" t="n"/>
+      <c r="BV39" s="29" t="n"/>
+      <c r="BW39" s="24" t="n"/>
+      <c r="BX39" s="30" t="n"/>
+      <c r="BY39" s="27" t="n"/>
+      <c r="BZ39" s="24" t="n"/>
+      <c r="CA39" s="31" t="n"/>
+      <c r="CB39" s="24" t="n"/>
+      <c r="CC39" s="24" t="n"/>
+      <c r="CD39" s="24" t="n"/>
+      <c r="CE39" s="24" t="n"/>
+      <c r="CF39" s="24" t="n"/>
+      <c r="CG39" s="24" t="n"/>
+      <c r="CH39" s="24" t="n"/>
+      <c r="CI39" s="24" t="n"/>
+      <c r="CJ39" s="24" t="n"/>
+      <c r="CK39" s="24" t="n"/>
+      <c r="CL39" s="24" t="n"/>
+      <c r="CM39" s="24" t="n"/>
+      <c r="CN39" s="24" t="n"/>
+      <c r="CO39" s="24" t="n"/>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>62843cbec2364d66</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>62236</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>Imperial</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I40" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J40" s="25" t="n"/>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L40" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M40" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N40" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O40" s="28" t="n">
+        <v>0.526234</v>
+      </c>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="28" t="n">
+        <v>-0.044581</v>
+      </c>
+      <c r="R40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U40" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V40" s="24" t="n"/>
+      <c r="W40" s="26" t="n"/>
+      <c r="X40" s="26" t="n"/>
+      <c r="Y40" s="25" t="n"/>
+      <c r="Z40" s="26" t="n"/>
+      <c r="AA40" s="28" t="n"/>
+      <c r="AB40" s="28" t="n"/>
+      <c r="AC40" s="30" t="n"/>
+      <c r="AD40" s="24" t="n"/>
+      <c r="AE40" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-imp-bst-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF40" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG40" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH40" s="24" t="n"/>
+      <c r="AI40" s="31" t="n"/>
+      <c r="AJ40" s="31" t="n"/>
+      <c r="AK40" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL40" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM40" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN40" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO40" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP40" s="24" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="AQ40" s="24" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="AR40" s="24" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="AS40" s="24" t="inlineStr">
+        <is>
+          <t>Imperial</t>
+        </is>
+      </c>
+      <c r="AT40" s="24" t="inlineStr">
+        <is>
+          <t>Imperial</t>
+        </is>
+      </c>
+      <c r="AU40" s="24" t="inlineStr">
+        <is>
+          <t>Imperial</t>
+        </is>
+      </c>
+      <c r="AV40" s="24" t="n"/>
+      <c r="AW40" s="24" t="n"/>
+      <c r="AX40" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY40" s="24" t="n"/>
+      <c r="AZ40" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA40" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB40" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC40" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD40" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE40" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF40" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG40" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH40" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:00.381650Z</t>
+        </is>
+      </c>
+      <c r="BI40" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ40" s="25" t="n"/>
+      <c r="BK40" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL40" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM40" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN40" s="28" t="n"/>
+      <c r="BO40" s="28" t="n"/>
+      <c r="BP40" s="25" t="n"/>
+      <c r="BQ40" s="27" t="n"/>
+      <c r="BR40" s="28" t="n"/>
+      <c r="BS40" s="28" t="n"/>
+      <c r="BT40" s="28" t="n"/>
+      <c r="BU40" s="25" t="n"/>
+      <c r="BV40" s="29" t="n"/>
+      <c r="BW40" s="24" t="n"/>
+      <c r="BX40" s="30" t="n"/>
+      <c r="BY40" s="27" t="n"/>
+      <c r="BZ40" s="24" t="n"/>
+      <c r="CA40" s="31" t="n"/>
+      <c r="CB40" s="24" t="n"/>
+      <c r="CC40" s="24" t="n"/>
+      <c r="CD40" s="24" t="n"/>
+      <c r="CE40" s="24" t="n"/>
+      <c r="CF40" s="24" t="n"/>
+      <c r="CG40" s="24" t="n"/>
+      <c r="CH40" s="24" t="n"/>
+      <c r="CI40" s="24" t="n"/>
+      <c r="CJ40" s="24" t="n"/>
+      <c r="CK40" s="24" t="n"/>
+      <c r="CL40" s="24" t="n"/>
+      <c r="CM40" s="24" t="n"/>
+      <c r="CN40" s="24" t="n"/>
+      <c r="CO40" s="24" t="n"/>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>2e1b6c7ba1ed46a9</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:01.501477Z</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T22:00:00Z</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>62282</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>Marsborne</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>LAG Gaming</t>
+        </is>
+      </c>
+      <c r="H41" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I41" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J41" s="25" t="n"/>
+      <c r="K41" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M41" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N41" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O41" s="28" t="n">
+        <v>0.585167</v>
+      </c>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="28" t="n">
+        <v>-0.024208</v>
+      </c>
+      <c r="R41" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="S41" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U41" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V41" s="24" t="n"/>
+      <c r="W41" s="26" t="n"/>
+      <c r="X41" s="26" t="n"/>
+      <c r="Y41" s="25" t="n"/>
+      <c r="Z41" s="26" t="n"/>
+      <c r="AA41" s="28" t="n"/>
+      <c r="AB41" s="28" t="n"/>
+      <c r="AC41" s="30" t="n"/>
+      <c r="AD41" s="24" t="n"/>
+      <c r="AE41" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-lag-mars-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF41" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG41" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH41" s="24" t="n"/>
+      <c r="AI41" s="31" t="n"/>
+      <c r="AJ41" s="31" t="n"/>
+      <c r="AK41" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL41" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM41" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN41" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO41" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP41" s="24" t="inlineStr">
+        <is>
+          <t>Marsborne</t>
+        </is>
+      </c>
+      <c r="AQ41" s="24" t="inlineStr">
+        <is>
+          <t>Marsborne</t>
+        </is>
+      </c>
+      <c r="AR41" s="24" t="inlineStr">
+        <is>
+          <t>Marsborne</t>
+        </is>
+      </c>
+      <c r="AS41" s="24" t="inlineStr">
+        <is>
+          <t>LAG Gaming</t>
+        </is>
+      </c>
+      <c r="AT41" s="24" t="inlineStr">
+        <is>
+          <t>LAG Gaming</t>
+        </is>
+      </c>
+      <c r="AU41" s="24" t="inlineStr">
+        <is>
+          <t>LAG Gaming</t>
+        </is>
+      </c>
+      <c r="AV41" s="24" t="n"/>
+      <c r="AW41" s="24" t="n"/>
+      <c r="AX41" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY41" s="24" t="n"/>
+      <c r="AZ41" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA41" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BB41" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC41" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD41" s="24" t="inlineStr">
+        <is>
+          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+        </is>
+      </c>
+      <c r="BE41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG41" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH41" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:00:00.888591Z</t>
+        </is>
+      </c>
+      <c r="BI41" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ41" s="25" t="n"/>
+      <c r="BK41" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL41" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM41" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN41" s="28" t="n"/>
+      <c r="BO41" s="28" t="n"/>
+      <c r="BP41" s="25" t="n"/>
+      <c r="BQ41" s="27" t="n"/>
+      <c r="BR41" s="28" t="n"/>
+      <c r="BS41" s="28" t="n"/>
+      <c r="BT41" s="28" t="n"/>
+      <c r="BU41" s="25" t="n"/>
+      <c r="BV41" s="29" t="n"/>
+      <c r="BW41" s="24" t="n"/>
+      <c r="BX41" s="30" t="n"/>
+      <c r="BY41" s="27" t="n"/>
+      <c r="BZ41" s="24" t="n"/>
+      <c r="CA41" s="31" t="n"/>
+      <c r="CB41" s="24" t="n"/>
+      <c r="CC41" s="24" t="n"/>
+      <c r="CD41" s="24" t="n"/>
+      <c r="CE41" s="24" t="n"/>
+      <c r="CF41" s="24" t="n"/>
+      <c r="CG41" s="24" t="n"/>
+      <c r="CH41" s="24" t="n"/>
+      <c r="CI41" s="24" t="n"/>
+      <c r="CJ41" s="24" t="n"/>
+      <c r="CK41" s="24" t="n"/>
+      <c r="CL41" s="24" t="n"/>
+      <c r="CM41" s="24" t="n"/>
+      <c r="CN41" s="24" t="n"/>
+      <c r="CO41" s="24" t="n"/>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>f1c4fd97f35b453f</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:08:42.519814Z</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>63706</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>Mai Tai</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>Entropy</t>
+        </is>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M42" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N42" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O42" s="28" t="n">
+        <v>0.609287</v>
+      </c>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="28" t="n">
+        <v>0.029455</v>
+      </c>
+      <c r="R42" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="S42" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T42" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U42" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V42" s="24" t="n"/>
+      <c r="W42" s="26" t="n"/>
+      <c r="X42" s="26" t="n"/>
+      <c r="Y42" s="25" t="n"/>
+      <c r="Z42" s="26" t="n"/>
+      <c r="AA42" s="28" t="n"/>
+      <c r="AB42" s="28" t="n"/>
+      <c r="AC42" s="30" t="n"/>
+      <c r="AD42" s="24" t="n"/>
+      <c r="AE42" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-ent-mta-2026-07-28).</t>
+        </is>
+      </c>
+      <c r="AF42" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG42" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH42" s="24" t="n"/>
+      <c r="AI42" s="31" t="n"/>
+      <c r="AJ42" s="31" t="n"/>
+      <c r="AK42" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM42" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN42" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO42" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP42" s="24" t="inlineStr">
+        <is>
+          <t>Mai Tai</t>
+        </is>
+      </c>
+      <c r="AQ42" s="24" t="inlineStr">
+        <is>
+          <t>Mai Tai</t>
+        </is>
+      </c>
+      <c r="AR42" s="24" t="inlineStr">
+        <is>
+          <t>Mai Tai</t>
+        </is>
+      </c>
+      <c r="AS42" s="24" t="inlineStr">
+        <is>
+          <t>Entropy</t>
+        </is>
+      </c>
+      <c r="AT42" s="24" t="inlineStr">
+        <is>
+          <t>Entropy</t>
+        </is>
+      </c>
+      <c r="AU42" s="24" t="inlineStr">
+        <is>
+          <t>Entropy</t>
+        </is>
+      </c>
+      <c r="AV42" s="24" t="n"/>
+      <c r="AW42" s="24" t="n"/>
+      <c r="AX42" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY42" s="24" t="n"/>
+      <c r="AZ42" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA42" s="24" t="inlineStr">
+        <is>
+          <t>083967481304d1dc27bfb10e14bb394ac08ceeda4b7f4e87080bc0131a2aed37</t>
+        </is>
+      </c>
+      <c r="BB42" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC42" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD42" s="24" t="inlineStr">
+        <is>
+          <t>083967481304d1dc27bfb10e14bb394ac08ceeda4b7f4e87080bc0131a2aed37</t>
+        </is>
+      </c>
+      <c r="BE42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG42" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH42" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T02:08:19.728443Z</t>
+        </is>
+      </c>
+      <c r="BI42" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ42" s="25" t="n"/>
+      <c r="BK42" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL42" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM42" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN42" s="28" t="n"/>
+      <c r="BO42" s="28" t="n"/>
+      <c r="BP42" s="25" t="n"/>
+      <c r="BQ42" s="27" t="n"/>
+      <c r="BR42" s="28" t="n"/>
+      <c r="BS42" s="28" t="n"/>
+      <c r="BT42" s="28" t="n"/>
+      <c r="BU42" s="25" t="n"/>
+      <c r="BV42" s="29" t="n"/>
+      <c r="BW42" s="24" t="n"/>
+      <c r="BX42" s="30" t="n"/>
+      <c r="BY42" s="27" t="n"/>
+      <c r="BZ42" s="24" t="n"/>
+      <c r="CA42" s="31" t="n"/>
+      <c r="CB42" s="24" t="n"/>
+      <c r="CC42" s="24" t="n"/>
+      <c r="CD42" s="24" t="n"/>
+      <c r="CE42" s="24" t="n"/>
+      <c r="CF42" s="24" t="n"/>
+      <c r="CG42" s="24" t="n"/>
+      <c r="CH42" s="24" t="n"/>
+      <c r="CI42" s="24" t="n"/>
+      <c r="CJ42" s="24" t="n"/>
+      <c r="CK42" s="24" t="n"/>
+      <c r="CL42" s="24" t="n"/>
+      <c r="CM42" s="24" t="n"/>
+      <c r="CN42" s="24" t="n"/>
+      <c r="CO42" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO42" headerRowCount="1">
-  <autoFilter ref="A1:CO42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO35" headerRowCount="1">
+  <autoFilter ref="A1:CO35"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$42)</f>
+        <f>COUNTA('Picks'!$A$2:$A$35)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$42,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$35,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$42,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$35,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$42,"settled",'Picks'!$V$2:$V$42,"win")+COUNTIFS('Picks'!$U$2:$U$42,"settled",'Picks'!$V$2:$V$42,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"win")+COUNTIFS('Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$42,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$35,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$42,"&gt;0",'Picks'!$V$2:$V$42,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$42,"&gt;0",'Picks'!$V$2:$V$42,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$42,"&gt;0",'Picks'!$V$2:$V$42,"win")/(COUNTIFS('Picks'!$BX$2:$BX$42,"&gt;0",'Picks'!$V$2:$V$42,"win")+COUNTIFS('Picks'!$BX$2:$BX$42,"&gt;0",'Picks'!$V$2:$V$42,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"win")/(COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"win")+COUNTIFS('Picks'!$BX$2:$BX$35,"&gt;0",'Picks'!$V$2:$V$35,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$42)/SUM('Picks'!$BX$2:$BX$42),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$35)/SUM('Picks'!$BX$2:$BX$35),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$42)</f>
+        <f>SUM('Picks'!$BY$2:$BY$35)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$42,"&lt;&gt;",'Picks'!$AB$2:$AB$42),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$35,"&lt;&gt;",'Picks'!$AB$2:$AB$35),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$42,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$42,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$35,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$35,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$42,'Picks'!$AM$2:$AM$42,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$35,'Picks'!$AM$2:$AM$35,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$42,$A14,'Picks'!$U$2:$U$42,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A14,'Picks'!$U$2:$U$35,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$42,$A14,'Picks'!$U$2:$U$42,"settled",'Picks'!$V$2:$V$42,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A14,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$42,$A14,'Picks'!$U$2:$U$42,"settled",'Picks'!$V$2:$V$42,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A14,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$42,'Picks'!$H$2:$H$42,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$35,'Picks'!$H$2:$H$35,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$42,'Picks'!$H$2:$H$42,$A14,'Picks'!$U$2:$U$42,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$35,'Picks'!$H$2:$H$35,$A14,'Picks'!$U$2:$U$35,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$42,$A15,'Picks'!$U$2:$U$42,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A15,'Picks'!$U$2:$U$35,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$42,$A15,'Picks'!$U$2:$U$42,"settled",'Picks'!$V$2:$V$42,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A15,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$42,$A15,'Picks'!$U$2:$U$42,"settled",'Picks'!$V$2:$V$42,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A15,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$42,'Picks'!$H$2:$H$42,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$35,'Picks'!$H$2:$H$35,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$42,'Picks'!$H$2:$H$42,$A15,'Picks'!$U$2:$U$42,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$35,'Picks'!$H$2:$H$35,$A15,'Picks'!$U$2:$U$35,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$42,$A16,'Picks'!$U$2:$U$42,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A16,'Picks'!$U$2:$U$35,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$42,$A16,'Picks'!$U$2:$U$42,"settled",'Picks'!$V$2:$V$42,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A16,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$42,$A16,'Picks'!$U$2:$U$42,"settled",'Picks'!$V$2:$V$42,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$35,$A16,'Picks'!$U$2:$U$35,"settled",'Picks'!$V$2:$V$35,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$42,'Picks'!$H$2:$H$42,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$35,'Picks'!$H$2:$H$35,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$42,'Picks'!$H$2:$H$42,$A16,'Picks'!$U$2:$U$42,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$35,'Picks'!$H$2:$H$35,$A16,'Picks'!$U$2:$U$35,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO42"/>
+  <dimension ref="A1:CO35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7632,12 +7632,12 @@
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>d7ae167da1244103</t>
+          <t>93b5f70c558b45c0</t>
         </is>
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T05:05:50.168792Z</t>
         </is>
       </c>
       <c r="C24" s="24" t="inlineStr">
@@ -7682,20 +7682,20 @@
         </is>
       </c>
       <c r="L24" s="26" t="n">
-        <v>-194</v>
+        <v>-203</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.492611</v>
       </c>
       <c r="N24" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.669967</v>
       </c>
       <c r="O24" s="28" t="n">
         <v>0.582559</v>
       </c>
       <c r="P24" s="28" t="n"/>
       <c r="Q24" s="28" t="n">
-        <v>-0.077305</v>
+        <v>-0.087408</v>
       </c>
       <c r="R24" s="26" t="n">
         <v>0</v>
@@ -7710,21 +7710,35 @@
       </c>
       <c r="U24" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V24" s="24" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y24" s="25" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n"/>
-      <c r="AD24" s="24" t="n"/>
+      <c r="AC24" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:12:25.605160Z</t>
+        </is>
+      </c>
       <c r="AE24" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-33-hon-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-33-hon-2026-07-28).</t>
         </is>
       </c>
       <c r="AF24" s="31" t="inlineStr">
@@ -7808,7 +7822,7 @@
       </c>
       <c r="BA24" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>40c2937bc668bb862cf7af94b4e50bd7f49459da4b5b52e8a268f7bbef6d0377</t>
         </is>
       </c>
       <c r="BB24" s="24" t="inlineStr">
@@ -7823,7 +7837,7 @@
       </c>
       <c r="BD24" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>40c2937bc668bb862cf7af94b4e50bd7f49459da4b5b52e8a268f7bbef6d0377</t>
         </is>
       </c>
       <c r="BE24" s="24" t="inlineStr">
@@ -7843,7 +7857,7 @@
       </c>
       <c r="BH24" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:39.276046Z</t>
+          <t>2026-07-28T05:05:25.239075Z</t>
         </is>
       </c>
       <c r="BI24" s="24" t="inlineStr">
@@ -7853,13 +7867,13 @@
       </c>
       <c r="BJ24" s="25" t="n"/>
       <c r="BK24" s="26" t="n">
-        <v>-194</v>
+        <v>-203</v>
       </c>
       <c r="BL24" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.492611</v>
       </c>
       <c r="BM24" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.669967</v>
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
@@ -7893,12 +7907,12 @@
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>c7533602b6d8481c</t>
+          <t>093c354a28414f32</t>
         </is>
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T05:05:50.168792Z</t>
         </is>
       </c>
       <c r="C25" s="24" t="inlineStr">
@@ -7971,18 +7985,32 @@
       </c>
       <c r="U25" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="n"/>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y25" s="25" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n"/>
-      <c r="AD25" s="24" t="n"/>
+      <c r="AC25" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:12:26.880937Z</t>
+        </is>
+      </c>
       <c r="AE25" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-bpl-enjoy-2026-07-28).</t>
@@ -7995,7 +8023,7 @@
       </c>
       <c r="AG25" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH25" s="24" t="n"/>
@@ -8069,7 +8097,7 @@
       </c>
       <c r="BA25" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>40c2937bc668bb862cf7af94b4e50bd7f49459da4b5b52e8a268f7bbef6d0377</t>
         </is>
       </c>
       <c r="BB25" s="24" t="inlineStr">
@@ -8084,7 +8112,7 @@
       </c>
       <c r="BD25" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>40c2937bc668bb862cf7af94b4e50bd7f49459da4b5b52e8a268f7bbef6d0377</t>
         </is>
       </c>
       <c r="BE25" s="24" t="inlineStr">
@@ -8104,7 +8132,7 @@
       </c>
       <c r="BH25" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:39.784703Z</t>
+          <t>2026-07-28T05:05:25.710714Z</t>
         </is>
       </c>
       <c r="BI25" s="24" t="inlineStr">
@@ -8154,22 +8182,22 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>22f0867f90b74019</t>
+          <t>2c82d66aa3c94dc1</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T05:05:50.168792Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T10:00:00Z</t>
+          <t>2026-07-28T08:00:00Z</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>64432</t>
+          <t>63706</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -8179,12 +8207,12 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Entropy</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -8204,26 +8232,26 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>186</v>
+        <v>-144</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>2.86</v>
+        <v>1.694444</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.590164</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.509533</v>
+        <v>0.609287</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>0.159883</v>
+        <v>0.019123</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="S26" s="29" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="T26" s="24" t="inlineStr">
         <is>
@@ -8232,21 +8260,35 @@
       </c>
       <c r="U26" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V26" s="24" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y26" s="25" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n"/>
-      <c r="AD26" s="24" t="n"/>
+      <c r="AC26" s="30" t="n">
+        <v>1.0417</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T11:12:28.150737Z</t>
+        </is>
+      </c>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-cs2-nvo-mouzn-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-ent-mta-2026-07-28).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8287,32 +8329,32 @@
       </c>
       <c r="AP26" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AQ26" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AR26" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AS26" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Entropy</t>
         </is>
       </c>
       <c r="AT26" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Entropy</t>
         </is>
       </c>
       <c r="AU26" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Entropy</t>
         </is>
       </c>
       <c r="AV26" s="24" t="n"/>
@@ -8330,7 +8372,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>40c2937bc668bb862cf7af94b4e50bd7f49459da4b5b52e8a268f7bbef6d0377</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8345,7 +8387,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>40c2937bc668bb862cf7af94b4e50bd7f49459da4b5b52e8a268f7bbef6d0377</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8365,7 +8407,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:40.889369Z</t>
+          <t>2026-07-28T05:05:26.235601Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8375,13 +8417,13 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>186</v>
+        <v>-144</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>2.86</v>
+        <v>1.694444</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.590164</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
@@ -8415,12 +8457,12 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>310d6c4312fd480c</t>
+          <t>4aeb4483162e48f6</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T08:11:54.722189Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
@@ -8465,20 +8507,20 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.561798</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.640288</v>
       </c>
       <c r="O27" s="28" t="n">
         <v>0.580775</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>-0.048855</v>
+        <v>-0.059513</v>
       </c>
       <c r="R27" s="26" t="n">
         <v>0</v>
@@ -8493,21 +8535,35 @@
       </c>
       <c r="U27" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y27" s="25" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n"/>
-      <c r="AD27" s="24" t="n"/>
+      <c r="AC27" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:18:28.305151Z</t>
+        </is>
+      </c>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-astr-navij-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-astr-navij-2026-07-28).</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -8591,7 +8647,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -8606,7 +8662,7 @@
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -8626,7 +8682,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:41.424963Z</t>
+          <t>2026-07-28T08:11:30.924763Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -8636,13 +8692,13 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.561798</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.640288</v>
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
@@ -8676,22 +8732,22 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>b248eb6e992643dc</t>
+          <t>c91d65dba9384013</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T08:11:54.722189Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T11:00:00Z</t>
+          <t>2026-07-28T10:00:00Z</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>63307</t>
+          <t>64432</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
@@ -8701,12 +8757,12 @@
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
-          <t>ex-MANA eSports</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="G28" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr">
@@ -8726,49 +8782,63 @@
         </is>
       </c>
       <c r="L28" s="26" t="n">
-        <v>-223</v>
+        <v>150</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.5</v>
       </c>
       <c r="N28" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.4</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>0.628318</v>
+        <v>0.509533</v>
       </c>
       <c r="P28" s="28" t="n"/>
       <c r="Q28" s="28" t="n">
-        <v>-0.062084</v>
+        <v>0.109533</v>
       </c>
       <c r="R28" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S28" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U28" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V28" s="24" t="n"/>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
       <c r="Y28" s="25" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n"/>
-      <c r="AD28" s="24" t="n"/>
+      <c r="AC28" s="30" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:18:29.601810Z</t>
+        </is>
+      </c>
       <c r="AE28" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-re-exmana-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-nvo-mouzn-2026-07-28).</t>
         </is>
       </c>
       <c r="AF28" s="31" t="inlineStr">
@@ -8778,7 +8848,7 @@
       </c>
       <c r="AG28" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH28" s="24" t="n"/>
@@ -8786,7 +8856,7 @@
       <c r="AJ28" s="31" t="n"/>
       <c r="AK28" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL28" s="26" t="n">
@@ -8794,47 +8864,47 @@
       </c>
       <c r="AM28" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN28" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO28" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP28" s="24" t="inlineStr">
         <is>
-          <t>ex-MANA eSports</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AQ28" s="24" t="inlineStr">
         <is>
-          <t>ex-MANA eSports</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AR28" s="24" t="inlineStr">
         <is>
-          <t>ex-MANA eSports</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AS28" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AT28" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AU28" s="24" t="inlineStr">
         <is>
-          <t>Rune Eaters</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AV28" s="24" t="n"/>
@@ -8852,7 +8922,7 @@
       </c>
       <c r="BA28" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BB28" s="24" t="inlineStr">
@@ -8867,7 +8937,7 @@
       </c>
       <c r="BD28" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BE28" s="24" t="inlineStr">
@@ -8887,7 +8957,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:41.919045Z</t>
+          <t>2026-07-28T08:11:31.472875Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -8897,13 +8967,13 @@
       </c>
       <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
-        <v>-223</v>
+        <v>150</v>
       </c>
       <c r="BL28" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.5</v>
       </c>
       <c r="BM28" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.4</v>
       </c>
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
@@ -8937,12 +9007,12 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>386e4dc745654aff</t>
+          <t>5524b0018b2d4912</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T08:11:54.722189Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -8952,7 +9022,7 @@
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>63359</t>
+          <t>63358</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -8962,12 +9032,12 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Atreides</t>
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr">
@@ -8977,7 +9047,7 @@
       </c>
       <c r="I29" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J29" s="25" t="n"/>
@@ -8987,26 +9057,26 @@
         </is>
       </c>
       <c r="L29" s="26" t="n">
-        <v>-108</v>
+        <v>-163</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.613497</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.619772</v>
       </c>
       <c r="O29" s="28" t="n">
-        <v>0.589686</v>
+        <v>0.563287</v>
       </c>
       <c r="P29" s="28" t="n"/>
       <c r="Q29" s="28" t="n">
-        <v>0.070455</v>
+        <v>-0.056485</v>
       </c>
       <c r="R29" s="26" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="S29" s="29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="T29" s="24" t="inlineStr">
         <is>
@@ -9015,21 +9085,35 @@
       </c>
       <c r="U29" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V29" s="24" t="n"/>
-      <c r="W29" s="26" t="n"/>
-      <c r="X29" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y29" s="25" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n"/>
-      <c r="AD29" s="24" t="n"/>
+      <c r="AC29" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:18:30.793558Z</t>
+        </is>
+      </c>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-btf-g2a-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-atr-erx-2026-07-28).</t>
         </is>
       </c>
       <c r="AF29" s="31" t="inlineStr">
@@ -9039,7 +9123,7 @@
       </c>
       <c r="AG29" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH29" s="24" t="n"/>
@@ -9047,7 +9131,7 @@
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL29" s="26" t="n">
@@ -9055,47 +9139,47 @@
       </c>
       <c r="AM29" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN29" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO29" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP29" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AQ29" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AR29" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AS29" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Atreides</t>
         </is>
       </c>
       <c r="AT29" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Atreides</t>
         </is>
       </c>
       <c r="AU29" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Atreides</t>
         </is>
       </c>
       <c r="AV29" s="24" t="n"/>
@@ -9113,7 +9197,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -9128,7 +9212,7 @@
       </c>
       <c r="BD29" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BE29" s="24" t="inlineStr">
@@ -9148,7 +9232,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:42.419976Z</t>
+          <t>2026-07-28T08:11:32.006493Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -9158,13 +9242,13 @@
       </c>
       <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
-        <v>-108</v>
+        <v>-163</v>
       </c>
       <c r="BL29" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.613497</v>
       </c>
       <c r="BM29" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.619772</v>
       </c>
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
@@ -9198,12 +9282,12 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>8515f4ed46bc404c</t>
+          <t>b7eca6d4eec845a7</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T08:11:54.722189Z</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -9213,7 +9297,7 @@
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>64367</t>
+          <t>63359</t>
         </is>
       </c>
       <c r="E30" s="24" t="inlineStr">
@@ -9223,12 +9307,12 @@
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>G2 Ares</t>
         </is>
       </c>
       <c r="G30" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="H30" s="24" t="inlineStr">
@@ -9248,26 +9332,26 @@
         </is>
       </c>
       <c r="L30" s="26" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="N30" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.5</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>0.525641</v>
+        <v>0.589686</v>
       </c>
       <c r="P30" s="28" t="n"/>
       <c r="Q30" s="28" t="n">
-        <v>0.06481199999999999</v>
+        <v>0.089686</v>
       </c>
       <c r="R30" s="26" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="S30" s="29" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="T30" s="24" t="inlineStr">
         <is>
@@ -9276,21 +9360,35 @@
       </c>
       <c r="U30" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V30" s="24" t="n"/>
-      <c r="W30" s="26" t="n"/>
-      <c r="X30" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y30" s="25" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n"/>
-      <c r="AD30" s="24" t="n"/>
+      <c r="AC30" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD30" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:18:32.074524Z</t>
+        </is>
+      </c>
       <c r="AE30" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-bpl-bbp-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-btf-g2a-2026-07-28).</t>
         </is>
       </c>
       <c r="AF30" s="31" t="inlineStr">
@@ -9300,7 +9398,7 @@
       </c>
       <c r="AG30" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH30" s="24" t="n"/>
@@ -9331,32 +9429,32 @@
       </c>
       <c r="AP30" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>G2 Ares</t>
         </is>
       </c>
       <c r="AQ30" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>G2 Ares</t>
         </is>
       </c>
       <c r="AR30" s="24" t="inlineStr">
         <is>
-          <t>Bebop</t>
+          <t>G2 Ares</t>
         </is>
       </c>
       <c r="AS30" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AT30" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AU30" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AV30" s="24" t="n"/>
@@ -9374,7 +9472,7 @@
       </c>
       <c r="BA30" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BB30" s="24" t="inlineStr">
@@ -9389,7 +9487,7 @@
       </c>
       <c r="BD30" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BE30" s="24" t="inlineStr">
@@ -9409,7 +9507,7 @@
       </c>
       <c r="BH30" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:42.912018Z</t>
+          <t>2026-07-28T08:11:32.486834Z</t>
         </is>
       </c>
       <c r="BI30" s="24" t="inlineStr">
@@ -9419,13 +9517,13 @@
       </c>
       <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="BL30" s="27" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BM30" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.5</v>
       </c>
       <c r="BN30" s="28" t="n"/>
       <c r="BO30" s="28" t="n"/>
@@ -9459,12 +9557,12 @@
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>e0cf1c2d06654c1f</t>
+          <t>19f3cfc9755c488c</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T08:11:54.722189Z</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
@@ -9474,7 +9572,7 @@
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>63358</t>
+          <t>64367</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
@@ -9484,12 +9582,12 @@
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
         <is>
-          <t>Atreides</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr">
@@ -9499,7 +9597,7 @@
       </c>
       <c r="I31" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J31" s="25" t="n"/>
@@ -9509,49 +9607,63 @@
         </is>
       </c>
       <c r="L31" s="26" t="n">
-        <v>-163</v>
+        <v>113</v>
       </c>
       <c r="M31" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.13</v>
       </c>
       <c r="N31" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.469484</v>
       </c>
       <c r="O31" s="28" t="n">
-        <v>0.563287</v>
+        <v>0.525641</v>
       </c>
       <c r="P31" s="28" t="n"/>
       <c r="Q31" s="28" t="n">
-        <v>-0.056485</v>
+        <v>0.056157</v>
       </c>
       <c r="R31" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="S31" s="29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S31" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U31" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V31" s="24" t="n"/>
-      <c r="W31" s="26" t="n"/>
-      <c r="X31" s="26" t="n"/>
       <c r="Y31" s="25" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="30" t="n"/>
-      <c r="AD31" s="24" t="n"/>
+      <c r="AC31" s="30" t="n">
+        <v>0.8475</v>
+      </c>
+      <c r="AD31" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:18:33.321611Z</t>
+        </is>
+      </c>
       <c r="AE31" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-atr-erx-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-bpl-bbp-2026-07-28).</t>
         </is>
       </c>
       <c r="AF31" s="31" t="inlineStr">
@@ -9569,7 +9681,7 @@
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL31" s="26" t="n">
@@ -9577,47 +9689,47 @@
       </c>
       <c r="AM31" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN31" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO31" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP31" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="AQ31" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="AR31" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Bebop</t>
         </is>
       </c>
       <c r="AS31" s="24" t="inlineStr">
         <is>
-          <t>Atreides</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AT31" s="24" t="inlineStr">
         <is>
-          <t>Atreides</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AU31" s="24" t="inlineStr">
         <is>
-          <t>Atreides</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AV31" s="24" t="n"/>
@@ -9635,7 +9747,7 @@
       </c>
       <c r="BA31" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BB31" s="24" t="inlineStr">
@@ -9650,7 +9762,7 @@
       </c>
       <c r="BD31" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BE31" s="24" t="inlineStr">
@@ -9670,7 +9782,7 @@
       </c>
       <c r="BH31" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:43.417305Z</t>
+          <t>2026-07-28T08:11:33.028196Z</t>
         </is>
       </c>
       <c r="BI31" s="24" t="inlineStr">
@@ -9680,13 +9792,13 @@
       </c>
       <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
-        <v>-163</v>
+        <v>113</v>
       </c>
       <c r="BL31" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.13</v>
       </c>
       <c r="BM31" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.469484</v>
       </c>
       <c r="BN31" s="28" t="n"/>
       <c r="BO31" s="28" t="n"/>
@@ -9720,22 +9832,22 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>999ba6d2f5984911</t>
+          <t>8e6e337790c549e4</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T08:11:54.722189Z</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T14:00:00Z</t>
+          <t>2026-07-28T11:00:00Z</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>63707</t>
+          <t>63307</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
@@ -9745,12 +9857,12 @@
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>UNiTY esports</t>
+          <t>ex-MANA eSports</t>
         </is>
       </c>
       <c r="G32" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr">
@@ -9770,23 +9882,23 @@
         </is>
       </c>
       <c r="L32" s="26" t="n">
-        <v>-150</v>
+        <v>-213</v>
       </c>
       <c r="M32" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.469484</v>
       </c>
       <c r="N32" s="28" t="n">
-        <v>0.6</v>
+        <v>0.680511</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>0.6484839999999999</v>
+        <v>0.628318</v>
       </c>
       <c r="P32" s="28" t="n"/>
       <c r="Q32" s="28" t="n">
-        <v>0.048484</v>
+        <v>-0.052193</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="S32" s="29" t="n">
         <v>0</v>
@@ -9798,21 +9910,35 @@
       </c>
       <c r="U32" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V32" s="24" t="n"/>
-      <c r="W32" s="26" t="n"/>
-      <c r="X32" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y32" s="25" t="n"/>
       <c r="Z32" s="26" t="n"/>
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="30" t="n"/>
-      <c r="AD32" s="24" t="n"/>
+      <c r="AC32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-28T14:18:34.655414Z</t>
+        </is>
+      </c>
       <c r="AE32" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-erx-unity-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-re-exmana-2026-07-28).</t>
         </is>
       </c>
       <c r="AF32" s="31" t="inlineStr">
@@ -9848,37 +9974,37 @@
       </c>
       <c r="AO32" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP32" s="24" t="inlineStr">
         <is>
-          <t>UNiTY esports</t>
+          <t>ex-MANA eSports</t>
         </is>
       </c>
       <c r="AQ32" s="24" t="inlineStr">
         <is>
-          <t>UNiTY esports</t>
+          <t>ex-MANA eSports</t>
         </is>
       </c>
       <c r="AR32" s="24" t="inlineStr">
         <is>
-          <t>UNiTY esports</t>
+          <t>ex-MANA eSports</t>
         </is>
       </c>
       <c r="AS32" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AT32" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AU32" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Rune Eaters</t>
         </is>
       </c>
       <c r="AV32" s="24" t="n"/>
@@ -9896,7 +10022,7 @@
       </c>
       <c r="BA32" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BB32" s="24" t="inlineStr">
@@ -9911,7 +10037,7 @@
       </c>
       <c r="BD32" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>bc55e868a05b19a7a0abd9e0981ea1ca6d73030b07b9e89e745ea990df232cdb</t>
         </is>
       </c>
       <c r="BE32" s="24" t="inlineStr">
@@ -9931,7 +10057,7 @@
       </c>
       <c r="BH32" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:43.912117Z</t>
+          <t>2026-07-28T08:11:33.566611Z</t>
         </is>
       </c>
       <c r="BI32" s="24" t="inlineStr">
@@ -9941,13 +10067,13 @@
       </c>
       <c r="BJ32" s="25" t="n"/>
       <c r="BK32" s="26" t="n">
-        <v>-150</v>
+        <v>-213</v>
       </c>
       <c r="BL32" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.469484</v>
       </c>
       <c r="BM32" s="28" t="n">
-        <v>0.6</v>
+        <v>0.680511</v>
       </c>
       <c r="BN32" s="28" t="n"/>
       <c r="BO32" s="28" t="n"/>
@@ -9981,12 +10107,12 @@
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>7b476b8e853b4e29</t>
+          <t>6e5f892cbf794422</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T11:17:59.302295Z</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -9996,7 +10122,7 @@
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>63360</t>
+          <t>63707</t>
         </is>
       </c>
       <c r="E33" s="24" t="inlineStr">
@@ -10006,12 +10132,12 @@
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="G33" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="H33" s="24" t="inlineStr">
@@ -10021,7 +10147,7 @@
       </c>
       <c r="I33" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J33" s="25" t="n"/>
@@ -10031,26 +10157,26 @@
         </is>
       </c>
       <c r="L33" s="26" t="n">
-        <v>108</v>
+        <v>-144</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>2.08</v>
+        <v>1.694444</v>
       </c>
       <c r="N33" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.590164</v>
       </c>
       <c r="O33" s="28" t="n">
-        <v>0.53791</v>
+        <v>0.648231</v>
       </c>
       <c r="P33" s="28" t="n"/>
       <c r="Q33" s="28" t="n">
-        <v>0.057141</v>
+        <v>0.058067</v>
       </c>
       <c r="R33" s="26" t="n">
         <v>49</v>
       </c>
       <c r="S33" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33" s="24" t="inlineStr">
         <is>
@@ -10073,7 +10199,7 @@
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-btf-jpu-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-erx-unity-2026-07-28).</t>
         </is>
       </c>
       <c r="AF33" s="31" t="inlineStr">
@@ -10091,7 +10217,7 @@
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL33" s="26" t="n">
@@ -10099,47 +10225,47 @@
       </c>
       <c r="AM33" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN33" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO33" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP33" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="AQ33" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="AR33" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="AS33" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AT33" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AU33" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AV33" s="24" t="n"/>
@@ -10157,7 +10283,7 @@
       </c>
       <c r="BA33" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>2b10a508f0b7c33f18d6ceeb867088d36516a5ff42abbccd848c68e2c7ca105c</t>
         </is>
       </c>
       <c r="BB33" s="24" t="inlineStr">
@@ -10172,7 +10298,7 @@
       </c>
       <c r="BD33" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>2b10a508f0b7c33f18d6ceeb867088d36516a5ff42abbccd848c68e2c7ca105c</t>
         </is>
       </c>
       <c r="BE33" s="24" t="inlineStr">
@@ -10192,7 +10318,7 @@
       </c>
       <c r="BH33" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:45.363088Z</t>
+          <t>2026-07-28T11:17:39.606356Z</t>
         </is>
       </c>
       <c r="BI33" s="24" t="inlineStr">
@@ -10202,13 +10328,13 @@
       </c>
       <c r="BJ33" s="25" t="n"/>
       <c r="BK33" s="26" t="n">
-        <v>108</v>
+        <v>-144</v>
       </c>
       <c r="BL33" s="27" t="n">
-        <v>2.08</v>
+        <v>1.694444</v>
       </c>
       <c r="BM33" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.590164</v>
       </c>
       <c r="BN33" s="28" t="n"/>
       <c r="BO33" s="28" t="n"/>
@@ -10242,22 +10368,22 @@
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>4dedd6963b9c4ebd</t>
+          <t>539315bfdce242f4</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T11:17:59.302295Z</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T17:00:00Z</t>
+          <t>2026-07-28T14:00:00Z</t>
         </is>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>63362</t>
+          <t>63360</t>
         </is>
       </c>
       <c r="E34" s="24" t="inlineStr">
@@ -10267,12 +10393,12 @@
       </c>
       <c r="F34" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="G34" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="H34" s="24" t="inlineStr">
@@ -10292,23 +10418,23 @@
         </is>
       </c>
       <c r="L34" s="26" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="M34" s="27" t="n">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="N34" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.469484</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>0.548241</v>
+        <v>0.53772</v>
       </c>
       <c r="P34" s="28" t="n"/>
       <c r="Q34" s="28" t="n">
-        <v>0.107712</v>
+        <v>0.068236</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="S34" s="29" t="n">
         <v>1</v>
@@ -10334,7 +10460,7 @@
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-sparta-g2a-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-btf-jpu-2026-07-28).</t>
         </is>
       </c>
       <c r="AF34" s="31" t="inlineStr">
@@ -10375,32 +10501,32 @@
       </c>
       <c r="AP34" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AQ34" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AR34" s="24" t="inlineStr">
         <is>
-          <t>G2 Ares</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AS34" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AT34" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AU34" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AV34" s="24" t="n"/>
@@ -10418,7 +10544,7 @@
       </c>
       <c r="BA34" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>2b10a508f0b7c33f18d6ceeb867088d36516a5ff42abbccd848c68e2c7ca105c</t>
         </is>
       </c>
       <c r="BB34" s="24" t="inlineStr">
@@ -10433,7 +10559,7 @@
       </c>
       <c r="BD34" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>2b10a508f0b7c33f18d6ceeb867088d36516a5ff42abbccd848c68e2c7ca105c</t>
         </is>
       </c>
       <c r="BE34" s="24" t="inlineStr">
@@ -10453,7 +10579,7 @@
       </c>
       <c r="BH34" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:47.940507Z</t>
+          <t>2026-07-28T11:17:40.063714Z</t>
         </is>
       </c>
       <c r="BI34" s="24" t="inlineStr">
@@ -10463,13 +10589,13 @@
       </c>
       <c r="BJ34" s="25" t="n"/>
       <c r="BK34" s="26" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="BL34" s="27" t="n">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="BM34" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.469484</v>
       </c>
       <c r="BN34" s="28" t="n"/>
       <c r="BO34" s="28" t="n"/>
@@ -10503,22 +10629,22 @@
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>b76147fdbe3547e4</t>
+          <t>ecda5b659d244084</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
+          <t>2026-07-28T14:24:09.023643Z</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T17:00:00Z</t>
+          <t>2026-07-28T15:00:00Z</t>
         </is>
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>63363</t>
+          <t>61517</t>
         </is>
       </c>
       <c r="E35" s="24" t="inlineStr">
@@ -10528,12 +10654,12 @@
       </c>
       <c r="F35" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>BakS eSports</t>
         </is>
       </c>
       <c r="G35" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>TDK</t>
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr">
@@ -10543,7 +10669,7 @@
       </c>
       <c r="I35" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J35" s="25" t="n"/>
@@ -10553,26 +10679,26 @@
         </is>
       </c>
       <c r="L35" s="26" t="n">
-        <v>113</v>
+        <v>-194</v>
       </c>
       <c r="M35" s="27" t="n">
-        <v>2.13</v>
+        <v>1.515464</v>
       </c>
       <c r="N35" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.659864</v>
       </c>
       <c r="O35" s="28" t="n">
-        <v>0.553566</v>
+        <v>0.907919</v>
       </c>
       <c r="P35" s="28" t="n"/>
       <c r="Q35" s="28" t="n">
-        <v>0.084082</v>
+        <v>0.248055</v>
       </c>
       <c r="R35" s="26" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="S35" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T35" s="24" t="inlineStr">
         <is>
@@ -10595,7 +10721,7 @@
       <c r="AD35" s="24" t="n"/>
       <c r="AE35" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-cshp-lav-2026-07-28).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-tdk-baks-2026-07-28).</t>
         </is>
       </c>
       <c r="AF35" s="31" t="inlineStr">
@@ -10636,32 +10762,32 @@
       </c>
       <c r="AP35" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>BakS eSports</t>
         </is>
       </c>
       <c r="AQ35" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>BakS eSports</t>
         </is>
       </c>
       <c r="AR35" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>BakS eSports</t>
         </is>
       </c>
       <c r="AS35" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>TDK</t>
         </is>
       </c>
       <c r="AT35" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>TDK</t>
         </is>
       </c>
       <c r="AU35" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>TDK</t>
         </is>
       </c>
       <c r="AV35" s="24" t="n"/>
@@ -10679,7 +10805,7 @@
       </c>
       <c r="BA35" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>b7be26981f98c7c049773609859384b830ed2600e5d283ac2efb1545695d5e3e</t>
         </is>
       </c>
       <c r="BB35" s="24" t="inlineStr">
@@ -10694,7 +10820,7 @@
       </c>
       <c r="BD35" s="24" t="inlineStr">
         <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
+          <t>b7be26981f98c7c049773609859384b830ed2600e5d283ac2efb1545695d5e3e</t>
         </is>
       </c>
       <c r="BE35" s="24" t="inlineStr">
@@ -10714,7 +10840,7 @@
       </c>
       <c r="BH35" s="24" t="inlineStr">
         <is>
-          <t>2026-07-28T01:59:49.411771Z</t>
+          <t>2026-07-28T14:23:49.113149Z</t>
         </is>
       </c>
       <c r="BI35" s="24" t="inlineStr">
@@ -10724,13 +10850,13 @@
       </c>
       <c r="BJ35" s="25" t="n"/>
       <c r="BK35" s="26" t="n">
-        <v>113</v>
+        <v>-194</v>
       </c>
       <c r="BL35" s="27" t="n">
-        <v>2.13</v>
+        <v>1.515464</v>
       </c>
       <c r="BM35" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.659864</v>
       </c>
       <c r="BN35" s="28" t="n"/>
       <c r="BO35" s="28" t="n"/>
@@ -10761,1833 +10887,6 @@
       <c r="CN35" s="24" t="n"/>
       <c r="CO35" s="24" t="n"/>
     </row>
-    <row r="36" ht="36" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>e38e6b2beb2f4bef</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>63311</t>
-        </is>
-      </c>
-      <c r="E36" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F36" s="24" t="inlineStr">
-        <is>
-          <t>UNiTY esports</t>
-        </is>
-      </c>
-      <c r="G36" s="24" t="inlineStr">
-        <is>
-          <t>los kogutos</t>
-        </is>
-      </c>
-      <c r="H36" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I36" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J36" s="25" t="n"/>
-      <c r="K36" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L36" s="26" t="n">
-        <v>170</v>
-      </c>
-      <c r="M36" s="27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N36" s="28" t="n">
-        <v>0.37037</v>
-      </c>
-      <c r="O36" s="28" t="n">
-        <v>0.536588</v>
-      </c>
-      <c r="P36" s="28" t="n"/>
-      <c r="Q36" s="28" t="n">
-        <v>0.166218</v>
-      </c>
-      <c r="R36" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S36" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U36" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V36" s="24" t="n"/>
-      <c r="W36" s="26" t="n"/>
-      <c r="X36" s="26" t="n"/>
-      <c r="Y36" s="25" t="n"/>
-      <c r="Z36" s="26" t="n"/>
-      <c r="AA36" s="28" t="n"/>
-      <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="30" t="n"/>
-      <c r="AD36" s="24" t="n"/>
-      <c r="AE36" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-cs2-lk-unity-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF36" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG36" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH36" s="24" t="n"/>
-      <c r="AI36" s="31" t="n"/>
-      <c r="AJ36" s="31" t="n"/>
-      <c r="AK36" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL36" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM36" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN36" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO36" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP36" s="24" t="inlineStr">
-        <is>
-          <t>UNiTY esports</t>
-        </is>
-      </c>
-      <c r="AQ36" s="24" t="inlineStr">
-        <is>
-          <t>UNiTY esports</t>
-        </is>
-      </c>
-      <c r="AR36" s="24" t="inlineStr">
-        <is>
-          <t>UNiTY esports</t>
-        </is>
-      </c>
-      <c r="AS36" s="24" t="inlineStr">
-        <is>
-          <t>los kogutos</t>
-        </is>
-      </c>
-      <c r="AT36" s="24" t="inlineStr">
-        <is>
-          <t>los kogutos</t>
-        </is>
-      </c>
-      <c r="AU36" s="24" t="inlineStr">
-        <is>
-          <t>los kogutos</t>
-        </is>
-      </c>
-      <c r="AV36" s="24" t="n"/>
-      <c r="AW36" s="24" t="n"/>
-      <c r="AX36" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY36" s="24" t="n"/>
-      <c r="AZ36" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA36" s="24" t="inlineStr">
-        <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
-        </is>
-      </c>
-      <c r="BB36" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC36" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD36" s="24" t="inlineStr">
-        <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
-        </is>
-      </c>
-      <c r="BE36" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF36" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG36" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH36" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:49.932343Z</t>
-        </is>
-      </c>
-      <c r="BI36" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ36" s="25" t="n"/>
-      <c r="BK36" s="26" t="n">
-        <v>170</v>
-      </c>
-      <c r="BL36" s="27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BM36" s="28" t="n">
-        <v>0.37037</v>
-      </c>
-      <c r="BN36" s="28" t="n"/>
-      <c r="BO36" s="28" t="n"/>
-      <c r="BP36" s="25" t="n"/>
-      <c r="BQ36" s="27" t="n"/>
-      <c r="BR36" s="28" t="n"/>
-      <c r="BS36" s="28" t="n"/>
-      <c r="BT36" s="28" t="n"/>
-      <c r="BU36" s="25" t="n"/>
-      <c r="BV36" s="29" t="n"/>
-      <c r="BW36" s="24" t="n"/>
-      <c r="BX36" s="30" t="n"/>
-      <c r="BY36" s="27" t="n"/>
-      <c r="BZ36" s="24" t="n"/>
-      <c r="CA36" s="31" t="n"/>
-      <c r="CB36" s="24" t="n"/>
-      <c r="CC36" s="24" t="n"/>
-      <c r="CD36" s="24" t="n"/>
-      <c r="CE36" s="24" t="n"/>
-      <c r="CF36" s="24" t="n"/>
-      <c r="CG36" s="24" t="n"/>
-      <c r="CH36" s="24" t="n"/>
-      <c r="CI36" s="24" t="n"/>
-      <c r="CJ36" s="24" t="n"/>
-      <c r="CK36" s="24" t="n"/>
-      <c r="CL36" s="24" t="n"/>
-      <c r="CM36" s="24" t="n"/>
-      <c r="CN36" s="24" t="n"/>
-      <c r="CO36" s="24" t="n"/>
-    </row>
-    <row r="37" ht="36" customHeight="1">
-      <c r="A37" s="24" t="inlineStr">
-        <is>
-          <t>4710a7b97eb84e81</t>
-        </is>
-      </c>
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T17:00:00Z</t>
-        </is>
-      </c>
-      <c r="D37" s="24" t="inlineStr">
-        <is>
-          <t>64369</t>
-        </is>
-      </c>
-      <c r="E37" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F37" s="24" t="inlineStr">
-        <is>
-          <t>Falcons Force</t>
-        </is>
-      </c>
-      <c r="G37" s="24" t="inlineStr">
-        <is>
-          <t>Misa Esports</t>
-        </is>
-      </c>
-      <c r="H37" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I37" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J37" s="25" t="n"/>
-      <c r="K37" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L37" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="M37" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="N37" s="28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O37" s="28" t="n">
-        <v>0.5211479999999999</v>
-      </c>
-      <c r="P37" s="28" t="n"/>
-      <c r="Q37" s="28" t="n">
-        <v>0.021148</v>
-      </c>
-      <c r="R37" s="26" t="n">
-        <v>31</v>
-      </c>
-      <c r="S37" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U37" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V37" s="24" t="n"/>
-      <c r="W37" s="26" t="n"/>
-      <c r="X37" s="26" t="n"/>
-      <c r="Y37" s="25" t="n"/>
-      <c r="Z37" s="26" t="n"/>
-      <c r="AA37" s="28" t="n"/>
-      <c r="AB37" s="28" t="n"/>
-      <c r="AC37" s="30" t="n"/>
-      <c r="AD37" s="24" t="n"/>
-      <c r="AE37" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-misa-falf-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF37" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG37" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH37" s="24" t="n"/>
-      <c r="AI37" s="31" t="n"/>
-      <c r="AJ37" s="31" t="n"/>
-      <c r="AK37" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL37" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM37" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN37" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO37" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP37" s="24" t="inlineStr">
-        <is>
-          <t>Falcons Force</t>
-        </is>
-      </c>
-      <c r="AQ37" s="24" t="inlineStr">
-        <is>
-          <t>Falcons Force</t>
-        </is>
-      </c>
-      <c r="AR37" s="24" t="inlineStr">
-        <is>
-          <t>Falcons Force</t>
-        </is>
-      </c>
-      <c r="AS37" s="24" t="inlineStr">
-        <is>
-          <t>Misa Esports</t>
-        </is>
-      </c>
-      <c r="AT37" s="24" t="inlineStr">
-        <is>
-          <t>Misa Esports</t>
-        </is>
-      </c>
-      <c r="AU37" s="24" t="inlineStr">
-        <is>
-          <t>Misa Esports</t>
-        </is>
-      </c>
-      <c r="AV37" s="24" t="n"/>
-      <c r="AW37" s="24" t="n"/>
-      <c r="AX37" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY37" s="24" t="n"/>
-      <c r="AZ37" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA37" s="24" t="inlineStr">
-        <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
-        </is>
-      </c>
-      <c r="BB37" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC37" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD37" s="24" t="inlineStr">
-        <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
-        </is>
-      </c>
-      <c r="BE37" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF37" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG37" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH37" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:50.504855Z</t>
-        </is>
-      </c>
-      <c r="BI37" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ37" s="25" t="n"/>
-      <c r="BK37" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="BL37" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM37" s="28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN37" s="28" t="n"/>
-      <c r="BO37" s="28" t="n"/>
-      <c r="BP37" s="25" t="n"/>
-      <c r="BQ37" s="27" t="n"/>
-      <c r="BR37" s="28" t="n"/>
-      <c r="BS37" s="28" t="n"/>
-      <c r="BT37" s="28" t="n"/>
-      <c r="BU37" s="25" t="n"/>
-      <c r="BV37" s="29" t="n"/>
-      <c r="BW37" s="24" t="n"/>
-      <c r="BX37" s="30" t="n"/>
-      <c r="BY37" s="27" t="n"/>
-      <c r="BZ37" s="24" t="n"/>
-      <c r="CA37" s="31" t="n"/>
-      <c r="CB37" s="24" t="n"/>
-      <c r="CC37" s="24" t="n"/>
-      <c r="CD37" s="24" t="n"/>
-      <c r="CE37" s="24" t="n"/>
-      <c r="CF37" s="24" t="n"/>
-      <c r="CG37" s="24" t="n"/>
-      <c r="CH37" s="24" t="n"/>
-      <c r="CI37" s="24" t="n"/>
-      <c r="CJ37" s="24" t="n"/>
-      <c r="CK37" s="24" t="n"/>
-      <c r="CL37" s="24" t="n"/>
-      <c r="CM37" s="24" t="n"/>
-      <c r="CN37" s="24" t="n"/>
-      <c r="CO37" s="24" t="n"/>
-    </row>
-    <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="24" t="inlineStr">
-        <is>
-          <t>bbcd2c2ef81f4286</t>
-        </is>
-      </c>
-      <c r="B38" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>61708</t>
-        </is>
-      </c>
-      <c r="E38" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F38" s="24" t="inlineStr">
-        <is>
-          <t>largadosypelados</t>
-        </is>
-      </c>
-      <c r="G38" s="24" t="inlineStr">
-        <is>
-          <t>Bounty Hunters Esports</t>
-        </is>
-      </c>
-      <c r="H38" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I38" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J38" s="25" t="n"/>
-      <c r="K38" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L38" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="M38" s="27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="N38" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="O38" s="28" t="n">
-        <v>0.730996</v>
-      </c>
-      <c r="P38" s="28" t="n"/>
-      <c r="Q38" s="28" t="n">
-        <v>0.250227</v>
-      </c>
-      <c r="R38" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S38" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U38" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V38" s="24" t="n"/>
-      <c r="W38" s="26" t="n"/>
-      <c r="X38" s="26" t="n"/>
-      <c r="Y38" s="25" t="n"/>
-      <c r="Z38" s="26" t="n"/>
-      <c r="AA38" s="28" t="n"/>
-      <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="30" t="n"/>
-      <c r="AD38" s="24" t="n"/>
-      <c r="AE38" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-cs2-bhe-ldp-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF38" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG38" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH38" s="24" t="n"/>
-      <c r="AI38" s="31" t="n"/>
-      <c r="AJ38" s="31" t="n"/>
-      <c r="AK38" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL38" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM38" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN38" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO38" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP38" s="24" t="inlineStr">
-        <is>
-          <t>largadosypelados</t>
-        </is>
-      </c>
-      <c r="AQ38" s="24" t="inlineStr">
-        <is>
-          <t>largadosypelados</t>
-        </is>
-      </c>
-      <c r="AR38" s="24" t="inlineStr">
-        <is>
-          <t>largadosypelados</t>
-        </is>
-      </c>
-      <c r="AS38" s="24" t="inlineStr">
-        <is>
-          <t>Bounty Hunters Esports</t>
-        </is>
-      </c>
-      <c r="AT38" s="24" t="inlineStr">
-        <is>
-          <t>Bounty Hunters Esports</t>
-        </is>
-      </c>
-      <c r="AU38" s="24" t="inlineStr">
-        <is>
-          <t>Bounty Hunters Esports</t>
-        </is>
-      </c>
-      <c r="AV38" s="24" t="n"/>
-      <c r="AW38" s="24" t="n"/>
-      <c r="AX38" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY38" s="24" t="n"/>
-      <c r="AZ38" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA38" s="24" t="inlineStr">
-        <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
-        </is>
-      </c>
-      <c r="BB38" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC38" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD38" s="24" t="inlineStr">
-        <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
-        </is>
-      </c>
-      <c r="BE38" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF38" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG38" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH38" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:51.025834Z</t>
-        </is>
-      </c>
-      <c r="BI38" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ38" s="25" t="n"/>
-      <c r="BK38" s="26" t="n">
-        <v>108</v>
-      </c>
-      <c r="BL38" s="27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BM38" s="28" t="n">
-        <v>0.480769</v>
-      </c>
-      <c r="BN38" s="28" t="n"/>
-      <c r="BO38" s="28" t="n"/>
-      <c r="BP38" s="25" t="n"/>
-      <c r="BQ38" s="27" t="n"/>
-      <c r="BR38" s="28" t="n"/>
-      <c r="BS38" s="28" t="n"/>
-      <c r="BT38" s="28" t="n"/>
-      <c r="BU38" s="25" t="n"/>
-      <c r="BV38" s="29" t="n"/>
-      <c r="BW38" s="24" t="n"/>
-      <c r="BX38" s="30" t="n"/>
-      <c r="BY38" s="27" t="n"/>
-      <c r="BZ38" s="24" t="n"/>
-      <c r="CA38" s="31" t="n"/>
-      <c r="CB38" s="24" t="n"/>
-      <c r="CC38" s="24" t="n"/>
-      <c r="CD38" s="24" t="n"/>
-      <c r="CE38" s="24" t="n"/>
-      <c r="CF38" s="24" t="n"/>
-      <c r="CG38" s="24" t="n"/>
-      <c r="CH38" s="24" t="n"/>
-      <c r="CI38" s="24" t="n"/>
-      <c r="CJ38" s="24" t="n"/>
-      <c r="CK38" s="24" t="n"/>
-      <c r="CL38" s="24" t="n"/>
-      <c r="CM38" s="24" t="n"/>
-      <c r="CN38" s="24" t="n"/>
-      <c r="CO38" s="24" t="n"/>
-    </row>
-    <row r="39" ht="36" customHeight="1">
-      <c r="A39" s="24" t="inlineStr">
-        <is>
-          <t>1ef28cef3128445f</t>
-        </is>
-      </c>
-      <c r="B39" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
-        </is>
-      </c>
-      <c r="C39" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="D39" s="24" t="inlineStr">
-        <is>
-          <t>62235</t>
-        </is>
-      </c>
-      <c r="E39" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F39" s="24" t="inlineStr">
-        <is>
-          <t>QUINTESSÊNCIA</t>
-        </is>
-      </c>
-      <c r="G39" s="24" t="inlineStr">
-        <is>
-          <t>ALKA GAMING</t>
-        </is>
-      </c>
-      <c r="H39" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I39" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J39" s="25" t="n"/>
-      <c r="K39" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L39" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M39" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="N39" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="O39" s="28" t="n">
-        <v>0.690487</v>
-      </c>
-      <c r="P39" s="28" t="n"/>
-      <c r="Q39" s="28" t="n">
-        <v>8.500000000000001e-05</v>
-      </c>
-      <c r="R39" s="26" t="n">
-        <v>20</v>
-      </c>
-      <c r="S39" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U39" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V39" s="24" t="n"/>
-      <c r="W39" s="26" t="n"/>
-      <c r="X39" s="26" t="n"/>
-      <c r="Y39" s="25" t="n"/>
-      <c r="Z39" s="26" t="n"/>
-      <c r="AA39" s="28" t="n"/>
-      <c r="AB39" s="28" t="n"/>
-      <c r="AC39" s="30" t="n"/>
-      <c r="AD39" s="24" t="n"/>
-      <c r="AE39" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-alka-quin-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF39" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG39" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH39" s="24" t="n"/>
-      <c r="AI39" s="31" t="n"/>
-      <c r="AJ39" s="31" t="n"/>
-      <c r="AK39" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL39" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM39" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN39" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO39" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP39" s="24" t="inlineStr">
-        <is>
-          <t>QUINTESSÊNCIA</t>
-        </is>
-      </c>
-      <c r="AQ39" s="24" t="inlineStr">
-        <is>
-          <t>QUINTESSÊNCIA</t>
-        </is>
-      </c>
-      <c r="AR39" s="24" t="inlineStr">
-        <is>
-          <t>QUINTESSÊNCIA</t>
-        </is>
-      </c>
-      <c r="AS39" s="24" t="inlineStr">
-        <is>
-          <t>ALKA GAMING</t>
-        </is>
-      </c>
-      <c r="AT39" s="24" t="inlineStr">
-        <is>
-          <t>ALKA GAMING</t>
-        </is>
-      </c>
-      <c r="AU39" s="24" t="inlineStr">
-        <is>
-          <t>ALKA GAMING</t>
-        </is>
-      </c>
-      <c r="AV39" s="24" t="n"/>
-      <c r="AW39" s="24" t="n"/>
-      <c r="AX39" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY39" s="24" t="n"/>
-      <c r="AZ39" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA39" s="24" t="inlineStr">
-        <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
-        </is>
-      </c>
-      <c r="BB39" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC39" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD39" s="24" t="inlineStr">
-        <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
-        </is>
-      </c>
-      <c r="BE39" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF39" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG39" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH39" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T01:59:59.872308Z</t>
-        </is>
-      </c>
-      <c r="BI39" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ39" s="25" t="n"/>
-      <c r="BK39" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL39" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="BM39" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="BN39" s="28" t="n"/>
-      <c r="BO39" s="28" t="n"/>
-      <c r="BP39" s="25" t="n"/>
-      <c r="BQ39" s="27" t="n"/>
-      <c r="BR39" s="28" t="n"/>
-      <c r="BS39" s="28" t="n"/>
-      <c r="BT39" s="28" t="n"/>
-      <c r="BU39" s="25" t="n"/>
-      <c r="BV39" s="29" t="n"/>
-      <c r="BW39" s="24" t="n"/>
-      <c r="BX39" s="30" t="n"/>
-      <c r="BY39" s="27" t="n"/>
-      <c r="BZ39" s="24" t="n"/>
-      <c r="CA39" s="31" t="n"/>
-      <c r="CB39" s="24" t="n"/>
-      <c r="CC39" s="24" t="n"/>
-      <c r="CD39" s="24" t="n"/>
-      <c r="CE39" s="24" t="n"/>
-      <c r="CF39" s="24" t="n"/>
-      <c r="CG39" s="24" t="n"/>
-      <c r="CH39" s="24" t="n"/>
-      <c r="CI39" s="24" t="n"/>
-      <c r="CJ39" s="24" t="n"/>
-      <c r="CK39" s="24" t="n"/>
-      <c r="CL39" s="24" t="n"/>
-      <c r="CM39" s="24" t="n"/>
-      <c r="CN39" s="24" t="n"/>
-      <c r="CO39" s="24" t="n"/>
-    </row>
-    <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
-        <is>
-          <t>62843cbec2364d66</t>
-        </is>
-      </c>
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T21:00:00Z</t>
-        </is>
-      </c>
-      <c r="D40" s="24" t="inlineStr">
-        <is>
-          <t>62236</t>
-        </is>
-      </c>
-      <c r="E40" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F40" s="24" t="inlineStr">
-        <is>
-          <t>BESTIA</t>
-        </is>
-      </c>
-      <c r="G40" s="24" t="inlineStr">
-        <is>
-          <t>Imperial</t>
-        </is>
-      </c>
-      <c r="H40" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I40" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J40" s="25" t="n"/>
-      <c r="K40" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L40" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="M40" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="N40" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="O40" s="28" t="n">
-        <v>0.526234</v>
-      </c>
-      <c r="P40" s="28" t="n"/>
-      <c r="Q40" s="28" t="n">
-        <v>-0.044581</v>
-      </c>
-      <c r="R40" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U40" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V40" s="24" t="n"/>
-      <c r="W40" s="26" t="n"/>
-      <c r="X40" s="26" t="n"/>
-      <c r="Y40" s="25" t="n"/>
-      <c r="Z40" s="26" t="n"/>
-      <c r="AA40" s="28" t="n"/>
-      <c r="AB40" s="28" t="n"/>
-      <c r="AC40" s="30" t="n"/>
-      <c r="AD40" s="24" t="n"/>
-      <c r="AE40" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-imp-bst-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF40" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG40" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH40" s="24" t="n"/>
-      <c r="AI40" s="31" t="n"/>
-      <c r="AJ40" s="31" t="n"/>
-      <c r="AK40" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL40" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM40" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN40" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO40" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP40" s="24" t="inlineStr">
-        <is>
-          <t>BESTIA</t>
-        </is>
-      </c>
-      <c r="AQ40" s="24" t="inlineStr">
-        <is>
-          <t>BESTIA</t>
-        </is>
-      </c>
-      <c r="AR40" s="24" t="inlineStr">
-        <is>
-          <t>BESTIA</t>
-        </is>
-      </c>
-      <c r="AS40" s="24" t="inlineStr">
-        <is>
-          <t>Imperial</t>
-        </is>
-      </c>
-      <c r="AT40" s="24" t="inlineStr">
-        <is>
-          <t>Imperial</t>
-        </is>
-      </c>
-      <c r="AU40" s="24" t="inlineStr">
-        <is>
-          <t>Imperial</t>
-        </is>
-      </c>
-      <c r="AV40" s="24" t="n"/>
-      <c r="AW40" s="24" t="n"/>
-      <c r="AX40" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY40" s="24" t="n"/>
-      <c r="AZ40" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA40" s="24" t="inlineStr">
-        <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
-        </is>
-      </c>
-      <c r="BB40" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC40" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD40" s="24" t="inlineStr">
-        <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
-        </is>
-      </c>
-      <c r="BE40" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF40" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG40" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH40" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:00.381650Z</t>
-        </is>
-      </c>
-      <c r="BI40" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ40" s="25" t="n"/>
-      <c r="BK40" s="26" t="n">
-        <v>-133</v>
-      </c>
-      <c r="BL40" s="27" t="n">
-        <v>1.75188</v>
-      </c>
-      <c r="BM40" s="28" t="n">
-        <v>0.570815</v>
-      </c>
-      <c r="BN40" s="28" t="n"/>
-      <c r="BO40" s="28" t="n"/>
-      <c r="BP40" s="25" t="n"/>
-      <c r="BQ40" s="27" t="n"/>
-      <c r="BR40" s="28" t="n"/>
-      <c r="BS40" s="28" t="n"/>
-      <c r="BT40" s="28" t="n"/>
-      <c r="BU40" s="25" t="n"/>
-      <c r="BV40" s="29" t="n"/>
-      <c r="BW40" s="24" t="n"/>
-      <c r="BX40" s="30" t="n"/>
-      <c r="BY40" s="27" t="n"/>
-      <c r="BZ40" s="24" t="n"/>
-      <c r="CA40" s="31" t="n"/>
-      <c r="CB40" s="24" t="n"/>
-      <c r="CC40" s="24" t="n"/>
-      <c r="CD40" s="24" t="n"/>
-      <c r="CE40" s="24" t="n"/>
-      <c r="CF40" s="24" t="n"/>
-      <c r="CG40" s="24" t="n"/>
-      <c r="CH40" s="24" t="n"/>
-      <c r="CI40" s="24" t="n"/>
-      <c r="CJ40" s="24" t="n"/>
-      <c r="CK40" s="24" t="n"/>
-      <c r="CL40" s="24" t="n"/>
-      <c r="CM40" s="24" t="n"/>
-      <c r="CN40" s="24" t="n"/>
-      <c r="CO40" s="24" t="n"/>
-    </row>
-    <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>2e1b6c7ba1ed46a9</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:01.501477Z</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T22:00:00Z</t>
-        </is>
-      </c>
-      <c r="D41" s="24" t="inlineStr">
-        <is>
-          <t>62282</t>
-        </is>
-      </c>
-      <c r="E41" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F41" s="24" t="inlineStr">
-        <is>
-          <t>Marsborne</t>
-        </is>
-      </c>
-      <c r="G41" s="24" t="inlineStr">
-        <is>
-          <t>LAG Gaming</t>
-        </is>
-      </c>
-      <c r="H41" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I41" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J41" s="25" t="n"/>
-      <c r="K41" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L41" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="M41" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="N41" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="O41" s="28" t="n">
-        <v>0.585167</v>
-      </c>
-      <c r="P41" s="28" t="n"/>
-      <c r="Q41" s="28" t="n">
-        <v>-0.024208</v>
-      </c>
-      <c r="R41" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="S41" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U41" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V41" s="24" t="n"/>
-      <c r="W41" s="26" t="n"/>
-      <c r="X41" s="26" t="n"/>
-      <c r="Y41" s="25" t="n"/>
-      <c r="Z41" s="26" t="n"/>
-      <c r="AA41" s="28" t="n"/>
-      <c r="AB41" s="28" t="n"/>
-      <c r="AC41" s="30" t="n"/>
-      <c r="AD41" s="24" t="n"/>
-      <c r="AE41" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-lag-mars-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF41" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG41" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH41" s="24" t="n"/>
-      <c r="AI41" s="31" t="n"/>
-      <c r="AJ41" s="31" t="n"/>
-      <c r="AK41" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL41" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM41" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN41" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO41" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP41" s="24" t="inlineStr">
-        <is>
-          <t>Marsborne</t>
-        </is>
-      </c>
-      <c r="AQ41" s="24" t="inlineStr">
-        <is>
-          <t>Marsborne</t>
-        </is>
-      </c>
-      <c r="AR41" s="24" t="inlineStr">
-        <is>
-          <t>Marsborne</t>
-        </is>
-      </c>
-      <c r="AS41" s="24" t="inlineStr">
-        <is>
-          <t>LAG Gaming</t>
-        </is>
-      </c>
-      <c r="AT41" s="24" t="inlineStr">
-        <is>
-          <t>LAG Gaming</t>
-        </is>
-      </c>
-      <c r="AU41" s="24" t="inlineStr">
-        <is>
-          <t>LAG Gaming</t>
-        </is>
-      </c>
-      <c r="AV41" s="24" t="n"/>
-      <c r="AW41" s="24" t="n"/>
-      <c r="AX41" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY41" s="24" t="n"/>
-      <c r="AZ41" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA41" s="24" t="inlineStr">
-        <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
-        </is>
-      </c>
-      <c r="BB41" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC41" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD41" s="24" t="inlineStr">
-        <is>
-          <t>da5537802607ba1fbdae985f92f1b67c327aaa91913ae14bcd767a484004f207</t>
-        </is>
-      </c>
-      <c r="BE41" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF41" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG41" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH41" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:00:00.888591Z</t>
-        </is>
-      </c>
-      <c r="BI41" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ41" s="25" t="n"/>
-      <c r="BK41" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="BL41" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="BM41" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="BN41" s="28" t="n"/>
-      <c r="BO41" s="28" t="n"/>
-      <c r="BP41" s="25" t="n"/>
-      <c r="BQ41" s="27" t="n"/>
-      <c r="BR41" s="28" t="n"/>
-      <c r="BS41" s="28" t="n"/>
-      <c r="BT41" s="28" t="n"/>
-      <c r="BU41" s="25" t="n"/>
-      <c r="BV41" s="29" t="n"/>
-      <c r="BW41" s="24" t="n"/>
-      <c r="BX41" s="30" t="n"/>
-      <c r="BY41" s="27" t="n"/>
-      <c r="BZ41" s="24" t="n"/>
-      <c r="CA41" s="31" t="n"/>
-      <c r="CB41" s="24" t="n"/>
-      <c r="CC41" s="24" t="n"/>
-      <c r="CD41" s="24" t="n"/>
-      <c r="CE41" s="24" t="n"/>
-      <c r="CF41" s="24" t="n"/>
-      <c r="CG41" s="24" t="n"/>
-      <c r="CH41" s="24" t="n"/>
-      <c r="CI41" s="24" t="n"/>
-      <c r="CJ41" s="24" t="n"/>
-      <c r="CK41" s="24" t="n"/>
-      <c r="CL41" s="24" t="n"/>
-      <c r="CM41" s="24" t="n"/>
-      <c r="CN41" s="24" t="n"/>
-      <c r="CO41" s="24" t="n"/>
-    </row>
-    <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="24" t="inlineStr">
-        <is>
-          <t>f1c4fd97f35b453f</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:08:42.519814Z</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="D42" s="24" t="inlineStr">
-        <is>
-          <t>63706</t>
-        </is>
-      </c>
-      <c r="E42" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F42" s="24" t="inlineStr">
-        <is>
-          <t>Mai Tai</t>
-        </is>
-      </c>
-      <c r="G42" s="24" t="inlineStr">
-        <is>
-          <t>Entropy</t>
-        </is>
-      </c>
-      <c r="H42" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I42" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J42" s="25" t="n"/>
-      <c r="K42" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L42" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="M42" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="N42" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="O42" s="28" t="n">
-        <v>0.609287</v>
-      </c>
-      <c r="P42" s="28" t="n"/>
-      <c r="Q42" s="28" t="n">
-        <v>0.029455</v>
-      </c>
-      <c r="R42" s="26" t="n">
-        <v>35</v>
-      </c>
-      <c r="S42" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T42" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U42" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V42" s="24" t="n"/>
-      <c r="W42" s="26" t="n"/>
-      <c r="X42" s="26" t="n"/>
-      <c r="Y42" s="25" t="n"/>
-      <c r="Z42" s="26" t="n"/>
-      <c r="AA42" s="28" t="n"/>
-      <c r="AB42" s="28" t="n"/>
-      <c r="AC42" s="30" t="n"/>
-      <c r="AD42" s="24" t="n"/>
-      <c r="AE42" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-ent-mta-2026-07-28).</t>
-        </is>
-      </c>
-      <c r="AF42" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG42" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH42" s="24" t="n"/>
-      <c r="AI42" s="31" t="n"/>
-      <c r="AJ42" s="31" t="n"/>
-      <c r="AK42" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL42" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM42" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN42" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO42" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP42" s="24" t="inlineStr">
-        <is>
-          <t>Mai Tai</t>
-        </is>
-      </c>
-      <c r="AQ42" s="24" t="inlineStr">
-        <is>
-          <t>Mai Tai</t>
-        </is>
-      </c>
-      <c r="AR42" s="24" t="inlineStr">
-        <is>
-          <t>Mai Tai</t>
-        </is>
-      </c>
-      <c r="AS42" s="24" t="inlineStr">
-        <is>
-          <t>Entropy</t>
-        </is>
-      </c>
-      <c r="AT42" s="24" t="inlineStr">
-        <is>
-          <t>Entropy</t>
-        </is>
-      </c>
-      <c r="AU42" s="24" t="inlineStr">
-        <is>
-          <t>Entropy</t>
-        </is>
-      </c>
-      <c r="AV42" s="24" t="n"/>
-      <c r="AW42" s="24" t="n"/>
-      <c r="AX42" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY42" s="24" t="n"/>
-      <c r="AZ42" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA42" s="24" t="inlineStr">
-        <is>
-          <t>083967481304d1dc27bfb10e14bb394ac08ceeda4b7f4e87080bc0131a2aed37</t>
-        </is>
-      </c>
-      <c r="BB42" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC42" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD42" s="24" t="inlineStr">
-        <is>
-          <t>083967481304d1dc27bfb10e14bb394ac08ceeda4b7f4e87080bc0131a2aed37</t>
-        </is>
-      </c>
-      <c r="BE42" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF42" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG42" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH42" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-28T02:08:19.728443Z</t>
-        </is>
-      </c>
-      <c r="BI42" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ42" s="25" t="n"/>
-      <c r="BK42" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="BL42" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="BM42" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="BN42" s="28" t="n"/>
-      <c r="BO42" s="28" t="n"/>
-      <c r="BP42" s="25" t="n"/>
-      <c r="BQ42" s="27" t="n"/>
-      <c r="BR42" s="28" t="n"/>
-      <c r="BS42" s="28" t="n"/>
-      <c r="BT42" s="28" t="n"/>
-      <c r="BU42" s="25" t="n"/>
-      <c r="BV42" s="29" t="n"/>
-      <c r="BW42" s="24" t="n"/>
-      <c r="BX42" s="30" t="n"/>
-      <c r="BY42" s="27" t="n"/>
-      <c r="BZ42" s="24" t="n"/>
-      <c r="CA42" s="31" t="n"/>
-      <c r="CB42" s="24" t="n"/>
-      <c r="CC42" s="24" t="n"/>
-      <c r="CD42" s="24" t="n"/>
-      <c r="CE42" s="24" t="n"/>
-      <c r="CF42" s="24" t="n"/>
-      <c r="CG42" s="24" t="n"/>
-      <c r="CH42" s="24" t="n"/>
-      <c r="CI42" s="24" t="n"/>
-      <c r="CJ42" s="24" t="n"/>
-      <c r="CK42" s="24" t="n"/>
-      <c r="CL42" s="24" t="n"/>
-      <c r="CM42" s="24" t="n"/>
-      <c r="CN42" s="24" t="n"/>
-      <c r="CO42" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO118" headerRowCount="1">
-  <autoFilter ref="A1:CO118"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO117" headerRowCount="1">
+  <autoFilter ref="A1:CO117"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$118)</f>
+        <f>COUNTA('Picks'!$A$2:$A$117)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$118,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$117,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$118,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$117,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$118,"settled",'Picks'!$V$2:$V$118,"win")+COUNTIFS('Picks'!$U$2:$U$118,"settled",'Picks'!$V$2:$V$118,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"win")+COUNTIFS('Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$118,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$117,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$118,"&gt;0",'Picks'!$V$2:$V$118,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$118,"&gt;0",'Picks'!$V$2:$V$118,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$118,"&gt;0",'Picks'!$V$2:$V$118,"win")/(COUNTIFS('Picks'!$BX$2:$BX$118,"&gt;0",'Picks'!$V$2:$V$118,"win")+COUNTIFS('Picks'!$BX$2:$BX$118,"&gt;0",'Picks'!$V$2:$V$118,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"win")/(COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"win")+COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$118)/SUM('Picks'!$BX$2:$BX$118),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$117)/SUM('Picks'!$BX$2:$BX$117),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$118)</f>
+        <f>SUM('Picks'!$BY$2:$BY$117)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$118,"&lt;&gt;",'Picks'!$AB$2:$AB$118),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$117,"&lt;&gt;",'Picks'!$AB$2:$AB$117),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$118,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$118,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$117,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$117,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$118,'Picks'!$AM$2:$AM$118,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$117,'Picks'!$AM$2:$AM$117,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$118,$A14,'Picks'!$U$2:$U$118,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A14,'Picks'!$U$2:$U$117,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$118,$A14,'Picks'!$U$2:$U$118,"settled",'Picks'!$V$2:$V$118,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A14,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$118,$A14,'Picks'!$U$2:$U$118,"settled",'Picks'!$V$2:$V$118,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A14,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$118,'Picks'!$H$2:$H$118,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$117,'Picks'!$H$2:$H$117,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$118,'Picks'!$H$2:$H$118,$A14,'Picks'!$U$2:$U$118,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$117,'Picks'!$H$2:$H$117,$A14,'Picks'!$U$2:$U$117,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$118,$A15,'Picks'!$U$2:$U$118,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A15,'Picks'!$U$2:$U$117,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$118,$A15,'Picks'!$U$2:$U$118,"settled",'Picks'!$V$2:$V$118,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A15,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$118,$A15,'Picks'!$U$2:$U$118,"settled",'Picks'!$V$2:$V$118,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A15,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$118,'Picks'!$H$2:$H$118,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$117,'Picks'!$H$2:$H$117,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$118,'Picks'!$H$2:$H$118,$A15,'Picks'!$U$2:$U$118,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$117,'Picks'!$H$2:$H$117,$A15,'Picks'!$U$2:$U$117,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$118,$A16,'Picks'!$U$2:$U$118,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A16,'Picks'!$U$2:$U$117,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$118,$A16,'Picks'!$U$2:$U$118,"settled",'Picks'!$V$2:$V$118,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A16,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$118,$A16,'Picks'!$U$2:$U$118,"settled",'Picks'!$V$2:$V$118,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$117,$A16,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$118,'Picks'!$H$2:$H$118,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$117,'Picks'!$H$2:$H$117,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$118,'Picks'!$H$2:$H$118,$A16,'Picks'!$U$2:$U$118,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$117,'Picks'!$H$2:$H$117,$A16,'Picks'!$U$2:$U$117,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO118"/>
+  <dimension ref="A1:CO117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -26093,18 +26093,32 @@
       </c>
       <c r="U91" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V91" s="24" t="n"/>
-      <c r="W91" s="26" t="n"/>
-      <c r="X91" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V91" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W91" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X91" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y91" s="25" t="n"/>
       <c r="Z91" s="26" t="n"/>
       <c r="AA91" s="28" t="n"/>
       <c r="AB91" s="28" t="n"/>
-      <c r="AC91" s="30" t="n"/>
-      <c r="AD91" s="24" t="n"/>
+      <c r="AC91" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD91" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:22:40.724235Z</t>
+        </is>
+      </c>
       <c r="AE91" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-cs2-gs-mel-2026-07-30).</t>
@@ -26117,7 +26131,7 @@
       </c>
       <c r="AG91" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH91" s="24" t="n"/>
@@ -26876,18 +26890,32 @@
       </c>
       <c r="U94" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V94" s="24" t="n"/>
-      <c r="W94" s="26" t="n"/>
-      <c r="X94" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V94" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W94" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y94" s="25" t="n"/>
       <c r="Z94" s="26" t="n"/>
       <c r="AA94" s="28" t="n"/>
       <c r="AB94" s="28" t="n"/>
-      <c r="AC94" s="30" t="n"/>
-      <c r="AD94" s="24" t="n"/>
+      <c r="AC94" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD94" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:22:44.729094Z</t>
+        </is>
+      </c>
       <c r="AE94" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-sinqu-bjng-2026-07-30).</t>
@@ -26900,7 +26928,7 @@
       </c>
       <c r="AG94" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH94" s="24" t="n"/>
@@ -28364,12 +28392,12 @@
     <row r="100" ht="36" customHeight="1">
       <c r="A100" s="24" t="inlineStr">
         <is>
-          <t>ffa07b633bed4f46</t>
+          <t>2c35fc5baa9b4e42</t>
         </is>
       </c>
       <c r="B100" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C100" s="24" t="inlineStr">
@@ -28414,23 +28442,23 @@
         </is>
       </c>
       <c r="L100" s="26" t="n">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="M100" s="27" t="n">
-        <v>2.04</v>
+        <v>1.925926</v>
       </c>
       <c r="N100" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.519231</v>
       </c>
       <c r="O100" s="28" t="n">
-        <v>0.6620780000000001</v>
+        <v>0.662039</v>
       </c>
       <c r="P100" s="28" t="n"/>
       <c r="Q100" s="28" t="n">
-        <v>0.171882</v>
+        <v>0.142808</v>
       </c>
       <c r="R100" s="26" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="S100" s="29" t="n">
         <v>2</v>
@@ -28456,7 +28484,7 @@
       <c r="AD100" s="24" t="n"/>
       <c r="AE100" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-cs2-sng-frt-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-sng-frt-2026-07-30).</t>
         </is>
       </c>
       <c r="AF100" s="31" t="inlineStr">
@@ -28540,7 +28568,7 @@
       </c>
       <c r="BA100" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB100" s="24" t="inlineStr">
@@ -28555,7 +28583,7 @@
       </c>
       <c r="BD100" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE100" s="24" t="inlineStr">
@@ -28575,7 +28603,7 @@
       </c>
       <c r="BH100" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:27.303905Z</t>
+          <t>2026-07-30T17:21:38.234981Z</t>
         </is>
       </c>
       <c r="BI100" s="24" t="inlineStr">
@@ -28585,13 +28613,13 @@
       </c>
       <c r="BJ100" s="25" t="n"/>
       <c r="BK100" s="26" t="n">
-        <v>104</v>
+        <v>-108</v>
       </c>
       <c r="BL100" s="27" t="n">
-        <v>2.04</v>
+        <v>1.925926</v>
       </c>
       <c r="BM100" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.519231</v>
       </c>
       <c r="BN100" s="28" t="n"/>
       <c r="BO100" s="28" t="n"/>
@@ -28625,12 +28653,12 @@
     <row r="101" ht="36" customHeight="1">
       <c r="A101" s="24" t="inlineStr">
         <is>
-          <t>1cdad3c4e3ea4552</t>
+          <t>92e6d786395a4cc3</t>
         </is>
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C101" s="24" t="inlineStr">
@@ -28684,11 +28712,11 @@
         <v>0.669967</v>
       </c>
       <c r="O101" s="28" t="n">
-        <v>0.551683</v>
+        <v>0.551875</v>
       </c>
       <c r="P101" s="28" t="n"/>
       <c r="Q101" s="28" t="n">
-        <v>-0.118284</v>
+        <v>-0.118092</v>
       </c>
       <c r="R101" s="26" t="n">
         <v>0</v>
@@ -28801,7 +28829,7 @@
       </c>
       <c r="BA101" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB101" s="24" t="inlineStr">
@@ -28816,7 +28844,7 @@
       </c>
       <c r="BD101" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE101" s="24" t="inlineStr">
@@ -28836,7 +28864,7 @@
       </c>
       <c r="BH101" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:27.746474Z</t>
+          <t>2026-07-30T17:21:39.226781Z</t>
         </is>
       </c>
       <c r="BI101" s="24" t="inlineStr">
@@ -28886,12 +28914,12 @@
     <row r="102" ht="36" customHeight="1">
       <c r="A102" s="24" t="inlineStr">
         <is>
-          <t>8e7f773050aa4c7d</t>
+          <t>59024be33a944192</t>
         </is>
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C102" s="24" t="inlineStr">
@@ -28945,11 +28973,11 @@
         <v>0.680511</v>
       </c>
       <c r="O102" s="28" t="n">
-        <v>0.589317</v>
+        <v>0.589224</v>
       </c>
       <c r="P102" s="28" t="n"/>
       <c r="Q102" s="28" t="n">
-        <v>-0.091194</v>
+        <v>-0.09128699999999999</v>
       </c>
       <c r="R102" s="26" t="n">
         <v>0</v>
@@ -29062,7 +29090,7 @@
       </c>
       <c r="BA102" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB102" s="24" t="inlineStr">
@@ -29077,7 +29105,7 @@
       </c>
       <c r="BD102" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE102" s="24" t="inlineStr">
@@ -29097,7 +29125,7 @@
       </c>
       <c r="BH102" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:28.644615Z</t>
+          <t>2026-07-30T17:21:39.762691Z</t>
         </is>
       </c>
       <c r="BI102" s="24" t="inlineStr">
@@ -29147,12 +29175,12 @@
     <row r="103" ht="36" customHeight="1">
       <c r="A103" s="24" t="inlineStr">
         <is>
-          <t>4140a1dd982c4d22</t>
+          <t>8f1497d766eb4ac6</t>
         </is>
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C103" s="24" t="inlineStr">
@@ -29162,7 +29190,7 @@
       </c>
       <c r="D103" s="24" t="inlineStr">
         <is>
-          <t>66614</t>
+          <t>66613</t>
         </is>
       </c>
       <c r="E103" s="24" t="inlineStr">
@@ -29172,12 +29200,12 @@
       </c>
       <c r="F103" s="24" t="inlineStr">
         <is>
-          <t>NEXORA</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="G103" s="24" t="inlineStr">
         <is>
-          <t>Strael-Bora</t>
+          <t>Younglings</t>
         </is>
       </c>
       <c r="H103" s="24" t="inlineStr">
@@ -29187,7 +29215,7 @@
       </c>
       <c r="I103" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J103" s="25" t="n"/>
@@ -29197,26 +29225,26 @@
         </is>
       </c>
       <c r="L103" s="26" t="n">
-        <v>138</v>
+        <v>-117</v>
       </c>
       <c r="M103" s="27" t="n">
-        <v>2.38</v>
+        <v>1.854701</v>
       </c>
       <c r="N103" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.539171</v>
       </c>
       <c r="O103" s="28" t="n">
-        <v>0.541443</v>
+        <v>0.576671</v>
       </c>
       <c r="P103" s="28" t="n"/>
       <c r="Q103" s="28" t="n">
-        <v>0.121275</v>
+        <v>0.0375</v>
       </c>
       <c r="R103" s="26" t="n">
-        <v>81</v>
+        <v>39</v>
       </c>
       <c r="S103" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T103" s="24" t="inlineStr">
         <is>
@@ -29239,7 +29267,7 @@
       <c r="AD103" s="24" t="n"/>
       <c r="AE103" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-sb-nexo-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-yl-bg-2026-07-30).</t>
         </is>
       </c>
       <c r="AF103" s="31" t="inlineStr">
@@ -29280,32 +29308,32 @@
       </c>
       <c r="AP103" s="24" t="inlineStr">
         <is>
-          <t>NEXORA</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AQ103" s="24" t="inlineStr">
         <is>
-          <t>NEXORA</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AR103" s="24" t="inlineStr">
         <is>
-          <t>NEXORA</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AS103" s="24" t="inlineStr">
         <is>
-          <t>Strael-Bora</t>
+          <t>Younglings</t>
         </is>
       </c>
       <c r="AT103" s="24" t="inlineStr">
         <is>
-          <t>Strael-Bora</t>
+          <t>Younglings</t>
         </is>
       </c>
       <c r="AU103" s="24" t="inlineStr">
         <is>
-          <t>Strael-Bora</t>
+          <t>Younglings</t>
         </is>
       </c>
       <c r="AV103" s="24" t="n"/>
@@ -29323,7 +29351,7 @@
       </c>
       <c r="BA103" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB103" s="24" t="inlineStr">
@@ -29338,7 +29366,7 @@
       </c>
       <c r="BD103" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE103" s="24" t="inlineStr">
@@ -29358,7 +29386,7 @@
       </c>
       <c r="BH103" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:29.676246Z</t>
+          <t>2026-07-30T17:21:40.939739Z</t>
         </is>
       </c>
       <c r="BI103" s="24" t="inlineStr">
@@ -29368,13 +29396,13 @@
       </c>
       <c r="BJ103" s="25" t="n"/>
       <c r="BK103" s="26" t="n">
-        <v>138</v>
+        <v>-117</v>
       </c>
       <c r="BL103" s="27" t="n">
-        <v>2.38</v>
+        <v>1.854701</v>
       </c>
       <c r="BM103" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.539171</v>
       </c>
       <c r="BN103" s="28" t="n"/>
       <c r="BO103" s="28" t="n"/>
@@ -29408,12 +29436,12 @@
     <row r="104" ht="36" customHeight="1">
       <c r="A104" s="24" t="inlineStr">
         <is>
-          <t>29a69441f1734eaa</t>
+          <t>b2d8d5b49e1446fc</t>
         </is>
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C104" s="24" t="inlineStr">
@@ -29423,7 +29451,7 @@
       </c>
       <c r="D104" s="24" t="inlineStr">
         <is>
-          <t>66617</t>
+          <t>66614</t>
         </is>
       </c>
       <c r="E104" s="24" t="inlineStr">
@@ -29433,12 +29461,12 @@
       </c>
       <c r="F104" s="24" t="inlineStr">
         <is>
-          <t>Hermine Esports Club</t>
+          <t>NEXORA</t>
         </is>
       </c>
       <c r="G104" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>Strael-Bora</t>
         </is>
       </c>
       <c r="H104" s="24" t="inlineStr">
@@ -29448,7 +29476,7 @@
       </c>
       <c r="I104" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J104" s="25" t="n"/>
@@ -29458,23 +29486,23 @@
         </is>
       </c>
       <c r="L104" s="26" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="M104" s="27" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="N104" s="28" t="n">
-        <v>0.5</v>
+        <v>0.429185</v>
       </c>
       <c r="O104" s="28" t="n">
-        <v>0.554756</v>
+        <v>0.541314</v>
       </c>
       <c r="P104" s="28" t="n"/>
       <c r="Q104" s="28" t="n">
-        <v>0.054756</v>
+        <v>0.112129</v>
       </c>
       <c r="R104" s="26" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="S104" s="29" t="n">
         <v>1</v>
@@ -29500,7 +29528,7 @@
       <c r="AD104" s="24" t="n"/>
       <c r="AE104" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-mel-hec-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-cs2-sb-nexo-2026-07-30).</t>
         </is>
       </c>
       <c r="AF104" s="31" t="inlineStr">
@@ -29541,32 +29569,32 @@
       </c>
       <c r="AP104" s="24" t="inlineStr">
         <is>
-          <t>Hermine Esports Club</t>
+          <t>NEXORA</t>
         </is>
       </c>
       <c r="AQ104" s="24" t="inlineStr">
         <is>
-          <t>Hermine Esports Club</t>
+          <t>NEXORA</t>
         </is>
       </c>
       <c r="AR104" s="24" t="inlineStr">
         <is>
-          <t>Hermine Esports Club</t>
+          <t>NEXORA</t>
         </is>
       </c>
       <c r="AS104" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>Strael-Bora</t>
         </is>
       </c>
       <c r="AT104" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>Strael-Bora</t>
         </is>
       </c>
       <c r="AU104" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>Strael-Bora</t>
         </is>
       </c>
       <c r="AV104" s="24" t="n"/>
@@ -29584,7 +29612,7 @@
       </c>
       <c r="BA104" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB104" s="24" t="inlineStr">
@@ -29599,7 +29627,7 @@
       </c>
       <c r="BD104" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE104" s="24" t="inlineStr">
@@ -29619,7 +29647,7 @@
       </c>
       <c r="BH104" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:30.122924Z</t>
+          <t>2026-07-30T17:21:41.486408Z</t>
         </is>
       </c>
       <c r="BI104" s="24" t="inlineStr">
@@ -29629,13 +29657,13 @@
       </c>
       <c r="BJ104" s="25" t="n"/>
       <c r="BK104" s="26" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="BL104" s="27" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="BM104" s="28" t="n">
-        <v>0.5</v>
+        <v>0.429185</v>
       </c>
       <c r="BN104" s="28" t="n"/>
       <c r="BO104" s="28" t="n"/>
@@ -29669,12 +29697,12 @@
     <row r="105" ht="36" customHeight="1">
       <c r="A105" s="24" t="inlineStr">
         <is>
-          <t>fcff171f11ed40cb</t>
+          <t>0b57d92459db4322</t>
         </is>
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C105" s="24" t="inlineStr">
@@ -29684,7 +29712,7 @@
       </c>
       <c r="D105" s="24" t="inlineStr">
         <is>
-          <t>66610</t>
+          <t>66617</t>
         </is>
       </c>
       <c r="E105" s="24" t="inlineStr">
@@ -29694,12 +29722,12 @@
       </c>
       <c r="F105" s="24" t="inlineStr">
         <is>
-          <t>LFO UKRAINE</t>
+          <t>Hermine Esports Club</t>
         </is>
       </c>
       <c r="G105" s="24" t="inlineStr">
         <is>
-          <t>OldBoys</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="H105" s="24" t="inlineStr">
@@ -29719,26 +29747,26 @@
         </is>
       </c>
       <c r="L105" s="26" t="n">
-        <v>122</v>
+        <v>-104</v>
       </c>
       <c r="M105" s="27" t="n">
-        <v>2.22</v>
+        <v>1.961538</v>
       </c>
       <c r="N105" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.509804</v>
       </c>
       <c r="O105" s="28" t="n">
-        <v>0.522795</v>
+        <v>0.5549500000000001</v>
       </c>
       <c r="P105" s="28" t="n"/>
       <c r="Q105" s="28" t="n">
-        <v>0.07234500000000001</v>
+        <v>0.045146</v>
       </c>
       <c r="R105" s="26" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="S105" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T105" s="24" t="inlineStr">
         <is>
@@ -29761,7 +29789,7 @@
       <c r="AD105" s="24" t="n"/>
       <c r="AE105" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-oboys-lfouk-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-mel-hec-2026-07-30).</t>
         </is>
       </c>
       <c r="AF105" s="31" t="inlineStr">
@@ -29779,7 +29807,7 @@
       <c r="AJ105" s="31" t="n"/>
       <c r="AK105" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL105" s="26" t="n">
@@ -29787,47 +29815,47 @@
       </c>
       <c r="AM105" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN105" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO105" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP105" s="24" t="inlineStr">
         <is>
-          <t>LFO UKRAINE</t>
+          <t>Hermine Esports Club</t>
         </is>
       </c>
       <c r="AQ105" s="24" t="inlineStr">
         <is>
-          <t>LFO UKRAINE</t>
+          <t>Hermine Esports Club</t>
         </is>
       </c>
       <c r="AR105" s="24" t="inlineStr">
         <is>
-          <t>LFO UKRAINE</t>
+          <t>Hermine Esports Club</t>
         </is>
       </c>
       <c r="AS105" s="24" t="inlineStr">
         <is>
-          <t>OldBoys</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="AT105" s="24" t="inlineStr">
         <is>
-          <t>OldBoys</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="AU105" s="24" t="inlineStr">
         <is>
-          <t>OldBoys</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="AV105" s="24" t="n"/>
@@ -29845,7 +29873,7 @@
       </c>
       <c r="BA105" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB105" s="24" t="inlineStr">
@@ -29860,7 +29888,7 @@
       </c>
       <c r="BD105" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE105" s="24" t="inlineStr">
@@ -29880,7 +29908,7 @@
       </c>
       <c r="BH105" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:31.077916Z</t>
+          <t>2026-07-30T17:21:42.057537Z</t>
         </is>
       </c>
       <c r="BI105" s="24" t="inlineStr">
@@ -29890,13 +29918,13 @@
       </c>
       <c r="BJ105" s="25" t="n"/>
       <c r="BK105" s="26" t="n">
-        <v>122</v>
+        <v>-104</v>
       </c>
       <c r="BL105" s="27" t="n">
-        <v>2.22</v>
+        <v>1.961538</v>
       </c>
       <c r="BM105" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.509804</v>
       </c>
       <c r="BN105" s="28" t="n"/>
       <c r="BO105" s="28" t="n"/>
@@ -29930,12 +29958,12 @@
     <row r="106" ht="36" customHeight="1">
       <c r="A106" s="24" t="inlineStr">
         <is>
-          <t>092b746ba28948b3</t>
+          <t>98d5f75e5066475f</t>
         </is>
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C106" s="24" t="inlineStr">
@@ -29945,7 +29973,7 @@
       </c>
       <c r="D106" s="24" t="inlineStr">
         <is>
-          <t>66613</t>
+          <t>66610</t>
         </is>
       </c>
       <c r="E106" s="24" t="inlineStr">
@@ -29955,12 +29983,12 @@
       </c>
       <c r="F106" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>LFO UKRAINE</t>
         </is>
       </c>
       <c r="G106" s="24" t="inlineStr">
         <is>
-          <t>Younglings</t>
+          <t>OldBoys</t>
         </is>
       </c>
       <c r="H106" s="24" t="inlineStr">
@@ -29980,26 +30008,26 @@
         </is>
       </c>
       <c r="L106" s="26" t="n">
-        <v>-117</v>
+        <v>122</v>
       </c>
       <c r="M106" s="27" t="n">
-        <v>1.854701</v>
+        <v>2.22</v>
       </c>
       <c r="N106" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.45045</v>
       </c>
       <c r="O106" s="28" t="n">
-        <v>0.576464</v>
+        <v>0.522969</v>
       </c>
       <c r="P106" s="28" t="n"/>
       <c r="Q106" s="28" t="n">
-        <v>0.037293</v>
+        <v>0.072519</v>
       </c>
       <c r="R106" s="26" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="S106" s="29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T106" s="24" t="inlineStr">
         <is>
@@ -30022,7 +30050,7 @@
       <c r="AD106" s="24" t="n"/>
       <c r="AE106" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-yl-bg-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-oboys-lfouk-2026-07-30).</t>
         </is>
       </c>
       <c r="AF106" s="31" t="inlineStr">
@@ -30040,7 +30068,7 @@
       <c r="AJ106" s="31" t="n"/>
       <c r="AK106" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL106" s="26" t="n">
@@ -30048,47 +30076,47 @@
       </c>
       <c r="AM106" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN106" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO106" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP106" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>LFO UKRAINE</t>
         </is>
       </c>
       <c r="AQ106" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>LFO UKRAINE</t>
         </is>
       </c>
       <c r="AR106" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>LFO UKRAINE</t>
         </is>
       </c>
       <c r="AS106" s="24" t="inlineStr">
         <is>
-          <t>Younglings</t>
+          <t>OldBoys</t>
         </is>
       </c>
       <c r="AT106" s="24" t="inlineStr">
         <is>
-          <t>Younglings</t>
+          <t>OldBoys</t>
         </is>
       </c>
       <c r="AU106" s="24" t="inlineStr">
         <is>
-          <t>Younglings</t>
+          <t>OldBoys</t>
         </is>
       </c>
       <c r="AV106" s="24" t="n"/>
@@ -30106,7 +30134,7 @@
       </c>
       <c r="BA106" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB106" s="24" t="inlineStr">
@@ -30121,7 +30149,7 @@
       </c>
       <c r="BD106" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE106" s="24" t="inlineStr">
@@ -30141,7 +30169,7 @@
       </c>
       <c r="BH106" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:31.539734Z</t>
+          <t>2026-07-30T17:21:43.123721Z</t>
         </is>
       </c>
       <c r="BI106" s="24" t="inlineStr">
@@ -30151,13 +30179,13 @@
       </c>
       <c r="BJ106" s="25" t="n"/>
       <c r="BK106" s="26" t="n">
-        <v>-117</v>
+        <v>122</v>
       </c>
       <c r="BL106" s="27" t="n">
-        <v>1.854701</v>
+        <v>2.22</v>
       </c>
       <c r="BM106" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.45045</v>
       </c>
       <c r="BN106" s="28" t="n"/>
       <c r="BO106" s="28" t="n"/>
@@ -30191,12 +30219,12 @@
     <row r="107" ht="36" customHeight="1">
       <c r="A107" s="24" t="inlineStr">
         <is>
-          <t>5ea8352301c747e6</t>
+          <t>e48aa89383564c1b</t>
         </is>
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C107" s="24" t="inlineStr">
@@ -30250,11 +30278,11 @@
         <v>0.359712</v>
       </c>
       <c r="O107" s="28" t="n">
-        <v>0.53389</v>
+        <v>0.534071</v>
       </c>
       <c r="P107" s="28" t="n"/>
       <c r="Q107" s="28" t="n">
-        <v>0.174178</v>
+        <v>0.174359</v>
       </c>
       <c r="R107" s="26" t="n">
         <v>100</v>
@@ -30367,7 +30395,7 @@
       </c>
       <c r="BA107" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB107" s="24" t="inlineStr">
@@ -30382,7 +30410,7 @@
       </c>
       <c r="BD107" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE107" s="24" t="inlineStr">
@@ -30402,7 +30430,7 @@
       </c>
       <c r="BH107" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:32.123396Z</t>
+          <t>2026-07-30T17:21:43.729769Z</t>
         </is>
       </c>
       <c r="BI107" s="24" t="inlineStr">
@@ -30452,12 +30480,12 @@
     <row r="108" ht="36" customHeight="1">
       <c r="A108" s="24" t="inlineStr">
         <is>
-          <t>55c326eaf3db423c</t>
+          <t>3c961bbafdc54f09</t>
         </is>
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C108" s="24" t="inlineStr">
@@ -30511,11 +30539,11 @@
         <v>0.659864</v>
       </c>
       <c r="O108" s="28" t="n">
-        <v>0.537423</v>
+        <v>0.537606</v>
       </c>
       <c r="P108" s="28" t="n"/>
       <c r="Q108" s="28" t="n">
-        <v>-0.122441</v>
+        <v>-0.122258</v>
       </c>
       <c r="R108" s="26" t="n">
         <v>0</v>
@@ -30628,7 +30656,7 @@
       </c>
       <c r="BA108" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB108" s="24" t="inlineStr">
@@ -30643,7 +30671,7 @@
       </c>
       <c r="BD108" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE108" s="24" t="inlineStr">
@@ -30663,7 +30691,7 @@
       </c>
       <c r="BH108" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:32.565820Z</t>
+          <t>2026-07-30T17:21:44.257986Z</t>
         </is>
       </c>
       <c r="BI108" s="24" t="inlineStr">
@@ -30713,12 +30741,12 @@
     <row r="109" ht="36" customHeight="1">
       <c r="A109" s="24" t="inlineStr">
         <is>
-          <t>cb3ee25b21bb4efd</t>
+          <t>a405ebf6921142a4</t>
         </is>
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C109" s="24" t="inlineStr">
@@ -30772,11 +30800,11 @@
         <v>0.480769</v>
       </c>
       <c r="O109" s="28" t="n">
-        <v>0.5433210000000001</v>
+        <v>0.543193</v>
       </c>
       <c r="P109" s="28" t="n"/>
       <c r="Q109" s="28" t="n">
-        <v>0.062552</v>
+        <v>0.062424</v>
       </c>
       <c r="R109" s="26" t="n">
         <v>51</v>
@@ -30889,7 +30917,7 @@
       </c>
       <c r="BA109" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB109" s="24" t="inlineStr">
@@ -30904,7 +30932,7 @@
       </c>
       <c r="BD109" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE109" s="24" t="inlineStr">
@@ -30924,7 +30952,7 @@
       </c>
       <c r="BH109" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:33.548064Z</t>
+          <t>2026-07-30T17:21:45.323638Z</t>
         </is>
       </c>
       <c r="BI109" s="24" t="inlineStr">
@@ -30974,12 +31002,12 @@
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="24" t="inlineStr">
         <is>
-          <t>df2485759f324547</t>
+          <t>c8b8655f1314492a</t>
         </is>
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C110" s="24" t="inlineStr">
@@ -31033,14 +31061,14 @@
         <v>0.519231</v>
       </c>
       <c r="O110" s="28" t="n">
-        <v>0.676216</v>
+        <v>0.676465</v>
       </c>
       <c r="P110" s="28" t="n"/>
       <c r="Q110" s="28" t="n">
-        <v>0.156985</v>
+        <v>0.157234</v>
       </c>
       <c r="R110" s="26" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S110" s="29" t="n">
         <v>2</v>
@@ -31150,7 +31178,7 @@
       </c>
       <c r="BA110" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB110" s="24" t="inlineStr">
@@ -31165,7 +31193,7 @@
       </c>
       <c r="BD110" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE110" s="24" t="inlineStr">
@@ -31185,7 +31213,7 @@
       </c>
       <c r="BH110" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:34.094425Z</t>
+          <t>2026-07-30T17:21:45.909267Z</t>
         </is>
       </c>
       <c r="BI110" s="24" t="inlineStr">
@@ -31235,12 +31263,12 @@
     <row r="111" ht="36" customHeight="1">
       <c r="A111" s="24" t="inlineStr">
         <is>
-          <t>30f2192731034700</t>
+          <t>08875836e52b464b</t>
         </is>
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C111" s="24" t="inlineStr">
@@ -31294,11 +31322,11 @@
         <v>0.5594710000000001</v>
       </c>
       <c r="O111" s="28" t="n">
-        <v>0.688034</v>
+        <v>0.688286</v>
       </c>
       <c r="P111" s="28" t="n"/>
       <c r="Q111" s="28" t="n">
-        <v>0.128563</v>
+        <v>0.128815</v>
       </c>
       <c r="R111" s="26" t="n">
         <v>84</v>
@@ -31411,7 +31439,7 @@
       </c>
       <c r="BA111" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB111" s="24" t="inlineStr">
@@ -31426,7 +31454,7 @@
       </c>
       <c r="BD111" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE111" s="24" t="inlineStr">
@@ -31446,7 +31474,7 @@
       </c>
       <c r="BH111" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:34.584817Z</t>
+          <t>2026-07-30T17:21:47.628354Z</t>
         </is>
       </c>
       <c r="BI111" s="24" t="inlineStr">
@@ -31496,12 +31524,12 @@
     <row r="112" ht="36" customHeight="1">
       <c r="A112" s="24" t="inlineStr">
         <is>
-          <t>82f7173aaabc4383</t>
+          <t>f187fe1ca4924cc0</t>
         </is>
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C112" s="24" t="inlineStr">
@@ -31555,11 +31583,11 @@
         <v>0.480769</v>
       </c>
       <c r="O112" s="28" t="n">
-        <v>0.71909</v>
+        <v>0.719348</v>
       </c>
       <c r="P112" s="28" t="n"/>
       <c r="Q112" s="28" t="n">
-        <v>0.238321</v>
+        <v>0.238579</v>
       </c>
       <c r="R112" s="26" t="n">
         <v>100</v>
@@ -31672,7 +31700,7 @@
       </c>
       <c r="BA112" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB112" s="24" t="inlineStr">
@@ -31687,7 +31715,7 @@
       </c>
       <c r="BD112" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE112" s="24" t="inlineStr">
@@ -31707,7 +31735,7 @@
       </c>
       <c r="BH112" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:36.505125Z</t>
+          <t>2026-07-30T17:21:49.268706Z</t>
         </is>
       </c>
       <c r="BI112" s="24" t="inlineStr">
@@ -31757,22 +31785,22 @@
     <row r="113" ht="36" customHeight="1">
       <c r="A113" s="24" t="inlineStr">
         <is>
-          <t>01b2a484bd7d4582</t>
+          <t>96c160cdb00f46c5</t>
         </is>
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C113" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T12:30:00Z</t>
+          <t>2026-07-31T14:00:00Z</t>
         </is>
       </c>
       <c r="D113" s="24" t="inlineStr">
         <is>
-          <t>66411</t>
+          <t>64927</t>
         </is>
       </c>
       <c r="E113" s="24" t="inlineStr">
@@ -31782,12 +31810,12 @@
       </c>
       <c r="F113" s="24" t="inlineStr">
         <is>
-          <t>MOUZ</t>
+          <t>Trainwrecks eSports</t>
         </is>
       </c>
       <c r="G113" s="24" t="inlineStr">
         <is>
-          <t>3DMAX</t>
+          <t>ROUNDS</t>
         </is>
       </c>
       <c r="H113" s="24" t="inlineStr">
@@ -31797,7 +31825,7 @@
       </c>
       <c r="I113" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J113" s="25" t="n"/>
@@ -31807,26 +31835,26 @@
         </is>
       </c>
       <c r="L113" s="26" t="n">
-        <v>144</v>
+        <v>-178</v>
       </c>
       <c r="M113" s="27" t="n">
-        <v>2.44</v>
+        <v>1.561798</v>
       </c>
       <c r="N113" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.640288</v>
       </c>
       <c r="O113" s="28" t="n">
-        <v>0.671111</v>
+        <v>0.644533</v>
       </c>
       <c r="P113" s="28" t="n"/>
       <c r="Q113" s="28" t="n">
-        <v>0.261275</v>
+        <v>0.004245</v>
       </c>
       <c r="R113" s="26" t="n">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="S113" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T113" s="24" t="inlineStr">
         <is>
@@ -31849,7 +31877,7 @@
       <c r="AD113" s="24" t="n"/>
       <c r="AE113" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-cs2-3dmax-mouz-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-rgg-tera-2026-07-31).</t>
         </is>
       </c>
       <c r="AF113" s="31" t="inlineStr">
@@ -31867,7 +31895,7 @@
       <c r="AJ113" s="31" t="n"/>
       <c r="AK113" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL113" s="26" t="n">
@@ -31875,47 +31903,47 @@
       </c>
       <c r="AM113" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN113" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO113" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP113" s="24" t="inlineStr">
         <is>
-          <t>MOUZ</t>
+          <t>Trainwrecks eSports</t>
         </is>
       </c>
       <c r="AQ113" s="24" t="inlineStr">
         <is>
-          <t>MOUZ</t>
+          <t>Trainwrecks eSports</t>
         </is>
       </c>
       <c r="AR113" s="24" t="inlineStr">
         <is>
-          <t>MOUZ</t>
+          <t>Trainwrecks eSports</t>
         </is>
       </c>
       <c r="AS113" s="24" t="inlineStr">
         <is>
-          <t>3DMAX</t>
+          <t>ROUNDS</t>
         </is>
       </c>
       <c r="AT113" s="24" t="inlineStr">
         <is>
-          <t>3DMAX</t>
+          <t>ROUNDS</t>
         </is>
       </c>
       <c r="AU113" s="24" t="inlineStr">
         <is>
-          <t>3DMAX</t>
+          <t>ROUNDS</t>
         </is>
       </c>
       <c r="AV113" s="24" t="n"/>
@@ -31933,7 +31961,7 @@
       </c>
       <c r="BA113" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB113" s="24" t="inlineStr">
@@ -31948,7 +31976,7 @@
       </c>
       <c r="BD113" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE113" s="24" t="inlineStr">
@@ -31968,7 +31996,7 @@
       </c>
       <c r="BH113" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:39.517006Z</t>
+          <t>2026-07-30T17:21:53.385941Z</t>
         </is>
       </c>
       <c r="BI113" s="24" t="inlineStr">
@@ -31978,13 +32006,13 @@
       </c>
       <c r="BJ113" s="25" t="n"/>
       <c r="BK113" s="26" t="n">
-        <v>144</v>
+        <v>-178</v>
       </c>
       <c r="BL113" s="27" t="n">
-        <v>2.44</v>
+        <v>1.561798</v>
       </c>
       <c r="BM113" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.640288</v>
       </c>
       <c r="BN113" s="28" t="n"/>
       <c r="BO113" s="28" t="n"/>
@@ -32018,12 +32046,12 @@
     <row r="114" ht="36" customHeight="1">
       <c r="A114" s="24" t="inlineStr">
         <is>
-          <t>1bada20b117347d8</t>
+          <t>4d785da94abe40ff</t>
         </is>
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C114" s="24" t="inlineStr">
@@ -32077,11 +32105,11 @@
         <v>0.62963</v>
       </c>
       <c r="O114" s="28" t="n">
-        <v>0.697797</v>
+        <v>0.698051</v>
       </c>
       <c r="P114" s="28" t="n"/>
       <c r="Q114" s="28" t="n">
-        <v>0.06816700000000001</v>
+        <v>0.068421</v>
       </c>
       <c r="R114" s="26" t="n">
         <v>54</v>
@@ -32194,7 +32222,7 @@
       </c>
       <c r="BA114" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB114" s="24" t="inlineStr">
@@ -32209,7 +32237,7 @@
       </c>
       <c r="BD114" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE114" s="24" t="inlineStr">
@@ -32229,7 +32257,7 @@
       </c>
       <c r="BH114" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:39.995435Z</t>
+          <t>2026-07-30T17:21:54.000232Z</t>
         </is>
       </c>
       <c r="BI114" s="24" t="inlineStr">
@@ -32279,22 +32307,22 @@
     <row r="115" ht="36" customHeight="1">
       <c r="A115" s="24" t="inlineStr">
         <is>
-          <t>35554b8a95214676</t>
+          <t>620107eee4424354</t>
         </is>
       </c>
       <c r="B115" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C115" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T14:00:00Z</t>
+          <t>2026-07-31T17:00:00Z</t>
         </is>
       </c>
       <c r="D115" s="24" t="inlineStr">
         <is>
-          <t>64927</t>
+          <t>66536</t>
         </is>
       </c>
       <c r="E115" s="24" t="inlineStr">
@@ -32304,12 +32332,12 @@
       </c>
       <c r="F115" s="24" t="inlineStr">
         <is>
-          <t>Trainwrecks eSports</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="G115" s="24" t="inlineStr">
         <is>
-          <t>ROUNDS</t>
+          <t>JiJieHao</t>
         </is>
       </c>
       <c r="H115" s="24" t="inlineStr">
@@ -32329,26 +32357,26 @@
         </is>
       </c>
       <c r="L115" s="26" t="n">
-        <v>-186</v>
+        <v>-213</v>
       </c>
       <c r="M115" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.469484</v>
       </c>
       <c r="N115" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.680511</v>
       </c>
       <c r="O115" s="28" t="n">
-        <v>0.644294</v>
+        <v>0.71083</v>
       </c>
       <c r="P115" s="28" t="n"/>
       <c r="Q115" s="28" t="n">
-        <v>-0.006056</v>
+        <v>0.030319</v>
       </c>
       <c r="R115" s="26" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="S115" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T115" s="24" t="inlineStr">
         <is>
@@ -32371,7 +32399,7 @@
       <c r="AD115" s="24" t="n"/>
       <c r="AE115" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-cs2-rgg-tera-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jjh-bpl-2026-07-31).</t>
         </is>
       </c>
       <c r="AF115" s="31" t="inlineStr">
@@ -32389,7 +32417,7 @@
       <c r="AJ115" s="31" t="n"/>
       <c r="AK115" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL115" s="26" t="n">
@@ -32397,47 +32425,47 @@
       </c>
       <c r="AM115" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN115" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO115" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP115" s="24" t="inlineStr">
         <is>
-          <t>Trainwrecks eSports</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AQ115" s="24" t="inlineStr">
         <is>
-          <t>Trainwrecks eSports</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AR115" s="24" t="inlineStr">
         <is>
-          <t>Trainwrecks eSports</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AS115" s="24" t="inlineStr">
         <is>
-          <t>ROUNDS</t>
+          <t>JiJieHao</t>
         </is>
       </c>
       <c r="AT115" s="24" t="inlineStr">
         <is>
-          <t>ROUNDS</t>
+          <t>JiJieHao</t>
         </is>
       </c>
       <c r="AU115" s="24" t="inlineStr">
         <is>
-          <t>ROUNDS</t>
+          <t>JiJieHao</t>
         </is>
       </c>
       <c r="AV115" s="24" t="n"/>
@@ -32455,7 +32483,7 @@
       </c>
       <c r="BA115" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB115" s="24" t="inlineStr">
@@ -32470,7 +32498,7 @@
       </c>
       <c r="BD115" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE115" s="24" t="inlineStr">
@@ -32490,7 +32518,7 @@
       </c>
       <c r="BH115" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:40.467515Z</t>
+          <t>2026-07-30T17:21:54.989141Z</t>
         </is>
       </c>
       <c r="BI115" s="24" t="inlineStr">
@@ -32500,13 +32528,13 @@
       </c>
       <c r="BJ115" s="25" t="n"/>
       <c r="BK115" s="26" t="n">
-        <v>-186</v>
+        <v>-213</v>
       </c>
       <c r="BL115" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.469484</v>
       </c>
       <c r="BM115" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.680511</v>
       </c>
       <c r="BN115" s="28" t="n"/>
       <c r="BO115" s="28" t="n"/>
@@ -32540,12 +32568,12 @@
     <row r="116" ht="36" customHeight="1">
       <c r="A116" s="24" t="inlineStr">
         <is>
-          <t>99a88fd916e04b88</t>
+          <t>e5a0a39cbd2c4206</t>
         </is>
       </c>
       <c r="B116" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C116" s="24" t="inlineStr">
@@ -32555,7 +32583,7 @@
       </c>
       <c r="D116" s="24" t="inlineStr">
         <is>
-          <t>66536</t>
+          <t>66547</t>
         </is>
       </c>
       <c r="E116" s="24" t="inlineStr">
@@ -32565,12 +32593,12 @@
       </c>
       <c r="F116" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="G116" s="24" t="inlineStr">
         <is>
-          <t>JiJieHao</t>
+          <t>CYBERSHOKE Esports</t>
         </is>
       </c>
       <c r="H116" s="24" t="inlineStr">
@@ -32580,7 +32608,7 @@
       </c>
       <c r="I116" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J116" s="25" t="n"/>
@@ -32590,26 +32618,26 @@
         </is>
       </c>
       <c r="L116" s="26" t="n">
-        <v>-213</v>
+        <v>203</v>
       </c>
       <c r="M116" s="27" t="n">
-        <v>1.469484</v>
+        <v>3.03</v>
       </c>
       <c r="N116" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.330033</v>
       </c>
       <c r="O116" s="28" t="n">
-        <v>0.691882</v>
+        <v>0.6625490000000001</v>
       </c>
       <c r="P116" s="28" t="n"/>
       <c r="Q116" s="28" t="n">
-        <v>0.011371</v>
+        <v>0.332516</v>
       </c>
       <c r="R116" s="26" t="n">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="S116" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T116" s="24" t="inlineStr">
         <is>
@@ -32632,7 +32660,7 @@
       <c r="AD116" s="24" t="n"/>
       <c r="AE116" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jjh-bpl-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-cs2-cs-sta-2026-07-31).</t>
         </is>
       </c>
       <c r="AF116" s="31" t="inlineStr">
@@ -32650,7 +32678,7 @@
       <c r="AJ116" s="31" t="n"/>
       <c r="AK116" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL116" s="26" t="n">
@@ -32658,47 +32686,47 @@
       </c>
       <c r="AM116" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN116" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO116" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP116" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="AQ116" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="AR116" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="AS116" s="24" t="inlineStr">
         <is>
-          <t>JiJieHao</t>
+          <t>CYBERSHOKE Esports</t>
         </is>
       </c>
       <c r="AT116" s="24" t="inlineStr">
         <is>
-          <t>JiJieHao</t>
+          <t>CYBERSHOKE Esports</t>
         </is>
       </c>
       <c r="AU116" s="24" t="inlineStr">
         <is>
-          <t>JiJieHao</t>
+          <t>CYBERSHOKE Esports</t>
         </is>
       </c>
       <c r="AV116" s="24" t="n"/>
@@ -32716,7 +32744,7 @@
       </c>
       <c r="BA116" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB116" s="24" t="inlineStr">
@@ -32731,7 +32759,7 @@
       </c>
       <c r="BD116" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE116" s="24" t="inlineStr">
@@ -32751,7 +32779,7 @@
       </c>
       <c r="BH116" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:41.909156Z</t>
+          <t>2026-07-30T17:21:55.589981Z</t>
         </is>
       </c>
       <c r="BI116" s="24" t="inlineStr">
@@ -32761,13 +32789,13 @@
       </c>
       <c r="BJ116" s="25" t="n"/>
       <c r="BK116" s="26" t="n">
-        <v>-213</v>
+        <v>203</v>
       </c>
       <c r="BL116" s="27" t="n">
-        <v>1.469484</v>
+        <v>3.03</v>
       </c>
       <c r="BM116" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.330033</v>
       </c>
       <c r="BN116" s="28" t="n"/>
       <c r="BO116" s="28" t="n"/>
@@ -32801,22 +32829,22 @@
     <row r="117" ht="36" customHeight="1">
       <c r="A117" s="24" t="inlineStr">
         <is>
-          <t>e412f828f0494a39</t>
+          <t>c8a3c7c1e18349d0</t>
         </is>
       </c>
       <c r="B117" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
+          <t>2026-07-30T17:21:57.239232Z</t>
         </is>
       </c>
       <c r="C117" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T17:00:00Z</t>
+          <t>2026-07-31T18:00:00Z</t>
         </is>
       </c>
       <c r="D117" s="24" t="inlineStr">
         <is>
-          <t>66547</t>
+          <t>65109</t>
         </is>
       </c>
       <c r="E117" s="24" t="inlineStr">
@@ -32826,12 +32854,12 @@
       </c>
       <c r="F117" s="24" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="G117" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Esports</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="H117" s="24" t="inlineStr">
@@ -32841,7 +32869,7 @@
       </c>
       <c r="I117" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J117" s="25" t="n"/>
@@ -32851,23 +32879,23 @@
         </is>
       </c>
       <c r="L117" s="26" t="n">
-        <v>203</v>
+        <v>-170</v>
       </c>
       <c r="M117" s="27" t="n">
-        <v>3.03</v>
+        <v>1.588235</v>
       </c>
       <c r="N117" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.62963</v>
       </c>
       <c r="O117" s="28" t="n">
-        <v>0.662587</v>
+        <v>0.541981</v>
       </c>
       <c r="P117" s="28" t="n"/>
       <c r="Q117" s="28" t="n">
-        <v>0.332554</v>
+        <v>-0.087649</v>
       </c>
       <c r="R117" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S117" s="29" t="n">
         <v>0</v>
@@ -32893,7 +32921,7 @@
       <c r="AD117" s="24" t="n"/>
       <c r="AE117" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-cs2-cs-sta-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-paina-rush-2026-07-31).</t>
         </is>
       </c>
       <c r="AF117" s="31" t="inlineStr">
@@ -32929,37 +32957,37 @@
       </c>
       <c r="AO117" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP117" s="24" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="AQ117" s="24" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="AR117" s="24" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="AS117" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Esports</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="AT117" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Esports</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="AU117" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Esports</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="AV117" s="24" t="n"/>
@@ -32977,7 +33005,7 @@
       </c>
       <c r="BA117" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BB117" s="24" t="inlineStr">
@@ -32992,7 +33020,7 @@
       </c>
       <c r="BD117" s="24" t="inlineStr">
         <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
+          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
         </is>
       </c>
       <c r="BE117" s="24" t="inlineStr">
@@ -33012,7 +33040,7 @@
       </c>
       <c r="BH117" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T16:55:42.899241Z</t>
+          <t>2026-07-30T17:21:57.236262Z</t>
         </is>
       </c>
       <c r="BI117" s="24" t="inlineStr">
@@ -33022,13 +33050,13 @@
       </c>
       <c r="BJ117" s="25" t="n"/>
       <c r="BK117" s="26" t="n">
-        <v>203</v>
+        <v>-170</v>
       </c>
       <c r="BL117" s="27" t="n">
-        <v>3.03</v>
+        <v>1.588235</v>
       </c>
       <c r="BM117" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.62963</v>
       </c>
       <c r="BN117" s="28" t="n"/>
       <c r="BO117" s="28" t="n"/>
@@ -33059,267 +33087,6 @@
       <c r="CN117" s="24" t="n"/>
       <c r="CO117" s="24" t="n"/>
     </row>
-    <row r="118" ht="36" customHeight="1">
-      <c r="A118" s="24" t="inlineStr">
-        <is>
-          <t>7d181f854cfc4eac</t>
-        </is>
-      </c>
-      <c r="B118" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T16:55:43.918344Z</t>
-        </is>
-      </c>
-      <c r="C118" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-31T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D118" s="24" t="inlineStr">
-        <is>
-          <t>65109</t>
-        </is>
-      </c>
-      <c r="E118" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F118" s="24" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
-      <c r="G118" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="H118" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I118" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J118" s="25" t="n"/>
-      <c r="K118" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L118" s="26" t="n">
-        <v>-170</v>
-      </c>
-      <c r="M118" s="27" t="n">
-        <v>1.588235</v>
-      </c>
-      <c r="N118" s="28" t="n">
-        <v>0.62963</v>
-      </c>
-      <c r="O118" s="28" t="n">
-        <v>0.541795</v>
-      </c>
-      <c r="P118" s="28" t="n"/>
-      <c r="Q118" s="28" t="n">
-        <v>-0.087835</v>
-      </c>
-      <c r="R118" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T118" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="U118" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V118" s="24" t="n"/>
-      <c r="W118" s="26" t="n"/>
-      <c r="X118" s="26" t="n"/>
-      <c r="Y118" s="25" t="n"/>
-      <c r="Z118" s="26" t="n"/>
-      <c r="AA118" s="28" t="n"/>
-      <c r="AB118" s="28" t="n"/>
-      <c r="AC118" s="30" t="n"/>
-      <c r="AD118" s="24" t="n"/>
-      <c r="AE118" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-paina-rush-2026-07-31).</t>
-        </is>
-      </c>
-      <c r="AF118" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG118" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH118" s="24" t="n"/>
-      <c r="AI118" s="31" t="n"/>
-      <c r="AJ118" s="31" t="n"/>
-      <c r="AK118" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL118" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM118" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN118" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO118" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP118" s="24" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
-      <c r="AQ118" s="24" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
-      <c r="AR118" s="24" t="inlineStr">
-        <is>
-          <t>Rush</t>
-        </is>
-      </c>
-      <c r="AS118" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AT118" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AU118" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AV118" s="24" t="n"/>
-      <c r="AW118" s="24" t="n"/>
-      <c r="AX118" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY118" s="24" t="n"/>
-      <c r="AZ118" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA118" s="24" t="inlineStr">
-        <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
-        </is>
-      </c>
-      <c r="BB118" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC118" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BD118" s="24" t="inlineStr">
-        <is>
-          <t>20e27ad25c309367babd477909aaf456b3eeff4b6a3d4b27706d8f38244b6304</t>
-        </is>
-      </c>
-      <c r="BE118" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF118" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG118" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v4</t>
-        </is>
-      </c>
-      <c r="BH118" s="24" t="inlineStr">
-        <is>
-          <t>2026-07-30T16:55:43.917299Z</t>
-        </is>
-      </c>
-      <c r="BI118" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ118" s="25" t="n"/>
-      <c r="BK118" s="26" t="n">
-        <v>-170</v>
-      </c>
-      <c r="BL118" s="27" t="n">
-        <v>1.588235</v>
-      </c>
-      <c r="BM118" s="28" t="n">
-        <v>0.62963</v>
-      </c>
-      <c r="BN118" s="28" t="n"/>
-      <c r="BO118" s="28" t="n"/>
-      <c r="BP118" s="25" t="n"/>
-      <c r="BQ118" s="27" t="n"/>
-      <c r="BR118" s="28" t="n"/>
-      <c r="BS118" s="28" t="n"/>
-      <c r="BT118" s="28" t="n"/>
-      <c r="BU118" s="25" t="n"/>
-      <c r="BV118" s="29" t="n"/>
-      <c r="BW118" s="24" t="n"/>
-      <c r="BX118" s="30" t="n"/>
-      <c r="BY118" s="27" t="n"/>
-      <c r="BZ118" s="24" t="n"/>
-      <c r="CA118" s="31" t="n"/>
-      <c r="CB118" s="24" t="n"/>
-      <c r="CC118" s="24" t="n"/>
-      <c r="CD118" s="24" t="n"/>
-      <c r="CE118" s="24" t="n"/>
-      <c r="CF118" s="24" t="n"/>
-      <c r="CG118" s="24" t="n"/>
-      <c r="CH118" s="24" t="n"/>
-      <c r="CI118" s="24" t="n"/>
-      <c r="CJ118" s="24" t="n"/>
-      <c r="CK118" s="24" t="n"/>
-      <c r="CL118" s="24" t="n"/>
-      <c r="CM118" s="24" t="n"/>
-      <c r="CN118" s="24" t="n"/>
-      <c r="CO118" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO117" headerRowCount="1">
-  <autoFilter ref="A1:CO117"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO118" headerRowCount="1">
+  <autoFilter ref="A1:CO118"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$117)</f>
+        <f>COUNTA('Picks'!$A$2:$A$118)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$117,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$118,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$117,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$118,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"win")+COUNTIFS('Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$118,"settled",'Picks'!$V$2:$V$118,"win")+COUNTIFS('Picks'!$U$2:$U$118,"settled",'Picks'!$V$2:$V$118,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$117,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$118,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$118,"&gt;0",'Picks'!$V$2:$V$118,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$118,"&gt;0",'Picks'!$V$2:$V$118,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"win")/(COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"win")+COUNTIFS('Picks'!$BX$2:$BX$117,"&gt;0",'Picks'!$V$2:$V$117,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$118,"&gt;0",'Picks'!$V$2:$V$118,"win")/(COUNTIFS('Picks'!$BX$2:$BX$118,"&gt;0",'Picks'!$V$2:$V$118,"win")+COUNTIFS('Picks'!$BX$2:$BX$118,"&gt;0",'Picks'!$V$2:$V$118,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$117)/SUM('Picks'!$BX$2:$BX$117),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$118)/SUM('Picks'!$BX$2:$BX$118),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$117)</f>
+        <f>SUM('Picks'!$BY$2:$BY$118)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$117,"&lt;&gt;",'Picks'!$AB$2:$AB$117),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$118,"&lt;&gt;",'Picks'!$AB$2:$AB$118),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$117,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$117,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$118,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$118,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$117,'Picks'!$AM$2:$AM$117,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$118,'Picks'!$AM$2:$AM$118,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$117,$A14,'Picks'!$U$2:$U$117,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$118,$A14,'Picks'!$U$2:$U$118,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$117,$A14,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$118,$A14,'Picks'!$U$2:$U$118,"settled",'Picks'!$V$2:$V$118,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$117,$A14,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$118,$A14,'Picks'!$U$2:$U$118,"settled",'Picks'!$V$2:$V$118,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$117,'Picks'!$H$2:$H$117,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$118,'Picks'!$H$2:$H$118,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$117,'Picks'!$H$2:$H$117,$A14,'Picks'!$U$2:$U$117,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$118,'Picks'!$H$2:$H$118,$A14,'Picks'!$U$2:$U$118,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$117,$A15,'Picks'!$U$2:$U$117,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$118,$A15,'Picks'!$U$2:$U$118,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$117,$A15,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$118,$A15,'Picks'!$U$2:$U$118,"settled",'Picks'!$V$2:$V$118,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$117,$A15,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$118,$A15,'Picks'!$U$2:$U$118,"settled",'Picks'!$V$2:$V$118,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$117,'Picks'!$H$2:$H$117,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$118,'Picks'!$H$2:$H$118,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$117,'Picks'!$H$2:$H$117,$A15,'Picks'!$U$2:$U$117,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$118,'Picks'!$H$2:$H$118,$A15,'Picks'!$U$2:$U$118,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$117,$A16,'Picks'!$U$2:$U$117,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$118,$A16,'Picks'!$U$2:$U$118,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$117,$A16,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$118,$A16,'Picks'!$U$2:$U$118,"settled",'Picks'!$V$2:$V$118,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$117,$A16,'Picks'!$U$2:$U$117,"settled",'Picks'!$V$2:$V$117,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$118,$A16,'Picks'!$U$2:$U$118,"settled",'Picks'!$V$2:$V$118,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$117,'Picks'!$H$2:$H$117,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$118,'Picks'!$H$2:$H$118,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$117,'Picks'!$H$2:$H$117,$A16,'Picks'!$U$2:$U$117,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$118,'Picks'!$H$2:$H$118,$A16,'Picks'!$U$2:$U$118,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO117"/>
+  <dimension ref="A1:CO118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -28653,12 +28653,12 @@
     <row r="101" ht="36" customHeight="1">
       <c r="A101" s="24" t="inlineStr">
         <is>
-          <t>92e6d786395a4cc3</t>
+          <t>cc11add30c6d4c33</t>
         </is>
       </c>
       <c r="B101" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C101" s="24" t="inlineStr">
@@ -28829,7 +28829,7 @@
       </c>
       <c r="BA101" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB101" s="24" t="inlineStr">
@@ -28844,7 +28844,7 @@
       </c>
       <c r="BD101" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE101" s="24" t="inlineStr">
@@ -28864,7 +28864,7 @@
       </c>
       <c r="BH101" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:39.226781Z</t>
+          <t>2026-07-30T17:39:16.378343Z</t>
         </is>
       </c>
       <c r="BI101" s="24" t="inlineStr">
@@ -28914,12 +28914,12 @@
     <row r="102" ht="36" customHeight="1">
       <c r="A102" s="24" t="inlineStr">
         <is>
-          <t>59024be33a944192</t>
+          <t>e169a4bf30f04457</t>
         </is>
       </c>
       <c r="B102" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C102" s="24" t="inlineStr">
@@ -29090,7 +29090,7 @@
       </c>
       <c r="BA102" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB102" s="24" t="inlineStr">
@@ -29105,7 +29105,7 @@
       </c>
       <c r="BD102" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE102" s="24" t="inlineStr">
@@ -29125,7 +29125,7 @@
       </c>
       <c r="BH102" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:39.762691Z</t>
+          <t>2026-07-30T17:39:16.963785Z</t>
         </is>
       </c>
       <c r="BI102" s="24" t="inlineStr">
@@ -29175,12 +29175,12 @@
     <row r="103" ht="36" customHeight="1">
       <c r="A103" s="24" t="inlineStr">
         <is>
-          <t>8f1497d766eb4ac6</t>
+          <t>8bcb181772a3459f</t>
         </is>
       </c>
       <c r="B103" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C103" s="24" t="inlineStr">
@@ -29190,7 +29190,7 @@
       </c>
       <c r="D103" s="24" t="inlineStr">
         <is>
-          <t>66613</t>
+          <t>66610</t>
         </is>
       </c>
       <c r="E103" s="24" t="inlineStr">
@@ -29200,12 +29200,12 @@
       </c>
       <c r="F103" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>LFO UKRAINE</t>
         </is>
       </c>
       <c r="G103" s="24" t="inlineStr">
         <is>
-          <t>Younglings</t>
+          <t>OldBoys</t>
         </is>
       </c>
       <c r="H103" s="24" t="inlineStr">
@@ -29225,26 +29225,26 @@
         </is>
       </c>
       <c r="L103" s="26" t="n">
-        <v>-117</v>
+        <v>122</v>
       </c>
       <c r="M103" s="27" t="n">
-        <v>1.854701</v>
+        <v>2.22</v>
       </c>
       <c r="N103" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.45045</v>
       </c>
       <c r="O103" s="28" t="n">
-        <v>0.576671</v>
+        <v>0.522969</v>
       </c>
       <c r="P103" s="28" t="n"/>
       <c r="Q103" s="28" t="n">
-        <v>0.0375</v>
+        <v>0.072519</v>
       </c>
       <c r="R103" s="26" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="S103" s="29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T103" s="24" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
       <c r="AD103" s="24" t="n"/>
       <c r="AE103" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-yl-bg-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-oboys-lfouk-2026-07-30).</t>
         </is>
       </c>
       <c r="AF103" s="31" t="inlineStr">
@@ -29285,7 +29285,7 @@
       <c r="AJ103" s="31" t="n"/>
       <c r="AK103" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL103" s="26" t="n">
@@ -29293,47 +29293,47 @@
       </c>
       <c r="AM103" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN103" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO103" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP103" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>LFO UKRAINE</t>
         </is>
       </c>
       <c r="AQ103" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>LFO UKRAINE</t>
         </is>
       </c>
       <c r="AR103" s="24" t="inlineStr">
         <is>
-          <t>Banger Gang</t>
+          <t>LFO UKRAINE</t>
         </is>
       </c>
       <c r="AS103" s="24" t="inlineStr">
         <is>
-          <t>Younglings</t>
+          <t>OldBoys</t>
         </is>
       </c>
       <c r="AT103" s="24" t="inlineStr">
         <is>
-          <t>Younglings</t>
+          <t>OldBoys</t>
         </is>
       </c>
       <c r="AU103" s="24" t="inlineStr">
         <is>
-          <t>Younglings</t>
+          <t>OldBoys</t>
         </is>
       </c>
       <c r="AV103" s="24" t="n"/>
@@ -29351,7 +29351,7 @@
       </c>
       <c r="BA103" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB103" s="24" t="inlineStr">
@@ -29366,7 +29366,7 @@
       </c>
       <c r="BD103" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE103" s="24" t="inlineStr">
@@ -29386,7 +29386,7 @@
       </c>
       <c r="BH103" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:40.939739Z</t>
+          <t>2026-07-30T17:39:18.083849Z</t>
         </is>
       </c>
       <c r="BI103" s="24" t="inlineStr">
@@ -29396,13 +29396,13 @@
       </c>
       <c r="BJ103" s="25" t="n"/>
       <c r="BK103" s="26" t="n">
-        <v>-117</v>
+        <v>122</v>
       </c>
       <c r="BL103" s="27" t="n">
-        <v>1.854701</v>
+        <v>2.22</v>
       </c>
       <c r="BM103" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.45045</v>
       </c>
       <c r="BN103" s="28" t="n"/>
       <c r="BO103" s="28" t="n"/>
@@ -29436,12 +29436,12 @@
     <row r="104" ht="36" customHeight="1">
       <c r="A104" s="24" t="inlineStr">
         <is>
-          <t>b2d8d5b49e1446fc</t>
+          <t>74167ca9bfcc41d8</t>
         </is>
       </c>
       <c r="B104" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C104" s="24" t="inlineStr">
@@ -29451,7 +29451,7 @@
       </c>
       <c r="D104" s="24" t="inlineStr">
         <is>
-          <t>66614</t>
+          <t>66611</t>
         </is>
       </c>
       <c r="E104" s="24" t="inlineStr">
@@ -29461,12 +29461,12 @@
       </c>
       <c r="F104" s="24" t="inlineStr">
         <is>
-          <t>NEXORA</t>
+          <t>Benched gods</t>
         </is>
       </c>
       <c r="G104" s="24" t="inlineStr">
         <is>
-          <t>Strael-Bora</t>
+          <t>Wave Esports</t>
         </is>
       </c>
       <c r="H104" s="24" t="inlineStr">
@@ -29476,7 +29476,7 @@
       </c>
       <c r="I104" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J104" s="25" t="n"/>
@@ -29486,26 +29486,26 @@
         </is>
       </c>
       <c r="L104" s="26" t="n">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="M104" s="27" t="n">
-        <v>2.33</v>
+        <v>2.78</v>
       </c>
       <c r="N104" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.359712</v>
       </c>
       <c r="O104" s="28" t="n">
-        <v>0.541314</v>
+        <v>0.534071</v>
       </c>
       <c r="P104" s="28" t="n"/>
       <c r="Q104" s="28" t="n">
-        <v>0.112129</v>
+        <v>0.174359</v>
       </c>
       <c r="R104" s="26" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="S104" s="29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T104" s="24" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
       <c r="AD104" s="24" t="n"/>
       <c r="AE104" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-cs2-sb-nexo-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-cs2-wave-bge-2026-07-30).</t>
         </is>
       </c>
       <c r="AF104" s="31" t="inlineStr">
@@ -29546,7 +29546,7 @@
       <c r="AJ104" s="31" t="n"/>
       <c r="AK104" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL104" s="26" t="n">
@@ -29554,47 +29554,47 @@
       </c>
       <c r="AM104" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN104" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO104" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP104" s="24" t="inlineStr">
         <is>
-          <t>NEXORA</t>
+          <t>Benched gods</t>
         </is>
       </c>
       <c r="AQ104" s="24" t="inlineStr">
         <is>
-          <t>NEXORA</t>
+          <t>Benched gods</t>
         </is>
       </c>
       <c r="AR104" s="24" t="inlineStr">
         <is>
-          <t>NEXORA</t>
+          <t>Benched gods</t>
         </is>
       </c>
       <c r="AS104" s="24" t="inlineStr">
         <is>
-          <t>Strael-Bora</t>
+          <t>Wave Esports</t>
         </is>
       </c>
       <c r="AT104" s="24" t="inlineStr">
         <is>
-          <t>Strael-Bora</t>
+          <t>Wave Esports</t>
         </is>
       </c>
       <c r="AU104" s="24" t="inlineStr">
         <is>
-          <t>Strael-Bora</t>
+          <t>Wave Esports</t>
         </is>
       </c>
       <c r="AV104" s="24" t="n"/>
@@ -29612,7 +29612,7 @@
       </c>
       <c r="BA104" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB104" s="24" t="inlineStr">
@@ -29627,7 +29627,7 @@
       </c>
       <c r="BD104" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE104" s="24" t="inlineStr">
@@ -29647,7 +29647,7 @@
       </c>
       <c r="BH104" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:41.486408Z</t>
+          <t>2026-07-30T17:39:18.653762Z</t>
         </is>
       </c>
       <c r="BI104" s="24" t="inlineStr">
@@ -29657,13 +29657,13 @@
       </c>
       <c r="BJ104" s="25" t="n"/>
       <c r="BK104" s="26" t="n">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="BL104" s="27" t="n">
-        <v>2.33</v>
+        <v>2.78</v>
       </c>
       <c r="BM104" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.359712</v>
       </c>
       <c r="BN104" s="28" t="n"/>
       <c r="BO104" s="28" t="n"/>
@@ -29697,12 +29697,12 @@
     <row r="105" ht="36" customHeight="1">
       <c r="A105" s="24" t="inlineStr">
         <is>
-          <t>0b57d92459db4322</t>
+          <t>bbcfb2bda4064ad0</t>
         </is>
       </c>
       <c r="B105" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C105" s="24" t="inlineStr">
@@ -29712,7 +29712,7 @@
       </c>
       <c r="D105" s="24" t="inlineStr">
         <is>
-          <t>66617</t>
+          <t>66613</t>
         </is>
       </c>
       <c r="E105" s="24" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="F105" s="24" t="inlineStr">
         <is>
-          <t>Hermine Esports Club</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="G105" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>Younglings</t>
         </is>
       </c>
       <c r="H105" s="24" t="inlineStr">
@@ -29747,26 +29747,26 @@
         </is>
       </c>
       <c r="L105" s="26" t="n">
-        <v>-104</v>
+        <v>-117</v>
       </c>
       <c r="M105" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.854701</v>
       </c>
       <c r="N105" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.539171</v>
       </c>
       <c r="O105" s="28" t="n">
-        <v>0.5549500000000001</v>
+        <v>0.576671</v>
       </c>
       <c r="P105" s="28" t="n"/>
       <c r="Q105" s="28" t="n">
-        <v>0.045146</v>
+        <v>0.0375</v>
       </c>
       <c r="R105" s="26" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="S105" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T105" s="24" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
       <c r="AD105" s="24" t="n"/>
       <c r="AE105" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-mel-hec-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-yl-bg-2026-07-30).</t>
         </is>
       </c>
       <c r="AF105" s="31" t="inlineStr">
@@ -29830,32 +29830,32 @@
       </c>
       <c r="AP105" s="24" t="inlineStr">
         <is>
-          <t>Hermine Esports Club</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AQ105" s="24" t="inlineStr">
         <is>
-          <t>Hermine Esports Club</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AR105" s="24" t="inlineStr">
         <is>
-          <t>Hermine Esports Club</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AS105" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>Younglings</t>
         </is>
       </c>
       <c r="AT105" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>Younglings</t>
         </is>
       </c>
       <c r="AU105" s="24" t="inlineStr">
         <is>
-          <t>mellren</t>
+          <t>Younglings</t>
         </is>
       </c>
       <c r="AV105" s="24" t="n"/>
@@ -29873,7 +29873,7 @@
       </c>
       <c r="BA105" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB105" s="24" t="inlineStr">
@@ -29888,7 +29888,7 @@
       </c>
       <c r="BD105" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE105" s="24" t="inlineStr">
@@ -29908,7 +29908,7 @@
       </c>
       <c r="BH105" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:42.057537Z</t>
+          <t>2026-07-30T17:39:19.238371Z</t>
         </is>
       </c>
       <c r="BI105" s="24" t="inlineStr">
@@ -29918,13 +29918,13 @@
       </c>
       <c r="BJ105" s="25" t="n"/>
       <c r="BK105" s="26" t="n">
-        <v>-104</v>
+        <v>-117</v>
       </c>
       <c r="BL105" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.854701</v>
       </c>
       <c r="BM105" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.539171</v>
       </c>
       <c r="BN105" s="28" t="n"/>
       <c r="BO105" s="28" t="n"/>
@@ -29958,12 +29958,12 @@
     <row r="106" ht="36" customHeight="1">
       <c r="A106" s="24" t="inlineStr">
         <is>
-          <t>98d5f75e5066475f</t>
+          <t>9759b28202ac4e46</t>
         </is>
       </c>
       <c r="B106" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C106" s="24" t="inlineStr">
@@ -29973,7 +29973,7 @@
       </c>
       <c r="D106" s="24" t="inlineStr">
         <is>
-          <t>66610</t>
+          <t>66614</t>
         </is>
       </c>
       <c r="E106" s="24" t="inlineStr">
@@ -29983,12 +29983,12 @@
       </c>
       <c r="F106" s="24" t="inlineStr">
         <is>
-          <t>LFO UKRAINE</t>
+          <t>NEXORA</t>
         </is>
       </c>
       <c r="G106" s="24" t="inlineStr">
         <is>
-          <t>OldBoys</t>
+          <t>Strael-Bora</t>
         </is>
       </c>
       <c r="H106" s="24" t="inlineStr">
@@ -29998,7 +29998,7 @@
       </c>
       <c r="I106" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J106" s="25" t="n"/>
@@ -30008,26 +30008,26 @@
         </is>
       </c>
       <c r="L106" s="26" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="M106" s="27" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="N106" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.429185</v>
       </c>
       <c r="O106" s="28" t="n">
-        <v>0.522969</v>
+        <v>0.541314</v>
       </c>
       <c r="P106" s="28" t="n"/>
       <c r="Q106" s="28" t="n">
-        <v>0.072519</v>
+        <v>0.112129</v>
       </c>
       <c r="R106" s="26" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="S106" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T106" s="24" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
       <c r="AD106" s="24" t="n"/>
       <c r="AE106" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-oboys-lfouk-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-cs2-sb-nexo-2026-07-30).</t>
         </is>
       </c>
       <c r="AF106" s="31" t="inlineStr">
@@ -30068,7 +30068,7 @@
       <c r="AJ106" s="31" t="n"/>
       <c r="AK106" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL106" s="26" t="n">
@@ -30076,47 +30076,47 @@
       </c>
       <c r="AM106" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN106" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO106" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP106" s="24" t="inlineStr">
         <is>
-          <t>LFO UKRAINE</t>
+          <t>NEXORA</t>
         </is>
       </c>
       <c r="AQ106" s="24" t="inlineStr">
         <is>
-          <t>LFO UKRAINE</t>
+          <t>NEXORA</t>
         </is>
       </c>
       <c r="AR106" s="24" t="inlineStr">
         <is>
-          <t>LFO UKRAINE</t>
+          <t>NEXORA</t>
         </is>
       </c>
       <c r="AS106" s="24" t="inlineStr">
         <is>
-          <t>OldBoys</t>
+          <t>Strael-Bora</t>
         </is>
       </c>
       <c r="AT106" s="24" t="inlineStr">
         <is>
-          <t>OldBoys</t>
+          <t>Strael-Bora</t>
         </is>
       </c>
       <c r="AU106" s="24" t="inlineStr">
         <is>
-          <t>OldBoys</t>
+          <t>Strael-Bora</t>
         </is>
       </c>
       <c r="AV106" s="24" t="n"/>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="BA106" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB106" s="24" t="inlineStr">
@@ -30149,7 +30149,7 @@
       </c>
       <c r="BD106" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE106" s="24" t="inlineStr">
@@ -30169,7 +30169,7 @@
       </c>
       <c r="BH106" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:43.123721Z</t>
+          <t>2026-07-30T17:39:19.828746Z</t>
         </is>
       </c>
       <c r="BI106" s="24" t="inlineStr">
@@ -30179,13 +30179,13 @@
       </c>
       <c r="BJ106" s="25" t="n"/>
       <c r="BK106" s="26" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="BL106" s="27" t="n">
-        <v>2.22</v>
+        <v>2.33</v>
       </c>
       <c r="BM106" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.429185</v>
       </c>
       <c r="BN106" s="28" t="n"/>
       <c r="BO106" s="28" t="n"/>
@@ -30219,12 +30219,12 @@
     <row r="107" ht="36" customHeight="1">
       <c r="A107" s="24" t="inlineStr">
         <is>
-          <t>e48aa89383564c1b</t>
+          <t>799c4b2c7f4e47fc</t>
         </is>
       </c>
       <c r="B107" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C107" s="24" t="inlineStr">
@@ -30234,7 +30234,7 @@
       </c>
       <c r="D107" s="24" t="inlineStr">
         <is>
-          <t>66611</t>
+          <t>66617</t>
         </is>
       </c>
       <c r="E107" s="24" t="inlineStr">
@@ -30244,12 +30244,12 @@
       </c>
       <c r="F107" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>Hermine Esports Club</t>
         </is>
       </c>
       <c r="G107" s="24" t="inlineStr">
         <is>
-          <t>Wave Esports</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="H107" s="24" t="inlineStr">
@@ -30269,26 +30269,26 @@
         </is>
       </c>
       <c r="L107" s="26" t="n">
-        <v>178</v>
+        <v>-113</v>
       </c>
       <c r="M107" s="27" t="n">
-        <v>2.78</v>
+        <v>1.884956</v>
       </c>
       <c r="N107" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.530516</v>
       </c>
       <c r="O107" s="28" t="n">
-        <v>0.534071</v>
+        <v>0.6041840000000001</v>
       </c>
       <c r="P107" s="28" t="n"/>
       <c r="Q107" s="28" t="n">
-        <v>0.174359</v>
+        <v>0.073668</v>
       </c>
       <c r="R107" s="26" t="n">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="S107" s="29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T107" s="24" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
       <c r="AD107" s="24" t="n"/>
       <c r="AE107" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3600 (market_slug=aec-cs2-wave-bge-2026-07-30).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-cs2-mel-hec-2026-07-30).</t>
         </is>
       </c>
       <c r="AF107" s="31" t="inlineStr">
@@ -30329,7 +30329,7 @@
       <c r="AJ107" s="31" t="n"/>
       <c r="AK107" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL107" s="26" t="n">
@@ -30337,47 +30337,47 @@
       </c>
       <c r="AM107" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN107" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO107" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP107" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>Hermine Esports Club</t>
         </is>
       </c>
       <c r="AQ107" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>Hermine Esports Club</t>
         </is>
       </c>
       <c r="AR107" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>Hermine Esports Club</t>
         </is>
       </c>
       <c r="AS107" s="24" t="inlineStr">
         <is>
-          <t>Wave Esports</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="AT107" s="24" t="inlineStr">
         <is>
-          <t>Wave Esports</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="AU107" s="24" t="inlineStr">
         <is>
-          <t>Wave Esports</t>
+          <t>mellren</t>
         </is>
       </c>
       <c r="AV107" s="24" t="n"/>
@@ -30395,7 +30395,7 @@
       </c>
       <c r="BA107" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB107" s="24" t="inlineStr">
@@ -30410,7 +30410,7 @@
       </c>
       <c r="BD107" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE107" s="24" t="inlineStr">
@@ -30430,7 +30430,7 @@
       </c>
       <c r="BH107" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:43.729769Z</t>
+          <t>2026-07-30T17:39:20.974476Z</t>
         </is>
       </c>
       <c r="BI107" s="24" t="inlineStr">
@@ -30440,13 +30440,13 @@
       </c>
       <c r="BJ107" s="25" t="n"/>
       <c r="BK107" s="26" t="n">
-        <v>178</v>
+        <v>-113</v>
       </c>
       <c r="BL107" s="27" t="n">
-        <v>2.78</v>
+        <v>1.884956</v>
       </c>
       <c r="BM107" s="28" t="n">
-        <v>0.359712</v>
+        <v>0.530516</v>
       </c>
       <c r="BN107" s="28" t="n"/>
       <c r="BO107" s="28" t="n"/>
@@ -30480,12 +30480,12 @@
     <row r="108" ht="36" customHeight="1">
       <c r="A108" s="24" t="inlineStr">
         <is>
-          <t>3c961bbafdc54f09</t>
+          <t>ca11b120ae53451a</t>
         </is>
       </c>
       <c r="B108" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C108" s="24" t="inlineStr">
@@ -30656,7 +30656,7 @@
       </c>
       <c r="BA108" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB108" s="24" t="inlineStr">
@@ -30671,7 +30671,7 @@
       </c>
       <c r="BD108" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE108" s="24" t="inlineStr">
@@ -30691,7 +30691,7 @@
       </c>
       <c r="BH108" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:44.257986Z</t>
+          <t>2026-07-30T17:39:21.455371Z</t>
         </is>
       </c>
       <c r="BI108" s="24" t="inlineStr">
@@ -30741,12 +30741,12 @@
     <row r="109" ht="36" customHeight="1">
       <c r="A109" s="24" t="inlineStr">
         <is>
-          <t>a405ebf6921142a4</t>
+          <t>02a1c87665ab464d</t>
         </is>
       </c>
       <c r="B109" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C109" s="24" t="inlineStr">
@@ -30917,7 +30917,7 @@
       </c>
       <c r="BA109" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB109" s="24" t="inlineStr">
@@ -30932,7 +30932,7 @@
       </c>
       <c r="BD109" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE109" s="24" t="inlineStr">
@@ -30952,7 +30952,7 @@
       </c>
       <c r="BH109" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:45.323638Z</t>
+          <t>2026-07-30T17:39:22.557396Z</t>
         </is>
       </c>
       <c r="BI109" s="24" t="inlineStr">
@@ -31002,12 +31002,12 @@
     <row r="110" ht="36" customHeight="1">
       <c r="A110" s="24" t="inlineStr">
         <is>
-          <t>c8b8655f1314492a</t>
+          <t>e37e5dc67c1a4d7c</t>
         </is>
       </c>
       <c r="B110" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C110" s="24" t="inlineStr">
@@ -31017,7 +31017,7 @@
       </c>
       <c r="D110" s="24" t="inlineStr">
         <is>
-          <t>66545</t>
+          <t>66535</t>
         </is>
       </c>
       <c r="E110" s="24" t="inlineStr">
@@ -31027,12 +31027,12 @@
       </c>
       <c r="F110" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="G110" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Infinite</t>
         </is>
       </c>
       <c r="H110" s="24" t="inlineStr">
@@ -31052,23 +31052,23 @@
         </is>
       </c>
       <c r="L110" s="26" t="n">
-        <v>-108</v>
+        <v>-127</v>
       </c>
       <c r="M110" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.787402</v>
       </c>
       <c r="N110" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O110" s="28" t="n">
-        <v>0.676465</v>
+        <v>0.688286</v>
       </c>
       <c r="P110" s="28" t="n"/>
       <c r="Q110" s="28" t="n">
-        <v>0.157234</v>
+        <v>0.128815</v>
       </c>
       <c r="R110" s="26" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="S110" s="29" t="n">
         <v>2</v>
@@ -31094,7 +31094,7 @@
       <c r="AD110" s="24" t="n"/>
       <c r="AE110" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-bmb-lc-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-cs2-inf-sparta-2026-07-31).</t>
         </is>
       </c>
       <c r="AF110" s="31" t="inlineStr">
@@ -31135,32 +31135,32 @@
       </c>
       <c r="AP110" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AQ110" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AR110" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AS110" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Infinite</t>
         </is>
       </c>
       <c r="AT110" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Infinite</t>
         </is>
       </c>
       <c r="AU110" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Infinite</t>
         </is>
       </c>
       <c r="AV110" s="24" t="n"/>
@@ -31178,7 +31178,7 @@
       </c>
       <c r="BA110" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB110" s="24" t="inlineStr">
@@ -31193,7 +31193,7 @@
       </c>
       <c r="BD110" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE110" s="24" t="inlineStr">
@@ -31213,7 +31213,7 @@
       </c>
       <c r="BH110" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:45.909267Z</t>
+          <t>2026-07-30T17:39:24.025060Z</t>
         </is>
       </c>
       <c r="BI110" s="24" t="inlineStr">
@@ -31223,13 +31223,13 @@
       </c>
       <c r="BJ110" s="25" t="n"/>
       <c r="BK110" s="26" t="n">
-        <v>-108</v>
+        <v>-127</v>
       </c>
       <c r="BL110" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.787402</v>
       </c>
       <c r="BM110" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN110" s="28" t="n"/>
       <c r="BO110" s="28" t="n"/>
@@ -31263,12 +31263,12 @@
     <row r="111" ht="36" customHeight="1">
       <c r="A111" s="24" t="inlineStr">
         <is>
-          <t>08875836e52b464b</t>
+          <t>8603055062c14cae</t>
         </is>
       </c>
       <c r="B111" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C111" s="24" t="inlineStr">
@@ -31278,7 +31278,7 @@
       </c>
       <c r="D111" s="24" t="inlineStr">
         <is>
-          <t>66535</t>
+          <t>66545</t>
         </is>
       </c>
       <c r="E111" s="24" t="inlineStr">
@@ -31288,12 +31288,12 @@
       </c>
       <c r="F111" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="G111" s="24" t="inlineStr">
         <is>
-          <t>Infinite</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="H111" s="24" t="inlineStr">
@@ -31313,23 +31313,23 @@
         </is>
       </c>
       <c r="L111" s="26" t="n">
-        <v>-127</v>
+        <v>-108</v>
       </c>
       <c r="M111" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.925926</v>
       </c>
       <c r="N111" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.519231</v>
       </c>
       <c r="O111" s="28" t="n">
-        <v>0.688286</v>
+        <v>0.676465</v>
       </c>
       <c r="P111" s="28" t="n"/>
       <c r="Q111" s="28" t="n">
-        <v>0.128815</v>
+        <v>0.157234</v>
       </c>
       <c r="R111" s="26" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="S111" s="29" t="n">
         <v>2</v>
@@ -31355,7 +31355,7 @@
       <c r="AD111" s="24" t="n"/>
       <c r="AE111" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-cs2-inf-sparta-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.5200 (market_slug=aec-cs2-bmb-lc-2026-07-31).</t>
         </is>
       </c>
       <c r="AF111" s="31" t="inlineStr">
@@ -31396,32 +31396,32 @@
       </c>
       <c r="AP111" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AQ111" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AR111" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AS111" s="24" t="inlineStr">
         <is>
-          <t>Infinite</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AT111" s="24" t="inlineStr">
         <is>
-          <t>Infinite</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AU111" s="24" t="inlineStr">
         <is>
-          <t>Infinite</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AV111" s="24" t="n"/>
@@ -31439,7 +31439,7 @@
       </c>
       <c r="BA111" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB111" s="24" t="inlineStr">
@@ -31454,7 +31454,7 @@
       </c>
       <c r="BD111" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE111" s="24" t="inlineStr">
@@ -31474,7 +31474,7 @@
       </c>
       <c r="BH111" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:47.628354Z</t>
+          <t>2026-07-30T17:39:24.587765Z</t>
         </is>
       </c>
       <c r="BI111" s="24" t="inlineStr">
@@ -31484,13 +31484,13 @@
       </c>
       <c r="BJ111" s="25" t="n"/>
       <c r="BK111" s="26" t="n">
-        <v>-127</v>
+        <v>-108</v>
       </c>
       <c r="BL111" s="27" t="n">
-        <v>1.787402</v>
+        <v>1.925926</v>
       </c>
       <c r="BM111" s="28" t="n">
-        <v>0.5594710000000001</v>
+        <v>0.519231</v>
       </c>
       <c r="BN111" s="28" t="n"/>
       <c r="BO111" s="28" t="n"/>
@@ -31524,12 +31524,12 @@
     <row r="112" ht="36" customHeight="1">
       <c r="A112" s="24" t="inlineStr">
         <is>
-          <t>f187fe1ca4924cc0</t>
+          <t>fb7763419d7d45d1</t>
         </is>
       </c>
       <c r="B112" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C112" s="24" t="inlineStr">
@@ -31700,7 +31700,7 @@
       </c>
       <c r="BA112" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB112" s="24" t="inlineStr">
@@ -31715,7 +31715,7 @@
       </c>
       <c r="BD112" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE112" s="24" t="inlineStr">
@@ -31735,7 +31735,7 @@
       </c>
       <c r="BH112" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:49.268706Z</t>
+          <t>2026-07-30T17:39:26.656791Z</t>
         </is>
       </c>
       <c r="BI112" s="24" t="inlineStr">
@@ -31785,22 +31785,22 @@
     <row r="113" ht="36" customHeight="1">
       <c r="A113" s="24" t="inlineStr">
         <is>
-          <t>96c160cdb00f46c5</t>
+          <t>261f2f66de0d4317</t>
         </is>
       </c>
       <c r="B113" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C113" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T14:00:00Z</t>
+          <t>2026-07-31T12:30:00Z</t>
         </is>
       </c>
       <c r="D113" s="24" t="inlineStr">
         <is>
-          <t>64927</t>
+          <t>66411</t>
         </is>
       </c>
       <c r="E113" s="24" t="inlineStr">
@@ -31810,12 +31810,12 @@
       </c>
       <c r="F113" s="24" t="inlineStr">
         <is>
-          <t>Trainwrecks eSports</t>
+          <t>MOUZ</t>
         </is>
       </c>
       <c r="G113" s="24" t="inlineStr">
         <is>
-          <t>ROUNDS</t>
+          <t>3DMAX</t>
         </is>
       </c>
       <c r="H113" s="24" t="inlineStr">
@@ -31825,7 +31825,7 @@
       </c>
       <c r="I113" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J113" s="25" t="n"/>
@@ -31835,26 +31835,26 @@
         </is>
       </c>
       <c r="L113" s="26" t="n">
-        <v>-178</v>
+        <v>-156</v>
       </c>
       <c r="M113" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.641026</v>
       </c>
       <c r="N113" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.609375</v>
       </c>
       <c r="O113" s="28" t="n">
-        <v>0.644533</v>
+        <v>0.671079</v>
       </c>
       <c r="P113" s="28" t="n"/>
       <c r="Q113" s="28" t="n">
-        <v>0.004245</v>
+        <v>0.061704</v>
       </c>
       <c r="R113" s="26" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="S113" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T113" s="24" t="inlineStr">
         <is>
@@ -31877,7 +31877,7 @@
       <c r="AD113" s="24" t="n"/>
       <c r="AE113" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-rgg-tera-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-3dmax-mouz-2026-07-31).</t>
         </is>
       </c>
       <c r="AF113" s="31" t="inlineStr">
@@ -31895,7 +31895,7 @@
       <c r="AJ113" s="31" t="n"/>
       <c r="AK113" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL113" s="26" t="n">
@@ -31903,47 +31903,47 @@
       </c>
       <c r="AM113" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN113" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO113" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP113" s="24" t="inlineStr">
         <is>
-          <t>Trainwrecks eSports</t>
+          <t>MOUZ</t>
         </is>
       </c>
       <c r="AQ113" s="24" t="inlineStr">
         <is>
-          <t>Trainwrecks eSports</t>
+          <t>MOUZ</t>
         </is>
       </c>
       <c r="AR113" s="24" t="inlineStr">
         <is>
-          <t>Trainwrecks eSports</t>
+          <t>MOUZ</t>
         </is>
       </c>
       <c r="AS113" s="24" t="inlineStr">
         <is>
-          <t>ROUNDS</t>
+          <t>3DMAX</t>
         </is>
       </c>
       <c r="AT113" s="24" t="inlineStr">
         <is>
-          <t>ROUNDS</t>
+          <t>3DMAX</t>
         </is>
       </c>
       <c r="AU113" s="24" t="inlineStr">
         <is>
-          <t>ROUNDS</t>
+          <t>3DMAX</t>
         </is>
       </c>
       <c r="AV113" s="24" t="n"/>
@@ -31961,7 +31961,7 @@
       </c>
       <c r="BA113" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB113" s="24" t="inlineStr">
@@ -31976,7 +31976,7 @@
       </c>
       <c r="BD113" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE113" s="24" t="inlineStr">
@@ -31996,7 +31996,7 @@
       </c>
       <c r="BH113" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:53.385941Z</t>
+          <t>2026-07-30T17:39:29.166587Z</t>
         </is>
       </c>
       <c r="BI113" s="24" t="inlineStr">
@@ -32006,13 +32006,13 @@
       </c>
       <c r="BJ113" s="25" t="n"/>
       <c r="BK113" s="26" t="n">
-        <v>-178</v>
+        <v>-156</v>
       </c>
       <c r="BL113" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.641026</v>
       </c>
       <c r="BM113" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.609375</v>
       </c>
       <c r="BN113" s="28" t="n"/>
       <c r="BO113" s="28" t="n"/>
@@ -32046,12 +32046,12 @@
     <row r="114" ht="36" customHeight="1">
       <c r="A114" s="24" t="inlineStr">
         <is>
-          <t>4d785da94abe40ff</t>
+          <t>21099c68c04344f2</t>
         </is>
       </c>
       <c r="B114" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C114" s="24" t="inlineStr">
@@ -32061,7 +32061,7 @@
       </c>
       <c r="D114" s="24" t="inlineStr">
         <is>
-          <t>66549</t>
+          <t>64927</t>
         </is>
       </c>
       <c r="E114" s="24" t="inlineStr">
@@ -32071,12 +32071,12 @@
       </c>
       <c r="F114" s="24" t="inlineStr">
         <is>
-          <t>megoshort</t>
+          <t>Trainwrecks eSports</t>
         </is>
       </c>
       <c r="G114" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>ROUNDS</t>
         </is>
       </c>
       <c r="H114" s="24" t="inlineStr">
@@ -32096,26 +32096,26 @@
         </is>
       </c>
       <c r="L114" s="26" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="M114" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.561798</v>
       </c>
       <c r="N114" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.640288</v>
       </c>
       <c r="O114" s="28" t="n">
-        <v>0.698051</v>
+        <v>0.644533</v>
       </c>
       <c r="P114" s="28" t="n"/>
       <c r="Q114" s="28" t="n">
-        <v>0.068421</v>
+        <v>0.004245</v>
       </c>
       <c r="R114" s="26" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="S114" s="29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T114" s="24" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
       <c r="AD114" s="24" t="n"/>
       <c r="AE114" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-lav-mego-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-rgg-tera-2026-07-31).</t>
         </is>
       </c>
       <c r="AF114" s="31" t="inlineStr">
@@ -32156,7 +32156,7 @@
       <c r="AJ114" s="31" t="n"/>
       <c r="AK114" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL114" s="26" t="n">
@@ -32164,47 +32164,47 @@
       </c>
       <c r="AM114" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN114" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO114" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP114" s="24" t="inlineStr">
         <is>
-          <t>megoshort</t>
+          <t>Trainwrecks eSports</t>
         </is>
       </c>
       <c r="AQ114" s="24" t="inlineStr">
         <is>
-          <t>megoshort</t>
+          <t>Trainwrecks eSports</t>
         </is>
       </c>
       <c r="AR114" s="24" t="inlineStr">
         <is>
-          <t>megoshort</t>
+          <t>Trainwrecks eSports</t>
         </is>
       </c>
       <c r="AS114" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>ROUNDS</t>
         </is>
       </c>
       <c r="AT114" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>ROUNDS</t>
         </is>
       </c>
       <c r="AU114" s="24" t="inlineStr">
         <is>
-          <t>Lavked</t>
+          <t>ROUNDS</t>
         </is>
       </c>
       <c r="AV114" s="24" t="n"/>
@@ -32222,7 +32222,7 @@
       </c>
       <c r="BA114" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB114" s="24" t="inlineStr">
@@ -32237,7 +32237,7 @@
       </c>
       <c r="BD114" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE114" s="24" t="inlineStr">
@@ -32257,7 +32257,7 @@
       </c>
       <c r="BH114" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:54.000232Z</t>
+          <t>2026-07-30T17:39:30.221823Z</t>
         </is>
       </c>
       <c r="BI114" s="24" t="inlineStr">
@@ -32267,13 +32267,13 @@
       </c>
       <c r="BJ114" s="25" t="n"/>
       <c r="BK114" s="26" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="BL114" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.561798</v>
       </c>
       <c r="BM114" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.640288</v>
       </c>
       <c r="BN114" s="28" t="n"/>
       <c r="BO114" s="28" t="n"/>
@@ -32307,22 +32307,22 @@
     <row r="115" ht="36" customHeight="1">
       <c r="A115" s="24" t="inlineStr">
         <is>
-          <t>620107eee4424354</t>
+          <t>3ff24e9835444273</t>
         </is>
       </c>
       <c r="B115" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C115" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T17:00:00Z</t>
+          <t>2026-07-31T14:00:00Z</t>
         </is>
       </c>
       <c r="D115" s="24" t="inlineStr">
         <is>
-          <t>66536</t>
+          <t>66549</t>
         </is>
       </c>
       <c r="E115" s="24" t="inlineStr">
@@ -32332,12 +32332,12 @@
       </c>
       <c r="F115" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>megoshort</t>
         </is>
       </c>
       <c r="G115" s="24" t="inlineStr">
         <is>
-          <t>JiJieHao</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="H115" s="24" t="inlineStr">
@@ -32357,23 +32357,23 @@
         </is>
       </c>
       <c r="L115" s="26" t="n">
-        <v>-213</v>
+        <v>-178</v>
       </c>
       <c r="M115" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.561798</v>
       </c>
       <c r="N115" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.640288</v>
       </c>
       <c r="O115" s="28" t="n">
-        <v>0.71083</v>
+        <v>0.698051</v>
       </c>
       <c r="P115" s="28" t="n"/>
       <c r="Q115" s="28" t="n">
-        <v>0.030319</v>
+        <v>0.057763</v>
       </c>
       <c r="R115" s="26" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="S115" s="29" t="n">
         <v>2</v>
@@ -32399,7 +32399,7 @@
       <c r="AD115" s="24" t="n"/>
       <c r="AE115" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jjh-bpl-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-lav-mego-2026-07-31).</t>
         </is>
       </c>
       <c r="AF115" s="31" t="inlineStr">
@@ -32440,32 +32440,32 @@
       </c>
       <c r="AP115" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>megoshort</t>
         </is>
       </c>
       <c r="AQ115" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>megoshort</t>
         </is>
       </c>
       <c r="AR115" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>megoshort</t>
         </is>
       </c>
       <c r="AS115" s="24" t="inlineStr">
         <is>
-          <t>JiJieHao</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AT115" s="24" t="inlineStr">
         <is>
-          <t>JiJieHao</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AU115" s="24" t="inlineStr">
         <is>
-          <t>JiJieHao</t>
+          <t>Lavked</t>
         </is>
       </c>
       <c r="AV115" s="24" t="n"/>
@@ -32483,7 +32483,7 @@
       </c>
       <c r="BA115" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB115" s="24" t="inlineStr">
@@ -32498,7 +32498,7 @@
       </c>
       <c r="BD115" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE115" s="24" t="inlineStr">
@@ -32518,7 +32518,7 @@
       </c>
       <c r="BH115" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:54.989141Z</t>
+          <t>2026-07-30T17:39:30.737863Z</t>
         </is>
       </c>
       <c r="BI115" s="24" t="inlineStr">
@@ -32528,13 +32528,13 @@
       </c>
       <c r="BJ115" s="25" t="n"/>
       <c r="BK115" s="26" t="n">
-        <v>-213</v>
+        <v>-178</v>
       </c>
       <c r="BL115" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.561798</v>
       </c>
       <c r="BM115" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.640288</v>
       </c>
       <c r="BN115" s="28" t="n"/>
       <c r="BO115" s="28" t="n"/>
@@ -32568,12 +32568,12 @@
     <row r="116" ht="36" customHeight="1">
       <c r="A116" s="24" t="inlineStr">
         <is>
-          <t>e5a0a39cbd2c4206</t>
+          <t>fc0bb373ae4a40cb</t>
         </is>
       </c>
       <c r="B116" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C116" s="24" t="inlineStr">
@@ -32583,7 +32583,7 @@
       </c>
       <c r="D116" s="24" t="inlineStr">
         <is>
-          <t>66547</t>
+          <t>66536</t>
         </is>
       </c>
       <c r="E116" s="24" t="inlineStr">
@@ -32593,12 +32593,12 @@
       </c>
       <c r="F116" s="24" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="G116" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Esports</t>
+          <t>JiJieHao</t>
         </is>
       </c>
       <c r="H116" s="24" t="inlineStr">
@@ -32608,7 +32608,7 @@
       </c>
       <c r="I116" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J116" s="25" t="n"/>
@@ -32618,26 +32618,26 @@
         </is>
       </c>
       <c r="L116" s="26" t="n">
-        <v>203</v>
+        <v>-213</v>
       </c>
       <c r="M116" s="27" t="n">
-        <v>3.03</v>
+        <v>1.469484</v>
       </c>
       <c r="N116" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.680511</v>
       </c>
       <c r="O116" s="28" t="n">
-        <v>0.6625490000000001</v>
+        <v>0.71083</v>
       </c>
       <c r="P116" s="28" t="n"/>
       <c r="Q116" s="28" t="n">
-        <v>0.332516</v>
+        <v>0.030319</v>
       </c>
       <c r="R116" s="26" t="n">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="S116" s="29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T116" s="24" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
       <c r="AD116" s="24" t="n"/>
       <c r="AE116" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-cs2-cs-sta-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jjh-bpl-2026-07-31).</t>
         </is>
       </c>
       <c r="AF116" s="31" t="inlineStr">
@@ -32678,7 +32678,7 @@
       <c r="AJ116" s="31" t="n"/>
       <c r="AK116" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL116" s="26" t="n">
@@ -32686,47 +32686,47 @@
       </c>
       <c r="AM116" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN116" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO116" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP116" s="24" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AQ116" s="24" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AR116" s="24" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AS116" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Esports</t>
+          <t>JiJieHao</t>
         </is>
       </c>
       <c r="AT116" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Esports</t>
+          <t>JiJieHao</t>
         </is>
       </c>
       <c r="AU116" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Esports</t>
+          <t>JiJieHao</t>
         </is>
       </c>
       <c r="AV116" s="24" t="n"/>
@@ -32744,7 +32744,7 @@
       </c>
       <c r="BA116" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB116" s="24" t="inlineStr">
@@ -32759,7 +32759,7 @@
       </c>
       <c r="BD116" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE116" s="24" t="inlineStr">
@@ -32779,7 +32779,7 @@
       </c>
       <c r="BH116" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:55.589981Z</t>
+          <t>2026-07-30T17:39:32.209281Z</t>
         </is>
       </c>
       <c r="BI116" s="24" t="inlineStr">
@@ -32789,13 +32789,13 @@
       </c>
       <c r="BJ116" s="25" t="n"/>
       <c r="BK116" s="26" t="n">
-        <v>203</v>
+        <v>-213</v>
       </c>
       <c r="BL116" s="27" t="n">
-        <v>3.03</v>
+        <v>1.469484</v>
       </c>
       <c r="BM116" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.680511</v>
       </c>
       <c r="BN116" s="28" t="n"/>
       <c r="BO116" s="28" t="n"/>
@@ -32829,22 +32829,22 @@
     <row r="117" ht="36" customHeight="1">
       <c r="A117" s="24" t="inlineStr">
         <is>
-          <t>c8a3c7c1e18349d0</t>
+          <t>1745fd49c3cf4456</t>
         </is>
       </c>
       <c r="B117" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.239232Z</t>
+          <t>2026-07-30T17:39:33.709014Z</t>
         </is>
       </c>
       <c r="C117" s="24" t="inlineStr">
         <is>
-          <t>2026-07-31T18:00:00Z</t>
+          <t>2026-07-31T17:00:00Z</t>
         </is>
       </c>
       <c r="D117" s="24" t="inlineStr">
         <is>
-          <t>65109</t>
+          <t>66547</t>
         </is>
       </c>
       <c r="E117" s="24" t="inlineStr">
@@ -32854,12 +32854,12 @@
       </c>
       <c r="F117" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="G117" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>CYBERSHOKE Esports</t>
         </is>
       </c>
       <c r="H117" s="24" t="inlineStr">
@@ -32869,7 +32869,7 @@
       </c>
       <c r="I117" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J117" s="25" t="n"/>
@@ -32879,23 +32879,23 @@
         </is>
       </c>
       <c r="L117" s="26" t="n">
-        <v>-170</v>
+        <v>203</v>
       </c>
       <c r="M117" s="27" t="n">
-        <v>1.588235</v>
+        <v>3.03</v>
       </c>
       <c r="N117" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.330033</v>
       </c>
       <c r="O117" s="28" t="n">
-        <v>0.541981</v>
+        <v>0.6625490000000001</v>
       </c>
       <c r="P117" s="28" t="n"/>
       <c r="Q117" s="28" t="n">
-        <v>-0.087649</v>
+        <v>0.332516</v>
       </c>
       <c r="R117" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S117" s="29" t="n">
         <v>0</v>
@@ -32921,7 +32921,7 @@
       <c r="AD117" s="24" t="n"/>
       <c r="AE117" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-paina-rush-2026-07-31).</t>
+          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-cs2-cs-sta-2026-07-31).</t>
         </is>
       </c>
       <c r="AF117" s="31" t="inlineStr">
@@ -32957,37 +32957,37 @@
       </c>
       <c r="AO117" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP117" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="AQ117" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="AR117" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="AS117" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>CYBERSHOKE Esports</t>
         </is>
       </c>
       <c r="AT117" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>CYBERSHOKE Esports</t>
         </is>
       </c>
       <c r="AU117" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>CYBERSHOKE Esports</t>
         </is>
       </c>
       <c r="AV117" s="24" t="n"/>
@@ -33005,7 +33005,7 @@
       </c>
       <c r="BA117" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BB117" s="24" t="inlineStr">
@@ -33020,7 +33020,7 @@
       </c>
       <c r="BD117" s="24" t="inlineStr">
         <is>
-          <t>18d8584fd12db2518575a2d8c1f78fa5fe4fd17b7dabdb05853c15298a7d39d8</t>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
         </is>
       </c>
       <c r="BE117" s="24" t="inlineStr">
@@ -33040,7 +33040,7 @@
       </c>
       <c r="BH117" s="24" t="inlineStr">
         <is>
-          <t>2026-07-30T17:21:57.236262Z</t>
+          <t>2026-07-30T17:39:32.703384Z</t>
         </is>
       </c>
       <c r="BI117" s="24" t="inlineStr">
@@ -33050,13 +33050,13 @@
       </c>
       <c r="BJ117" s="25" t="n"/>
       <c r="BK117" s="26" t="n">
-        <v>-170</v>
+        <v>203</v>
       </c>
       <c r="BL117" s="27" t="n">
-        <v>1.588235</v>
+        <v>3.03</v>
       </c>
       <c r="BM117" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.330033</v>
       </c>
       <c r="BN117" s="28" t="n"/>
       <c r="BO117" s="28" t="n"/>
@@ -33087,6 +33087,267 @@
       <c r="CN117" s="24" t="n"/>
       <c r="CO117" s="24" t="n"/>
     </row>
+    <row r="118" ht="36" customHeight="1">
+      <c r="A118" s="24" t="inlineStr">
+        <is>
+          <t>d282c6364bfb455d</t>
+        </is>
+      </c>
+      <c r="B118" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:39:33.709014Z</t>
+        </is>
+      </c>
+      <c r="C118" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-31T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D118" s="24" t="inlineStr">
+        <is>
+          <t>65109</t>
+        </is>
+      </c>
+      <c r="E118" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F118" s="24" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="G118" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="H118" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I118" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J118" s="25" t="n"/>
+      <c r="K118" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L118" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M118" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N118" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O118" s="28" t="n">
+        <v>0.541981</v>
+      </c>
+      <c r="P118" s="28" t="n"/>
+      <c r="Q118" s="28" t="n">
+        <v>-0.087649</v>
+      </c>
+      <c r="R118" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="U118" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V118" s="24" t="n"/>
+      <c r="W118" s="26" t="n"/>
+      <c r="X118" s="26" t="n"/>
+      <c r="Y118" s="25" t="n"/>
+      <c r="Z118" s="26" t="n"/>
+      <c r="AA118" s="28" t="n"/>
+      <c r="AB118" s="28" t="n"/>
+      <c r="AC118" s="30" t="n"/>
+      <c r="AD118" s="24" t="n"/>
+      <c r="AE118" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-paina-rush-2026-07-31).</t>
+        </is>
+      </c>
+      <c r="AF118" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG118" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH118" s="24" t="n"/>
+      <c r="AI118" s="31" t="n"/>
+      <c r="AJ118" s="31" t="n"/>
+      <c r="AK118" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL118" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM118" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN118" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO118" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP118" s="24" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="AQ118" s="24" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="AR118" s="24" t="inlineStr">
+        <is>
+          <t>Rush</t>
+        </is>
+      </c>
+      <c r="AS118" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AT118" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AU118" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AV118" s="24" t="n"/>
+      <c r="AW118" s="24" t="n"/>
+      <c r="AX118" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY118" s="24" t="n"/>
+      <c r="AZ118" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA118" s="24" t="inlineStr">
+        <is>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
+        </is>
+      </c>
+      <c r="BB118" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC118" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BD118" s="24" t="inlineStr">
+        <is>
+          <t>22565d893b086e259783b1719f457d57b8a6f61c6ac0ebc7176c253c0f9f41da</t>
+        </is>
+      </c>
+      <c r="BE118" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF118" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG118" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v4</t>
+        </is>
+      </c>
+      <c r="BH118" s="24" t="inlineStr">
+        <is>
+          <t>2026-07-30T17:39:33.235569Z</t>
+        </is>
+      </c>
+      <c r="BI118" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ118" s="25" t="n"/>
+      <c r="BK118" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL118" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM118" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN118" s="28" t="n"/>
+      <c r="BO118" s="28" t="n"/>
+      <c r="BP118" s="25" t="n"/>
+      <c r="BQ118" s="27" t="n"/>
+      <c r="BR118" s="28" t="n"/>
+      <c r="BS118" s="28" t="n"/>
+      <c r="BT118" s="28" t="n"/>
+      <c r="BU118" s="25" t="n"/>
+      <c r="BV118" s="29" t="n"/>
+      <c r="BW118" s="24" t="n"/>
+      <c r="BX118" s="30" t="n"/>
+      <c r="BY118" s="27" t="n"/>
+      <c r="BZ118" s="24" t="n"/>
+      <c r="CA118" s="31" t="n"/>
+      <c r="CB118" s="24" t="n"/>
+      <c r="CC118" s="24" t="n"/>
+      <c r="CD118" s="24" t="n"/>
+      <c r="CE118" s="24" t="n"/>
+      <c r="CF118" s="24" t="n"/>
+      <c r="CG118" s="24" t="n"/>
+      <c r="CH118" s="24" t="n"/>
+      <c r="CI118" s="24" t="n"/>
+      <c r="CJ118" s="24" t="n"/>
+      <c r="CK118" s="24" t="n"/>
+      <c r="CL118" s="24" t="n"/>
+      <c r="CM118" s="24" t="n"/>
+      <c r="CN118" s="24" t="n"/>
+      <c r="CO118" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO31" headerRowCount="1">
-  <autoFilter ref="A1:CO31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO51" headerRowCount="1">
+  <autoFilter ref="A1:CO51"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$31)</f>
+        <f>COUNTA('Picks'!$A$2:$A$51)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$31,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$51,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")+COUNTIFS('Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")+COUNTIFS('Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$31,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$51,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")/(COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")+COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")/(COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")+COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$31)/SUM('Picks'!$BX$2:$BX$31),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$51)/SUM('Picks'!$BX$2:$BX$51),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$31)</f>
+        <f>SUM('Picks'!$BY$2:$BY$51)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$31,"&lt;&gt;",'Picks'!$AB$2:$AB$31),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$51,"&lt;&gt;",'Picks'!$AB$2:$AB$51),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$31,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$51,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$31,'Picks'!$AM$2:$AM$31,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$51,'Picks'!$AM$2:$AM$51,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO31"/>
+  <dimension ref="A1:CO51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7878,18 +7878,38 @@
       </c>
       <c r="U24" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V24" s="24" t="n"/>
-      <c r="W24" s="26" t="n"/>
-      <c r="X24" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y24" s="25" t="n"/>
-      <c r="Z24" s="26" t="n"/>
-      <c r="AA24" s="28" t="n"/>
-      <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n"/>
-      <c r="AD24" s="24" t="n"/>
+      <c r="Z24" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="AA24" s="28" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AB24" s="28" t="n">
+        <v>-0.00037</v>
+      </c>
+      <c r="AC24" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-01T23:51:04.754069Z</t>
+        </is>
+      </c>
       <c r="AE24" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-cs2-mco-pce-2026-08-01).</t>
@@ -7902,7 +7922,7 @@
       </c>
       <c r="AG24" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH24" s="24" t="n"/>
@@ -8032,8 +8052,12 @@
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
       <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
-      <c r="BR24" s="28" t="n"/>
+      <c r="BQ24" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BR24" s="28" t="n">
+        <v>0.37</v>
+      </c>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
       <c r="BU24" s="25" t="n"/>
@@ -8139,18 +8163,38 @@
       </c>
       <c r="U25" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="n"/>
-      <c r="W25" s="26" t="n"/>
-      <c r="X25" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y25" s="25" t="n"/>
-      <c r="Z25" s="26" t="n"/>
-      <c r="AA25" s="28" t="n"/>
-      <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n"/>
-      <c r="AD25" s="24" t="n"/>
+      <c r="Z25" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="AA25" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AB25" s="28" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AC25" s="30" t="n">
+        <v>0.8197</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-01T23:51:05.985257Z</t>
+        </is>
+      </c>
       <c r="AE25" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-fxw7-bst-2026-08-01).</t>
@@ -8293,8 +8337,12 @@
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
       <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
-      <c r="BR25" s="28" t="n"/>
+      <c r="BQ25" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BR25" s="28" t="n">
+        <v>0.55</v>
+      </c>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
       <c r="BU25" s="25" t="n"/>
@@ -8322,22 +8370,22 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>6e4450fff49a4c51</t>
+          <t>c34108fc34b14497</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:55.844077Z</t>
+          <t>2026-08-01T23:54:53.636521Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-02T00:30:00Z</t>
         </is>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>67510</t>
+          <t>68172</t>
         </is>
       </c>
       <c r="E26" s="24" t="inlineStr">
@@ -8347,12 +8395,12 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>Marsborne</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>SportsBetExpert</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -8362,7 +8410,7 @@
       </c>
       <c r="I26" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J26" s="25" t="n"/>
@@ -8372,49 +8420,69 @@
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>-233</v>
+        <v>-127</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.787402</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.562783</v>
+        <v>0.600127</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>-0.136917</v>
+        <v>0.040656</v>
       </c>
       <c r="R26" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" s="29" t="n">
+      <c r="X26" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T26" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U26" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V26" s="24" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
       <c r="Y26" s="25" t="n"/>
-      <c r="Z26" s="26" t="n"/>
-      <c r="AA26" s="28" t="n"/>
-      <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n"/>
-      <c r="AD26" s="24" t="n"/>
+      <c r="Z26" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA26" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB26" s="28" t="n">
+        <v>0.000529</v>
+      </c>
+      <c r="AC26" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T03:26:10.888583Z</t>
+        </is>
+      </c>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-cs2-spo-mars-2026-08-02).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -8424,7 +8492,7 @@
       </c>
       <c r="AG26" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH26" s="24" t="n"/>
@@ -8432,7 +8500,7 @@
       <c r="AJ26" s="31" t="n"/>
       <c r="AK26" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL26" s="26" t="n">
@@ -8440,47 +8508,47 @@
       </c>
       <c r="AM26" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN26" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO26" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP26" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>Marsborne</t>
         </is>
       </c>
       <c r="AQ26" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>Marsborne</t>
         </is>
       </c>
       <c r="AR26" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>Marsborne</t>
         </is>
       </c>
       <c r="AS26" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>SportsBetExpert</t>
         </is>
       </c>
       <c r="AT26" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>SportsBetExpert</t>
         </is>
       </c>
       <c r="AU26" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>SportsBetExpert</t>
         </is>
       </c>
       <c r="AV26" s="24" t="n"/>
@@ -8498,7 +8566,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>66c8ed5c731f2059876aac6fbc24a8ff8e521bea211c3db7b24b22de67e36356</t>
+          <t>124bb01c66650940a67a9125e9f0677482f15aec343dc7b3e847d2027a63cccc</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -8513,7 +8581,7 @@
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>66c8ed5c731f2059876aac6fbc24a8ff8e521bea211c3db7b24b22de67e36356</t>
+          <t>124bb01c66650940a67a9125e9f0677482f15aec343dc7b3e847d2027a63cccc</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -8533,7 +8601,7 @@
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:48.712881Z</t>
+          <t>2026-08-01T23:54:40.651895Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -8543,19 +8611,23 @@
       </c>
       <c r="BJ26" s="25" t="n"/>
       <c r="BK26" s="26" t="n">
-        <v>-233</v>
+        <v>-127</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.787402</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
       <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
-      <c r="BR26" s="28" t="n"/>
+      <c r="BQ26" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR26" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
       <c r="BU26" s="25" t="n"/>
@@ -8583,22 +8655,22 @@
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>dfb1e44c655e4e99</t>
+          <t>e76cd04180224da1</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:55.844077Z</t>
+          <t>2026-08-02T05:46:09.037156Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T23:00:00Z</t>
+          <t>2026-08-02T06:00:00Z</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>68043</t>
+          <t>69473</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -8608,12 +8680,12 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>Donstu Esports</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>Omega</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -8633,26 +8705,26 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>-104</v>
+        <v>-163</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.613497</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.619772</v>
       </c>
       <c r="O27" s="28" t="n">
-        <v>0.569302</v>
+        <v>0.516714</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>0.059498</v>
+        <v>-0.103058</v>
       </c>
       <c r="R27" s="26" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="S27" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T27" s="24" t="inlineStr">
         <is>
@@ -8675,7 +8747,7 @@
       <c r="AD27" s="24" t="n"/>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-omg-dnt-2026-08-02).</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -8711,37 +8783,37 @@
       </c>
       <c r="AO27" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP27" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>Donstu Esports</t>
         </is>
       </c>
       <c r="AQ27" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>Donstu Esports</t>
         </is>
       </c>
       <c r="AR27" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>Donstu Esports</t>
         </is>
       </c>
       <c r="AS27" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>Omega</t>
         </is>
       </c>
       <c r="AT27" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>Omega</t>
         </is>
       </c>
       <c r="AU27" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>Omega</t>
         </is>
       </c>
       <c r="AV27" s="24" t="n"/>
@@ -8759,7 +8831,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>66c8ed5c731f2059876aac6fbc24a8ff8e521bea211c3db7b24b22de67e36356</t>
+          <t>890f1896c7e0d77ff69d9df2bbddadb5ff0c26cc29c26b7bddf0796d0d1f6a99</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -8774,7 +8846,7 @@
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>66c8ed5c731f2059876aac6fbc24a8ff8e521bea211c3db7b24b22de67e36356</t>
+          <t>890f1896c7e0d77ff69d9df2bbddadb5ff0c26cc29c26b7bddf0796d0d1f6a99</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -8794,7 +8866,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T20:32:55.841353Z</t>
+          <t>2026-08-02T05:45:44.454299Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -8804,13 +8876,13 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>-104</v>
+        <v>-163</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.613497</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.619772</v>
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
@@ -8844,12 +8916,12 @@
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>c38aa687c57945bd</t>
+          <t>4acb1571094d423e</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:25.937290Z</t>
+          <t>2026-08-02T07:16:24.505191Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -8894,20 +8966,20 @@
         </is>
       </c>
       <c r="L28" s="26" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="N28" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.429185</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>0.6854170000000001</v>
+        <v>0.685703</v>
       </c>
       <c r="P28" s="28" t="n"/>
       <c r="Q28" s="28" t="n">
-        <v>0.244888</v>
+        <v>0.256518</v>
       </c>
       <c r="R28" s="26" t="n">
         <v>100</v>
@@ -8936,7 +9008,7 @@
       <c r="AD28" s="24" t="n"/>
       <c r="AE28" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-pcific-ff-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-cs2-pcific-ff-2026-08-02).</t>
         </is>
       </c>
       <c r="AF28" s="31" t="inlineStr">
@@ -9020,7 +9092,7 @@
       </c>
       <c r="BA28" s="24" t="inlineStr">
         <is>
-          <t>d50792bb506a20912e2f4121c3471394498423e61f3d19bf1b2285fb92c74388</t>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
         </is>
       </c>
       <c r="BB28" s="24" t="inlineStr">
@@ -9035,7 +9107,7 @@
       </c>
       <c r="BD28" s="24" t="inlineStr">
         <is>
-          <t>d50792bb506a20912e2f4121c3471394498423e61f3d19bf1b2285fb92c74388</t>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
         </is>
       </c>
       <c r="BE28" s="24" t="inlineStr">
@@ -9055,7 +9127,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:06.139795Z</t>
+          <t>2026-08-02T07:16:00.086133Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -9065,13 +9137,13 @@
       </c>
       <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="BL28" s="27" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="BM28" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.429185</v>
       </c>
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
@@ -9105,12 +9177,12 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>4e89e2de4d584be4</t>
+          <t>de9c7d7a4e164358</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:25.937290Z</t>
+          <t>2026-08-02T07:16:24.505191Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -9120,7 +9192,7 @@
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>66809</t>
+          <t>69137</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -9130,12 +9202,12 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>CYBERSHOKE Esports</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>GenOne</t>
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr">
@@ -9145,7 +9217,7 @@
       </c>
       <c r="I29" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J29" s="25" t="n"/>
@@ -9155,26 +9227,26 @@
         </is>
       </c>
       <c r="L29" s="26" t="n">
-        <v>223</v>
+        <v>138</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>3.23</v>
+        <v>2.38</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.420168</v>
       </c>
       <c r="O29" s="28" t="n">
-        <v>0.53149</v>
+        <v>0.820206</v>
       </c>
       <c r="P29" s="28" t="n"/>
       <c r="Q29" s="28" t="n">
-        <v>0.221892</v>
+        <v>0.400038</v>
       </c>
       <c r="R29" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S29" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T29" s="24" t="inlineStr">
         <is>
@@ -9197,7 +9269,7 @@
       <c r="AD29" s="24" t="n"/>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-cs2-9ine-brute-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-g1-cs-2026-08-02).</t>
         </is>
       </c>
       <c r="AF29" s="31" t="inlineStr">
@@ -9215,7 +9287,7 @@
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL29" s="26" t="n">
@@ -9223,47 +9295,47 @@
       </c>
       <c r="AM29" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN29" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO29" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP29" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>CYBERSHOKE Esports</t>
         </is>
       </c>
       <c r="AQ29" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>CYBERSHOKE Esports</t>
         </is>
       </c>
       <c r="AR29" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>CYBERSHOKE Esports</t>
         </is>
       </c>
       <c r="AS29" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>GenOne</t>
         </is>
       </c>
       <c r="AT29" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>GenOne</t>
         </is>
       </c>
       <c r="AU29" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>GenOne</t>
         </is>
       </c>
       <c r="AV29" s="24" t="n"/>
@@ -9281,7 +9353,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>d50792bb506a20912e2f4121c3471394498423e61f3d19bf1b2285fb92c74388</t>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -9296,7 +9368,7 @@
       </c>
       <c r="BD29" s="24" t="inlineStr">
         <is>
-          <t>d50792bb506a20912e2f4121c3471394498423e61f3d19bf1b2285fb92c74388</t>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
         </is>
       </c>
       <c r="BE29" s="24" t="inlineStr">
@@ -9316,7 +9388,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:08.292176Z</t>
+          <t>2026-08-02T07:16:01.689501Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -9326,13 +9398,13 @@
       </c>
       <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
-        <v>223</v>
+        <v>138</v>
       </c>
       <c r="BL29" s="27" t="n">
-        <v>3.23</v>
+        <v>2.38</v>
       </c>
       <c r="BM29" s="28" t="n">
-        <v>0.309598</v>
+        <v>0.420168</v>
       </c>
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
@@ -9366,22 +9438,22 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>84abab51690f4f8d</t>
+          <t>43f1421683da42a9</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:25.937290Z</t>
+          <t>2026-08-02T07:16:24.505191Z</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:00:00Z</t>
+          <t>2026-08-02T10:00:00Z</t>
         </is>
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>68261</t>
+          <t>69163</t>
         </is>
       </c>
       <c r="E30" s="24" t="inlineStr">
@@ -9391,12 +9463,12 @@
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="G30" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Sinners</t>
         </is>
       </c>
       <c r="H30" s="24" t="inlineStr">
@@ -9416,26 +9488,26 @@
         </is>
       </c>
       <c r="L30" s="26" t="n">
-        <v>-150</v>
+        <v>-178</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.561798</v>
       </c>
       <c r="N30" s="28" t="n">
-        <v>0.6</v>
+        <v>0.640288</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>0.65372</v>
+        <v>0.626061</v>
       </c>
       <c r="P30" s="28" t="n"/>
       <c r="Q30" s="28" t="n">
-        <v>0.05372</v>
+        <v>-0.014227</v>
       </c>
       <c r="R30" s="26" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="S30" s="29" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="T30" s="24" t="inlineStr">
         <is>
@@ -9458,7 +9530,7 @@
       <c r="AD30" s="24" t="n"/>
       <c r="AE30" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-bmb-ff-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sin-sparta-2026-08-02).</t>
         </is>
       </c>
       <c r="AF30" s="31" t="inlineStr">
@@ -9494,37 +9566,37 @@
       </c>
       <c r="AO30" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP30" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AQ30" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AR30" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AS30" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Sinners</t>
         </is>
       </c>
       <c r="AT30" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Sinners</t>
         </is>
       </c>
       <c r="AU30" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Sinners</t>
         </is>
       </c>
       <c r="AV30" s="24" t="n"/>
@@ -9542,7 +9614,7 @@
       </c>
       <c r="BA30" s="24" t="inlineStr">
         <is>
-          <t>d50792bb506a20912e2f4121c3471394498423e61f3d19bf1b2285fb92c74388</t>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
         </is>
       </c>
       <c r="BB30" s="24" t="inlineStr">
@@ -9557,7 +9629,7 @@
       </c>
       <c r="BD30" s="24" t="inlineStr">
         <is>
-          <t>d50792bb506a20912e2f4121c3471394498423e61f3d19bf1b2285fb92c74388</t>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
         </is>
       </c>
       <c r="BE30" s="24" t="inlineStr">
@@ -9577,7 +9649,7 @@
       </c>
       <c r="BH30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:09.863967Z</t>
+          <t>2026-08-02T07:16:02.201908Z</t>
         </is>
       </c>
       <c r="BI30" s="24" t="inlineStr">
@@ -9587,13 +9659,13 @@
       </c>
       <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
-        <v>-150</v>
+        <v>-178</v>
       </c>
       <c r="BL30" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.561798</v>
       </c>
       <c r="BM30" s="28" t="n">
-        <v>0.6</v>
+        <v>0.640288</v>
       </c>
       <c r="BN30" s="28" t="n"/>
       <c r="BO30" s="28" t="n"/>
@@ -9627,22 +9699,22 @@
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>9bf61f216f3e4087</t>
+          <t>363e66a45db74321</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:25.937290Z</t>
+          <t>2026-08-02T07:16:24.505191Z</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:00:00Z</t>
+          <t>2026-08-02T10:00:00Z</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>68255</t>
+          <t>69413</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
@@ -9652,12 +9724,12 @@
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>ex-1win</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr">
@@ -9677,26 +9749,26 @@
         </is>
       </c>
       <c r="L31" s="26" t="n">
-        <v>-104</v>
+        <v>-178</v>
       </c>
       <c r="M31" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.561798</v>
       </c>
       <c r="N31" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.640288</v>
       </c>
       <c r="O31" s="28" t="n">
-        <v>0.543527</v>
+        <v>0.714955</v>
       </c>
       <c r="P31" s="28" t="n"/>
       <c r="Q31" s="28" t="n">
-        <v>0.033723</v>
+        <v>0.074667</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="S31" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T31" s="24" t="inlineStr">
         <is>
@@ -9719,7 +9791,7 @@
       <c r="AD31" s="24" t="n"/>
       <c r="AE31" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-mouzn-wba-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-lc-ewx-2026-08-02).</t>
         </is>
       </c>
       <c r="AF31" s="31" t="inlineStr">
@@ -9760,32 +9832,32 @@
       </c>
       <c r="AP31" s="24" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>ex-1win</t>
         </is>
       </c>
       <c r="AQ31" s="24" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>ex-1win</t>
         </is>
       </c>
       <c r="AR31" s="24" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>ex-1win</t>
         </is>
       </c>
       <c r="AS31" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AT31" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AU31" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Lazer Cats</t>
         </is>
       </c>
       <c r="AV31" s="24" t="n"/>
@@ -9803,7 +9875,7 @@
       </c>
       <c r="BA31" s="24" t="inlineStr">
         <is>
-          <t>d50792bb506a20912e2f4121c3471394498423e61f3d19bf1b2285fb92c74388</t>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
         </is>
       </c>
       <c r="BB31" s="24" t="inlineStr">
@@ -9818,7 +9890,7 @@
       </c>
       <c r="BD31" s="24" t="inlineStr">
         <is>
-          <t>d50792bb506a20912e2f4121c3471394498423e61f3d19bf1b2285fb92c74388</t>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
         </is>
       </c>
       <c r="BE31" s="24" t="inlineStr">
@@ -9838,7 +9910,7 @@
       </c>
       <c r="BH31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-01T21:24:12.835583Z</t>
+          <t>2026-08-02T07:16:02.743627Z</t>
         </is>
       </c>
       <c r="BI31" s="24" t="inlineStr">
@@ -9848,13 +9920,13 @@
       </c>
       <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
-        <v>-104</v>
+        <v>-178</v>
       </c>
       <c r="BL31" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.561798</v>
       </c>
       <c r="BM31" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.640288</v>
       </c>
       <c r="BN31" s="28" t="n"/>
       <c r="BO31" s="28" t="n"/>
@@ -9885,6 +9957,5226 @@
       <c r="CN31" s="24" t="n"/>
       <c r="CO31" s="24" t="n"/>
     </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>8ebd4ec09a7e4bc8</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>66809</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Brute</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>9INE</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.531502</v>
+      </c>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n">
+        <v>0.201469</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S32" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="n"/>
+      <c r="W32" s="26" t="n"/>
+      <c r="X32" s="26" t="n"/>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n"/>
+      <c r="AA32" s="28" t="n"/>
+      <c r="AB32" s="28" t="n"/>
+      <c r="AC32" s="30" t="n"/>
+      <c r="AD32" s="24" t="n"/>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-cs2-9ine-brute-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG32" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="inlineStr">
+        <is>
+          <t>Brute</t>
+        </is>
+      </c>
+      <c r="AQ32" s="24" t="inlineStr">
+        <is>
+          <t>Brute</t>
+        </is>
+      </c>
+      <c r="AR32" s="24" t="inlineStr">
+        <is>
+          <t>Brute</t>
+        </is>
+      </c>
+      <c r="AS32" s="24" t="inlineStr">
+        <is>
+          <t>9INE</t>
+        </is>
+      </c>
+      <c r="AT32" s="24" t="inlineStr">
+        <is>
+          <t>9INE</t>
+        </is>
+      </c>
+      <c r="AU32" s="24" t="inlineStr">
+        <is>
+          <t>9INE</t>
+        </is>
+      </c>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA32" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB32" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC32" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD32" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG32" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:03.217761Z</t>
+        </is>
+      </c>
+      <c r="BI32" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n">
+        <v>203</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BM32" s="28" t="n">
+        <v>0.330033</v>
+      </c>
+      <c r="BN32" s="28" t="n"/>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
+      <c r="BR32" s="28" t="n"/>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+      <c r="CB32" s="24" t="n"/>
+      <c r="CC32" s="24" t="n"/>
+      <c r="CD32" s="24" t="n"/>
+      <c r="CE32" s="24" t="n"/>
+      <c r="CF32" s="24" t="n"/>
+      <c r="CG32" s="24" t="n"/>
+      <c r="CH32" s="24" t="n"/>
+      <c r="CI32" s="24" t="n"/>
+      <c r="CJ32" s="24" t="n"/>
+      <c r="CK32" s="24" t="n"/>
+      <c r="CL32" s="24" t="n"/>
+      <c r="CM32" s="24" t="n"/>
+      <c r="CN32" s="24" t="n"/>
+      <c r="CO32" s="24" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>14cd5e66285b4c08</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>66836</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Sangal ALTERS</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>Teletubisie</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <v>0.690392</v>
+      </c>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n">
+        <v>0.180588</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S33" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T33" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U33" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="n"/>
+      <c r="W33" s="26" t="n"/>
+      <c r="X33" s="26" t="n"/>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="26" t="n"/>
+      <c r="AA33" s="28" t="n"/>
+      <c r="AB33" s="28" t="n"/>
+      <c r="AC33" s="30" t="n"/>
+      <c r="AD33" s="24" t="n"/>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-ttbs-sng-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG33" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="31" t="n"/>
+      <c r="AK33" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN33" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO33" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP33" s="24" t="inlineStr">
+        <is>
+          <t>Sangal ALTERS</t>
+        </is>
+      </c>
+      <c r="AQ33" s="24" t="inlineStr">
+        <is>
+          <t>Sangal ALTERS</t>
+        </is>
+      </c>
+      <c r="AR33" s="24" t="inlineStr">
+        <is>
+          <t>Sangal ALTERS</t>
+        </is>
+      </c>
+      <c r="AS33" s="24" t="inlineStr">
+        <is>
+          <t>Teletubisie</t>
+        </is>
+      </c>
+      <c r="AT33" s="24" t="inlineStr">
+        <is>
+          <t>Teletubisie</t>
+        </is>
+      </c>
+      <c r="AU33" s="24" t="inlineStr">
+        <is>
+          <t>Teletubisie</t>
+        </is>
+      </c>
+      <c r="AV33" s="24" t="n"/>
+      <c r="AW33" s="24" t="n"/>
+      <c r="AX33" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY33" s="24" t="n"/>
+      <c r="AZ33" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA33" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB33" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC33" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD33" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG33" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:04.165652Z</t>
+        </is>
+      </c>
+      <c r="BI33" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ33" s="25" t="n"/>
+      <c r="BK33" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL33" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM33" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN33" s="28" t="n"/>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
+      <c r="BR33" s="28" t="n"/>
+      <c r="BS33" s="28" t="n"/>
+      <c r="BT33" s="28" t="n"/>
+      <c r="BU33" s="25" t="n"/>
+      <c r="BV33" s="29" t="n"/>
+      <c r="BW33" s="24" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
+      <c r="BZ33" s="24" t="n"/>
+      <c r="CA33" s="31" t="n"/>
+      <c r="CB33" s="24" t="n"/>
+      <c r="CC33" s="24" t="n"/>
+      <c r="CD33" s="24" t="n"/>
+      <c r="CE33" s="24" t="n"/>
+      <c r="CF33" s="24" t="n"/>
+      <c r="CG33" s="24" t="n"/>
+      <c r="CH33" s="24" t="n"/>
+      <c r="CI33" s="24" t="n"/>
+      <c r="CJ33" s="24" t="n"/>
+      <c r="CK33" s="24" t="n"/>
+      <c r="CL33" s="24" t="n"/>
+      <c r="CM33" s="24" t="n"/>
+      <c r="CN33" s="24" t="n"/>
+      <c r="CO33" s="24" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>7b498ee9442c4348</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>69252</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>NEW VISION</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <v>0.539188</v>
+      </c>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n">
+        <v>-0.031627</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S34" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U34" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="n"/>
+      <c r="W34" s="26" t="n"/>
+      <c r="X34" s="26" t="n"/>
+      <c r="Y34" s="25" t="n"/>
+      <c r="Z34" s="26" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="30" t="n"/>
+      <c r="AD34" s="24" t="n"/>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-ica-nve-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG34" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH34" s="24" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM34" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP34" s="24" t="inlineStr">
+        <is>
+          <t>NEW VISION</t>
+        </is>
+      </c>
+      <c r="AQ34" s="24" t="inlineStr">
+        <is>
+          <t>NEW VISION</t>
+        </is>
+      </c>
+      <c r="AR34" s="24" t="inlineStr">
+        <is>
+          <t>NEW VISION</t>
+        </is>
+      </c>
+      <c r="AS34" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="AT34" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="AU34" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="AV34" s="24" t="n"/>
+      <c r="AW34" s="24" t="n"/>
+      <c r="AX34" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY34" s="24" t="n"/>
+      <c r="AZ34" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA34" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB34" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC34" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD34" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG34" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:04.648612Z</t>
+        </is>
+      </c>
+      <c r="BI34" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ34" s="25" t="n"/>
+      <c r="BK34" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL34" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM34" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN34" s="28" t="n"/>
+      <c r="BO34" s="28" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
+      <c r="BR34" s="28" t="n"/>
+      <c r="BS34" s="28" t="n"/>
+      <c r="BT34" s="28" t="n"/>
+      <c r="BU34" s="25" t="n"/>
+      <c r="BV34" s="29" t="n"/>
+      <c r="BW34" s="24" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
+      <c r="BZ34" s="24" t="n"/>
+      <c r="CA34" s="31" t="n"/>
+      <c r="CB34" s="24" t="n"/>
+      <c r="CC34" s="24" t="n"/>
+      <c r="CD34" s="24" t="n"/>
+      <c r="CE34" s="24" t="n"/>
+      <c r="CF34" s="24" t="n"/>
+      <c r="CG34" s="24" t="n"/>
+      <c r="CH34" s="24" t="n"/>
+      <c r="CI34" s="24" t="n"/>
+      <c r="CJ34" s="24" t="n"/>
+      <c r="CK34" s="24" t="n"/>
+      <c r="CL34" s="24" t="n"/>
+      <c r="CM34" s="24" t="n"/>
+      <c r="CN34" s="24" t="n"/>
+      <c r="CO34" s="24" t="n"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>bd05189ae788427d</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>68673</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>Sashi Esport</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N35" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O35" s="28" t="n">
+        <v>0.5938369999999999</v>
+      </c>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n">
+        <v>-0.066027</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T35" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U35" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V35" s="24" t="n"/>
+      <c r="W35" s="26" t="n"/>
+      <c r="X35" s="26" t="n"/>
+      <c r="Y35" s="25" t="n"/>
+      <c r="Z35" s="26" t="n"/>
+      <c r="AA35" s="28" t="n"/>
+      <c r="AB35" s="28" t="n"/>
+      <c r="AC35" s="30" t="n"/>
+      <c r="AD35" s="24" t="n"/>
+      <c r="AE35" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-bpl-sashi-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF35" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG35" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="31" t="n"/>
+      <c r="AJ35" s="31" t="n"/>
+      <c r="AK35" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM35" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP35" s="24" t="inlineStr">
+        <is>
+          <t>Sashi Esport</t>
+        </is>
+      </c>
+      <c r="AQ35" s="24" t="inlineStr">
+        <is>
+          <t>Sashi Esport</t>
+        </is>
+      </c>
+      <c r="AR35" s="24" t="inlineStr">
+        <is>
+          <t>Sashi Esport</t>
+        </is>
+      </c>
+      <c r="AS35" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AT35" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AU35" s="24" t="inlineStr">
+        <is>
+          <t>Black Phoenix</t>
+        </is>
+      </c>
+      <c r="AV35" s="24" t="n"/>
+      <c r="AW35" s="24" t="n"/>
+      <c r="AX35" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY35" s="24" t="n"/>
+      <c r="AZ35" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA35" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB35" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC35" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD35" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG35" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:05.156748Z</t>
+        </is>
+      </c>
+      <c r="BI35" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ35" s="25" t="n"/>
+      <c r="BK35" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL35" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM35" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN35" s="28" t="n"/>
+      <c r="BO35" s="28" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
+      <c r="BR35" s="28" t="n"/>
+      <c r="BS35" s="28" t="n"/>
+      <c r="BT35" s="28" t="n"/>
+      <c r="BU35" s="25" t="n"/>
+      <c r="BV35" s="29" t="n"/>
+      <c r="BW35" s="24" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
+      <c r="BZ35" s="24" t="n"/>
+      <c r="CA35" s="31" t="n"/>
+      <c r="CB35" s="24" t="n"/>
+      <c r="CC35" s="24" t="n"/>
+      <c r="CD35" s="24" t="n"/>
+      <c r="CE35" s="24" t="n"/>
+      <c r="CF35" s="24" t="n"/>
+      <c r="CG35" s="24" t="n"/>
+      <c r="CH35" s="24" t="n"/>
+      <c r="CI35" s="24" t="n"/>
+      <c r="CJ35" s="24" t="n"/>
+      <c r="CK35" s="24" t="n"/>
+      <c r="CL35" s="24" t="n"/>
+      <c r="CM35" s="24" t="n"/>
+      <c r="CN35" s="24" t="n"/>
+      <c r="CO35" s="24" t="n"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>54f939fba9ce4c88</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>68255</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>WBT</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <v>0.543496</v>
+      </c>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n">
+        <v>-0.027319</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="S36" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U36" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="n"/>
+      <c r="W36" s="26" t="n"/>
+      <c r="X36" s="26" t="n"/>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="26" t="n"/>
+      <c r="AA36" s="28" t="n"/>
+      <c r="AB36" s="28" t="n"/>
+      <c r="AC36" s="30" t="n"/>
+      <c r="AD36" s="24" t="n"/>
+      <c r="AE36" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-mouzn-wba-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF36" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG36" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="31" t="n"/>
+      <c r="AK36" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN36" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO36" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP36" s="24" t="inlineStr">
+        <is>
+          <t>WBT</t>
+        </is>
+      </c>
+      <c r="AQ36" s="24" t="inlineStr">
+        <is>
+          <t>WBT</t>
+        </is>
+      </c>
+      <c r="AR36" s="24" t="inlineStr">
+        <is>
+          <t>WBT</t>
+        </is>
+      </c>
+      <c r="AS36" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="AT36" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="AU36" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ NXT</t>
+        </is>
+      </c>
+      <c r="AV36" s="24" t="n"/>
+      <c r="AW36" s="24" t="n"/>
+      <c r="AX36" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY36" s="24" t="n"/>
+      <c r="AZ36" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA36" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB36" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC36" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD36" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG36" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:05.691452Z</t>
+        </is>
+      </c>
+      <c r="BI36" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ36" s="25" t="n"/>
+      <c r="BK36" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL36" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM36" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN36" s="28" t="n"/>
+      <c r="BO36" s="28" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
+      <c r="BR36" s="28" t="n"/>
+      <c r="BS36" s="28" t="n"/>
+      <c r="BT36" s="28" t="n"/>
+      <c r="BU36" s="25" t="n"/>
+      <c r="BV36" s="29" t="n"/>
+      <c r="BW36" s="24" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
+      <c r="BZ36" s="24" t="n"/>
+      <c r="CA36" s="31" t="n"/>
+      <c r="CB36" s="24" t="n"/>
+      <c r="CC36" s="24" t="n"/>
+      <c r="CD36" s="24" t="n"/>
+      <c r="CE36" s="24" t="n"/>
+      <c r="CF36" s="24" t="n"/>
+      <c r="CG36" s="24" t="n"/>
+      <c r="CH36" s="24" t="n"/>
+      <c r="CI36" s="24" t="n"/>
+      <c r="CJ36" s="24" t="n"/>
+      <c r="CK36" s="24" t="n"/>
+      <c r="CL36" s="24" t="n"/>
+      <c r="CM36" s="24" t="n"/>
+      <c r="CN36" s="24" t="n"/>
+      <c r="CO36" s="24" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>fd511ab61a09473b</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>68256</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>Noir Verse</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N37" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O37" s="28" t="n">
+        <v>0.620288</v>
+      </c>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="28" t="n">
+        <v>-0.070114</v>
+      </c>
+      <c r="R37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T37" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U37" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="n"/>
+      <c r="W37" s="26" t="n"/>
+      <c r="X37" s="26" t="n"/>
+      <c r="Y37" s="25" t="n"/>
+      <c r="Z37" s="26" t="n"/>
+      <c r="AA37" s="28" t="n"/>
+      <c r="AB37" s="28" t="n"/>
+      <c r="AC37" s="30" t="n"/>
+      <c r="AD37" s="24" t="n"/>
+      <c r="AE37" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-lk-nvo-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF37" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG37" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH37" s="24" t="n"/>
+      <c r="AI37" s="31" t="n"/>
+      <c r="AJ37" s="31" t="n"/>
+      <c r="AK37" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL37" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM37" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN37" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO37" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP37" s="24" t="inlineStr">
+        <is>
+          <t>Noir Verse</t>
+        </is>
+      </c>
+      <c r="AQ37" s="24" t="inlineStr">
+        <is>
+          <t>Noir Verse</t>
+        </is>
+      </c>
+      <c r="AR37" s="24" t="inlineStr">
+        <is>
+          <t>Noir Verse</t>
+        </is>
+      </c>
+      <c r="AS37" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="AT37" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="AU37" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="AV37" s="24" t="n"/>
+      <c r="AW37" s="24" t="n"/>
+      <c r="AX37" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY37" s="24" t="n"/>
+      <c r="AZ37" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA37" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB37" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC37" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD37" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG37" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:06.178300Z</t>
+        </is>
+      </c>
+      <c r="BI37" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ37" s="25" t="n"/>
+      <c r="BK37" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL37" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM37" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN37" s="28" t="n"/>
+      <c r="BO37" s="28" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
+      <c r="BR37" s="28" t="n"/>
+      <c r="BS37" s="28" t="n"/>
+      <c r="BT37" s="28" t="n"/>
+      <c r="BU37" s="25" t="n"/>
+      <c r="BV37" s="29" t="n"/>
+      <c r="BW37" s="24" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
+      <c r="BZ37" s="24" t="n"/>
+      <c r="CA37" s="31" t="n"/>
+      <c r="CB37" s="24" t="n"/>
+      <c r="CC37" s="24" t="n"/>
+      <c r="CD37" s="24" t="n"/>
+      <c r="CE37" s="24" t="n"/>
+      <c r="CF37" s="24" t="n"/>
+      <c r="CG37" s="24" t="n"/>
+      <c r="CH37" s="24" t="n"/>
+      <c r="CI37" s="24" t="n"/>
+      <c r="CJ37" s="24" t="n"/>
+      <c r="CK37" s="24" t="n"/>
+      <c r="CL37" s="24" t="n"/>
+      <c r="CM37" s="24" t="n"/>
+      <c r="CN37" s="24" t="n"/>
+      <c r="CO37" s="24" t="n"/>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>98d6637e728e4660</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>68257</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>DragonClaw</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N38" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O38" s="28" t="n">
+        <v>0.6758999999999999</v>
+      </c>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n">
+        <v>0.136729</v>
+      </c>
+      <c r="R38" s="26" t="n">
+        <v>88</v>
+      </c>
+      <c r="S38" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T38" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U38" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="n"/>
+      <c r="W38" s="26" t="n"/>
+      <c r="X38" s="26" t="n"/>
+      <c r="Y38" s="25" t="n"/>
+      <c r="Z38" s="26" t="n"/>
+      <c r="AA38" s="28" t="n"/>
+      <c r="AB38" s="28" t="n"/>
+      <c r="AC38" s="30" t="n"/>
+      <c r="AD38" s="24" t="n"/>
+      <c r="AE38" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-dc-for-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF38" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG38" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH38" s="24" t="n"/>
+      <c r="AI38" s="31" t="n"/>
+      <c r="AJ38" s="31" t="n"/>
+      <c r="AK38" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM38" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN38" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO38" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP38" s="24" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+      <c r="AQ38" s="24" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+      <c r="AR38" s="24" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+      <c r="AS38" s="24" t="inlineStr">
+        <is>
+          <t>DragonClaw</t>
+        </is>
+      </c>
+      <c r="AT38" s="24" t="inlineStr">
+        <is>
+          <t>DragonClaw</t>
+        </is>
+      </c>
+      <c r="AU38" s="24" t="inlineStr">
+        <is>
+          <t>DragonClaw</t>
+        </is>
+      </c>
+      <c r="AV38" s="24" t="n"/>
+      <c r="AW38" s="24" t="n"/>
+      <c r="AX38" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY38" s="24" t="n"/>
+      <c r="AZ38" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA38" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB38" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC38" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD38" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG38" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:06.663767Z</t>
+        </is>
+      </c>
+      <c r="BI38" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ38" s="25" t="n"/>
+      <c r="BK38" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL38" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM38" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN38" s="28" t="n"/>
+      <c r="BO38" s="28" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
+      <c r="BR38" s="28" t="n"/>
+      <c r="BS38" s="28" t="n"/>
+      <c r="BT38" s="28" t="n"/>
+      <c r="BU38" s="25" t="n"/>
+      <c r="BV38" s="29" t="n"/>
+      <c r="BW38" s="24" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
+      <c r="BZ38" s="24" t="n"/>
+      <c r="CA38" s="31" t="n"/>
+      <c r="CB38" s="24" t="n"/>
+      <c r="CC38" s="24" t="n"/>
+      <c r="CD38" s="24" t="n"/>
+      <c r="CE38" s="24" t="n"/>
+      <c r="CF38" s="24" t="n"/>
+      <c r="CG38" s="24" t="n"/>
+      <c r="CH38" s="24" t="n"/>
+      <c r="CI38" s="24" t="n"/>
+      <c r="CJ38" s="24" t="n"/>
+      <c r="CK38" s="24" t="n"/>
+      <c r="CL38" s="24" t="n"/>
+      <c r="CM38" s="24" t="n"/>
+      <c r="CN38" s="24" t="n"/>
+      <c r="CO38" s="24" t="n"/>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>b1ad3c78351b497f</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>68258</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>ex-MANA eSports</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="H39" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J39" s="25" t="n"/>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L39" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M39" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N39" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O39" s="28" t="n">
+        <v>0.583544</v>
+      </c>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="28" t="n">
+        <v>-0.07632</v>
+      </c>
+      <c r="R39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T39" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U39" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V39" s="24" t="n"/>
+      <c r="W39" s="26" t="n"/>
+      <c r="X39" s="26" t="n"/>
+      <c r="Y39" s="25" t="n"/>
+      <c r="Z39" s="26" t="n"/>
+      <c r="AA39" s="28" t="n"/>
+      <c r="AB39" s="28" t="n"/>
+      <c r="AC39" s="30" t="n"/>
+      <c r="AD39" s="24" t="n"/>
+      <c r="AE39" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-ica-exmana-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF39" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG39" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH39" s="24" t="n"/>
+      <c r="AI39" s="31" t="n"/>
+      <c r="AJ39" s="31" t="n"/>
+      <c r="AK39" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL39" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM39" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN39" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO39" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP39" s="24" t="inlineStr">
+        <is>
+          <t>ex-MANA eSports</t>
+        </is>
+      </c>
+      <c r="AQ39" s="24" t="inlineStr">
+        <is>
+          <t>ex-MANA eSports</t>
+        </is>
+      </c>
+      <c r="AR39" s="24" t="inlineStr">
+        <is>
+          <t>ex-MANA eSports</t>
+        </is>
+      </c>
+      <c r="AS39" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="AT39" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="AU39" s="24" t="inlineStr">
+        <is>
+          <t>Inner Circle Academy</t>
+        </is>
+      </c>
+      <c r="AV39" s="24" t="n"/>
+      <c r="AW39" s="24" t="n"/>
+      <c r="AX39" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY39" s="24" t="n"/>
+      <c r="AZ39" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA39" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB39" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC39" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD39" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG39" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:07.143550Z</t>
+        </is>
+      </c>
+      <c r="BI39" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ39" s="25" t="n"/>
+      <c r="BK39" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL39" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM39" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN39" s="28" t="n"/>
+      <c r="BO39" s="28" t="n"/>
+      <c r="BP39" s="25" t="n"/>
+      <c r="BQ39" s="27" t="n"/>
+      <c r="BR39" s="28" t="n"/>
+      <c r="BS39" s="28" t="n"/>
+      <c r="BT39" s="28" t="n"/>
+      <c r="BU39" s="25" t="n"/>
+      <c r="BV39" s="29" t="n"/>
+      <c r="BW39" s="24" t="n"/>
+      <c r="BX39" s="30" t="n"/>
+      <c r="BY39" s="27" t="n"/>
+      <c r="BZ39" s="24" t="n"/>
+      <c r="CA39" s="31" t="n"/>
+      <c r="CB39" s="24" t="n"/>
+      <c r="CC39" s="24" t="n"/>
+      <c r="CD39" s="24" t="n"/>
+      <c r="CE39" s="24" t="n"/>
+      <c r="CF39" s="24" t="n"/>
+      <c r="CG39" s="24" t="n"/>
+      <c r="CH39" s="24" t="n"/>
+      <c r="CI39" s="24" t="n"/>
+      <c r="CJ39" s="24" t="n"/>
+      <c r="CK39" s="24" t="n"/>
+      <c r="CL39" s="24" t="n"/>
+      <c r="CM39" s="24" t="n"/>
+      <c r="CN39" s="24" t="n"/>
+      <c r="CO39" s="24" t="n"/>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>7f074a9ff64d4fa9</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>68259</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>Vexar</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>Leo Team</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I40" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J40" s="25" t="n"/>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L40" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M40" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N40" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O40" s="28" t="n">
+        <v>0.563968</v>
+      </c>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="28" t="n">
+        <v>0.1438</v>
+      </c>
+      <c r="R40" s="26" t="n">
+        <v>92</v>
+      </c>
+      <c r="S40" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U40" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V40" s="24" t="n"/>
+      <c r="W40" s="26" t="n"/>
+      <c r="X40" s="26" t="n"/>
+      <c r="Y40" s="25" t="n"/>
+      <c r="Z40" s="26" t="n"/>
+      <c r="AA40" s="28" t="n"/>
+      <c r="AB40" s="28" t="n"/>
+      <c r="AC40" s="30" t="n"/>
+      <c r="AD40" s="24" t="n"/>
+      <c r="AE40" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-leo-vexar-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF40" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG40" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH40" s="24" t="n"/>
+      <c r="AI40" s="31" t="n"/>
+      <c r="AJ40" s="31" t="n"/>
+      <c r="AK40" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL40" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM40" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN40" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO40" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP40" s="24" t="inlineStr">
+        <is>
+          <t>Vexar</t>
+        </is>
+      </c>
+      <c r="AQ40" s="24" t="inlineStr">
+        <is>
+          <t>Vexar</t>
+        </is>
+      </c>
+      <c r="AR40" s="24" t="inlineStr">
+        <is>
+          <t>Vexar</t>
+        </is>
+      </c>
+      <c r="AS40" s="24" t="inlineStr">
+        <is>
+          <t>Leo Team</t>
+        </is>
+      </c>
+      <c r="AT40" s="24" t="inlineStr">
+        <is>
+          <t>Leo Team</t>
+        </is>
+      </c>
+      <c r="AU40" s="24" t="inlineStr">
+        <is>
+          <t>Leo Team</t>
+        </is>
+      </c>
+      <c r="AV40" s="24" t="n"/>
+      <c r="AW40" s="24" t="n"/>
+      <c r="AX40" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY40" s="24" t="n"/>
+      <c r="AZ40" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA40" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB40" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC40" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD40" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE40" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF40" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG40" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:07.634080Z</t>
+        </is>
+      </c>
+      <c r="BI40" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ40" s="25" t="n"/>
+      <c r="BK40" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL40" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM40" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN40" s="28" t="n"/>
+      <c r="BO40" s="28" t="n"/>
+      <c r="BP40" s="25" t="n"/>
+      <c r="BQ40" s="27" t="n"/>
+      <c r="BR40" s="28" t="n"/>
+      <c r="BS40" s="28" t="n"/>
+      <c r="BT40" s="28" t="n"/>
+      <c r="BU40" s="25" t="n"/>
+      <c r="BV40" s="29" t="n"/>
+      <c r="BW40" s="24" t="n"/>
+      <c r="BX40" s="30" t="n"/>
+      <c r="BY40" s="27" t="n"/>
+      <c r="BZ40" s="24" t="n"/>
+      <c r="CA40" s="31" t="n"/>
+      <c r="CB40" s="24" t="n"/>
+      <c r="CC40" s="24" t="n"/>
+      <c r="CD40" s="24" t="n"/>
+      <c r="CE40" s="24" t="n"/>
+      <c r="CF40" s="24" t="n"/>
+      <c r="CG40" s="24" t="n"/>
+      <c r="CH40" s="24" t="n"/>
+      <c r="CI40" s="24" t="n"/>
+      <c r="CJ40" s="24" t="n"/>
+      <c r="CK40" s="24" t="n"/>
+      <c r="CL40" s="24" t="n"/>
+      <c r="CM40" s="24" t="n"/>
+      <c r="CN40" s="24" t="n"/>
+      <c r="CO40" s="24" t="n"/>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>7ab4e6dbbee94678</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>68261</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>BASEMENT BOYS</t>
+        </is>
+      </c>
+      <c r="H41" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I41" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J41" s="25" t="n"/>
+      <c r="K41" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M41" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N41" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O41" s="28" t="n">
+        <v>0.65398</v>
+      </c>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="28" t="n">
+        <v>0.05398</v>
+      </c>
+      <c r="R41" s="26" t="n">
+        <v>47</v>
+      </c>
+      <c r="S41" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T41" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U41" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V41" s="24" t="n"/>
+      <c r="W41" s="26" t="n"/>
+      <c r="X41" s="26" t="n"/>
+      <c r="Y41" s="25" t="n"/>
+      <c r="Z41" s="26" t="n"/>
+      <c r="AA41" s="28" t="n"/>
+      <c r="AB41" s="28" t="n"/>
+      <c r="AC41" s="30" t="n"/>
+      <c r="AD41" s="24" t="n"/>
+      <c r="AE41" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-bmb-ff-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF41" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG41" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH41" s="24" t="n"/>
+      <c r="AI41" s="31" t="n"/>
+      <c r="AJ41" s="31" t="n"/>
+      <c r="AK41" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL41" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM41" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN41" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO41" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP41" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="AQ41" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="AR41" s="24" t="inlineStr">
+        <is>
+          <t>Fire Flux Esports</t>
+        </is>
+      </c>
+      <c r="AS41" s="24" t="inlineStr">
+        <is>
+          <t>BASEMENT BOYS</t>
+        </is>
+      </c>
+      <c r="AT41" s="24" t="inlineStr">
+        <is>
+          <t>BASEMENT BOYS</t>
+        </is>
+      </c>
+      <c r="AU41" s="24" t="inlineStr">
+        <is>
+          <t>BASEMENT BOYS</t>
+        </is>
+      </c>
+      <c r="AV41" s="24" t="n"/>
+      <c r="AW41" s="24" t="n"/>
+      <c r="AX41" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY41" s="24" t="n"/>
+      <c r="AZ41" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA41" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB41" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC41" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD41" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG41" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:08.677895Z</t>
+        </is>
+      </c>
+      <c r="BI41" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ41" s="25" t="n"/>
+      <c r="BK41" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL41" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM41" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN41" s="28" t="n"/>
+      <c r="BO41" s="28" t="n"/>
+      <c r="BP41" s="25" t="n"/>
+      <c r="BQ41" s="27" t="n"/>
+      <c r="BR41" s="28" t="n"/>
+      <c r="BS41" s="28" t="n"/>
+      <c r="BT41" s="28" t="n"/>
+      <c r="BU41" s="25" t="n"/>
+      <c r="BV41" s="29" t="n"/>
+      <c r="BW41" s="24" t="n"/>
+      <c r="BX41" s="30" t="n"/>
+      <c r="BY41" s="27" t="n"/>
+      <c r="BZ41" s="24" t="n"/>
+      <c r="CA41" s="31" t="n"/>
+      <c r="CB41" s="24" t="n"/>
+      <c r="CC41" s="24" t="n"/>
+      <c r="CD41" s="24" t="n"/>
+      <c r="CE41" s="24" t="n"/>
+      <c r="CF41" s="24" t="n"/>
+      <c r="CG41" s="24" t="n"/>
+      <c r="CH41" s="24" t="n"/>
+      <c r="CI41" s="24" t="n"/>
+      <c r="CJ41" s="24" t="n"/>
+      <c r="CK41" s="24" t="n"/>
+      <c r="CL41" s="24" t="n"/>
+      <c r="CM41" s="24" t="n"/>
+      <c r="CN41" s="24" t="n"/>
+      <c r="CO41" s="24" t="n"/>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>5a94d37632b84824</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:00:00Z</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>68277</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>Favbet</t>
+        </is>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M42" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N42" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O42" s="28" t="n">
+        <v>0.74691</v>
+      </c>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="28" t="n">
+        <v>0.09656000000000001</v>
+      </c>
+      <c r="R42" s="26" t="n">
+        <v>68</v>
+      </c>
+      <c r="S42" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T42" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U42" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V42" s="24" t="n"/>
+      <c r="W42" s="26" t="n"/>
+      <c r="X42" s="26" t="n"/>
+      <c r="Y42" s="25" t="n"/>
+      <c r="Z42" s="26" t="n"/>
+      <c r="AA42" s="28" t="n"/>
+      <c r="AB42" s="28" t="n"/>
+      <c r="AC42" s="30" t="n"/>
+      <c r="AD42" s="24" t="n"/>
+      <c r="AE42" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-cs2-fav-misa-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF42" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG42" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH42" s="24" t="n"/>
+      <c r="AI42" s="31" t="n"/>
+      <c r="AJ42" s="31" t="n"/>
+      <c r="AK42" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM42" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN42" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO42" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP42" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="AQ42" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="AR42" s="24" t="inlineStr">
+        <is>
+          <t>Misa Esports</t>
+        </is>
+      </c>
+      <c r="AS42" s="24" t="inlineStr">
+        <is>
+          <t>Favbet</t>
+        </is>
+      </c>
+      <c r="AT42" s="24" t="inlineStr">
+        <is>
+          <t>Favbet</t>
+        </is>
+      </c>
+      <c r="AU42" s="24" t="inlineStr">
+        <is>
+          <t>Favbet</t>
+        </is>
+      </c>
+      <c r="AV42" s="24" t="n"/>
+      <c r="AW42" s="24" t="n"/>
+      <c r="AX42" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY42" s="24" t="n"/>
+      <c r="AZ42" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA42" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB42" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC42" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD42" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG42" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:09.248034Z</t>
+        </is>
+      </c>
+      <c r="BI42" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ42" s="25" t="n"/>
+      <c r="BK42" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL42" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM42" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN42" s="28" t="n"/>
+      <c r="BO42" s="28" t="n"/>
+      <c r="BP42" s="25" t="n"/>
+      <c r="BQ42" s="27" t="n"/>
+      <c r="BR42" s="28" t="n"/>
+      <c r="BS42" s="28" t="n"/>
+      <c r="BT42" s="28" t="n"/>
+      <c r="BU42" s="25" t="n"/>
+      <c r="BV42" s="29" t="n"/>
+      <c r="BW42" s="24" t="n"/>
+      <c r="BX42" s="30" t="n"/>
+      <c r="BY42" s="27" t="n"/>
+      <c r="BZ42" s="24" t="n"/>
+      <c r="CA42" s="31" t="n"/>
+      <c r="CB42" s="24" t="n"/>
+      <c r="CC42" s="24" t="n"/>
+      <c r="CD42" s="24" t="n"/>
+      <c r="CE42" s="24" t="n"/>
+      <c r="CF42" s="24" t="n"/>
+      <c r="CG42" s="24" t="n"/>
+      <c r="CH42" s="24" t="n"/>
+      <c r="CI42" s="24" t="n"/>
+      <c r="CJ42" s="24" t="n"/>
+      <c r="CK42" s="24" t="n"/>
+      <c r="CL42" s="24" t="n"/>
+      <c r="CM42" s="24" t="n"/>
+      <c r="CN42" s="24" t="n"/>
+      <c r="CO42" s="24" t="n"/>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>7da850e10ee34806</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>69254</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I43" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J43" s="25" t="n"/>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L43" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M43" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N43" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O43" s="28" t="n">
+        <v>0.661873</v>
+      </c>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="28" t="n">
+        <v>0.032243</v>
+      </c>
+      <c r="R43" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="S43" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T43" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U43" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V43" s="24" t="n"/>
+      <c r="W43" s="26" t="n"/>
+      <c r="X43" s="26" t="n"/>
+      <c r="Y43" s="25" t="n"/>
+      <c r="Z43" s="26" t="n"/>
+      <c r="AA43" s="28" t="n"/>
+      <c r="AB43" s="28" t="n"/>
+      <c r="AC43" s="30" t="n"/>
+      <c r="AD43" s="24" t="n"/>
+      <c r="AE43" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-erx-hon-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF43" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG43" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH43" s="24" t="n"/>
+      <c r="AI43" s="31" t="n"/>
+      <c r="AJ43" s="31" t="n"/>
+      <c r="AK43" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL43" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM43" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN43" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO43" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP43" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="AQ43" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="AR43" s="24" t="inlineStr">
+        <is>
+          <t>Honvéd</t>
+        </is>
+      </c>
+      <c r="AS43" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AT43" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AU43" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AV43" s="24" t="n"/>
+      <c r="AW43" s="24" t="n"/>
+      <c r="AX43" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY43" s="24" t="n"/>
+      <c r="AZ43" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA43" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB43" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC43" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD43" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE43" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF43" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG43" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:09.718841Z</t>
+        </is>
+      </c>
+      <c r="BI43" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ43" s="25" t="n"/>
+      <c r="BK43" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL43" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM43" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN43" s="28" t="n"/>
+      <c r="BO43" s="28" t="n"/>
+      <c r="BP43" s="25" t="n"/>
+      <c r="BQ43" s="27" t="n"/>
+      <c r="BR43" s="28" t="n"/>
+      <c r="BS43" s="28" t="n"/>
+      <c r="BT43" s="28" t="n"/>
+      <c r="BU43" s="25" t="n"/>
+      <c r="BV43" s="29" t="n"/>
+      <c r="BW43" s="24" t="n"/>
+      <c r="BX43" s="30" t="n"/>
+      <c r="BY43" s="27" t="n"/>
+      <c r="BZ43" s="24" t="n"/>
+      <c r="CA43" s="31" t="n"/>
+      <c r="CB43" s="24" t="n"/>
+      <c r="CC43" s="24" t="n"/>
+      <c r="CD43" s="24" t="n"/>
+      <c r="CE43" s="24" t="n"/>
+      <c r="CF43" s="24" t="n"/>
+      <c r="CG43" s="24" t="n"/>
+      <c r="CH43" s="24" t="n"/>
+      <c r="CI43" s="24" t="n"/>
+      <c r="CJ43" s="24" t="n"/>
+      <c r="CK43" s="24" t="n"/>
+      <c r="CL43" s="24" t="n"/>
+      <c r="CM43" s="24" t="n"/>
+      <c r="CN43" s="24" t="n"/>
+      <c r="CO43" s="24" t="n"/>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>fdfc810e7ffe4402</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>69263</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="inlineStr">
+        <is>
+          <t>Mai Tai</t>
+        </is>
+      </c>
+      <c r="H44" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J44" s="25" t="n"/>
+      <c r="K44" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L44" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M44" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N44" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O44" s="28" t="n">
+        <v>0.6664099999999999</v>
+      </c>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="28" t="n">
+        <v>0.06641</v>
+      </c>
+      <c r="R44" s="26" t="n">
+        <v>53</v>
+      </c>
+      <c r="S44" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T44" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U44" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V44" s="24" t="n"/>
+      <c r="W44" s="26" t="n"/>
+      <c r="X44" s="26" t="n"/>
+      <c r="Y44" s="25" t="n"/>
+      <c r="Z44" s="26" t="n"/>
+      <c r="AA44" s="28" t="n"/>
+      <c r="AB44" s="28" t="n"/>
+      <c r="AC44" s="30" t="n"/>
+      <c r="AD44" s="24" t="n"/>
+      <c r="AE44" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF44" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG44" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH44" s="24" t="n"/>
+      <c r="AI44" s="31" t="n"/>
+      <c r="AJ44" s="31" t="n"/>
+      <c r="AK44" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL44" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM44" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN44" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO44" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP44" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="AQ44" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="AR44" s="24" t="inlineStr">
+        <is>
+          <t>ENJOY</t>
+        </is>
+      </c>
+      <c r="AS44" s="24" t="inlineStr">
+        <is>
+          <t>Mai Tai</t>
+        </is>
+      </c>
+      <c r="AT44" s="24" t="inlineStr">
+        <is>
+          <t>Mai Tai</t>
+        </is>
+      </c>
+      <c r="AU44" s="24" t="inlineStr">
+        <is>
+          <t>Mai Tai</t>
+        </is>
+      </c>
+      <c r="AV44" s="24" t="n"/>
+      <c r="AW44" s="24" t="n"/>
+      <c r="AX44" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY44" s="24" t="n"/>
+      <c r="AZ44" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA44" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB44" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC44" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD44" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE44" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF44" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG44" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:11.282396Z</t>
+        </is>
+      </c>
+      <c r="BI44" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ44" s="25" t="n"/>
+      <c r="BK44" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL44" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM44" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN44" s="28" t="n"/>
+      <c r="BO44" s="28" t="n"/>
+      <c r="BP44" s="25" t="n"/>
+      <c r="BQ44" s="27" t="n"/>
+      <c r="BR44" s="28" t="n"/>
+      <c r="BS44" s="28" t="n"/>
+      <c r="BT44" s="28" t="n"/>
+      <c r="BU44" s="25" t="n"/>
+      <c r="BV44" s="29" t="n"/>
+      <c r="BW44" s="24" t="n"/>
+      <c r="BX44" s="30" t="n"/>
+      <c r="BY44" s="27" t="n"/>
+      <c r="BZ44" s="24" t="n"/>
+      <c r="CA44" s="31" t="n"/>
+      <c r="CB44" s="24" t="n"/>
+      <c r="CC44" s="24" t="n"/>
+      <c r="CD44" s="24" t="n"/>
+      <c r="CE44" s="24" t="n"/>
+      <c r="CF44" s="24" t="n"/>
+      <c r="CG44" s="24" t="n"/>
+      <c r="CH44" s="24" t="n"/>
+      <c r="CI44" s="24" t="n"/>
+      <c r="CJ44" s="24" t="n"/>
+      <c r="CK44" s="24" t="n"/>
+      <c r="CL44" s="24" t="n"/>
+      <c r="CM44" s="24" t="n"/>
+      <c r="CN44" s="24" t="n"/>
+      <c r="CO44" s="24" t="n"/>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>b3b5330f268c41ad</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>69289</t>
+        </is>
+      </c>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="G45" s="24" t="inlineStr">
+        <is>
+          <t>ShindeN</t>
+        </is>
+      </c>
+      <c r="H45" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I45" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J45" s="25" t="n"/>
+      <c r="K45" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L45" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="M45" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N45" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="O45" s="28" t="n">
+        <v>0.510415</v>
+      </c>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="28" t="n">
+        <v>0.09024699999999999</v>
+      </c>
+      <c r="R45" s="26" t="n">
+        <v>65</v>
+      </c>
+      <c r="S45" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U45" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V45" s="24" t="n"/>
+      <c r="W45" s="26" t="n"/>
+      <c r="X45" s="26" t="n"/>
+      <c r="Y45" s="25" t="n"/>
+      <c r="Z45" s="26" t="n"/>
+      <c r="AA45" s="28" t="n"/>
+      <c r="AB45" s="28" t="n"/>
+      <c r="AC45" s="30" t="n"/>
+      <c r="AD45" s="24" t="n"/>
+      <c r="AE45" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-shin-bst-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF45" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG45" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH45" s="24" t="n"/>
+      <c r="AI45" s="31" t="n"/>
+      <c r="AJ45" s="31" t="n"/>
+      <c r="AK45" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL45" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM45" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN45" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO45" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP45" s="24" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="AQ45" s="24" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="AR45" s="24" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="AS45" s="24" t="inlineStr">
+        <is>
+          <t>ShindeN</t>
+        </is>
+      </c>
+      <c r="AT45" s="24" t="inlineStr">
+        <is>
+          <t>ShindeN</t>
+        </is>
+      </c>
+      <c r="AU45" s="24" t="inlineStr">
+        <is>
+          <t>ShindeN</t>
+        </is>
+      </c>
+      <c r="AV45" s="24" t="n"/>
+      <c r="AW45" s="24" t="n"/>
+      <c r="AX45" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY45" s="24" t="n"/>
+      <c r="AZ45" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA45" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB45" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC45" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD45" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE45" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF45" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG45" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:11.856492Z</t>
+        </is>
+      </c>
+      <c r="BI45" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ45" s="25" t="n"/>
+      <c r="BK45" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="BL45" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM45" s="28" t="n">
+        <v>0.420168</v>
+      </c>
+      <c r="BN45" s="28" t="n"/>
+      <c r="BO45" s="28" t="n"/>
+      <c r="BP45" s="25" t="n"/>
+      <c r="BQ45" s="27" t="n"/>
+      <c r="BR45" s="28" t="n"/>
+      <c r="BS45" s="28" t="n"/>
+      <c r="BT45" s="28" t="n"/>
+      <c r="BU45" s="25" t="n"/>
+      <c r="BV45" s="29" t="n"/>
+      <c r="BW45" s="24" t="n"/>
+      <c r="BX45" s="30" t="n"/>
+      <c r="BY45" s="27" t="n"/>
+      <c r="BZ45" s="24" t="n"/>
+      <c r="CA45" s="31" t="n"/>
+      <c r="CB45" s="24" t="n"/>
+      <c r="CC45" s="24" t="n"/>
+      <c r="CD45" s="24" t="n"/>
+      <c r="CE45" s="24" t="n"/>
+      <c r="CF45" s="24" t="n"/>
+      <c r="CG45" s="24" t="n"/>
+      <c r="CH45" s="24" t="n"/>
+      <c r="CI45" s="24" t="n"/>
+      <c r="CJ45" s="24" t="n"/>
+      <c r="CK45" s="24" t="n"/>
+      <c r="CL45" s="24" t="n"/>
+      <c r="CM45" s="24" t="n"/>
+      <c r="CN45" s="24" t="n"/>
+      <c r="CO45" s="24" t="n"/>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>15f2408e29fd4258</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>67577</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>SNAILKICK Club</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>Lixxx Club</t>
+        </is>
+      </c>
+      <c r="H46" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I46" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J46" s="25" t="n"/>
+      <c r="K46" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L46" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M46" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N46" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O46" s="28" t="n">
+        <v>0.5266110000000001</v>
+      </c>
+      <c r="P46" s="28" t="n"/>
+      <c r="Q46" s="28" t="n">
+        <v>-0.113677</v>
+      </c>
+      <c r="R46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U46" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V46" s="24" t="n"/>
+      <c r="W46" s="26" t="n"/>
+      <c r="X46" s="26" t="n"/>
+      <c r="Y46" s="25" t="n"/>
+      <c r="Z46" s="26" t="n"/>
+      <c r="AA46" s="28" t="n"/>
+      <c r="AB46" s="28" t="n"/>
+      <c r="AC46" s="30" t="n"/>
+      <c r="AD46" s="24" t="n"/>
+      <c r="AE46" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF46" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG46" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH46" s="24" t="n"/>
+      <c r="AI46" s="31" t="n"/>
+      <c r="AJ46" s="31" t="n"/>
+      <c r="AK46" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL46" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM46" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN46" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO46" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP46" s="24" t="inlineStr">
+        <is>
+          <t>SNAILKICK Club</t>
+        </is>
+      </c>
+      <c r="AQ46" s="24" t="inlineStr">
+        <is>
+          <t>SNAILKICK Club</t>
+        </is>
+      </c>
+      <c r="AR46" s="24" t="inlineStr">
+        <is>
+          <t>SNAILKICK Club</t>
+        </is>
+      </c>
+      <c r="AS46" s="24" t="inlineStr">
+        <is>
+          <t>Lixxx Club</t>
+        </is>
+      </c>
+      <c r="AT46" s="24" t="inlineStr">
+        <is>
+          <t>Lixxx Club</t>
+        </is>
+      </c>
+      <c r="AU46" s="24" t="inlineStr">
+        <is>
+          <t>Lixxx Club</t>
+        </is>
+      </c>
+      <c r="AV46" s="24" t="n"/>
+      <c r="AW46" s="24" t="n"/>
+      <c r="AX46" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY46" s="24" t="n"/>
+      <c r="AZ46" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA46" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB46" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC46" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD46" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE46" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF46" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG46" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:12.356484Z</t>
+        </is>
+      </c>
+      <c r="BI46" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ46" s="25" t="n"/>
+      <c r="BK46" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL46" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM46" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN46" s="28" t="n"/>
+      <c r="BO46" s="28" t="n"/>
+      <c r="BP46" s="25" t="n"/>
+      <c r="BQ46" s="27" t="n"/>
+      <c r="BR46" s="28" t="n"/>
+      <c r="BS46" s="28" t="n"/>
+      <c r="BT46" s="28" t="n"/>
+      <c r="BU46" s="25" t="n"/>
+      <c r="BV46" s="29" t="n"/>
+      <c r="BW46" s="24" t="n"/>
+      <c r="BX46" s="30" t="n"/>
+      <c r="BY46" s="27" t="n"/>
+      <c r="BZ46" s="24" t="n"/>
+      <c r="CA46" s="31" t="n"/>
+      <c r="CB46" s="24" t="n"/>
+      <c r="CC46" s="24" t="n"/>
+      <c r="CD46" s="24" t="n"/>
+      <c r="CE46" s="24" t="n"/>
+      <c r="CF46" s="24" t="n"/>
+      <c r="CG46" s="24" t="n"/>
+      <c r="CH46" s="24" t="n"/>
+      <c r="CI46" s="24" t="n"/>
+      <c r="CJ46" s="24" t="n"/>
+      <c r="CK46" s="24" t="n"/>
+      <c r="CL46" s="24" t="n"/>
+      <c r="CM46" s="24" t="n"/>
+      <c r="CN46" s="24" t="n"/>
+      <c r="CO46" s="24" t="n"/>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>588fedbfd6204f81</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>67576</t>
+        </is>
+      </c>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>mokrivskiy Club</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="H47" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I47" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J47" s="25" t="n"/>
+      <c r="K47" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L47" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M47" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N47" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O47" s="28" t="n">
+        <v>0.57939</v>
+      </c>
+      <c r="P47" s="28" t="n"/>
+      <c r="Q47" s="28" t="n">
+        <v>0.22974</v>
+      </c>
+      <c r="R47" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S47" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T47" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U47" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V47" s="24" t="n"/>
+      <c r="W47" s="26" t="n"/>
+      <c r="X47" s="26" t="n"/>
+      <c r="Y47" s="25" t="n"/>
+      <c r="Z47" s="26" t="n"/>
+      <c r="AA47" s="28" t="n"/>
+      <c r="AB47" s="28" t="n"/>
+      <c r="AC47" s="30" t="n"/>
+      <c r="AD47" s="24" t="n"/>
+      <c r="AE47" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF47" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG47" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH47" s="24" t="n"/>
+      <c r="AI47" s="31" t="n"/>
+      <c r="AJ47" s="31" t="n"/>
+      <c r="AK47" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL47" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM47" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN47" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO47" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP47" s="24" t="inlineStr">
+        <is>
+          <t>mokrivskiy Club</t>
+        </is>
+      </c>
+      <c r="AQ47" s="24" t="inlineStr">
+        <is>
+          <t>mokrivskiy Club</t>
+        </is>
+      </c>
+      <c r="AR47" s="24" t="inlineStr">
+        <is>
+          <t>mokrivskiy Club</t>
+        </is>
+      </c>
+      <c r="AS47" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AT47" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AU47" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AV47" s="24" t="n"/>
+      <c r="AW47" s="24" t="n"/>
+      <c r="AX47" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY47" s="24" t="n"/>
+      <c r="AZ47" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA47" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB47" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC47" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD47" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE47" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF47" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG47" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:12.889350Z</t>
+        </is>
+      </c>
+      <c r="BI47" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ47" s="25" t="n"/>
+      <c r="BK47" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL47" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BM47" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN47" s="28" t="n"/>
+      <c r="BO47" s="28" t="n"/>
+      <c r="BP47" s="25" t="n"/>
+      <c r="BQ47" s="27" t="n"/>
+      <c r="BR47" s="28" t="n"/>
+      <c r="BS47" s="28" t="n"/>
+      <c r="BT47" s="28" t="n"/>
+      <c r="BU47" s="25" t="n"/>
+      <c r="BV47" s="29" t="n"/>
+      <c r="BW47" s="24" t="n"/>
+      <c r="BX47" s="30" t="n"/>
+      <c r="BY47" s="27" t="n"/>
+      <c r="BZ47" s="24" t="n"/>
+      <c r="CA47" s="31" t="n"/>
+      <c r="CB47" s="24" t="n"/>
+      <c r="CC47" s="24" t="n"/>
+      <c r="CD47" s="24" t="n"/>
+      <c r="CE47" s="24" t="n"/>
+      <c r="CF47" s="24" t="n"/>
+      <c r="CG47" s="24" t="n"/>
+      <c r="CH47" s="24" t="n"/>
+      <c r="CI47" s="24" t="n"/>
+      <c r="CJ47" s="24" t="n"/>
+      <c r="CK47" s="24" t="n"/>
+      <c r="CL47" s="24" t="n"/>
+      <c r="CM47" s="24" t="n"/>
+      <c r="CN47" s="24" t="n"/>
+      <c r="CO47" s="24" t="n"/>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>df5fbea4dd924549</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>67510</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>Johnny Speeds</t>
+        </is>
+      </c>
+      <c r="G48" s="24" t="inlineStr">
+        <is>
+          <t>Metizport</t>
+        </is>
+      </c>
+      <c r="H48" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I48" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J48" s="25" t="n"/>
+      <c r="K48" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L48" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M48" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N48" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O48" s="28" t="n">
+        <v>0.562959</v>
+      </c>
+      <c r="P48" s="28" t="n"/>
+      <c r="Q48" s="28" t="n">
+        <v>-0.127443</v>
+      </c>
+      <c r="R48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U48" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V48" s="24" t="n"/>
+      <c r="W48" s="26" t="n"/>
+      <c r="X48" s="26" t="n"/>
+      <c r="Y48" s="25" t="n"/>
+      <c r="Z48" s="26" t="n"/>
+      <c r="AA48" s="28" t="n"/>
+      <c r="AB48" s="28" t="n"/>
+      <c r="AC48" s="30" t="n"/>
+      <c r="AD48" s="24" t="n"/>
+      <c r="AE48" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF48" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG48" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH48" s="24" t="n"/>
+      <c r="AI48" s="31" t="n"/>
+      <c r="AJ48" s="31" t="n"/>
+      <c r="AK48" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL48" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM48" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN48" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO48" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP48" s="24" t="inlineStr">
+        <is>
+          <t>Johnny Speeds</t>
+        </is>
+      </c>
+      <c r="AQ48" s="24" t="inlineStr">
+        <is>
+          <t>Johnny Speeds</t>
+        </is>
+      </c>
+      <c r="AR48" s="24" t="inlineStr">
+        <is>
+          <t>Johnny Speeds</t>
+        </is>
+      </c>
+      <c r="AS48" s="24" t="inlineStr">
+        <is>
+          <t>Metizport</t>
+        </is>
+      </c>
+      <c r="AT48" s="24" t="inlineStr">
+        <is>
+          <t>Metizport</t>
+        </is>
+      </c>
+      <c r="AU48" s="24" t="inlineStr">
+        <is>
+          <t>Metizport</t>
+        </is>
+      </c>
+      <c r="AV48" s="24" t="n"/>
+      <c r="AW48" s="24" t="n"/>
+      <c r="AX48" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY48" s="24" t="n"/>
+      <c r="AZ48" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA48" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB48" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC48" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD48" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE48" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF48" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG48" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:15.647933Z</t>
+        </is>
+      </c>
+      <c r="BI48" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ48" s="25" t="n"/>
+      <c r="BK48" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL48" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM48" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN48" s="28" t="n"/>
+      <c r="BO48" s="28" t="n"/>
+      <c r="BP48" s="25" t="n"/>
+      <c r="BQ48" s="27" t="n"/>
+      <c r="BR48" s="28" t="n"/>
+      <c r="BS48" s="28" t="n"/>
+      <c r="BT48" s="28" t="n"/>
+      <c r="BU48" s="25" t="n"/>
+      <c r="BV48" s="29" t="n"/>
+      <c r="BW48" s="24" t="n"/>
+      <c r="BX48" s="30" t="n"/>
+      <c r="BY48" s="27" t="n"/>
+      <c r="BZ48" s="24" t="n"/>
+      <c r="CA48" s="31" t="n"/>
+      <c r="CB48" s="24" t="n"/>
+      <c r="CC48" s="24" t="n"/>
+      <c r="CD48" s="24" t="n"/>
+      <c r="CE48" s="24" t="n"/>
+      <c r="CF48" s="24" t="n"/>
+      <c r="CG48" s="24" t="n"/>
+      <c r="CH48" s="24" t="n"/>
+      <c r="CI48" s="24" t="n"/>
+      <c r="CJ48" s="24" t="n"/>
+      <c r="CK48" s="24" t="n"/>
+      <c r="CL48" s="24" t="n"/>
+      <c r="CM48" s="24" t="n"/>
+      <c r="CN48" s="24" t="n"/>
+      <c r="CO48" s="24" t="n"/>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>bdd3531261214a53</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>67514</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="H49" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I49" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J49" s="25" t="n"/>
+      <c r="K49" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L49" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="M49" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N49" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O49" s="28" t="n">
+        <v>0.640064</v>
+      </c>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="28" t="n">
+        <v>0.140064</v>
+      </c>
+      <c r="R49" s="26" t="n">
+        <v>90</v>
+      </c>
+      <c r="S49" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T49" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U49" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V49" s="24" t="n"/>
+      <c r="W49" s="26" t="n"/>
+      <c r="X49" s="26" t="n"/>
+      <c r="Y49" s="25" t="n"/>
+      <c r="Z49" s="26" t="n"/>
+      <c r="AA49" s="28" t="n"/>
+      <c r="AB49" s="28" t="n"/>
+      <c r="AC49" s="30" t="n"/>
+      <c r="AD49" s="24" t="n"/>
+      <c r="AE49" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF49" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG49" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH49" s="24" t="n"/>
+      <c r="AI49" s="31" t="n"/>
+      <c r="AJ49" s="31" t="n"/>
+      <c r="AK49" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL49" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM49" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN49" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO49" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP49" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="AQ49" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="AR49" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="AS49" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AT49" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AU49" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AV49" s="24" t="n"/>
+      <c r="AW49" s="24" t="n"/>
+      <c r="AX49" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY49" s="24" t="n"/>
+      <c r="AZ49" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA49" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB49" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC49" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD49" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE49" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF49" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG49" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:17.283191Z</t>
+        </is>
+      </c>
+      <c r="BI49" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ49" s="25" t="n"/>
+      <c r="BK49" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL49" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM49" s="28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN49" s="28" t="n"/>
+      <c r="BO49" s="28" t="n"/>
+      <c r="BP49" s="25" t="n"/>
+      <c r="BQ49" s="27" t="n"/>
+      <c r="BR49" s="28" t="n"/>
+      <c r="BS49" s="28" t="n"/>
+      <c r="BT49" s="28" t="n"/>
+      <c r="BU49" s="25" t="n"/>
+      <c r="BV49" s="29" t="n"/>
+      <c r="BW49" s="24" t="n"/>
+      <c r="BX49" s="30" t="n"/>
+      <c r="BY49" s="27" t="n"/>
+      <c r="BZ49" s="24" t="n"/>
+      <c r="CA49" s="31" t="n"/>
+      <c r="CB49" s="24" t="n"/>
+      <c r="CC49" s="24" t="n"/>
+      <c r="CD49" s="24" t="n"/>
+      <c r="CE49" s="24" t="n"/>
+      <c r="CF49" s="24" t="n"/>
+      <c r="CG49" s="24" t="n"/>
+      <c r="CH49" s="24" t="n"/>
+      <c r="CI49" s="24" t="n"/>
+      <c r="CJ49" s="24" t="n"/>
+      <c r="CK49" s="24" t="n"/>
+      <c r="CL49" s="24" t="n"/>
+      <c r="CM49" s="24" t="n"/>
+      <c r="CN49" s="24" t="n"/>
+      <c r="CO49" s="24" t="n"/>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>243c49bec8c540a2</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>67578</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="G50" s="24" t="inlineStr">
+        <is>
+          <t>Recrent Club</t>
+        </is>
+      </c>
+      <c r="H50" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I50" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J50" s="25" t="n"/>
+      <c r="K50" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L50" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M50" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N50" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O50" s="28" t="n">
+        <v>0.5266110000000001</v>
+      </c>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="28" t="n">
+        <v>-0.103019</v>
+      </c>
+      <c r="R50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U50" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V50" s="24" t="n"/>
+      <c r="W50" s="26" t="n"/>
+      <c r="X50" s="26" t="n"/>
+      <c r="Y50" s="25" t="n"/>
+      <c r="Z50" s="26" t="n"/>
+      <c r="AA50" s="28" t="n"/>
+      <c r="AB50" s="28" t="n"/>
+      <c r="AC50" s="30" t="n"/>
+      <c r="AD50" s="24" t="n"/>
+      <c r="AE50" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF50" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG50" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH50" s="24" t="n"/>
+      <c r="AI50" s="31" t="n"/>
+      <c r="AJ50" s="31" t="n"/>
+      <c r="AK50" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL50" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM50" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN50" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO50" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP50" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AQ50" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AR50" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AS50" s="24" t="inlineStr">
+        <is>
+          <t>Recrent Club</t>
+        </is>
+      </c>
+      <c r="AT50" s="24" t="inlineStr">
+        <is>
+          <t>Recrent Club</t>
+        </is>
+      </c>
+      <c r="AU50" s="24" t="inlineStr">
+        <is>
+          <t>Recrent Club</t>
+        </is>
+      </c>
+      <c r="AV50" s="24" t="n"/>
+      <c r="AW50" s="24" t="n"/>
+      <c r="AX50" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY50" s="24" t="n"/>
+      <c r="AZ50" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA50" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB50" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC50" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD50" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE50" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF50" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG50" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:17.856987Z</t>
+        </is>
+      </c>
+      <c r="BI50" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ50" s="25" t="n"/>
+      <c r="BK50" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL50" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM50" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN50" s="28" t="n"/>
+      <c r="BO50" s="28" t="n"/>
+      <c r="BP50" s="25" t="n"/>
+      <c r="BQ50" s="27" t="n"/>
+      <c r="BR50" s="28" t="n"/>
+      <c r="BS50" s="28" t="n"/>
+      <c r="BT50" s="28" t="n"/>
+      <c r="BU50" s="25" t="n"/>
+      <c r="BV50" s="29" t="n"/>
+      <c r="BW50" s="24" t="n"/>
+      <c r="BX50" s="30" t="n"/>
+      <c r="BY50" s="27" t="n"/>
+      <c r="BZ50" s="24" t="n"/>
+      <c r="CA50" s="31" t="n"/>
+      <c r="CB50" s="24" t="n"/>
+      <c r="CC50" s="24" t="n"/>
+      <c r="CD50" s="24" t="n"/>
+      <c r="CE50" s="24" t="n"/>
+      <c r="CF50" s="24" t="n"/>
+      <c r="CG50" s="24" t="n"/>
+      <c r="CH50" s="24" t="n"/>
+      <c r="CI50" s="24" t="n"/>
+      <c r="CJ50" s="24" t="n"/>
+      <c r="CK50" s="24" t="n"/>
+      <c r="CL50" s="24" t="n"/>
+      <c r="CM50" s="24" t="n"/>
+      <c r="CN50" s="24" t="n"/>
+      <c r="CO50" s="24" t="n"/>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>509e7f0ed553481e</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.505191Z</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>68043</t>
+        </is>
+      </c>
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="H51" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I51" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J51" s="25" t="n"/>
+      <c r="K51" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L51" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M51" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N51" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O51" s="28" t="n">
+        <v>0.569433</v>
+      </c>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="28" t="n">
+        <v>0.118983</v>
+      </c>
+      <c r="R51" s="26" t="n">
+        <v>79</v>
+      </c>
+      <c r="S51" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T51" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U51" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V51" s="24" t="n"/>
+      <c r="W51" s="26" t="n"/>
+      <c r="X51" s="26" t="n"/>
+      <c r="Y51" s="25" t="n"/>
+      <c r="Z51" s="26" t="n"/>
+      <c r="AA51" s="28" t="n"/>
+      <c r="AB51" s="28" t="n"/>
+      <c r="AC51" s="30" t="n"/>
+      <c r="AD51" s="24" t="n"/>
+      <c r="AE51" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF51" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG51" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH51" s="24" t="n"/>
+      <c r="AI51" s="31" t="n"/>
+      <c r="AJ51" s="31" t="n"/>
+      <c r="AK51" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL51" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM51" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN51" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO51" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP51" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AQ51" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AR51" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AS51" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AT51" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AU51" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AV51" s="24" t="n"/>
+      <c r="AW51" s="24" t="n"/>
+      <c r="AX51" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY51" s="24" t="n"/>
+      <c r="AZ51" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA51" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BB51" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC51" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD51" s="24" t="inlineStr">
+        <is>
+          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+        </is>
+      </c>
+      <c r="BE51" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF51" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG51" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:16:24.503358Z</t>
+        </is>
+      </c>
+      <c r="BI51" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ51" s="25" t="n"/>
+      <c r="BK51" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL51" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM51" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN51" s="28" t="n"/>
+      <c r="BO51" s="28" t="n"/>
+      <c r="BP51" s="25" t="n"/>
+      <c r="BQ51" s="27" t="n"/>
+      <c r="BR51" s="28" t="n"/>
+      <c r="BS51" s="28" t="n"/>
+      <c r="BT51" s="28" t="n"/>
+      <c r="BU51" s="25" t="n"/>
+      <c r="BV51" s="29" t="n"/>
+      <c r="BW51" s="24" t="n"/>
+      <c r="BX51" s="30" t="n"/>
+      <c r="BY51" s="27" t="n"/>
+      <c r="BZ51" s="24" t="n"/>
+      <c r="CA51" s="31" t="n"/>
+      <c r="CB51" s="24" t="n"/>
+      <c r="CC51" s="24" t="n"/>
+      <c r="CD51" s="24" t="n"/>
+      <c r="CE51" s="24" t="n"/>
+      <c r="CF51" s="24" t="n"/>
+      <c r="CG51" s="24" t="n"/>
+      <c r="CH51" s="24" t="n"/>
+      <c r="CI51" s="24" t="n"/>
+      <c r="CJ51" s="24" t="n"/>
+      <c r="CK51" s="24" t="n"/>
+      <c r="CL51" s="24" t="n"/>
+      <c r="CM51" s="24" t="n"/>
+      <c r="CN51" s="24" t="n"/>
+      <c r="CO51" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO51" headerRowCount="1">
-  <autoFilter ref="A1:CO51"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO53" headerRowCount="1">
+  <autoFilter ref="A1:CO53"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$51)</f>
+        <f>COUNTA('Picks'!$A$2:$A$53)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$51,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$53,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$51,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$53,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")+COUNTIFS('Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")+COUNTIFS('Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$51,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$53,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")/(COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"win")+COUNTIFS('Picks'!$BX$2:$BX$51,"&gt;0",'Picks'!$V$2:$V$51,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"win")/(COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"win")+COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$51)/SUM('Picks'!$BX$2:$BX$51),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$53)/SUM('Picks'!$BX$2:$BX$53),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$51)</f>
+        <f>SUM('Picks'!$BY$2:$BY$53)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$51,"&lt;&gt;",'Picks'!$AB$2:$AB$51),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$53,"&lt;&gt;",'Picks'!$AB$2:$AB$53),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$51,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$51,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$53,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$53,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$51,'Picks'!$AM$2:$AM$51,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$53,'Picks'!$AM$2:$AM$53,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$53,'Picks'!$H$2:$H$53,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A14,'Picks'!$U$2:$U$51,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$53,'Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$53,'Picks'!$H$2:$H$53,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A15,'Picks'!$U$2:$U$51,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$53,'Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled",'Picks'!$V$2:$V$51,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$51,'Picks'!$H$2:$H$51,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$53,'Picks'!$H$2:$H$53,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$51,'Picks'!$H$2:$H$51,$A16,'Picks'!$U$2:$U$51,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$53,'Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO51"/>
+  <dimension ref="A1:CO53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8733,18 +8733,38 @@
       </c>
       <c r="U27" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y27" s="25" t="n"/>
-      <c r="Z27" s="26" t="n"/>
-      <c r="AA27" s="28" t="n"/>
-      <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n"/>
-      <c r="AD27" s="24" t="n"/>
+      <c r="Z27" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="AA27" s="28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB27" s="28" t="n">
+        <v>0.08022799999999999</v>
+      </c>
+      <c r="AC27" s="30" t="n">
+        <v>0.6135</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T08:20:46.255052Z</t>
+        </is>
+      </c>
       <c r="AE27" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-omg-dnt-2026-08-02).</t>
@@ -8887,8 +8907,12 @@
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
       <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
-      <c r="BR27" s="28" t="n"/>
+      <c r="BQ27" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BR27" s="28" t="n">
+        <v>0.7</v>
+      </c>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
       <c r="BU27" s="25" t="n"/>
@@ -9177,12 +9201,12 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>de9c7d7a4e164358</t>
+          <t>6a875257547b4c46</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -9236,11 +9260,11 @@
         <v>0.420168</v>
       </c>
       <c r="O29" s="28" t="n">
-        <v>0.820206</v>
+        <v>0.820361</v>
       </c>
       <c r="P29" s="28" t="n"/>
       <c r="Q29" s="28" t="n">
-        <v>0.400038</v>
+        <v>0.400193</v>
       </c>
       <c r="R29" s="26" t="n">
         <v>100</v>
@@ -9353,7 +9377,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -9368,7 +9392,7 @@
       </c>
       <c r="BD29" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE29" s="24" t="inlineStr">
@@ -9388,7 +9412,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:01.689501Z</t>
+          <t>2026-08-02T08:19:07.601616Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -9438,12 +9462,12 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>43f1421683da42a9</t>
+          <t>432caac9002149a8</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -9497,11 +9521,11 @@
         <v>0.640288</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>0.626061</v>
+        <v>0.626221</v>
       </c>
       <c r="P30" s="28" t="n"/>
       <c r="Q30" s="28" t="n">
-        <v>-0.014227</v>
+        <v>-0.014067</v>
       </c>
       <c r="R30" s="26" t="n">
         <v>13</v>
@@ -9614,7 +9638,7 @@
       </c>
       <c r="BA30" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB30" s="24" t="inlineStr">
@@ -9629,7 +9653,7 @@
       </c>
       <c r="BD30" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE30" s="24" t="inlineStr">
@@ -9649,7 +9673,7 @@
       </c>
       <c r="BH30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:02.201908Z</t>
+          <t>2026-08-02T08:19:08.072917Z</t>
         </is>
       </c>
       <c r="BI30" s="24" t="inlineStr">
@@ -9699,12 +9723,12 @@
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>363e66a45db74321</t>
+          <t>669f2759c6a84d14</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
@@ -9749,23 +9773,23 @@
         </is>
       </c>
       <c r="L31" s="26" t="n">
-        <v>-178</v>
+        <v>-213</v>
       </c>
       <c r="M31" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.469484</v>
       </c>
       <c r="N31" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.680511</v>
       </c>
       <c r="O31" s="28" t="n">
-        <v>0.714955</v>
+        <v>0.714926</v>
       </c>
       <c r="P31" s="28" t="n"/>
       <c r="Q31" s="28" t="n">
-        <v>0.074667</v>
+        <v>0.034415</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="S31" s="29" t="n">
         <v>2</v>
@@ -9791,7 +9815,7 @@
       <c r="AD31" s="24" t="n"/>
       <c r="AE31" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-lc-ewx-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-lc-ewx-2026-08-02).</t>
         </is>
       </c>
       <c r="AF31" s="31" t="inlineStr">
@@ -9875,7 +9899,7 @@
       </c>
       <c r="BA31" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB31" s="24" t="inlineStr">
@@ -9890,7 +9914,7 @@
       </c>
       <c r="BD31" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE31" s="24" t="inlineStr">
@@ -9910,7 +9934,7 @@
       </c>
       <c r="BH31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:02.743627Z</t>
+          <t>2026-08-02T08:19:08.739294Z</t>
         </is>
       </c>
       <c r="BI31" s="24" t="inlineStr">
@@ -9920,13 +9944,13 @@
       </c>
       <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
-        <v>-178</v>
+        <v>-213</v>
       </c>
       <c r="BL31" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.469484</v>
       </c>
       <c r="BM31" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.680511</v>
       </c>
       <c r="BN31" s="28" t="n"/>
       <c r="BO31" s="28" t="n"/>
@@ -9960,12 +9984,12 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>8ebd4ec09a7e4bc8</t>
+          <t>766179d9252f497f</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
@@ -10019,11 +10043,11 @@
         <v>0.330033</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>0.531502</v>
+        <v>0.531394</v>
       </c>
       <c r="P32" s="28" t="n"/>
       <c r="Q32" s="28" t="n">
-        <v>0.201469</v>
+        <v>0.201361</v>
       </c>
       <c r="R32" s="26" t="n">
         <v>100</v>
@@ -10136,7 +10160,7 @@
       </c>
       <c r="BA32" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB32" s="24" t="inlineStr">
@@ -10151,7 +10175,7 @@
       </c>
       <c r="BD32" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE32" s="24" t="inlineStr">
@@ -10171,7 +10195,7 @@
       </c>
       <c r="BH32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:03.217761Z</t>
+          <t>2026-08-02T08:19:09.283371Z</t>
         </is>
       </c>
       <c r="BI32" s="24" t="inlineStr">
@@ -10221,12 +10245,12 @@
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>14cd5e66285b4c08</t>
+          <t>79721cb291414869</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -10280,11 +10304,11 @@
         <v>0.509804</v>
       </c>
       <c r="O33" s="28" t="n">
-        <v>0.690392</v>
+        <v>0.690561</v>
       </c>
       <c r="P33" s="28" t="n"/>
       <c r="Q33" s="28" t="n">
-        <v>0.180588</v>
+        <v>0.180757</v>
       </c>
       <c r="R33" s="26" t="n">
         <v>100</v>
@@ -10397,7 +10421,7 @@
       </c>
       <c r="BA33" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB33" s="24" t="inlineStr">
@@ -10412,7 +10436,7 @@
       </c>
       <c r="BD33" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE33" s="24" t="inlineStr">
@@ -10432,7 +10456,7 @@
       </c>
       <c r="BH33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:04.165652Z</t>
+          <t>2026-08-02T08:19:10.390430Z</t>
         </is>
       </c>
       <c r="BI33" s="24" t="inlineStr">
@@ -10482,12 +10506,12 @@
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>7b498ee9442c4348</t>
+          <t>e4924d7adf5e4d7e</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -10541,11 +10565,11 @@
         <v>0.570815</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>0.539188</v>
+        <v>0.539324</v>
       </c>
       <c r="P34" s="28" t="n"/>
       <c r="Q34" s="28" t="n">
-        <v>-0.031627</v>
+        <v>-0.031491</v>
       </c>
       <c r="R34" s="26" t="n">
         <v>4</v>
@@ -10658,7 +10682,7 @@
       </c>
       <c r="BA34" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB34" s="24" t="inlineStr">
@@ -10673,7 +10697,7 @@
       </c>
       <c r="BD34" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE34" s="24" t="inlineStr">
@@ -10693,7 +10717,7 @@
       </c>
       <c r="BH34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:04.648612Z</t>
+          <t>2026-08-02T08:19:10.873207Z</t>
         </is>
       </c>
       <c r="BI34" s="24" t="inlineStr">
@@ -10743,12 +10767,12 @@
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>bd05189ae788427d</t>
+          <t>c5ae0071bc0c4138</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -10793,20 +10817,20 @@
         </is>
       </c>
       <c r="L35" s="26" t="n">
-        <v>-194</v>
+        <v>-213</v>
       </c>
       <c r="M35" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.469484</v>
       </c>
       <c r="N35" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.680511</v>
       </c>
       <c r="O35" s="28" t="n">
-        <v>0.5938369999999999</v>
+        <v>0.593754</v>
       </c>
       <c r="P35" s="28" t="n"/>
       <c r="Q35" s="28" t="n">
-        <v>-0.066027</v>
+        <v>-0.086757</v>
       </c>
       <c r="R35" s="26" t="n">
         <v>0</v>
@@ -10835,7 +10859,7 @@
       <c r="AD35" s="24" t="n"/>
       <c r="AE35" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-bpl-sashi-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-bpl-sashi-2026-08-02).</t>
         </is>
       </c>
       <c r="AF35" s="31" t="inlineStr">
@@ -10919,7 +10943,7 @@
       </c>
       <c r="BA35" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB35" s="24" t="inlineStr">
@@ -10934,7 +10958,7 @@
       </c>
       <c r="BD35" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE35" s="24" t="inlineStr">
@@ -10954,7 +10978,7 @@
       </c>
       <c r="BH35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:05.156748Z</t>
+          <t>2026-08-02T08:19:11.376481Z</t>
         </is>
       </c>
       <c r="BI35" s="24" t="inlineStr">
@@ -10964,13 +10988,13 @@
       </c>
       <c r="BJ35" s="25" t="n"/>
       <c r="BK35" s="26" t="n">
-        <v>-194</v>
+        <v>-213</v>
       </c>
       <c r="BL35" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.469484</v>
       </c>
       <c r="BM35" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.680511</v>
       </c>
       <c r="BN35" s="28" t="n"/>
       <c r="BO35" s="28" t="n"/>
@@ -11004,12 +11028,12 @@
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>54f939fba9ce4c88</t>
+          <t>29031686a1a34516</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
@@ -11063,11 +11087,11 @@
         <v>0.570815</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>0.543496</v>
+        <v>0.543392</v>
       </c>
       <c r="P36" s="28" t="n"/>
       <c r="Q36" s="28" t="n">
-        <v>-0.027319</v>
+        <v>-0.027423</v>
       </c>
       <c r="R36" s="26" t="n">
         <v>6</v>
@@ -11180,7 +11204,7 @@
       </c>
       <c r="BA36" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB36" s="24" t="inlineStr">
@@ -11195,7 +11219,7 @@
       </c>
       <c r="BD36" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE36" s="24" t="inlineStr">
@@ -11215,7 +11239,7 @@
       </c>
       <c r="BH36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:05.691452Z</t>
+          <t>2026-08-02T08:19:11.845647Z</t>
         </is>
       </c>
       <c r="BI36" s="24" t="inlineStr">
@@ -11265,12 +11289,12 @@
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>fd511ab61a09473b</t>
+          <t>8e88fab96b2b4ac8</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
@@ -11324,11 +11348,11 @@
         <v>0.690402</v>
       </c>
       <c r="O37" s="28" t="n">
-        <v>0.620288</v>
+        <v>0.620448</v>
       </c>
       <c r="P37" s="28" t="n"/>
       <c r="Q37" s="28" t="n">
-        <v>-0.070114</v>
+        <v>-0.069954</v>
       </c>
       <c r="R37" s="26" t="n">
         <v>0</v>
@@ -11441,7 +11465,7 @@
       </c>
       <c r="BA37" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB37" s="24" t="inlineStr">
@@ -11456,7 +11480,7 @@
       </c>
       <c r="BD37" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE37" s="24" t="inlineStr">
@@ -11476,7 +11500,7 @@
       </c>
       <c r="BH37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:06.178300Z</t>
+          <t>2026-08-02T08:19:12.309327Z</t>
         </is>
       </c>
       <c r="BI37" s="24" t="inlineStr">
@@ -11526,12 +11550,12 @@
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>98d6637e728e4660</t>
+          <t>56ae020f00c84725</t>
         </is>
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
@@ -11576,23 +11600,23 @@
         </is>
       </c>
       <c r="L38" s="26" t="n">
-        <v>-117</v>
+        <v>-104</v>
       </c>
       <c r="M38" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.961538</v>
       </c>
       <c r="N38" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.509804</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.676069</v>
       </c>
       <c r="P38" s="28" t="n"/>
       <c r="Q38" s="28" t="n">
-        <v>0.136729</v>
+        <v>0.166265</v>
       </c>
       <c r="R38" s="26" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="S38" s="29" t="n">
         <v>1.75</v>
@@ -11618,7 +11642,7 @@
       <c r="AD38" s="24" t="n"/>
       <c r="AE38" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-cs2-dc-for-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-dc-for-2026-08-02).</t>
         </is>
       </c>
       <c r="AF38" s="31" t="inlineStr">
@@ -11702,7 +11726,7 @@
       </c>
       <c r="BA38" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB38" s="24" t="inlineStr">
@@ -11717,7 +11741,7 @@
       </c>
       <c r="BD38" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE38" s="24" t="inlineStr">
@@ -11737,7 +11761,7 @@
       </c>
       <c r="BH38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:06.663767Z</t>
+          <t>2026-08-02T08:19:12.784904Z</t>
         </is>
       </c>
       <c r="BI38" s="24" t="inlineStr">
@@ -11747,13 +11771,13 @@
       </c>
       <c r="BJ38" s="25" t="n"/>
       <c r="BK38" s="26" t="n">
-        <v>-117</v>
+        <v>-104</v>
       </c>
       <c r="BL38" s="27" t="n">
-        <v>1.854701</v>
+        <v>1.961538</v>
       </c>
       <c r="BM38" s="28" t="n">
-        <v>0.539171</v>
+        <v>0.509804</v>
       </c>
       <c r="BN38" s="28" t="n"/>
       <c r="BO38" s="28" t="n"/>
@@ -11787,12 +11811,12 @@
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>b1ad3c78351b497f</t>
+          <t>8b14dcae8bc9432a</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
@@ -11837,20 +11861,20 @@
         </is>
       </c>
       <c r="L39" s="26" t="n">
-        <v>-194</v>
+        <v>-186</v>
       </c>
       <c r="M39" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.537634</v>
       </c>
       <c r="N39" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.65035</v>
       </c>
       <c r="O39" s="28" t="n">
-        <v>0.583544</v>
+        <v>0.583693</v>
       </c>
       <c r="P39" s="28" t="n"/>
       <c r="Q39" s="28" t="n">
-        <v>-0.07632</v>
+        <v>-0.06665699999999999</v>
       </c>
       <c r="R39" s="26" t="n">
         <v>0</v>
@@ -11879,7 +11903,7 @@
       <c r="AD39" s="24" t="n"/>
       <c r="AE39" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-ica-exmana-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-cs2-ica-exmana-2026-08-02).</t>
         </is>
       </c>
       <c r="AF39" s="31" t="inlineStr">
@@ -11963,7 +11987,7 @@
       </c>
       <c r="BA39" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB39" s="24" t="inlineStr">
@@ -11978,7 +12002,7 @@
       </c>
       <c r="BD39" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE39" s="24" t="inlineStr">
@@ -11998,7 +12022,7 @@
       </c>
       <c r="BH39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:07.143550Z</t>
+          <t>2026-08-02T08:19:13.318644Z</t>
         </is>
       </c>
       <c r="BI39" s="24" t="inlineStr">
@@ -12008,13 +12032,13 @@
       </c>
       <c r="BJ39" s="25" t="n"/>
       <c r="BK39" s="26" t="n">
-        <v>-194</v>
+        <v>-186</v>
       </c>
       <c r="BL39" s="27" t="n">
-        <v>1.515464</v>
+        <v>1.537634</v>
       </c>
       <c r="BM39" s="28" t="n">
-        <v>0.659864</v>
+        <v>0.65035</v>
       </c>
       <c r="BN39" s="28" t="n"/>
       <c r="BO39" s="28" t="n"/>
@@ -12048,12 +12072,12 @@
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>7f074a9ff64d4fa9</t>
+          <t>c88045061170496c</t>
         </is>
       </c>
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
@@ -12107,11 +12131,11 @@
         <v>0.420168</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>0.563968</v>
+        <v>0.563872</v>
       </c>
       <c r="P40" s="28" t="n"/>
       <c r="Q40" s="28" t="n">
-        <v>0.1438</v>
+        <v>0.143704</v>
       </c>
       <c r="R40" s="26" t="n">
         <v>92</v>
@@ -12224,7 +12248,7 @@
       </c>
       <c r="BA40" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB40" s="24" t="inlineStr">
@@ -12239,7 +12263,7 @@
       </c>
       <c r="BD40" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE40" s="24" t="inlineStr">
@@ -12259,7 +12283,7 @@
       </c>
       <c r="BH40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:07.634080Z</t>
+          <t>2026-08-02T08:19:13.866447Z</t>
         </is>
       </c>
       <c r="BI40" s="24" t="inlineStr">
@@ -12309,12 +12333,12 @@
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>7ab4e6dbbee94678</t>
+          <t>ca4f76153b4b49b9</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
@@ -12368,11 +12392,11 @@
         <v>0.6</v>
       </c>
       <c r="O41" s="28" t="n">
-        <v>0.65398</v>
+        <v>0.6541439999999999</v>
       </c>
       <c r="P41" s="28" t="n"/>
       <c r="Q41" s="28" t="n">
-        <v>0.05398</v>
+        <v>0.054144</v>
       </c>
       <c r="R41" s="26" t="n">
         <v>47</v>
@@ -12485,7 +12509,7 @@
       </c>
       <c r="BA41" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB41" s="24" t="inlineStr">
@@ -12500,7 +12524,7 @@
       </c>
       <c r="BD41" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE41" s="24" t="inlineStr">
@@ -12520,7 +12544,7 @@
       </c>
       <c r="BH41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:08.677895Z</t>
+          <t>2026-08-02T08:19:15.050508Z</t>
         </is>
       </c>
       <c r="BI41" s="24" t="inlineStr">
@@ -12570,12 +12594,12 @@
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>5a94d37632b84824</t>
+          <t>1ec8b20859c94f21</t>
         </is>
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
@@ -12629,11 +12653,11 @@
         <v>0.65035</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>0.74691</v>
+        <v>0.747081</v>
       </c>
       <c r="P42" s="28" t="n"/>
       <c r="Q42" s="28" t="n">
-        <v>0.09656000000000001</v>
+        <v>0.096731</v>
       </c>
       <c r="R42" s="26" t="n">
         <v>68</v>
@@ -12746,7 +12770,7 @@
       </c>
       <c r="BA42" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB42" s="24" t="inlineStr">
@@ -12761,7 +12785,7 @@
       </c>
       <c r="BD42" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE42" s="24" t="inlineStr">
@@ -12781,7 +12805,7 @@
       </c>
       <c r="BH42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:09.248034Z</t>
+          <t>2026-08-02T08:19:15.582287Z</t>
         </is>
       </c>
       <c r="BI42" s="24" t="inlineStr">
@@ -12831,12 +12855,12 @@
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>7da850e10ee34806</t>
+          <t>decb9ca4ca3d4bae</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
@@ -12881,23 +12905,23 @@
         </is>
       </c>
       <c r="L43" s="26" t="n">
-        <v>-170</v>
+        <v>-163</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.613497</v>
       </c>
       <c r="N43" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.619772</v>
       </c>
       <c r="O43" s="28" t="n">
-        <v>0.661873</v>
+        <v>0.662043</v>
       </c>
       <c r="P43" s="28" t="n"/>
       <c r="Q43" s="28" t="n">
-        <v>0.032243</v>
+        <v>0.042271</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="S43" s="29" t="n">
         <v>1.75</v>
@@ -12923,7 +12947,7 @@
       <c r="AD43" s="24" t="n"/>
       <c r="AE43" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-erx-hon-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-erx-hon-2026-08-02).</t>
         </is>
       </c>
       <c r="AF43" s="31" t="inlineStr">
@@ -13007,7 +13031,7 @@
       </c>
       <c r="BA43" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB43" s="24" t="inlineStr">
@@ -13022,7 +13046,7 @@
       </c>
       <c r="BD43" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE43" s="24" t="inlineStr">
@@ -13042,7 +13066,7 @@
       </c>
       <c r="BH43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:09.718841Z</t>
+          <t>2026-08-02T08:19:16.117377Z</t>
         </is>
       </c>
       <c r="BI43" s="24" t="inlineStr">
@@ -13052,13 +13076,13 @@
       </c>
       <c r="BJ43" s="25" t="n"/>
       <c r="BK43" s="26" t="n">
-        <v>-170</v>
+        <v>-163</v>
       </c>
       <c r="BL43" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.613497</v>
       </c>
       <c r="BM43" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.619772</v>
       </c>
       <c r="BN43" s="28" t="n"/>
       <c r="BO43" s="28" t="n"/>
@@ -13092,12 +13116,12 @@
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>fdfc810e7ffe4402</t>
+          <t>4f82f9ad0e214efb</t>
         </is>
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
@@ -13142,23 +13166,23 @@
         </is>
       </c>
       <c r="L44" s="26" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.641026</v>
       </c>
       <c r="N44" s="28" t="n">
-        <v>0.6</v>
+        <v>0.609375</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>0.6664099999999999</v>
+        <v>0.66636</v>
       </c>
       <c r="P44" s="28" t="n"/>
       <c r="Q44" s="28" t="n">
-        <v>0.06641</v>
+        <v>0.056985</v>
       </c>
       <c r="R44" s="26" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="S44" s="29" t="n">
         <v>1.75</v>
@@ -13184,7 +13208,7 @@
       <c r="AD44" s="24" t="n"/>
       <c r="AE44" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
         </is>
       </c>
       <c r="AF44" s="31" t="inlineStr">
@@ -13268,7 +13292,7 @@
       </c>
       <c r="BA44" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB44" s="24" t="inlineStr">
@@ -13283,7 +13307,7 @@
       </c>
       <c r="BD44" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE44" s="24" t="inlineStr">
@@ -13303,7 +13327,7 @@
       </c>
       <c r="BH44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:11.282396Z</t>
+          <t>2026-08-02T08:19:17.713467Z</t>
         </is>
       </c>
       <c r="BI44" s="24" t="inlineStr">
@@ -13313,13 +13337,13 @@
       </c>
       <c r="BJ44" s="25" t="n"/>
       <c r="BK44" s="26" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="BL44" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.641026</v>
       </c>
       <c r="BM44" s="28" t="n">
-        <v>0.6</v>
+        <v>0.609375</v>
       </c>
       <c r="BN44" s="28" t="n"/>
       <c r="BO44" s="28" t="n"/>
@@ -13353,12 +13377,12 @@
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>b3b5330f268c41ad</t>
+          <t>87d265955cc34abf</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
@@ -13403,23 +13427,23 @@
         </is>
       </c>
       <c r="L45" s="26" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="M45" s="27" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="N45" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.4</v>
       </c>
       <c r="O45" s="28" t="n">
-        <v>0.510415</v>
+        <v>0.510543</v>
       </c>
       <c r="P45" s="28" t="n"/>
       <c r="Q45" s="28" t="n">
-        <v>0.09024699999999999</v>
+        <v>0.110543</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="S45" s="29" t="n">
         <v>1</v>
@@ -13445,7 +13469,7 @@
       <c r="AD45" s="24" t="n"/>
       <c r="AE45" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-shin-bst-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-shin-bst-2026-08-02).</t>
         </is>
       </c>
       <c r="AF45" s="31" t="inlineStr">
@@ -13529,7 +13553,7 @@
       </c>
       <c r="BA45" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB45" s="24" t="inlineStr">
@@ -13544,7 +13568,7 @@
       </c>
       <c r="BD45" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE45" s="24" t="inlineStr">
@@ -13564,7 +13588,7 @@
       </c>
       <c r="BH45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:11.856492Z</t>
+          <t>2026-08-02T08:19:18.366310Z</t>
         </is>
       </c>
       <c r="BI45" s="24" t="inlineStr">
@@ -13574,13 +13598,13 @@
       </c>
       <c r="BJ45" s="25" t="n"/>
       <c r="BK45" s="26" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="BL45" s="27" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="BM45" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.4</v>
       </c>
       <c r="BN45" s="28" t="n"/>
       <c r="BO45" s="28" t="n"/>
@@ -13614,12 +13638,12 @@
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>15f2408e29fd4258</t>
+          <t>09df7b524a97466a</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
@@ -13673,11 +13697,11 @@
         <v>0.640288</v>
       </c>
       <c r="O46" s="28" t="n">
-        <v>0.5266110000000001</v>
+        <v>0.526743</v>
       </c>
       <c r="P46" s="28" t="n"/>
       <c r="Q46" s="28" t="n">
-        <v>-0.113677</v>
+        <v>-0.113545</v>
       </c>
       <c r="R46" s="26" t="n">
         <v>0</v>
@@ -13790,7 +13814,7 @@
       </c>
       <c r="BA46" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB46" s="24" t="inlineStr">
@@ -13805,7 +13829,7 @@
       </c>
       <c r="BD46" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE46" s="24" t="inlineStr">
@@ -13825,7 +13849,7 @@
       </c>
       <c r="BH46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:12.356484Z</t>
+          <t>2026-08-02T08:19:18.951273Z</t>
         </is>
       </c>
       <c r="BI46" s="24" t="inlineStr">
@@ -13875,12 +13899,12 @@
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>588fedbfd6204f81</t>
+          <t>b50cdfc659ba4798</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
@@ -13925,20 +13949,20 @@
         </is>
       </c>
       <c r="L47" s="26" t="n">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.390625</v>
       </c>
       <c r="O47" s="28" t="n">
-        <v>0.57939</v>
+        <v>0.579539</v>
       </c>
       <c r="P47" s="28" t="n"/>
       <c r="Q47" s="28" t="n">
-        <v>0.22974</v>
+        <v>0.188914</v>
       </c>
       <c r="R47" s="26" t="n">
         <v>100</v>
@@ -13967,7 +13991,7 @@
       <c r="AD47" s="24" t="n"/>
       <c r="AE47" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
         </is>
       </c>
       <c r="AF47" s="31" t="inlineStr">
@@ -14051,7 +14075,7 @@
       </c>
       <c r="BA47" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB47" s="24" t="inlineStr">
@@ -14066,7 +14090,7 @@
       </c>
       <c r="BD47" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE47" s="24" t="inlineStr">
@@ -14086,7 +14110,7 @@
       </c>
       <c r="BH47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:12.889350Z</t>
+          <t>2026-08-02T08:19:19.608833Z</t>
         </is>
       </c>
       <c r="BI47" s="24" t="inlineStr">
@@ -14096,13 +14120,13 @@
       </c>
       <c r="BJ47" s="25" t="n"/>
       <c r="BK47" s="26" t="n">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="BL47" s="27" t="n">
-        <v>2.86</v>
+        <v>2.56</v>
       </c>
       <c r="BM47" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.390625</v>
       </c>
       <c r="BN47" s="28" t="n"/>
       <c r="BO47" s="28" t="n"/>
@@ -14136,22 +14160,22 @@
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>df5fbea4dd924549</t>
+          <t>e41a38b5a7264af3</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-03T08:00:00Z</t>
         </is>
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>67510</t>
+          <t>67490</t>
         </is>
       </c>
       <c r="E48" s="24" t="inlineStr">
@@ -14161,12 +14185,12 @@
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>VP.Prodigy</t>
         </is>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Eternal Fire Academy</t>
         </is>
       </c>
       <c r="H48" s="24" t="inlineStr">
@@ -14176,7 +14200,7 @@
       </c>
       <c r="I48" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J48" s="25" t="n"/>
@@ -14195,17 +14219,17 @@
         <v>0.690402</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>0.562959</v>
+        <v>0.646647</v>
       </c>
       <c r="P48" s="28" t="n"/>
       <c r="Q48" s="28" t="n">
-        <v>-0.127443</v>
+        <v>-0.043755</v>
       </c>
       <c r="R48" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S48" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T48" s="24" t="inlineStr">
         <is>
@@ -14228,7 +14252,7 @@
       <c r="AD48" s="24" t="n"/>
       <c r="AE48" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-efa-vpp-2026-08-03).</t>
         </is>
       </c>
       <c r="AF48" s="31" t="inlineStr">
@@ -14269,32 +14293,32 @@
       </c>
       <c r="AP48" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>VP.Prodigy</t>
         </is>
       </c>
       <c r="AQ48" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>VP.Prodigy</t>
         </is>
       </c>
       <c r="AR48" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>VP.Prodigy</t>
         </is>
       </c>
       <c r="AS48" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Eternal Fire Academy</t>
         </is>
       </c>
       <c r="AT48" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Eternal Fire Academy</t>
         </is>
       </c>
       <c r="AU48" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Eternal Fire Academy</t>
         </is>
       </c>
       <c r="AV48" s="24" t="n"/>
@@ -14312,7 +14336,7 @@
       </c>
       <c r="BA48" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB48" s="24" t="inlineStr">
@@ -14327,7 +14351,7 @@
       </c>
       <c r="BD48" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE48" s="24" t="inlineStr">
@@ -14347,7 +14371,7 @@
       </c>
       <c r="BH48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:15.647933Z</t>
+          <t>2026-08-02T08:19:20.659011Z</t>
         </is>
       </c>
       <c r="BI48" s="24" t="inlineStr">
@@ -14397,22 +14421,22 @@
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>bdd3531261214a53</t>
+          <t>cb9b1b93c1334fe0</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:30:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>67514</t>
+          <t>67510</t>
         </is>
       </c>
       <c r="E49" s="24" t="inlineStr">
@@ -14422,12 +14446,12 @@
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>Passion Academy</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr">
@@ -14447,26 +14471,26 @@
         </is>
       </c>
       <c r="L49" s="26" t="n">
-        <v>100</v>
+        <v>-223</v>
       </c>
       <c r="M49" s="27" t="n">
-        <v>2</v>
+        <v>1.44843</v>
       </c>
       <c r="N49" s="28" t="n">
-        <v>0.5</v>
+        <v>0.690402</v>
       </c>
       <c r="O49" s="28" t="n">
-        <v>0.640064</v>
+        <v>0.563104</v>
       </c>
       <c r="P49" s="28" t="n"/>
       <c r="Q49" s="28" t="n">
-        <v>0.140064</v>
+        <v>-0.127298</v>
       </c>
       <c r="R49" s="26" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="S49" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T49" s="24" t="inlineStr">
         <is>
@@ -14489,7 +14513,7 @@
       <c r="AD49" s="24" t="n"/>
       <c r="AE49" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
         </is>
       </c>
       <c r="AF49" s="31" t="inlineStr">
@@ -14507,7 +14531,7 @@
       <c r="AJ49" s="31" t="n"/>
       <c r="AK49" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL49" s="26" t="n">
@@ -14515,47 +14539,47 @@
       </c>
       <c r="AM49" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN49" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO49" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP49" s="24" t="inlineStr">
         <is>
-          <t>Passion Academy</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AQ49" s="24" t="inlineStr">
         <is>
-          <t>Passion Academy</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AR49" s="24" t="inlineStr">
         <is>
-          <t>Passion Academy</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AS49" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AT49" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AU49" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AV49" s="24" t="n"/>
@@ -14573,7 +14597,7 @@
       </c>
       <c r="BA49" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB49" s="24" t="inlineStr">
@@ -14588,7 +14612,7 @@
       </c>
       <c r="BD49" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE49" s="24" t="inlineStr">
@@ -14608,7 +14632,7 @@
       </c>
       <c r="BH49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:17.283191Z</t>
+          <t>2026-08-02T08:19:22.224868Z</t>
         </is>
       </c>
       <c r="BI49" s="24" t="inlineStr">
@@ -14618,13 +14642,13 @@
       </c>
       <c r="BJ49" s="25" t="n"/>
       <c r="BK49" s="26" t="n">
-        <v>100</v>
+        <v>-223</v>
       </c>
       <c r="BL49" s="27" t="n">
-        <v>2</v>
+        <v>1.44843</v>
       </c>
       <c r="BM49" s="28" t="n">
-        <v>0.5</v>
+        <v>0.690402</v>
       </c>
       <c r="BN49" s="28" t="n"/>
       <c r="BO49" s="28" t="n"/>
@@ -14658,22 +14682,22 @@
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>243c49bec8c540a2</t>
+          <t>b4249330287542e3</t>
         </is>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T11:00:00Z</t>
+          <t>2026-08-03T10:30:00Z</t>
         </is>
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>67578</t>
+          <t>67514</t>
         </is>
       </c>
       <c r="E50" s="24" t="inlineStr">
@@ -14683,12 +14707,12 @@
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr">
@@ -14708,26 +14732,26 @@
         </is>
       </c>
       <c r="L50" s="26" t="n">
-        <v>-170</v>
+        <v>-122</v>
       </c>
       <c r="M50" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.819672</v>
       </c>
       <c r="N50" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.54955</v>
       </c>
       <c r="O50" s="28" t="n">
-        <v>0.5266110000000001</v>
+        <v>0.640228</v>
       </c>
       <c r="P50" s="28" t="n"/>
       <c r="Q50" s="28" t="n">
-        <v>-0.103019</v>
+        <v>0.09067799999999999</v>
       </c>
       <c r="R50" s="26" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="S50" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T50" s="24" t="inlineStr">
         <is>
@@ -14750,7 +14774,7 @@
       <c r="AD50" s="24" t="n"/>
       <c r="AE50" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
         </is>
       </c>
       <c r="AF50" s="31" t="inlineStr">
@@ -14768,7 +14792,7 @@
       <c r="AJ50" s="31" t="n"/>
       <c r="AK50" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL50" s="26" t="n">
@@ -14776,47 +14800,47 @@
       </c>
       <c r="AM50" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN50" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO50" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP50" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AQ50" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AR50" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AS50" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AT50" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AU50" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AV50" s="24" t="n"/>
@@ -14834,7 +14858,7 @@
       </c>
       <c r="BA50" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB50" s="24" t="inlineStr">
@@ -14849,7 +14873,7 @@
       </c>
       <c r="BD50" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE50" s="24" t="inlineStr">
@@ -14869,7 +14893,7 @@
       </c>
       <c r="BH50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:17.856987Z</t>
+          <t>2026-08-02T08:19:23.793481Z</t>
         </is>
       </c>
       <c r="BI50" s="24" t="inlineStr">
@@ -14879,13 +14903,13 @@
       </c>
       <c r="BJ50" s="25" t="n"/>
       <c r="BK50" s="26" t="n">
-        <v>-170</v>
+        <v>-122</v>
       </c>
       <c r="BL50" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.819672</v>
       </c>
       <c r="BM50" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.54955</v>
       </c>
       <c r="BN50" s="28" t="n"/>
       <c r="BO50" s="28" t="n"/>
@@ -14919,22 +14943,22 @@
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>509e7f0ed553481e</t>
+          <t>6127dbef3f574b64</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.505191Z</t>
+          <t>2026-08-02T08:19:31.181747Z</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T23:00:00Z</t>
+          <t>2026-08-03T11:00:00Z</t>
         </is>
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>68043</t>
+          <t>67578</t>
         </is>
       </c>
       <c r="E51" s="24" t="inlineStr">
@@ -14944,12 +14968,12 @@
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="H51" s="24" t="inlineStr">
@@ -14969,26 +14993,26 @@
         </is>
       </c>
       <c r="L51" s="26" t="n">
-        <v>122</v>
+        <v>-170</v>
       </c>
       <c r="M51" s="27" t="n">
-        <v>2.22</v>
+        <v>1.588235</v>
       </c>
       <c r="N51" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.62963</v>
       </c>
       <c r="O51" s="28" t="n">
-        <v>0.569433</v>
+        <v>0.526743</v>
       </c>
       <c r="P51" s="28" t="n"/>
       <c r="Q51" s="28" t="n">
-        <v>0.118983</v>
+        <v>-0.102887</v>
       </c>
       <c r="R51" s="26" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="S51" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T51" s="24" t="inlineStr">
         <is>
@@ -15011,7 +15035,7 @@
       <c r="AD51" s="24" t="n"/>
       <c r="AE51" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
         </is>
       </c>
       <c r="AF51" s="31" t="inlineStr">
@@ -15052,32 +15076,32 @@
       </c>
       <c r="AP51" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AQ51" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AR51" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AS51" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AT51" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AU51" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AV51" s="24" t="n"/>
@@ -15095,7 +15119,7 @@
       </c>
       <c r="BA51" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BB51" s="24" t="inlineStr">
@@ -15110,7 +15134,7 @@
       </c>
       <c r="BD51" s="24" t="inlineStr">
         <is>
-          <t>43d985cc5d70edc577b4f1cac09fef882d817938dc77ba88e4cdf7954d2f8c58</t>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
         </is>
       </c>
       <c r="BE51" s="24" t="inlineStr">
@@ -15130,7 +15154,7 @@
       </c>
       <c r="BH51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:16:24.503358Z</t>
+          <t>2026-08-02T08:19:24.359608Z</t>
         </is>
       </c>
       <c r="BI51" s="24" t="inlineStr">
@@ -15140,13 +15164,13 @@
       </c>
       <c r="BJ51" s="25" t="n"/>
       <c r="BK51" s="26" t="n">
-        <v>122</v>
+        <v>-170</v>
       </c>
       <c r="BL51" s="27" t="n">
-        <v>2.22</v>
+        <v>1.588235</v>
       </c>
       <c r="BM51" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.62963</v>
       </c>
       <c r="BN51" s="28" t="n"/>
       <c r="BO51" s="28" t="n"/>
@@ -15177,6 +15201,528 @@
       <c r="CN51" s="24" t="n"/>
       <c r="CO51" s="24" t="n"/>
     </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>0d54aead8b234deb</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T08:19:31.181747Z</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>67579</t>
+        </is>
+      </c>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="H52" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J52" s="25" t="n"/>
+      <c r="K52" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L52" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="M52" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N52" s="28" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="O52" s="28" t="n">
+        <v>0.526658</v>
+      </c>
+      <c r="P52" s="28" t="n"/>
+      <c r="Q52" s="28" t="n">
+        <v>0.21706</v>
+      </c>
+      <c r="R52" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S52" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U52" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V52" s="24" t="n"/>
+      <c r="W52" s="26" t="n"/>
+      <c r="X52" s="26" t="n"/>
+      <c r="Y52" s="25" t="n"/>
+      <c r="Z52" s="26" t="n"/>
+      <c r="AA52" s="28" t="n"/>
+      <c r="AB52" s="28" t="n"/>
+      <c r="AC52" s="30" t="n"/>
+      <c r="AD52" s="24" t="n"/>
+      <c r="AE52" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF52" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG52" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH52" s="24" t="n"/>
+      <c r="AI52" s="31" t="n"/>
+      <c r="AJ52" s="31" t="n"/>
+      <c r="AK52" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL52" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM52" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN52" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO52" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP52" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AQ52" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AR52" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AS52" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AT52" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AU52" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AV52" s="24" t="n"/>
+      <c r="AW52" s="24" t="n"/>
+      <c r="AX52" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY52" s="24" t="n"/>
+      <c r="AZ52" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA52" s="24" t="inlineStr">
+        <is>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+        </is>
+      </c>
+      <c r="BB52" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC52" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD52" s="24" t="inlineStr">
+        <is>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+        </is>
+      </c>
+      <c r="BE52" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF52" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG52" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T08:19:25.914540Z</t>
+        </is>
+      </c>
+      <c r="BI52" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ52" s="25" t="n"/>
+      <c r="BK52" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="BL52" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BM52" s="28" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="BN52" s="28" t="n"/>
+      <c r="BO52" s="28" t="n"/>
+      <c r="BP52" s="25" t="n"/>
+      <c r="BQ52" s="27" t="n"/>
+      <c r="BR52" s="28" t="n"/>
+      <c r="BS52" s="28" t="n"/>
+      <c r="BT52" s="28" t="n"/>
+      <c r="BU52" s="25" t="n"/>
+      <c r="BV52" s="29" t="n"/>
+      <c r="BW52" s="24" t="n"/>
+      <c r="BX52" s="30" t="n"/>
+      <c r="BY52" s="27" t="n"/>
+      <c r="BZ52" s="24" t="n"/>
+      <c r="CA52" s="31" t="n"/>
+      <c r="CB52" s="24" t="n"/>
+      <c r="CC52" s="24" t="n"/>
+      <c r="CD52" s="24" t="n"/>
+      <c r="CE52" s="24" t="n"/>
+      <c r="CF52" s="24" t="n"/>
+      <c r="CG52" s="24" t="n"/>
+      <c r="CH52" s="24" t="n"/>
+      <c r="CI52" s="24" t="n"/>
+      <c r="CJ52" s="24" t="n"/>
+      <c r="CK52" s="24" t="n"/>
+      <c r="CL52" s="24" t="n"/>
+      <c r="CM52" s="24" t="n"/>
+      <c r="CN52" s="24" t="n"/>
+      <c r="CO52" s="24" t="n"/>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>6448946bd28040a7</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T08:19:31.181747Z</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>68043</t>
+        </is>
+      </c>
+      <c r="E53" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F53" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="G53" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="H53" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I53" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J53" s="25" t="n"/>
+      <c r="K53" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L53" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M53" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N53" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="O53" s="28" t="n">
+        <v>0.569576</v>
+      </c>
+      <c r="P53" s="28" t="n"/>
+      <c r="Q53" s="28" t="n">
+        <v>0.100092</v>
+      </c>
+      <c r="R53" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="S53" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T53" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U53" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V53" s="24" t="n"/>
+      <c r="W53" s="26" t="n"/>
+      <c r="X53" s="26" t="n"/>
+      <c r="Y53" s="25" t="n"/>
+      <c r="Z53" s="26" t="n"/>
+      <c r="AA53" s="28" t="n"/>
+      <c r="AB53" s="28" t="n"/>
+      <c r="AC53" s="30" t="n"/>
+      <c r="AD53" s="24" t="n"/>
+      <c r="AE53" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF53" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG53" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH53" s="24" t="n"/>
+      <c r="AI53" s="31" t="n"/>
+      <c r="AJ53" s="31" t="n"/>
+      <c r="AK53" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL53" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM53" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN53" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO53" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP53" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AQ53" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AR53" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AS53" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AT53" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AU53" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AV53" s="24" t="n"/>
+      <c r="AW53" s="24" t="n"/>
+      <c r="AX53" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY53" s="24" t="n"/>
+      <c r="AZ53" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA53" s="24" t="inlineStr">
+        <is>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+        </is>
+      </c>
+      <c r="BB53" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC53" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD53" s="24" t="inlineStr">
+        <is>
+          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+        </is>
+      </c>
+      <c r="BE53" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF53" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG53" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH53" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T08:19:31.178279Z</t>
+        </is>
+      </c>
+      <c r="BI53" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ53" s="25" t="n"/>
+      <c r="BK53" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="BL53" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM53" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="BN53" s="28" t="n"/>
+      <c r="BO53" s="28" t="n"/>
+      <c r="BP53" s="25" t="n"/>
+      <c r="BQ53" s="27" t="n"/>
+      <c r="BR53" s="28" t="n"/>
+      <c r="BS53" s="28" t="n"/>
+      <c r="BT53" s="28" t="n"/>
+      <c r="BU53" s="25" t="n"/>
+      <c r="BV53" s="29" t="n"/>
+      <c r="BW53" s="24" t="n"/>
+      <c r="BX53" s="30" t="n"/>
+      <c r="BY53" s="27" t="n"/>
+      <c r="BZ53" s="24" t="n"/>
+      <c r="CA53" s="31" t="n"/>
+      <c r="CB53" s="24" t="n"/>
+      <c r="CC53" s="24" t="n"/>
+      <c r="CD53" s="24" t="n"/>
+      <c r="CE53" s="24" t="n"/>
+      <c r="CF53" s="24" t="n"/>
+      <c r="CG53" s="24" t="n"/>
+      <c r="CH53" s="24" t="n"/>
+      <c r="CI53" s="24" t="n"/>
+      <c r="CJ53" s="24" t="n"/>
+      <c r="CK53" s="24" t="n"/>
+      <c r="CL53" s="24" t="n"/>
+      <c r="CM53" s="24" t="n"/>
+      <c r="CN53" s="24" t="n"/>
+      <c r="CO53" s="24" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO53" headerRowCount="1">
-  <autoFilter ref="A1:CO53"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO49" headerRowCount="1">
+  <autoFilter ref="A1:CO49"/>
   <tableColumns count="93">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -752,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$53)</f>
+        <f>COUNTA('Picks'!$A$2:$A$49)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$53,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$49,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$53,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$49,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")+COUNTIFS('Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$49,"settled",'Picks'!$V$2:$V$49,"win")+COUNTIFS('Picks'!$U$2:$U$49,"settled",'Picks'!$V$2:$V$49,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$53,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$49,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$49,"&gt;0",'Picks'!$V$2:$V$49,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$49,"&gt;0",'Picks'!$V$2:$V$49,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"win")/(COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"win")+COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$49,"&gt;0",'Picks'!$V$2:$V$49,"win")/(COUNTIFS('Picks'!$BX$2:$BX$49,"&gt;0",'Picks'!$V$2:$V$49,"win")+COUNTIFS('Picks'!$BX$2:$BX$49,"&gt;0",'Picks'!$V$2:$V$49,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$53)/SUM('Picks'!$BX$2:$BX$53),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$49)/SUM('Picks'!$BX$2:$BX$49),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$53)</f>
+        <f>SUM('Picks'!$BY$2:$BY$49)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$53,"&lt;&gt;",'Picks'!$AB$2:$AB$53),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$49,"&lt;&gt;",'Picks'!$AB$2:$AB$49),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$53,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$53,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$49,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$49,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$53,'Picks'!$AM$2:$AM$53,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$49,'Picks'!$AM$2:$AM$49,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$49,$A14,'Picks'!$U$2:$U$49,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$49,$A14,'Picks'!$U$2:$U$49,"settled",'Picks'!$V$2:$V$49,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$49,$A14,'Picks'!$U$2:$U$49,"settled",'Picks'!$V$2:$V$49,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$53,'Picks'!$H$2:$H$53,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$49,'Picks'!$H$2:$H$49,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$53,'Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$49,'Picks'!$H$2:$H$49,$A14,'Picks'!$U$2:$U$49,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$49,$A15,'Picks'!$U$2:$U$49,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$49,$A15,'Picks'!$U$2:$U$49,"settled",'Picks'!$V$2:$V$49,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$49,$A15,'Picks'!$U$2:$U$49,"settled",'Picks'!$V$2:$V$49,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$53,'Picks'!$H$2:$H$53,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$49,'Picks'!$H$2:$H$49,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$53,'Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$49,'Picks'!$H$2:$H$49,$A15,'Picks'!$U$2:$U$49,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$49,$A16,'Picks'!$U$2:$U$49,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$49,$A16,'Picks'!$U$2:$U$49,"settled",'Picks'!$V$2:$V$49,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$49,$A16,'Picks'!$U$2:$U$49,"settled",'Picks'!$V$2:$V$49,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$53,'Picks'!$H$2:$H$53,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$49,'Picks'!$H$2:$H$49,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$53,'Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$49,'Picks'!$H$2:$H$49,$A16,'Picks'!$U$2:$U$49,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO53"/>
+  <dimension ref="A1:CO49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9201,22 +9201,22 @@
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>6a875257547b4c46</t>
+          <t>0276cc81aadc4f01</t>
         </is>
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:00Z</t>
+          <t>2026-08-02T10:30:00Z</t>
         </is>
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>69137</t>
+          <t>66836</t>
         </is>
       </c>
       <c r="E29" s="24" t="inlineStr">
@@ -9226,12 +9226,12 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Esports</t>
+          <t>Sangal ALTERS</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
         <is>
-          <t>GenOne</t>
+          <t>Teletubisie</t>
         </is>
       </c>
       <c r="H29" s="24" t="inlineStr">
@@ -9251,20 +9251,20 @@
         </is>
       </c>
       <c r="L29" s="26" t="n">
-        <v>138</v>
+        <v>-104</v>
       </c>
       <c r="M29" s="27" t="n">
-        <v>2.38</v>
+        <v>1.961538</v>
       </c>
       <c r="N29" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.509804</v>
       </c>
       <c r="O29" s="28" t="n">
-        <v>0.820361</v>
+        <v>0.690561</v>
       </c>
       <c r="P29" s="28" t="n"/>
       <c r="Q29" s="28" t="n">
-        <v>0.400193</v>
+        <v>0.180757</v>
       </c>
       <c r="R29" s="26" t="n">
         <v>100</v>
@@ -9293,7 +9293,7 @@
       <c r="AD29" s="24" t="n"/>
       <c r="AE29" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-g1-cs-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-ttbs-sng-2026-08-02).</t>
         </is>
       </c>
       <c r="AF29" s="31" t="inlineStr">
@@ -9311,7 +9311,7 @@
       <c r="AJ29" s="31" t="n"/>
       <c r="AK29" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL29" s="26" t="n">
@@ -9319,47 +9319,47 @@
       </c>
       <c r="AM29" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN29" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO29" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP29" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Esports</t>
+          <t>Sangal ALTERS</t>
         </is>
       </c>
       <c r="AQ29" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Esports</t>
+          <t>Sangal ALTERS</t>
         </is>
       </c>
       <c r="AR29" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Esports</t>
+          <t>Sangal ALTERS</t>
         </is>
       </c>
       <c r="AS29" s="24" t="inlineStr">
         <is>
-          <t>GenOne</t>
+          <t>Teletubisie</t>
         </is>
       </c>
       <c r="AT29" s="24" t="inlineStr">
         <is>
-          <t>GenOne</t>
+          <t>Teletubisie</t>
         </is>
       </c>
       <c r="AU29" s="24" t="inlineStr">
         <is>
-          <t>GenOne</t>
+          <t>Teletubisie</t>
         </is>
       </c>
       <c r="AV29" s="24" t="n"/>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="BA29" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB29" s="24" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="BD29" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE29" s="24" t="inlineStr">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="BH29" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:07.601616Z</t>
+          <t>2026-08-02T09:59:44.064703Z</t>
         </is>
       </c>
       <c r="BI29" s="24" t="inlineStr">
@@ -9422,13 +9422,13 @@
       </c>
       <c r="BJ29" s="25" t="n"/>
       <c r="BK29" s="26" t="n">
-        <v>138</v>
+        <v>-104</v>
       </c>
       <c r="BL29" s="27" t="n">
-        <v>2.38</v>
+        <v>1.961538</v>
       </c>
       <c r="BM29" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.509804</v>
       </c>
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
@@ -9462,22 +9462,22 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>432caac9002149a8</t>
+          <t>7890942306624702</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:00Z</t>
+          <t>2026-08-02T11:00:00Z</t>
         </is>
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>69163</t>
+          <t>69252</t>
         </is>
       </c>
       <c r="E30" s="24" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>NEW VISION</t>
         </is>
       </c>
       <c r="G30" s="24" t="inlineStr">
         <is>
-          <t>Sinners</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="H30" s="24" t="inlineStr">
@@ -9512,26 +9512,26 @@
         </is>
       </c>
       <c r="L30" s="26" t="n">
-        <v>-178</v>
+        <v>-133</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.75188</v>
       </c>
       <c r="N30" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.570815</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>0.626221</v>
+        <v>0.539324</v>
       </c>
       <c r="P30" s="28" t="n"/>
       <c r="Q30" s="28" t="n">
-        <v>-0.014067</v>
+        <v>-0.031491</v>
       </c>
       <c r="R30" s="26" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="S30" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T30" s="24" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
       <c r="AD30" s="24" t="n"/>
       <c r="AE30" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sin-sparta-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-ica-nve-2026-08-02).</t>
         </is>
       </c>
       <c r="AF30" s="31" t="inlineStr">
@@ -9595,32 +9595,32 @@
       </c>
       <c r="AP30" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>NEW VISION</t>
         </is>
       </c>
       <c r="AQ30" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>NEW VISION</t>
         </is>
       </c>
       <c r="AR30" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>NEW VISION</t>
         </is>
       </c>
       <c r="AS30" s="24" t="inlineStr">
         <is>
-          <t>Sinners</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AT30" s="24" t="inlineStr">
         <is>
-          <t>Sinners</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AU30" s="24" t="inlineStr">
         <is>
-          <t>Sinners</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AV30" s="24" t="n"/>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="BA30" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB30" s="24" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="BD30" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE30" s="24" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="BH30" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:08.072917Z</t>
+          <t>2026-08-02T09:59:44.535838Z</t>
         </is>
       </c>
       <c r="BI30" s="24" t="inlineStr">
@@ -9683,13 +9683,13 @@
       </c>
       <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
-        <v>-178</v>
+        <v>-133</v>
       </c>
       <c r="BL30" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.75188</v>
       </c>
       <c r="BM30" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.570815</v>
       </c>
       <c r="BN30" s="28" t="n"/>
       <c r="BO30" s="28" t="n"/>
@@ -9723,22 +9723,22 @@
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>669f2759c6a84d14</t>
+          <t>9f280e9d1f384c60</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:00Z</t>
+          <t>2026-08-02T13:00:00Z</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>69413</t>
+          <t>68673</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
@@ -9748,12 +9748,12 @@
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>ex-1win</t>
+          <t>Sashi Esport</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr">
@@ -9773,26 +9773,26 @@
         </is>
       </c>
       <c r="L31" s="26" t="n">
-        <v>-213</v>
+        <v>-203</v>
       </c>
       <c r="M31" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.492611</v>
       </c>
       <c r="N31" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.669967</v>
       </c>
       <c r="O31" s="28" t="n">
-        <v>0.714926</v>
+        <v>0.593754</v>
       </c>
       <c r="P31" s="28" t="n"/>
       <c r="Q31" s="28" t="n">
-        <v>0.034415</v>
+        <v>-0.076213</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="S31" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T31" s="24" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
       <c r="AD31" s="24" t="n"/>
       <c r="AE31" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-lc-ewx-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-bpl-sashi-2026-08-02).</t>
         </is>
       </c>
       <c r="AF31" s="31" t="inlineStr">
@@ -9833,7 +9833,7 @@
       <c r="AJ31" s="31" t="n"/>
       <c r="AK31" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL31" s="26" t="n">
@@ -9841,47 +9841,47 @@
       </c>
       <c r="AM31" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN31" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO31" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP31" s="24" t="inlineStr">
         <is>
-          <t>ex-1win</t>
+          <t>Sashi Esport</t>
         </is>
       </c>
       <c r="AQ31" s="24" t="inlineStr">
         <is>
-          <t>ex-1win</t>
+          <t>Sashi Esport</t>
         </is>
       </c>
       <c r="AR31" s="24" t="inlineStr">
         <is>
-          <t>ex-1win</t>
+          <t>Sashi Esport</t>
         </is>
       </c>
       <c r="AS31" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AT31" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AU31" s="24" t="inlineStr">
         <is>
-          <t>Lazer Cats</t>
+          <t>Black Phoenix</t>
         </is>
       </c>
       <c r="AV31" s="24" t="n"/>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="BA31" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB31" s="24" t="inlineStr">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="BD31" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE31" s="24" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="BH31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:08.739294Z</t>
+          <t>2026-08-02T09:59:45.037220Z</t>
         </is>
       </c>
       <c r="BI31" s="24" t="inlineStr">
@@ -9944,13 +9944,13 @@
       </c>
       <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
-        <v>-213</v>
+        <v>-203</v>
       </c>
       <c r="BL31" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.492611</v>
       </c>
       <c r="BM31" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.669967</v>
       </c>
       <c r="BN31" s="28" t="n"/>
       <c r="BO31" s="28" t="n"/>
@@ -9984,22 +9984,22 @@
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>766179d9252f497f</t>
+          <t>3904a03493c1476b</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:00Z</t>
+          <t>2026-08-02T13:00:00Z</t>
         </is>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>66809</t>
+          <t>68255</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>WBT</t>
         </is>
       </c>
       <c r="G32" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr">
@@ -10034,23 +10034,23 @@
         </is>
       </c>
       <c r="L32" s="26" t="n">
-        <v>203</v>
+        <v>-133</v>
       </c>
       <c r="M32" s="27" t="n">
-        <v>3.03</v>
+        <v>1.75188</v>
       </c>
       <c r="N32" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.570815</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>0.531394</v>
+        <v>0.543392</v>
       </c>
       <c r="P32" s="28" t="n"/>
       <c r="Q32" s="28" t="n">
-        <v>0.201361</v>
+        <v>-0.027423</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="S32" s="29" t="n">
         <v>1</v>
@@ -10076,7 +10076,7 @@
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-cs2-9ine-brute-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-mouzn-wba-2026-08-02).</t>
         </is>
       </c>
       <c r="AF32" s="31" t="inlineStr">
@@ -10094,7 +10094,7 @@
       <c r="AJ32" s="31" t="n"/>
       <c r="AK32" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL32" s="26" t="n">
@@ -10102,47 +10102,47 @@
       </c>
       <c r="AM32" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN32" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO32" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP32" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>WBT</t>
         </is>
       </c>
       <c r="AQ32" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>WBT</t>
         </is>
       </c>
       <c r="AR32" s="24" t="inlineStr">
         <is>
-          <t>Brute</t>
+          <t>WBT</t>
         </is>
       </c>
       <c r="AS32" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AT32" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AU32" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AV32" s="24" t="n"/>
@@ -10160,7 +10160,7 @@
       </c>
       <c r="BA32" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB32" s="24" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="BD32" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE32" s="24" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="BH32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:09.283371Z</t>
+          <t>2026-08-02T09:59:45.600229Z</t>
         </is>
       </c>
       <c r="BI32" s="24" t="inlineStr">
@@ -10205,13 +10205,13 @@
       </c>
       <c r="BJ32" s="25" t="n"/>
       <c r="BK32" s="26" t="n">
-        <v>203</v>
+        <v>-133</v>
       </c>
       <c r="BL32" s="27" t="n">
-        <v>3.03</v>
+        <v>1.75188</v>
       </c>
       <c r="BM32" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.570815</v>
       </c>
       <c r="BN32" s="28" t="n"/>
       <c r="BO32" s="28" t="n"/>
@@ -10245,22 +10245,22 @@
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>79721cb291414869</t>
+          <t>02a02b088b82494b</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:30:00Z</t>
+          <t>2026-08-02T13:00:00Z</t>
         </is>
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>66836</t>
+          <t>68256</t>
         </is>
       </c>
       <c r="E33" s="24" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
-          <t>Sangal ALTERS</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="G33" s="24" t="inlineStr">
         <is>
-          <t>Teletubisie</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="H33" s="24" t="inlineStr">
@@ -10295,26 +10295,26 @@
         </is>
       </c>
       <c r="L33" s="26" t="n">
-        <v>-104</v>
+        <v>-223</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.44843</v>
       </c>
       <c r="N33" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.690402</v>
       </c>
       <c r="O33" s="28" t="n">
-        <v>0.690561</v>
+        <v>0.620448</v>
       </c>
       <c r="P33" s="28" t="n"/>
       <c r="Q33" s="28" t="n">
-        <v>0.180757</v>
+        <v>-0.069954</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S33" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T33" s="24" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-ttbs-sng-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-lk-nvo-2026-08-02).</t>
         </is>
       </c>
       <c r="AF33" s="31" t="inlineStr">
@@ -10355,7 +10355,7 @@
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL33" s="26" t="n">
@@ -10363,47 +10363,47 @@
       </c>
       <c r="AM33" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN33" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO33" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP33" s="24" t="inlineStr">
         <is>
-          <t>Sangal ALTERS</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AQ33" s="24" t="inlineStr">
         <is>
-          <t>Sangal ALTERS</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AR33" s="24" t="inlineStr">
         <is>
-          <t>Sangal ALTERS</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AS33" s="24" t="inlineStr">
         <is>
-          <t>Teletubisie</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AT33" s="24" t="inlineStr">
         <is>
-          <t>Teletubisie</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AU33" s="24" t="inlineStr">
         <is>
-          <t>Teletubisie</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AV33" s="24" t="n"/>
@@ -10421,7 +10421,7 @@
       </c>
       <c r="BA33" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB33" s="24" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="BD33" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE33" s="24" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="BH33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:10.390430Z</t>
+          <t>2026-08-02T09:59:46.158629Z</t>
         </is>
       </c>
       <c r="BI33" s="24" t="inlineStr">
@@ -10466,13 +10466,13 @@
       </c>
       <c r="BJ33" s="25" t="n"/>
       <c r="BK33" s="26" t="n">
-        <v>-104</v>
+        <v>-223</v>
       </c>
       <c r="BL33" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.44843</v>
       </c>
       <c r="BM33" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.690402</v>
       </c>
       <c r="BN33" s="28" t="n"/>
       <c r="BO33" s="28" t="n"/>
@@ -10506,22 +10506,22 @@
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>e4924d7adf5e4d7e</t>
+          <t>61b537b0f1324864</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T11:00:00Z</t>
+          <t>2026-08-02T13:00:00Z</t>
         </is>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>69252</t>
+          <t>68257</t>
         </is>
       </c>
       <c r="E34" s="24" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="F34" s="24" t="inlineStr">
         <is>
-          <t>NEW VISION</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="G34" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>DragonClaw</t>
         </is>
       </c>
       <c r="H34" s="24" t="inlineStr">
@@ -10556,26 +10556,26 @@
         </is>
       </c>
       <c r="L34" s="26" t="n">
-        <v>-133</v>
+        <v>-113</v>
       </c>
       <c r="M34" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.884956</v>
       </c>
       <c r="N34" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.530516</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>0.539324</v>
+        <v>0.676069</v>
       </c>
       <c r="P34" s="28" t="n"/>
       <c r="Q34" s="28" t="n">
-        <v>-0.031491</v>
+        <v>0.145553</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="S34" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T34" s="24" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-ica-nve-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-cs2-dc-for-2026-08-02).</t>
         </is>
       </c>
       <c r="AF34" s="31" t="inlineStr">
@@ -10616,7 +10616,7 @@
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL34" s="26" t="n">
@@ -10624,47 +10624,47 @@
       </c>
       <c r="AM34" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN34" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO34" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP34" s="24" t="inlineStr">
         <is>
-          <t>NEW VISION</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AQ34" s="24" t="inlineStr">
         <is>
-          <t>NEW VISION</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AR34" s="24" t="inlineStr">
         <is>
-          <t>NEW VISION</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AS34" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>DragonClaw</t>
         </is>
       </c>
       <c r="AT34" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>DragonClaw</t>
         </is>
       </c>
       <c r="AU34" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>DragonClaw</t>
         </is>
       </c>
       <c r="AV34" s="24" t="n"/>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="BA34" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB34" s="24" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="BD34" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE34" s="24" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="BH34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:10.873207Z</t>
+          <t>2026-08-02T09:59:46.682984Z</t>
         </is>
       </c>
       <c r="BI34" s="24" t="inlineStr">
@@ -10727,13 +10727,13 @@
       </c>
       <c r="BJ34" s="25" t="n"/>
       <c r="BK34" s="26" t="n">
-        <v>-133</v>
+        <v>-113</v>
       </c>
       <c r="BL34" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.884956</v>
       </c>
       <c r="BM34" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.530516</v>
       </c>
       <c r="BN34" s="28" t="n"/>
       <c r="BO34" s="28" t="n"/>
@@ -10767,12 +10767,12 @@
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>c5ae0071bc0c4138</t>
+          <t>b74b5d38bcc34cfc</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>68673</t>
+          <t>68258</t>
         </is>
       </c>
       <c r="E35" s="24" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="F35" s="24" t="inlineStr">
         <is>
-          <t>Sashi Esport</t>
+          <t>ex-MANA eSports</t>
         </is>
       </c>
       <c r="G35" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="I35" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J35" s="25" t="n"/>
@@ -10817,20 +10817,20 @@
         </is>
       </c>
       <c r="L35" s="26" t="n">
-        <v>-213</v>
+        <v>-203</v>
       </c>
       <c r="M35" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.492611</v>
       </c>
       <c r="N35" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.669967</v>
       </c>
       <c r="O35" s="28" t="n">
-        <v>0.593754</v>
+        <v>0.583693</v>
       </c>
       <c r="P35" s="28" t="n"/>
       <c r="Q35" s="28" t="n">
-        <v>-0.086757</v>
+        <v>-0.086274</v>
       </c>
       <c r="R35" s="26" t="n">
         <v>0</v>
@@ -10859,7 +10859,7 @@
       <c r="AD35" s="24" t="n"/>
       <c r="AE35" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-bpl-sashi-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-ica-exmana-2026-08-02).</t>
         </is>
       </c>
       <c r="AF35" s="31" t="inlineStr">
@@ -10900,32 +10900,32 @@
       </c>
       <c r="AP35" s="24" t="inlineStr">
         <is>
-          <t>Sashi Esport</t>
+          <t>ex-MANA eSports</t>
         </is>
       </c>
       <c r="AQ35" s="24" t="inlineStr">
         <is>
-          <t>Sashi Esport</t>
+          <t>ex-MANA eSports</t>
         </is>
       </c>
       <c r="AR35" s="24" t="inlineStr">
         <is>
-          <t>Sashi Esport</t>
+          <t>ex-MANA eSports</t>
         </is>
       </c>
       <c r="AS35" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AT35" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AU35" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AV35" s="24" t="n"/>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="BA35" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB35" s="24" t="inlineStr">
@@ -10958,7 +10958,7 @@
       </c>
       <c r="BD35" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE35" s="24" t="inlineStr">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="BH35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:11.376481Z</t>
+          <t>2026-08-02T09:59:47.204216Z</t>
         </is>
       </c>
       <c r="BI35" s="24" t="inlineStr">
@@ -10988,13 +10988,13 @@
       </c>
       <c r="BJ35" s="25" t="n"/>
       <c r="BK35" s="26" t="n">
-        <v>-213</v>
+        <v>-203</v>
       </c>
       <c r="BL35" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.492611</v>
       </c>
       <c r="BM35" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.669967</v>
       </c>
       <c r="BN35" s="28" t="n"/>
       <c r="BO35" s="28" t="n"/>
@@ -11028,12 +11028,12 @@
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>29031686a1a34516</t>
+          <t>a71808496ac04951</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>68255</t>
+          <t>68259</t>
         </is>
       </c>
       <c r="E36" s="24" t="inlineStr">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="F36" s="24" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>Vexar</t>
         </is>
       </c>
       <c r="G36" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Leo Team</t>
         </is>
       </c>
       <c r="H36" s="24" t="inlineStr">
@@ -11078,23 +11078,23 @@
         </is>
       </c>
       <c r="L36" s="26" t="n">
-        <v>-133</v>
+        <v>138</v>
       </c>
       <c r="M36" s="27" t="n">
-        <v>1.75188</v>
+        <v>2.38</v>
       </c>
       <c r="N36" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.420168</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>0.543392</v>
+        <v>0.563872</v>
       </c>
       <c r="P36" s="28" t="n"/>
       <c r="Q36" s="28" t="n">
-        <v>-0.027423</v>
+        <v>0.143704</v>
       </c>
       <c r="R36" s="26" t="n">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="S36" s="29" t="n">
         <v>1</v>
@@ -11120,7 +11120,7 @@
       <c r="AD36" s="24" t="n"/>
       <c r="AE36" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-mouzn-wba-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-leo-vexar-2026-08-02).</t>
         </is>
       </c>
       <c r="AF36" s="31" t="inlineStr">
@@ -11156,37 +11156,37 @@
       </c>
       <c r="AO36" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP36" s="24" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>Vexar</t>
         </is>
       </c>
       <c r="AQ36" s="24" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>Vexar</t>
         </is>
       </c>
       <c r="AR36" s="24" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>Vexar</t>
         </is>
       </c>
       <c r="AS36" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Leo Team</t>
         </is>
       </c>
       <c r="AT36" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Leo Team</t>
         </is>
       </c>
       <c r="AU36" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>Leo Team</t>
         </is>
       </c>
       <c r="AV36" s="24" t="n"/>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="BA36" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB36" s="24" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="BD36" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE36" s="24" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="BH36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:11.845647Z</t>
+          <t>2026-08-02T09:59:47.738958Z</t>
         </is>
       </c>
       <c r="BI36" s="24" t="inlineStr">
@@ -11249,13 +11249,13 @@
       </c>
       <c r="BJ36" s="25" t="n"/>
       <c r="BK36" s="26" t="n">
-        <v>-133</v>
+        <v>138</v>
       </c>
       <c r="BL36" s="27" t="n">
-        <v>1.75188</v>
+        <v>2.38</v>
       </c>
       <c r="BM36" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.420168</v>
       </c>
       <c r="BN36" s="28" t="n"/>
       <c r="BO36" s="28" t="n"/>
@@ -11289,12 +11289,12 @@
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>8e88fab96b2b4ac8</t>
+          <t>e06a6be4d99e43cd</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>68256</t>
+          <t>68261</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
@@ -11314,12 +11314,12 @@
       </c>
       <c r="F37" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="G37" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="H37" s="24" t="inlineStr">
@@ -11339,26 +11339,26 @@
         </is>
       </c>
       <c r="L37" s="26" t="n">
-        <v>-223</v>
+        <v>-150</v>
       </c>
       <c r="M37" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.666667</v>
       </c>
       <c r="N37" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.6</v>
       </c>
       <c r="O37" s="28" t="n">
-        <v>0.620448</v>
+        <v>0.6541439999999999</v>
       </c>
       <c r="P37" s="28" t="n"/>
       <c r="Q37" s="28" t="n">
-        <v>-0.069954</v>
+        <v>0.054144</v>
       </c>
       <c r="R37" s="26" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="S37" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T37" s="24" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
       <c r="AD37" s="24" t="n"/>
       <c r="AE37" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-lk-nvo-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-bmb-ff-2026-08-02).</t>
         </is>
       </c>
       <c r="AF37" s="31" t="inlineStr">
@@ -11417,37 +11417,37 @@
       </c>
       <c r="AO37" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP37" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="AQ37" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="AR37" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="AS37" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AT37" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AU37" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AV37" s="24" t="n"/>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="BA37" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB37" s="24" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="BD37" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE37" s="24" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="BH37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:12.309327Z</t>
+          <t>2026-08-02T09:59:48.671997Z</t>
         </is>
       </c>
       <c r="BI37" s="24" t="inlineStr">
@@ -11510,13 +11510,13 @@
       </c>
       <c r="BJ37" s="25" t="n"/>
       <c r="BK37" s="26" t="n">
-        <v>-223</v>
+        <v>-150</v>
       </c>
       <c r="BL37" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.666667</v>
       </c>
       <c r="BM37" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.6</v>
       </c>
       <c r="BN37" s="28" t="n"/>
       <c r="BO37" s="28" t="n"/>
@@ -11550,12 +11550,12 @@
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>56ae020f00c84725</t>
+          <t>fc69b57d435f4ed9</t>
         </is>
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="D38" s="24" t="inlineStr">
         <is>
-          <t>68257</t>
+          <t>68277</t>
         </is>
       </c>
       <c r="E38" s="24" t="inlineStr">
@@ -11575,12 +11575,12 @@
       </c>
       <c r="F38" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Misa Esports</t>
         </is>
       </c>
       <c r="G38" s="24" t="inlineStr">
         <is>
-          <t>DragonClaw</t>
+          <t>Favbet</t>
         </is>
       </c>
       <c r="H38" s="24" t="inlineStr">
@@ -11600,26 +11600,26 @@
         </is>
       </c>
       <c r="L38" s="26" t="n">
-        <v>-104</v>
+        <v>-178</v>
       </c>
       <c r="M38" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.561798</v>
       </c>
       <c r="N38" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.640288</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>0.676069</v>
+        <v>0.747081</v>
       </c>
       <c r="P38" s="28" t="n"/>
       <c r="Q38" s="28" t="n">
-        <v>0.166265</v>
+        <v>0.106793</v>
       </c>
       <c r="R38" s="26" t="n">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="S38" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T38" s="24" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
       <c r="AD38" s="24" t="n"/>
       <c r="AE38" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-dc-for-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-fav-misa-2026-08-02).</t>
         </is>
       </c>
       <c r="AF38" s="31" t="inlineStr">
@@ -11660,7 +11660,7 @@
       <c r="AJ38" s="31" t="n"/>
       <c r="AK38" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL38" s="26" t="n">
@@ -11668,47 +11668,47 @@
       </c>
       <c r="AM38" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN38" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO38" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP38" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Misa Esports</t>
         </is>
       </c>
       <c r="AQ38" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Misa Esports</t>
         </is>
       </c>
       <c r="AR38" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Misa Esports</t>
         </is>
       </c>
       <c r="AS38" s="24" t="inlineStr">
         <is>
-          <t>DragonClaw</t>
+          <t>Favbet</t>
         </is>
       </c>
       <c r="AT38" s="24" t="inlineStr">
         <is>
-          <t>DragonClaw</t>
+          <t>Favbet</t>
         </is>
       </c>
       <c r="AU38" s="24" t="inlineStr">
         <is>
-          <t>DragonClaw</t>
+          <t>Favbet</t>
         </is>
       </c>
       <c r="AV38" s="24" t="n"/>
@@ -11726,7 +11726,7 @@
       </c>
       <c r="BA38" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB38" s="24" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="BD38" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE38" s="24" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="BH38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:12.784904Z</t>
+          <t>2026-08-02T09:59:49.257041Z</t>
         </is>
       </c>
       <c r="BI38" s="24" t="inlineStr">
@@ -11771,13 +11771,13 @@
       </c>
       <c r="BJ38" s="25" t="n"/>
       <c r="BK38" s="26" t="n">
-        <v>-104</v>
+        <v>-178</v>
       </c>
       <c r="BL38" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.561798</v>
       </c>
       <c r="BM38" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.640288</v>
       </c>
       <c r="BN38" s="28" t="n"/>
       <c r="BO38" s="28" t="n"/>
@@ -11811,22 +11811,22 @@
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>8b14dcae8bc9432a</t>
+          <t>0618b43e418b498a</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:00:00Z</t>
+          <t>2026-08-02T14:00:00Z</t>
         </is>
       </c>
       <c r="D39" s="24" t="inlineStr">
         <is>
-          <t>68258</t>
+          <t>69254</t>
         </is>
       </c>
       <c r="E39" s="24" t="inlineStr">
@@ -11836,12 +11836,12 @@
       </c>
       <c r="F39" s="24" t="inlineStr">
         <is>
-          <t>ex-MANA eSports</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G39" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="H39" s="24" t="inlineStr">
@@ -11861,26 +11861,26 @@
         </is>
       </c>
       <c r="L39" s="26" t="n">
-        <v>-186</v>
+        <v>-203</v>
       </c>
       <c r="M39" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.492611</v>
       </c>
       <c r="N39" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.669967</v>
       </c>
       <c r="O39" s="28" t="n">
-        <v>0.583693</v>
+        <v>0.662043</v>
       </c>
       <c r="P39" s="28" t="n"/>
       <c r="Q39" s="28" t="n">
-        <v>-0.06665699999999999</v>
+        <v>-0.007924</v>
       </c>
       <c r="R39" s="26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S39" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T39" s="24" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
       <c r="AD39" s="24" t="n"/>
       <c r="AE39" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-cs2-ica-exmana-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-erx-hon-2026-08-02).</t>
         </is>
       </c>
       <c r="AF39" s="31" t="inlineStr">
@@ -11944,32 +11944,32 @@
       </c>
       <c r="AP39" s="24" t="inlineStr">
         <is>
-          <t>ex-MANA eSports</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="AQ39" s="24" t="inlineStr">
         <is>
-          <t>ex-MANA eSports</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="AR39" s="24" t="inlineStr">
         <is>
-          <t>ex-MANA eSports</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="AS39" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AT39" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AU39" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>ex-RUSTEC</t>
         </is>
       </c>
       <c r="AV39" s="24" t="n"/>
@@ -11987,7 +11987,7 @@
       </c>
       <c r="BA39" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB39" s="24" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="BD39" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE39" s="24" t="inlineStr">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="BH39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:13.318644Z</t>
+          <t>2026-08-02T09:59:49.723521Z</t>
         </is>
       </c>
       <c r="BI39" s="24" t="inlineStr">
@@ -12032,13 +12032,13 @@
       </c>
       <c r="BJ39" s="25" t="n"/>
       <c r="BK39" s="26" t="n">
-        <v>-186</v>
+        <v>-203</v>
       </c>
       <c r="BL39" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.492611</v>
       </c>
       <c r="BM39" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.669967</v>
       </c>
       <c r="BN39" s="28" t="n"/>
       <c r="BO39" s="28" t="n"/>
@@ -12072,22 +12072,22 @@
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>c88045061170496c</t>
+          <t>105c3a3a07cd451c</t>
         </is>
       </c>
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:00:00Z</t>
+          <t>2026-08-02T17:00:00Z</t>
         </is>
       </c>
       <c r="D40" s="24" t="inlineStr">
         <is>
-          <t>68259</t>
+          <t>69263</t>
         </is>
       </c>
       <c r="E40" s="24" t="inlineStr">
@@ -12097,12 +12097,12 @@
       </c>
       <c r="F40" s="24" t="inlineStr">
         <is>
-          <t>Vexar</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="G40" s="24" t="inlineStr">
         <is>
-          <t>Leo Team</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="H40" s="24" t="inlineStr">
@@ -12122,26 +12122,26 @@
         </is>
       </c>
       <c r="L40" s="26" t="n">
-        <v>138</v>
+        <v>-156</v>
       </c>
       <c r="M40" s="27" t="n">
-        <v>2.38</v>
+        <v>1.641026</v>
       </c>
       <c r="N40" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.609375</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>0.563872</v>
+        <v>0.66636</v>
       </c>
       <c r="P40" s="28" t="n"/>
       <c r="Q40" s="28" t="n">
-        <v>0.143704</v>
+        <v>0.056985</v>
       </c>
       <c r="R40" s="26" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="S40" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T40" s="24" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
       <c r="AD40" s="24" t="n"/>
       <c r="AE40" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-leo-vexar-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
         </is>
       </c>
       <c r="AF40" s="31" t="inlineStr">
@@ -12182,7 +12182,7 @@
       <c r="AJ40" s="31" t="n"/>
       <c r="AK40" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL40" s="26" t="n">
@@ -12190,47 +12190,47 @@
       </c>
       <c r="AM40" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN40" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO40" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP40" s="24" t="inlineStr">
         <is>
-          <t>Vexar</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AQ40" s="24" t="inlineStr">
         <is>
-          <t>Vexar</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AR40" s="24" t="inlineStr">
         <is>
-          <t>Vexar</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AS40" s="24" t="inlineStr">
         <is>
-          <t>Leo Team</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AT40" s="24" t="inlineStr">
         <is>
-          <t>Leo Team</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AU40" s="24" t="inlineStr">
         <is>
-          <t>Leo Team</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AV40" s="24" t="n"/>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="BA40" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB40" s="24" t="inlineStr">
@@ -12263,7 +12263,7 @@
       </c>
       <c r="BD40" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE40" s="24" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="BH40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:13.866447Z</t>
+          <t>2026-08-02T09:59:51.297257Z</t>
         </is>
       </c>
       <c r="BI40" s="24" t="inlineStr">
@@ -12293,13 +12293,13 @@
       </c>
       <c r="BJ40" s="25" t="n"/>
       <c r="BK40" s="26" t="n">
-        <v>138</v>
+        <v>-156</v>
       </c>
       <c r="BL40" s="27" t="n">
-        <v>2.38</v>
+        <v>1.641026</v>
       </c>
       <c r="BM40" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.609375</v>
       </c>
       <c r="BN40" s="28" t="n"/>
       <c r="BO40" s="28" t="n"/>
@@ -12333,22 +12333,22 @@
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>ca4f76153b4b49b9</t>
+          <t>a6760f9308b440ac</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:00:00Z</t>
+          <t>2026-08-02T18:00:00Z</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>68261</t>
+          <t>69289</t>
         </is>
       </c>
       <c r="E41" s="24" t="inlineStr">
@@ -12358,12 +12358,12 @@
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="G41" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="H41" s="24" t="inlineStr">
@@ -12383,26 +12383,26 @@
         </is>
       </c>
       <c r="L41" s="26" t="n">
-        <v>-150</v>
+        <v>138</v>
       </c>
       <c r="M41" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.38</v>
       </c>
       <c r="N41" s="28" t="n">
-        <v>0.6</v>
+        <v>0.420168</v>
       </c>
       <c r="O41" s="28" t="n">
-        <v>0.6541439999999999</v>
+        <v>0.510543</v>
       </c>
       <c r="P41" s="28" t="n"/>
       <c r="Q41" s="28" t="n">
-        <v>0.054144</v>
+        <v>0.090375</v>
       </c>
       <c r="R41" s="26" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="S41" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T41" s="24" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
       <c r="AD41" s="24" t="n"/>
       <c r="AE41" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-bmb-ff-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-shin-bst-2026-08-02).</t>
         </is>
       </c>
       <c r="AF41" s="31" t="inlineStr">
@@ -12461,37 +12461,37 @@
       </c>
       <c r="AO41" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP41" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AQ41" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AR41" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AS41" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="AT41" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="AU41" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="AV41" s="24" t="n"/>
@@ -12509,7 +12509,7 @@
       </c>
       <c r="BA41" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB41" s="24" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="BD41" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE41" s="24" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="BH41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:15.050508Z</t>
+          <t>2026-08-02T09:59:51.837185Z</t>
         </is>
       </c>
       <c r="BI41" s="24" t="inlineStr">
@@ -12554,13 +12554,13 @@
       </c>
       <c r="BJ41" s="25" t="n"/>
       <c r="BK41" s="26" t="n">
-        <v>-150</v>
+        <v>138</v>
       </c>
       <c r="BL41" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.38</v>
       </c>
       <c r="BM41" s="28" t="n">
-        <v>0.6</v>
+        <v>0.420168</v>
       </c>
       <c r="BN41" s="28" t="n"/>
       <c r="BO41" s="28" t="n"/>
@@ -12594,22 +12594,22 @@
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>1ec8b20859c94f21</t>
+          <t>3460f0ab2ea84c55</t>
         </is>
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:00:00Z</t>
+          <t>2026-08-02T19:15:00Z</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>68277</t>
+          <t>67577</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="F42" s="24" t="inlineStr">
         <is>
-          <t>Misa Esports</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="G42" s="24" t="inlineStr">
         <is>
-          <t>Favbet</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="H42" s="24" t="inlineStr">
@@ -12644,26 +12644,26 @@
         </is>
       </c>
       <c r="L42" s="26" t="n">
-        <v>-186</v>
+        <v>-150</v>
       </c>
       <c r="M42" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.666667</v>
       </c>
       <c r="N42" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.6</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>0.747081</v>
+        <v>0.526743</v>
       </c>
       <c r="P42" s="28" t="n"/>
       <c r="Q42" s="28" t="n">
-        <v>0.096731</v>
+        <v>-0.073257</v>
       </c>
       <c r="R42" s="26" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="S42" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T42" s="24" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
       <c r="AD42" s="24" t="n"/>
       <c r="AE42" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-cs2-fav-misa-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
         </is>
       </c>
       <c r="AF42" s="31" t="inlineStr">
@@ -12727,32 +12727,32 @@
       </c>
       <c r="AP42" s="24" t="inlineStr">
         <is>
-          <t>Misa Esports</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AQ42" s="24" t="inlineStr">
         <is>
-          <t>Misa Esports</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AR42" s="24" t="inlineStr">
         <is>
-          <t>Misa Esports</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AS42" s="24" t="inlineStr">
         <is>
-          <t>Favbet</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AT42" s="24" t="inlineStr">
         <is>
-          <t>Favbet</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AU42" s="24" t="inlineStr">
         <is>
-          <t>Favbet</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AV42" s="24" t="n"/>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="BA42" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB42" s="24" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="BD42" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE42" s="24" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="BH42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:15.582287Z</t>
+          <t>2026-08-02T09:59:52.331890Z</t>
         </is>
       </c>
       <c r="BI42" s="24" t="inlineStr">
@@ -12815,13 +12815,13 @@
       </c>
       <c r="BJ42" s="25" t="n"/>
       <c r="BK42" s="26" t="n">
-        <v>-186</v>
+        <v>-150</v>
       </c>
       <c r="BL42" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.666667</v>
       </c>
       <c r="BM42" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.6</v>
       </c>
       <c r="BN42" s="28" t="n"/>
       <c r="BO42" s="28" t="n"/>
@@ -12855,22 +12855,22 @@
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>decb9ca4ca3d4bae</t>
+          <t>d34bac6e45ff4a97</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T14:00:00Z</t>
+          <t>2026-08-02T19:15:00Z</t>
         </is>
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>69254</t>
+          <t>67576</t>
         </is>
       </c>
       <c r="E43" s="24" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="G43" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="H43" s="24" t="inlineStr">
@@ -12905,26 +12905,26 @@
         </is>
       </c>
       <c r="L43" s="26" t="n">
-        <v>-163</v>
+        <v>156</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.56</v>
       </c>
       <c r="N43" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.390625</v>
       </c>
       <c r="O43" s="28" t="n">
-        <v>0.662043</v>
+        <v>0.579539</v>
       </c>
       <c r="P43" s="28" t="n"/>
       <c r="Q43" s="28" t="n">
-        <v>0.042271</v>
+        <v>0.188914</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="S43" s="29" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="T43" s="24" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
       <c r="AD43" s="24" t="n"/>
       <c r="AE43" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-erx-hon-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
         </is>
       </c>
       <c r="AF43" s="31" t="inlineStr">
@@ -12965,7 +12965,7 @@
       <c r="AJ43" s="31" t="n"/>
       <c r="AK43" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL43" s="26" t="n">
@@ -12973,47 +12973,47 @@
       </c>
       <c r="AM43" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN43" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO43" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP43" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AQ43" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AR43" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AS43" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AT43" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AU43" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AV43" s="24" t="n"/>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="BA43" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB43" s="24" t="inlineStr">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="BD43" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE43" s="24" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="BH43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:16.117377Z</t>
+          <t>2026-08-02T09:59:52.846665Z</t>
         </is>
       </c>
       <c r="BI43" s="24" t="inlineStr">
@@ -13076,13 +13076,13 @@
       </c>
       <c r="BJ43" s="25" t="n"/>
       <c r="BK43" s="26" t="n">
-        <v>-163</v>
+        <v>156</v>
       </c>
       <c r="BL43" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.56</v>
       </c>
       <c r="BM43" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.390625</v>
       </c>
       <c r="BN43" s="28" t="n"/>
       <c r="BO43" s="28" t="n"/>
@@ -13116,22 +13116,22 @@
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>4f82f9ad0e214efb</t>
+          <t>deca0c777f084a7c</t>
         </is>
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:00:00Z</t>
+          <t>2026-08-03T08:00:00Z</t>
         </is>
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>69263</t>
+          <t>67490</t>
         </is>
       </c>
       <c r="E44" s="24" t="inlineStr">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="F44" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>VP.Prodigy</t>
         </is>
       </c>
       <c r="G44" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Eternal Fire Academy</t>
         </is>
       </c>
       <c r="H44" s="24" t="inlineStr">
@@ -13166,23 +13166,23 @@
         </is>
       </c>
       <c r="L44" s="26" t="n">
-        <v>-156</v>
+        <v>-223</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.44843</v>
       </c>
       <c r="N44" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.690402</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>0.66636</v>
+        <v>0.646647</v>
       </c>
       <c r="P44" s="28" t="n"/>
       <c r="Q44" s="28" t="n">
-        <v>0.056985</v>
+        <v>-0.043755</v>
       </c>
       <c r="R44" s="26" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="S44" s="29" t="n">
         <v>1.75</v>
@@ -13208,7 +13208,7 @@
       <c r="AD44" s="24" t="n"/>
       <c r="AE44" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-efa-vpp-2026-08-03).</t>
         </is>
       </c>
       <c r="AF44" s="31" t="inlineStr">
@@ -13226,7 +13226,7 @@
       <c r="AJ44" s="31" t="n"/>
       <c r="AK44" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL44" s="26" t="n">
@@ -13234,47 +13234,47 @@
       </c>
       <c r="AM44" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN44" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO44" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP44" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>VP.Prodigy</t>
         </is>
       </c>
       <c r="AQ44" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>VP.Prodigy</t>
         </is>
       </c>
       <c r="AR44" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>VP.Prodigy</t>
         </is>
       </c>
       <c r="AS44" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Eternal Fire Academy</t>
         </is>
       </c>
       <c r="AT44" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Eternal Fire Academy</t>
         </is>
       </c>
       <c r="AU44" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Eternal Fire Academy</t>
         </is>
       </c>
       <c r="AV44" s="24" t="n"/>
@@ -13292,7 +13292,7 @@
       </c>
       <c r="BA44" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB44" s="24" t="inlineStr">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="BD44" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE44" s="24" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="BH44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:17.713467Z</t>
+          <t>2026-08-02T09:59:53.863040Z</t>
         </is>
       </c>
       <c r="BI44" s="24" t="inlineStr">
@@ -13337,13 +13337,13 @@
       </c>
       <c r="BJ44" s="25" t="n"/>
       <c r="BK44" s="26" t="n">
-        <v>-156</v>
+        <v>-223</v>
       </c>
       <c r="BL44" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.44843</v>
       </c>
       <c r="BM44" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.690402</v>
       </c>
       <c r="BN44" s="28" t="n"/>
       <c r="BO44" s="28" t="n"/>
@@ -13377,22 +13377,22 @@
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>87d265955cc34abf</t>
+          <t>9bba252f704c4c22</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:00:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>69289</t>
+          <t>67510</t>
         </is>
       </c>
       <c r="E45" s="24" t="inlineStr">
@@ -13402,12 +13402,12 @@
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="G45" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="H45" s="24" t="inlineStr">
@@ -13427,23 +13427,23 @@
         </is>
       </c>
       <c r="L45" s="26" t="n">
-        <v>150</v>
+        <v>-223</v>
       </c>
       <c r="M45" s="27" t="n">
-        <v>2.5</v>
+        <v>1.44843</v>
       </c>
       <c r="N45" s="28" t="n">
-        <v>0.4</v>
+        <v>0.690402</v>
       </c>
       <c r="O45" s="28" t="n">
-        <v>0.510543</v>
+        <v>0.563104</v>
       </c>
       <c r="P45" s="28" t="n"/>
       <c r="Q45" s="28" t="n">
-        <v>0.110543</v>
+        <v>-0.127298</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="S45" s="29" t="n">
         <v>1</v>
@@ -13469,7 +13469,7 @@
       <c r="AD45" s="24" t="n"/>
       <c r="AE45" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-shin-bst-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
         </is>
       </c>
       <c r="AF45" s="31" t="inlineStr">
@@ -13510,32 +13510,32 @@
       </c>
       <c r="AP45" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AQ45" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AR45" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AS45" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AT45" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AU45" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AV45" s="24" t="n"/>
@@ -13553,7 +13553,7 @@
       </c>
       <c r="BA45" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB45" s="24" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="BD45" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE45" s="24" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="BH45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:18.366310Z</t>
+          <t>2026-08-02T09:59:55.692466Z</t>
         </is>
       </c>
       <c r="BI45" s="24" t="inlineStr">
@@ -13598,13 +13598,13 @@
       </c>
       <c r="BJ45" s="25" t="n"/>
       <c r="BK45" s="26" t="n">
-        <v>150</v>
+        <v>-223</v>
       </c>
       <c r="BL45" s="27" t="n">
-        <v>2.5</v>
+        <v>1.44843</v>
       </c>
       <c r="BM45" s="28" t="n">
-        <v>0.4</v>
+        <v>0.690402</v>
       </c>
       <c r="BN45" s="28" t="n"/>
       <c r="BO45" s="28" t="n"/>
@@ -13638,22 +13638,22 @@
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>09df7b524a97466a</t>
+          <t>50cdc781309648ec</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:15:00Z</t>
+          <t>2026-08-03T10:30:00Z</t>
         </is>
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>67577</t>
+          <t>67514</t>
         </is>
       </c>
       <c r="E46" s="24" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="G46" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="H46" s="24" t="inlineStr">
@@ -13688,26 +13688,26 @@
         </is>
       </c>
       <c r="L46" s="26" t="n">
-        <v>-178</v>
+        <v>-122</v>
       </c>
       <c r="M46" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.819672</v>
       </c>
       <c r="N46" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.54955</v>
       </c>
       <c r="O46" s="28" t="n">
-        <v>0.526743</v>
+        <v>0.640228</v>
       </c>
       <c r="P46" s="28" t="n"/>
       <c r="Q46" s="28" t="n">
-        <v>-0.113545</v>
+        <v>0.09067799999999999</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="S46" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T46" s="24" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
       <c r="AD46" s="24" t="n"/>
       <c r="AE46" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
         </is>
       </c>
       <c r="AF46" s="31" t="inlineStr">
@@ -13748,7 +13748,7 @@
       <c r="AJ46" s="31" t="n"/>
       <c r="AK46" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL46" s="26" t="n">
@@ -13756,47 +13756,47 @@
       </c>
       <c r="AM46" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN46" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO46" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP46" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AQ46" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AR46" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AS46" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AT46" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AU46" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AV46" s="24" t="n"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="BA46" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB46" s="24" t="inlineStr">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="BD46" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE46" s="24" t="inlineStr">
@@ -13849,7 +13849,7 @@
       </c>
       <c r="BH46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:18.951273Z</t>
+          <t>2026-08-02T09:59:57.251438Z</t>
         </is>
       </c>
       <c r="BI46" s="24" t="inlineStr">
@@ -13859,13 +13859,13 @@
       </c>
       <c r="BJ46" s="25" t="n"/>
       <c r="BK46" s="26" t="n">
-        <v>-178</v>
+        <v>-122</v>
       </c>
       <c r="BL46" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.819672</v>
       </c>
       <c r="BM46" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.54955</v>
       </c>
       <c r="BN46" s="28" t="n"/>
       <c r="BO46" s="28" t="n"/>
@@ -13899,22 +13899,22 @@
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>b50cdfc659ba4798</t>
+          <t>d5bc9a8496d6494a</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:15:00Z</t>
+          <t>2026-08-03T11:00:00Z</t>
         </is>
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>67576</t>
+          <t>67578</t>
         </is>
       </c>
       <c r="E47" s="24" t="inlineStr">
@@ -13924,12 +13924,12 @@
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr">
@@ -13949,26 +13949,26 @@
         </is>
       </c>
       <c r="L47" s="26" t="n">
-        <v>156</v>
+        <v>-122</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>2.56</v>
+        <v>1.819672</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.54955</v>
       </c>
       <c r="O47" s="28" t="n">
-        <v>0.579539</v>
+        <v>0.526743</v>
       </c>
       <c r="P47" s="28" t="n"/>
       <c r="Q47" s="28" t="n">
-        <v>0.188914</v>
+        <v>-0.022807</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="S47" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T47" s="24" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
       <c r="AD47" s="24" t="n"/>
       <c r="AE47" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
         </is>
       </c>
       <c r="AF47" s="31" t="inlineStr">
@@ -14032,32 +14032,32 @@
       </c>
       <c r="AP47" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AQ47" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AR47" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AS47" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AT47" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AU47" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AV47" s="24" t="n"/>
@@ -14075,7 +14075,7 @@
       </c>
       <c r="BA47" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB47" s="24" t="inlineStr">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="BD47" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE47" s="24" t="inlineStr">
@@ -14110,7 +14110,7 @@
       </c>
       <c r="BH47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:19.608833Z</t>
+          <t>2026-08-02T09:59:57.770498Z</t>
         </is>
       </c>
       <c r="BI47" s="24" t="inlineStr">
@@ -14120,13 +14120,13 @@
       </c>
       <c r="BJ47" s="25" t="n"/>
       <c r="BK47" s="26" t="n">
-        <v>156</v>
+        <v>-122</v>
       </c>
       <c r="BL47" s="27" t="n">
-        <v>2.56</v>
+        <v>1.819672</v>
       </c>
       <c r="BM47" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.54955</v>
       </c>
       <c r="BN47" s="28" t="n"/>
       <c r="BO47" s="28" t="n"/>
@@ -14160,22 +14160,22 @@
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>e41a38b5a7264af3</t>
+          <t>0f4a18b629c841c0</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T08:00:00Z</t>
+          <t>2026-08-03T13:45:00Z</t>
         </is>
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>67490</t>
+          <t>67579</t>
         </is>
       </c>
       <c r="E48" s="24" t="inlineStr">
@@ -14185,12 +14185,12 @@
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>VP.Prodigy</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire Academy</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="H48" s="24" t="inlineStr">
@@ -14210,26 +14210,26 @@
         </is>
       </c>
       <c r="L48" s="26" t="n">
-        <v>-223</v>
+        <v>203</v>
       </c>
       <c r="M48" s="27" t="n">
-        <v>1.44843</v>
+        <v>3.03</v>
       </c>
       <c r="N48" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.330033</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>0.646647</v>
+        <v>0.526658</v>
       </c>
       <c r="P48" s="28" t="n"/>
       <c r="Q48" s="28" t="n">
-        <v>-0.043755</v>
+        <v>0.196625</v>
       </c>
       <c r="R48" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S48" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T48" s="24" t="inlineStr">
         <is>
@@ -14252,7 +14252,7 @@
       <c r="AD48" s="24" t="n"/>
       <c r="AE48" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-efa-vpp-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
         </is>
       </c>
       <c r="AF48" s="31" t="inlineStr">
@@ -14288,37 +14288,37 @@
       </c>
       <c r="AO48" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP48" s="24" t="inlineStr">
         <is>
-          <t>VP.Prodigy</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AQ48" s="24" t="inlineStr">
         <is>
-          <t>VP.Prodigy</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AR48" s="24" t="inlineStr">
         <is>
-          <t>VP.Prodigy</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AS48" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire Academy</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AT48" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire Academy</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AU48" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire Academy</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AV48" s="24" t="n"/>
@@ -14336,7 +14336,7 @@
       </c>
       <c r="BA48" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB48" s="24" t="inlineStr">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="BD48" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE48" s="24" t="inlineStr">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="BH48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:20.659011Z</t>
+          <t>2026-08-02T09:59:59.263922Z</t>
         </is>
       </c>
       <c r="BI48" s="24" t="inlineStr">
@@ -14381,13 +14381,13 @@
       </c>
       <c r="BJ48" s="25" t="n"/>
       <c r="BK48" s="26" t="n">
-        <v>-223</v>
+        <v>203</v>
       </c>
       <c r="BL48" s="27" t="n">
-        <v>1.44843</v>
+        <v>3.03</v>
       </c>
       <c r="BM48" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.330033</v>
       </c>
       <c r="BN48" s="28" t="n"/>
       <c r="BO48" s="28" t="n"/>
@@ -14421,22 +14421,22 @@
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>cb9b1b93c1334fe0</t>
+          <t>c821c1721eda4a68</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
+          <t>2026-08-02T10:00:04.561525Z</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-03T23:00:00Z</t>
         </is>
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>67510</t>
+          <t>68043</t>
         </is>
       </c>
       <c r="E49" s="24" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr">
@@ -14471,26 +14471,26 @@
         </is>
       </c>
       <c r="L49" s="26" t="n">
-        <v>-223</v>
+        <v>113</v>
       </c>
       <c r="M49" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.13</v>
       </c>
       <c r="N49" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.469484</v>
       </c>
       <c r="O49" s="28" t="n">
-        <v>0.563104</v>
+        <v>0.569576</v>
       </c>
       <c r="P49" s="28" t="n"/>
       <c r="Q49" s="28" t="n">
-        <v>-0.127298</v>
+        <v>0.100092</v>
       </c>
       <c r="R49" s="26" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="S49" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T49" s="24" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
       <c r="AD49" s="24" t="n"/>
       <c r="AE49" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
         </is>
       </c>
       <c r="AF49" s="31" t="inlineStr">
@@ -14549,37 +14549,37 @@
       </c>
       <c r="AO49" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP49" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="AQ49" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="AR49" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="AS49" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="AT49" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="AU49" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="AV49" s="24" t="n"/>
@@ -14597,7 +14597,7 @@
       </c>
       <c r="BA49" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BB49" s="24" t="inlineStr">
@@ -14612,7 +14612,7 @@
       </c>
       <c r="BD49" s="24" t="inlineStr">
         <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
+          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
         </is>
       </c>
       <c r="BE49" s="24" t="inlineStr">
@@ -14632,7 +14632,7 @@
       </c>
       <c r="BH49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T08:19:22.224868Z</t>
+          <t>2026-08-02T10:00:04.559918Z</t>
         </is>
       </c>
       <c r="BI49" s="24" t="inlineStr">
@@ -14642,13 +14642,13 @@
       </c>
       <c r="BJ49" s="25" t="n"/>
       <c r="BK49" s="26" t="n">
-        <v>-223</v>
+        <v>113</v>
       </c>
       <c r="BL49" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.13</v>
       </c>
       <c r="BM49" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.469484</v>
       </c>
       <c r="BN49" s="28" t="n"/>
       <c r="BO49" s="28" t="n"/>
@@ -14679,1050 +14679,6 @@
       <c r="CN49" s="24" t="n"/>
       <c r="CO49" s="24" t="n"/>
     </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="A50" s="24" t="inlineStr">
-        <is>
-          <t>b4249330287542e3</t>
-        </is>
-      </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:30:00Z</t>
-        </is>
-      </c>
-      <c r="D50" s="24" t="inlineStr">
-        <is>
-          <t>67514</t>
-        </is>
-      </c>
-      <c r="E50" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F50" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="G50" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="H50" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I50" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J50" s="25" t="n"/>
-      <c r="K50" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L50" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="M50" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="N50" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="O50" s="28" t="n">
-        <v>0.640228</v>
-      </c>
-      <c r="P50" s="28" t="n"/>
-      <c r="Q50" s="28" t="n">
-        <v>0.09067799999999999</v>
-      </c>
-      <c r="R50" s="26" t="n">
-        <v>65</v>
-      </c>
-      <c r="S50" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T50" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U50" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V50" s="24" t="n"/>
-      <c r="W50" s="26" t="n"/>
-      <c r="X50" s="26" t="n"/>
-      <c r="Y50" s="25" t="n"/>
-      <c r="Z50" s="26" t="n"/>
-      <c r="AA50" s="28" t="n"/>
-      <c r="AB50" s="28" t="n"/>
-      <c r="AC50" s="30" t="n"/>
-      <c r="AD50" s="24" t="n"/>
-      <c r="AE50" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF50" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG50" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH50" s="24" t="n"/>
-      <c r="AI50" s="31" t="n"/>
-      <c r="AJ50" s="31" t="n"/>
-      <c r="AK50" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL50" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM50" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN50" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO50" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP50" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AQ50" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AR50" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AS50" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="AT50" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="AU50" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="AV50" s="24" t="n"/>
-      <c r="AW50" s="24" t="n"/>
-      <c r="AX50" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY50" s="24" t="n"/>
-      <c r="AZ50" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA50" s="24" t="inlineStr">
-        <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
-        </is>
-      </c>
-      <c r="BB50" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC50" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD50" s="24" t="inlineStr">
-        <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
-        </is>
-      </c>
-      <c r="BE50" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF50" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG50" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH50" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T08:19:23.793481Z</t>
-        </is>
-      </c>
-      <c r="BI50" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ50" s="25" t="n"/>
-      <c r="BK50" s="26" t="n">
-        <v>-122</v>
-      </c>
-      <c r="BL50" s="27" t="n">
-        <v>1.819672</v>
-      </c>
-      <c r="BM50" s="28" t="n">
-        <v>0.54955</v>
-      </c>
-      <c r="BN50" s="28" t="n"/>
-      <c r="BO50" s="28" t="n"/>
-      <c r="BP50" s="25" t="n"/>
-      <c r="BQ50" s="27" t="n"/>
-      <c r="BR50" s="28" t="n"/>
-      <c r="BS50" s="28" t="n"/>
-      <c r="BT50" s="28" t="n"/>
-      <c r="BU50" s="25" t="n"/>
-      <c r="BV50" s="29" t="n"/>
-      <c r="BW50" s="24" t="n"/>
-      <c r="BX50" s="30" t="n"/>
-      <c r="BY50" s="27" t="n"/>
-      <c r="BZ50" s="24" t="n"/>
-      <c r="CA50" s="31" t="n"/>
-      <c r="CB50" s="24" t="n"/>
-      <c r="CC50" s="24" t="n"/>
-      <c r="CD50" s="24" t="n"/>
-      <c r="CE50" s="24" t="n"/>
-      <c r="CF50" s="24" t="n"/>
-      <c r="CG50" s="24" t="n"/>
-      <c r="CH50" s="24" t="n"/>
-      <c r="CI50" s="24" t="n"/>
-      <c r="CJ50" s="24" t="n"/>
-      <c r="CK50" s="24" t="n"/>
-      <c r="CL50" s="24" t="n"/>
-      <c r="CM50" s="24" t="n"/>
-      <c r="CN50" s="24" t="n"/>
-      <c r="CO50" s="24" t="n"/>
-    </row>
-    <row r="51" ht="36" customHeight="1">
-      <c r="A51" s="24" t="inlineStr">
-        <is>
-          <t>6127dbef3f574b64</t>
-        </is>
-      </c>
-      <c r="B51" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
-        </is>
-      </c>
-      <c r="C51" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="inlineStr">
-        <is>
-          <t>67578</t>
-        </is>
-      </c>
-      <c r="E51" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F51" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="G51" s="24" t="inlineStr">
-        <is>
-          <t>Recrent Club</t>
-        </is>
-      </c>
-      <c r="H51" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I51" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J51" s="25" t="n"/>
-      <c r="K51" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L51" s="26" t="n">
-        <v>-170</v>
-      </c>
-      <c r="M51" s="27" t="n">
-        <v>1.588235</v>
-      </c>
-      <c r="N51" s="28" t="n">
-        <v>0.62963</v>
-      </c>
-      <c r="O51" s="28" t="n">
-        <v>0.526743</v>
-      </c>
-      <c r="P51" s="28" t="n"/>
-      <c r="Q51" s="28" t="n">
-        <v>-0.102887</v>
-      </c>
-      <c r="R51" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T51" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U51" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V51" s="24" t="n"/>
-      <c r="W51" s="26" t="n"/>
-      <c r="X51" s="26" t="n"/>
-      <c r="Y51" s="25" t="n"/>
-      <c r="Z51" s="26" t="n"/>
-      <c r="AA51" s="28" t="n"/>
-      <c r="AB51" s="28" t="n"/>
-      <c r="AC51" s="30" t="n"/>
-      <c r="AD51" s="24" t="n"/>
-      <c r="AE51" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF51" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG51" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH51" s="24" t="n"/>
-      <c r="AI51" s="31" t="n"/>
-      <c r="AJ51" s="31" t="n"/>
-      <c r="AK51" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL51" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM51" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN51" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO51" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP51" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AQ51" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AR51" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AS51" s="24" t="inlineStr">
-        <is>
-          <t>Recrent Club</t>
-        </is>
-      </c>
-      <c r="AT51" s="24" t="inlineStr">
-        <is>
-          <t>Recrent Club</t>
-        </is>
-      </c>
-      <c r="AU51" s="24" t="inlineStr">
-        <is>
-          <t>Recrent Club</t>
-        </is>
-      </c>
-      <c r="AV51" s="24" t="n"/>
-      <c r="AW51" s="24" t="n"/>
-      <c r="AX51" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY51" s="24" t="n"/>
-      <c r="AZ51" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA51" s="24" t="inlineStr">
-        <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
-        </is>
-      </c>
-      <c r="BB51" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC51" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD51" s="24" t="inlineStr">
-        <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
-        </is>
-      </c>
-      <c r="BE51" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF51" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG51" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH51" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T08:19:24.359608Z</t>
-        </is>
-      </c>
-      <c r="BI51" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ51" s="25" t="n"/>
-      <c r="BK51" s="26" t="n">
-        <v>-170</v>
-      </c>
-      <c r="BL51" s="27" t="n">
-        <v>1.588235</v>
-      </c>
-      <c r="BM51" s="28" t="n">
-        <v>0.62963</v>
-      </c>
-      <c r="BN51" s="28" t="n"/>
-      <c r="BO51" s="28" t="n"/>
-      <c r="BP51" s="25" t="n"/>
-      <c r="BQ51" s="27" t="n"/>
-      <c r="BR51" s="28" t="n"/>
-      <c r="BS51" s="28" t="n"/>
-      <c r="BT51" s="28" t="n"/>
-      <c r="BU51" s="25" t="n"/>
-      <c r="BV51" s="29" t="n"/>
-      <c r="BW51" s="24" t="n"/>
-      <c r="BX51" s="30" t="n"/>
-      <c r="BY51" s="27" t="n"/>
-      <c r="BZ51" s="24" t="n"/>
-      <c r="CA51" s="31" t="n"/>
-      <c r="CB51" s="24" t="n"/>
-      <c r="CC51" s="24" t="n"/>
-      <c r="CD51" s="24" t="n"/>
-      <c r="CE51" s="24" t="n"/>
-      <c r="CF51" s="24" t="n"/>
-      <c r="CG51" s="24" t="n"/>
-      <c r="CH51" s="24" t="n"/>
-      <c r="CI51" s="24" t="n"/>
-      <c r="CJ51" s="24" t="n"/>
-      <c r="CK51" s="24" t="n"/>
-      <c r="CL51" s="24" t="n"/>
-      <c r="CM51" s="24" t="n"/>
-      <c r="CN51" s="24" t="n"/>
-      <c r="CO51" s="24" t="n"/>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="24" t="inlineStr">
-        <is>
-          <t>0d54aead8b234deb</t>
-        </is>
-      </c>
-      <c r="B52" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
-        </is>
-      </c>
-      <c r="C52" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T13:45:00Z</t>
-        </is>
-      </c>
-      <c r="D52" s="24" t="inlineStr">
-        <is>
-          <t>67579</t>
-        </is>
-      </c>
-      <c r="E52" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F52" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="G52" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="H52" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I52" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J52" s="25" t="n"/>
-      <c r="K52" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L52" s="26" t="n">
-        <v>223</v>
-      </c>
-      <c r="M52" s="27" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N52" s="28" t="n">
-        <v>0.309598</v>
-      </c>
-      <c r="O52" s="28" t="n">
-        <v>0.526658</v>
-      </c>
-      <c r="P52" s="28" t="n"/>
-      <c r="Q52" s="28" t="n">
-        <v>0.21706</v>
-      </c>
-      <c r="R52" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S52" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T52" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U52" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V52" s="24" t="n"/>
-      <c r="W52" s="26" t="n"/>
-      <c r="X52" s="26" t="n"/>
-      <c r="Y52" s="25" t="n"/>
-      <c r="Z52" s="26" t="n"/>
-      <c r="AA52" s="28" t="n"/>
-      <c r="AB52" s="28" t="n"/>
-      <c r="AC52" s="30" t="n"/>
-      <c r="AD52" s="24" t="n"/>
-      <c r="AE52" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF52" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG52" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH52" s="24" t="n"/>
-      <c r="AI52" s="31" t="n"/>
-      <c r="AJ52" s="31" t="n"/>
-      <c r="AK52" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL52" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM52" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN52" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO52" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP52" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="AQ52" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="AR52" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="AS52" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AT52" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AU52" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AV52" s="24" t="n"/>
-      <c r="AW52" s="24" t="n"/>
-      <c r="AX52" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY52" s="24" t="n"/>
-      <c r="AZ52" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA52" s="24" t="inlineStr">
-        <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
-        </is>
-      </c>
-      <c r="BB52" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC52" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD52" s="24" t="inlineStr">
-        <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
-        </is>
-      </c>
-      <c r="BE52" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF52" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG52" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH52" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T08:19:25.914540Z</t>
-        </is>
-      </c>
-      <c r="BI52" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ52" s="25" t="n"/>
-      <c r="BK52" s="26" t="n">
-        <v>223</v>
-      </c>
-      <c r="BL52" s="27" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="BM52" s="28" t="n">
-        <v>0.309598</v>
-      </c>
-      <c r="BN52" s="28" t="n"/>
-      <c r="BO52" s="28" t="n"/>
-      <c r="BP52" s="25" t="n"/>
-      <c r="BQ52" s="27" t="n"/>
-      <c r="BR52" s="28" t="n"/>
-      <c r="BS52" s="28" t="n"/>
-      <c r="BT52" s="28" t="n"/>
-      <c r="BU52" s="25" t="n"/>
-      <c r="BV52" s="29" t="n"/>
-      <c r="BW52" s="24" t="n"/>
-      <c r="BX52" s="30" t="n"/>
-      <c r="BY52" s="27" t="n"/>
-      <c r="BZ52" s="24" t="n"/>
-      <c r="CA52" s="31" t="n"/>
-      <c r="CB52" s="24" t="n"/>
-      <c r="CC52" s="24" t="n"/>
-      <c r="CD52" s="24" t="n"/>
-      <c r="CE52" s="24" t="n"/>
-      <c r="CF52" s="24" t="n"/>
-      <c r="CG52" s="24" t="n"/>
-      <c r="CH52" s="24" t="n"/>
-      <c r="CI52" s="24" t="n"/>
-      <c r="CJ52" s="24" t="n"/>
-      <c r="CK52" s="24" t="n"/>
-      <c r="CL52" s="24" t="n"/>
-      <c r="CM52" s="24" t="n"/>
-      <c r="CN52" s="24" t="n"/>
-      <c r="CO52" s="24" t="n"/>
-    </row>
-    <row r="53" ht="36" customHeight="1">
-      <c r="A53" s="24" t="inlineStr">
-        <is>
-          <t>6448946bd28040a7</t>
-        </is>
-      </c>
-      <c r="B53" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T08:19:31.181747Z</t>
-        </is>
-      </c>
-      <c r="C53" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T23:00:00Z</t>
-        </is>
-      </c>
-      <c r="D53" s="24" t="inlineStr">
-        <is>
-          <t>68043</t>
-        </is>
-      </c>
-      <c r="E53" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F53" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="G53" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="H53" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I53" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J53" s="25" t="n"/>
-      <c r="K53" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L53" s="26" t="n">
-        <v>113</v>
-      </c>
-      <c r="M53" s="27" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="N53" s="28" t="n">
-        <v>0.469484</v>
-      </c>
-      <c r="O53" s="28" t="n">
-        <v>0.569576</v>
-      </c>
-      <c r="P53" s="28" t="n"/>
-      <c r="Q53" s="28" t="n">
-        <v>0.100092</v>
-      </c>
-      <c r="R53" s="26" t="n">
-        <v>70</v>
-      </c>
-      <c r="S53" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T53" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U53" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V53" s="24" t="n"/>
-      <c r="W53" s="26" t="n"/>
-      <c r="X53" s="26" t="n"/>
-      <c r="Y53" s="25" t="n"/>
-      <c r="Z53" s="26" t="n"/>
-      <c r="AA53" s="28" t="n"/>
-      <c r="AB53" s="28" t="n"/>
-      <c r="AC53" s="30" t="n"/>
-      <c r="AD53" s="24" t="n"/>
-      <c r="AE53" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF53" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG53" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH53" s="24" t="n"/>
-      <c r="AI53" s="31" t="n"/>
-      <c r="AJ53" s="31" t="n"/>
-      <c r="AK53" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL53" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM53" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN53" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO53" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP53" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AQ53" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AR53" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AS53" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="AT53" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="AU53" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="AV53" s="24" t="n"/>
-      <c r="AW53" s="24" t="n"/>
-      <c r="AX53" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY53" s="24" t="n"/>
-      <c r="AZ53" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA53" s="24" t="inlineStr">
-        <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
-        </is>
-      </c>
-      <c r="BB53" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC53" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD53" s="24" t="inlineStr">
-        <is>
-          <t>a52e05351d357192c8fca202e5be339611d036af46f5d6cce585d03967334b2a</t>
-        </is>
-      </c>
-      <c r="BE53" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF53" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG53" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH53" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T08:19:31.178279Z</t>
-        </is>
-      </c>
-      <c r="BI53" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ53" s="25" t="n"/>
-      <c r="BK53" s="26" t="n">
-        <v>113</v>
-      </c>
-      <c r="BL53" s="27" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BM53" s="28" t="n">
-        <v>0.469484</v>
-      </c>
-      <c r="BN53" s="28" t="n"/>
-      <c r="BO53" s="28" t="n"/>
-      <c r="BP53" s="25" t="n"/>
-      <c r="BQ53" s="27" t="n"/>
-      <c r="BR53" s="28" t="n"/>
-      <c r="BS53" s="28" t="n"/>
-      <c r="BT53" s="28" t="n"/>
-      <c r="BU53" s="25" t="n"/>
-      <c r="BV53" s="29" t="n"/>
-      <c r="BW53" s="24" t="n"/>
-      <c r="BX53" s="30" t="n"/>
-      <c r="BY53" s="27" t="n"/>
-      <c r="BZ53" s="24" t="n"/>
-      <c r="CA53" s="31" t="n"/>
-      <c r="CB53" s="24" t="n"/>
-      <c r="CC53" s="24" t="n"/>
-      <c r="CD53" s="24" t="n"/>
-      <c r="CE53" s="24" t="n"/>
-      <c r="CF53" s="24" t="n"/>
-      <c r="CG53" s="24" t="n"/>
-      <c r="CH53" s="24" t="n"/>
-      <c r="CI53" s="24" t="n"/>
-      <c r="CJ53" s="24" t="n"/>
-      <c r="CK53" s="24" t="n"/>
-      <c r="CL53" s="24" t="n"/>
-      <c r="CM53" s="24" t="n"/>
-      <c r="CN53" s="24" t="n"/>
-      <c r="CO53" s="24" t="n"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO49" headerRowCount="1">
-  <autoFilter ref="A1:CO49"/>
-  <tableColumns count="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP48" headerRowCount="1">
+  <autoFilter ref="A1:CP48"/>
+  <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,6 +396,7 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
+    <tableColumn id="94" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -752,19 +753,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$49)</f>
+        <f>COUNTA('Picks'!$A$2:$A$48)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$49,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$48,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$49,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$49,"settled",'Picks'!$V$2:$V$49,"win")+COUNTIFS('Picks'!$U$2:$U$49,"settled",'Picks'!$V$2:$V$49,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")+COUNTIFS('Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -792,19 +793,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$49,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$48,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$49,"&gt;0",'Picks'!$V$2:$V$49,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$49,"&gt;0",'Picks'!$V$2:$V$49,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$49,"&gt;0",'Picks'!$V$2:$V$49,"win")/(COUNTIFS('Picks'!$BX$2:$BX$49,"&gt;0",'Picks'!$V$2:$V$49,"win")+COUNTIFS('Picks'!$BX$2:$BX$49,"&gt;0",'Picks'!$V$2:$V$49,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")/(COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")+COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$49)/SUM('Picks'!$BX$2:$BX$49),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$48)/SUM('Picks'!$BX$2:$BX$48),0)</f>
         <v/>
       </c>
     </row>
@@ -832,19 +833,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$49)</f>
+        <f>SUM('Picks'!$BY$2:$BY$48)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$49,"&lt;&gt;",'Picks'!$AB$2:$AB$49),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$48,"&lt;&gt;",'Picks'!$AB$2:$AB$48),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$49,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$49,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$48,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$49,'Picks'!$AM$2:$AM$49,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$48,'Picks'!$AM$2:$AM$48,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -899,15 +900,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$49,$A14,'Picks'!$U$2:$U$49,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$49,$A14,'Picks'!$U$2:$U$49,"settled",'Picks'!$V$2:$V$49,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$49,$A14,'Picks'!$U$2:$U$49,"settled",'Picks'!$V$2:$V$49,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -915,11 +916,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$49,'Picks'!$H$2:$H$49,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$49,'Picks'!$H$2:$H$49,$A14,'Picks'!$U$2:$U$49,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -930,15 +931,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$49,$A15,'Picks'!$U$2:$U$49,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$49,$A15,'Picks'!$U$2:$U$49,"settled",'Picks'!$V$2:$V$49,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$49,$A15,'Picks'!$U$2:$U$49,"settled",'Picks'!$V$2:$V$49,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -946,11 +947,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$49,'Picks'!$H$2:$H$49,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$49,'Picks'!$H$2:$H$49,$A15,'Picks'!$U$2:$U$49,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -961,15 +962,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$49,$A16,'Picks'!$U$2:$U$49,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$49,$A16,'Picks'!$U$2:$U$49,"settled",'Picks'!$V$2:$V$49,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$49,$A16,'Picks'!$U$2:$U$49,"settled",'Picks'!$V$2:$V$49,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -977,11 +978,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$49,'Picks'!$H$2:$H$49,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$49,'Picks'!$H$2:$H$49,$A16,'Picks'!$U$2:$U$49,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1010,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO49"/>
+  <dimension ref="A1:CP48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,6 +1107,7 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="17" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1572,6 +1574,11 @@
       <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
+        </is>
+      </c>
+      <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>trade_candidate</t>
         </is>
       </c>
     </row>
@@ -1859,6 +1866,7 @@
       <c r="CM2" s="24" t="n"/>
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2144,6 +2152,7 @@
       <c r="CM3" s="24" t="n"/>
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
+      <c r="CP3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2429,6 +2438,7 @@
       <c r="CM4" s="24" t="n"/>
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
+      <c r="CP4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2714,6 +2724,7 @@
       <c r="CM5" s="24" t="n"/>
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
+      <c r="CP5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -2999,6 +3010,7 @@
       <c r="CM6" s="24" t="n"/>
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
+      <c r="CP6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3260,6 +3272,7 @@
       <c r="CM7" s="24" t="n"/>
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
+      <c r="CP7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3545,6 +3558,7 @@
       <c r="CM8" s="24" t="n"/>
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
+      <c r="CP8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3830,6 +3844,7 @@
       <c r="CM9" s="24" t="n"/>
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4115,6 +4130,7 @@
       <c r="CM10" s="24" t="n"/>
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
+      <c r="CP10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4400,6 +4416,7 @@
       <c r="CM11" s="24" t="n"/>
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4685,6 +4702,7 @@
       <c r="CM12" s="24" t="n"/>
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -4970,6 +4988,7 @@
       <c r="CM13" s="24" t="n"/>
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5255,6 +5274,7 @@
       <c r="CM14" s="24" t="n"/>
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5540,6 +5560,7 @@
       <c r="CM15" s="24" t="n"/>
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5825,6 +5846,7 @@
       <c r="CM16" s="24" t="n"/>
       <c r="CN16" s="24" t="n"/>
       <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6110,6 +6132,7 @@
       <c r="CM17" s="24" t="n"/>
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -6395,6 +6418,7 @@
       <c r="CM18" s="24" t="n"/>
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
@@ -6680,6 +6704,7 @@
       <c r="CM19" s="24" t="n"/>
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
@@ -6965,6 +6990,7 @@
       <c r="CM20" s="24" t="n"/>
       <c r="CN20" s="24" t="n"/>
       <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
@@ -7250,6 +7276,7 @@
       <c r="CM21" s="24" t="n"/>
       <c r="CN21" s="24" t="n"/>
       <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
@@ -7535,6 +7562,7 @@
       <c r="CM22" s="24" t="n"/>
       <c r="CN22" s="24" t="n"/>
       <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
@@ -7796,6 +7824,7 @@
       <c r="CM23" s="24" t="n"/>
       <c r="CN23" s="24" t="n"/>
       <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
@@ -8081,6 +8110,7 @@
       <c r="CM24" s="24" t="n"/>
       <c r="CN24" s="24" t="n"/>
       <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
@@ -8366,6 +8396,7 @@
       <c r="CM25" s="24" t="n"/>
       <c r="CN25" s="24" t="n"/>
       <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
@@ -8651,6 +8682,7 @@
       <c r="CM26" s="24" t="n"/>
       <c r="CN26" s="24" t="n"/>
       <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
@@ -8936,6 +8968,7 @@
       <c r="CM27" s="24" t="n"/>
       <c r="CN27" s="24" t="n"/>
       <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
@@ -9018,18 +9051,38 @@
       </c>
       <c r="U28" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V28" s="24" t="n"/>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y28" s="25" t="n"/>
-      <c r="Z28" s="26" t="n"/>
-      <c r="AA28" s="28" t="n"/>
-      <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n"/>
-      <c r="AD28" s="24" t="n"/>
+      <c r="Z28" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="AA28" s="28" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AB28" s="28" t="n">
+        <v>0.000815</v>
+      </c>
+      <c r="AC28" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T11:45:02.787455Z</t>
+        </is>
+      </c>
       <c r="AE28" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-cs2-pcific-ff-2026-08-02).</t>
@@ -9042,7 +9095,7 @@
       </c>
       <c r="AG28" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH28" s="24" t="n"/>
@@ -9172,8 +9225,12 @@
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
       <c r="BP28" s="25" t="n"/>
-      <c r="BQ28" s="27" t="n"/>
-      <c r="BR28" s="28" t="n"/>
+      <c r="BQ28" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BR28" s="28" t="n">
+        <v>0.43</v>
+      </c>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
       <c r="BU28" s="25" t="n"/>
@@ -9197,6 +9254,7 @@
       <c r="CM28" s="24" t="n"/>
       <c r="CN28" s="24" t="n"/>
       <c r="CO28" s="24" t="n"/>
+      <c r="CP28" s="24" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
@@ -9458,6 +9516,7 @@
       <c r="CM29" s="24" t="n"/>
       <c r="CN29" s="24" t="n"/>
       <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
@@ -9540,18 +9599,38 @@
       </c>
       <c r="U30" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V30" s="24" t="n"/>
-      <c r="W30" s="26" t="n"/>
-      <c r="X30" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y30" s="25" t="n"/>
-      <c r="Z30" s="26" t="n"/>
-      <c r="AA30" s="28" t="n"/>
-      <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n"/>
-      <c r="AD30" s="24" t="n"/>
+      <c r="Z30" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="AA30" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB30" s="28" t="n">
+        <v>-0.000815</v>
+      </c>
+      <c r="AC30" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T13:01:10.112601Z</t>
+        </is>
+      </c>
       <c r="AE30" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-ica-nve-2026-08-02).</t>
@@ -9564,7 +9643,7 @@
       </c>
       <c r="AG30" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH30" s="24" t="n"/>
@@ -9694,8 +9773,12 @@
       <c r="BN30" s="28" t="n"/>
       <c r="BO30" s="28" t="n"/>
       <c r="BP30" s="25" t="n"/>
-      <c r="BQ30" s="27" t="n"/>
-      <c r="BR30" s="28" t="n"/>
+      <c r="BQ30" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BR30" s="28" t="n">
+        <v>0.57</v>
+      </c>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
       <c r="BU30" s="25" t="n"/>
@@ -9719,16 +9802,17 @@
       <c r="CM30" s="24" t="n"/>
       <c r="CN30" s="24" t="n"/>
       <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>9f280e9d1f384c60</t>
+          <t>8c78149875be41de</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T12:30:33.225632Z</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
@@ -9738,7 +9822,7 @@
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>68673</t>
+          <t>68258</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
@@ -9748,12 +9832,12 @@
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>Sashi Esport</t>
+          <t>ex-MANA eSports</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr">
@@ -9763,7 +9847,7 @@
       </c>
       <c r="I31" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J31" s="25" t="n"/>
@@ -9773,20 +9857,20 @@
         </is>
       </c>
       <c r="L31" s="26" t="n">
-        <v>-203</v>
+        <v>-213</v>
       </c>
       <c r="M31" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.469484</v>
       </c>
       <c r="N31" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.680511</v>
       </c>
       <c r="O31" s="28" t="n">
-        <v>0.593754</v>
+        <v>0.583752</v>
       </c>
       <c r="P31" s="28" t="n"/>
       <c r="Q31" s="28" t="n">
-        <v>-0.076213</v>
+        <v>-0.096759</v>
       </c>
       <c r="R31" s="26" t="n">
         <v>0</v>
@@ -9815,7 +9899,7 @@
       <c r="AD31" s="24" t="n"/>
       <c r="AE31" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-bpl-sashi-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-ica-exmana-2026-08-02).</t>
         </is>
       </c>
       <c r="AF31" s="31" t="inlineStr">
@@ -9856,32 +9940,32 @@
       </c>
       <c r="AP31" s="24" t="inlineStr">
         <is>
-          <t>Sashi Esport</t>
+          <t>ex-MANA eSports</t>
         </is>
       </c>
       <c r="AQ31" s="24" t="inlineStr">
         <is>
-          <t>Sashi Esport</t>
+          <t>ex-MANA eSports</t>
         </is>
       </c>
       <c r="AR31" s="24" t="inlineStr">
         <is>
-          <t>Sashi Esport</t>
+          <t>ex-MANA eSports</t>
         </is>
       </c>
       <c r="AS31" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AT31" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AU31" s="24" t="inlineStr">
         <is>
-          <t>Black Phoenix</t>
+          <t>Inner Circle Academy</t>
         </is>
       </c>
       <c r="AV31" s="24" t="n"/>
@@ -9899,7 +9983,7 @@
       </c>
       <c r="BA31" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>bd7b44b2e86615e932309b2497f806ee2b5567367d785a2c9653f7a6fe2215fb</t>
         </is>
       </c>
       <c r="BB31" s="24" t="inlineStr">
@@ -9914,7 +9998,7 @@
       </c>
       <c r="BD31" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>bd7b44b2e86615e932309b2497f806ee2b5567367d785a2c9653f7a6fe2215fb</t>
         </is>
       </c>
       <c r="BE31" s="24" t="inlineStr">
@@ -9934,7 +10018,7 @@
       </c>
       <c r="BH31" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:45.037220Z</t>
+          <t>2026-08-02T12:30:13.091362Z</t>
         </is>
       </c>
       <c r="BI31" s="24" t="inlineStr">
@@ -9944,13 +10028,13 @@
       </c>
       <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
-        <v>-203</v>
+        <v>-213</v>
       </c>
       <c r="BL31" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.469484</v>
       </c>
       <c r="BM31" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.680511</v>
       </c>
       <c r="BN31" s="28" t="n"/>
       <c r="BO31" s="28" t="n"/>
@@ -9980,16 +10064,17 @@
       <c r="CM31" s="24" t="n"/>
       <c r="CN31" s="24" t="n"/>
       <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
         <is>
-          <t>3904a03493c1476b</t>
+          <t>6089a7bd20c542bc</t>
         </is>
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T12:30:33.225632Z</t>
         </is>
       </c>
       <c r="C32" s="24" t="inlineStr">
@@ -9999,7 +10084,7 @@
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>68255</t>
+          <t>68256</t>
         </is>
       </c>
       <c r="E32" s="24" t="inlineStr">
@@ -10009,12 +10094,12 @@
       </c>
       <c r="F32" s="24" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="G32" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr">
@@ -10024,7 +10109,7 @@
       </c>
       <c r="I32" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J32" s="25" t="n"/>
@@ -10034,26 +10119,26 @@
         </is>
       </c>
       <c r="L32" s="26" t="n">
-        <v>-133</v>
+        <v>-223</v>
       </c>
       <c r="M32" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.44843</v>
       </c>
       <c r="N32" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.690402</v>
       </c>
       <c r="O32" s="28" t="n">
-        <v>0.543392</v>
+        <v>0.620297</v>
       </c>
       <c r="P32" s="28" t="n"/>
       <c r="Q32" s="28" t="n">
-        <v>-0.027423</v>
+        <v>-0.070105</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S32" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T32" s="24" t="inlineStr">
         <is>
@@ -10076,7 +10161,7 @@
       <c r="AD32" s="24" t="n"/>
       <c r="AE32" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-mouzn-wba-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-lk-nvo-2026-08-02).</t>
         </is>
       </c>
       <c r="AF32" s="31" t="inlineStr">
@@ -10117,32 +10202,32 @@
       </c>
       <c r="AP32" s="24" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AQ32" s="24" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AR32" s="24" t="inlineStr">
         <is>
-          <t>WBT</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AS32" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AT32" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AU32" s="24" t="inlineStr">
         <is>
-          <t>MOUZ NXT</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AV32" s="24" t="n"/>
@@ -10160,7 +10245,7 @@
       </c>
       <c r="BA32" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>bd7b44b2e86615e932309b2497f806ee2b5567367d785a2c9653f7a6fe2215fb</t>
         </is>
       </c>
       <c r="BB32" s="24" t="inlineStr">
@@ -10175,7 +10260,7 @@
       </c>
       <c r="BD32" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>bd7b44b2e86615e932309b2497f806ee2b5567367d785a2c9653f7a6fe2215fb</t>
         </is>
       </c>
       <c r="BE32" s="24" t="inlineStr">
@@ -10195,7 +10280,7 @@
       </c>
       <c r="BH32" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:45.600229Z</t>
+          <t>2026-08-02T12:30:13.564896Z</t>
         </is>
       </c>
       <c r="BI32" s="24" t="inlineStr">
@@ -10205,13 +10290,13 @@
       </c>
       <c r="BJ32" s="25" t="n"/>
       <c r="BK32" s="26" t="n">
-        <v>-133</v>
+        <v>-223</v>
       </c>
       <c r="BL32" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.44843</v>
       </c>
       <c r="BM32" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.690402</v>
       </c>
       <c r="BN32" s="28" t="n"/>
       <c r="BO32" s="28" t="n"/>
@@ -10241,16 +10326,17 @@
       <c r="CM32" s="24" t="n"/>
       <c r="CN32" s="24" t="n"/>
       <c r="CO32" s="24" t="n"/>
+      <c r="CP32" s="24" t="n"/>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>02a02b088b82494b</t>
+          <t>2f30461e96204d71</t>
         </is>
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T12:30:33.225632Z</t>
         </is>
       </c>
       <c r="C33" s="24" t="inlineStr">
@@ -10260,7 +10346,7 @@
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>68256</t>
+          <t>68257</t>
         </is>
       </c>
       <c r="E33" s="24" t="inlineStr">
@@ -10270,12 +10356,12 @@
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="G33" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>DragonClaw</t>
         </is>
       </c>
       <c r="H33" s="24" t="inlineStr">
@@ -10295,26 +10381,26 @@
         </is>
       </c>
       <c r="L33" s="26" t="n">
-        <v>-223</v>
+        <v>-113</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.884956</v>
       </c>
       <c r="N33" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.530516</v>
       </c>
       <c r="O33" s="28" t="n">
-        <v>0.620448</v>
+        <v>0.67594</v>
       </c>
       <c r="P33" s="28" t="n"/>
       <c r="Q33" s="28" t="n">
-        <v>-0.069954</v>
+        <v>0.145424</v>
       </c>
       <c r="R33" s="26" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="S33" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T33" s="24" t="inlineStr">
         <is>
@@ -10337,7 +10423,7 @@
       <c r="AD33" s="24" t="n"/>
       <c r="AE33" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-lk-nvo-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-cs2-dc-for-2026-08-02).</t>
         </is>
       </c>
       <c r="AF33" s="31" t="inlineStr">
@@ -10355,7 +10441,7 @@
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL33" s="26" t="n">
@@ -10363,47 +10449,47 @@
       </c>
       <c r="AM33" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN33" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO33" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP33" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AQ33" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AR33" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AS33" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>DragonClaw</t>
         </is>
       </c>
       <c r="AT33" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>DragonClaw</t>
         </is>
       </c>
       <c r="AU33" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>DragonClaw</t>
         </is>
       </c>
       <c r="AV33" s="24" t="n"/>
@@ -10421,7 +10507,7 @@
       </c>
       <c r="BA33" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>bd7b44b2e86615e932309b2497f806ee2b5567367d785a2c9653f7a6fe2215fb</t>
         </is>
       </c>
       <c r="BB33" s="24" t="inlineStr">
@@ -10436,7 +10522,7 @@
       </c>
       <c r="BD33" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>bd7b44b2e86615e932309b2497f806ee2b5567367d785a2c9653f7a6fe2215fb</t>
         </is>
       </c>
       <c r="BE33" s="24" t="inlineStr">
@@ -10456,7 +10542,7 @@
       </c>
       <c r="BH33" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:46.158629Z</t>
+          <t>2026-08-02T12:30:14.025736Z</t>
         </is>
       </c>
       <c r="BI33" s="24" t="inlineStr">
@@ -10466,13 +10552,13 @@
       </c>
       <c r="BJ33" s="25" t="n"/>
       <c r="BK33" s="26" t="n">
-        <v>-223</v>
+        <v>-113</v>
       </c>
       <c r="BL33" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.884956</v>
       </c>
       <c r="BM33" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.530516</v>
       </c>
       <c r="BN33" s="28" t="n"/>
       <c r="BO33" s="28" t="n"/>
@@ -10502,16 +10588,17 @@
       <c r="CM33" s="24" t="n"/>
       <c r="CN33" s="24" t="n"/>
       <c r="CO33" s="24" t="n"/>
+      <c r="CP33" s="24" t="n"/>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>61b537b0f1324864</t>
+          <t>e5958621784d4f7f</t>
         </is>
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T12:30:33.225632Z</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -10521,7 +10608,7 @@
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>68257</t>
+          <t>68259</t>
         </is>
       </c>
       <c r="E34" s="24" t="inlineStr">
@@ -10531,12 +10618,12 @@
       </c>
       <c r="F34" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Vexar</t>
         </is>
       </c>
       <c r="G34" s="24" t="inlineStr">
         <is>
-          <t>DragonClaw</t>
+          <t>Leo Team</t>
         </is>
       </c>
       <c r="H34" s="24" t="inlineStr">
@@ -10546,7 +10633,7 @@
       </c>
       <c r="I34" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J34" s="25" t="n"/>
@@ -10556,26 +10643,26 @@
         </is>
       </c>
       <c r="L34" s="26" t="n">
-        <v>-113</v>
+        <v>138</v>
       </c>
       <c r="M34" s="27" t="n">
-        <v>1.884956</v>
+        <v>2.38</v>
       </c>
       <c r="N34" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.420168</v>
       </c>
       <c r="O34" s="28" t="n">
-        <v>0.676069</v>
+        <v>0.5635559999999999</v>
       </c>
       <c r="P34" s="28" t="n"/>
       <c r="Q34" s="28" t="n">
-        <v>0.145553</v>
+        <v>0.143388</v>
       </c>
       <c r="R34" s="26" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="S34" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T34" s="24" t="inlineStr">
         <is>
@@ -10598,7 +10685,7 @@
       <c r="AD34" s="24" t="n"/>
       <c r="AE34" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-cs2-dc-for-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-leo-vexar-2026-08-02).</t>
         </is>
       </c>
       <c r="AF34" s="31" t="inlineStr">
@@ -10616,7 +10703,7 @@
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL34" s="26" t="n">
@@ -10624,47 +10711,47 @@
       </c>
       <c r="AM34" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN34" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO34" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP34" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Vexar</t>
         </is>
       </c>
       <c r="AQ34" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Vexar</t>
         </is>
       </c>
       <c r="AR34" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Vexar</t>
         </is>
       </c>
       <c r="AS34" s="24" t="inlineStr">
         <is>
-          <t>DragonClaw</t>
+          <t>Leo Team</t>
         </is>
       </c>
       <c r="AT34" s="24" t="inlineStr">
         <is>
-          <t>DragonClaw</t>
+          <t>Leo Team</t>
         </is>
       </c>
       <c r="AU34" s="24" t="inlineStr">
         <is>
-          <t>DragonClaw</t>
+          <t>Leo Team</t>
         </is>
       </c>
       <c r="AV34" s="24" t="n"/>
@@ -10682,7 +10769,7 @@
       </c>
       <c r="BA34" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>bd7b44b2e86615e932309b2497f806ee2b5567367d785a2c9653f7a6fe2215fb</t>
         </is>
       </c>
       <c r="BB34" s="24" t="inlineStr">
@@ -10697,7 +10784,7 @@
       </c>
       <c r="BD34" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>bd7b44b2e86615e932309b2497f806ee2b5567367d785a2c9653f7a6fe2215fb</t>
         </is>
       </c>
       <c r="BE34" s="24" t="inlineStr">
@@ -10717,7 +10804,7 @@
       </c>
       <c r="BH34" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:46.682984Z</t>
+          <t>2026-08-02T12:30:14.500766Z</t>
         </is>
       </c>
       <c r="BI34" s="24" t="inlineStr">
@@ -10727,13 +10814,13 @@
       </c>
       <c r="BJ34" s="25" t="n"/>
       <c r="BK34" s="26" t="n">
-        <v>-113</v>
+        <v>138</v>
       </c>
       <c r="BL34" s="27" t="n">
-        <v>1.884956</v>
+        <v>2.38</v>
       </c>
       <c r="BM34" s="28" t="n">
-        <v>0.530516</v>
+        <v>0.420168</v>
       </c>
       <c r="BN34" s="28" t="n"/>
       <c r="BO34" s="28" t="n"/>
@@ -10763,16 +10850,17 @@
       <c r="CM34" s="24" t="n"/>
       <c r="CN34" s="24" t="n"/>
       <c r="CO34" s="24" t="n"/>
+      <c r="CP34" s="24" t="n"/>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>b74b5d38bcc34cfc</t>
+          <t>777a777696ed478d</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T12:30:33.225632Z</t>
         </is>
       </c>
       <c r="C35" s="24" t="inlineStr">
@@ -10782,7 +10870,7 @@
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>68258</t>
+          <t>68277</t>
         </is>
       </c>
       <c r="E35" s="24" t="inlineStr">
@@ -10792,12 +10880,12 @@
       </c>
       <c r="F35" s="24" t="inlineStr">
         <is>
-          <t>ex-MANA eSports</t>
+          <t>Misa Esports</t>
         </is>
       </c>
       <c r="G35" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>Favbet</t>
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr">
@@ -10817,26 +10905,26 @@
         </is>
       </c>
       <c r="L35" s="26" t="n">
-        <v>-203</v>
+        <v>-178</v>
       </c>
       <c r="M35" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.561798</v>
       </c>
       <c r="N35" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.640288</v>
       </c>
       <c r="O35" s="28" t="n">
-        <v>0.583693</v>
+        <v>0.74688</v>
       </c>
       <c r="P35" s="28" t="n"/>
       <c r="Q35" s="28" t="n">
-        <v>-0.086274</v>
+        <v>0.106592</v>
       </c>
       <c r="R35" s="26" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="S35" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T35" s="24" t="inlineStr">
         <is>
@@ -10859,7 +10947,7 @@
       <c r="AD35" s="24" t="n"/>
       <c r="AE35" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-ica-exmana-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-fav-misa-2026-08-02).</t>
         </is>
       </c>
       <c r="AF35" s="31" t="inlineStr">
@@ -10895,37 +10983,37 @@
       </c>
       <c r="AO35" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP35" s="24" t="inlineStr">
         <is>
-          <t>ex-MANA eSports</t>
+          <t>Misa Esports</t>
         </is>
       </c>
       <c r="AQ35" s="24" t="inlineStr">
         <is>
-          <t>ex-MANA eSports</t>
+          <t>Misa Esports</t>
         </is>
       </c>
       <c r="AR35" s="24" t="inlineStr">
         <is>
-          <t>ex-MANA eSports</t>
+          <t>Misa Esports</t>
         </is>
       </c>
       <c r="AS35" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>Favbet</t>
         </is>
       </c>
       <c r="AT35" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>Favbet</t>
         </is>
       </c>
       <c r="AU35" s="24" t="inlineStr">
         <is>
-          <t>Inner Circle Academy</t>
+          <t>Favbet</t>
         </is>
       </c>
       <c r="AV35" s="24" t="n"/>
@@ -10943,7 +11031,7 @@
       </c>
       <c r="BA35" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>bd7b44b2e86615e932309b2497f806ee2b5567367d785a2c9653f7a6fe2215fb</t>
         </is>
       </c>
       <c r="BB35" s="24" t="inlineStr">
@@ -10958,7 +11046,7 @@
       </c>
       <c r="BD35" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>bd7b44b2e86615e932309b2497f806ee2b5567367d785a2c9653f7a6fe2215fb</t>
         </is>
       </c>
       <c r="BE35" s="24" t="inlineStr">
@@ -10978,7 +11066,7 @@
       </c>
       <c r="BH35" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:47.204216Z</t>
+          <t>2026-08-02T12:30:14.970352Z</t>
         </is>
       </c>
       <c r="BI35" s="24" t="inlineStr">
@@ -10988,13 +11076,13 @@
       </c>
       <c r="BJ35" s="25" t="n"/>
       <c r="BK35" s="26" t="n">
-        <v>-203</v>
+        <v>-178</v>
       </c>
       <c r="BL35" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.561798</v>
       </c>
       <c r="BM35" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.640288</v>
       </c>
       <c r="BN35" s="28" t="n"/>
       <c r="BO35" s="28" t="n"/>
@@ -11024,16 +11112,17 @@
       <c r="CM35" s="24" t="n"/>
       <c r="CN35" s="24" t="n"/>
       <c r="CO35" s="24" t="n"/>
+      <c r="CP35" s="24" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>a71808496ac04951</t>
+          <t>cde934c0a2974b08</t>
         </is>
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T12:30:33.225632Z</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
@@ -11043,7 +11132,7 @@
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>68259</t>
+          <t>68261</t>
         </is>
       </c>
       <c r="E36" s="24" t="inlineStr">
@@ -11053,12 +11142,12 @@
       </c>
       <c r="F36" s="24" t="inlineStr">
         <is>
-          <t>Vexar</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="G36" s="24" t="inlineStr">
         <is>
-          <t>Leo Team</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="H36" s="24" t="inlineStr">
@@ -11068,7 +11157,7 @@
       </c>
       <c r="I36" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J36" s="25" t="n"/>
@@ -11078,26 +11167,26 @@
         </is>
       </c>
       <c r="L36" s="26" t="n">
-        <v>138</v>
+        <v>-138</v>
       </c>
       <c r="M36" s="27" t="n">
-        <v>2.38</v>
+        <v>1.724638</v>
       </c>
       <c r="N36" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.579832</v>
       </c>
       <c r="O36" s="28" t="n">
-        <v>0.563872</v>
+        <v>0.65406</v>
       </c>
       <c r="P36" s="28" t="n"/>
       <c r="Q36" s="28" t="n">
-        <v>0.143704</v>
+        <v>0.074228</v>
       </c>
       <c r="R36" s="26" t="n">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="S36" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T36" s="24" t="inlineStr">
         <is>
@@ -11120,7 +11209,7 @@
       <c r="AD36" s="24" t="n"/>
       <c r="AE36" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-leo-vexar-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-bmb-ff-2026-08-02).</t>
         </is>
       </c>
       <c r="AF36" s="31" t="inlineStr">
@@ -11161,32 +11250,32 @@
       </c>
       <c r="AP36" s="24" t="inlineStr">
         <is>
-          <t>Vexar</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="AQ36" s="24" t="inlineStr">
         <is>
-          <t>Vexar</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="AR36" s="24" t="inlineStr">
         <is>
-          <t>Vexar</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="AS36" s="24" t="inlineStr">
         <is>
-          <t>Leo Team</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AT36" s="24" t="inlineStr">
         <is>
-          <t>Leo Team</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AU36" s="24" t="inlineStr">
         <is>
-          <t>Leo Team</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AV36" s="24" t="n"/>
@@ -11204,7 +11293,7 @@
       </c>
       <c r="BA36" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>bd7b44b2e86615e932309b2497f806ee2b5567367d785a2c9653f7a6fe2215fb</t>
         </is>
       </c>
       <c r="BB36" s="24" t="inlineStr">
@@ -11219,7 +11308,7 @@
       </c>
       <c r="BD36" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>bd7b44b2e86615e932309b2497f806ee2b5567367d785a2c9653f7a6fe2215fb</t>
         </is>
       </c>
       <c r="BE36" s="24" t="inlineStr">
@@ -11239,7 +11328,7 @@
       </c>
       <c r="BH36" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:47.738958Z</t>
+          <t>2026-08-02T12:30:15.429687Z</t>
         </is>
       </c>
       <c r="BI36" s="24" t="inlineStr">
@@ -11249,13 +11338,13 @@
       </c>
       <c r="BJ36" s="25" t="n"/>
       <c r="BK36" s="26" t="n">
-        <v>138</v>
+        <v>-138</v>
       </c>
       <c r="BL36" s="27" t="n">
-        <v>2.38</v>
+        <v>1.724638</v>
       </c>
       <c r="BM36" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.579832</v>
       </c>
       <c r="BN36" s="28" t="n"/>
       <c r="BO36" s="28" t="n"/>
@@ -11285,16 +11374,17 @@
       <c r="CM36" s="24" t="n"/>
       <c r="CN36" s="24" t="n"/>
       <c r="CO36" s="24" t="n"/>
+      <c r="CP36" s="24" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>e06a6be4d99e43cd</t>
+          <t>d0efc22dca584b47</t>
         </is>
       </c>
       <c r="B37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T12:30:33.225632Z</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
@@ -11304,7 +11394,7 @@
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>68261</t>
+          <t>68255</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
@@ -11314,12 +11404,12 @@
       </c>
       <c r="F37" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>WBT</t>
         </is>
       </c>
       <c r="G37" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="H37" s="24" t="inlineStr">
@@ -11329,7 +11419,7 @@
       </c>
       <c r="I37" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J37" s="25" t="n"/>
@@ -11339,26 +11429,26 @@
         </is>
       </c>
       <c r="L37" s="26" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="M37" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.694444</v>
       </c>
       <c r="N37" s="28" t="n">
-        <v>0.6</v>
+        <v>0.590164</v>
       </c>
       <c r="O37" s="28" t="n">
-        <v>0.6541439999999999</v>
+        <v>0.543187</v>
       </c>
       <c r="P37" s="28" t="n"/>
       <c r="Q37" s="28" t="n">
-        <v>0.054144</v>
+        <v>-0.046977</v>
       </c>
       <c r="R37" s="26" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="S37" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T37" s="24" t="inlineStr">
         <is>
@@ -11381,7 +11471,7 @@
       <c r="AD37" s="24" t="n"/>
       <c r="AE37" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-bmb-ff-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-mouzn-wba-2026-08-02).</t>
         </is>
       </c>
       <c r="AF37" s="31" t="inlineStr">
@@ -11417,37 +11507,37 @@
       </c>
       <c r="AO37" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP37" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>WBT</t>
         </is>
       </c>
       <c r="AQ37" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>WBT</t>
         </is>
       </c>
       <c r="AR37" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>WBT</t>
         </is>
       </c>
       <c r="AS37" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AT37" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AU37" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>MOUZ NXT</t>
         </is>
       </c>
       <c r="AV37" s="24" t="n"/>
@@ -11465,7 +11555,7 @@
       </c>
       <c r="BA37" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>bd7b44b2e86615e932309b2497f806ee2b5567367d785a2c9653f7a6fe2215fb</t>
         </is>
       </c>
       <c r="BB37" s="24" t="inlineStr">
@@ -11480,7 +11570,7 @@
       </c>
       <c r="BD37" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>bd7b44b2e86615e932309b2497f806ee2b5567367d785a2c9653f7a6fe2215fb</t>
         </is>
       </c>
       <c r="BE37" s="24" t="inlineStr">
@@ -11500,7 +11590,7 @@
       </c>
       <c r="BH37" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:48.671997Z</t>
+          <t>2026-08-02T12:30:17.458438Z</t>
         </is>
       </c>
       <c r="BI37" s="24" t="inlineStr">
@@ -11510,13 +11600,13 @@
       </c>
       <c r="BJ37" s="25" t="n"/>
       <c r="BK37" s="26" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="BL37" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.694444</v>
       </c>
       <c r="BM37" s="28" t="n">
-        <v>0.6</v>
+        <v>0.590164</v>
       </c>
       <c r="BN37" s="28" t="n"/>
       <c r="BO37" s="28" t="n"/>
@@ -11546,26 +11636,27 @@
       <c r="CM37" s="24" t="n"/>
       <c r="CN37" s="24" t="n"/>
       <c r="CO37" s="24" t="n"/>
+      <c r="CP37" s="24" t="n"/>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>fc69b57d435f4ed9</t>
+          <t>70c73fb4130e4b04</t>
         </is>
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T13:07:50.282319Z</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:00:00Z</t>
+          <t>2026-08-02T17:00:00Z</t>
         </is>
       </c>
       <c r="D38" s="24" t="inlineStr">
         <is>
-          <t>68277</t>
+          <t>69263</t>
         </is>
       </c>
       <c r="E38" s="24" t="inlineStr">
@@ -11575,12 +11666,12 @@
       </c>
       <c r="F38" s="24" t="inlineStr">
         <is>
-          <t>Misa Esports</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="G38" s="24" t="inlineStr">
         <is>
-          <t>Favbet</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="H38" s="24" t="inlineStr">
@@ -11590,7 +11681,7 @@
       </c>
       <c r="I38" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J38" s="25" t="n"/>
@@ -11600,26 +11691,26 @@
         </is>
       </c>
       <c r="L38" s="26" t="n">
-        <v>-178</v>
+        <v>-170</v>
       </c>
       <c r="M38" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.588235</v>
       </c>
       <c r="N38" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.62963</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>0.747081</v>
+        <v>0.6659040000000001</v>
       </c>
       <c r="P38" s="28" t="n"/>
       <c r="Q38" s="28" t="n">
-        <v>0.106793</v>
+        <v>0.036274</v>
       </c>
       <c r="R38" s="26" t="n">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="S38" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T38" s="24" t="inlineStr">
         <is>
@@ -11642,7 +11733,7 @@
       <c r="AD38" s="24" t="n"/>
       <c r="AE38" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-fav-misa-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
         </is>
       </c>
       <c r="AF38" s="31" t="inlineStr">
@@ -11660,7 +11751,7 @@
       <c r="AJ38" s="31" t="n"/>
       <c r="AK38" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL38" s="26" t="n">
@@ -11668,47 +11759,47 @@
       </c>
       <c r="AM38" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN38" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO38" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP38" s="24" t="inlineStr">
         <is>
-          <t>Misa Esports</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AQ38" s="24" t="inlineStr">
         <is>
-          <t>Misa Esports</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AR38" s="24" t="inlineStr">
         <is>
-          <t>Misa Esports</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AS38" s="24" t="inlineStr">
         <is>
-          <t>Favbet</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AT38" s="24" t="inlineStr">
         <is>
-          <t>Favbet</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AU38" s="24" t="inlineStr">
         <is>
-          <t>Favbet</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AV38" s="24" t="n"/>
@@ -11726,7 +11817,7 @@
       </c>
       <c r="BA38" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BB38" s="24" t="inlineStr">
@@ -11741,7 +11832,7 @@
       </c>
       <c r="BD38" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BE38" s="24" t="inlineStr">
@@ -11761,7 +11852,7 @@
       </c>
       <c r="BH38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:49.257041Z</t>
+          <t>2026-08-02T13:07:36.093507Z</t>
         </is>
       </c>
       <c r="BI38" s="24" t="inlineStr">
@@ -11771,13 +11862,13 @@
       </c>
       <c r="BJ38" s="25" t="n"/>
       <c r="BK38" s="26" t="n">
-        <v>-178</v>
+        <v>-170</v>
       </c>
       <c r="BL38" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.588235</v>
       </c>
       <c r="BM38" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.62963</v>
       </c>
       <c r="BN38" s="28" t="n"/>
       <c r="BO38" s="28" t="n"/>
@@ -11807,26 +11898,27 @@
       <c r="CM38" s="24" t="n"/>
       <c r="CN38" s="24" t="n"/>
       <c r="CO38" s="24" t="n"/>
+      <c r="CP38" s="24" t="n"/>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>0618b43e418b498a</t>
+          <t>d7c4b733118b4e5d</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T13:07:50.282319Z</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T14:00:00Z</t>
+          <t>2026-08-02T18:00:00Z</t>
         </is>
       </c>
       <c r="D39" s="24" t="inlineStr">
         <is>
-          <t>69254</t>
+          <t>69289</t>
         </is>
       </c>
       <c r="E39" s="24" t="inlineStr">
@@ -11836,12 +11928,12 @@
       </c>
       <c r="F39" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="G39" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="H39" s="24" t="inlineStr">
@@ -11861,26 +11953,26 @@
         </is>
       </c>
       <c r="L39" s="26" t="n">
-        <v>-203</v>
+        <v>144</v>
       </c>
       <c r="M39" s="27" t="n">
-        <v>1.492611</v>
+        <v>2.44</v>
       </c>
       <c r="N39" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.409836</v>
       </c>
       <c r="O39" s="28" t="n">
-        <v>0.662043</v>
+        <v>0.510804</v>
       </c>
       <c r="P39" s="28" t="n"/>
       <c r="Q39" s="28" t="n">
-        <v>-0.007924</v>
+        <v>0.100968</v>
       </c>
       <c r="R39" s="26" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="S39" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T39" s="24" t="inlineStr">
         <is>
@@ -11903,7 +11995,7 @@
       <c r="AD39" s="24" t="n"/>
       <c r="AE39" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-erx-hon-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-cs2-shin-bst-2026-08-02).</t>
         </is>
       </c>
       <c r="AF39" s="31" t="inlineStr">
@@ -11944,32 +12036,32 @@
       </c>
       <c r="AP39" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AQ39" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AR39" s="24" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AS39" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="AT39" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="AU39" s="24" t="inlineStr">
         <is>
-          <t>ex-RUSTEC</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="AV39" s="24" t="n"/>
@@ -11987,7 +12079,7 @@
       </c>
       <c r="BA39" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BB39" s="24" t="inlineStr">
@@ -12002,7 +12094,7 @@
       </c>
       <c r="BD39" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BE39" s="24" t="inlineStr">
@@ -12022,7 +12114,7 @@
       </c>
       <c r="BH39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:49.723521Z</t>
+          <t>2026-08-02T13:07:36.582090Z</t>
         </is>
       </c>
       <c r="BI39" s="24" t="inlineStr">
@@ -12032,13 +12124,13 @@
       </c>
       <c r="BJ39" s="25" t="n"/>
       <c r="BK39" s="26" t="n">
-        <v>-203</v>
+        <v>144</v>
       </c>
       <c r="BL39" s="27" t="n">
-        <v>1.492611</v>
+        <v>2.44</v>
       </c>
       <c r="BM39" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.409836</v>
       </c>
       <c r="BN39" s="28" t="n"/>
       <c r="BO39" s="28" t="n"/>
@@ -12068,26 +12160,27 @@
       <c r="CM39" s="24" t="n"/>
       <c r="CN39" s="24" t="n"/>
       <c r="CO39" s="24" t="n"/>
+      <c r="CP39" s="24" t="n"/>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>105c3a3a07cd451c</t>
+          <t>f93d38b9d6484fa0</t>
         </is>
       </c>
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T13:07:50.282319Z</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:00:00Z</t>
+          <t>2026-08-02T19:15:00Z</t>
         </is>
       </c>
       <c r="D40" s="24" t="inlineStr">
         <is>
-          <t>69263</t>
+          <t>67577</t>
         </is>
       </c>
       <c r="E40" s="24" t="inlineStr">
@@ -12097,12 +12190,12 @@
       </c>
       <c r="F40" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="G40" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="H40" s="24" t="inlineStr">
@@ -12112,7 +12205,7 @@
       </c>
       <c r="I40" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J40" s="25" t="n"/>
@@ -12122,26 +12215,26 @@
         </is>
       </c>
       <c r="L40" s="26" t="n">
-        <v>-156</v>
+        <v>-150</v>
       </c>
       <c r="M40" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.666667</v>
       </c>
       <c r="N40" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.6</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>0.66636</v>
+        <v>0.526957</v>
       </c>
       <c r="P40" s="28" t="n"/>
       <c r="Q40" s="28" t="n">
-        <v>0.056985</v>
+        <v>-0.073043</v>
       </c>
       <c r="R40" s="26" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="S40" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T40" s="24" t="inlineStr">
         <is>
@@ -12164,7 +12257,7 @@
       <c r="AD40" s="24" t="n"/>
       <c r="AE40" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
         </is>
       </c>
       <c r="AF40" s="31" t="inlineStr">
@@ -12182,7 +12275,7 @@
       <c r="AJ40" s="31" t="n"/>
       <c r="AK40" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL40" s="26" t="n">
@@ -12190,47 +12283,47 @@
       </c>
       <c r="AM40" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN40" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO40" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP40" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AQ40" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AR40" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AS40" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AT40" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AU40" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AV40" s="24" t="n"/>
@@ -12248,7 +12341,7 @@
       </c>
       <c r="BA40" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BB40" s="24" t="inlineStr">
@@ -12263,7 +12356,7 @@
       </c>
       <c r="BD40" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BE40" s="24" t="inlineStr">
@@ -12283,7 +12376,7 @@
       </c>
       <c r="BH40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:51.297257Z</t>
+          <t>2026-08-02T13:07:37.163209Z</t>
         </is>
       </c>
       <c r="BI40" s="24" t="inlineStr">
@@ -12293,13 +12386,13 @@
       </c>
       <c r="BJ40" s="25" t="n"/>
       <c r="BK40" s="26" t="n">
-        <v>-156</v>
+        <v>-150</v>
       </c>
       <c r="BL40" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.666667</v>
       </c>
       <c r="BM40" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.6</v>
       </c>
       <c r="BN40" s="28" t="n"/>
       <c r="BO40" s="28" t="n"/>
@@ -12329,26 +12422,27 @@
       <c r="CM40" s="24" t="n"/>
       <c r="CN40" s="24" t="n"/>
       <c r="CO40" s="24" t="n"/>
+      <c r="CP40" s="24" t="n"/>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>a6760f9308b440ac</t>
+          <t>52e4ee83bf634645</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T13:07:50.282319Z</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:00:00Z</t>
+          <t>2026-08-02T19:15:00Z</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>69289</t>
+          <t>67576</t>
         </is>
       </c>
       <c r="E41" s="24" t="inlineStr">
@@ -12358,12 +12452,12 @@
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="G41" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="H41" s="24" t="inlineStr">
@@ -12383,26 +12477,26 @@
         </is>
       </c>
       <c r="L41" s="26" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="M41" s="27" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="N41" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.409836</v>
       </c>
       <c r="O41" s="28" t="n">
-        <v>0.510543</v>
+        <v>0.57967</v>
       </c>
       <c r="P41" s="28" t="n"/>
       <c r="Q41" s="28" t="n">
-        <v>0.090375</v>
+        <v>0.169834</v>
       </c>
       <c r="R41" s="26" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="S41" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T41" s="24" t="inlineStr">
         <is>
@@ -12425,7 +12519,7 @@
       <c r="AD41" s="24" t="n"/>
       <c r="AE41" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-shin-bst-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
         </is>
       </c>
       <c r="AF41" s="31" t="inlineStr">
@@ -12461,37 +12555,37 @@
       </c>
       <c r="AO41" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP41" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AQ41" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AR41" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AS41" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AT41" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AU41" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AV41" s="24" t="n"/>
@@ -12509,7 +12603,7 @@
       </c>
       <c r="BA41" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BB41" s="24" t="inlineStr">
@@ -12524,7 +12618,7 @@
       </c>
       <c r="BD41" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BE41" s="24" t="inlineStr">
@@ -12544,7 +12638,7 @@
       </c>
       <c r="BH41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:51.837185Z</t>
+          <t>2026-08-02T13:07:37.759778Z</t>
         </is>
       </c>
       <c r="BI41" s="24" t="inlineStr">
@@ -12554,13 +12648,13 @@
       </c>
       <c r="BJ41" s="25" t="n"/>
       <c r="BK41" s="26" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="BL41" s="27" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BM41" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.409836</v>
       </c>
       <c r="BN41" s="28" t="n"/>
       <c r="BO41" s="28" t="n"/>
@@ -12590,26 +12684,27 @@
       <c r="CM41" s="24" t="n"/>
       <c r="CN41" s="24" t="n"/>
       <c r="CO41" s="24" t="n"/>
+      <c r="CP41" s="24" t="n"/>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>3460f0ab2ea84c55</t>
+          <t>9527d0019f6c4248</t>
         </is>
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T13:07:50.282319Z</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:15:00Z</t>
+          <t>2026-08-03T08:00:00Z</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>67577</t>
+          <t>68288</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
@@ -12619,12 +12714,12 @@
       </c>
       <c r="F42" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>CYBERSHOKE Prospects</t>
         </is>
       </c>
       <c r="G42" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>WW Team</t>
         </is>
       </c>
       <c r="H42" s="24" t="inlineStr">
@@ -12634,7 +12729,7 @@
       </c>
       <c r="I42" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J42" s="25" t="n"/>
@@ -12644,26 +12739,26 @@
         </is>
       </c>
       <c r="L42" s="26" t="n">
-        <v>-150</v>
+        <v>156</v>
       </c>
       <c r="M42" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.56</v>
       </c>
       <c r="N42" s="28" t="n">
-        <v>0.6</v>
+        <v>0.390625</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>0.526743</v>
+        <v>0.704636</v>
       </c>
       <c r="P42" s="28" t="n"/>
       <c r="Q42" s="28" t="n">
-        <v>-0.073257</v>
+        <v>0.314011</v>
       </c>
       <c r="R42" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S42" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T42" s="24" t="inlineStr">
         <is>
@@ -12686,7 +12781,7 @@
       <c r="AD42" s="24" t="n"/>
       <c r="AE42" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-cs2-ww-cshp-2026-08-03).</t>
         </is>
       </c>
       <c r="AF42" s="31" t="inlineStr">
@@ -12727,32 +12822,32 @@
       </c>
       <c r="AP42" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>CYBERSHOKE Prospects</t>
         </is>
       </c>
       <c r="AQ42" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>CYBERSHOKE Prospects</t>
         </is>
       </c>
       <c r="AR42" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>CYBERSHOKE Prospects</t>
         </is>
       </c>
       <c r="AS42" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>WW Team</t>
         </is>
       </c>
       <c r="AT42" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>WW Team</t>
         </is>
       </c>
       <c r="AU42" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>WW Team</t>
         </is>
       </c>
       <c r="AV42" s="24" t="n"/>
@@ -12770,7 +12865,7 @@
       </c>
       <c r="BA42" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BB42" s="24" t="inlineStr">
@@ -12785,7 +12880,7 @@
       </c>
       <c r="BD42" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BE42" s="24" t="inlineStr">
@@ -12805,7 +12900,7 @@
       </c>
       <c r="BH42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:52.331890Z</t>
+          <t>2026-08-02T13:07:39.841997Z</t>
         </is>
       </c>
       <c r="BI42" s="24" t="inlineStr">
@@ -12815,13 +12910,13 @@
       </c>
       <c r="BJ42" s="25" t="n"/>
       <c r="BK42" s="26" t="n">
-        <v>-150</v>
+        <v>156</v>
       </c>
       <c r="BL42" s="27" t="n">
-        <v>1.666667</v>
+        <v>2.56</v>
       </c>
       <c r="BM42" s="28" t="n">
-        <v>0.6</v>
+        <v>0.390625</v>
       </c>
       <c r="BN42" s="28" t="n"/>
       <c r="BO42" s="28" t="n"/>
@@ -12851,26 +12946,27 @@
       <c r="CM42" s="24" t="n"/>
       <c r="CN42" s="24" t="n"/>
       <c r="CO42" s="24" t="n"/>
+      <c r="CP42" s="24" t="n"/>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>d34bac6e45ff4a97</t>
+          <t>293daddbe23b43ea</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T13:07:50.282319Z</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:15:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>67576</t>
+          <t>67510</t>
         </is>
       </c>
       <c r="E43" s="24" t="inlineStr">
@@ -12880,12 +12976,12 @@
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="G43" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="H43" s="24" t="inlineStr">
@@ -12905,26 +13001,26 @@
         </is>
       </c>
       <c r="L43" s="26" t="n">
-        <v>156</v>
+        <v>-223</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>2.56</v>
+        <v>1.44843</v>
       </c>
       <c r="N43" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.690402</v>
       </c>
       <c r="O43" s="28" t="n">
-        <v>0.579539</v>
+        <v>0.563182</v>
       </c>
       <c r="P43" s="28" t="n"/>
       <c r="Q43" s="28" t="n">
-        <v>0.188914</v>
+        <v>-0.12722</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S43" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T43" s="24" t="inlineStr">
         <is>
@@ -12947,7 +13043,7 @@
       <c r="AD43" s="24" t="n"/>
       <c r="AE43" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
         </is>
       </c>
       <c r="AF43" s="31" t="inlineStr">
@@ -12983,37 +13079,37 @@
       </c>
       <c r="AO43" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP43" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AQ43" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AR43" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AS43" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AT43" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AU43" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AV43" s="24" t="n"/>
@@ -13031,7 +13127,7 @@
       </c>
       <c r="BA43" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BB43" s="24" t="inlineStr">
@@ -13046,7 +13142,7 @@
       </c>
       <c r="BD43" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BE43" s="24" t="inlineStr">
@@ -13066,7 +13162,7 @@
       </c>
       <c r="BH43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:52.846665Z</t>
+          <t>2026-08-02T13:07:40.888258Z</t>
         </is>
       </c>
       <c r="BI43" s="24" t="inlineStr">
@@ -13076,13 +13172,13 @@
       </c>
       <c r="BJ43" s="25" t="n"/>
       <c r="BK43" s="26" t="n">
-        <v>156</v>
+        <v>-223</v>
       </c>
       <c r="BL43" s="27" t="n">
-        <v>2.56</v>
+        <v>1.44843</v>
       </c>
       <c r="BM43" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.690402</v>
       </c>
       <c r="BN43" s="28" t="n"/>
       <c r="BO43" s="28" t="n"/>
@@ -13112,26 +13208,27 @@
       <c r="CM43" s="24" t="n"/>
       <c r="CN43" s="24" t="n"/>
       <c r="CO43" s="24" t="n"/>
+      <c r="CP43" s="24" t="n"/>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>deca0c777f084a7c</t>
+          <t>a5c27a9bba5846d9</t>
         </is>
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T13:07:50.282319Z</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T08:00:00Z</t>
+          <t>2026-08-03T11:00:00Z</t>
         </is>
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>67490</t>
+          <t>69135</t>
         </is>
       </c>
       <c r="E44" s="24" t="inlineStr">
@@ -13141,12 +13238,12 @@
       </c>
       <c r="F44" s="24" t="inlineStr">
         <is>
-          <t>VP.Prodigy</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="G44" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire Academy</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="H44" s="24" t="inlineStr">
@@ -13156,7 +13253,7 @@
       </c>
       <c r="I44" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J44" s="25" t="n"/>
@@ -13166,26 +13263,26 @@
         </is>
       </c>
       <c r="L44" s="26" t="n">
-        <v>-223</v>
+        <v>-170</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.588235</v>
       </c>
       <c r="N44" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.62963</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>0.646647</v>
+        <v>0.527215</v>
       </c>
       <c r="P44" s="28" t="n"/>
       <c r="Q44" s="28" t="n">
-        <v>-0.043755</v>
+        <v>-0.102415</v>
       </c>
       <c r="R44" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S44" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T44" s="24" t="inlineStr">
         <is>
@@ -13208,7 +13305,7 @@
       <c r="AD44" s="24" t="n"/>
       <c r="AE44" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-efa-vpp-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-1win-exruby-2026-08-03).</t>
         </is>
       </c>
       <c r="AF44" s="31" t="inlineStr">
@@ -13249,32 +13346,32 @@
       </c>
       <c r="AP44" s="24" t="inlineStr">
         <is>
-          <t>VP.Prodigy</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AQ44" s="24" t="inlineStr">
         <is>
-          <t>VP.Prodigy</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AR44" s="24" t="inlineStr">
         <is>
-          <t>VP.Prodigy</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AS44" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire Academy</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="AT44" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire Academy</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="AU44" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire Academy</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="AV44" s="24" t="n"/>
@@ -13292,7 +13389,7 @@
       </c>
       <c r="BA44" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BB44" s="24" t="inlineStr">
@@ -13307,7 +13404,7 @@
       </c>
       <c r="BD44" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BE44" s="24" t="inlineStr">
@@ -13327,7 +13424,7 @@
       </c>
       <c r="BH44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:53.863040Z</t>
+          <t>2026-08-02T13:07:43.369564Z</t>
         </is>
       </c>
       <c r="BI44" s="24" t="inlineStr">
@@ -13337,13 +13434,13 @@
       </c>
       <c r="BJ44" s="25" t="n"/>
       <c r="BK44" s="26" t="n">
-        <v>-223</v>
+        <v>-170</v>
       </c>
       <c r="BL44" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.588235</v>
       </c>
       <c r="BM44" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.62963</v>
       </c>
       <c r="BN44" s="28" t="n"/>
       <c r="BO44" s="28" t="n"/>
@@ -13373,26 +13470,27 @@
       <c r="CM44" s="24" t="n"/>
       <c r="CN44" s="24" t="n"/>
       <c r="CO44" s="24" t="n"/>
+      <c r="CP44" s="24" t="n"/>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>9bba252f704c4c22</t>
+          <t>0c1d277a9d214da8</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T13:07:50.282319Z</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-03T11:00:00Z</t>
         </is>
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>67510</t>
+          <t>67578</t>
         </is>
       </c>
       <c r="E45" s="24" t="inlineStr">
@@ -13402,12 +13500,12 @@
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="G45" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="H45" s="24" t="inlineStr">
@@ -13427,23 +13525,23 @@
         </is>
       </c>
       <c r="L45" s="26" t="n">
-        <v>-223</v>
+        <v>-122</v>
       </c>
       <c r="M45" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.819672</v>
       </c>
       <c r="N45" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.54955</v>
       </c>
       <c r="O45" s="28" t="n">
-        <v>0.563104</v>
+        <v>0.526957</v>
       </c>
       <c r="P45" s="28" t="n"/>
       <c r="Q45" s="28" t="n">
-        <v>-0.127298</v>
+        <v>-0.022593</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S45" s="29" t="n">
         <v>1</v>
@@ -13469,7 +13567,7 @@
       <c r="AD45" s="24" t="n"/>
       <c r="AE45" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
         </is>
       </c>
       <c r="AF45" s="31" t="inlineStr">
@@ -13505,37 +13603,37 @@
       </c>
       <c r="AO45" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP45" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AQ45" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AR45" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AS45" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AT45" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AU45" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AV45" s="24" t="n"/>
@@ -13553,7 +13651,7 @@
       </c>
       <c r="BA45" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BB45" s="24" t="inlineStr">
@@ -13568,7 +13666,7 @@
       </c>
       <c r="BD45" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BE45" s="24" t="inlineStr">
@@ -13588,7 +13686,7 @@
       </c>
       <c r="BH45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:55.692466Z</t>
+          <t>2026-08-02T13:07:43.897046Z</t>
         </is>
       </c>
       <c r="BI45" s="24" t="inlineStr">
@@ -13598,13 +13696,13 @@
       </c>
       <c r="BJ45" s="25" t="n"/>
       <c r="BK45" s="26" t="n">
-        <v>-223</v>
+        <v>-122</v>
       </c>
       <c r="BL45" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.819672</v>
       </c>
       <c r="BM45" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.54955</v>
       </c>
       <c r="BN45" s="28" t="n"/>
       <c r="BO45" s="28" t="n"/>
@@ -13634,26 +13732,27 @@
       <c r="CM45" s="24" t="n"/>
       <c r="CN45" s="24" t="n"/>
       <c r="CO45" s="24" t="n"/>
+      <c r="CP45" s="24" t="n"/>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>50cdc781309648ec</t>
+          <t>28f61e71bb5c4b2e</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T13:07:50.282319Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:30:00Z</t>
+          <t>2026-08-03T13:45:00Z</t>
         </is>
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>67514</t>
+          <t>67579</t>
         </is>
       </c>
       <c r="E46" s="24" t="inlineStr">
@@ -13663,12 +13762,12 @@
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
-          <t>Passion Academy</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="G46" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="H46" s="24" t="inlineStr">
@@ -13678,7 +13777,7 @@
       </c>
       <c r="I46" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J46" s="25" t="n"/>
@@ -13688,26 +13787,26 @@
         </is>
       </c>
       <c r="L46" s="26" t="n">
-        <v>-122</v>
+        <v>203</v>
       </c>
       <c r="M46" s="27" t="n">
-        <v>1.819672</v>
+        <v>3.03</v>
       </c>
       <c r="N46" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.330033</v>
       </c>
       <c r="O46" s="28" t="n">
-        <v>0.640228</v>
+        <v>0.5263640000000001</v>
       </c>
       <c r="P46" s="28" t="n"/>
       <c r="Q46" s="28" t="n">
-        <v>0.09067799999999999</v>
+        <v>0.196331</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="S46" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T46" s="24" t="inlineStr">
         <is>
@@ -13730,7 +13829,7 @@
       <c r="AD46" s="24" t="n"/>
       <c r="AE46" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
         </is>
       </c>
       <c r="AF46" s="31" t="inlineStr">
@@ -13748,7 +13847,7 @@
       <c r="AJ46" s="31" t="n"/>
       <c r="AK46" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL46" s="26" t="n">
@@ -13756,47 +13855,47 @@
       </c>
       <c r="AM46" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN46" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO46" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP46" s="24" t="inlineStr">
         <is>
-          <t>Passion Academy</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AQ46" s="24" t="inlineStr">
         <is>
-          <t>Passion Academy</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AR46" s="24" t="inlineStr">
         <is>
-          <t>Passion Academy</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AS46" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AT46" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AU46" s="24" t="inlineStr">
         <is>
-          <t>EAC Rising</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AV46" s="24" t="n"/>
@@ -13814,7 +13913,7 @@
       </c>
       <c r="BA46" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BB46" s="24" t="inlineStr">
@@ -13829,7 +13928,7 @@
       </c>
       <c r="BD46" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BE46" s="24" t="inlineStr">
@@ -13849,7 +13948,7 @@
       </c>
       <c r="BH46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:57.251438Z</t>
+          <t>2026-08-02T13:07:44.969369Z</t>
         </is>
       </c>
       <c r="BI46" s="24" t="inlineStr">
@@ -13859,13 +13958,13 @@
       </c>
       <c r="BJ46" s="25" t="n"/>
       <c r="BK46" s="26" t="n">
-        <v>-122</v>
+        <v>203</v>
       </c>
       <c r="BL46" s="27" t="n">
-        <v>1.819672</v>
+        <v>3.03</v>
       </c>
       <c r="BM46" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.330033</v>
       </c>
       <c r="BN46" s="28" t="n"/>
       <c r="BO46" s="28" t="n"/>
@@ -13895,26 +13994,27 @@
       <c r="CM46" s="24" t="n"/>
       <c r="CN46" s="24" t="n"/>
       <c r="CO46" s="24" t="n"/>
+      <c r="CP46" s="24" t="n"/>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>d5bc9a8496d6494a</t>
+          <t>d60c391c21d847b7</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T13:07:50.282319Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T11:00:00Z</t>
+          <t>2026-08-03T14:00:00Z</t>
         </is>
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>67578</t>
+          <t>68292</t>
         </is>
       </c>
       <c r="E47" s="24" t="inlineStr">
@@ -13924,12 +14024,12 @@
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>ARCRED</t>
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr">
@@ -13949,26 +14049,26 @@
         </is>
       </c>
       <c r="L47" s="26" t="n">
-        <v>-122</v>
+        <v>-186</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.537634</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.65035</v>
       </c>
       <c r="O47" s="28" t="n">
-        <v>0.526743</v>
+        <v>0.613928</v>
       </c>
       <c r="P47" s="28" t="n"/>
       <c r="Q47" s="28" t="n">
-        <v>-0.022807</v>
+        <v>-0.036422</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="S47" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T47" s="24" t="inlineStr">
         <is>
@@ -13991,7 +14091,7 @@
       <c r="AD47" s="24" t="n"/>
       <c r="AE47" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-cs2-arc-btf-2026-08-03).</t>
         </is>
       </c>
       <c r="AF47" s="31" t="inlineStr">
@@ -14027,37 +14127,37 @@
       </c>
       <c r="AO47" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP47" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AQ47" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AR47" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AS47" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>ARCRED</t>
         </is>
       </c>
       <c r="AT47" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>ARCRED</t>
         </is>
       </c>
       <c r="AU47" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>ARCRED</t>
         </is>
       </c>
       <c r="AV47" s="24" t="n"/>
@@ -14075,7 +14175,7 @@
       </c>
       <c r="BA47" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BB47" s="24" t="inlineStr">
@@ -14090,7 +14190,7 @@
       </c>
       <c r="BD47" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BE47" s="24" t="inlineStr">
@@ -14110,7 +14210,7 @@
       </c>
       <c r="BH47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:57.770498Z</t>
+          <t>2026-08-02T13:07:46.045093Z</t>
         </is>
       </c>
       <c r="BI47" s="24" t="inlineStr">
@@ -14120,13 +14220,13 @@
       </c>
       <c r="BJ47" s="25" t="n"/>
       <c r="BK47" s="26" t="n">
-        <v>-122</v>
+        <v>-186</v>
       </c>
       <c r="BL47" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.537634</v>
       </c>
       <c r="BM47" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.65035</v>
       </c>
       <c r="BN47" s="28" t="n"/>
       <c r="BO47" s="28" t="n"/>
@@ -14156,26 +14256,27 @@
       <c r="CM47" s="24" t="n"/>
       <c r="CN47" s="24" t="n"/>
       <c r="CO47" s="24" t="n"/>
+      <c r="CP47" s="24" t="n"/>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>0f4a18b629c841c0</t>
+          <t>8d2f4d4fb47640e6</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
+          <t>2026-08-02T13:07:50.282319Z</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T13:45:00Z</t>
+          <t>2026-08-03T23:00:00Z</t>
         </is>
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>67579</t>
+          <t>68043</t>
         </is>
       </c>
       <c r="E48" s="24" t="inlineStr">
@@ -14185,12 +14286,12 @@
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="H48" s="24" t="inlineStr">
@@ -14200,7 +14301,7 @@
       </c>
       <c r="I48" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J48" s="25" t="n"/>
@@ -14210,26 +14311,26 @@
         </is>
       </c>
       <c r="L48" s="26" t="n">
-        <v>203</v>
+        <v>113</v>
       </c>
       <c r="M48" s="27" t="n">
-        <v>3.03</v>
+        <v>2.13</v>
       </c>
       <c r="N48" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.469484</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>0.526658</v>
+        <v>0.569723</v>
       </c>
       <c r="P48" s="28" t="n"/>
       <c r="Q48" s="28" t="n">
-        <v>0.196625</v>
+        <v>0.100239</v>
       </c>
       <c r="R48" s="26" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="S48" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T48" s="24" t="inlineStr">
         <is>
@@ -14252,7 +14353,7 @@
       <c r="AD48" s="24" t="n"/>
       <c r="AE48" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
         </is>
       </c>
       <c r="AF48" s="31" t="inlineStr">
@@ -14293,32 +14394,32 @@
       </c>
       <c r="AP48" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="AQ48" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="AR48" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="AS48" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="AT48" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="AU48" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="AV48" s="24" t="n"/>
@@ -14336,7 +14437,7 @@
       </c>
       <c r="BA48" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BB48" s="24" t="inlineStr">
@@ -14351,7 +14452,7 @@
       </c>
       <c r="BD48" s="24" t="inlineStr">
         <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
+          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
         </is>
       </c>
       <c r="BE48" s="24" t="inlineStr">
@@ -14371,7 +14472,7 @@
       </c>
       <c r="BH48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T09:59:59.263922Z</t>
+          <t>2026-08-02T13:07:50.279981Z</t>
         </is>
       </c>
       <c r="BI48" s="24" t="inlineStr">
@@ -14381,13 +14482,13 @@
       </c>
       <c r="BJ48" s="25" t="n"/>
       <c r="BK48" s="26" t="n">
-        <v>203</v>
+        <v>113</v>
       </c>
       <c r="BL48" s="27" t="n">
-        <v>3.03</v>
+        <v>2.13</v>
       </c>
       <c r="BM48" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.469484</v>
       </c>
       <c r="BN48" s="28" t="n"/>
       <c r="BO48" s="28" t="n"/>
@@ -14417,267 +14518,7 @@
       <c r="CM48" s="24" t="n"/>
       <c r="CN48" s="24" t="n"/>
       <c r="CO48" s="24" t="n"/>
-    </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="A49" s="24" t="inlineStr">
-        <is>
-          <t>c821c1721eda4a68</t>
-        </is>
-      </c>
-      <c r="B49" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T10:00:04.561525Z</t>
-        </is>
-      </c>
-      <c r="C49" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T23:00:00Z</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="inlineStr">
-        <is>
-          <t>68043</t>
-        </is>
-      </c>
-      <c r="E49" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F49" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="G49" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="H49" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I49" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J49" s="25" t="n"/>
-      <c r="K49" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L49" s="26" t="n">
-        <v>113</v>
-      </c>
-      <c r="M49" s="27" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="N49" s="28" t="n">
-        <v>0.469484</v>
-      </c>
-      <c r="O49" s="28" t="n">
-        <v>0.569576</v>
-      </c>
-      <c r="P49" s="28" t="n"/>
-      <c r="Q49" s="28" t="n">
-        <v>0.100092</v>
-      </c>
-      <c r="R49" s="26" t="n">
-        <v>70</v>
-      </c>
-      <c r="S49" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T49" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U49" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V49" s="24" t="n"/>
-      <c r="W49" s="26" t="n"/>
-      <c r="X49" s="26" t="n"/>
-      <c r="Y49" s="25" t="n"/>
-      <c r="Z49" s="26" t="n"/>
-      <c r="AA49" s="28" t="n"/>
-      <c r="AB49" s="28" t="n"/>
-      <c r="AC49" s="30" t="n"/>
-      <c r="AD49" s="24" t="n"/>
-      <c r="AE49" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF49" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG49" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH49" s="24" t="n"/>
-      <c r="AI49" s="31" t="n"/>
-      <c r="AJ49" s="31" t="n"/>
-      <c r="AK49" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL49" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM49" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN49" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO49" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP49" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AQ49" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AR49" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AS49" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="AT49" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="AU49" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="AV49" s="24" t="n"/>
-      <c r="AW49" s="24" t="n"/>
-      <c r="AX49" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY49" s="24" t="n"/>
-      <c r="AZ49" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA49" s="24" t="inlineStr">
-        <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
-        </is>
-      </c>
-      <c r="BB49" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC49" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD49" s="24" t="inlineStr">
-        <is>
-          <t>06138ffc8334cb69044b84c6e2b37aa9a4e0b6bd4f08ef7c62950d9e210f4364</t>
-        </is>
-      </c>
-      <c r="BE49" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF49" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG49" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH49" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T10:00:04.559918Z</t>
-        </is>
-      </c>
-      <c r="BI49" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ49" s="25" t="n"/>
-      <c r="BK49" s="26" t="n">
-        <v>113</v>
-      </c>
-      <c r="BL49" s="27" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BM49" s="28" t="n">
-        <v>0.469484</v>
-      </c>
-      <c r="BN49" s="28" t="n"/>
-      <c r="BO49" s="28" t="n"/>
-      <c r="BP49" s="25" t="n"/>
-      <c r="BQ49" s="27" t="n"/>
-      <c r="BR49" s="28" t="n"/>
-      <c r="BS49" s="28" t="n"/>
-      <c r="BT49" s="28" t="n"/>
-      <c r="BU49" s="25" t="n"/>
-      <c r="BV49" s="29" t="n"/>
-      <c r="BW49" s="24" t="n"/>
-      <c r="BX49" s="30" t="n"/>
-      <c r="BY49" s="27" t="n"/>
-      <c r="BZ49" s="24" t="n"/>
-      <c r="CA49" s="31" t="n"/>
-      <c r="CB49" s="24" t="n"/>
-      <c r="CC49" s="24" t="n"/>
-      <c r="CD49" s="24" t="n"/>
-      <c r="CE49" s="24" t="n"/>
-      <c r="CF49" s="24" t="n"/>
-      <c r="CG49" s="24" t="n"/>
-      <c r="CH49" s="24" t="n"/>
-      <c r="CI49" s="24" t="n"/>
-      <c r="CJ49" s="24" t="n"/>
-      <c r="CK49" s="24" t="n"/>
-      <c r="CL49" s="24" t="n"/>
-      <c r="CM49" s="24" t="n"/>
-      <c r="CN49" s="24" t="n"/>
-      <c r="CO49" s="24" t="n"/>
+      <c r="CP48" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP48" headerRowCount="1">
-  <autoFilter ref="A1:CP48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP53" headerRowCount="1">
+  <autoFilter ref="A1:CP53"/>
   <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -753,19 +753,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$48)</f>
+        <f>COUNTA('Picks'!$A$2:$A$53)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$48,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$53,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$48,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$53,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")+COUNTIFS('Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")+COUNTIFS('Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -793,19 +793,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$48,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$53,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")/(COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"win")+COUNTIFS('Picks'!$BX$2:$BX$48,"&gt;0",'Picks'!$V$2:$V$48,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"win")/(COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"win")+COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$48)/SUM('Picks'!$BX$2:$BX$48),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$53)/SUM('Picks'!$BX$2:$BX$53),0)</f>
         <v/>
       </c>
     </row>
@@ -833,19 +833,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$48)</f>
+        <f>SUM('Picks'!$BY$2:$BY$53)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$48,"&lt;&gt;",'Picks'!$AB$2:$AB$48),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$53,"&lt;&gt;",'Picks'!$AB$2:$AB$53),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$48,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$48,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$53,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$53,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$48,'Picks'!$AM$2:$AM$48,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$53,'Picks'!$AM$2:$AM$53,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -900,15 +900,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -916,11 +916,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$53,'Picks'!$H$2:$H$53,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A14,'Picks'!$U$2:$U$48,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$53,'Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -931,15 +931,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -947,11 +947,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$53,'Picks'!$H$2:$H$53,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A15,'Picks'!$U$2:$U$48,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$53,'Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -962,15 +962,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled",'Picks'!$V$2:$V$48,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -978,11 +978,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$48,'Picks'!$H$2:$H$48,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$53,'Picks'!$H$2:$H$53,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$48,'Picks'!$H$2:$H$48,$A16,'Picks'!$U$2:$U$48,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$53,'Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP48"/>
+  <dimension ref="A1:CP53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9337,18 +9337,28 @@
       </c>
       <c r="U29" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V29" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W29" s="26" t="n"/>
       <c r="X29" s="26" t="n"/>
       <c r="Y29" s="25" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n"/>
-      <c r="AD29" s="24" t="n"/>
+      <c r="AC29" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:52:44.718315Z</t>
+        </is>
+      </c>
       <c r="AE29" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-ttbs-sng-2026-08-02).</t>
@@ -9497,7 +9507,11 @@
       <c r="BT29" s="28" t="n"/>
       <c r="BU29" s="25" t="n"/>
       <c r="BV29" s="29" t="n"/>
-      <c r="BW29" s="24" t="n"/>
+      <c r="BW29" s="24" t="inlineStr">
+        <is>
+          <t>esports market settled to a non-binary price (forfeit/postponement per market rules)</t>
+        </is>
+      </c>
       <c r="BX29" s="30" t="n"/>
       <c r="BY29" s="27" t="n"/>
       <c r="BZ29" s="24" t="n"/>
@@ -9885,18 +9899,38 @@
       </c>
       <c r="U31" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V31" s="24" t="n"/>
-      <c r="W31" s="26" t="n"/>
-      <c r="X31" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X31" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y31" s="25" t="n"/>
-      <c r="Z31" s="26" t="n"/>
-      <c r="AA31" s="28" t="n"/>
-      <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="30" t="n"/>
-      <c r="AD31" s="24" t="n"/>
+      <c r="Z31" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="AA31" s="28" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AB31" s="28" t="n">
+        <v>-0.000511</v>
+      </c>
+      <c r="AC31" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:52:46.144484Z</t>
+        </is>
+      </c>
       <c r="AE31" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-ica-exmana-2026-08-02).</t>
@@ -9909,7 +9943,7 @@
       </c>
       <c r="AG31" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH31" s="24" t="n"/>
@@ -10039,8 +10073,12 @@
       <c r="BN31" s="28" t="n"/>
       <c r="BO31" s="28" t="n"/>
       <c r="BP31" s="25" t="n"/>
-      <c r="BQ31" s="27" t="n"/>
-      <c r="BR31" s="28" t="n"/>
+      <c r="BQ31" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BR31" s="28" t="n">
+        <v>0.68</v>
+      </c>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
       <c r="BU31" s="25" t="n"/>
@@ -10147,18 +10185,38 @@
       </c>
       <c r="U32" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V32" s="24" t="n"/>
-      <c r="W32" s="26" t="n"/>
-      <c r="X32" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y32" s="25" t="n"/>
-      <c r="Z32" s="26" t="n"/>
-      <c r="AA32" s="28" t="n"/>
-      <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="30" t="n"/>
-      <c r="AD32" s="24" t="n"/>
+      <c r="Z32" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="AA32" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB32" s="28" t="n">
+        <v>-0.000402</v>
+      </c>
+      <c r="AC32" s="30" t="n">
+        <v>0.6726</v>
+      </c>
+      <c r="AD32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:52:47.515855Z</t>
+        </is>
+      </c>
       <c r="AE32" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-lk-nvo-2026-08-02).</t>
@@ -10301,8 +10359,12 @@
       <c r="BN32" s="28" t="n"/>
       <c r="BO32" s="28" t="n"/>
       <c r="BP32" s="25" t="n"/>
-      <c r="BQ32" s="27" t="n"/>
-      <c r="BR32" s="28" t="n"/>
+      <c r="BQ32" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BR32" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="BS32" s="28" t="n"/>
       <c r="BT32" s="28" t="n"/>
       <c r="BU32" s="25" t="n"/>
@@ -10671,18 +10733,38 @@
       </c>
       <c r="U34" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V34" s="24" t="n"/>
-      <c r="W34" s="26" t="n"/>
-      <c r="X34" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y34" s="25" t="n"/>
-      <c r="Z34" s="26" t="n"/>
-      <c r="AA34" s="28" t="n"/>
-      <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="30" t="n"/>
-      <c r="AD34" s="24" t="n"/>
+      <c r="Z34" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="AA34" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AB34" s="28" t="n">
+        <v>-0.000168</v>
+      </c>
+      <c r="AC34" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:52:49.918955Z</t>
+        </is>
+      </c>
       <c r="AE34" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-leo-vexar-2026-08-02).</t>
@@ -10695,7 +10777,7 @@
       </c>
       <c r="AG34" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH34" s="24" t="n"/>
@@ -10825,8 +10907,12 @@
       <c r="BN34" s="28" t="n"/>
       <c r="BO34" s="28" t="n"/>
       <c r="BP34" s="25" t="n"/>
-      <c r="BQ34" s="27" t="n"/>
-      <c r="BR34" s="28" t="n"/>
+      <c r="BQ34" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BR34" s="28" t="n">
+        <v>0.42</v>
+      </c>
       <c r="BS34" s="28" t="n"/>
       <c r="BT34" s="28" t="n"/>
       <c r="BU34" s="25" t="n"/>
@@ -11195,18 +11281,38 @@
       </c>
       <c r="U36" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V36" s="24" t="n"/>
-      <c r="W36" s="26" t="n"/>
-      <c r="X36" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X36" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y36" s="25" t="n"/>
-      <c r="Z36" s="26" t="n"/>
-      <c r="AA36" s="28" t="n"/>
-      <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="30" t="n"/>
-      <c r="AD36" s="24" t="n"/>
+      <c r="Z36" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="AA36" s="28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB36" s="28" t="n">
+        <v>0.000168</v>
+      </c>
+      <c r="AC36" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:52:52.334786Z</t>
+        </is>
+      </c>
       <c r="AE36" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-bmb-ff-2026-08-02).</t>
@@ -11219,7 +11325,7 @@
       </c>
       <c r="AG36" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH36" s="24" t="n"/>
@@ -11349,8 +11455,12 @@
       <c r="BN36" s="28" t="n"/>
       <c r="BO36" s="28" t="n"/>
       <c r="BP36" s="25" t="n"/>
-      <c r="BQ36" s="27" t="n"/>
-      <c r="BR36" s="28" t="n"/>
+      <c r="BQ36" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BR36" s="28" t="n">
+        <v>0.58</v>
+      </c>
       <c r="BS36" s="28" t="n"/>
       <c r="BT36" s="28" t="n"/>
       <c r="BU36" s="25" t="n"/>
@@ -11457,18 +11567,38 @@
       </c>
       <c r="U37" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V37" s="24" t="n"/>
-      <c r="W37" s="26" t="n"/>
-      <c r="X37" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W37" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X37" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y37" s="25" t="n"/>
-      <c r="Z37" s="26" t="n"/>
-      <c r="AA37" s="28" t="n"/>
-      <c r="AB37" s="28" t="n"/>
-      <c r="AC37" s="30" t="n"/>
-      <c r="AD37" s="24" t="n"/>
+      <c r="Z37" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="AA37" s="28" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AB37" s="28" t="n">
+        <v>-0.000164</v>
+      </c>
+      <c r="AC37" s="30" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="AD37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:52:53.615878Z</t>
+        </is>
+      </c>
       <c r="AE37" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-mouzn-wba-2026-08-02).</t>
@@ -11611,8 +11741,12 @@
       <c r="BN37" s="28" t="n"/>
       <c r="BO37" s="28" t="n"/>
       <c r="BP37" s="25" t="n"/>
-      <c r="BQ37" s="27" t="n"/>
-      <c r="BR37" s="28" t="n"/>
+      <c r="BQ37" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BR37" s="28" t="n">
+        <v>0.59</v>
+      </c>
       <c r="BS37" s="28" t="n"/>
       <c r="BT37" s="28" t="n"/>
       <c r="BU37" s="25" t="n"/>
@@ -11641,12 +11775,12 @@
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>70c73fb4130e4b04</t>
+          <t>ff4c023688d14058</t>
         </is>
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:50.282319Z</t>
+          <t>2026-08-02T15:51:41.323824Z</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
@@ -11656,7 +11790,7 @@
       </c>
       <c r="D38" s="24" t="inlineStr">
         <is>
-          <t>69263</t>
+          <t>69680</t>
         </is>
       </c>
       <c r="E38" s="24" t="inlineStr">
@@ -11666,12 +11800,12 @@
       </c>
       <c r="F38" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="G38" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="H38" s="24" t="inlineStr">
@@ -11691,23 +11825,23 @@
         </is>
       </c>
       <c r="L38" s="26" t="n">
-        <v>-170</v>
+        <v>-156</v>
       </c>
       <c r="M38" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.641026</v>
       </c>
       <c r="N38" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.609375</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>0.6659040000000001</v>
+        <v>0.653037</v>
       </c>
       <c r="P38" s="28" t="n"/>
       <c r="Q38" s="28" t="n">
-        <v>0.036274</v>
+        <v>0.043662</v>
       </c>
       <c r="R38" s="26" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="S38" s="29" t="n">
         <v>1.75</v>
@@ -11733,7 +11867,7 @@
       <c r="AD38" s="24" t="n"/>
       <c r="AE38" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-for-lk-2026-08-02).</t>
         </is>
       </c>
       <c r="AF38" s="31" t="inlineStr">
@@ -11774,32 +11908,32 @@
       </c>
       <c r="AP38" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AQ38" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AR38" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AS38" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AT38" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AU38" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AV38" s="24" t="n"/>
@@ -11817,7 +11951,7 @@
       </c>
       <c r="BA38" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BB38" s="24" t="inlineStr">
@@ -11832,7 +11966,7 @@
       </c>
       <c r="BD38" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BE38" s="24" t="inlineStr">
@@ -11852,7 +11986,7 @@
       </c>
       <c r="BH38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:36.093507Z</t>
+          <t>2026-08-02T15:51:25.435587Z</t>
         </is>
       </c>
       <c r="BI38" s="24" t="inlineStr">
@@ -11862,13 +11996,13 @@
       </c>
       <c r="BJ38" s="25" t="n"/>
       <c r="BK38" s="26" t="n">
-        <v>-170</v>
+        <v>-156</v>
       </c>
       <c r="BL38" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.641026</v>
       </c>
       <c r="BM38" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.609375</v>
       </c>
       <c r="BN38" s="28" t="n"/>
       <c r="BO38" s="28" t="n"/>
@@ -11898,27 +12032,31 @@
       <c r="CM38" s="24" t="n"/>
       <c r="CN38" s="24" t="n"/>
       <c r="CO38" s="24" t="n"/>
-      <c r="CP38" s="24" t="n"/>
+      <c r="CP38" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>d7c4b733118b4e5d</t>
+          <t>add1d14a4c2b420d</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:50.282319Z</t>
+          <t>2026-08-02T15:51:41.323824Z</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:00:00Z</t>
+          <t>2026-08-02T17:00:00Z</t>
         </is>
       </c>
       <c r="D39" s="24" t="inlineStr">
         <is>
-          <t>69289</t>
+          <t>69681</t>
         </is>
       </c>
       <c r="E39" s="24" t="inlineStr">
@@ -11928,12 +12066,12 @@
       </c>
       <c r="F39" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="G39" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="H39" s="24" t="inlineStr">
@@ -11943,7 +12081,7 @@
       </c>
       <c r="I39" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J39" s="25" t="n"/>
@@ -11953,26 +12091,26 @@
         </is>
       </c>
       <c r="L39" s="26" t="n">
-        <v>144</v>
+        <v>-203</v>
       </c>
       <c r="M39" s="27" t="n">
-        <v>2.44</v>
+        <v>1.492611</v>
       </c>
       <c r="N39" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.669967</v>
       </c>
       <c r="O39" s="28" t="n">
-        <v>0.510804</v>
+        <v>0.616374</v>
       </c>
       <c r="P39" s="28" t="n"/>
       <c r="Q39" s="28" t="n">
-        <v>0.100968</v>
+        <v>-0.053593</v>
       </c>
       <c r="R39" s="26" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="S39" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T39" s="24" t="inlineStr">
         <is>
@@ -11995,7 +12133,7 @@
       <c r="AD39" s="24" t="n"/>
       <c r="AE39" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-cs2-shin-bst-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-mta-bmb-2026-08-02).</t>
         </is>
       </c>
       <c r="AF39" s="31" t="inlineStr">
@@ -12036,32 +12174,32 @@
       </c>
       <c r="AP39" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AQ39" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AR39" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AS39" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AT39" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AU39" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AV39" s="24" t="n"/>
@@ -12079,7 +12217,7 @@
       </c>
       <c r="BA39" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BB39" s="24" t="inlineStr">
@@ -12094,7 +12232,7 @@
       </c>
       <c r="BD39" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BE39" s="24" t="inlineStr">
@@ -12114,7 +12252,7 @@
       </c>
       <c r="BH39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:36.582090Z</t>
+          <t>2026-08-02T15:51:25.920075Z</t>
         </is>
       </c>
       <c r="BI39" s="24" t="inlineStr">
@@ -12124,13 +12262,13 @@
       </c>
       <c r="BJ39" s="25" t="n"/>
       <c r="BK39" s="26" t="n">
-        <v>144</v>
+        <v>-203</v>
       </c>
       <c r="BL39" s="27" t="n">
-        <v>2.44</v>
+        <v>1.492611</v>
       </c>
       <c r="BM39" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.669967</v>
       </c>
       <c r="BN39" s="28" t="n"/>
       <c r="BO39" s="28" t="n"/>
@@ -12160,27 +12298,31 @@
       <c r="CM39" s="24" t="n"/>
       <c r="CN39" s="24" t="n"/>
       <c r="CO39" s="24" t="n"/>
-      <c r="CP39" s="24" t="n"/>
+      <c r="CP39" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>f93d38b9d6484fa0</t>
+          <t>a975d9cc6cd1438a</t>
         </is>
       </c>
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:50.282319Z</t>
+          <t>2026-08-02T15:51:41.323824Z</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:15:00Z</t>
+          <t>2026-08-02T17:00:00Z</t>
         </is>
       </c>
       <c r="D40" s="24" t="inlineStr">
         <is>
-          <t>67577</t>
+          <t>69682</t>
         </is>
       </c>
       <c r="E40" s="24" t="inlineStr">
@@ -12190,12 +12332,12 @@
       </c>
       <c r="F40" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="G40" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="H40" s="24" t="inlineStr">
@@ -12215,26 +12357,26 @@
         </is>
       </c>
       <c r="L40" s="26" t="n">
-        <v>-150</v>
+        <v>-170</v>
       </c>
       <c r="M40" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.588235</v>
       </c>
       <c r="N40" s="28" t="n">
-        <v>0.6</v>
+        <v>0.62963</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>0.526957</v>
+        <v>0.684497</v>
       </c>
       <c r="P40" s="28" t="n"/>
       <c r="Q40" s="28" t="n">
-        <v>-0.073043</v>
+        <v>0.054867</v>
       </c>
       <c r="R40" s="26" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="S40" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T40" s="24" t="inlineStr">
         <is>
@@ -12257,7 +12399,7 @@
       <c r="AD40" s="24" t="n"/>
       <c r="AE40" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-bw-ff-2026-08-02).</t>
         </is>
       </c>
       <c r="AF40" s="31" t="inlineStr">
@@ -12298,32 +12440,32 @@
       </c>
       <c r="AP40" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="AQ40" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="AR40" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="AS40" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="AT40" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="AU40" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="AV40" s="24" t="n"/>
@@ -12341,7 +12483,7 @@
       </c>
       <c r="BA40" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BB40" s="24" t="inlineStr">
@@ -12356,7 +12498,7 @@
       </c>
       <c r="BD40" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BE40" s="24" t="inlineStr">
@@ -12376,7 +12518,7 @@
       </c>
       <c r="BH40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:37.163209Z</t>
+          <t>2026-08-02T15:51:26.448910Z</t>
         </is>
       </c>
       <c r="BI40" s="24" t="inlineStr">
@@ -12386,13 +12528,13 @@
       </c>
       <c r="BJ40" s="25" t="n"/>
       <c r="BK40" s="26" t="n">
-        <v>-150</v>
+        <v>-170</v>
       </c>
       <c r="BL40" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.588235</v>
       </c>
       <c r="BM40" s="28" t="n">
-        <v>0.6</v>
+        <v>0.62963</v>
       </c>
       <c r="BN40" s="28" t="n"/>
       <c r="BO40" s="28" t="n"/>
@@ -12422,27 +12564,31 @@
       <c r="CM40" s="24" t="n"/>
       <c r="CN40" s="24" t="n"/>
       <c r="CO40" s="24" t="n"/>
-      <c r="CP40" s="24" t="n"/>
+      <c r="CP40" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>52e4ee83bf634645</t>
+          <t>b1eff2d834ee4531</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:50.282319Z</t>
+          <t>2026-08-02T15:51:41.323824Z</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:15:00Z</t>
+          <t>2026-08-02T18:00:00Z</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>67576</t>
+          <t>69289</t>
         </is>
       </c>
       <c r="E41" s="24" t="inlineStr">
@@ -12452,12 +12598,12 @@
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="G41" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="H41" s="24" t="inlineStr">
@@ -12477,26 +12623,26 @@
         </is>
       </c>
       <c r="L41" s="26" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="M41" s="27" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="N41" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.420168</v>
       </c>
       <c r="O41" s="28" t="n">
-        <v>0.57967</v>
+        <v>0.51088</v>
       </c>
       <c r="P41" s="28" t="n"/>
       <c r="Q41" s="28" t="n">
-        <v>0.169834</v>
+        <v>0.090712</v>
       </c>
       <c r="R41" s="26" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="S41" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T41" s="24" t="inlineStr">
         <is>
@@ -12519,7 +12665,7 @@
       <c r="AD41" s="24" t="n"/>
       <c r="AE41" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-shin-bst-2026-08-02).</t>
         </is>
       </c>
       <c r="AF41" s="31" t="inlineStr">
@@ -12555,37 +12701,37 @@
       </c>
       <c r="AO41" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP41" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AQ41" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AR41" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AS41" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="AT41" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="AU41" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="AV41" s="24" t="n"/>
@@ -12603,7 +12749,7 @@
       </c>
       <c r="BA41" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BB41" s="24" t="inlineStr">
@@ -12618,7 +12764,7 @@
       </c>
       <c r="BD41" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BE41" s="24" t="inlineStr">
@@ -12638,7 +12784,7 @@
       </c>
       <c r="BH41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:37.759778Z</t>
+          <t>2026-08-02T15:51:27.457693Z</t>
         </is>
       </c>
       <c r="BI41" s="24" t="inlineStr">
@@ -12648,13 +12794,13 @@
       </c>
       <c r="BJ41" s="25" t="n"/>
       <c r="BK41" s="26" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="BL41" s="27" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="BM41" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.420168</v>
       </c>
       <c r="BN41" s="28" t="n"/>
       <c r="BO41" s="28" t="n"/>
@@ -12684,27 +12830,31 @@
       <c r="CM41" s="24" t="n"/>
       <c r="CN41" s="24" t="n"/>
       <c r="CO41" s="24" t="n"/>
-      <c r="CP41" s="24" t="n"/>
+      <c r="CP41" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>9527d0019f6c4248</t>
+          <t>4cc088e9a58a432c</t>
         </is>
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:50.282319Z</t>
+          <t>2026-08-02T15:51:41.323824Z</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T08:00:00Z</t>
+          <t>2026-08-02T19:15:00Z</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>68288</t>
+          <t>67576</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
@@ -12714,12 +12864,12 @@
       </c>
       <c r="F42" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="G42" s="24" t="inlineStr">
         <is>
-          <t>WW Team</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="H42" s="24" t="inlineStr">
@@ -12729,7 +12879,7 @@
       </c>
       <c r="I42" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J42" s="25" t="n"/>
@@ -12739,26 +12889,26 @@
         </is>
       </c>
       <c r="L42" s="26" t="n">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="M42" s="27" t="n">
-        <v>2.56</v>
+        <v>2.27</v>
       </c>
       <c r="N42" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.440529</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>0.704636</v>
+        <v>0.579723</v>
       </c>
       <c r="P42" s="28" t="n"/>
       <c r="Q42" s="28" t="n">
-        <v>0.314011</v>
+        <v>0.139194</v>
       </c>
       <c r="R42" s="26" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="S42" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T42" s="24" t="inlineStr">
         <is>
@@ -12781,7 +12931,7 @@
       <c r="AD42" s="24" t="n"/>
       <c r="AE42" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-cs2-ww-cshp-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
         </is>
       </c>
       <c r="AF42" s="31" t="inlineStr">
@@ -12822,32 +12972,32 @@
       </c>
       <c r="AP42" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AQ42" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AR42" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AS42" s="24" t="inlineStr">
         <is>
-          <t>WW Team</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AT42" s="24" t="inlineStr">
         <is>
-          <t>WW Team</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AU42" s="24" t="inlineStr">
         <is>
-          <t>WW Team</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AV42" s="24" t="n"/>
@@ -12865,7 +13015,7 @@
       </c>
       <c r="BA42" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BB42" s="24" t="inlineStr">
@@ -12880,7 +13030,7 @@
       </c>
       <c r="BD42" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BE42" s="24" t="inlineStr">
@@ -12900,7 +13050,7 @@
       </c>
       <c r="BH42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:39.841997Z</t>
+          <t>2026-08-02T15:51:27.987395Z</t>
         </is>
       </c>
       <c r="BI42" s="24" t="inlineStr">
@@ -12910,13 +13060,13 @@
       </c>
       <c r="BJ42" s="25" t="n"/>
       <c r="BK42" s="26" t="n">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="BL42" s="27" t="n">
-        <v>2.56</v>
+        <v>2.27</v>
       </c>
       <c r="BM42" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.440529</v>
       </c>
       <c r="BN42" s="28" t="n"/>
       <c r="BO42" s="28" t="n"/>
@@ -12946,27 +13096,31 @@
       <c r="CM42" s="24" t="n"/>
       <c r="CN42" s="24" t="n"/>
       <c r="CO42" s="24" t="n"/>
-      <c r="CP42" s="24" t="n"/>
+      <c r="CP42" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>293daddbe23b43ea</t>
+          <t>dcd060b9a66d4474</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:50.282319Z</t>
+          <t>2026-08-02T15:51:41.323824Z</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-02T19:15:00Z</t>
         </is>
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>67510</t>
+          <t>67577</t>
         </is>
       </c>
       <c r="E43" s="24" t="inlineStr">
@@ -12976,12 +13130,12 @@
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="G43" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="H43" s="24" t="inlineStr">
@@ -13001,20 +13155,20 @@
         </is>
       </c>
       <c r="L43" s="26" t="n">
-        <v>-223</v>
+        <v>-156</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.641026</v>
       </c>
       <c r="N43" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.609375</v>
       </c>
       <c r="O43" s="28" t="n">
-        <v>0.563182</v>
+        <v>0.5270280000000001</v>
       </c>
       <c r="P43" s="28" t="n"/>
       <c r="Q43" s="28" t="n">
-        <v>-0.12722</v>
+        <v>-0.082347</v>
       </c>
       <c r="R43" s="26" t="n">
         <v>0</v>
@@ -13043,7 +13197,7 @@
       <c r="AD43" s="24" t="n"/>
       <c r="AE43" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
         </is>
       </c>
       <c r="AF43" s="31" t="inlineStr">
@@ -13079,37 +13233,37 @@
       </c>
       <c r="AO43" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP43" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AQ43" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AR43" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AS43" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AT43" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AU43" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AV43" s="24" t="n"/>
@@ -13127,7 +13281,7 @@
       </c>
       <c r="BA43" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BB43" s="24" t="inlineStr">
@@ -13142,7 +13296,7 @@
       </c>
       <c r="BD43" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BE43" s="24" t="inlineStr">
@@ -13162,7 +13316,7 @@
       </c>
       <c r="BH43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:40.888258Z</t>
+          <t>2026-08-02T15:51:28.508356Z</t>
         </is>
       </c>
       <c r="BI43" s="24" t="inlineStr">
@@ -13172,13 +13326,13 @@
       </c>
       <c r="BJ43" s="25" t="n"/>
       <c r="BK43" s="26" t="n">
-        <v>-223</v>
+        <v>-156</v>
       </c>
       <c r="BL43" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.641026</v>
       </c>
       <c r="BM43" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.609375</v>
       </c>
       <c r="BN43" s="28" t="n"/>
       <c r="BO43" s="28" t="n"/>
@@ -13208,27 +13362,31 @@
       <c r="CM43" s="24" t="n"/>
       <c r="CN43" s="24" t="n"/>
       <c r="CO43" s="24" t="n"/>
-      <c r="CP43" s="24" t="n"/>
+      <c r="CP43" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>a5c27a9bba5846d9</t>
+          <t>8b565a880bc641fd</t>
         </is>
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:50.282319Z</t>
+          <t>2026-08-02T15:51:41.323824Z</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T11:00:00Z</t>
+          <t>2026-08-03T08:00:00Z</t>
         </is>
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>69135</t>
+          <t>68288</t>
         </is>
       </c>
       <c r="E44" s="24" t="inlineStr">
@@ -13238,12 +13396,12 @@
       </c>
       <c r="F44" s="24" t="inlineStr">
         <is>
-          <t>ex-RUBY</t>
+          <t>CYBERSHOKE Prospects</t>
         </is>
       </c>
       <c r="G44" s="24" t="inlineStr">
         <is>
-          <t>1WIN</t>
+          <t>WW Team</t>
         </is>
       </c>
       <c r="H44" s="24" t="inlineStr">
@@ -13253,7 +13411,7 @@
       </c>
       <c r="I44" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J44" s="25" t="n"/>
@@ -13263,26 +13421,26 @@
         </is>
       </c>
       <c r="L44" s="26" t="n">
-        <v>-170</v>
+        <v>156</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>1.588235</v>
+        <v>2.56</v>
       </c>
       <c r="N44" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.390625</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>0.527215</v>
+        <v>0.704469</v>
       </c>
       <c r="P44" s="28" t="n"/>
       <c r="Q44" s="28" t="n">
-        <v>-0.102415</v>
+        <v>0.313844</v>
       </c>
       <c r="R44" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S44" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T44" s="24" t="inlineStr">
         <is>
@@ -13305,7 +13463,7 @@
       <c r="AD44" s="24" t="n"/>
       <c r="AE44" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-1win-exruby-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-cs2-ww-cshp-2026-08-03).</t>
         </is>
       </c>
       <c r="AF44" s="31" t="inlineStr">
@@ -13341,37 +13499,37 @@
       </c>
       <c r="AO44" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP44" s="24" t="inlineStr">
         <is>
-          <t>ex-RUBY</t>
+          <t>CYBERSHOKE Prospects</t>
         </is>
       </c>
       <c r="AQ44" s="24" t="inlineStr">
         <is>
-          <t>ex-RUBY</t>
+          <t>CYBERSHOKE Prospects</t>
         </is>
       </c>
       <c r="AR44" s="24" t="inlineStr">
         <is>
-          <t>ex-RUBY</t>
+          <t>CYBERSHOKE Prospects</t>
         </is>
       </c>
       <c r="AS44" s="24" t="inlineStr">
         <is>
-          <t>1WIN</t>
+          <t>WW Team</t>
         </is>
       </c>
       <c r="AT44" s="24" t="inlineStr">
         <is>
-          <t>1WIN</t>
+          <t>WW Team</t>
         </is>
       </c>
       <c r="AU44" s="24" t="inlineStr">
         <is>
-          <t>1WIN</t>
+          <t>WW Team</t>
         </is>
       </c>
       <c r="AV44" s="24" t="n"/>
@@ -13389,7 +13547,7 @@
       </c>
       <c r="BA44" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BB44" s="24" t="inlineStr">
@@ -13404,7 +13562,7 @@
       </c>
       <c r="BD44" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BE44" s="24" t="inlineStr">
@@ -13424,7 +13582,7 @@
       </c>
       <c r="BH44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:43.369564Z</t>
+          <t>2026-08-02T15:51:29.628121Z</t>
         </is>
       </c>
       <c r="BI44" s="24" t="inlineStr">
@@ -13434,13 +13592,13 @@
       </c>
       <c r="BJ44" s="25" t="n"/>
       <c r="BK44" s="26" t="n">
-        <v>-170</v>
+        <v>156</v>
       </c>
       <c r="BL44" s="27" t="n">
-        <v>1.588235</v>
+        <v>2.56</v>
       </c>
       <c r="BM44" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.390625</v>
       </c>
       <c r="BN44" s="28" t="n"/>
       <c r="BO44" s="28" t="n"/>
@@ -13470,27 +13628,31 @@
       <c r="CM44" s="24" t="n"/>
       <c r="CN44" s="24" t="n"/>
       <c r="CO44" s="24" t="n"/>
-      <c r="CP44" s="24" t="n"/>
+      <c r="CP44" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>0c1d277a9d214da8</t>
+          <t>29fd0577e0e047f2</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:50.282319Z</t>
+          <t>2026-08-02T15:51:41.323824Z</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T11:00:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>67578</t>
+          <t>67510</t>
         </is>
       </c>
       <c r="E45" s="24" t="inlineStr">
@@ -13500,12 +13662,12 @@
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="G45" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="H45" s="24" t="inlineStr">
@@ -13525,23 +13687,23 @@
         </is>
       </c>
       <c r="L45" s="26" t="n">
-        <v>-122</v>
+        <v>-223</v>
       </c>
       <c r="M45" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.44843</v>
       </c>
       <c r="N45" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.690402</v>
       </c>
       <c r="O45" s="28" t="n">
-        <v>0.526957</v>
+        <v>0.56316</v>
       </c>
       <c r="P45" s="28" t="n"/>
       <c r="Q45" s="28" t="n">
-        <v>-0.022593</v>
+        <v>-0.127242</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S45" s="29" t="n">
         <v>1</v>
@@ -13567,7 +13729,7 @@
       <c r="AD45" s="24" t="n"/>
       <c r="AE45" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
         </is>
       </c>
       <c r="AF45" s="31" t="inlineStr">
@@ -13603,37 +13765,37 @@
       </c>
       <c r="AO45" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP45" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AQ45" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AR45" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AS45" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AT45" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AU45" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AV45" s="24" t="n"/>
@@ -13651,7 +13813,7 @@
       </c>
       <c r="BA45" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BB45" s="24" t="inlineStr">
@@ -13666,7 +13828,7 @@
       </c>
       <c r="BD45" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BE45" s="24" t="inlineStr">
@@ -13686,7 +13848,7 @@
       </c>
       <c r="BH45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:43.897046Z</t>
+          <t>2026-08-02T15:51:31.160500Z</t>
         </is>
       </c>
       <c r="BI45" s="24" t="inlineStr">
@@ -13696,13 +13858,13 @@
       </c>
       <c r="BJ45" s="25" t="n"/>
       <c r="BK45" s="26" t="n">
-        <v>-122</v>
+        <v>-223</v>
       </c>
       <c r="BL45" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.44843</v>
       </c>
       <c r="BM45" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.690402</v>
       </c>
       <c r="BN45" s="28" t="n"/>
       <c r="BO45" s="28" t="n"/>
@@ -13732,27 +13894,31 @@
       <c r="CM45" s="24" t="n"/>
       <c r="CN45" s="24" t="n"/>
       <c r="CO45" s="24" t="n"/>
-      <c r="CP45" s="24" t="n"/>
+      <c r="CP45" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>28f61e71bb5c4b2e</t>
+          <t>0cc692592b584103</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:50.282319Z</t>
+          <t>2026-08-02T15:51:41.323824Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T13:45:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>67579</t>
+          <t>68289</t>
         </is>
       </c>
       <c r="E46" s="24" t="inlineStr">
@@ -13762,12 +13928,12 @@
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="G46" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="H46" s="24" t="inlineStr">
@@ -13777,7 +13943,7 @@
       </c>
       <c r="I46" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J46" s="25" t="n"/>
@@ -13787,26 +13953,26 @@
         </is>
       </c>
       <c r="L46" s="26" t="n">
-        <v>203</v>
+        <v>-138</v>
       </c>
       <c r="M46" s="27" t="n">
-        <v>3.03</v>
+        <v>1.724638</v>
       </c>
       <c r="N46" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.579832</v>
       </c>
       <c r="O46" s="28" t="n">
-        <v>0.5263640000000001</v>
+        <v>0.599394</v>
       </c>
       <c r="P46" s="28" t="n"/>
       <c r="Q46" s="28" t="n">
-        <v>0.196331</v>
+        <v>0.019562</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="S46" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T46" s="24" t="inlineStr">
         <is>
@@ -13829,7 +13995,7 @@
       <c r="AD46" s="24" t="n"/>
       <c r="AE46" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3300 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
         </is>
       </c>
       <c r="AF46" s="31" t="inlineStr">
@@ -13847,7 +14013,7 @@
       <c r="AJ46" s="31" t="n"/>
       <c r="AK46" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL46" s="26" t="n">
@@ -13855,47 +14021,47 @@
       </c>
       <c r="AM46" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN46" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO46" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP46" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="AQ46" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="AR46" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="AS46" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="AT46" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="AU46" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="AV46" s="24" t="n"/>
@@ -13913,7 +14079,7 @@
       </c>
       <c r="BA46" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BB46" s="24" t="inlineStr">
@@ -13928,7 +14094,7 @@
       </c>
       <c r="BD46" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BE46" s="24" t="inlineStr">
@@ -13948,7 +14114,7 @@
       </c>
       <c r="BH46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:44.969369Z</t>
+          <t>2026-08-02T15:51:31.676274Z</t>
         </is>
       </c>
       <c r="BI46" s="24" t="inlineStr">
@@ -13958,13 +14124,13 @@
       </c>
       <c r="BJ46" s="25" t="n"/>
       <c r="BK46" s="26" t="n">
-        <v>203</v>
+        <v>-138</v>
       </c>
       <c r="BL46" s="27" t="n">
-        <v>3.03</v>
+        <v>1.724638</v>
       </c>
       <c r="BM46" s="28" t="n">
-        <v>0.330033</v>
+        <v>0.579832</v>
       </c>
       <c r="BN46" s="28" t="n"/>
       <c r="BO46" s="28" t="n"/>
@@ -13994,27 +14160,31 @@
       <c r="CM46" s="24" t="n"/>
       <c r="CN46" s="24" t="n"/>
       <c r="CO46" s="24" t="n"/>
-      <c r="CP46" s="24" t="n"/>
+      <c r="CP46" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>d60c391c21d847b7</t>
+          <t>b4129a3a513c483d</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:50.282319Z</t>
+          <t>2026-08-02T15:51:41.323824Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T14:00:00Z</t>
+          <t>2026-08-03T11:00:00Z</t>
         </is>
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>68292</t>
+          <t>69267</t>
         </is>
       </c>
       <c r="E47" s="24" t="inlineStr">
@@ -14024,12 +14194,12 @@
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
-          <t>ARCRED</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr">
@@ -14049,23 +14219,23 @@
         </is>
       </c>
       <c r="L47" s="26" t="n">
-        <v>-186</v>
+        <v>-213</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.469484</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.680511</v>
       </c>
       <c r="O47" s="28" t="n">
-        <v>0.613928</v>
+        <v>0.62913</v>
       </c>
       <c r="P47" s="28" t="n"/>
       <c r="Q47" s="28" t="n">
-        <v>-0.036422</v>
+        <v>-0.051381</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S47" s="29" t="n">
         <v>1.5</v>
@@ -14091,7 +14261,7 @@
       <c r="AD47" s="24" t="n"/>
       <c r="AE47" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-cs2-arc-btf-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jpu-lk-2026-08-03).</t>
         </is>
       </c>
       <c r="AF47" s="31" t="inlineStr">
@@ -14132,32 +14302,32 @@
       </c>
       <c r="AP47" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AQ47" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AR47" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AS47" s="24" t="inlineStr">
         <is>
-          <t>ARCRED</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AT47" s="24" t="inlineStr">
         <is>
-          <t>ARCRED</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AU47" s="24" t="inlineStr">
         <is>
-          <t>ARCRED</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AV47" s="24" t="n"/>
@@ -14175,7 +14345,7 @@
       </c>
       <c r="BA47" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BB47" s="24" t="inlineStr">
@@ -14190,7 +14360,7 @@
       </c>
       <c r="BD47" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BE47" s="24" t="inlineStr">
@@ -14210,7 +14380,7 @@
       </c>
       <c r="BH47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:46.045093Z</t>
+          <t>2026-08-02T15:51:34.287196Z</t>
         </is>
       </c>
       <c r="BI47" s="24" t="inlineStr">
@@ -14220,13 +14390,13 @@
       </c>
       <c r="BJ47" s="25" t="n"/>
       <c r="BK47" s="26" t="n">
-        <v>-186</v>
+        <v>-213</v>
       </c>
       <c r="BL47" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.469484</v>
       </c>
       <c r="BM47" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.680511</v>
       </c>
       <c r="BN47" s="28" t="n"/>
       <c r="BO47" s="28" t="n"/>
@@ -14256,27 +14426,31 @@
       <c r="CM47" s="24" t="n"/>
       <c r="CN47" s="24" t="n"/>
       <c r="CO47" s="24" t="n"/>
-      <c r="CP47" s="24" t="n"/>
+      <c r="CP47" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>8d2f4d4fb47640e6</t>
+          <t>28dc3f7209da4b8c</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:50.282319Z</t>
+          <t>2026-08-02T15:51:41.323824Z</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T23:00:00Z</t>
+          <t>2026-08-03T11:00:00Z</t>
         </is>
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>68043</t>
+          <t>69135</t>
         </is>
       </c>
       <c r="E48" s="24" t="inlineStr">
@@ -14286,12 +14460,12 @@
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="H48" s="24" t="inlineStr">
@@ -14311,26 +14485,26 @@
         </is>
       </c>
       <c r="L48" s="26" t="n">
-        <v>113</v>
+        <v>-163</v>
       </c>
       <c r="M48" s="27" t="n">
-        <v>2.13</v>
+        <v>1.613497</v>
       </c>
       <c r="N48" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.619772</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>0.569723</v>
+        <v>0.527344</v>
       </c>
       <c r="P48" s="28" t="n"/>
       <c r="Q48" s="28" t="n">
-        <v>0.100239</v>
+        <v>-0.092428</v>
       </c>
       <c r="R48" s="26" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="S48" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T48" s="24" t="inlineStr">
         <is>
@@ -14353,7 +14527,7 @@
       <c r="AD48" s="24" t="n"/>
       <c r="AE48" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4700 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-1win-exruby-2026-08-03).</t>
         </is>
       </c>
       <c r="AF48" s="31" t="inlineStr">
@@ -14389,37 +14563,37 @@
       </c>
       <c r="AO48" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP48" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AQ48" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AR48" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AS48" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="AT48" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="AU48" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="AV48" s="24" t="n"/>
@@ -14437,7 +14611,7 @@
       </c>
       <c r="BA48" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BB48" s="24" t="inlineStr">
@@ -14452,7 +14626,7 @@
       </c>
       <c r="BD48" s="24" t="inlineStr">
         <is>
-          <t>90a833898e793d48aa6ce23d298a692fd7b914cfa51b8101005c627e8a886f30</t>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
         </is>
       </c>
       <c r="BE48" s="24" t="inlineStr">
@@ -14472,7 +14646,7 @@
       </c>
       <c r="BH48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T13:07:50.279981Z</t>
+          <t>2026-08-02T15:51:34.811836Z</t>
         </is>
       </c>
       <c r="BI48" s="24" t="inlineStr">
@@ -14482,13 +14656,13 @@
       </c>
       <c r="BJ48" s="25" t="n"/>
       <c r="BK48" s="26" t="n">
-        <v>113</v>
+        <v>-163</v>
       </c>
       <c r="BL48" s="27" t="n">
-        <v>2.13</v>
+        <v>1.613497</v>
       </c>
       <c r="BM48" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.619772</v>
       </c>
       <c r="BN48" s="28" t="n"/>
       <c r="BO48" s="28" t="n"/>
@@ -14518,7 +14692,1341 @@
       <c r="CM48" s="24" t="n"/>
       <c r="CN48" s="24" t="n"/>
       <c r="CO48" s="24" t="n"/>
-      <c r="CP48" s="24" t="n"/>
+      <c r="CP48" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>e4e741f10bd84db0</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:41.323824Z</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>67578</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>Recrent Club</t>
+        </is>
+      </c>
+      <c r="H49" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I49" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J49" s="25" t="n"/>
+      <c r="K49" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L49" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M49" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N49" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O49" s="28" t="n">
+        <v>0.5270280000000001</v>
+      </c>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="28" t="n">
+        <v>-0.072972</v>
+      </c>
+      <c r="R49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U49" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V49" s="24" t="n"/>
+      <c r="W49" s="26" t="n"/>
+      <c r="X49" s="26" t="n"/>
+      <c r="Y49" s="25" t="n"/>
+      <c r="Z49" s="26" t="n"/>
+      <c r="AA49" s="28" t="n"/>
+      <c r="AB49" s="28" t="n"/>
+      <c r="AC49" s="30" t="n"/>
+      <c r="AD49" s="24" t="n"/>
+      <c r="AE49" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF49" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG49" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH49" s="24" t="n"/>
+      <c r="AI49" s="31" t="n"/>
+      <c r="AJ49" s="31" t="n"/>
+      <c r="AK49" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL49" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM49" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN49" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO49" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP49" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AQ49" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AR49" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AS49" s="24" t="inlineStr">
+        <is>
+          <t>Recrent Club</t>
+        </is>
+      </c>
+      <c r="AT49" s="24" t="inlineStr">
+        <is>
+          <t>Recrent Club</t>
+        </is>
+      </c>
+      <c r="AU49" s="24" t="inlineStr">
+        <is>
+          <t>Recrent Club</t>
+        </is>
+      </c>
+      <c r="AV49" s="24" t="n"/>
+      <c r="AW49" s="24" t="n"/>
+      <c r="AX49" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY49" s="24" t="n"/>
+      <c r="AZ49" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA49" s="24" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="BB49" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC49" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD49" s="24" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="BE49" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF49" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG49" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:35.357223Z</t>
+        </is>
+      </c>
+      <c r="BI49" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ49" s="25" t="n"/>
+      <c r="BK49" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL49" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM49" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN49" s="28" t="n"/>
+      <c r="BO49" s="28" t="n"/>
+      <c r="BP49" s="25" t="n"/>
+      <c r="BQ49" s="27" t="n"/>
+      <c r="BR49" s="28" t="n"/>
+      <c r="BS49" s="28" t="n"/>
+      <c r="BT49" s="28" t="n"/>
+      <c r="BU49" s="25" t="n"/>
+      <c r="BV49" s="29" t="n"/>
+      <c r="BW49" s="24" t="n"/>
+      <c r="BX49" s="30" t="n"/>
+      <c r="BY49" s="27" t="n"/>
+      <c r="BZ49" s="24" t="n"/>
+      <c r="CA49" s="31" t="n"/>
+      <c r="CB49" s="24" t="n"/>
+      <c r="CC49" s="24" t="n"/>
+      <c r="CD49" s="24" t="n"/>
+      <c r="CE49" s="24" t="n"/>
+      <c r="CF49" s="24" t="n"/>
+      <c r="CG49" s="24" t="n"/>
+      <c r="CH49" s="24" t="n"/>
+      <c r="CI49" s="24" t="n"/>
+      <c r="CJ49" s="24" t="n"/>
+      <c r="CK49" s="24" t="n"/>
+      <c r="CL49" s="24" t="n"/>
+      <c r="CM49" s="24" t="n"/>
+      <c r="CN49" s="24" t="n"/>
+      <c r="CO49" s="24" t="n"/>
+      <c r="CP49" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>f4969aeb2da94d49</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:41.323824Z</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>67579</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="G50" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="H50" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I50" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J50" s="25" t="n"/>
+      <c r="K50" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L50" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="M50" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N50" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="O50" s="28" t="n">
+        <v>0.526276</v>
+      </c>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="28" t="n">
+        <v>0.18614</v>
+      </c>
+      <c r="R50" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S50" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U50" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V50" s="24" t="n"/>
+      <c r="W50" s="26" t="n"/>
+      <c r="X50" s="26" t="n"/>
+      <c r="Y50" s="25" t="n"/>
+      <c r="Z50" s="26" t="n"/>
+      <c r="AA50" s="28" t="n"/>
+      <c r="AB50" s="28" t="n"/>
+      <c r="AC50" s="30" t="n"/>
+      <c r="AD50" s="24" t="n"/>
+      <c r="AE50" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF50" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG50" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH50" s="24" t="n"/>
+      <c r="AI50" s="31" t="n"/>
+      <c r="AJ50" s="31" t="n"/>
+      <c r="AK50" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL50" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM50" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN50" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO50" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP50" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AQ50" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AR50" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AS50" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AT50" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AU50" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AV50" s="24" t="n"/>
+      <c r="AW50" s="24" t="n"/>
+      <c r="AX50" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY50" s="24" t="n"/>
+      <c r="AZ50" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA50" s="24" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="BB50" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC50" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD50" s="24" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="BE50" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF50" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG50" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:35.908816Z</t>
+        </is>
+      </c>
+      <c r="BI50" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ50" s="25" t="n"/>
+      <c r="BK50" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="BL50" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BM50" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="BN50" s="28" t="n"/>
+      <c r="BO50" s="28" t="n"/>
+      <c r="BP50" s="25" t="n"/>
+      <c r="BQ50" s="27" t="n"/>
+      <c r="BR50" s="28" t="n"/>
+      <c r="BS50" s="28" t="n"/>
+      <c r="BT50" s="28" t="n"/>
+      <c r="BU50" s="25" t="n"/>
+      <c r="BV50" s="29" t="n"/>
+      <c r="BW50" s="24" t="n"/>
+      <c r="BX50" s="30" t="n"/>
+      <c r="BY50" s="27" t="n"/>
+      <c r="BZ50" s="24" t="n"/>
+      <c r="CA50" s="31" t="n"/>
+      <c r="CB50" s="24" t="n"/>
+      <c r="CC50" s="24" t="n"/>
+      <c r="CD50" s="24" t="n"/>
+      <c r="CE50" s="24" t="n"/>
+      <c r="CF50" s="24" t="n"/>
+      <c r="CG50" s="24" t="n"/>
+      <c r="CH50" s="24" t="n"/>
+      <c r="CI50" s="24" t="n"/>
+      <c r="CJ50" s="24" t="n"/>
+      <c r="CK50" s="24" t="n"/>
+      <c r="CL50" s="24" t="n"/>
+      <c r="CM50" s="24" t="n"/>
+      <c r="CN50" s="24" t="n"/>
+      <c r="CO50" s="24" t="n"/>
+      <c r="CP50" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>1cffdca8c7bc4808</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:41.323824Z</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>68292</t>
+        </is>
+      </c>
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>ARCRED</t>
+        </is>
+      </c>
+      <c r="H51" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I51" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J51" s="25" t="n"/>
+      <c r="K51" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L51" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M51" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N51" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O51" s="28" t="n">
+        <v>0.614071</v>
+      </c>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="28" t="n">
+        <v>-0.036279</v>
+      </c>
+      <c r="R51" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S51" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T51" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U51" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V51" s="24" t="n"/>
+      <c r="W51" s="26" t="n"/>
+      <c r="X51" s="26" t="n"/>
+      <c r="Y51" s="25" t="n"/>
+      <c r="Z51" s="26" t="n"/>
+      <c r="AA51" s="28" t="n"/>
+      <c r="AB51" s="28" t="n"/>
+      <c r="AC51" s="30" t="n"/>
+      <c r="AD51" s="24" t="n"/>
+      <c r="AE51" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-cs2-arc-btf-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF51" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG51" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH51" s="24" t="n"/>
+      <c r="AI51" s="31" t="n"/>
+      <c r="AJ51" s="31" t="n"/>
+      <c r="AK51" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL51" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM51" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN51" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO51" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP51" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AQ51" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AR51" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AS51" s="24" t="inlineStr">
+        <is>
+          <t>ARCRED</t>
+        </is>
+      </c>
+      <c r="AT51" s="24" t="inlineStr">
+        <is>
+          <t>ARCRED</t>
+        </is>
+      </c>
+      <c r="AU51" s="24" t="inlineStr">
+        <is>
+          <t>ARCRED</t>
+        </is>
+      </c>
+      <c r="AV51" s="24" t="n"/>
+      <c r="AW51" s="24" t="n"/>
+      <c r="AX51" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY51" s="24" t="n"/>
+      <c r="AZ51" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA51" s="24" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="BB51" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC51" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD51" s="24" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="BE51" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF51" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG51" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:36.873973Z</t>
+        </is>
+      </c>
+      <c r="BI51" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ51" s="25" t="n"/>
+      <c r="BK51" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL51" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM51" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN51" s="28" t="n"/>
+      <c r="BO51" s="28" t="n"/>
+      <c r="BP51" s="25" t="n"/>
+      <c r="BQ51" s="27" t="n"/>
+      <c r="BR51" s="28" t="n"/>
+      <c r="BS51" s="28" t="n"/>
+      <c r="BT51" s="28" t="n"/>
+      <c r="BU51" s="25" t="n"/>
+      <c r="BV51" s="29" t="n"/>
+      <c r="BW51" s="24" t="n"/>
+      <c r="BX51" s="30" t="n"/>
+      <c r="BY51" s="27" t="n"/>
+      <c r="BZ51" s="24" t="n"/>
+      <c r="CA51" s="31" t="n"/>
+      <c r="CB51" s="24" t="n"/>
+      <c r="CC51" s="24" t="n"/>
+      <c r="CD51" s="24" t="n"/>
+      <c r="CE51" s="24" t="n"/>
+      <c r="CF51" s="24" t="n"/>
+      <c r="CG51" s="24" t="n"/>
+      <c r="CH51" s="24" t="n"/>
+      <c r="CI51" s="24" t="n"/>
+      <c r="CJ51" s="24" t="n"/>
+      <c r="CK51" s="24" t="n"/>
+      <c r="CL51" s="24" t="n"/>
+      <c r="CM51" s="24" t="n"/>
+      <c r="CN51" s="24" t="n"/>
+      <c r="CO51" s="24" t="n"/>
+      <c r="CP51" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>9369df9452e344ef</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:41.323824Z</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="H52" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J52" s="25" t="n"/>
+      <c r="K52" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L52" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M52" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N52" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O52" s="28" t="n">
+        <v>0.6819730000000001</v>
+      </c>
+      <c r="P52" s="28" t="n"/>
+      <c r="Q52" s="28" t="n">
+        <v>0.041685</v>
+      </c>
+      <c r="R52" s="26" t="n">
+        <v>41</v>
+      </c>
+      <c r="S52" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T52" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U52" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V52" s="24" t="n"/>
+      <c r="W52" s="26" t="n"/>
+      <c r="X52" s="26" t="n"/>
+      <c r="Y52" s="25" t="n"/>
+      <c r="Z52" s="26" t="n"/>
+      <c r="AA52" s="28" t="n"/>
+      <c r="AB52" s="28" t="n"/>
+      <c r="AC52" s="30" t="n"/>
+      <c r="AD52" s="24" t="n"/>
+      <c r="AE52" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF52" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG52" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH52" s="24" t="n"/>
+      <c r="AI52" s="31" t="n"/>
+      <c r="AJ52" s="31" t="n"/>
+      <c r="AK52" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL52" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM52" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN52" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO52" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP52" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AQ52" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AR52" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AS52" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AT52" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AU52" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AV52" s="24" t="n"/>
+      <c r="AW52" s="24" t="n"/>
+      <c r="AX52" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY52" s="24" t="n"/>
+      <c r="AZ52" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA52" s="24" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="BB52" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC52" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD52" s="24" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="BE52" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF52" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG52" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:37.423413Z</t>
+        </is>
+      </c>
+      <c r="BI52" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ52" s="25" t="n"/>
+      <c r="BK52" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL52" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM52" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN52" s="28" t="n"/>
+      <c r="BO52" s="28" t="n"/>
+      <c r="BP52" s="25" t="n"/>
+      <c r="BQ52" s="27" t="n"/>
+      <c r="BR52" s="28" t="n"/>
+      <c r="BS52" s="28" t="n"/>
+      <c r="BT52" s="28" t="n"/>
+      <c r="BU52" s="25" t="n"/>
+      <c r="BV52" s="29" t="n"/>
+      <c r="BW52" s="24" t="n"/>
+      <c r="BX52" s="30" t="n"/>
+      <c r="BY52" s="27" t="n"/>
+      <c r="BZ52" s="24" t="n"/>
+      <c r="CA52" s="31" t="n"/>
+      <c r="CB52" s="24" t="n"/>
+      <c r="CC52" s="24" t="n"/>
+      <c r="CD52" s="24" t="n"/>
+      <c r="CE52" s="24" t="n"/>
+      <c r="CF52" s="24" t="n"/>
+      <c r="CG52" s="24" t="n"/>
+      <c r="CH52" s="24" t="n"/>
+      <c r="CI52" s="24" t="n"/>
+      <c r="CJ52" s="24" t="n"/>
+      <c r="CK52" s="24" t="n"/>
+      <c r="CL52" s="24" t="n"/>
+      <c r="CM52" s="24" t="n"/>
+      <c r="CN52" s="24" t="n"/>
+      <c r="CO52" s="24" t="n"/>
+      <c r="CP52" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>495eaed7b34a4c93</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:41.323824Z</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>68043</t>
+        </is>
+      </c>
+      <c r="E53" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F53" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="G53" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="H53" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I53" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J53" s="25" t="n"/>
+      <c r="K53" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L53" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M53" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N53" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O53" s="28" t="n">
+        <v>0.5697990000000001</v>
+      </c>
+      <c r="P53" s="28" t="n"/>
+      <c r="Q53" s="28" t="n">
+        <v>0.119349</v>
+      </c>
+      <c r="R53" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="S53" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T53" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U53" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V53" s="24" t="n"/>
+      <c r="W53" s="26" t="n"/>
+      <c r="X53" s="26" t="n"/>
+      <c r="Y53" s="25" t="n"/>
+      <c r="Z53" s="26" t="n"/>
+      <c r="AA53" s="28" t="n"/>
+      <c r="AB53" s="28" t="n"/>
+      <c r="AC53" s="30" t="n"/>
+      <c r="AD53" s="24" t="n"/>
+      <c r="AE53" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF53" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG53" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH53" s="24" t="n"/>
+      <c r="AI53" s="31" t="n"/>
+      <c r="AJ53" s="31" t="n"/>
+      <c r="AK53" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL53" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM53" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN53" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO53" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP53" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AQ53" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AR53" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AS53" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AT53" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AU53" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AV53" s="24" t="n"/>
+      <c r="AW53" s="24" t="n"/>
+      <c r="AX53" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY53" s="24" t="n"/>
+      <c r="AZ53" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA53" s="24" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="BB53" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC53" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD53" s="24" t="inlineStr">
+        <is>
+          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+        </is>
+      </c>
+      <c r="BE53" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF53" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG53" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH53" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:41.320292Z</t>
+        </is>
+      </c>
+      <c r="BI53" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ53" s="25" t="n"/>
+      <c r="BK53" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL53" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM53" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN53" s="28" t="n"/>
+      <c r="BO53" s="28" t="n"/>
+      <c r="BP53" s="25" t="n"/>
+      <c r="BQ53" s="27" t="n"/>
+      <c r="BR53" s="28" t="n"/>
+      <c r="BS53" s="28" t="n"/>
+      <c r="BT53" s="28" t="n"/>
+      <c r="BU53" s="25" t="n"/>
+      <c r="BV53" s="29" t="n"/>
+      <c r="BW53" s="24" t="n"/>
+      <c r="BX53" s="30" t="n"/>
+      <c r="BY53" s="27" t="n"/>
+      <c r="BZ53" s="24" t="n"/>
+      <c r="CA53" s="31" t="n"/>
+      <c r="CB53" s="24" t="n"/>
+      <c r="CC53" s="24" t="n"/>
+      <c r="CD53" s="24" t="n"/>
+      <c r="CE53" s="24" t="n"/>
+      <c r="CF53" s="24" t="n"/>
+      <c r="CG53" s="24" t="n"/>
+      <c r="CH53" s="24" t="n"/>
+      <c r="CI53" s="24" t="n"/>
+      <c r="CJ53" s="24" t="n"/>
+      <c r="CK53" s="24" t="n"/>
+      <c r="CL53" s="24" t="n"/>
+      <c r="CM53" s="24" t="n"/>
+      <c r="CN53" s="24" t="n"/>
+      <c r="CO53" s="24" t="n"/>
+      <c r="CP53" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP53" headerRowCount="1">
-  <autoFilter ref="A1:CP53"/>
-  <tableColumns count="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ54" headerRowCount="1">
+  <autoFilter ref="A1:CQ54"/>
+  <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,7 +396,8 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="trade_candidate"/>
+    <tableColumn id="94" name="market_residual_probability"/>
+    <tableColumn id="95" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -753,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$53)</f>
+        <f>COUNTA('Picks'!$A$2:$A$54)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$53,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$54,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$53,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$54,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")+COUNTIFS('Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"win")+COUNTIFS('Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -793,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$53,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$54,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"win")/(COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"win")+COUNTIFS('Picks'!$BX$2:$BX$53,"&gt;0",'Picks'!$V$2:$V$53,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"win")/(COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"win")+COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$53)/SUM('Picks'!$BX$2:$BX$53),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$54)/SUM('Picks'!$BX$2:$BX$54),0)</f>
         <v/>
       </c>
     </row>
@@ -833,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$53)</f>
+        <f>SUM('Picks'!$BY$2:$BY$54)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$53,"&lt;&gt;",'Picks'!$AB$2:$AB$53),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$54,"&lt;&gt;",'Picks'!$AB$2:$AB$54),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$53,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$53,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$54,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$54,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$53,'Picks'!$AM$2:$AM$53,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$54,'Picks'!$AM$2:$AM$54,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -900,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A14,'Picks'!$U$2:$U$54,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A14,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A14,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -916,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$53,'Picks'!$H$2:$H$53,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$54,'Picks'!$H$2:$H$54,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$53,'Picks'!$H$2:$H$53,$A14,'Picks'!$U$2:$U$53,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$54,'Picks'!$H$2:$H$54,$A14,'Picks'!$U$2:$U$54,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -931,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A15,'Picks'!$U$2:$U$54,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A15,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A15,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -947,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$53,'Picks'!$H$2:$H$53,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$54,'Picks'!$H$2:$H$54,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$53,'Picks'!$H$2:$H$53,$A15,'Picks'!$U$2:$U$53,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$54,'Picks'!$H$2:$H$54,$A15,'Picks'!$U$2:$U$54,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -962,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A16,'Picks'!$U$2:$U$54,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A16,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled",'Picks'!$V$2:$V$53,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$54,$A16,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -978,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$53,'Picks'!$H$2:$H$53,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$54,'Picks'!$H$2:$H$54,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$53,'Picks'!$H$2:$H$53,$A16,'Picks'!$U$2:$U$53,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$54,'Picks'!$H$2:$H$54,$A16,'Picks'!$U$2:$U$54,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1011,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP53"/>
+  <dimension ref="A1:CQ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1107,7 +1108,8 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
-    <col width="17" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="17" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1577,6 +1579,11 @@
         </is>
       </c>
       <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>market_residual_probability</t>
+        </is>
+      </c>
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1867,6 +1874,7 @@
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
+      <c r="CQ2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2153,6 +2161,7 @@
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
+      <c r="CQ3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2439,6 +2448,7 @@
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
+      <c r="CQ4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2725,6 +2735,7 @@
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
+      <c r="CQ5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3011,6 +3022,7 @@
       <c r="CN6" s="24" t="n"/>
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
+      <c r="CQ6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3273,6 +3285,7 @@
       <c r="CN7" s="24" t="n"/>
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
+      <c r="CQ7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3559,6 +3572,7 @@
       <c r="CN8" s="24" t="n"/>
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
+      <c r="CQ8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3845,6 +3859,7 @@
       <c r="CN9" s="24" t="n"/>
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
+      <c r="CQ9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4131,6 +4146,7 @@
       <c r="CN10" s="24" t="n"/>
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
+      <c r="CQ10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4417,6 +4433,7 @@
       <c r="CN11" s="24" t="n"/>
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4703,6 +4720,7 @@
       <c r="CN12" s="24" t="n"/>
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -4989,6 +5007,7 @@
       <c r="CN13" s="24" t="n"/>
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5275,6 +5294,7 @@
       <c r="CN14" s="24" t="n"/>
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5561,6 +5581,7 @@
       <c r="CN15" s="24" t="n"/>
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5847,6 +5868,7 @@
       <c r="CN16" s="24" t="n"/>
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6133,6 +6155,7 @@
       <c r="CN17" s="24" t="n"/>
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -6419,6 +6442,7 @@
       <c r="CN18" s="24" t="n"/>
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
@@ -6705,6 +6729,7 @@
       <c r="CN19" s="24" t="n"/>
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
@@ -6991,6 +7016,7 @@
       <c r="CN20" s="24" t="n"/>
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
@@ -7277,6 +7303,7 @@
       <c r="CN21" s="24" t="n"/>
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
@@ -7563,6 +7590,7 @@
       <c r="CN22" s="24" t="n"/>
       <c r="CO22" s="24" t="n"/>
       <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
@@ -7825,6 +7853,7 @@
       <c r="CN23" s="24" t="n"/>
       <c r="CO23" s="24" t="n"/>
       <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
@@ -8111,6 +8140,7 @@
       <c r="CN24" s="24" t="n"/>
       <c r="CO24" s="24" t="n"/>
       <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
@@ -8397,6 +8427,7 @@
       <c r="CN25" s="24" t="n"/>
       <c r="CO25" s="24" t="n"/>
       <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
@@ -8683,6 +8714,7 @@
       <c r="CN26" s="24" t="n"/>
       <c r="CO26" s="24" t="n"/>
       <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
@@ -8969,6 +9001,7 @@
       <c r="CN27" s="24" t="n"/>
       <c r="CO27" s="24" t="n"/>
       <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="n"/>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
@@ -9255,6 +9288,7 @@
       <c r="CN28" s="24" t="n"/>
       <c r="CO28" s="24" t="n"/>
       <c r="CP28" s="24" t="n"/>
+      <c r="CQ28" s="24" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
@@ -9531,6 +9565,7 @@
       <c r="CN29" s="24" t="n"/>
       <c r="CO29" s="24" t="n"/>
       <c r="CP29" s="24" t="n"/>
+      <c r="CQ29" s="24" t="n"/>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
@@ -9817,6 +9852,7 @@
       <c r="CN30" s="24" t="n"/>
       <c r="CO30" s="24" t="n"/>
       <c r="CP30" s="24" t="n"/>
+      <c r="CQ30" s="24" t="n"/>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
@@ -10103,6 +10139,7 @@
       <c r="CN31" s="24" t="n"/>
       <c r="CO31" s="24" t="n"/>
       <c r="CP31" s="24" t="n"/>
+      <c r="CQ31" s="24" t="n"/>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
@@ -10389,6 +10426,7 @@
       <c r="CN32" s="24" t="n"/>
       <c r="CO32" s="24" t="n"/>
       <c r="CP32" s="24" t="n"/>
+      <c r="CQ32" s="24" t="n"/>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
@@ -10651,6 +10689,7 @@
       <c r="CN33" s="24" t="n"/>
       <c r="CO33" s="24" t="n"/>
       <c r="CP33" s="24" t="n"/>
+      <c r="CQ33" s="24" t="n"/>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
@@ -10937,6 +10976,7 @@
       <c r="CN34" s="24" t="n"/>
       <c r="CO34" s="24" t="n"/>
       <c r="CP34" s="24" t="n"/>
+      <c r="CQ34" s="24" t="n"/>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
@@ -11199,6 +11239,7 @@
       <c r="CN35" s="24" t="n"/>
       <c r="CO35" s="24" t="n"/>
       <c r="CP35" s="24" t="n"/>
+      <c r="CQ35" s="24" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
@@ -11485,6 +11526,7 @@
       <c r="CN36" s="24" t="n"/>
       <c r="CO36" s="24" t="n"/>
       <c r="CP36" s="24" t="n"/>
+      <c r="CQ36" s="24" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
@@ -11771,16 +11813,17 @@
       <c r="CN37" s="24" t="n"/>
       <c r="CO37" s="24" t="n"/>
       <c r="CP37" s="24" t="n"/>
+      <c r="CQ37" s="24" t="n"/>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>ff4c023688d14058</t>
+          <t>f385338f671d4616</t>
         </is>
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
@@ -11790,7 +11833,7 @@
       </c>
       <c r="D38" s="24" t="inlineStr">
         <is>
-          <t>69680</t>
+          <t>69681</t>
         </is>
       </c>
       <c r="E38" s="24" t="inlineStr">
@@ -11800,12 +11843,12 @@
       </c>
       <c r="F38" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="G38" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="H38" s="24" t="inlineStr">
@@ -11825,26 +11868,26 @@
         </is>
       </c>
       <c r="L38" s="26" t="n">
-        <v>-156</v>
+        <v>-223</v>
       </c>
       <c r="M38" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.44843</v>
       </c>
       <c r="N38" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.690402</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>0.653037</v>
+        <v>0.616241</v>
       </c>
       <c r="P38" s="28" t="n"/>
       <c r="Q38" s="28" t="n">
-        <v>0.043662</v>
+        <v>-0.074161</v>
       </c>
       <c r="R38" s="26" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="S38" s="29" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="T38" s="24" t="inlineStr">
         <is>
@@ -11867,7 +11910,7 @@
       <c r="AD38" s="24" t="n"/>
       <c r="AE38" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-for-lk-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mta-bmb-2026-08-02).</t>
         </is>
       </c>
       <c r="AF38" s="31" t="inlineStr">
@@ -11885,7 +11928,7 @@
       <c r="AJ38" s="31" t="n"/>
       <c r="AK38" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL38" s="26" t="n">
@@ -11893,47 +11936,47 @@
       </c>
       <c r="AM38" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN38" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO38" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP38" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AQ38" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AR38" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AS38" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AT38" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AU38" s="24" t="inlineStr">
         <is>
-          <t>Fortress</t>
+          <t>Mai Tai</t>
         </is>
       </c>
       <c r="AV38" s="24" t="n"/>
@@ -11951,7 +11994,7 @@
       </c>
       <c r="BA38" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB38" s="24" t="inlineStr">
@@ -11966,7 +12009,7 @@
       </c>
       <c r="BD38" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE38" s="24" t="inlineStr">
@@ -11986,7 +12029,7 @@
       </c>
       <c r="BH38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:25.435587Z</t>
+          <t>2026-08-02T16:14:57.846727Z</t>
         </is>
       </c>
       <c r="BI38" s="24" t="inlineStr">
@@ -11996,13 +12039,13 @@
       </c>
       <c r="BJ38" s="25" t="n"/>
       <c r="BK38" s="26" t="n">
-        <v>-156</v>
+        <v>-223</v>
       </c>
       <c r="BL38" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.44843</v>
       </c>
       <c r="BM38" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.690402</v>
       </c>
       <c r="BN38" s="28" t="n"/>
       <c r="BO38" s="28" t="n"/>
@@ -12032,21 +12075,22 @@
       <c r="CM38" s="24" t="n"/>
       <c r="CN38" s="24" t="n"/>
       <c r="CO38" s="24" t="n"/>
-      <c r="CP38" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CP38" s="24" t="n"/>
+      <c r="CQ38" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>add1d14a4c2b420d</t>
+          <t>3665df6053ba4abb</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
@@ -12056,7 +12100,7 @@
       </c>
       <c r="D39" s="24" t="inlineStr">
         <is>
-          <t>69681</t>
+          <t>69263</t>
         </is>
       </c>
       <c r="E39" s="24" t="inlineStr">
@@ -12066,7 +12110,7 @@
       </c>
       <c r="F39" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="G39" s="24" t="inlineStr">
@@ -12091,26 +12135,26 @@
         </is>
       </c>
       <c r="L39" s="26" t="n">
-        <v>-203</v>
+        <v>-233</v>
       </c>
       <c r="M39" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.429185</v>
       </c>
       <c r="N39" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.6997</v>
       </c>
       <c r="O39" s="28" t="n">
-        <v>0.616374</v>
+        <v>0.680308</v>
       </c>
       <c r="P39" s="28" t="n"/>
       <c r="Q39" s="28" t="n">
-        <v>-0.053593</v>
+        <v>-0.019392</v>
       </c>
       <c r="R39" s="26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S39" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T39" s="24" t="inlineStr">
         <is>
@@ -12133,7 +12177,7 @@
       <c r="AD39" s="24" t="n"/>
       <c r="AE39" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-mta-bmb-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
         </is>
       </c>
       <c r="AF39" s="31" t="inlineStr">
@@ -12174,17 +12218,17 @@
       </c>
       <c r="AP39" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AQ39" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AR39" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AS39" s="24" t="inlineStr">
@@ -12217,7 +12261,7 @@
       </c>
       <c r="BA39" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB39" s="24" t="inlineStr">
@@ -12232,7 +12276,7 @@
       </c>
       <c r="BD39" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE39" s="24" t="inlineStr">
@@ -12252,7 +12296,7 @@
       </c>
       <c r="BH39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:25.920075Z</t>
+          <t>2026-08-02T16:14:58.340278Z</t>
         </is>
       </c>
       <c r="BI39" s="24" t="inlineStr">
@@ -12262,13 +12306,13 @@
       </c>
       <c r="BJ39" s="25" t="n"/>
       <c r="BK39" s="26" t="n">
-        <v>-203</v>
+        <v>-233</v>
       </c>
       <c r="BL39" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.429185</v>
       </c>
       <c r="BM39" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.6997</v>
       </c>
       <c r="BN39" s="28" t="n"/>
       <c r="BO39" s="28" t="n"/>
@@ -12298,7 +12342,8 @@
       <c r="CM39" s="24" t="n"/>
       <c r="CN39" s="24" t="n"/>
       <c r="CO39" s="24" t="n"/>
-      <c r="CP39" s="24" t="inlineStr">
+      <c r="CP39" s="24" t="n"/>
+      <c r="CQ39" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -12307,12 +12352,12 @@
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>a975d9cc6cd1438a</t>
+          <t>3bec5ce3b31644d1</t>
         </is>
       </c>
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
@@ -12357,23 +12402,23 @@
         </is>
       </c>
       <c r="L40" s="26" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="M40" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.561798</v>
       </c>
       <c r="N40" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.640288</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>0.684497</v>
+        <v>0.6842009999999999</v>
       </c>
       <c r="P40" s="28" t="n"/>
       <c r="Q40" s="28" t="n">
-        <v>0.054867</v>
+        <v>0.043913</v>
       </c>
       <c r="R40" s="26" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="S40" s="29" t="n">
         <v>2</v>
@@ -12399,7 +12444,7 @@
       <c r="AD40" s="24" t="n"/>
       <c r="AE40" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-bw-ff-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-bw-ff-2026-08-02).</t>
         </is>
       </c>
       <c r="AF40" s="31" t="inlineStr">
@@ -12483,7 +12528,7 @@
       </c>
       <c r="BA40" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB40" s="24" t="inlineStr">
@@ -12498,7 +12543,7 @@
       </c>
       <c r="BD40" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE40" s="24" t="inlineStr">
@@ -12518,7 +12563,7 @@
       </c>
       <c r="BH40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:26.448910Z</t>
+          <t>2026-08-02T16:14:58.893489Z</t>
         </is>
       </c>
       <c r="BI40" s="24" t="inlineStr">
@@ -12528,13 +12573,13 @@
       </c>
       <c r="BJ40" s="25" t="n"/>
       <c r="BK40" s="26" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="BL40" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.561798</v>
       </c>
       <c r="BM40" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.640288</v>
       </c>
       <c r="BN40" s="28" t="n"/>
       <c r="BO40" s="28" t="n"/>
@@ -12564,7 +12609,8 @@
       <c r="CM40" s="24" t="n"/>
       <c r="CN40" s="24" t="n"/>
       <c r="CO40" s="24" t="n"/>
-      <c r="CP40" s="24" t="inlineStr">
+      <c r="CP40" s="24" t="n"/>
+      <c r="CQ40" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -12573,22 +12619,22 @@
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>b1eff2d834ee4531</t>
+          <t>2fbf53bfe5054b4a</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:00:00Z</t>
+          <t>2026-08-02T17:00:00Z</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>69289</t>
+          <t>69679</t>
         </is>
       </c>
       <c r="E41" s="24" t="inlineStr">
@@ -12598,12 +12644,12 @@
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="G41" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>DragonClaw</t>
         </is>
       </c>
       <c r="H41" s="24" t="inlineStr">
@@ -12623,26 +12669,26 @@
         </is>
       </c>
       <c r="L41" s="26" t="n">
-        <v>138</v>
+        <v>-233</v>
       </c>
       <c r="M41" s="27" t="n">
-        <v>2.38</v>
+        <v>1.429185</v>
       </c>
       <c r="N41" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.6997</v>
       </c>
       <c r="O41" s="28" t="n">
-        <v>0.51088</v>
+        <v>0.632201</v>
       </c>
       <c r="P41" s="28" t="n"/>
       <c r="Q41" s="28" t="n">
-        <v>0.090712</v>
+        <v>-0.067499</v>
       </c>
       <c r="R41" s="26" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="S41" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T41" s="24" t="inlineStr">
         <is>
@@ -12665,7 +12711,7 @@
       <c r="AD41" s="24" t="n"/>
       <c r="AE41" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-cs2-shin-bst-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-cs2-dc-nvo-2026-08-02).</t>
         </is>
       </c>
       <c r="AF41" s="31" t="inlineStr">
@@ -12706,32 +12752,32 @@
       </c>
       <c r="AP41" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AQ41" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AR41" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>Noir Verse</t>
         </is>
       </c>
       <c r="AS41" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>DragonClaw</t>
         </is>
       </c>
       <c r="AT41" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>DragonClaw</t>
         </is>
       </c>
       <c r="AU41" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>DragonClaw</t>
         </is>
       </c>
       <c r="AV41" s="24" t="n"/>
@@ -12749,7 +12795,7 @@
       </c>
       <c r="BA41" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB41" s="24" t="inlineStr">
@@ -12764,7 +12810,7 @@
       </c>
       <c r="BD41" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE41" s="24" t="inlineStr">
@@ -12784,7 +12830,7 @@
       </c>
       <c r="BH41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:27.457693Z</t>
+          <t>2026-08-02T16:15:00.014811Z</t>
         </is>
       </c>
       <c r="BI41" s="24" t="inlineStr">
@@ -12794,13 +12840,13 @@
       </c>
       <c r="BJ41" s="25" t="n"/>
       <c r="BK41" s="26" t="n">
-        <v>138</v>
+        <v>-233</v>
       </c>
       <c r="BL41" s="27" t="n">
-        <v>2.38</v>
+        <v>1.429185</v>
       </c>
       <c r="BM41" s="28" t="n">
-        <v>0.420168</v>
+        <v>0.6997</v>
       </c>
       <c r="BN41" s="28" t="n"/>
       <c r="BO41" s="28" t="n"/>
@@ -12830,31 +12876,32 @@
       <c r="CM41" s="24" t="n"/>
       <c r="CN41" s="24" t="n"/>
       <c r="CO41" s="24" t="n"/>
-      <c r="CP41" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CP41" s="24" t="n"/>
+      <c r="CQ41" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>4cc088e9a58a432c</t>
+          <t>99b0c3dddef84564</t>
         </is>
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:15:00Z</t>
+          <t>2026-08-02T18:00:00Z</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>67576</t>
+          <t>69289</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
@@ -12864,12 +12911,12 @@
       </c>
       <c r="F42" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="G42" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="H42" s="24" t="inlineStr">
@@ -12889,26 +12936,26 @@
         </is>
       </c>
       <c r="L42" s="26" t="n">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="M42" s="27" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="N42" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.4</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>0.579723</v>
+        <v>0.510807</v>
       </c>
       <c r="P42" s="28" t="n"/>
       <c r="Q42" s="28" t="n">
-        <v>0.139194</v>
+        <v>0.110807</v>
       </c>
       <c r="R42" s="26" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="S42" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T42" s="24" t="inlineStr">
         <is>
@@ -12931,7 +12978,7 @@
       <c r="AD42" s="24" t="n"/>
       <c r="AE42" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-shin-bst-2026-08-02).</t>
         </is>
       </c>
       <c r="AF42" s="31" t="inlineStr">
@@ -12967,37 +13014,37 @@
       </c>
       <c r="AO42" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP42" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AQ42" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AR42" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AS42" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="AT42" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="AU42" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="AV42" s="24" t="n"/>
@@ -13015,7 +13062,7 @@
       </c>
       <c r="BA42" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB42" s="24" t="inlineStr">
@@ -13030,7 +13077,7 @@
       </c>
       <c r="BD42" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE42" s="24" t="inlineStr">
@@ -13050,7 +13097,7 @@
       </c>
       <c r="BH42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:27.987395Z</t>
+          <t>2026-08-02T16:15:01.130828Z</t>
         </is>
       </c>
       <c r="BI42" s="24" t="inlineStr">
@@ -13060,13 +13107,13 @@
       </c>
       <c r="BJ42" s="25" t="n"/>
       <c r="BK42" s="26" t="n">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="BL42" s="27" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="BM42" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.4</v>
       </c>
       <c r="BN42" s="28" t="n"/>
       <c r="BO42" s="28" t="n"/>
@@ -13096,7 +13143,8 @@
       <c r="CM42" s="24" t="n"/>
       <c r="CN42" s="24" t="n"/>
       <c r="CO42" s="24" t="n"/>
-      <c r="CP42" s="24" t="inlineStr">
+      <c r="CP42" s="24" t="n"/>
+      <c r="CQ42" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -13105,12 +13153,12 @@
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>dcd060b9a66d4474</t>
+          <t>c16eb6a46e7b4b0e</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
@@ -13120,7 +13168,7 @@
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>67577</t>
+          <t>67576</t>
         </is>
       </c>
       <c r="E43" s="24" t="inlineStr">
@@ -13130,12 +13178,12 @@
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="G43" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="H43" s="24" t="inlineStr">
@@ -13155,26 +13203,26 @@
         </is>
       </c>
       <c r="L43" s="26" t="n">
-        <v>-156</v>
+        <v>127</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>1.641026</v>
+        <v>2.27</v>
       </c>
       <c r="N43" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.440529</v>
       </c>
       <c r="O43" s="28" t="n">
-        <v>0.5270280000000001</v>
+        <v>0.57955</v>
       </c>
       <c r="P43" s="28" t="n"/>
       <c r="Q43" s="28" t="n">
-        <v>-0.082347</v>
+        <v>0.139021</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S43" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T43" s="24" t="inlineStr">
         <is>
@@ -13197,7 +13245,7 @@
       <c r="AD43" s="24" t="n"/>
       <c r="AE43" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
         </is>
       </c>
       <c r="AF43" s="31" t="inlineStr">
@@ -13238,32 +13286,32 @@
       </c>
       <c r="AP43" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AQ43" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AR43" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AS43" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AT43" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AU43" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AV43" s="24" t="n"/>
@@ -13281,7 +13329,7 @@
       </c>
       <c r="BA43" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB43" s="24" t="inlineStr">
@@ -13296,7 +13344,7 @@
       </c>
       <c r="BD43" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE43" s="24" t="inlineStr">
@@ -13316,7 +13364,7 @@
       </c>
       <c r="BH43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:28.508356Z</t>
+          <t>2026-08-02T16:15:01.749745Z</t>
         </is>
       </c>
       <c r="BI43" s="24" t="inlineStr">
@@ -13326,13 +13374,13 @@
       </c>
       <c r="BJ43" s="25" t="n"/>
       <c r="BK43" s="26" t="n">
-        <v>-156</v>
+        <v>127</v>
       </c>
       <c r="BL43" s="27" t="n">
-        <v>1.641026</v>
+        <v>2.27</v>
       </c>
       <c r="BM43" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.440529</v>
       </c>
       <c r="BN43" s="28" t="n"/>
       <c r="BO43" s="28" t="n"/>
@@ -13362,31 +13410,32 @@
       <c r="CM43" s="24" t="n"/>
       <c r="CN43" s="24" t="n"/>
       <c r="CO43" s="24" t="n"/>
-      <c r="CP43" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CP43" s="24" t="n"/>
+      <c r="CQ43" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>8b565a880bc641fd</t>
+          <t>a537748a25784e56</t>
         </is>
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T08:00:00Z</t>
+          <t>2026-08-02T19:15:00Z</t>
         </is>
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>68288</t>
+          <t>67577</t>
         </is>
       </c>
       <c r="E44" s="24" t="inlineStr">
@@ -13396,12 +13445,12 @@
       </c>
       <c r="F44" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="G44" s="24" t="inlineStr">
         <is>
-          <t>WW Team</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="H44" s="24" t="inlineStr">
@@ -13411,7 +13460,7 @@
       </c>
       <c r="I44" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J44" s="25" t="n"/>
@@ -13421,26 +13470,26 @@
         </is>
       </c>
       <c r="L44" s="26" t="n">
-        <v>156</v>
+        <v>-156</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>2.56</v>
+        <v>1.641026</v>
       </c>
       <c r="N44" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.609375</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>0.704469</v>
+        <v>0.526936</v>
       </c>
       <c r="P44" s="28" t="n"/>
       <c r="Q44" s="28" t="n">
-        <v>0.313844</v>
+        <v>-0.082439</v>
       </c>
       <c r="R44" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S44" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T44" s="24" t="inlineStr">
         <is>
@@ -13463,7 +13512,7 @@
       <c r="AD44" s="24" t="n"/>
       <c r="AE44" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-cs2-ww-cshp-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
         </is>
       </c>
       <c r="AF44" s="31" t="inlineStr">
@@ -13504,32 +13553,32 @@
       </c>
       <c r="AP44" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AQ44" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AR44" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AS44" s="24" t="inlineStr">
         <is>
-          <t>WW Team</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AT44" s="24" t="inlineStr">
         <is>
-          <t>WW Team</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AU44" s="24" t="inlineStr">
         <is>
-          <t>WW Team</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AV44" s="24" t="n"/>
@@ -13547,7 +13596,7 @@
       </c>
       <c r="BA44" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB44" s="24" t="inlineStr">
@@ -13562,7 +13611,7 @@
       </c>
       <c r="BD44" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE44" s="24" t="inlineStr">
@@ -13582,7 +13631,7 @@
       </c>
       <c r="BH44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:29.628121Z</t>
+          <t>2026-08-02T16:15:02.236713Z</t>
         </is>
       </c>
       <c r="BI44" s="24" t="inlineStr">
@@ -13592,13 +13641,13 @@
       </c>
       <c r="BJ44" s="25" t="n"/>
       <c r="BK44" s="26" t="n">
-        <v>156</v>
+        <v>-156</v>
       </c>
       <c r="BL44" s="27" t="n">
-        <v>2.56</v>
+        <v>1.641026</v>
       </c>
       <c r="BM44" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.609375</v>
       </c>
       <c r="BN44" s="28" t="n"/>
       <c r="BO44" s="28" t="n"/>
@@ -13628,31 +13677,32 @@
       <c r="CM44" s="24" t="n"/>
       <c r="CN44" s="24" t="n"/>
       <c r="CO44" s="24" t="n"/>
-      <c r="CP44" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CP44" s="24" t="n"/>
+      <c r="CQ44" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>29fd0577e0e047f2</t>
+          <t>8f3af3ca9e3a4409</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-03T08:00:00Z</t>
         </is>
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>67510</t>
+          <t>68288</t>
         </is>
       </c>
       <c r="E45" s="24" t="inlineStr">
@@ -13662,12 +13712,12 @@
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>CYBERSHOKE Prospects</t>
         </is>
       </c>
       <c r="G45" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>WW Team</t>
         </is>
       </c>
       <c r="H45" s="24" t="inlineStr">
@@ -13677,7 +13727,7 @@
       </c>
       <c r="I45" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J45" s="25" t="n"/>
@@ -13687,26 +13737,26 @@
         </is>
       </c>
       <c r="L45" s="26" t="n">
-        <v>-223</v>
+        <v>186</v>
       </c>
       <c r="M45" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.86</v>
       </c>
       <c r="N45" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.34965</v>
       </c>
       <c r="O45" s="28" t="n">
-        <v>0.56316</v>
+        <v>0.7042350000000001</v>
       </c>
       <c r="P45" s="28" t="n"/>
       <c r="Q45" s="28" t="n">
-        <v>-0.127242</v>
+        <v>0.354585</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S45" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T45" s="24" t="inlineStr">
         <is>
@@ -13729,7 +13779,7 @@
       <c r="AD45" s="24" t="n"/>
       <c r="AE45" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-cs2-ww-cshp-2026-08-03).</t>
         </is>
       </c>
       <c r="AF45" s="31" t="inlineStr">
@@ -13765,37 +13815,37 @@
       </c>
       <c r="AO45" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP45" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>CYBERSHOKE Prospects</t>
         </is>
       </c>
       <c r="AQ45" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>CYBERSHOKE Prospects</t>
         </is>
       </c>
       <c r="AR45" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>CYBERSHOKE Prospects</t>
         </is>
       </c>
       <c r="AS45" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>WW Team</t>
         </is>
       </c>
       <c r="AT45" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>WW Team</t>
         </is>
       </c>
       <c r="AU45" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>WW Team</t>
         </is>
       </c>
       <c r="AV45" s="24" t="n"/>
@@ -13813,7 +13863,7 @@
       </c>
       <c r="BA45" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB45" s="24" t="inlineStr">
@@ -13828,7 +13878,7 @@
       </c>
       <c r="BD45" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE45" s="24" t="inlineStr">
@@ -13848,7 +13898,7 @@
       </c>
       <c r="BH45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:31.160500Z</t>
+          <t>2026-08-02T16:15:03.660648Z</t>
         </is>
       </c>
       <c r="BI45" s="24" t="inlineStr">
@@ -13858,13 +13908,13 @@
       </c>
       <c r="BJ45" s="25" t="n"/>
       <c r="BK45" s="26" t="n">
-        <v>-223</v>
+        <v>186</v>
       </c>
       <c r="BL45" s="27" t="n">
-        <v>1.44843</v>
+        <v>2.86</v>
       </c>
       <c r="BM45" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.34965</v>
       </c>
       <c r="BN45" s="28" t="n"/>
       <c r="BO45" s="28" t="n"/>
@@ -13894,21 +13944,22 @@
       <c r="CM45" s="24" t="n"/>
       <c r="CN45" s="24" t="n"/>
       <c r="CO45" s="24" t="n"/>
-      <c r="CP45" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CP45" s="24" t="n"/>
+      <c r="CQ45" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>0cc692592b584103</t>
+          <t>f7d84bedbe6b465c</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
@@ -13962,11 +14013,11 @@
         <v>0.579832</v>
       </c>
       <c r="O46" s="28" t="n">
-        <v>0.599394</v>
+        <v>0.599195</v>
       </c>
       <c r="P46" s="28" t="n"/>
       <c r="Q46" s="28" t="n">
-        <v>0.019562</v>
+        <v>0.019363</v>
       </c>
       <c r="R46" s="26" t="n">
         <v>30</v>
@@ -14079,7 +14130,7 @@
       </c>
       <c r="BA46" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB46" s="24" t="inlineStr">
@@ -14094,7 +14145,7 @@
       </c>
       <c r="BD46" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE46" s="24" t="inlineStr">
@@ -14114,7 +14165,7 @@
       </c>
       <c r="BH46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:31.676274Z</t>
+          <t>2026-08-02T16:15:04.678326Z</t>
         </is>
       </c>
       <c r="BI46" s="24" t="inlineStr">
@@ -14160,7 +14211,8 @@
       <c r="CM46" s="24" t="n"/>
       <c r="CN46" s="24" t="n"/>
       <c r="CO46" s="24" t="n"/>
-      <c r="CP46" s="24" t="inlineStr">
+      <c r="CP46" s="24" t="n"/>
+      <c r="CQ46" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -14169,22 +14221,22 @@
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>b4129a3a513c483d</t>
+          <t>dffbe7e4fcdf4368</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T11:00:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>69267</t>
+          <t>67510</t>
         </is>
       </c>
       <c r="E47" s="24" t="inlineStr">
@@ -14194,12 +14246,12 @@
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr">
@@ -14219,26 +14271,26 @@
         </is>
       </c>
       <c r="L47" s="26" t="n">
-        <v>-213</v>
+        <v>-223</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.44843</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.690402</v>
       </c>
       <c r="O47" s="28" t="n">
-        <v>0.62913</v>
+        <v>0.563014</v>
       </c>
       <c r="P47" s="28" t="n"/>
       <c r="Q47" s="28" t="n">
-        <v>-0.051381</v>
+        <v>-0.127388</v>
       </c>
       <c r="R47" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S47" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T47" s="24" t="inlineStr">
         <is>
@@ -14261,7 +14313,7 @@
       <c r="AD47" s="24" t="n"/>
       <c r="AE47" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jpu-lk-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
         </is>
       </c>
       <c r="AF47" s="31" t="inlineStr">
@@ -14302,32 +14354,32 @@
       </c>
       <c r="AP47" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AQ47" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AR47" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AS47" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AT47" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AU47" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AV47" s="24" t="n"/>
@@ -14345,7 +14397,7 @@
       </c>
       <c r="BA47" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB47" s="24" t="inlineStr">
@@ -14360,7 +14412,7 @@
       </c>
       <c r="BD47" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE47" s="24" t="inlineStr">
@@ -14380,7 +14432,7 @@
       </c>
       <c r="BH47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:34.287196Z</t>
+          <t>2026-08-02T16:15:05.206115Z</t>
         </is>
       </c>
       <c r="BI47" s="24" t="inlineStr">
@@ -14390,13 +14442,13 @@
       </c>
       <c r="BJ47" s="25" t="n"/>
       <c r="BK47" s="26" t="n">
-        <v>-213</v>
+        <v>-223</v>
       </c>
       <c r="BL47" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.44843</v>
       </c>
       <c r="BM47" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.690402</v>
       </c>
       <c r="BN47" s="28" t="n"/>
       <c r="BO47" s="28" t="n"/>
@@ -14426,7 +14478,8 @@
       <c r="CM47" s="24" t="n"/>
       <c r="CN47" s="24" t="n"/>
       <c r="CO47" s="24" t="n"/>
-      <c r="CP47" s="24" t="inlineStr">
+      <c r="CP47" s="24" t="n"/>
+      <c r="CQ47" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -14435,12 +14488,12 @@
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>28dc3f7209da4b8c</t>
+          <t>3fc885d5fb374d1f</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
@@ -14450,7 +14503,7 @@
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>69135</t>
+          <t>69267</t>
         </is>
       </c>
       <c r="E48" s="24" t="inlineStr">
@@ -14460,12 +14513,12 @@
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>ex-RUBY</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
-          <t>1WIN</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="H48" s="24" t="inlineStr">
@@ -14485,26 +14538,26 @@
         </is>
       </c>
       <c r="L48" s="26" t="n">
-        <v>-163</v>
+        <v>-213</v>
       </c>
       <c r="M48" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.469484</v>
       </c>
       <c r="N48" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.680511</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>0.527344</v>
+        <v>0.628883</v>
       </c>
       <c r="P48" s="28" t="n"/>
       <c r="Q48" s="28" t="n">
-        <v>-0.092428</v>
+        <v>-0.051628</v>
       </c>
       <c r="R48" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S48" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T48" s="24" t="inlineStr">
         <is>
@@ -14527,7 +14580,7 @@
       <c r="AD48" s="24" t="n"/>
       <c r="AE48" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-1win-exruby-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jpu-lk-2026-08-03).</t>
         </is>
       </c>
       <c r="AF48" s="31" t="inlineStr">
@@ -14568,32 +14621,32 @@
       </c>
       <c r="AP48" s="24" t="inlineStr">
         <is>
-          <t>ex-RUBY</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AQ48" s="24" t="inlineStr">
         <is>
-          <t>ex-RUBY</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AR48" s="24" t="inlineStr">
         <is>
-          <t>ex-RUBY</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AS48" s="24" t="inlineStr">
         <is>
-          <t>1WIN</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AT48" s="24" t="inlineStr">
         <is>
-          <t>1WIN</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AU48" s="24" t="inlineStr">
         <is>
-          <t>1WIN</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AV48" s="24" t="n"/>
@@ -14611,7 +14664,7 @@
       </c>
       <c r="BA48" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB48" s="24" t="inlineStr">
@@ -14626,7 +14679,7 @@
       </c>
       <c r="BD48" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE48" s="24" t="inlineStr">
@@ -14646,7 +14699,7 @@
       </c>
       <c r="BH48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:34.811836Z</t>
+          <t>2026-08-02T16:15:07.681014Z</t>
         </is>
       </c>
       <c r="BI48" s="24" t="inlineStr">
@@ -14656,13 +14709,13 @@
       </c>
       <c r="BJ48" s="25" t="n"/>
       <c r="BK48" s="26" t="n">
-        <v>-163</v>
+        <v>-213</v>
       </c>
       <c r="BL48" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.469484</v>
       </c>
       <c r="BM48" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.680511</v>
       </c>
       <c r="BN48" s="28" t="n"/>
       <c r="BO48" s="28" t="n"/>
@@ -14692,7 +14745,8 @@
       <c r="CM48" s="24" t="n"/>
       <c r="CN48" s="24" t="n"/>
       <c r="CO48" s="24" t="n"/>
-      <c r="CP48" s="24" t="inlineStr">
+      <c r="CP48" s="24" t="n"/>
+      <c r="CQ48" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -14701,12 +14755,12 @@
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>e4e741f10bd84db0</t>
+          <t>8d5696a8efae4319</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
@@ -14716,7 +14770,7 @@
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>67578</t>
+          <t>69135</t>
         </is>
       </c>
       <c r="E49" s="24" t="inlineStr">
@@ -14726,12 +14780,12 @@
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr">
@@ -14751,20 +14805,20 @@
         </is>
       </c>
       <c r="L49" s="26" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="M49" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.641026</v>
       </c>
       <c r="N49" s="28" t="n">
-        <v>0.6</v>
+        <v>0.609375</v>
       </c>
       <c r="O49" s="28" t="n">
-        <v>0.5270280000000001</v>
+        <v>0.527254</v>
       </c>
       <c r="P49" s="28" t="n"/>
       <c r="Q49" s="28" t="n">
-        <v>-0.072972</v>
+        <v>-0.082121</v>
       </c>
       <c r="R49" s="26" t="n">
         <v>0</v>
@@ -14793,7 +14847,7 @@
       <c r="AD49" s="24" t="n"/>
       <c r="AE49" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-1win-exruby-2026-08-03).</t>
         </is>
       </c>
       <c r="AF49" s="31" t="inlineStr">
@@ -14829,37 +14883,37 @@
       </c>
       <c r="AO49" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP49" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AQ49" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AR49" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AS49" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="AT49" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="AU49" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="AV49" s="24" t="n"/>
@@ -14877,7 +14931,7 @@
       </c>
       <c r="BA49" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB49" s="24" t="inlineStr">
@@ -14892,7 +14946,7 @@
       </c>
       <c r="BD49" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE49" s="24" t="inlineStr">
@@ -14912,7 +14966,7 @@
       </c>
       <c r="BH49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:35.357223Z</t>
+          <t>2026-08-02T16:15:08.249635Z</t>
         </is>
       </c>
       <c r="BI49" s="24" t="inlineStr">
@@ -14922,13 +14976,13 @@
       </c>
       <c r="BJ49" s="25" t="n"/>
       <c r="BK49" s="26" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="BL49" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.641026</v>
       </c>
       <c r="BM49" s="28" t="n">
-        <v>0.6</v>
+        <v>0.609375</v>
       </c>
       <c r="BN49" s="28" t="n"/>
       <c r="BO49" s="28" t="n"/>
@@ -14958,7 +15012,8 @@
       <c r="CM49" s="24" t="n"/>
       <c r="CN49" s="24" t="n"/>
       <c r="CO49" s="24" t="n"/>
-      <c r="CP49" s="24" t="inlineStr">
+      <c r="CP49" s="24" t="n"/>
+      <c r="CQ49" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -14967,22 +15022,22 @@
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>f4969aeb2da94d49</t>
+          <t>58de58897ee54660</t>
         </is>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T13:45:00Z</t>
+          <t>2026-08-03T11:00:00Z</t>
         </is>
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>67579</t>
+          <t>67578</t>
         </is>
       </c>
       <c r="E50" s="24" t="inlineStr">
@@ -14992,12 +15047,12 @@
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr">
@@ -15007,7 +15062,7 @@
       </c>
       <c r="I50" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J50" s="25" t="n"/>
@@ -15017,23 +15072,23 @@
         </is>
       </c>
       <c r="L50" s="26" t="n">
-        <v>194</v>
+        <v>-150</v>
       </c>
       <c r="M50" s="27" t="n">
-        <v>2.94</v>
+        <v>1.666667</v>
       </c>
       <c r="N50" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.6</v>
       </c>
       <c r="O50" s="28" t="n">
-        <v>0.526276</v>
+        <v>0.526936</v>
       </c>
       <c r="P50" s="28" t="n"/>
       <c r="Q50" s="28" t="n">
-        <v>0.18614</v>
+        <v>-0.073064</v>
       </c>
       <c r="R50" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S50" s="29" t="n">
         <v>1</v>
@@ -15059,7 +15114,7 @@
       <c r="AD50" s="24" t="n"/>
       <c r="AE50" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
         </is>
       </c>
       <c r="AF50" s="31" t="inlineStr">
@@ -15100,32 +15155,32 @@
       </c>
       <c r="AP50" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AQ50" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AR50" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AS50" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AT50" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AU50" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AV50" s="24" t="n"/>
@@ -15143,7 +15198,7 @@
       </c>
       <c r="BA50" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB50" s="24" t="inlineStr">
@@ -15158,7 +15213,7 @@
       </c>
       <c r="BD50" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE50" s="24" t="inlineStr">
@@ -15178,7 +15233,7 @@
       </c>
       <c r="BH50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:35.908816Z</t>
+          <t>2026-08-02T16:15:08.773065Z</t>
         </is>
       </c>
       <c r="BI50" s="24" t="inlineStr">
@@ -15188,13 +15243,13 @@
       </c>
       <c r="BJ50" s="25" t="n"/>
       <c r="BK50" s="26" t="n">
-        <v>194</v>
+        <v>-150</v>
       </c>
       <c r="BL50" s="27" t="n">
-        <v>2.94</v>
+        <v>1.666667</v>
       </c>
       <c r="BM50" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.6</v>
       </c>
       <c r="BN50" s="28" t="n"/>
       <c r="BO50" s="28" t="n"/>
@@ -15224,31 +15279,32 @@
       <c r="CM50" s="24" t="n"/>
       <c r="CN50" s="24" t="n"/>
       <c r="CO50" s="24" t="n"/>
-      <c r="CP50" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CP50" s="24" t="n"/>
+      <c r="CQ50" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>1cffdca8c7bc4808</t>
+          <t>524fb6f75b7e4bb1</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T14:00:00Z</t>
+          <t>2026-08-03T13:45:00Z</t>
         </is>
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>68292</t>
+          <t>67579</t>
         </is>
       </c>
       <c r="E51" s="24" t="inlineStr">
@@ -15258,12 +15314,12 @@
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
-          <t>ARCRED</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="H51" s="24" t="inlineStr">
@@ -15273,7 +15329,7 @@
       </c>
       <c r="I51" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J51" s="25" t="n"/>
@@ -15283,26 +15339,26 @@
         </is>
       </c>
       <c r="L51" s="26" t="n">
-        <v>-186</v>
+        <v>194</v>
       </c>
       <c r="M51" s="27" t="n">
-        <v>1.537634</v>
+        <v>2.94</v>
       </c>
       <c r="N51" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.340136</v>
       </c>
       <c r="O51" s="28" t="n">
-        <v>0.614071</v>
+        <v>0.5262829999999999</v>
       </c>
       <c r="P51" s="28" t="n"/>
       <c r="Q51" s="28" t="n">
-        <v>-0.036279</v>
+        <v>0.186147</v>
       </c>
       <c r="R51" s="26" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="S51" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T51" s="24" t="inlineStr">
         <is>
@@ -15325,7 +15381,7 @@
       <c r="AD51" s="24" t="n"/>
       <c r="AE51" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-cs2-arc-btf-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
         </is>
       </c>
       <c r="AF51" s="31" t="inlineStr">
@@ -15361,37 +15417,37 @@
       </c>
       <c r="AO51" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP51" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AQ51" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AR51" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AS51" s="24" t="inlineStr">
         <is>
-          <t>ARCRED</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AT51" s="24" t="inlineStr">
         <is>
-          <t>ARCRED</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AU51" s="24" t="inlineStr">
         <is>
-          <t>ARCRED</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AV51" s="24" t="n"/>
@@ -15409,7 +15465,7 @@
       </c>
       <c r="BA51" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB51" s="24" t="inlineStr">
@@ -15424,7 +15480,7 @@
       </c>
       <c r="BD51" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE51" s="24" t="inlineStr">
@@ -15444,7 +15500,7 @@
       </c>
       <c r="BH51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:36.873973Z</t>
+          <t>2026-08-02T16:15:09.305570Z</t>
         </is>
       </c>
       <c r="BI51" s="24" t="inlineStr">
@@ -15454,13 +15510,13 @@
       </c>
       <c r="BJ51" s="25" t="n"/>
       <c r="BK51" s="26" t="n">
-        <v>-186</v>
+        <v>194</v>
       </c>
       <c r="BL51" s="27" t="n">
-        <v>1.537634</v>
+        <v>2.94</v>
       </c>
       <c r="BM51" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.340136</v>
       </c>
       <c r="BN51" s="28" t="n"/>
       <c r="BO51" s="28" t="n"/>
@@ -15490,21 +15546,22 @@
       <c r="CM51" s="24" t="n"/>
       <c r="CN51" s="24" t="n"/>
       <c r="CO51" s="24" t="n"/>
-      <c r="CP51" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CP51" s="24" t="n"/>
+      <c r="CQ51" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>9369df9452e344ef</t>
+          <t>13cd0b530de04f9a</t>
         </is>
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
@@ -15514,7 +15571,7 @@
       </c>
       <c r="D52" s="24" t="inlineStr">
         <is>
-          <t>69268</t>
+          <t>68292</t>
         </is>
       </c>
       <c r="E52" s="24" t="inlineStr">
@@ -15524,12 +15581,12 @@
       </c>
       <c r="F52" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="G52" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>ARCRED</t>
         </is>
       </c>
       <c r="H52" s="24" t="inlineStr">
@@ -15558,17 +15615,17 @@
         <v>0.640288</v>
       </c>
       <c r="O52" s="28" t="n">
-        <v>0.6819730000000001</v>
+        <v>0.6138479999999999</v>
       </c>
       <c r="P52" s="28" t="n"/>
       <c r="Q52" s="28" t="n">
-        <v>0.041685</v>
+        <v>-0.02644</v>
       </c>
       <c r="R52" s="26" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="S52" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T52" s="24" t="inlineStr">
         <is>
@@ -15591,7 +15648,7 @@
       <c r="AD52" s="24" t="n"/>
       <c r="AE52" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-arc-btf-2026-08-03).</t>
         </is>
       </c>
       <c r="AF52" s="31" t="inlineStr">
@@ -15609,7 +15666,7 @@
       <c r="AJ52" s="31" t="n"/>
       <c r="AK52" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL52" s="26" t="n">
@@ -15617,47 +15674,47 @@
       </c>
       <c r="AM52" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN52" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO52" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP52" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AQ52" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AR52" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AS52" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>ARCRED</t>
         </is>
       </c>
       <c r="AT52" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>ARCRED</t>
         </is>
       </c>
       <c r="AU52" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>ARCRED</t>
         </is>
       </c>
       <c r="AV52" s="24" t="n"/>
@@ -15675,7 +15732,7 @@
       </c>
       <c r="BA52" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB52" s="24" t="inlineStr">
@@ -15690,7 +15747,7 @@
       </c>
       <c r="BD52" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE52" s="24" t="inlineStr">
@@ -15710,7 +15767,7 @@
       </c>
       <c r="BH52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:37.423413Z</t>
+          <t>2026-08-02T16:15:09.759475Z</t>
         </is>
       </c>
       <c r="BI52" s="24" t="inlineStr">
@@ -15756,31 +15813,32 @@
       <c r="CM52" s="24" t="n"/>
       <c r="CN52" s="24" t="n"/>
       <c r="CO52" s="24" t="n"/>
-      <c r="CP52" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CP52" s="24" t="n"/>
+      <c r="CQ52" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>495eaed7b34a4c93</t>
+          <t>29fb553152eb4466</t>
         </is>
       </c>
       <c r="B53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.323824Z</t>
+          <t>2026-08-02T16:15:14.476529Z</t>
         </is>
       </c>
       <c r="C53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T23:00:00Z</t>
+          <t>2026-08-03T14:00:00Z</t>
         </is>
       </c>
       <c r="D53" s="24" t="inlineStr">
         <is>
-          <t>68043</t>
+          <t>69268</t>
         </is>
       </c>
       <c r="E53" s="24" t="inlineStr">
@@ -15790,12 +15848,12 @@
       </c>
       <c r="F53" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="G53" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="H53" s="24" t="inlineStr">
@@ -15815,26 +15873,26 @@
         </is>
       </c>
       <c r="L53" s="26" t="n">
-        <v>122</v>
+        <v>-178</v>
       </c>
       <c r="M53" s="27" t="n">
-        <v>2.22</v>
+        <v>1.561798</v>
       </c>
       <c r="N53" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.640288</v>
       </c>
       <c r="O53" s="28" t="n">
-        <v>0.5697990000000001</v>
+        <v>0.662883</v>
       </c>
       <c r="P53" s="28" t="n"/>
       <c r="Q53" s="28" t="n">
-        <v>0.119349</v>
+        <v>0.022595</v>
       </c>
       <c r="R53" s="26" t="n">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="S53" s="29" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="T53" s="24" t="inlineStr">
         <is>
@@ -15857,7 +15915,7 @@
       <c r="AD53" s="24" t="n"/>
       <c r="AE53" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
         </is>
       </c>
       <c r="AF53" s="31" t="inlineStr">
@@ -15875,7 +15933,7 @@
       <c r="AJ53" s="31" t="n"/>
       <c r="AK53" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL53" s="26" t="n">
@@ -15883,47 +15941,47 @@
       </c>
       <c r="AM53" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN53" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO53" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP53" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AQ53" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AR53" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AS53" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AT53" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AU53" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AV53" s="24" t="n"/>
@@ -15941,7 +15999,7 @@
       </c>
       <c r="BA53" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BB53" s="24" t="inlineStr">
@@ -15956,7 +16014,7 @@
       </c>
       <c r="BD53" s="24" t="inlineStr">
         <is>
-          <t>fd9cf8a872a6fb2106f2c32f1ebfcd0ded61283a97c1b08ceb3f2a98e39fcf6d</t>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
         </is>
       </c>
       <c r="BE53" s="24" t="inlineStr">
@@ -15976,7 +16034,7 @@
       </c>
       <c r="BH53" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T15:51:41.320292Z</t>
+          <t>2026-08-02T16:15:10.799851Z</t>
         </is>
       </c>
       <c r="BI53" s="24" t="inlineStr">
@@ -15986,13 +16044,13 @@
       </c>
       <c r="BJ53" s="25" t="n"/>
       <c r="BK53" s="26" t="n">
-        <v>122</v>
+        <v>-178</v>
       </c>
       <c r="BL53" s="27" t="n">
-        <v>2.22</v>
+        <v>1.561798</v>
       </c>
       <c r="BM53" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.640288</v>
       </c>
       <c r="BN53" s="28" t="n"/>
       <c r="BO53" s="28" t="n"/>
@@ -16022,7 +16080,275 @@
       <c r="CM53" s="24" t="n"/>
       <c r="CN53" s="24" t="n"/>
       <c r="CO53" s="24" t="n"/>
-      <c r="CP53" s="24" t="inlineStr">
+      <c r="CP53" s="24" t="n"/>
+      <c r="CQ53" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>02d2fc0ac6f14768</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:14.476529Z</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr">
+        <is>
+          <t>68043</t>
+        </is>
+      </c>
+      <c r="E54" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F54" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="G54" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="H54" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I54" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J54" s="25" t="n"/>
+      <c r="K54" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L54" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M54" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N54" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O54" s="28" t="n">
+        <v>0.569642</v>
+      </c>
+      <c r="P54" s="28" t="n"/>
+      <c r="Q54" s="28" t="n">
+        <v>0.119192</v>
+      </c>
+      <c r="R54" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="S54" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T54" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U54" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V54" s="24" t="n"/>
+      <c r="W54" s="26" t="n"/>
+      <c r="X54" s="26" t="n"/>
+      <c r="Y54" s="25" t="n"/>
+      <c r="Z54" s="26" t="n"/>
+      <c r="AA54" s="28" t="n"/>
+      <c r="AB54" s="28" t="n"/>
+      <c r="AC54" s="30" t="n"/>
+      <c r="AD54" s="24" t="n"/>
+      <c r="AE54" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF54" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG54" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH54" s="24" t="n"/>
+      <c r="AI54" s="31" t="n"/>
+      <c r="AJ54" s="31" t="n"/>
+      <c r="AK54" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL54" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM54" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN54" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO54" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP54" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AQ54" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AR54" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AS54" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AT54" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AU54" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AV54" s="24" t="n"/>
+      <c r="AW54" s="24" t="n"/>
+      <c r="AX54" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY54" s="24" t="n"/>
+      <c r="AZ54" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA54" s="24" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="BB54" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC54" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD54" s="24" t="inlineStr">
+        <is>
+          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+        </is>
+      </c>
+      <c r="BE54" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF54" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG54" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH54" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T16:15:14.474993Z</t>
+        </is>
+      </c>
+      <c r="BI54" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ54" s="25" t="n"/>
+      <c r="BK54" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL54" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM54" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN54" s="28" t="n"/>
+      <c r="BO54" s="28" t="n"/>
+      <c r="BP54" s="25" t="n"/>
+      <c r="BQ54" s="27" t="n"/>
+      <c r="BR54" s="28" t="n"/>
+      <c r="BS54" s="28" t="n"/>
+      <c r="BT54" s="28" t="n"/>
+      <c r="BU54" s="25" t="n"/>
+      <c r="BV54" s="29" t="n"/>
+      <c r="BW54" s="24" t="n"/>
+      <c r="BX54" s="30" t="n"/>
+      <c r="BY54" s="27" t="n"/>
+      <c r="BZ54" s="24" t="n"/>
+      <c r="CA54" s="31" t="n"/>
+      <c r="CB54" s="24" t="n"/>
+      <c r="CC54" s="24" t="n"/>
+      <c r="CD54" s="24" t="n"/>
+      <c r="CE54" s="24" t="n"/>
+      <c r="CF54" s="24" t="n"/>
+      <c r="CG54" s="24" t="n"/>
+      <c r="CH54" s="24" t="n"/>
+      <c r="CI54" s="24" t="n"/>
+      <c r="CJ54" s="24" t="n"/>
+      <c r="CK54" s="24" t="n"/>
+      <c r="CL54" s="24" t="n"/>
+      <c r="CM54" s="24" t="n"/>
+      <c r="CN54" s="24" t="n"/>
+      <c r="CO54" s="24" t="n"/>
+      <c r="CP54" s="24" t="n"/>
+      <c r="CQ54" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ54" headerRowCount="1">
-  <autoFilter ref="A1:CQ54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ52" headerRowCount="1">
+  <autoFilter ref="A1:CQ52"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$54)</f>
+        <f>COUNTA('Picks'!$A$2:$A$52)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$54,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$52,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$54,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$52,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"win")+COUNTIFS('Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")+COUNTIFS('Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$54,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$52,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"win")/(COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"win")+COUNTIFS('Picks'!$BX$2:$BX$54,"&gt;0",'Picks'!$V$2:$V$54,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")/(COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")+COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$54)/SUM('Picks'!$BX$2:$BX$54),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$52)/SUM('Picks'!$BX$2:$BX$52),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$54)</f>
+        <f>SUM('Picks'!$BY$2:$BY$52)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$54,"&lt;&gt;",'Picks'!$AB$2:$AB$54),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$52,"&lt;&gt;",'Picks'!$AB$2:$AB$52),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$54,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$54,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$52,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$52,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$54,'Picks'!$AM$2:$AM$54,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$52,'Picks'!$AM$2:$AM$52,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A14,'Picks'!$U$2:$U$54,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A14,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A14,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$54,'Picks'!$H$2:$H$54,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$54,'Picks'!$H$2:$H$54,$A14,'Picks'!$U$2:$U$54,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A15,'Picks'!$U$2:$U$54,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A15,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A15,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$54,'Picks'!$H$2:$H$54,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$54,'Picks'!$H$2:$H$54,$A15,'Picks'!$U$2:$U$54,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A16,'Picks'!$U$2:$U$54,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A16,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$54,$A16,'Picks'!$U$2:$U$54,"settled",'Picks'!$V$2:$V$54,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$54,'Picks'!$H$2:$H$54,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$54,'Picks'!$H$2:$H$54,$A16,'Picks'!$U$2:$U$54,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ54"/>
+  <dimension ref="A1:CQ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11818,12 +11818,12 @@
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
         <is>
-          <t>f385338f671d4616</t>
+          <t>7905526784ac475b</t>
         </is>
       </c>
       <c r="B38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D38" s="24" t="inlineStr">
         <is>
-          <t>69681</t>
+          <t>69682</t>
         </is>
       </c>
       <c r="E38" s="24" t="inlineStr">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="F38" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="G38" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="H38" s="24" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="I38" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J38" s="25" t="n"/>
@@ -11868,26 +11868,26 @@
         </is>
       </c>
       <c r="L38" s="26" t="n">
-        <v>-223</v>
+        <v>-156</v>
       </c>
       <c r="M38" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.641026</v>
       </c>
       <c r="N38" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.609375</v>
       </c>
       <c r="O38" s="28" t="n">
-        <v>0.616241</v>
+        <v>0.684208</v>
       </c>
       <c r="P38" s="28" t="n"/>
       <c r="Q38" s="28" t="n">
-        <v>-0.074161</v>
+        <v>0.074833</v>
       </c>
       <c r="R38" s="26" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="S38" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T38" s="24" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
       <c r="AD38" s="24" t="n"/>
       <c r="AE38" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mta-bmb-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-bw-ff-2026-08-02).</t>
         </is>
       </c>
       <c r="AF38" s="31" t="inlineStr">
@@ -11946,37 +11946,37 @@
       </c>
       <c r="AO38" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP38" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="AQ38" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="AR38" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Fire Flux Esports</t>
         </is>
       </c>
       <c r="AS38" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="AT38" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="AU38" s="24" t="inlineStr">
         <is>
-          <t>Mai Tai</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="AV38" s="24" t="n"/>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="BA38" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB38" s="24" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="BD38" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE38" s="24" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="BH38" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:57.846727Z</t>
+          <t>2026-08-02T16:53:18.155145Z</t>
         </is>
       </c>
       <c r="BI38" s="24" t="inlineStr">
@@ -12039,13 +12039,13 @@
       </c>
       <c r="BJ38" s="25" t="n"/>
       <c r="BK38" s="26" t="n">
-        <v>-223</v>
+        <v>-156</v>
       </c>
       <c r="BL38" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.641026</v>
       </c>
       <c r="BM38" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.609375</v>
       </c>
       <c r="BN38" s="28" t="n"/>
       <c r="BO38" s="28" t="n"/>
@@ -12078,19 +12078,19 @@
       <c r="CP38" s="24" t="n"/>
       <c r="CQ38" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>3665df6053ba4abb</t>
+          <t>44e35a31d8a14488</t>
         </is>
       </c>
       <c r="B39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
@@ -12135,23 +12135,23 @@
         </is>
       </c>
       <c r="L39" s="26" t="n">
-        <v>-233</v>
+        <v>-194</v>
       </c>
       <c r="M39" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.515464</v>
       </c>
       <c r="N39" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.659864</v>
       </c>
       <c r="O39" s="28" t="n">
-        <v>0.680308</v>
+        <v>0.68024</v>
       </c>
       <c r="P39" s="28" t="n"/>
       <c r="Q39" s="28" t="n">
-        <v>-0.019392</v>
+        <v>0.020376</v>
       </c>
       <c r="R39" s="26" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="S39" s="29" t="n">
         <v>1.75</v>
@@ -12177,7 +12177,7 @@
       <c r="AD39" s="24" t="n"/>
       <c r="AE39" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-cs2-mta-enjoy-2026-08-02).</t>
         </is>
       </c>
       <c r="AF39" s="31" t="inlineStr">
@@ -12195,7 +12195,7 @@
       <c r="AJ39" s="31" t="n"/>
       <c r="AK39" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL39" s="26" t="n">
@@ -12203,17 +12203,17 @@
       </c>
       <c r="AM39" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN39" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO39" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP39" s="24" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="BA39" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB39" s="24" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="BD39" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE39" s="24" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="BH39" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:58.340278Z</t>
+          <t>2026-08-02T16:53:19.829844Z</t>
         </is>
       </c>
       <c r="BI39" s="24" t="inlineStr">
@@ -12306,13 +12306,13 @@
       </c>
       <c r="BJ39" s="25" t="n"/>
       <c r="BK39" s="26" t="n">
-        <v>-233</v>
+        <v>-194</v>
       </c>
       <c r="BL39" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.515464</v>
       </c>
       <c r="BM39" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.659864</v>
       </c>
       <c r="BN39" s="28" t="n"/>
       <c r="BO39" s="28" t="n"/>
@@ -12345,29 +12345,29 @@
       <c r="CP39" s="24" t="n"/>
       <c r="CQ39" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>3bec5ce3b31644d1</t>
+          <t>a73267a4377d41b1</t>
         </is>
       </c>
       <c r="B40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:00:00Z</t>
+          <t>2026-08-02T18:00:00Z</t>
         </is>
       </c>
       <c r="D40" s="24" t="inlineStr">
         <is>
-          <t>69682</t>
+          <t>69289</t>
         </is>
       </c>
       <c r="E40" s="24" t="inlineStr">
@@ -12377,12 +12377,12 @@
       </c>
       <c r="F40" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="G40" s="24" t="inlineStr">
         <is>
-          <t>Bushido Wildcats</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="H40" s="24" t="inlineStr">
@@ -12402,26 +12402,26 @@
         </is>
       </c>
       <c r="L40" s="26" t="n">
-        <v>-178</v>
+        <v>150</v>
       </c>
       <c r="M40" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.5</v>
       </c>
       <c r="N40" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.4</v>
       </c>
       <c r="O40" s="28" t="n">
-        <v>0.6842009999999999</v>
+        <v>0.510848</v>
       </c>
       <c r="P40" s="28" t="n"/>
       <c r="Q40" s="28" t="n">
-        <v>0.043913</v>
+        <v>0.110848</v>
       </c>
       <c r="R40" s="26" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="S40" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T40" s="24" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
       <c r="AD40" s="24" t="n"/>
       <c r="AE40" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-bw-ff-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-shin-bst-2026-08-02).</t>
         </is>
       </c>
       <c r="AF40" s="31" t="inlineStr">
@@ -12480,37 +12480,37 @@
       </c>
       <c r="AO40" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP40" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AQ40" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AR40" s="24" t="inlineStr">
         <is>
-          <t>Fire Flux Esports</t>
+          <t>BESTIA</t>
         </is>
       </c>
       <c r="AS40" s="24" t="inlineStr">
         <is>
-          <t>Bushido Wildcats</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="AT40" s="24" t="inlineStr">
         <is>
-          <t>Bushido Wildcats</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="AU40" s="24" t="inlineStr">
         <is>
-          <t>Bushido Wildcats</t>
+          <t>ShindeN</t>
         </is>
       </c>
       <c r="AV40" s="24" t="n"/>
@@ -12528,7 +12528,7 @@
       </c>
       <c r="BA40" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB40" s="24" t="inlineStr">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="BD40" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE40" s="24" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="BH40" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:14:58.893489Z</t>
+          <t>2026-08-02T16:53:20.304048Z</t>
         </is>
       </c>
       <c r="BI40" s="24" t="inlineStr">
@@ -12573,13 +12573,13 @@
       </c>
       <c r="BJ40" s="25" t="n"/>
       <c r="BK40" s="26" t="n">
-        <v>-178</v>
+        <v>150</v>
       </c>
       <c r="BL40" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.5</v>
       </c>
       <c r="BM40" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.4</v>
       </c>
       <c r="BN40" s="28" t="n"/>
       <c r="BO40" s="28" t="n"/>
@@ -12619,22 +12619,22 @@
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>2fbf53bfe5054b4a</t>
+          <t>7aa6e3ac894d4715</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:00:00Z</t>
+          <t>2026-08-02T19:15:00Z</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>69679</t>
+          <t>67576</t>
         </is>
       </c>
       <c r="E41" s="24" t="inlineStr">
@@ -12644,12 +12644,12 @@
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="G41" s="24" t="inlineStr">
         <is>
-          <t>DragonClaw</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="H41" s="24" t="inlineStr">
@@ -12669,26 +12669,26 @@
         </is>
       </c>
       <c r="L41" s="26" t="n">
-        <v>-233</v>
+        <v>127</v>
       </c>
       <c r="M41" s="27" t="n">
-        <v>1.429185</v>
+        <v>2.27</v>
       </c>
       <c r="N41" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.440529</v>
       </c>
       <c r="O41" s="28" t="n">
-        <v>0.632201</v>
+        <v>0.579552</v>
       </c>
       <c r="P41" s="28" t="n"/>
       <c r="Q41" s="28" t="n">
-        <v>-0.067499</v>
+        <v>0.139023</v>
       </c>
       <c r="R41" s="26" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S41" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T41" s="24" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
       <c r="AD41" s="24" t="n"/>
       <c r="AE41" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-cs2-dc-nvo-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
         </is>
       </c>
       <c r="AF41" s="31" t="inlineStr">
@@ -12747,37 +12747,37 @@
       </c>
       <c r="AO41" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP41" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AQ41" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AR41" s="24" t="inlineStr">
         <is>
-          <t>Noir Verse</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AS41" s="24" t="inlineStr">
         <is>
-          <t>DragonClaw</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AT41" s="24" t="inlineStr">
         <is>
-          <t>DragonClaw</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AU41" s="24" t="inlineStr">
         <is>
-          <t>DragonClaw</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AV41" s="24" t="n"/>
@@ -12795,7 +12795,7 @@
       </c>
       <c r="BA41" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB41" s="24" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="BD41" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE41" s="24" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="BH41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:00.014811Z</t>
+          <t>2026-08-02T16:53:20.814282Z</t>
         </is>
       </c>
       <c r="BI41" s="24" t="inlineStr">
@@ -12840,13 +12840,13 @@
       </c>
       <c r="BJ41" s="25" t="n"/>
       <c r="BK41" s="26" t="n">
-        <v>-233</v>
+        <v>127</v>
       </c>
       <c r="BL41" s="27" t="n">
-        <v>1.429185</v>
+        <v>2.27</v>
       </c>
       <c r="BM41" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.440529</v>
       </c>
       <c r="BN41" s="28" t="n"/>
       <c r="BO41" s="28" t="n"/>
@@ -12879,29 +12879,29 @@
       <c r="CP41" s="24" t="n"/>
       <c r="CQ41" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>99b0c3dddef84564</t>
+          <t>7355b34cf4c145a3</t>
         </is>
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T18:00:00Z</t>
+          <t>2026-08-02T19:15:00Z</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>69289</t>
+          <t>67577</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
@@ -12911,12 +12911,12 @@
       </c>
       <c r="F42" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="G42" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="H42" s="24" t="inlineStr">
@@ -12936,23 +12936,23 @@
         </is>
       </c>
       <c r="L42" s="26" t="n">
-        <v>150</v>
+        <v>-156</v>
       </c>
       <c r="M42" s="27" t="n">
-        <v>2.5</v>
+        <v>1.641026</v>
       </c>
       <c r="N42" s="28" t="n">
-        <v>0.4</v>
+        <v>0.609375</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>0.510807</v>
+        <v>0.526938</v>
       </c>
       <c r="P42" s="28" t="n"/>
       <c r="Q42" s="28" t="n">
-        <v>0.110807</v>
+        <v>-0.082437</v>
       </c>
       <c r="R42" s="26" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="S42" s="29" t="n">
         <v>1</v>
@@ -12978,7 +12978,7 @@
       <c r="AD42" s="24" t="n"/>
       <c r="AE42" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-shin-bst-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
         </is>
       </c>
       <c r="AF42" s="31" t="inlineStr">
@@ -13014,37 +13014,37 @@
       </c>
       <c r="AO42" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP42" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AQ42" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AR42" s="24" t="inlineStr">
         <is>
-          <t>BESTIA</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AS42" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AT42" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AU42" s="24" t="inlineStr">
         <is>
-          <t>ShindeN</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AV42" s="24" t="n"/>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="BA42" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB42" s="24" t="inlineStr">
@@ -13077,7 +13077,7 @@
       </c>
       <c r="BD42" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE42" s="24" t="inlineStr">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="BH42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:01.130828Z</t>
+          <t>2026-08-02T16:53:21.312852Z</t>
         </is>
       </c>
       <c r="BI42" s="24" t="inlineStr">
@@ -13107,13 +13107,13 @@
       </c>
       <c r="BJ42" s="25" t="n"/>
       <c r="BK42" s="26" t="n">
-        <v>150</v>
+        <v>-156</v>
       </c>
       <c r="BL42" s="27" t="n">
-        <v>2.5</v>
+        <v>1.641026</v>
       </c>
       <c r="BM42" s="28" t="n">
-        <v>0.4</v>
+        <v>0.609375</v>
       </c>
       <c r="BN42" s="28" t="n"/>
       <c r="BO42" s="28" t="n"/>
@@ -13146,29 +13146,29 @@
       <c r="CP42" s="24" t="n"/>
       <c r="CQ42" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>c16eb6a46e7b4b0e</t>
+          <t>2dda10f3de244689</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:15:00Z</t>
+          <t>2026-08-03T08:00:00Z</t>
         </is>
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>67576</t>
+          <t>68288</t>
         </is>
       </c>
       <c r="E43" s="24" t="inlineStr">
@@ -13178,12 +13178,12 @@
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>CYBERSHOKE Prospects</t>
         </is>
       </c>
       <c r="G43" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>WW Team</t>
         </is>
       </c>
       <c r="H43" s="24" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="I43" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J43" s="25" t="n"/>
@@ -13203,26 +13203,26 @@
         </is>
       </c>
       <c r="L43" s="26" t="n">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>2.27</v>
+        <v>2.86</v>
       </c>
       <c r="N43" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.34965</v>
       </c>
       <c r="O43" s="28" t="n">
-        <v>0.57955</v>
+        <v>0.704234</v>
       </c>
       <c r="P43" s="28" t="n"/>
       <c r="Q43" s="28" t="n">
-        <v>0.139021</v>
+        <v>0.354584</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="S43" s="29" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="T43" s="24" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
       <c r="AD43" s="24" t="n"/>
       <c r="AE43" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-cs2-ww-cshp-2026-08-03).</t>
         </is>
       </c>
       <c r="AF43" s="31" t="inlineStr">
@@ -13286,32 +13286,32 @@
       </c>
       <c r="AP43" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>CYBERSHOKE Prospects</t>
         </is>
       </c>
       <c r="AQ43" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>CYBERSHOKE Prospects</t>
         </is>
       </c>
       <c r="AR43" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>CYBERSHOKE Prospects</t>
         </is>
       </c>
       <c r="AS43" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>WW Team</t>
         </is>
       </c>
       <c r="AT43" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>WW Team</t>
         </is>
       </c>
       <c r="AU43" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>WW Team</t>
         </is>
       </c>
       <c r="AV43" s="24" t="n"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="BA43" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB43" s="24" t="inlineStr">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="BD43" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE43" s="24" t="inlineStr">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="BH43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:01.749745Z</t>
+          <t>2026-08-02T16:53:23.458560Z</t>
         </is>
       </c>
       <c r="BI43" s="24" t="inlineStr">
@@ -13374,13 +13374,13 @@
       </c>
       <c r="BJ43" s="25" t="n"/>
       <c r="BK43" s="26" t="n">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="BL43" s="27" t="n">
-        <v>2.27</v>
+        <v>2.86</v>
       </c>
       <c r="BM43" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.34965</v>
       </c>
       <c r="BN43" s="28" t="n"/>
       <c r="BO43" s="28" t="n"/>
@@ -13420,22 +13420,22 @@
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>a537748a25784e56</t>
+          <t>335788f335fc4171</t>
         </is>
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:15:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>67577</t>
+          <t>67510</t>
         </is>
       </c>
       <c r="E44" s="24" t="inlineStr">
@@ -13445,12 +13445,12 @@
       </c>
       <c r="F44" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="G44" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="H44" s="24" t="inlineStr">
@@ -13470,20 +13470,20 @@
         </is>
       </c>
       <c r="L44" s="26" t="n">
-        <v>-156</v>
+        <v>-223</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.44843</v>
       </c>
       <c r="N44" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.690402</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>0.526936</v>
+        <v>0.563046</v>
       </c>
       <c r="P44" s="28" t="n"/>
       <c r="Q44" s="28" t="n">
-        <v>-0.082439</v>
+        <v>-0.127356</v>
       </c>
       <c r="R44" s="26" t="n">
         <v>0</v>
@@ -13512,7 +13512,7 @@
       <c r="AD44" s="24" t="n"/>
       <c r="AE44" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
         </is>
       </c>
       <c r="AF44" s="31" t="inlineStr">
@@ -13548,37 +13548,37 @@
       </c>
       <c r="AO44" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP44" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AQ44" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AR44" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AS44" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AT44" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AU44" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AV44" s="24" t="n"/>
@@ -13596,7 +13596,7 @@
       </c>
       <c r="BA44" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB44" s="24" t="inlineStr">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="BD44" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE44" s="24" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="BH44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:02.236713Z</t>
+          <t>2026-08-02T16:53:24.972799Z</t>
         </is>
       </c>
       <c r="BI44" s="24" t="inlineStr">
@@ -13641,13 +13641,13 @@
       </c>
       <c r="BJ44" s="25" t="n"/>
       <c r="BK44" s="26" t="n">
-        <v>-156</v>
+        <v>-223</v>
       </c>
       <c r="BL44" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.44843</v>
       </c>
       <c r="BM44" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.690402</v>
       </c>
       <c r="BN44" s="28" t="n"/>
       <c r="BO44" s="28" t="n"/>
@@ -13687,22 +13687,22 @@
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>8f3af3ca9e3a4409</t>
+          <t>764e0a0baf8d46d6</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T08:00:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>68288</t>
+          <t>68289</t>
         </is>
       </c>
       <c r="E45" s="24" t="inlineStr">
@@ -13712,12 +13712,12 @@
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="G45" s="24" t="inlineStr">
         <is>
-          <t>WW Team</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="H45" s="24" t="inlineStr">
@@ -13727,7 +13727,7 @@
       </c>
       <c r="I45" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J45" s="25" t="n"/>
@@ -13737,26 +13737,26 @@
         </is>
       </c>
       <c r="L45" s="26" t="n">
-        <v>186</v>
+        <v>-138</v>
       </c>
       <c r="M45" s="27" t="n">
-        <v>2.86</v>
+        <v>1.724638</v>
       </c>
       <c r="N45" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.579832</v>
       </c>
       <c r="O45" s="28" t="n">
-        <v>0.7042350000000001</v>
+        <v>0.599198</v>
       </c>
       <c r="P45" s="28" t="n"/>
       <c r="Q45" s="28" t="n">
-        <v>0.354585</v>
+        <v>0.019366</v>
       </c>
       <c r="R45" s="26" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="S45" s="29" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="T45" s="24" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
       <c r="AD45" s="24" t="n"/>
       <c r="AE45" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-cs2-ww-cshp-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
         </is>
       </c>
       <c r="AF45" s="31" t="inlineStr">
@@ -13797,7 +13797,7 @@
       <c r="AJ45" s="31" t="n"/>
       <c r="AK45" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL45" s="26" t="n">
@@ -13805,47 +13805,47 @@
       </c>
       <c r="AM45" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN45" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO45" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP45" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="AQ45" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="AR45" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="AS45" s="24" t="inlineStr">
         <is>
-          <t>WW Team</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="AT45" s="24" t="inlineStr">
         <is>
-          <t>WW Team</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="AU45" s="24" t="inlineStr">
         <is>
-          <t>WW Team</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="AV45" s="24" t="n"/>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="BA45" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB45" s="24" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="BD45" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE45" s="24" t="inlineStr">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="BH45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:03.660648Z</t>
+          <t>2026-08-02T16:53:25.545768Z</t>
         </is>
       </c>
       <c r="BI45" s="24" t="inlineStr">
@@ -13908,13 +13908,13 @@
       </c>
       <c r="BJ45" s="25" t="n"/>
       <c r="BK45" s="26" t="n">
-        <v>186</v>
+        <v>-138</v>
       </c>
       <c r="BL45" s="27" t="n">
-        <v>2.86</v>
+        <v>1.724638</v>
       </c>
       <c r="BM45" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.579832</v>
       </c>
       <c r="BN45" s="28" t="n"/>
       <c r="BO45" s="28" t="n"/>
@@ -13954,22 +13954,22 @@
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>f7d84bedbe6b465c</t>
+          <t>1a4598e6fc31416c</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-03T11:00:00Z</t>
         </is>
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>68289</t>
+          <t>67578</t>
         </is>
       </c>
       <c r="E46" s="24" t="inlineStr">
@@ -13979,12 +13979,12 @@
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="G46" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="H46" s="24" t="inlineStr">
@@ -14004,26 +14004,26 @@
         </is>
       </c>
       <c r="L46" s="26" t="n">
-        <v>-138</v>
+        <v>-150</v>
       </c>
       <c r="M46" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.666667</v>
       </c>
       <c r="N46" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.6</v>
       </c>
       <c r="O46" s="28" t="n">
-        <v>0.599195</v>
+        <v>0.526938</v>
       </c>
       <c r="P46" s="28" t="n"/>
       <c r="Q46" s="28" t="n">
-        <v>0.019363</v>
+        <v>-0.073062</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="S46" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T46" s="24" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
       <c r="AD46" s="24" t="n"/>
       <c r="AE46" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
         </is>
       </c>
       <c r="AF46" s="31" t="inlineStr">
@@ -14064,7 +14064,7 @@
       <c r="AJ46" s="31" t="n"/>
       <c r="AK46" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL46" s="26" t="n">
@@ -14072,47 +14072,47 @@
       </c>
       <c r="AM46" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN46" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO46" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP46" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AQ46" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AR46" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AS46" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AT46" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AU46" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AV46" s="24" t="n"/>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="BA46" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB46" s="24" t="inlineStr">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="BD46" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE46" s="24" t="inlineStr">
@@ -14165,7 +14165,7 @@
       </c>
       <c r="BH46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:04.678326Z</t>
+          <t>2026-08-02T16:53:27.133627Z</t>
         </is>
       </c>
       <c r="BI46" s="24" t="inlineStr">
@@ -14175,13 +14175,13 @@
       </c>
       <c r="BJ46" s="25" t="n"/>
       <c r="BK46" s="26" t="n">
-        <v>-138</v>
+        <v>-150</v>
       </c>
       <c r="BL46" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.666667</v>
       </c>
       <c r="BM46" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.6</v>
       </c>
       <c r="BN46" s="28" t="n"/>
       <c r="BO46" s="28" t="n"/>
@@ -14214,29 +14214,29 @@
       <c r="CP46" s="24" t="n"/>
       <c r="CQ46" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>dffbe7e4fcdf4368</t>
+          <t>b9cdb810520747b9</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-03T11:00:00Z</t>
         </is>
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>67510</t>
+          <t>69135</t>
         </is>
       </c>
       <c r="E47" s="24" t="inlineStr">
@@ -14246,12 +14246,12 @@
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr">
@@ -14271,20 +14271,20 @@
         </is>
       </c>
       <c r="L47" s="26" t="n">
-        <v>-223</v>
+        <v>-156</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.641026</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.609375</v>
       </c>
       <c r="O47" s="28" t="n">
-        <v>0.563014</v>
+        <v>0.527203</v>
       </c>
       <c r="P47" s="28" t="n"/>
       <c r="Q47" s="28" t="n">
-        <v>-0.127388</v>
+        <v>-0.082172</v>
       </c>
       <c r="R47" s="26" t="n">
         <v>0</v>
@@ -14313,7 +14313,7 @@
       <c r="AD47" s="24" t="n"/>
       <c r="AE47" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-1win-exruby-2026-08-03).</t>
         </is>
       </c>
       <c r="AF47" s="31" t="inlineStr">
@@ -14354,32 +14354,32 @@
       </c>
       <c r="AP47" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AQ47" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AR47" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AS47" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="AT47" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="AU47" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="AV47" s="24" t="n"/>
@@ -14397,7 +14397,7 @@
       </c>
       <c r="BA47" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB47" s="24" t="inlineStr">
@@ -14412,7 +14412,7 @@
       </c>
       <c r="BD47" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE47" s="24" t="inlineStr">
@@ -14432,7 +14432,7 @@
       </c>
       <c r="BH47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:05.206115Z</t>
+          <t>2026-08-02T16:53:27.628665Z</t>
         </is>
       </c>
       <c r="BI47" s="24" t="inlineStr">
@@ -14442,13 +14442,13 @@
       </c>
       <c r="BJ47" s="25" t="n"/>
       <c r="BK47" s="26" t="n">
-        <v>-223</v>
+        <v>-156</v>
       </c>
       <c r="BL47" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.641026</v>
       </c>
       <c r="BM47" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.609375</v>
       </c>
       <c r="BN47" s="28" t="n"/>
       <c r="BO47" s="28" t="n"/>
@@ -14488,12 +14488,12 @@
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>3fc885d5fb374d1f</t>
+          <t>5db8343fe430460b</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
@@ -14547,11 +14547,11 @@
         <v>0.680511</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>0.628883</v>
+        <v>0.628889</v>
       </c>
       <c r="P48" s="28" t="n"/>
       <c r="Q48" s="28" t="n">
-        <v>-0.051628</v>
+        <v>-0.051622</v>
       </c>
       <c r="R48" s="26" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
       </c>
       <c r="BA48" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB48" s="24" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="BD48" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE48" s="24" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="BH48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:07.681014Z</t>
+          <t>2026-08-02T16:53:28.112728Z</t>
         </is>
       </c>
       <c r="BI48" s="24" t="inlineStr">
@@ -14755,22 +14755,22 @@
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>8d5696a8efae4319</t>
+          <t>1873182b7743440f</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T11:00:00Z</t>
+          <t>2026-08-03T13:45:00Z</t>
         </is>
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>69135</t>
+          <t>67579</t>
         </is>
       </c>
       <c r="E49" s="24" t="inlineStr">
@@ -14780,12 +14780,12 @@
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>ex-RUBY</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
-          <t>1WIN</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="I49" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J49" s="25" t="n"/>
@@ -14805,23 +14805,23 @@
         </is>
       </c>
       <c r="L49" s="26" t="n">
-        <v>-156</v>
+        <v>194</v>
       </c>
       <c r="M49" s="27" t="n">
-        <v>1.641026</v>
+        <v>2.94</v>
       </c>
       <c r="N49" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.340136</v>
       </c>
       <c r="O49" s="28" t="n">
-        <v>0.527254</v>
+        <v>0.526281</v>
       </c>
       <c r="P49" s="28" t="n"/>
       <c r="Q49" s="28" t="n">
-        <v>-0.082121</v>
+        <v>0.186145</v>
       </c>
       <c r="R49" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S49" s="29" t="n">
         <v>1</v>
@@ -14847,7 +14847,7 @@
       <c r="AD49" s="24" t="n"/>
       <c r="AE49" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-1win-exruby-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
         </is>
       </c>
       <c r="AF49" s="31" t="inlineStr">
@@ -14883,37 +14883,37 @@
       </c>
       <c r="AO49" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP49" s="24" t="inlineStr">
         <is>
-          <t>ex-RUBY</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AQ49" s="24" t="inlineStr">
         <is>
-          <t>ex-RUBY</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AR49" s="24" t="inlineStr">
         <is>
-          <t>ex-RUBY</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AS49" s="24" t="inlineStr">
         <is>
-          <t>1WIN</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AT49" s="24" t="inlineStr">
         <is>
-          <t>1WIN</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AU49" s="24" t="inlineStr">
         <is>
-          <t>1WIN</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AV49" s="24" t="n"/>
@@ -14931,7 +14931,7 @@
       </c>
       <c r="BA49" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB49" s="24" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="BD49" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE49" s="24" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="BH49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:08.249635Z</t>
+          <t>2026-08-02T16:53:28.608319Z</t>
         </is>
       </c>
       <c r="BI49" s="24" t="inlineStr">
@@ -14976,13 +14976,13 @@
       </c>
       <c r="BJ49" s="25" t="n"/>
       <c r="BK49" s="26" t="n">
-        <v>-156</v>
+        <v>194</v>
       </c>
       <c r="BL49" s="27" t="n">
-        <v>1.641026</v>
+        <v>2.94</v>
       </c>
       <c r="BM49" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.340136</v>
       </c>
       <c r="BN49" s="28" t="n"/>
       <c r="BO49" s="28" t="n"/>
@@ -15015,29 +15015,29 @@
       <c r="CP49" s="24" t="n"/>
       <c r="CQ49" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>58de58897ee54660</t>
+          <t>17895dec8a5c4c08</t>
         </is>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T11:00:00Z</t>
+          <t>2026-08-03T14:00:00Z</t>
         </is>
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>67578</t>
+          <t>68292</t>
         </is>
       </c>
       <c r="E50" s="24" t="inlineStr">
@@ -15047,12 +15047,12 @@
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>ARCRED</t>
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr">
@@ -15072,26 +15072,26 @@
         </is>
       </c>
       <c r="L50" s="26" t="n">
-        <v>-150</v>
+        <v>-178</v>
       </c>
       <c r="M50" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.561798</v>
       </c>
       <c r="N50" s="28" t="n">
-        <v>0.6</v>
+        <v>0.640288</v>
       </c>
       <c r="O50" s="28" t="n">
-        <v>0.526936</v>
+        <v>0.613947</v>
       </c>
       <c r="P50" s="28" t="n"/>
       <c r="Q50" s="28" t="n">
-        <v>-0.073064</v>
+        <v>-0.026341</v>
       </c>
       <c r="R50" s="26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S50" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T50" s="24" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
       <c r="AD50" s="24" t="n"/>
       <c r="AE50" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-arc-btf-2026-08-03).</t>
         </is>
       </c>
       <c r="AF50" s="31" t="inlineStr">
@@ -15150,37 +15150,37 @@
       </c>
       <c r="AO50" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP50" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AQ50" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AR50" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AS50" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>ARCRED</t>
         </is>
       </c>
       <c r="AT50" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>ARCRED</t>
         </is>
       </c>
       <c r="AU50" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>ARCRED</t>
         </is>
       </c>
       <c r="AV50" s="24" t="n"/>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="BA50" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB50" s="24" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="BD50" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE50" s="24" t="inlineStr">
@@ -15233,7 +15233,7 @@
       </c>
       <c r="BH50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:08.773065Z</t>
+          <t>2026-08-02T16:53:29.071469Z</t>
         </is>
       </c>
       <c r="BI50" s="24" t="inlineStr">
@@ -15243,13 +15243,13 @@
       </c>
       <c r="BJ50" s="25" t="n"/>
       <c r="BK50" s="26" t="n">
-        <v>-150</v>
+        <v>-178</v>
       </c>
       <c r="BL50" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.561798</v>
       </c>
       <c r="BM50" s="28" t="n">
-        <v>0.6</v>
+        <v>0.640288</v>
       </c>
       <c r="BN50" s="28" t="n"/>
       <c r="BO50" s="28" t="n"/>
@@ -15289,22 +15289,22 @@
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>524fb6f75b7e4bb1</t>
+          <t>f50546f646024b4f</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T13:45:00Z</t>
+          <t>2026-08-03T14:00:00Z</t>
         </is>
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>67579</t>
+          <t>69268</t>
         </is>
       </c>
       <c r="E51" s="24" t="inlineStr">
@@ -15314,12 +15314,12 @@
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="H51" s="24" t="inlineStr">
@@ -15329,7 +15329,7 @@
       </c>
       <c r="I51" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J51" s="25" t="n"/>
@@ -15339,26 +15339,26 @@
         </is>
       </c>
       <c r="L51" s="26" t="n">
-        <v>194</v>
+        <v>-178</v>
       </c>
       <c r="M51" s="27" t="n">
-        <v>2.94</v>
+        <v>1.561798</v>
       </c>
       <c r="N51" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.640288</v>
       </c>
       <c r="O51" s="28" t="n">
-        <v>0.5262829999999999</v>
+        <v>0.663025</v>
       </c>
       <c r="P51" s="28" t="n"/>
       <c r="Q51" s="28" t="n">
-        <v>0.186147</v>
+        <v>0.022737</v>
       </c>
       <c r="R51" s="26" t="n">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="S51" s="29" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="T51" s="24" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
       <c r="AD51" s="24" t="n"/>
       <c r="AE51" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
         </is>
       </c>
       <c r="AF51" s="31" t="inlineStr">
@@ -15399,7 +15399,7 @@
       <c r="AJ51" s="31" t="n"/>
       <c r="AK51" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL51" s="26" t="n">
@@ -15407,47 +15407,47 @@
       </c>
       <c r="AM51" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN51" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO51" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP51" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AQ51" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AR51" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AS51" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AT51" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AU51" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AV51" s="24" t="n"/>
@@ -15465,7 +15465,7 @@
       </c>
       <c r="BA51" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB51" s="24" t="inlineStr">
@@ -15480,7 +15480,7 @@
       </c>
       <c r="BD51" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE51" s="24" t="inlineStr">
@@ -15500,7 +15500,7 @@
       </c>
       <c r="BH51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:09.305570Z</t>
+          <t>2026-08-02T16:53:29.527479Z</t>
         </is>
       </c>
       <c r="BI51" s="24" t="inlineStr">
@@ -15510,13 +15510,13 @@
       </c>
       <c r="BJ51" s="25" t="n"/>
       <c r="BK51" s="26" t="n">
-        <v>194</v>
+        <v>-178</v>
       </c>
       <c r="BL51" s="27" t="n">
-        <v>2.94</v>
+        <v>1.561798</v>
       </c>
       <c r="BM51" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.640288</v>
       </c>
       <c r="BN51" s="28" t="n"/>
       <c r="BO51" s="28" t="n"/>
@@ -15556,22 +15556,22 @@
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>13cd0b530de04f9a</t>
+          <t>bb2073accd074022</t>
         </is>
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
+          <t>2026-08-02T16:53:33.678893Z</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T14:00:00Z</t>
+          <t>2026-08-03T23:00:00Z</t>
         </is>
       </c>
       <c r="D52" s="24" t="inlineStr">
         <is>
-          <t>68292</t>
+          <t>68043</t>
         </is>
       </c>
       <c r="E52" s="24" t="inlineStr">
@@ -15581,12 +15581,12 @@
       </c>
       <c r="F52" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="G52" s="24" t="inlineStr">
         <is>
-          <t>ARCRED</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="H52" s="24" t="inlineStr">
@@ -15606,26 +15606,26 @@
         </is>
       </c>
       <c r="L52" s="26" t="n">
-        <v>-178</v>
+        <v>122</v>
       </c>
       <c r="M52" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.22</v>
       </c>
       <c r="N52" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.45045</v>
       </c>
       <c r="O52" s="28" t="n">
-        <v>0.6138479999999999</v>
+        <v>0.569644</v>
       </c>
       <c r="P52" s="28" t="n"/>
       <c r="Q52" s="28" t="n">
-        <v>-0.02644</v>
+        <v>0.119194</v>
       </c>
       <c r="R52" s="26" t="n">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="S52" s="29" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T52" s="24" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
       <c r="AD52" s="24" t="n"/>
       <c r="AE52" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-arc-btf-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
         </is>
       </c>
       <c r="AF52" s="31" t="inlineStr">
@@ -15684,37 +15684,37 @@
       </c>
       <c r="AO52" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP52" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="AQ52" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="AR52" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="AS52" s="24" t="inlineStr">
         <is>
-          <t>ARCRED</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="AT52" s="24" t="inlineStr">
         <is>
-          <t>ARCRED</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="AU52" s="24" t="inlineStr">
         <is>
-          <t>ARCRED</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="AV52" s="24" t="n"/>
@@ -15732,7 +15732,7 @@
       </c>
       <c r="BA52" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BB52" s="24" t="inlineStr">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="BD52" s="24" t="inlineStr">
         <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
+          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
         </is>
       </c>
       <c r="BE52" s="24" t="inlineStr">
@@ -15767,7 +15767,7 @@
       </c>
       <c r="BH52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T16:15:09.759475Z</t>
+          <t>2026-08-02T16:53:33.675629Z</t>
         </is>
       </c>
       <c r="BI52" s="24" t="inlineStr">
@@ -15777,13 +15777,13 @@
       </c>
       <c r="BJ52" s="25" t="n"/>
       <c r="BK52" s="26" t="n">
-        <v>-178</v>
+        <v>122</v>
       </c>
       <c r="BL52" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.22</v>
       </c>
       <c r="BM52" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.45045</v>
       </c>
       <c r="BN52" s="28" t="n"/>
       <c r="BO52" s="28" t="n"/>
@@ -15816,540 +15816,6 @@
       <c r="CP52" s="24" t="n"/>
       <c r="CQ52" s="24" t="inlineStr">
         <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="36" customHeight="1">
-      <c r="A53" s="24" t="inlineStr">
-        <is>
-          <t>29fb553152eb4466</t>
-        </is>
-      </c>
-      <c r="B53" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
-        </is>
-      </c>
-      <c r="C53" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D53" s="24" t="inlineStr">
-        <is>
-          <t>69268</t>
-        </is>
-      </c>
-      <c r="E53" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F53" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="G53" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="H53" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I53" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J53" s="25" t="n"/>
-      <c r="K53" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L53" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M53" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N53" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O53" s="28" t="n">
-        <v>0.662883</v>
-      </c>
-      <c r="P53" s="28" t="n"/>
-      <c r="Q53" s="28" t="n">
-        <v>0.022595</v>
-      </c>
-      <c r="R53" s="26" t="n">
-        <v>31</v>
-      </c>
-      <c r="S53" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T53" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U53" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V53" s="24" t="n"/>
-      <c r="W53" s="26" t="n"/>
-      <c r="X53" s="26" t="n"/>
-      <c r="Y53" s="25" t="n"/>
-      <c r="Z53" s="26" t="n"/>
-      <c r="AA53" s="28" t="n"/>
-      <c r="AB53" s="28" t="n"/>
-      <c r="AC53" s="30" t="n"/>
-      <c r="AD53" s="24" t="n"/>
-      <c r="AE53" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF53" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG53" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH53" s="24" t="n"/>
-      <c r="AI53" s="31" t="n"/>
-      <c r="AJ53" s="31" t="n"/>
-      <c r="AK53" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL53" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM53" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN53" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO53" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP53" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AQ53" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AR53" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AS53" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AT53" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AU53" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AV53" s="24" t="n"/>
-      <c r="AW53" s="24" t="n"/>
-      <c r="AX53" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY53" s="24" t="n"/>
-      <c r="AZ53" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA53" s="24" t="inlineStr">
-        <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
-        </is>
-      </c>
-      <c r="BB53" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC53" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD53" s="24" t="inlineStr">
-        <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
-        </is>
-      </c>
-      <c r="BE53" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF53" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG53" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH53" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:15:10.799851Z</t>
-        </is>
-      </c>
-      <c r="BI53" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ53" s="25" t="n"/>
-      <c r="BK53" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL53" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM53" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN53" s="28" t="n"/>
-      <c r="BO53" s="28" t="n"/>
-      <c r="BP53" s="25" t="n"/>
-      <c r="BQ53" s="27" t="n"/>
-      <c r="BR53" s="28" t="n"/>
-      <c r="BS53" s="28" t="n"/>
-      <c r="BT53" s="28" t="n"/>
-      <c r="BU53" s="25" t="n"/>
-      <c r="BV53" s="29" t="n"/>
-      <c r="BW53" s="24" t="n"/>
-      <c r="BX53" s="30" t="n"/>
-      <c r="BY53" s="27" t="n"/>
-      <c r="BZ53" s="24" t="n"/>
-      <c r="CA53" s="31" t="n"/>
-      <c r="CB53" s="24" t="n"/>
-      <c r="CC53" s="24" t="n"/>
-      <c r="CD53" s="24" t="n"/>
-      <c r="CE53" s="24" t="n"/>
-      <c r="CF53" s="24" t="n"/>
-      <c r="CG53" s="24" t="n"/>
-      <c r="CH53" s="24" t="n"/>
-      <c r="CI53" s="24" t="n"/>
-      <c r="CJ53" s="24" t="n"/>
-      <c r="CK53" s="24" t="n"/>
-      <c r="CL53" s="24" t="n"/>
-      <c r="CM53" s="24" t="n"/>
-      <c r="CN53" s="24" t="n"/>
-      <c r="CO53" s="24" t="n"/>
-      <c r="CP53" s="24" t="n"/>
-      <c r="CQ53" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="36" customHeight="1">
-      <c r="A54" s="24" t="inlineStr">
-        <is>
-          <t>02d2fc0ac6f14768</t>
-        </is>
-      </c>
-      <c r="B54" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:15:14.476529Z</t>
-        </is>
-      </c>
-      <c r="C54" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T23:00:00Z</t>
-        </is>
-      </c>
-      <c r="D54" s="24" t="inlineStr">
-        <is>
-          <t>68043</t>
-        </is>
-      </c>
-      <c r="E54" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F54" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="G54" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="H54" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I54" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J54" s="25" t="n"/>
-      <c r="K54" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L54" s="26" t="n">
-        <v>122</v>
-      </c>
-      <c r="M54" s="27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="N54" s="28" t="n">
-        <v>0.45045</v>
-      </c>
-      <c r="O54" s="28" t="n">
-        <v>0.569642</v>
-      </c>
-      <c r="P54" s="28" t="n"/>
-      <c r="Q54" s="28" t="n">
-        <v>0.119192</v>
-      </c>
-      <c r="R54" s="26" t="n">
-        <v>80</v>
-      </c>
-      <c r="S54" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T54" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U54" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V54" s="24" t="n"/>
-      <c r="W54" s="26" t="n"/>
-      <c r="X54" s="26" t="n"/>
-      <c r="Y54" s="25" t="n"/>
-      <c r="Z54" s="26" t="n"/>
-      <c r="AA54" s="28" t="n"/>
-      <c r="AB54" s="28" t="n"/>
-      <c r="AC54" s="30" t="n"/>
-      <c r="AD54" s="24" t="n"/>
-      <c r="AE54" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF54" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG54" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH54" s="24" t="n"/>
-      <c r="AI54" s="31" t="n"/>
-      <c r="AJ54" s="31" t="n"/>
-      <c r="AK54" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL54" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM54" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN54" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO54" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP54" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AQ54" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AR54" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AS54" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="AT54" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="AU54" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="AV54" s="24" t="n"/>
-      <c r="AW54" s="24" t="n"/>
-      <c r="AX54" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY54" s="24" t="n"/>
-      <c r="AZ54" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA54" s="24" t="inlineStr">
-        <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
-        </is>
-      </c>
-      <c r="BB54" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC54" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD54" s="24" t="inlineStr">
-        <is>
-          <t>be57084f1d7fbd4d502df5071cd07ad0aef0fe46ec9ff6b18e470efb3b2bbfd4</t>
-        </is>
-      </c>
-      <c r="BE54" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF54" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG54" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH54" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:15:14.474993Z</t>
-        </is>
-      </c>
-      <c r="BI54" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ54" s="25" t="n"/>
-      <c r="BK54" s="26" t="n">
-        <v>122</v>
-      </c>
-      <c r="BL54" s="27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BM54" s="28" t="n">
-        <v>0.45045</v>
-      </c>
-      <c r="BN54" s="28" t="n"/>
-      <c r="BO54" s="28" t="n"/>
-      <c r="BP54" s="25" t="n"/>
-      <c r="BQ54" s="27" t="n"/>
-      <c r="BR54" s="28" t="n"/>
-      <c r="BS54" s="28" t="n"/>
-      <c r="BT54" s="28" t="n"/>
-      <c r="BU54" s="25" t="n"/>
-      <c r="BV54" s="29" t="n"/>
-      <c r="BW54" s="24" t="n"/>
-      <c r="BX54" s="30" t="n"/>
-      <c r="BY54" s="27" t="n"/>
-      <c r="BZ54" s="24" t="n"/>
-      <c r="CA54" s="31" t="n"/>
-      <c r="CB54" s="24" t="n"/>
-      <c r="CC54" s="24" t="n"/>
-      <c r="CD54" s="24" t="n"/>
-      <c r="CE54" s="24" t="n"/>
-      <c r="CF54" s="24" t="n"/>
-      <c r="CG54" s="24" t="n"/>
-      <c r="CH54" s="24" t="n"/>
-      <c r="CI54" s="24" t="n"/>
-      <c r="CJ54" s="24" t="n"/>
-      <c r="CK54" s="24" t="n"/>
-      <c r="CL54" s="24" t="n"/>
-      <c r="CM54" s="24" t="n"/>
-      <c r="CN54" s="24" t="n"/>
-      <c r="CO54" s="24" t="n"/>
-      <c r="CP54" s="24" t="n"/>
-      <c r="CQ54" s="24" t="inlineStr">
-        <is>
           <t>True</t>
         </is>
       </c>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ52" headerRowCount="1">
-  <autoFilter ref="A1:CQ52"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ39" headerRowCount="1">
+  <autoFilter ref="A1:CQ39"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$52)</f>
+        <f>COUNTA('Picks'!$A$2:$A$39)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$52,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$39,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$52,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")+COUNTIFS('Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$52,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$39,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")/(COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")+COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")/(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$52)/SUM('Picks'!$BX$2:$BX$52),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$39)/SUM('Picks'!$BX$2:$BX$39),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$52)</f>
+        <f>SUM('Picks'!$BY$2:$BY$39)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$52,"&lt;&gt;",'Picks'!$AB$2:$AB$52),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$39,"&lt;&gt;",'Picks'!$AB$2:$AB$39),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$52,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$52,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$52,'Picks'!$AM$2:$AM$52,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$39,'Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ52"/>
+  <dimension ref="A1:CQ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12349,3477 +12349,6 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="36" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
-        <is>
-          <t>a73267a4377d41b1</t>
-        </is>
-      </c>
-      <c r="B40" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:33.678893Z</t>
-        </is>
-      </c>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:00:00Z</t>
-        </is>
-      </c>
-      <c r="D40" s="24" t="inlineStr">
-        <is>
-          <t>69289</t>
-        </is>
-      </c>
-      <c r="E40" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F40" s="24" t="inlineStr">
-        <is>
-          <t>BESTIA</t>
-        </is>
-      </c>
-      <c r="G40" s="24" t="inlineStr">
-        <is>
-          <t>ShindeN</t>
-        </is>
-      </c>
-      <c r="H40" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I40" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J40" s="25" t="n"/>
-      <c r="K40" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L40" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="M40" s="27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N40" s="28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O40" s="28" t="n">
-        <v>0.510848</v>
-      </c>
-      <c r="P40" s="28" t="n"/>
-      <c r="Q40" s="28" t="n">
-        <v>0.110848</v>
-      </c>
-      <c r="R40" s="26" t="n">
-        <v>75</v>
-      </c>
-      <c r="S40" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T40" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U40" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V40" s="24" t="n"/>
-      <c r="W40" s="26" t="n"/>
-      <c r="X40" s="26" t="n"/>
-      <c r="Y40" s="25" t="n"/>
-      <c r="Z40" s="26" t="n"/>
-      <c r="AA40" s="28" t="n"/>
-      <c r="AB40" s="28" t="n"/>
-      <c r="AC40" s="30" t="n"/>
-      <c r="AD40" s="24" t="n"/>
-      <c r="AE40" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-shin-bst-2026-08-02).</t>
-        </is>
-      </c>
-      <c r="AF40" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG40" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH40" s="24" t="n"/>
-      <c r="AI40" s="31" t="n"/>
-      <c r="AJ40" s="31" t="n"/>
-      <c r="AK40" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL40" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM40" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN40" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO40" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP40" s="24" t="inlineStr">
-        <is>
-          <t>BESTIA</t>
-        </is>
-      </c>
-      <c r="AQ40" s="24" t="inlineStr">
-        <is>
-          <t>BESTIA</t>
-        </is>
-      </c>
-      <c r="AR40" s="24" t="inlineStr">
-        <is>
-          <t>BESTIA</t>
-        </is>
-      </c>
-      <c r="AS40" s="24" t="inlineStr">
-        <is>
-          <t>ShindeN</t>
-        </is>
-      </c>
-      <c r="AT40" s="24" t="inlineStr">
-        <is>
-          <t>ShindeN</t>
-        </is>
-      </c>
-      <c r="AU40" s="24" t="inlineStr">
-        <is>
-          <t>ShindeN</t>
-        </is>
-      </c>
-      <c r="AV40" s="24" t="n"/>
-      <c r="AW40" s="24" t="n"/>
-      <c r="AX40" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY40" s="24" t="n"/>
-      <c r="AZ40" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA40" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BB40" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC40" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD40" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BE40" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF40" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG40" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH40" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:20.304048Z</t>
-        </is>
-      </c>
-      <c r="BI40" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ40" s="25" t="n"/>
-      <c r="BK40" s="26" t="n">
-        <v>150</v>
-      </c>
-      <c r="BL40" s="27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BM40" s="28" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BN40" s="28" t="n"/>
-      <c r="BO40" s="28" t="n"/>
-      <c r="BP40" s="25" t="n"/>
-      <c r="BQ40" s="27" t="n"/>
-      <c r="BR40" s="28" t="n"/>
-      <c r="BS40" s="28" t="n"/>
-      <c r="BT40" s="28" t="n"/>
-      <c r="BU40" s="25" t="n"/>
-      <c r="BV40" s="29" t="n"/>
-      <c r="BW40" s="24" t="n"/>
-      <c r="BX40" s="30" t="n"/>
-      <c r="BY40" s="27" t="n"/>
-      <c r="BZ40" s="24" t="n"/>
-      <c r="CA40" s="31" t="n"/>
-      <c r="CB40" s="24" t="n"/>
-      <c r="CC40" s="24" t="n"/>
-      <c r="CD40" s="24" t="n"/>
-      <c r="CE40" s="24" t="n"/>
-      <c r="CF40" s="24" t="n"/>
-      <c r="CG40" s="24" t="n"/>
-      <c r="CH40" s="24" t="n"/>
-      <c r="CI40" s="24" t="n"/>
-      <c r="CJ40" s="24" t="n"/>
-      <c r="CK40" s="24" t="n"/>
-      <c r="CL40" s="24" t="n"/>
-      <c r="CM40" s="24" t="n"/>
-      <c r="CN40" s="24" t="n"/>
-      <c r="CO40" s="24" t="n"/>
-      <c r="CP40" s="24" t="n"/>
-      <c r="CQ40" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>7aa6e3ac894d4715</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:33.678893Z</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T19:15:00Z</t>
-        </is>
-      </c>
-      <c r="D41" s="24" t="inlineStr">
-        <is>
-          <t>67576</t>
-        </is>
-      </c>
-      <c r="E41" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F41" s="24" t="inlineStr">
-        <is>
-          <t>mokrivskiy Club</t>
-        </is>
-      </c>
-      <c r="G41" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="H41" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I41" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J41" s="25" t="n"/>
-      <c r="K41" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L41" s="26" t="n">
-        <v>127</v>
-      </c>
-      <c r="M41" s="27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="N41" s="28" t="n">
-        <v>0.440529</v>
-      </c>
-      <c r="O41" s="28" t="n">
-        <v>0.579552</v>
-      </c>
-      <c r="P41" s="28" t="n"/>
-      <c r="Q41" s="28" t="n">
-        <v>0.139023</v>
-      </c>
-      <c r="R41" s="26" t="n">
-        <v>90</v>
-      </c>
-      <c r="S41" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T41" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U41" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V41" s="24" t="n"/>
-      <c r="W41" s="26" t="n"/>
-      <c r="X41" s="26" t="n"/>
-      <c r="Y41" s="25" t="n"/>
-      <c r="Z41" s="26" t="n"/>
-      <c r="AA41" s="28" t="n"/>
-      <c r="AB41" s="28" t="n"/>
-      <c r="AC41" s="30" t="n"/>
-      <c r="AD41" s="24" t="n"/>
-      <c r="AE41" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
-        </is>
-      </c>
-      <c r="AF41" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG41" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH41" s="24" t="n"/>
-      <c r="AI41" s="31" t="n"/>
-      <c r="AJ41" s="31" t="n"/>
-      <c r="AK41" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL41" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM41" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN41" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO41" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP41" s="24" t="inlineStr">
-        <is>
-          <t>mokrivskiy Club</t>
-        </is>
-      </c>
-      <c r="AQ41" s="24" t="inlineStr">
-        <is>
-          <t>mokrivskiy Club</t>
-        </is>
-      </c>
-      <c r="AR41" s="24" t="inlineStr">
-        <is>
-          <t>mokrivskiy Club</t>
-        </is>
-      </c>
-      <c r="AS41" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="AT41" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="AU41" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="AV41" s="24" t="n"/>
-      <c r="AW41" s="24" t="n"/>
-      <c r="AX41" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY41" s="24" t="n"/>
-      <c r="AZ41" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA41" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BB41" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC41" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD41" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BE41" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF41" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG41" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH41" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:20.814282Z</t>
-        </is>
-      </c>
-      <c r="BI41" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ41" s="25" t="n"/>
-      <c r="BK41" s="26" t="n">
-        <v>127</v>
-      </c>
-      <c r="BL41" s="27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BM41" s="28" t="n">
-        <v>0.440529</v>
-      </c>
-      <c r="BN41" s="28" t="n"/>
-      <c r="BO41" s="28" t="n"/>
-      <c r="BP41" s="25" t="n"/>
-      <c r="BQ41" s="27" t="n"/>
-      <c r="BR41" s="28" t="n"/>
-      <c r="BS41" s="28" t="n"/>
-      <c r="BT41" s="28" t="n"/>
-      <c r="BU41" s="25" t="n"/>
-      <c r="BV41" s="29" t="n"/>
-      <c r="BW41" s="24" t="n"/>
-      <c r="BX41" s="30" t="n"/>
-      <c r="BY41" s="27" t="n"/>
-      <c r="BZ41" s="24" t="n"/>
-      <c r="CA41" s="31" t="n"/>
-      <c r="CB41" s="24" t="n"/>
-      <c r="CC41" s="24" t="n"/>
-      <c r="CD41" s="24" t="n"/>
-      <c r="CE41" s="24" t="n"/>
-      <c r="CF41" s="24" t="n"/>
-      <c r="CG41" s="24" t="n"/>
-      <c r="CH41" s="24" t="n"/>
-      <c r="CI41" s="24" t="n"/>
-      <c r="CJ41" s="24" t="n"/>
-      <c r="CK41" s="24" t="n"/>
-      <c r="CL41" s="24" t="n"/>
-      <c r="CM41" s="24" t="n"/>
-      <c r="CN41" s="24" t="n"/>
-      <c r="CO41" s="24" t="n"/>
-      <c r="CP41" s="24" t="n"/>
-      <c r="CQ41" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="24" t="inlineStr">
-        <is>
-          <t>7355b34cf4c145a3</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:33.678893Z</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T19:15:00Z</t>
-        </is>
-      </c>
-      <c r="D42" s="24" t="inlineStr">
-        <is>
-          <t>67577</t>
-        </is>
-      </c>
-      <c r="E42" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F42" s="24" t="inlineStr">
-        <is>
-          <t>SNAILKICK Club</t>
-        </is>
-      </c>
-      <c r="G42" s="24" t="inlineStr">
-        <is>
-          <t>Lixxx Club</t>
-        </is>
-      </c>
-      <c r="H42" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I42" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J42" s="25" t="n"/>
-      <c r="K42" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L42" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="M42" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="N42" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="O42" s="28" t="n">
-        <v>0.526938</v>
-      </c>
-      <c r="P42" s="28" t="n"/>
-      <c r="Q42" s="28" t="n">
-        <v>-0.082437</v>
-      </c>
-      <c r="R42" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T42" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U42" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V42" s="24" t="n"/>
-      <c r="W42" s="26" t="n"/>
-      <c r="X42" s="26" t="n"/>
-      <c r="Y42" s="25" t="n"/>
-      <c r="Z42" s="26" t="n"/>
-      <c r="AA42" s="28" t="n"/>
-      <c r="AB42" s="28" t="n"/>
-      <c r="AC42" s="30" t="n"/>
-      <c r="AD42" s="24" t="n"/>
-      <c r="AE42" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
-        </is>
-      </c>
-      <c r="AF42" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG42" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH42" s="24" t="n"/>
-      <c r="AI42" s="31" t="n"/>
-      <c r="AJ42" s="31" t="n"/>
-      <c r="AK42" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL42" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM42" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN42" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO42" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP42" s="24" t="inlineStr">
-        <is>
-          <t>SNAILKICK Club</t>
-        </is>
-      </c>
-      <c r="AQ42" s="24" t="inlineStr">
-        <is>
-          <t>SNAILKICK Club</t>
-        </is>
-      </c>
-      <c r="AR42" s="24" t="inlineStr">
-        <is>
-          <t>SNAILKICK Club</t>
-        </is>
-      </c>
-      <c r="AS42" s="24" t="inlineStr">
-        <is>
-          <t>Lixxx Club</t>
-        </is>
-      </c>
-      <c r="AT42" s="24" t="inlineStr">
-        <is>
-          <t>Lixxx Club</t>
-        </is>
-      </c>
-      <c r="AU42" s="24" t="inlineStr">
-        <is>
-          <t>Lixxx Club</t>
-        </is>
-      </c>
-      <c r="AV42" s="24" t="n"/>
-      <c r="AW42" s="24" t="n"/>
-      <c r="AX42" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY42" s="24" t="n"/>
-      <c r="AZ42" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA42" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BB42" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC42" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD42" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BE42" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF42" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG42" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH42" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:21.312852Z</t>
-        </is>
-      </c>
-      <c r="BI42" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ42" s="25" t="n"/>
-      <c r="BK42" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="BL42" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="BM42" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="BN42" s="28" t="n"/>
-      <c r="BO42" s="28" t="n"/>
-      <c r="BP42" s="25" t="n"/>
-      <c r="BQ42" s="27" t="n"/>
-      <c r="BR42" s="28" t="n"/>
-      <c r="BS42" s="28" t="n"/>
-      <c r="BT42" s="28" t="n"/>
-      <c r="BU42" s="25" t="n"/>
-      <c r="BV42" s="29" t="n"/>
-      <c r="BW42" s="24" t="n"/>
-      <c r="BX42" s="30" t="n"/>
-      <c r="BY42" s="27" t="n"/>
-      <c r="BZ42" s="24" t="n"/>
-      <c r="CA42" s="31" t="n"/>
-      <c r="CB42" s="24" t="n"/>
-      <c r="CC42" s="24" t="n"/>
-      <c r="CD42" s="24" t="n"/>
-      <c r="CE42" s="24" t="n"/>
-      <c r="CF42" s="24" t="n"/>
-      <c r="CG42" s="24" t="n"/>
-      <c r="CH42" s="24" t="n"/>
-      <c r="CI42" s="24" t="n"/>
-      <c r="CJ42" s="24" t="n"/>
-      <c r="CK42" s="24" t="n"/>
-      <c r="CL42" s="24" t="n"/>
-      <c r="CM42" s="24" t="n"/>
-      <c r="CN42" s="24" t="n"/>
-      <c r="CO42" s="24" t="n"/>
-      <c r="CP42" s="24" t="n"/>
-      <c r="CQ42" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="24" t="inlineStr">
-        <is>
-          <t>2dda10f3de244689</t>
-        </is>
-      </c>
-      <c r="B43" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:33.678893Z</t>
-        </is>
-      </c>
-      <c r="C43" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T08:00:00Z</t>
-        </is>
-      </c>
-      <c r="D43" s="24" t="inlineStr">
-        <is>
-          <t>68288</t>
-        </is>
-      </c>
-      <c r="E43" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F43" s="24" t="inlineStr">
-        <is>
-          <t>CYBERSHOKE Prospects</t>
-        </is>
-      </c>
-      <c r="G43" s="24" t="inlineStr">
-        <is>
-          <t>WW Team</t>
-        </is>
-      </c>
-      <c r="H43" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I43" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J43" s="25" t="n"/>
-      <c r="K43" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L43" s="26" t="n">
-        <v>186</v>
-      </c>
-      <c r="M43" s="27" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="N43" s="28" t="n">
-        <v>0.34965</v>
-      </c>
-      <c r="O43" s="28" t="n">
-        <v>0.704234</v>
-      </c>
-      <c r="P43" s="28" t="n"/>
-      <c r="Q43" s="28" t="n">
-        <v>0.354584</v>
-      </c>
-      <c r="R43" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S43" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T43" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U43" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V43" s="24" t="n"/>
-      <c r="W43" s="26" t="n"/>
-      <c r="X43" s="26" t="n"/>
-      <c r="Y43" s="25" t="n"/>
-      <c r="Z43" s="26" t="n"/>
-      <c r="AA43" s="28" t="n"/>
-      <c r="AB43" s="28" t="n"/>
-      <c r="AC43" s="30" t="n"/>
-      <c r="AD43" s="24" t="n"/>
-      <c r="AE43" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-cs2-ww-cshp-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF43" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG43" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH43" s="24" t="n"/>
-      <c r="AI43" s="31" t="n"/>
-      <c r="AJ43" s="31" t="n"/>
-      <c r="AK43" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL43" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM43" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN43" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO43" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP43" s="24" t="inlineStr">
-        <is>
-          <t>CYBERSHOKE Prospects</t>
-        </is>
-      </c>
-      <c r="AQ43" s="24" t="inlineStr">
-        <is>
-          <t>CYBERSHOKE Prospects</t>
-        </is>
-      </c>
-      <c r="AR43" s="24" t="inlineStr">
-        <is>
-          <t>CYBERSHOKE Prospects</t>
-        </is>
-      </c>
-      <c r="AS43" s="24" t="inlineStr">
-        <is>
-          <t>WW Team</t>
-        </is>
-      </c>
-      <c r="AT43" s="24" t="inlineStr">
-        <is>
-          <t>WW Team</t>
-        </is>
-      </c>
-      <c r="AU43" s="24" t="inlineStr">
-        <is>
-          <t>WW Team</t>
-        </is>
-      </c>
-      <c r="AV43" s="24" t="n"/>
-      <c r="AW43" s="24" t="n"/>
-      <c r="AX43" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY43" s="24" t="n"/>
-      <c r="AZ43" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA43" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BB43" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC43" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD43" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BE43" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF43" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG43" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH43" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:23.458560Z</t>
-        </is>
-      </c>
-      <c r="BI43" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ43" s="25" t="n"/>
-      <c r="BK43" s="26" t="n">
-        <v>186</v>
-      </c>
-      <c r="BL43" s="27" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BM43" s="28" t="n">
-        <v>0.34965</v>
-      </c>
-      <c r="BN43" s="28" t="n"/>
-      <c r="BO43" s="28" t="n"/>
-      <c r="BP43" s="25" t="n"/>
-      <c r="BQ43" s="27" t="n"/>
-      <c r="BR43" s="28" t="n"/>
-      <c r="BS43" s="28" t="n"/>
-      <c r="BT43" s="28" t="n"/>
-      <c r="BU43" s="25" t="n"/>
-      <c r="BV43" s="29" t="n"/>
-      <c r="BW43" s="24" t="n"/>
-      <c r="BX43" s="30" t="n"/>
-      <c r="BY43" s="27" t="n"/>
-      <c r="BZ43" s="24" t="n"/>
-      <c r="CA43" s="31" t="n"/>
-      <c r="CB43" s="24" t="n"/>
-      <c r="CC43" s="24" t="n"/>
-      <c r="CD43" s="24" t="n"/>
-      <c r="CE43" s="24" t="n"/>
-      <c r="CF43" s="24" t="n"/>
-      <c r="CG43" s="24" t="n"/>
-      <c r="CH43" s="24" t="n"/>
-      <c r="CI43" s="24" t="n"/>
-      <c r="CJ43" s="24" t="n"/>
-      <c r="CK43" s="24" t="n"/>
-      <c r="CL43" s="24" t="n"/>
-      <c r="CM43" s="24" t="n"/>
-      <c r="CN43" s="24" t="n"/>
-      <c r="CO43" s="24" t="n"/>
-      <c r="CP43" s="24" t="n"/>
-      <c r="CQ43" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="24" t="inlineStr">
-        <is>
-          <t>335788f335fc4171</t>
-        </is>
-      </c>
-      <c r="B44" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:33.678893Z</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:00:00Z</t>
-        </is>
-      </c>
-      <c r="D44" s="24" t="inlineStr">
-        <is>
-          <t>67510</t>
-        </is>
-      </c>
-      <c r="E44" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F44" s="24" t="inlineStr">
-        <is>
-          <t>Johnny Speeds</t>
-        </is>
-      </c>
-      <c r="G44" s="24" t="inlineStr">
-        <is>
-          <t>Metizport</t>
-        </is>
-      </c>
-      <c r="H44" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I44" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J44" s="25" t="n"/>
-      <c r="K44" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L44" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M44" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="N44" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="O44" s="28" t="n">
-        <v>0.563046</v>
-      </c>
-      <c r="P44" s="28" t="n"/>
-      <c r="Q44" s="28" t="n">
-        <v>-0.127356</v>
-      </c>
-      <c r="R44" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T44" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U44" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V44" s="24" t="n"/>
-      <c r="W44" s="26" t="n"/>
-      <c r="X44" s="26" t="n"/>
-      <c r="Y44" s="25" t="n"/>
-      <c r="Z44" s="26" t="n"/>
-      <c r="AA44" s="28" t="n"/>
-      <c r="AB44" s="28" t="n"/>
-      <c r="AC44" s="30" t="n"/>
-      <c r="AD44" s="24" t="n"/>
-      <c r="AE44" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF44" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG44" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH44" s="24" t="n"/>
-      <c r="AI44" s="31" t="n"/>
-      <c r="AJ44" s="31" t="n"/>
-      <c r="AK44" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL44" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM44" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN44" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO44" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP44" s="24" t="inlineStr">
-        <is>
-          <t>Johnny Speeds</t>
-        </is>
-      </c>
-      <c r="AQ44" s="24" t="inlineStr">
-        <is>
-          <t>Johnny Speeds</t>
-        </is>
-      </c>
-      <c r="AR44" s="24" t="inlineStr">
-        <is>
-          <t>Johnny Speeds</t>
-        </is>
-      </c>
-      <c r="AS44" s="24" t="inlineStr">
-        <is>
-          <t>Metizport</t>
-        </is>
-      </c>
-      <c r="AT44" s="24" t="inlineStr">
-        <is>
-          <t>Metizport</t>
-        </is>
-      </c>
-      <c r="AU44" s="24" t="inlineStr">
-        <is>
-          <t>Metizport</t>
-        </is>
-      </c>
-      <c r="AV44" s="24" t="n"/>
-      <c r="AW44" s="24" t="n"/>
-      <c r="AX44" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY44" s="24" t="n"/>
-      <c r="AZ44" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA44" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BB44" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC44" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD44" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BE44" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF44" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG44" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH44" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:24.972799Z</t>
-        </is>
-      </c>
-      <c r="BI44" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ44" s="25" t="n"/>
-      <c r="BK44" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL44" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="BM44" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="BN44" s="28" t="n"/>
-      <c r="BO44" s="28" t="n"/>
-      <c r="BP44" s="25" t="n"/>
-      <c r="BQ44" s="27" t="n"/>
-      <c r="BR44" s="28" t="n"/>
-      <c r="BS44" s="28" t="n"/>
-      <c r="BT44" s="28" t="n"/>
-      <c r="BU44" s="25" t="n"/>
-      <c r="BV44" s="29" t="n"/>
-      <c r="BW44" s="24" t="n"/>
-      <c r="BX44" s="30" t="n"/>
-      <c r="BY44" s="27" t="n"/>
-      <c r="BZ44" s="24" t="n"/>
-      <c r="CA44" s="31" t="n"/>
-      <c r="CB44" s="24" t="n"/>
-      <c r="CC44" s="24" t="n"/>
-      <c r="CD44" s="24" t="n"/>
-      <c r="CE44" s="24" t="n"/>
-      <c r="CF44" s="24" t="n"/>
-      <c r="CG44" s="24" t="n"/>
-      <c r="CH44" s="24" t="n"/>
-      <c r="CI44" s="24" t="n"/>
-      <c r="CJ44" s="24" t="n"/>
-      <c r="CK44" s="24" t="n"/>
-      <c r="CL44" s="24" t="n"/>
-      <c r="CM44" s="24" t="n"/>
-      <c r="CN44" s="24" t="n"/>
-      <c r="CO44" s="24" t="n"/>
-      <c r="CP44" s="24" t="n"/>
-      <c r="CQ44" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="36" customHeight="1">
-      <c r="A45" s="24" t="inlineStr">
-        <is>
-          <t>764e0a0baf8d46d6</t>
-        </is>
-      </c>
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:33.678893Z</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:00:00Z</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="inlineStr">
-        <is>
-          <t>68289</t>
-        </is>
-      </c>
-      <c r="E45" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F45" s="24" t="inlineStr">
-        <is>
-          <t>FURY</t>
-        </is>
-      </c>
-      <c r="G45" s="24" t="inlineStr">
-        <is>
-          <t>Mindfreak</t>
-        </is>
-      </c>
-      <c r="H45" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I45" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J45" s="25" t="n"/>
-      <c r="K45" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L45" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="M45" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="N45" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="O45" s="28" t="n">
-        <v>0.599198</v>
-      </c>
-      <c r="P45" s="28" t="n"/>
-      <c r="Q45" s="28" t="n">
-        <v>0.019366</v>
-      </c>
-      <c r="R45" s="26" t="n">
-        <v>30</v>
-      </c>
-      <c r="S45" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T45" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U45" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V45" s="24" t="n"/>
-      <c r="W45" s="26" t="n"/>
-      <c r="X45" s="26" t="n"/>
-      <c r="Y45" s="25" t="n"/>
-      <c r="Z45" s="26" t="n"/>
-      <c r="AA45" s="28" t="n"/>
-      <c r="AB45" s="28" t="n"/>
-      <c r="AC45" s="30" t="n"/>
-      <c r="AD45" s="24" t="n"/>
-      <c r="AE45" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF45" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG45" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH45" s="24" t="n"/>
-      <c r="AI45" s="31" t="n"/>
-      <c r="AJ45" s="31" t="n"/>
-      <c r="AK45" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL45" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM45" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN45" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO45" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP45" s="24" t="inlineStr">
-        <is>
-          <t>FURY</t>
-        </is>
-      </c>
-      <c r="AQ45" s="24" t="inlineStr">
-        <is>
-          <t>FURY</t>
-        </is>
-      </c>
-      <c r="AR45" s="24" t="inlineStr">
-        <is>
-          <t>FURY</t>
-        </is>
-      </c>
-      <c r="AS45" s="24" t="inlineStr">
-        <is>
-          <t>Mindfreak</t>
-        </is>
-      </c>
-      <c r="AT45" s="24" t="inlineStr">
-        <is>
-          <t>Mindfreak</t>
-        </is>
-      </c>
-      <c r="AU45" s="24" t="inlineStr">
-        <is>
-          <t>Mindfreak</t>
-        </is>
-      </c>
-      <c r="AV45" s="24" t="n"/>
-      <c r="AW45" s="24" t="n"/>
-      <c r="AX45" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY45" s="24" t="n"/>
-      <c r="AZ45" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA45" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BB45" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC45" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD45" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BE45" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF45" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG45" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH45" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:25.545768Z</t>
-        </is>
-      </c>
-      <c r="BI45" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ45" s="25" t="n"/>
-      <c r="BK45" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="BL45" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="BM45" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="BN45" s="28" t="n"/>
-      <c r="BO45" s="28" t="n"/>
-      <c r="BP45" s="25" t="n"/>
-      <c r="BQ45" s="27" t="n"/>
-      <c r="BR45" s="28" t="n"/>
-      <c r="BS45" s="28" t="n"/>
-      <c r="BT45" s="28" t="n"/>
-      <c r="BU45" s="25" t="n"/>
-      <c r="BV45" s="29" t="n"/>
-      <c r="BW45" s="24" t="n"/>
-      <c r="BX45" s="30" t="n"/>
-      <c r="BY45" s="27" t="n"/>
-      <c r="BZ45" s="24" t="n"/>
-      <c r="CA45" s="31" t="n"/>
-      <c r="CB45" s="24" t="n"/>
-      <c r="CC45" s="24" t="n"/>
-      <c r="CD45" s="24" t="n"/>
-      <c r="CE45" s="24" t="n"/>
-      <c r="CF45" s="24" t="n"/>
-      <c r="CG45" s="24" t="n"/>
-      <c r="CH45" s="24" t="n"/>
-      <c r="CI45" s="24" t="n"/>
-      <c r="CJ45" s="24" t="n"/>
-      <c r="CK45" s="24" t="n"/>
-      <c r="CL45" s="24" t="n"/>
-      <c r="CM45" s="24" t="n"/>
-      <c r="CN45" s="24" t="n"/>
-      <c r="CO45" s="24" t="n"/>
-      <c r="CP45" s="24" t="n"/>
-      <c r="CQ45" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="36" customHeight="1">
-      <c r="A46" s="24" t="inlineStr">
-        <is>
-          <t>1a4598e6fc31416c</t>
-        </is>
-      </c>
-      <c r="B46" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:33.678893Z</t>
-        </is>
-      </c>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="D46" s="24" t="inlineStr">
-        <is>
-          <t>67578</t>
-        </is>
-      </c>
-      <c r="E46" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F46" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="G46" s="24" t="inlineStr">
-        <is>
-          <t>Recrent Club</t>
-        </is>
-      </c>
-      <c r="H46" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I46" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J46" s="25" t="n"/>
-      <c r="K46" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L46" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="M46" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="N46" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O46" s="28" t="n">
-        <v>0.526938</v>
-      </c>
-      <c r="P46" s="28" t="n"/>
-      <c r="Q46" s="28" t="n">
-        <v>-0.073062</v>
-      </c>
-      <c r="R46" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T46" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U46" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V46" s="24" t="n"/>
-      <c r="W46" s="26" t="n"/>
-      <c r="X46" s="26" t="n"/>
-      <c r="Y46" s="25" t="n"/>
-      <c r="Z46" s="26" t="n"/>
-      <c r="AA46" s="28" t="n"/>
-      <c r="AB46" s="28" t="n"/>
-      <c r="AC46" s="30" t="n"/>
-      <c r="AD46" s="24" t="n"/>
-      <c r="AE46" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF46" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG46" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH46" s="24" t="n"/>
-      <c r="AI46" s="31" t="n"/>
-      <c r="AJ46" s="31" t="n"/>
-      <c r="AK46" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL46" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM46" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN46" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO46" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP46" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AQ46" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AR46" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AS46" s="24" t="inlineStr">
-        <is>
-          <t>Recrent Club</t>
-        </is>
-      </c>
-      <c r="AT46" s="24" t="inlineStr">
-        <is>
-          <t>Recrent Club</t>
-        </is>
-      </c>
-      <c r="AU46" s="24" t="inlineStr">
-        <is>
-          <t>Recrent Club</t>
-        </is>
-      </c>
-      <c r="AV46" s="24" t="n"/>
-      <c r="AW46" s="24" t="n"/>
-      <c r="AX46" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY46" s="24" t="n"/>
-      <c r="AZ46" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA46" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BB46" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC46" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD46" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BE46" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF46" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG46" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH46" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:27.133627Z</t>
-        </is>
-      </c>
-      <c r="BI46" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ46" s="25" t="n"/>
-      <c r="BK46" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="BL46" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="BM46" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BN46" s="28" t="n"/>
-      <c r="BO46" s="28" t="n"/>
-      <c r="BP46" s="25" t="n"/>
-      <c r="BQ46" s="27" t="n"/>
-      <c r="BR46" s="28" t="n"/>
-      <c r="BS46" s="28" t="n"/>
-      <c r="BT46" s="28" t="n"/>
-      <c r="BU46" s="25" t="n"/>
-      <c r="BV46" s="29" t="n"/>
-      <c r="BW46" s="24" t="n"/>
-      <c r="BX46" s="30" t="n"/>
-      <c r="BY46" s="27" t="n"/>
-      <c r="BZ46" s="24" t="n"/>
-      <c r="CA46" s="31" t="n"/>
-      <c r="CB46" s="24" t="n"/>
-      <c r="CC46" s="24" t="n"/>
-      <c r="CD46" s="24" t="n"/>
-      <c r="CE46" s="24" t="n"/>
-      <c r="CF46" s="24" t="n"/>
-      <c r="CG46" s="24" t="n"/>
-      <c r="CH46" s="24" t="n"/>
-      <c r="CI46" s="24" t="n"/>
-      <c r="CJ46" s="24" t="n"/>
-      <c r="CK46" s="24" t="n"/>
-      <c r="CL46" s="24" t="n"/>
-      <c r="CM46" s="24" t="n"/>
-      <c r="CN46" s="24" t="n"/>
-      <c r="CO46" s="24" t="n"/>
-      <c r="CP46" s="24" t="n"/>
-      <c r="CQ46" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="36" customHeight="1">
-      <c r="A47" s="24" t="inlineStr">
-        <is>
-          <t>b9cdb810520747b9</t>
-        </is>
-      </c>
-      <c r="B47" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:33.678893Z</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="inlineStr">
-        <is>
-          <t>69135</t>
-        </is>
-      </c>
-      <c r="E47" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F47" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUBY</t>
-        </is>
-      </c>
-      <c r="G47" s="24" t="inlineStr">
-        <is>
-          <t>1WIN</t>
-        </is>
-      </c>
-      <c r="H47" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I47" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J47" s="25" t="n"/>
-      <c r="K47" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L47" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="M47" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="N47" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="O47" s="28" t="n">
-        <v>0.527203</v>
-      </c>
-      <c r="P47" s="28" t="n"/>
-      <c r="Q47" s="28" t="n">
-        <v>-0.082172</v>
-      </c>
-      <c r="R47" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T47" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U47" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V47" s="24" t="n"/>
-      <c r="W47" s="26" t="n"/>
-      <c r="X47" s="26" t="n"/>
-      <c r="Y47" s="25" t="n"/>
-      <c r="Z47" s="26" t="n"/>
-      <c r="AA47" s="28" t="n"/>
-      <c r="AB47" s="28" t="n"/>
-      <c r="AC47" s="30" t="n"/>
-      <c r="AD47" s="24" t="n"/>
-      <c r="AE47" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-1win-exruby-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF47" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG47" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH47" s="24" t="n"/>
-      <c r="AI47" s="31" t="n"/>
-      <c r="AJ47" s="31" t="n"/>
-      <c r="AK47" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL47" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM47" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN47" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO47" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP47" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUBY</t>
-        </is>
-      </c>
-      <c r="AQ47" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUBY</t>
-        </is>
-      </c>
-      <c r="AR47" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUBY</t>
-        </is>
-      </c>
-      <c r="AS47" s="24" t="inlineStr">
-        <is>
-          <t>1WIN</t>
-        </is>
-      </c>
-      <c r="AT47" s="24" t="inlineStr">
-        <is>
-          <t>1WIN</t>
-        </is>
-      </c>
-      <c r="AU47" s="24" t="inlineStr">
-        <is>
-          <t>1WIN</t>
-        </is>
-      </c>
-      <c r="AV47" s="24" t="n"/>
-      <c r="AW47" s="24" t="n"/>
-      <c r="AX47" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY47" s="24" t="n"/>
-      <c r="AZ47" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA47" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BB47" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC47" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD47" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BE47" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF47" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG47" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH47" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:27.628665Z</t>
-        </is>
-      </c>
-      <c r="BI47" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ47" s="25" t="n"/>
-      <c r="BK47" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="BL47" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="BM47" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="BN47" s="28" t="n"/>
-      <c r="BO47" s="28" t="n"/>
-      <c r="BP47" s="25" t="n"/>
-      <c r="BQ47" s="27" t="n"/>
-      <c r="BR47" s="28" t="n"/>
-      <c r="BS47" s="28" t="n"/>
-      <c r="BT47" s="28" t="n"/>
-      <c r="BU47" s="25" t="n"/>
-      <c r="BV47" s="29" t="n"/>
-      <c r="BW47" s="24" t="n"/>
-      <c r="BX47" s="30" t="n"/>
-      <c r="BY47" s="27" t="n"/>
-      <c r="BZ47" s="24" t="n"/>
-      <c r="CA47" s="31" t="n"/>
-      <c r="CB47" s="24" t="n"/>
-      <c r="CC47" s="24" t="n"/>
-      <c r="CD47" s="24" t="n"/>
-      <c r="CE47" s="24" t="n"/>
-      <c r="CF47" s="24" t="n"/>
-      <c r="CG47" s="24" t="n"/>
-      <c r="CH47" s="24" t="n"/>
-      <c r="CI47" s="24" t="n"/>
-      <c r="CJ47" s="24" t="n"/>
-      <c r="CK47" s="24" t="n"/>
-      <c r="CL47" s="24" t="n"/>
-      <c r="CM47" s="24" t="n"/>
-      <c r="CN47" s="24" t="n"/>
-      <c r="CO47" s="24" t="n"/>
-      <c r="CP47" s="24" t="n"/>
-      <c r="CQ47" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="36" customHeight="1">
-      <c r="A48" s="24" t="inlineStr">
-        <is>
-          <t>5db8343fe430460b</t>
-        </is>
-      </c>
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:33.678893Z</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="inlineStr">
-        <is>
-          <t>69267</t>
-        </is>
-      </c>
-      <c r="E48" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F48" s="24" t="inlineStr">
-        <is>
-          <t>los kogutos</t>
-        </is>
-      </c>
-      <c r="G48" s="24" t="inlineStr">
-        <is>
-          <t>Just Players</t>
-        </is>
-      </c>
-      <c r="H48" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I48" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J48" s="25" t="n"/>
-      <c r="K48" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L48" s="26" t="n">
-        <v>-213</v>
-      </c>
-      <c r="M48" s="27" t="n">
-        <v>1.469484</v>
-      </c>
-      <c r="N48" s="28" t="n">
-        <v>0.680511</v>
-      </c>
-      <c r="O48" s="28" t="n">
-        <v>0.628889</v>
-      </c>
-      <c r="P48" s="28" t="n"/>
-      <c r="Q48" s="28" t="n">
-        <v>-0.051622</v>
-      </c>
-      <c r="R48" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T48" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U48" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V48" s="24" t="n"/>
-      <c r="W48" s="26" t="n"/>
-      <c r="X48" s="26" t="n"/>
-      <c r="Y48" s="25" t="n"/>
-      <c r="Z48" s="26" t="n"/>
-      <c r="AA48" s="28" t="n"/>
-      <c r="AB48" s="28" t="n"/>
-      <c r="AC48" s="30" t="n"/>
-      <c r="AD48" s="24" t="n"/>
-      <c r="AE48" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jpu-lk-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF48" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG48" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH48" s="24" t="n"/>
-      <c r="AI48" s="31" t="n"/>
-      <c r="AJ48" s="31" t="n"/>
-      <c r="AK48" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL48" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM48" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN48" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO48" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP48" s="24" t="inlineStr">
-        <is>
-          <t>los kogutos</t>
-        </is>
-      </c>
-      <c r="AQ48" s="24" t="inlineStr">
-        <is>
-          <t>los kogutos</t>
-        </is>
-      </c>
-      <c r="AR48" s="24" t="inlineStr">
-        <is>
-          <t>los kogutos</t>
-        </is>
-      </c>
-      <c r="AS48" s="24" t="inlineStr">
-        <is>
-          <t>Just Players</t>
-        </is>
-      </c>
-      <c r="AT48" s="24" t="inlineStr">
-        <is>
-          <t>Just Players</t>
-        </is>
-      </c>
-      <c r="AU48" s="24" t="inlineStr">
-        <is>
-          <t>Just Players</t>
-        </is>
-      </c>
-      <c r="AV48" s="24" t="n"/>
-      <c r="AW48" s="24" t="n"/>
-      <c r="AX48" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY48" s="24" t="n"/>
-      <c r="AZ48" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA48" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BB48" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC48" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD48" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BE48" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF48" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG48" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH48" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:28.112728Z</t>
-        </is>
-      </c>
-      <c r="BI48" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ48" s="25" t="n"/>
-      <c r="BK48" s="26" t="n">
-        <v>-213</v>
-      </c>
-      <c r="BL48" s="27" t="n">
-        <v>1.469484</v>
-      </c>
-      <c r="BM48" s="28" t="n">
-        <v>0.680511</v>
-      </c>
-      <c r="BN48" s="28" t="n"/>
-      <c r="BO48" s="28" t="n"/>
-      <c r="BP48" s="25" t="n"/>
-      <c r="BQ48" s="27" t="n"/>
-      <c r="BR48" s="28" t="n"/>
-      <c r="BS48" s="28" t="n"/>
-      <c r="BT48" s="28" t="n"/>
-      <c r="BU48" s="25" t="n"/>
-      <c r="BV48" s="29" t="n"/>
-      <c r="BW48" s="24" t="n"/>
-      <c r="BX48" s="30" t="n"/>
-      <c r="BY48" s="27" t="n"/>
-      <c r="BZ48" s="24" t="n"/>
-      <c r="CA48" s="31" t="n"/>
-      <c r="CB48" s="24" t="n"/>
-      <c r="CC48" s="24" t="n"/>
-      <c r="CD48" s="24" t="n"/>
-      <c r="CE48" s="24" t="n"/>
-      <c r="CF48" s="24" t="n"/>
-      <c r="CG48" s="24" t="n"/>
-      <c r="CH48" s="24" t="n"/>
-      <c r="CI48" s="24" t="n"/>
-      <c r="CJ48" s="24" t="n"/>
-      <c r="CK48" s="24" t="n"/>
-      <c r="CL48" s="24" t="n"/>
-      <c r="CM48" s="24" t="n"/>
-      <c r="CN48" s="24" t="n"/>
-      <c r="CO48" s="24" t="n"/>
-      <c r="CP48" s="24" t="n"/>
-      <c r="CQ48" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="A49" s="24" t="inlineStr">
-        <is>
-          <t>1873182b7743440f</t>
-        </is>
-      </c>
-      <c r="B49" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:33.678893Z</t>
-        </is>
-      </c>
-      <c r="C49" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T13:45:00Z</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="inlineStr">
-        <is>
-          <t>67579</t>
-        </is>
-      </c>
-      <c r="E49" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F49" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="G49" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="H49" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I49" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J49" s="25" t="n"/>
-      <c r="K49" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L49" s="26" t="n">
-        <v>194</v>
-      </c>
-      <c r="M49" s="27" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="N49" s="28" t="n">
-        <v>0.340136</v>
-      </c>
-      <c r="O49" s="28" t="n">
-        <v>0.526281</v>
-      </c>
-      <c r="P49" s="28" t="n"/>
-      <c r="Q49" s="28" t="n">
-        <v>0.186145</v>
-      </c>
-      <c r="R49" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S49" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T49" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U49" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V49" s="24" t="n"/>
-      <c r="W49" s="26" t="n"/>
-      <c r="X49" s="26" t="n"/>
-      <c r="Y49" s="25" t="n"/>
-      <c r="Z49" s="26" t="n"/>
-      <c r="AA49" s="28" t="n"/>
-      <c r="AB49" s="28" t="n"/>
-      <c r="AC49" s="30" t="n"/>
-      <c r="AD49" s="24" t="n"/>
-      <c r="AE49" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF49" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG49" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH49" s="24" t="n"/>
-      <c r="AI49" s="31" t="n"/>
-      <c r="AJ49" s="31" t="n"/>
-      <c r="AK49" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL49" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM49" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN49" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO49" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP49" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="AQ49" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="AR49" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="AS49" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AT49" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AU49" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AV49" s="24" t="n"/>
-      <c r="AW49" s="24" t="n"/>
-      <c r="AX49" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY49" s="24" t="n"/>
-      <c r="AZ49" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA49" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BB49" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC49" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD49" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BE49" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF49" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG49" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH49" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:28.608319Z</t>
-        </is>
-      </c>
-      <c r="BI49" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ49" s="25" t="n"/>
-      <c r="BK49" s="26" t="n">
-        <v>194</v>
-      </c>
-      <c r="BL49" s="27" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BM49" s="28" t="n">
-        <v>0.340136</v>
-      </c>
-      <c r="BN49" s="28" t="n"/>
-      <c r="BO49" s="28" t="n"/>
-      <c r="BP49" s="25" t="n"/>
-      <c r="BQ49" s="27" t="n"/>
-      <c r="BR49" s="28" t="n"/>
-      <c r="BS49" s="28" t="n"/>
-      <c r="BT49" s="28" t="n"/>
-      <c r="BU49" s="25" t="n"/>
-      <c r="BV49" s="29" t="n"/>
-      <c r="BW49" s="24" t="n"/>
-      <c r="BX49" s="30" t="n"/>
-      <c r="BY49" s="27" t="n"/>
-      <c r="BZ49" s="24" t="n"/>
-      <c r="CA49" s="31" t="n"/>
-      <c r="CB49" s="24" t="n"/>
-      <c r="CC49" s="24" t="n"/>
-      <c r="CD49" s="24" t="n"/>
-      <c r="CE49" s="24" t="n"/>
-      <c r="CF49" s="24" t="n"/>
-      <c r="CG49" s="24" t="n"/>
-      <c r="CH49" s="24" t="n"/>
-      <c r="CI49" s="24" t="n"/>
-      <c r="CJ49" s="24" t="n"/>
-      <c r="CK49" s="24" t="n"/>
-      <c r="CL49" s="24" t="n"/>
-      <c r="CM49" s="24" t="n"/>
-      <c r="CN49" s="24" t="n"/>
-      <c r="CO49" s="24" t="n"/>
-      <c r="CP49" s="24" t="n"/>
-      <c r="CQ49" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="A50" s="24" t="inlineStr">
-        <is>
-          <t>17895dec8a5c4c08</t>
-        </is>
-      </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:33.678893Z</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D50" s="24" t="inlineStr">
-        <is>
-          <t>68292</t>
-        </is>
-      </c>
-      <c r="E50" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F50" s="24" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="G50" s="24" t="inlineStr">
-        <is>
-          <t>ARCRED</t>
-        </is>
-      </c>
-      <c r="H50" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I50" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J50" s="25" t="n"/>
-      <c r="K50" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L50" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M50" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N50" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O50" s="28" t="n">
-        <v>0.613947</v>
-      </c>
-      <c r="P50" s="28" t="n"/>
-      <c r="Q50" s="28" t="n">
-        <v>-0.026341</v>
-      </c>
-      <c r="R50" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="S50" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T50" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U50" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V50" s="24" t="n"/>
-      <c r="W50" s="26" t="n"/>
-      <c r="X50" s="26" t="n"/>
-      <c r="Y50" s="25" t="n"/>
-      <c r="Z50" s="26" t="n"/>
-      <c r="AA50" s="28" t="n"/>
-      <c r="AB50" s="28" t="n"/>
-      <c r="AC50" s="30" t="n"/>
-      <c r="AD50" s="24" t="n"/>
-      <c r="AE50" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-arc-btf-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF50" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG50" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH50" s="24" t="n"/>
-      <c r="AI50" s="31" t="n"/>
-      <c r="AJ50" s="31" t="n"/>
-      <c r="AK50" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL50" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM50" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN50" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO50" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP50" s="24" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="AQ50" s="24" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="AR50" s="24" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="AS50" s="24" t="inlineStr">
-        <is>
-          <t>ARCRED</t>
-        </is>
-      </c>
-      <c r="AT50" s="24" t="inlineStr">
-        <is>
-          <t>ARCRED</t>
-        </is>
-      </c>
-      <c r="AU50" s="24" t="inlineStr">
-        <is>
-          <t>ARCRED</t>
-        </is>
-      </c>
-      <c r="AV50" s="24" t="n"/>
-      <c r="AW50" s="24" t="n"/>
-      <c r="AX50" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY50" s="24" t="n"/>
-      <c r="AZ50" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA50" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BB50" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC50" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD50" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BE50" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF50" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG50" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH50" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:29.071469Z</t>
-        </is>
-      </c>
-      <c r="BI50" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ50" s="25" t="n"/>
-      <c r="BK50" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL50" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM50" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN50" s="28" t="n"/>
-      <c r="BO50" s="28" t="n"/>
-      <c r="BP50" s="25" t="n"/>
-      <c r="BQ50" s="27" t="n"/>
-      <c r="BR50" s="28" t="n"/>
-      <c r="BS50" s="28" t="n"/>
-      <c r="BT50" s="28" t="n"/>
-      <c r="BU50" s="25" t="n"/>
-      <c r="BV50" s="29" t="n"/>
-      <c r="BW50" s="24" t="n"/>
-      <c r="BX50" s="30" t="n"/>
-      <c r="BY50" s="27" t="n"/>
-      <c r="BZ50" s="24" t="n"/>
-      <c r="CA50" s="31" t="n"/>
-      <c r="CB50" s="24" t="n"/>
-      <c r="CC50" s="24" t="n"/>
-      <c r="CD50" s="24" t="n"/>
-      <c r="CE50" s="24" t="n"/>
-      <c r="CF50" s="24" t="n"/>
-      <c r="CG50" s="24" t="n"/>
-      <c r="CH50" s="24" t="n"/>
-      <c r="CI50" s="24" t="n"/>
-      <c r="CJ50" s="24" t="n"/>
-      <c r="CK50" s="24" t="n"/>
-      <c r="CL50" s="24" t="n"/>
-      <c r="CM50" s="24" t="n"/>
-      <c r="CN50" s="24" t="n"/>
-      <c r="CO50" s="24" t="n"/>
-      <c r="CP50" s="24" t="n"/>
-      <c r="CQ50" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="36" customHeight="1">
-      <c r="A51" s="24" t="inlineStr">
-        <is>
-          <t>f50546f646024b4f</t>
-        </is>
-      </c>
-      <c r="B51" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:33.678893Z</t>
-        </is>
-      </c>
-      <c r="C51" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="inlineStr">
-        <is>
-          <t>69268</t>
-        </is>
-      </c>
-      <c r="E51" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F51" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="G51" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="H51" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I51" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J51" s="25" t="n"/>
-      <c r="K51" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L51" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M51" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N51" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O51" s="28" t="n">
-        <v>0.663025</v>
-      </c>
-      <c r="P51" s="28" t="n"/>
-      <c r="Q51" s="28" t="n">
-        <v>0.022737</v>
-      </c>
-      <c r="R51" s="26" t="n">
-        <v>31</v>
-      </c>
-      <c r="S51" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T51" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U51" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V51" s="24" t="n"/>
-      <c r="W51" s="26" t="n"/>
-      <c r="X51" s="26" t="n"/>
-      <c r="Y51" s="25" t="n"/>
-      <c r="Z51" s="26" t="n"/>
-      <c r="AA51" s="28" t="n"/>
-      <c r="AB51" s="28" t="n"/>
-      <c r="AC51" s="30" t="n"/>
-      <c r="AD51" s="24" t="n"/>
-      <c r="AE51" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF51" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG51" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH51" s="24" t="n"/>
-      <c r="AI51" s="31" t="n"/>
-      <c r="AJ51" s="31" t="n"/>
-      <c r="AK51" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL51" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM51" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN51" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO51" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP51" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AQ51" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AR51" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AS51" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AT51" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AU51" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AV51" s="24" t="n"/>
-      <c r="AW51" s="24" t="n"/>
-      <c r="AX51" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY51" s="24" t="n"/>
-      <c r="AZ51" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA51" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BB51" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC51" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD51" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BE51" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF51" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG51" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH51" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:29.527479Z</t>
-        </is>
-      </c>
-      <c r="BI51" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ51" s="25" t="n"/>
-      <c r="BK51" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL51" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM51" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN51" s="28" t="n"/>
-      <c r="BO51" s="28" t="n"/>
-      <c r="BP51" s="25" t="n"/>
-      <c r="BQ51" s="27" t="n"/>
-      <c r="BR51" s="28" t="n"/>
-      <c r="BS51" s="28" t="n"/>
-      <c r="BT51" s="28" t="n"/>
-      <c r="BU51" s="25" t="n"/>
-      <c r="BV51" s="29" t="n"/>
-      <c r="BW51" s="24" t="n"/>
-      <c r="BX51" s="30" t="n"/>
-      <c r="BY51" s="27" t="n"/>
-      <c r="BZ51" s="24" t="n"/>
-      <c r="CA51" s="31" t="n"/>
-      <c r="CB51" s="24" t="n"/>
-      <c r="CC51" s="24" t="n"/>
-      <c r="CD51" s="24" t="n"/>
-      <c r="CE51" s="24" t="n"/>
-      <c r="CF51" s="24" t="n"/>
-      <c r="CG51" s="24" t="n"/>
-      <c r="CH51" s="24" t="n"/>
-      <c r="CI51" s="24" t="n"/>
-      <c r="CJ51" s="24" t="n"/>
-      <c r="CK51" s="24" t="n"/>
-      <c r="CL51" s="24" t="n"/>
-      <c r="CM51" s="24" t="n"/>
-      <c r="CN51" s="24" t="n"/>
-      <c r="CO51" s="24" t="n"/>
-      <c r="CP51" s="24" t="n"/>
-      <c r="CQ51" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="24" t="inlineStr">
-        <is>
-          <t>bb2073accd074022</t>
-        </is>
-      </c>
-      <c r="B52" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:33.678893Z</t>
-        </is>
-      </c>
-      <c r="C52" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T23:00:00Z</t>
-        </is>
-      </c>
-      <c r="D52" s="24" t="inlineStr">
-        <is>
-          <t>68043</t>
-        </is>
-      </c>
-      <c r="E52" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F52" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="G52" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="H52" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I52" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J52" s="25" t="n"/>
-      <c r="K52" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L52" s="26" t="n">
-        <v>122</v>
-      </c>
-      <c r="M52" s="27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="N52" s="28" t="n">
-        <v>0.45045</v>
-      </c>
-      <c r="O52" s="28" t="n">
-        <v>0.569644</v>
-      </c>
-      <c r="P52" s="28" t="n"/>
-      <c r="Q52" s="28" t="n">
-        <v>0.119194</v>
-      </c>
-      <c r="R52" s="26" t="n">
-        <v>80</v>
-      </c>
-      <c r="S52" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T52" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U52" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V52" s="24" t="n"/>
-      <c r="W52" s="26" t="n"/>
-      <c r="X52" s="26" t="n"/>
-      <c r="Y52" s="25" t="n"/>
-      <c r="Z52" s="26" t="n"/>
-      <c r="AA52" s="28" t="n"/>
-      <c r="AB52" s="28" t="n"/>
-      <c r="AC52" s="30" t="n"/>
-      <c r="AD52" s="24" t="n"/>
-      <c r="AE52" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF52" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG52" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH52" s="24" t="n"/>
-      <c r="AI52" s="31" t="n"/>
-      <c r="AJ52" s="31" t="n"/>
-      <c r="AK52" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL52" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM52" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN52" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO52" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP52" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AQ52" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AR52" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AS52" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="AT52" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="AU52" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="AV52" s="24" t="n"/>
-      <c r="AW52" s="24" t="n"/>
-      <c r="AX52" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY52" s="24" t="n"/>
-      <c r="AZ52" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA52" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BB52" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC52" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD52" s="24" t="inlineStr">
-        <is>
-          <t>4c897e659ec9db491c18706ace7c94ba8af6df222c16d377d3bd7391aba18f91</t>
-        </is>
-      </c>
-      <c r="BE52" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF52" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG52" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH52" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T16:53:33.675629Z</t>
-        </is>
-      </c>
-      <c r="BI52" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ52" s="25" t="n"/>
-      <c r="BK52" s="26" t="n">
-        <v>122</v>
-      </c>
-      <c r="BL52" s="27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BM52" s="28" t="n">
-        <v>0.45045</v>
-      </c>
-      <c r="BN52" s="28" t="n"/>
-      <c r="BO52" s="28" t="n"/>
-      <c r="BP52" s="25" t="n"/>
-      <c r="BQ52" s="27" t="n"/>
-      <c r="BR52" s="28" t="n"/>
-      <c r="BS52" s="28" t="n"/>
-      <c r="BT52" s="28" t="n"/>
-      <c r="BU52" s="25" t="n"/>
-      <c r="BV52" s="29" t="n"/>
-      <c r="BW52" s="24" t="n"/>
-      <c r="BX52" s="30" t="n"/>
-      <c r="BY52" s="27" t="n"/>
-      <c r="BZ52" s="24" t="n"/>
-      <c r="CA52" s="31" t="n"/>
-      <c r="CB52" s="24" t="n"/>
-      <c r="CC52" s="24" t="n"/>
-      <c r="CD52" s="24" t="n"/>
-      <c r="CE52" s="24" t="n"/>
-      <c r="CF52" s="24" t="n"/>
-      <c r="CG52" s="24" t="n"/>
-      <c r="CH52" s="24" t="n"/>
-      <c r="CI52" s="24" t="n"/>
-      <c r="CJ52" s="24" t="n"/>
-      <c r="CK52" s="24" t="n"/>
-      <c r="CL52" s="24" t="n"/>
-      <c r="CM52" s="24" t="n"/>
-      <c r="CN52" s="24" t="n"/>
-      <c r="CO52" s="24" t="n"/>
-      <c r="CP52" s="24" t="n"/>
-      <c r="CQ52" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ39" headerRowCount="1">
-  <autoFilter ref="A1:CQ39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ52" headerRowCount="1">
+  <autoFilter ref="A1:CQ52"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$39)</f>
+        <f>COUNTA('Picks'!$A$2:$A$52)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$39,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$52,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$39,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$52,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")+COUNTIFS('Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$39,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$52,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")/(COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"win")+COUNTIFS('Picks'!$BX$2:$BX$39,"&gt;0",'Picks'!$V$2:$V$39,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")/(COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")+COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$39)/SUM('Picks'!$BX$2:$BX$39),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$52)/SUM('Picks'!$BX$2:$BX$52),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$39)</f>
+        <f>SUM('Picks'!$BY$2:$BY$52)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$39,"&lt;&gt;",'Picks'!$AB$2:$AB$39),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$52,"&lt;&gt;",'Picks'!$AB$2:$AB$52),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$39,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$52,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$52,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$39,'Picks'!$AM$2:$AM$39,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$52,'Picks'!$AM$2:$AM$52,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A14,'Picks'!$U$2:$U$39,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A15,'Picks'!$U$2:$U$39,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled",'Picks'!$V$2:$V$39,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$39,'Picks'!$H$2:$H$39,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$39,'Picks'!$H$2:$H$39,$A16,'Picks'!$U$2:$U$39,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ39"/>
+  <dimension ref="A1:CQ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12349,6 +12349,3477 @@
         </is>
       </c>
     </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>6c52c8bb3cb74a30</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.505470Z</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>69289</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>ShindeN</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I40" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J40" s="25" t="n"/>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L40" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M40" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N40" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O40" s="28" t="n">
+        <v>0.5108819999999999</v>
+      </c>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="28" t="n">
+        <v>0.110882</v>
+      </c>
+      <c r="R40" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="S40" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U40" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V40" s="24" t="n"/>
+      <c r="W40" s="26" t="n"/>
+      <c r="X40" s="26" t="n"/>
+      <c r="Y40" s="25" t="n"/>
+      <c r="Z40" s="26" t="n"/>
+      <c r="AA40" s="28" t="n"/>
+      <c r="AB40" s="28" t="n"/>
+      <c r="AC40" s="30" t="n"/>
+      <c r="AD40" s="24" t="n"/>
+      <c r="AE40" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-cs2-shin-bst-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF40" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG40" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH40" s="24" t="n"/>
+      <c r="AI40" s="31" t="n"/>
+      <c r="AJ40" s="31" t="n"/>
+      <c r="AK40" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL40" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM40" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN40" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO40" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP40" s="24" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="AQ40" s="24" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="AR40" s="24" t="inlineStr">
+        <is>
+          <t>BESTIA</t>
+        </is>
+      </c>
+      <c r="AS40" s="24" t="inlineStr">
+        <is>
+          <t>ShindeN</t>
+        </is>
+      </c>
+      <c r="AT40" s="24" t="inlineStr">
+        <is>
+          <t>ShindeN</t>
+        </is>
+      </c>
+      <c r="AU40" s="24" t="inlineStr">
+        <is>
+          <t>ShindeN</t>
+        </is>
+      </c>
+      <c r="AV40" s="24" t="n"/>
+      <c r="AW40" s="24" t="n"/>
+      <c r="AX40" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY40" s="24" t="n"/>
+      <c r="AZ40" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA40" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BB40" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC40" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD40" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BE40" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF40" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG40" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:28.086385Z</t>
+        </is>
+      </c>
+      <c r="BI40" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ40" s="25" t="n"/>
+      <c r="BK40" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL40" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM40" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN40" s="28" t="n"/>
+      <c r="BO40" s="28" t="n"/>
+      <c r="BP40" s="25" t="n"/>
+      <c r="BQ40" s="27" t="n"/>
+      <c r="BR40" s="28" t="n"/>
+      <c r="BS40" s="28" t="n"/>
+      <c r="BT40" s="28" t="n"/>
+      <c r="BU40" s="25" t="n"/>
+      <c r="BV40" s="29" t="n"/>
+      <c r="BW40" s="24" t="n"/>
+      <c r="BX40" s="30" t="n"/>
+      <c r="BY40" s="27" t="n"/>
+      <c r="BZ40" s="24" t="n"/>
+      <c r="CA40" s="31" t="n"/>
+      <c r="CB40" s="24" t="n"/>
+      <c r="CC40" s="24" t="n"/>
+      <c r="CD40" s="24" t="n"/>
+      <c r="CE40" s="24" t="n"/>
+      <c r="CF40" s="24" t="n"/>
+      <c r="CG40" s="24" t="n"/>
+      <c r="CH40" s="24" t="n"/>
+      <c r="CI40" s="24" t="n"/>
+      <c r="CJ40" s="24" t="n"/>
+      <c r="CK40" s="24" t="n"/>
+      <c r="CL40" s="24" t="n"/>
+      <c r="CM40" s="24" t="n"/>
+      <c r="CN40" s="24" t="n"/>
+      <c r="CO40" s="24" t="n"/>
+      <c r="CP40" s="24" t="n"/>
+      <c r="CQ40" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>44e90abb54a64c7a</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.505470Z</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>67576</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>mokrivskiy Club</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="H41" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I41" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J41" s="25" t="n"/>
+      <c r="K41" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M41" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N41" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O41" s="28" t="n">
+        <v>0.579552</v>
+      </c>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="28" t="n">
+        <v>0.139023</v>
+      </c>
+      <c r="R41" s="26" t="n">
+        <v>90</v>
+      </c>
+      <c r="S41" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T41" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U41" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V41" s="24" t="n"/>
+      <c r="W41" s="26" t="n"/>
+      <c r="X41" s="26" t="n"/>
+      <c r="Y41" s="25" t="n"/>
+      <c r="Z41" s="26" t="n"/>
+      <c r="AA41" s="28" t="n"/>
+      <c r="AB41" s="28" t="n"/>
+      <c r="AC41" s="30" t="n"/>
+      <c r="AD41" s="24" t="n"/>
+      <c r="AE41" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF41" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG41" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH41" s="24" t="n"/>
+      <c r="AI41" s="31" t="n"/>
+      <c r="AJ41" s="31" t="n"/>
+      <c r="AK41" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL41" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM41" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN41" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO41" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP41" s="24" t="inlineStr">
+        <is>
+          <t>mokrivskiy Club</t>
+        </is>
+      </c>
+      <c r="AQ41" s="24" t="inlineStr">
+        <is>
+          <t>mokrivskiy Club</t>
+        </is>
+      </c>
+      <c r="AR41" s="24" t="inlineStr">
+        <is>
+          <t>mokrivskiy Club</t>
+        </is>
+      </c>
+      <c r="AS41" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AT41" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AU41" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AV41" s="24" t="n"/>
+      <c r="AW41" s="24" t="n"/>
+      <c r="AX41" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY41" s="24" t="n"/>
+      <c r="AZ41" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA41" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BB41" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC41" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD41" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BE41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG41" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:28.594679Z</t>
+        </is>
+      </c>
+      <c r="BI41" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ41" s="25" t="n"/>
+      <c r="BK41" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL41" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM41" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN41" s="28" t="n"/>
+      <c r="BO41" s="28" t="n"/>
+      <c r="BP41" s="25" t="n"/>
+      <c r="BQ41" s="27" t="n"/>
+      <c r="BR41" s="28" t="n"/>
+      <c r="BS41" s="28" t="n"/>
+      <c r="BT41" s="28" t="n"/>
+      <c r="BU41" s="25" t="n"/>
+      <c r="BV41" s="29" t="n"/>
+      <c r="BW41" s="24" t="n"/>
+      <c r="BX41" s="30" t="n"/>
+      <c r="BY41" s="27" t="n"/>
+      <c r="BZ41" s="24" t="n"/>
+      <c r="CA41" s="31" t="n"/>
+      <c r="CB41" s="24" t="n"/>
+      <c r="CC41" s="24" t="n"/>
+      <c r="CD41" s="24" t="n"/>
+      <c r="CE41" s="24" t="n"/>
+      <c r="CF41" s="24" t="n"/>
+      <c r="CG41" s="24" t="n"/>
+      <c r="CH41" s="24" t="n"/>
+      <c r="CI41" s="24" t="n"/>
+      <c r="CJ41" s="24" t="n"/>
+      <c r="CK41" s="24" t="n"/>
+      <c r="CL41" s="24" t="n"/>
+      <c r="CM41" s="24" t="n"/>
+      <c r="CN41" s="24" t="n"/>
+      <c r="CO41" s="24" t="n"/>
+      <c r="CP41" s="24" t="n"/>
+      <c r="CQ41" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>320877f852464418</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.505470Z</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>67577</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>SNAILKICK Club</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>Lixxx Club</t>
+        </is>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M42" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N42" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O42" s="28" t="n">
+        <v>0.526938</v>
+      </c>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="28" t="n">
+        <v>-0.082437</v>
+      </c>
+      <c r="R42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U42" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V42" s="24" t="n"/>
+      <c r="W42" s="26" t="n"/>
+      <c r="X42" s="26" t="n"/>
+      <c r="Y42" s="25" t="n"/>
+      <c r="Z42" s="26" t="n"/>
+      <c r="AA42" s="28" t="n"/>
+      <c r="AB42" s="28" t="n"/>
+      <c r="AC42" s="30" t="n"/>
+      <c r="AD42" s="24" t="n"/>
+      <c r="AE42" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF42" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG42" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH42" s="24" t="n"/>
+      <c r="AI42" s="31" t="n"/>
+      <c r="AJ42" s="31" t="n"/>
+      <c r="AK42" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM42" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN42" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO42" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP42" s="24" t="inlineStr">
+        <is>
+          <t>SNAILKICK Club</t>
+        </is>
+      </c>
+      <c r="AQ42" s="24" t="inlineStr">
+        <is>
+          <t>SNAILKICK Club</t>
+        </is>
+      </c>
+      <c r="AR42" s="24" t="inlineStr">
+        <is>
+          <t>SNAILKICK Club</t>
+        </is>
+      </c>
+      <c r="AS42" s="24" t="inlineStr">
+        <is>
+          <t>Lixxx Club</t>
+        </is>
+      </c>
+      <c r="AT42" s="24" t="inlineStr">
+        <is>
+          <t>Lixxx Club</t>
+        </is>
+      </c>
+      <c r="AU42" s="24" t="inlineStr">
+        <is>
+          <t>Lixxx Club</t>
+        </is>
+      </c>
+      <c r="AV42" s="24" t="n"/>
+      <c r="AW42" s="24" t="n"/>
+      <c r="AX42" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY42" s="24" t="n"/>
+      <c r="AZ42" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA42" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BB42" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC42" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD42" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BE42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG42" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:29.080231Z</t>
+        </is>
+      </c>
+      <c r="BI42" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ42" s="25" t="n"/>
+      <c r="BK42" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL42" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM42" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN42" s="28" t="n"/>
+      <c r="BO42" s="28" t="n"/>
+      <c r="BP42" s="25" t="n"/>
+      <c r="BQ42" s="27" t="n"/>
+      <c r="BR42" s="28" t="n"/>
+      <c r="BS42" s="28" t="n"/>
+      <c r="BT42" s="28" t="n"/>
+      <c r="BU42" s="25" t="n"/>
+      <c r="BV42" s="29" t="n"/>
+      <c r="BW42" s="24" t="n"/>
+      <c r="BX42" s="30" t="n"/>
+      <c r="BY42" s="27" t="n"/>
+      <c r="BZ42" s="24" t="n"/>
+      <c r="CA42" s="31" t="n"/>
+      <c r="CB42" s="24" t="n"/>
+      <c r="CC42" s="24" t="n"/>
+      <c r="CD42" s="24" t="n"/>
+      <c r="CE42" s="24" t="n"/>
+      <c r="CF42" s="24" t="n"/>
+      <c r="CG42" s="24" t="n"/>
+      <c r="CH42" s="24" t="n"/>
+      <c r="CI42" s="24" t="n"/>
+      <c r="CJ42" s="24" t="n"/>
+      <c r="CK42" s="24" t="n"/>
+      <c r="CL42" s="24" t="n"/>
+      <c r="CM42" s="24" t="n"/>
+      <c r="CN42" s="24" t="n"/>
+      <c r="CO42" s="24" t="n"/>
+      <c r="CP42" s="24" t="n"/>
+      <c r="CQ42" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>648e1b3a3f924bfa</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.505470Z</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>68288</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>CYBERSHOKE Prospects</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="inlineStr">
+        <is>
+          <t>WW Team</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I43" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J43" s="25" t="n"/>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L43" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M43" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N43" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O43" s="28" t="n">
+        <v>0.704209</v>
+      </c>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="28" t="n">
+        <v>0.354559</v>
+      </c>
+      <c r="R43" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S43" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T43" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U43" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V43" s="24" t="n"/>
+      <c r="W43" s="26" t="n"/>
+      <c r="X43" s="26" t="n"/>
+      <c r="Y43" s="25" t="n"/>
+      <c r="Z43" s="26" t="n"/>
+      <c r="AA43" s="28" t="n"/>
+      <c r="AB43" s="28" t="n"/>
+      <c r="AC43" s="30" t="n"/>
+      <c r="AD43" s="24" t="n"/>
+      <c r="AE43" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-cs2-ww-cshp-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF43" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG43" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH43" s="24" t="n"/>
+      <c r="AI43" s="31" t="n"/>
+      <c r="AJ43" s="31" t="n"/>
+      <c r="AK43" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL43" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM43" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN43" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO43" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP43" s="24" t="inlineStr">
+        <is>
+          <t>CYBERSHOKE Prospects</t>
+        </is>
+      </c>
+      <c r="AQ43" s="24" t="inlineStr">
+        <is>
+          <t>CYBERSHOKE Prospects</t>
+        </is>
+      </c>
+      <c r="AR43" s="24" t="inlineStr">
+        <is>
+          <t>CYBERSHOKE Prospects</t>
+        </is>
+      </c>
+      <c r="AS43" s="24" t="inlineStr">
+        <is>
+          <t>WW Team</t>
+        </is>
+      </c>
+      <c r="AT43" s="24" t="inlineStr">
+        <is>
+          <t>WW Team</t>
+        </is>
+      </c>
+      <c r="AU43" s="24" t="inlineStr">
+        <is>
+          <t>WW Team</t>
+        </is>
+      </c>
+      <c r="AV43" s="24" t="n"/>
+      <c r="AW43" s="24" t="n"/>
+      <c r="AX43" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY43" s="24" t="n"/>
+      <c r="AZ43" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA43" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BB43" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC43" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD43" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BE43" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF43" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG43" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:30.555681Z</t>
+        </is>
+      </c>
+      <c r="BI43" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ43" s="25" t="n"/>
+      <c r="BK43" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL43" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BM43" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN43" s="28" t="n"/>
+      <c r="BO43" s="28" t="n"/>
+      <c r="BP43" s="25" t="n"/>
+      <c r="BQ43" s="27" t="n"/>
+      <c r="BR43" s="28" t="n"/>
+      <c r="BS43" s="28" t="n"/>
+      <c r="BT43" s="28" t="n"/>
+      <c r="BU43" s="25" t="n"/>
+      <c r="BV43" s="29" t="n"/>
+      <c r="BW43" s="24" t="n"/>
+      <c r="BX43" s="30" t="n"/>
+      <c r="BY43" s="27" t="n"/>
+      <c r="BZ43" s="24" t="n"/>
+      <c r="CA43" s="31" t="n"/>
+      <c r="CB43" s="24" t="n"/>
+      <c r="CC43" s="24" t="n"/>
+      <c r="CD43" s="24" t="n"/>
+      <c r="CE43" s="24" t="n"/>
+      <c r="CF43" s="24" t="n"/>
+      <c r="CG43" s="24" t="n"/>
+      <c r="CH43" s="24" t="n"/>
+      <c r="CI43" s="24" t="n"/>
+      <c r="CJ43" s="24" t="n"/>
+      <c r="CK43" s="24" t="n"/>
+      <c r="CL43" s="24" t="n"/>
+      <c r="CM43" s="24" t="n"/>
+      <c r="CN43" s="24" t="n"/>
+      <c r="CO43" s="24" t="n"/>
+      <c r="CP43" s="24" t="n"/>
+      <c r="CQ43" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>c613fbc4bd254f6f</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.505470Z</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="H44" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J44" s="25" t="n"/>
+      <c r="K44" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L44" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M44" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N44" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O44" s="28" t="n">
+        <v>0.599199</v>
+      </c>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="28" t="n">
+        <v>0.019367</v>
+      </c>
+      <c r="R44" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S44" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T44" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U44" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V44" s="24" t="n"/>
+      <c r="W44" s="26" t="n"/>
+      <c r="X44" s="26" t="n"/>
+      <c r="Y44" s="25" t="n"/>
+      <c r="Z44" s="26" t="n"/>
+      <c r="AA44" s="28" t="n"/>
+      <c r="AB44" s="28" t="n"/>
+      <c r="AC44" s="30" t="n"/>
+      <c r="AD44" s="24" t="n"/>
+      <c r="AE44" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF44" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG44" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH44" s="24" t="n"/>
+      <c r="AI44" s="31" t="n"/>
+      <c r="AJ44" s="31" t="n"/>
+      <c r="AK44" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL44" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM44" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN44" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO44" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP44" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="AQ44" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="AR44" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="AS44" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="AT44" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="AU44" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="AV44" s="24" t="n"/>
+      <c r="AW44" s="24" t="n"/>
+      <c r="AX44" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY44" s="24" t="n"/>
+      <c r="AZ44" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA44" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BB44" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC44" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD44" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BE44" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF44" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG44" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:31.821007Z</t>
+        </is>
+      </c>
+      <c r="BI44" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ44" s="25" t="n"/>
+      <c r="BK44" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL44" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM44" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN44" s="28" t="n"/>
+      <c r="BO44" s="28" t="n"/>
+      <c r="BP44" s="25" t="n"/>
+      <c r="BQ44" s="27" t="n"/>
+      <c r="BR44" s="28" t="n"/>
+      <c r="BS44" s="28" t="n"/>
+      <c r="BT44" s="28" t="n"/>
+      <c r="BU44" s="25" t="n"/>
+      <c r="BV44" s="29" t="n"/>
+      <c r="BW44" s="24" t="n"/>
+      <c r="BX44" s="30" t="n"/>
+      <c r="BY44" s="27" t="n"/>
+      <c r="BZ44" s="24" t="n"/>
+      <c r="CA44" s="31" t="n"/>
+      <c r="CB44" s="24" t="n"/>
+      <c r="CC44" s="24" t="n"/>
+      <c r="CD44" s="24" t="n"/>
+      <c r="CE44" s="24" t="n"/>
+      <c r="CF44" s="24" t="n"/>
+      <c r="CG44" s="24" t="n"/>
+      <c r="CH44" s="24" t="n"/>
+      <c r="CI44" s="24" t="n"/>
+      <c r="CJ44" s="24" t="n"/>
+      <c r="CK44" s="24" t="n"/>
+      <c r="CL44" s="24" t="n"/>
+      <c r="CM44" s="24" t="n"/>
+      <c r="CN44" s="24" t="n"/>
+      <c r="CO44" s="24" t="n"/>
+      <c r="CP44" s="24" t="n"/>
+      <c r="CQ44" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>d88562aa425c4b48</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.505470Z</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>67510</t>
+        </is>
+      </c>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>Johnny Speeds</t>
+        </is>
+      </c>
+      <c r="G45" s="24" t="inlineStr">
+        <is>
+          <t>Metizport</t>
+        </is>
+      </c>
+      <c r="H45" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I45" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J45" s="25" t="n"/>
+      <c r="K45" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L45" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M45" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N45" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O45" s="28" t="n">
+        <v>0.563071</v>
+      </c>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="28" t="n">
+        <v>-0.127331</v>
+      </c>
+      <c r="R45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U45" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V45" s="24" t="n"/>
+      <c r="W45" s="26" t="n"/>
+      <c r="X45" s="26" t="n"/>
+      <c r="Y45" s="25" t="n"/>
+      <c r="Z45" s="26" t="n"/>
+      <c r="AA45" s="28" t="n"/>
+      <c r="AB45" s="28" t="n"/>
+      <c r="AC45" s="30" t="n"/>
+      <c r="AD45" s="24" t="n"/>
+      <c r="AE45" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF45" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG45" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH45" s="24" t="n"/>
+      <c r="AI45" s="31" t="n"/>
+      <c r="AJ45" s="31" t="n"/>
+      <c r="AK45" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL45" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM45" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN45" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO45" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP45" s="24" t="inlineStr">
+        <is>
+          <t>Johnny Speeds</t>
+        </is>
+      </c>
+      <c r="AQ45" s="24" t="inlineStr">
+        <is>
+          <t>Johnny Speeds</t>
+        </is>
+      </c>
+      <c r="AR45" s="24" t="inlineStr">
+        <is>
+          <t>Johnny Speeds</t>
+        </is>
+      </c>
+      <c r="AS45" s="24" t="inlineStr">
+        <is>
+          <t>Metizport</t>
+        </is>
+      </c>
+      <c r="AT45" s="24" t="inlineStr">
+        <is>
+          <t>Metizport</t>
+        </is>
+      </c>
+      <c r="AU45" s="24" t="inlineStr">
+        <is>
+          <t>Metizport</t>
+        </is>
+      </c>
+      <c r="AV45" s="24" t="n"/>
+      <c r="AW45" s="24" t="n"/>
+      <c r="AX45" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY45" s="24" t="n"/>
+      <c r="AZ45" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA45" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BB45" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC45" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD45" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BE45" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF45" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG45" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:33.313201Z</t>
+        </is>
+      </c>
+      <c r="BI45" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ45" s="25" t="n"/>
+      <c r="BK45" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL45" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM45" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN45" s="28" t="n"/>
+      <c r="BO45" s="28" t="n"/>
+      <c r="BP45" s="25" t="n"/>
+      <c r="BQ45" s="27" t="n"/>
+      <c r="BR45" s="28" t="n"/>
+      <c r="BS45" s="28" t="n"/>
+      <c r="BT45" s="28" t="n"/>
+      <c r="BU45" s="25" t="n"/>
+      <c r="BV45" s="29" t="n"/>
+      <c r="BW45" s="24" t="n"/>
+      <c r="BX45" s="30" t="n"/>
+      <c r="BY45" s="27" t="n"/>
+      <c r="BZ45" s="24" t="n"/>
+      <c r="CA45" s="31" t="n"/>
+      <c r="CB45" s="24" t="n"/>
+      <c r="CC45" s="24" t="n"/>
+      <c r="CD45" s="24" t="n"/>
+      <c r="CE45" s="24" t="n"/>
+      <c r="CF45" s="24" t="n"/>
+      <c r="CG45" s="24" t="n"/>
+      <c r="CH45" s="24" t="n"/>
+      <c r="CI45" s="24" t="n"/>
+      <c r="CJ45" s="24" t="n"/>
+      <c r="CK45" s="24" t="n"/>
+      <c r="CL45" s="24" t="n"/>
+      <c r="CM45" s="24" t="n"/>
+      <c r="CN45" s="24" t="n"/>
+      <c r="CO45" s="24" t="n"/>
+      <c r="CP45" s="24" t="n"/>
+      <c r="CQ45" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>9a50bb7a0c2d4b8a</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.505470Z</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>69135</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUBY</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>1WIN</t>
+        </is>
+      </c>
+      <c r="H46" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I46" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J46" s="25" t="n"/>
+      <c r="K46" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L46" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M46" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N46" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O46" s="28" t="n">
+        <v>0.527201</v>
+      </c>
+      <c r="P46" s="28" t="n"/>
+      <c r="Q46" s="28" t="n">
+        <v>-0.092571</v>
+      </c>
+      <c r="R46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U46" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V46" s="24" t="n"/>
+      <c r="W46" s="26" t="n"/>
+      <c r="X46" s="26" t="n"/>
+      <c r="Y46" s="25" t="n"/>
+      <c r="Z46" s="26" t="n"/>
+      <c r="AA46" s="28" t="n"/>
+      <c r="AB46" s="28" t="n"/>
+      <c r="AC46" s="30" t="n"/>
+      <c r="AD46" s="24" t="n"/>
+      <c r="AE46" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-1win-exruby-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF46" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG46" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH46" s="24" t="n"/>
+      <c r="AI46" s="31" t="n"/>
+      <c r="AJ46" s="31" t="n"/>
+      <c r="AK46" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL46" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM46" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN46" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO46" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP46" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUBY</t>
+        </is>
+      </c>
+      <c r="AQ46" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUBY</t>
+        </is>
+      </c>
+      <c r="AR46" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUBY</t>
+        </is>
+      </c>
+      <c r="AS46" s="24" t="inlineStr">
+        <is>
+          <t>1WIN</t>
+        </is>
+      </c>
+      <c r="AT46" s="24" t="inlineStr">
+        <is>
+          <t>1WIN</t>
+        </is>
+      </c>
+      <c r="AU46" s="24" t="inlineStr">
+        <is>
+          <t>1WIN</t>
+        </is>
+      </c>
+      <c r="AV46" s="24" t="n"/>
+      <c r="AW46" s="24" t="n"/>
+      <c r="AX46" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY46" s="24" t="n"/>
+      <c r="AZ46" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA46" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BB46" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC46" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD46" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BE46" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF46" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG46" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:34.765803Z</t>
+        </is>
+      </c>
+      <c r="BI46" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ46" s="25" t="n"/>
+      <c r="BK46" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL46" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM46" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN46" s="28" t="n"/>
+      <c r="BO46" s="28" t="n"/>
+      <c r="BP46" s="25" t="n"/>
+      <c r="BQ46" s="27" t="n"/>
+      <c r="BR46" s="28" t="n"/>
+      <c r="BS46" s="28" t="n"/>
+      <c r="BT46" s="28" t="n"/>
+      <c r="BU46" s="25" t="n"/>
+      <c r="BV46" s="29" t="n"/>
+      <c r="BW46" s="24" t="n"/>
+      <c r="BX46" s="30" t="n"/>
+      <c r="BY46" s="27" t="n"/>
+      <c r="BZ46" s="24" t="n"/>
+      <c r="CA46" s="31" t="n"/>
+      <c r="CB46" s="24" t="n"/>
+      <c r="CC46" s="24" t="n"/>
+      <c r="CD46" s="24" t="n"/>
+      <c r="CE46" s="24" t="n"/>
+      <c r="CF46" s="24" t="n"/>
+      <c r="CG46" s="24" t="n"/>
+      <c r="CH46" s="24" t="n"/>
+      <c r="CI46" s="24" t="n"/>
+      <c r="CJ46" s="24" t="n"/>
+      <c r="CK46" s="24" t="n"/>
+      <c r="CL46" s="24" t="n"/>
+      <c r="CM46" s="24" t="n"/>
+      <c r="CN46" s="24" t="n"/>
+      <c r="CO46" s="24" t="n"/>
+      <c r="CP46" s="24" t="n"/>
+      <c r="CQ46" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>1ec174b7c2bb4a59</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.505470Z</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>69267</t>
+        </is>
+      </c>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="H47" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I47" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J47" s="25" t="n"/>
+      <c r="K47" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L47" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="M47" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="N47" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="O47" s="28" t="n">
+        <v>0.628836</v>
+      </c>
+      <c r="P47" s="28" t="n"/>
+      <c r="Q47" s="28" t="n">
+        <v>-0.051675</v>
+      </c>
+      <c r="R47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T47" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U47" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V47" s="24" t="n"/>
+      <c r="W47" s="26" t="n"/>
+      <c r="X47" s="26" t="n"/>
+      <c r="Y47" s="25" t="n"/>
+      <c r="Z47" s="26" t="n"/>
+      <c r="AA47" s="28" t="n"/>
+      <c r="AB47" s="28" t="n"/>
+      <c r="AC47" s="30" t="n"/>
+      <c r="AD47" s="24" t="n"/>
+      <c r="AE47" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jpu-lk-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF47" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG47" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH47" s="24" t="n"/>
+      <c r="AI47" s="31" t="n"/>
+      <c r="AJ47" s="31" t="n"/>
+      <c r="AK47" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL47" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM47" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN47" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO47" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP47" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="AQ47" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="AR47" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="AS47" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AT47" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AU47" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AV47" s="24" t="n"/>
+      <c r="AW47" s="24" t="n"/>
+      <c r="AX47" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY47" s="24" t="n"/>
+      <c r="AZ47" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA47" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BB47" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC47" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD47" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BE47" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF47" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG47" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:35.281516Z</t>
+        </is>
+      </c>
+      <c r="BI47" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ47" s="25" t="n"/>
+      <c r="BK47" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="BL47" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BM47" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="BN47" s="28" t="n"/>
+      <c r="BO47" s="28" t="n"/>
+      <c r="BP47" s="25" t="n"/>
+      <c r="BQ47" s="27" t="n"/>
+      <c r="BR47" s="28" t="n"/>
+      <c r="BS47" s="28" t="n"/>
+      <c r="BT47" s="28" t="n"/>
+      <c r="BU47" s="25" t="n"/>
+      <c r="BV47" s="29" t="n"/>
+      <c r="BW47" s="24" t="n"/>
+      <c r="BX47" s="30" t="n"/>
+      <c r="BY47" s="27" t="n"/>
+      <c r="BZ47" s="24" t="n"/>
+      <c r="CA47" s="31" t="n"/>
+      <c r="CB47" s="24" t="n"/>
+      <c r="CC47" s="24" t="n"/>
+      <c r="CD47" s="24" t="n"/>
+      <c r="CE47" s="24" t="n"/>
+      <c r="CF47" s="24" t="n"/>
+      <c r="CG47" s="24" t="n"/>
+      <c r="CH47" s="24" t="n"/>
+      <c r="CI47" s="24" t="n"/>
+      <c r="CJ47" s="24" t="n"/>
+      <c r="CK47" s="24" t="n"/>
+      <c r="CL47" s="24" t="n"/>
+      <c r="CM47" s="24" t="n"/>
+      <c r="CN47" s="24" t="n"/>
+      <c r="CO47" s="24" t="n"/>
+      <c r="CP47" s="24" t="n"/>
+      <c r="CQ47" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>6cf1e03d30cd49da</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.505470Z</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>67578</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="G48" s="24" t="inlineStr">
+        <is>
+          <t>Recrent Club</t>
+        </is>
+      </c>
+      <c r="H48" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I48" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J48" s="25" t="n"/>
+      <c r="K48" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L48" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M48" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N48" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O48" s="28" t="n">
+        <v>0.526938</v>
+      </c>
+      <c r="P48" s="28" t="n"/>
+      <c r="Q48" s="28" t="n">
+        <v>-0.073062</v>
+      </c>
+      <c r="R48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U48" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V48" s="24" t="n"/>
+      <c r="W48" s="26" t="n"/>
+      <c r="X48" s="26" t="n"/>
+      <c r="Y48" s="25" t="n"/>
+      <c r="Z48" s="26" t="n"/>
+      <c r="AA48" s="28" t="n"/>
+      <c r="AB48" s="28" t="n"/>
+      <c r="AC48" s="30" t="n"/>
+      <c r="AD48" s="24" t="n"/>
+      <c r="AE48" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF48" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG48" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH48" s="24" t="n"/>
+      <c r="AI48" s="31" t="n"/>
+      <c r="AJ48" s="31" t="n"/>
+      <c r="AK48" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL48" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM48" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN48" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO48" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP48" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AQ48" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AR48" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AS48" s="24" t="inlineStr">
+        <is>
+          <t>Recrent Club</t>
+        </is>
+      </c>
+      <c r="AT48" s="24" t="inlineStr">
+        <is>
+          <t>Recrent Club</t>
+        </is>
+      </c>
+      <c r="AU48" s="24" t="inlineStr">
+        <is>
+          <t>Recrent Club</t>
+        </is>
+      </c>
+      <c r="AV48" s="24" t="n"/>
+      <c r="AW48" s="24" t="n"/>
+      <c r="AX48" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY48" s="24" t="n"/>
+      <c r="AZ48" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA48" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BB48" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC48" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD48" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BE48" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF48" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG48" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:35.963959Z</t>
+        </is>
+      </c>
+      <c r="BI48" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ48" s="25" t="n"/>
+      <c r="BK48" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL48" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM48" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN48" s="28" t="n"/>
+      <c r="BO48" s="28" t="n"/>
+      <c r="BP48" s="25" t="n"/>
+      <c r="BQ48" s="27" t="n"/>
+      <c r="BR48" s="28" t="n"/>
+      <c r="BS48" s="28" t="n"/>
+      <c r="BT48" s="28" t="n"/>
+      <c r="BU48" s="25" t="n"/>
+      <c r="BV48" s="29" t="n"/>
+      <c r="BW48" s="24" t="n"/>
+      <c r="BX48" s="30" t="n"/>
+      <c r="BY48" s="27" t="n"/>
+      <c r="BZ48" s="24" t="n"/>
+      <c r="CA48" s="31" t="n"/>
+      <c r="CB48" s="24" t="n"/>
+      <c r="CC48" s="24" t="n"/>
+      <c r="CD48" s="24" t="n"/>
+      <c r="CE48" s="24" t="n"/>
+      <c r="CF48" s="24" t="n"/>
+      <c r="CG48" s="24" t="n"/>
+      <c r="CH48" s="24" t="n"/>
+      <c r="CI48" s="24" t="n"/>
+      <c r="CJ48" s="24" t="n"/>
+      <c r="CK48" s="24" t="n"/>
+      <c r="CL48" s="24" t="n"/>
+      <c r="CM48" s="24" t="n"/>
+      <c r="CN48" s="24" t="n"/>
+      <c r="CO48" s="24" t="n"/>
+      <c r="CP48" s="24" t="n"/>
+      <c r="CQ48" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>620ff57fc7604013</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.505470Z</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>67579</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="H49" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I49" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J49" s="25" t="n"/>
+      <c r="K49" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L49" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="M49" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N49" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="O49" s="28" t="n">
+        <v>0.526281</v>
+      </c>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="28" t="n">
+        <v>0.186145</v>
+      </c>
+      <c r="R49" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S49" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U49" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V49" s="24" t="n"/>
+      <c r="W49" s="26" t="n"/>
+      <c r="X49" s="26" t="n"/>
+      <c r="Y49" s="25" t="n"/>
+      <c r="Z49" s="26" t="n"/>
+      <c r="AA49" s="28" t="n"/>
+      <c r="AB49" s="28" t="n"/>
+      <c r="AC49" s="30" t="n"/>
+      <c r="AD49" s="24" t="n"/>
+      <c r="AE49" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF49" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG49" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH49" s="24" t="n"/>
+      <c r="AI49" s="31" t="n"/>
+      <c r="AJ49" s="31" t="n"/>
+      <c r="AK49" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL49" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM49" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN49" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO49" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP49" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AQ49" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AR49" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AS49" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AT49" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AU49" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AV49" s="24" t="n"/>
+      <c r="AW49" s="24" t="n"/>
+      <c r="AX49" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY49" s="24" t="n"/>
+      <c r="AZ49" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA49" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BB49" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC49" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD49" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BE49" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF49" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG49" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:36.441729Z</t>
+        </is>
+      </c>
+      <c r="BI49" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ49" s="25" t="n"/>
+      <c r="BK49" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="BL49" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BM49" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="BN49" s="28" t="n"/>
+      <c r="BO49" s="28" t="n"/>
+      <c r="BP49" s="25" t="n"/>
+      <c r="BQ49" s="27" t="n"/>
+      <c r="BR49" s="28" t="n"/>
+      <c r="BS49" s="28" t="n"/>
+      <c r="BT49" s="28" t="n"/>
+      <c r="BU49" s="25" t="n"/>
+      <c r="BV49" s="29" t="n"/>
+      <c r="BW49" s="24" t="n"/>
+      <c r="BX49" s="30" t="n"/>
+      <c r="BY49" s="27" t="n"/>
+      <c r="BZ49" s="24" t="n"/>
+      <c r="CA49" s="31" t="n"/>
+      <c r="CB49" s="24" t="n"/>
+      <c r="CC49" s="24" t="n"/>
+      <c r="CD49" s="24" t="n"/>
+      <c r="CE49" s="24" t="n"/>
+      <c r="CF49" s="24" t="n"/>
+      <c r="CG49" s="24" t="n"/>
+      <c r="CH49" s="24" t="n"/>
+      <c r="CI49" s="24" t="n"/>
+      <c r="CJ49" s="24" t="n"/>
+      <c r="CK49" s="24" t="n"/>
+      <c r="CL49" s="24" t="n"/>
+      <c r="CM49" s="24" t="n"/>
+      <c r="CN49" s="24" t="n"/>
+      <c r="CO49" s="24" t="n"/>
+      <c r="CP49" s="24" t="n"/>
+      <c r="CQ49" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>705c32a5b0274406</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.505470Z</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="G50" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="H50" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I50" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J50" s="25" t="n"/>
+      <c r="K50" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L50" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M50" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N50" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O50" s="28" t="n">
+        <v>0.663041</v>
+      </c>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="28" t="n">
+        <v>0.022753</v>
+      </c>
+      <c r="R50" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S50" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T50" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U50" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V50" s="24" t="n"/>
+      <c r="W50" s="26" t="n"/>
+      <c r="X50" s="26" t="n"/>
+      <c r="Y50" s="25" t="n"/>
+      <c r="Z50" s="26" t="n"/>
+      <c r="AA50" s="28" t="n"/>
+      <c r="AB50" s="28" t="n"/>
+      <c r="AC50" s="30" t="n"/>
+      <c r="AD50" s="24" t="n"/>
+      <c r="AE50" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF50" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG50" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH50" s="24" t="n"/>
+      <c r="AI50" s="31" t="n"/>
+      <c r="AJ50" s="31" t="n"/>
+      <c r="AK50" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL50" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM50" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN50" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO50" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP50" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AQ50" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AR50" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AS50" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AT50" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AU50" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AV50" s="24" t="n"/>
+      <c r="AW50" s="24" t="n"/>
+      <c r="AX50" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY50" s="24" t="n"/>
+      <c r="AZ50" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA50" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BB50" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC50" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD50" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BE50" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF50" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG50" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:36.924167Z</t>
+        </is>
+      </c>
+      <c r="BI50" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ50" s="25" t="n"/>
+      <c r="BK50" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL50" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM50" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN50" s="28" t="n"/>
+      <c r="BO50" s="28" t="n"/>
+      <c r="BP50" s="25" t="n"/>
+      <c r="BQ50" s="27" t="n"/>
+      <c r="BR50" s="28" t="n"/>
+      <c r="BS50" s="28" t="n"/>
+      <c r="BT50" s="28" t="n"/>
+      <c r="BU50" s="25" t="n"/>
+      <c r="BV50" s="29" t="n"/>
+      <c r="BW50" s="24" t="n"/>
+      <c r="BX50" s="30" t="n"/>
+      <c r="BY50" s="27" t="n"/>
+      <c r="BZ50" s="24" t="n"/>
+      <c r="CA50" s="31" t="n"/>
+      <c r="CB50" s="24" t="n"/>
+      <c r="CC50" s="24" t="n"/>
+      <c r="CD50" s="24" t="n"/>
+      <c r="CE50" s="24" t="n"/>
+      <c r="CF50" s="24" t="n"/>
+      <c r="CG50" s="24" t="n"/>
+      <c r="CH50" s="24" t="n"/>
+      <c r="CI50" s="24" t="n"/>
+      <c r="CJ50" s="24" t="n"/>
+      <c r="CK50" s="24" t="n"/>
+      <c r="CL50" s="24" t="n"/>
+      <c r="CM50" s="24" t="n"/>
+      <c r="CN50" s="24" t="n"/>
+      <c r="CO50" s="24" t="n"/>
+      <c r="CP50" s="24" t="n"/>
+      <c r="CQ50" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>8c5db8edc9b74634</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.505470Z</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>68292</t>
+        </is>
+      </c>
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>ARCRED</t>
+        </is>
+      </c>
+      <c r="H51" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I51" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J51" s="25" t="n"/>
+      <c r="K51" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L51" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M51" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N51" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O51" s="28" t="n">
+        <v>0.613913</v>
+      </c>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="28" t="n">
+        <v>-0.026375</v>
+      </c>
+      <c r="R51" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="S51" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T51" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U51" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V51" s="24" t="n"/>
+      <c r="W51" s="26" t="n"/>
+      <c r="X51" s="26" t="n"/>
+      <c r="Y51" s="25" t="n"/>
+      <c r="Z51" s="26" t="n"/>
+      <c r="AA51" s="28" t="n"/>
+      <c r="AB51" s="28" t="n"/>
+      <c r="AC51" s="30" t="n"/>
+      <c r="AD51" s="24" t="n"/>
+      <c r="AE51" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-arc-btf-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF51" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG51" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH51" s="24" t="n"/>
+      <c r="AI51" s="31" t="n"/>
+      <c r="AJ51" s="31" t="n"/>
+      <c r="AK51" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL51" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM51" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN51" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO51" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP51" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AQ51" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AR51" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AS51" s="24" t="inlineStr">
+        <is>
+          <t>ARCRED</t>
+        </is>
+      </c>
+      <c r="AT51" s="24" t="inlineStr">
+        <is>
+          <t>ARCRED</t>
+        </is>
+      </c>
+      <c r="AU51" s="24" t="inlineStr">
+        <is>
+          <t>ARCRED</t>
+        </is>
+      </c>
+      <c r="AV51" s="24" t="n"/>
+      <c r="AW51" s="24" t="n"/>
+      <c r="AX51" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY51" s="24" t="n"/>
+      <c r="AZ51" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA51" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BB51" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC51" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD51" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BE51" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF51" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG51" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:37.460336Z</t>
+        </is>
+      </c>
+      <c r="BI51" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ51" s="25" t="n"/>
+      <c r="BK51" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL51" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM51" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN51" s="28" t="n"/>
+      <c r="BO51" s="28" t="n"/>
+      <c r="BP51" s="25" t="n"/>
+      <c r="BQ51" s="27" t="n"/>
+      <c r="BR51" s="28" t="n"/>
+      <c r="BS51" s="28" t="n"/>
+      <c r="BT51" s="28" t="n"/>
+      <c r="BU51" s="25" t="n"/>
+      <c r="BV51" s="29" t="n"/>
+      <c r="BW51" s="24" t="n"/>
+      <c r="BX51" s="30" t="n"/>
+      <c r="BY51" s="27" t="n"/>
+      <c r="BZ51" s="24" t="n"/>
+      <c r="CA51" s="31" t="n"/>
+      <c r="CB51" s="24" t="n"/>
+      <c r="CC51" s="24" t="n"/>
+      <c r="CD51" s="24" t="n"/>
+      <c r="CE51" s="24" t="n"/>
+      <c r="CF51" s="24" t="n"/>
+      <c r="CG51" s="24" t="n"/>
+      <c r="CH51" s="24" t="n"/>
+      <c r="CI51" s="24" t="n"/>
+      <c r="CJ51" s="24" t="n"/>
+      <c r="CK51" s="24" t="n"/>
+      <c r="CL51" s="24" t="n"/>
+      <c r="CM51" s="24" t="n"/>
+      <c r="CN51" s="24" t="n"/>
+      <c r="CO51" s="24" t="n"/>
+      <c r="CP51" s="24" t="n"/>
+      <c r="CQ51" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>a2a899947aa94a98</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.505470Z</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>68043</t>
+        </is>
+      </c>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="H52" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J52" s="25" t="n"/>
+      <c r="K52" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L52" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M52" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N52" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O52" s="28" t="n">
+        <v>0.569636</v>
+      </c>
+      <c r="P52" s="28" t="n"/>
+      <c r="Q52" s="28" t="n">
+        <v>0.119186</v>
+      </c>
+      <c r="R52" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="S52" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T52" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U52" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V52" s="24" t="n"/>
+      <c r="W52" s="26" t="n"/>
+      <c r="X52" s="26" t="n"/>
+      <c r="Y52" s="25" t="n"/>
+      <c r="Z52" s="26" t="n"/>
+      <c r="AA52" s="28" t="n"/>
+      <c r="AB52" s="28" t="n"/>
+      <c r="AC52" s="30" t="n"/>
+      <c r="AD52" s="24" t="n"/>
+      <c r="AE52" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF52" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG52" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH52" s="24" t="n"/>
+      <c r="AI52" s="31" t="n"/>
+      <c r="AJ52" s="31" t="n"/>
+      <c r="AK52" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL52" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM52" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN52" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO52" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP52" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AQ52" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AR52" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AS52" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AT52" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AU52" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AV52" s="24" t="n"/>
+      <c r="AW52" s="24" t="n"/>
+      <c r="AX52" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY52" s="24" t="n"/>
+      <c r="AZ52" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA52" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BB52" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC52" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD52" s="24" t="inlineStr">
+        <is>
+          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+        </is>
+      </c>
+      <c r="BE52" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF52" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG52" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T17:48:41.504632Z</t>
+        </is>
+      </c>
+      <c r="BI52" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ52" s="25" t="n"/>
+      <c r="BK52" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL52" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM52" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN52" s="28" t="n"/>
+      <c r="BO52" s="28" t="n"/>
+      <c r="BP52" s="25" t="n"/>
+      <c r="BQ52" s="27" t="n"/>
+      <c r="BR52" s="28" t="n"/>
+      <c r="BS52" s="28" t="n"/>
+      <c r="BT52" s="28" t="n"/>
+      <c r="BU52" s="25" t="n"/>
+      <c r="BV52" s="29" t="n"/>
+      <c r="BW52" s="24" t="n"/>
+      <c r="BX52" s="30" t="n"/>
+      <c r="BY52" s="27" t="n"/>
+      <c r="BZ52" s="24" t="n"/>
+      <c r="CA52" s="31" t="n"/>
+      <c r="CB52" s="24" t="n"/>
+      <c r="CC52" s="24" t="n"/>
+      <c r="CD52" s="24" t="n"/>
+      <c r="CE52" s="24" t="n"/>
+      <c r="CF52" s="24" t="n"/>
+      <c r="CG52" s="24" t="n"/>
+      <c r="CH52" s="24" t="n"/>
+      <c r="CI52" s="24" t="n"/>
+      <c r="CJ52" s="24" t="n"/>
+      <c r="CK52" s="24" t="n"/>
+      <c r="CL52" s="24" t="n"/>
+      <c r="CM52" s="24" t="n"/>
+      <c r="CN52" s="24" t="n"/>
+      <c r="CO52" s="24" t="n"/>
+      <c r="CP52" s="24" t="n"/>
+      <c r="CQ52" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -12619,22 +12619,22 @@
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>44e90abb54a64c7a</t>
+          <t>7bc84868b2844b96</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:41.505470Z</t>
+          <t>2026-08-02T18:08:55.998248Z</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:15:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>67576</t>
+          <t>67510</t>
         </is>
       </c>
       <c r="E41" s="24" t="inlineStr">
@@ -12644,12 +12644,12 @@
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="G41" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="H41" s="24" t="inlineStr">
@@ -12669,26 +12669,26 @@
         </is>
       </c>
       <c r="L41" s="26" t="n">
-        <v>127</v>
+        <v>-223</v>
       </c>
       <c r="M41" s="27" t="n">
-        <v>2.27</v>
+        <v>1.44843</v>
       </c>
       <c r="N41" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.690402</v>
       </c>
       <c r="O41" s="28" t="n">
-        <v>0.579552</v>
+        <v>0.563071</v>
       </c>
       <c r="P41" s="28" t="n"/>
       <c r="Q41" s="28" t="n">
-        <v>0.139023</v>
+        <v>-0.127331</v>
       </c>
       <c r="R41" s="26" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="S41" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T41" s="24" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
       <c r="AD41" s="24" t="n"/>
       <c r="AE41" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
         </is>
       </c>
       <c r="AF41" s="31" t="inlineStr">
@@ -12747,37 +12747,37 @@
       </c>
       <c r="AO41" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP41" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AQ41" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AR41" s="24" t="inlineStr">
         <is>
-          <t>mokrivskiy Club</t>
+          <t>Johnny Speeds</t>
         </is>
       </c>
       <c r="AS41" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AT41" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AU41" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>Metizport</t>
         </is>
       </c>
       <c r="AV41" s="24" t="n"/>
@@ -12795,7 +12795,7 @@
       </c>
       <c r="BA41" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BB41" s="24" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="BD41" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BE41" s="24" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="BH41" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:28.594679Z</t>
+          <t>2026-08-02T18:08:47.796652Z</t>
         </is>
       </c>
       <c r="BI41" s="24" t="inlineStr">
@@ -12840,13 +12840,13 @@
       </c>
       <c r="BJ41" s="25" t="n"/>
       <c r="BK41" s="26" t="n">
-        <v>127</v>
+        <v>-223</v>
       </c>
       <c r="BL41" s="27" t="n">
-        <v>2.27</v>
+        <v>1.44843</v>
       </c>
       <c r="BM41" s="28" t="n">
-        <v>0.440529</v>
+        <v>0.690402</v>
       </c>
       <c r="BN41" s="28" t="n"/>
       <c r="BO41" s="28" t="n"/>
@@ -12879,29 +12879,29 @@
       <c r="CP41" s="24" t="n"/>
       <c r="CQ41" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>320877f852464418</t>
+          <t>e4703a062e3b4d09</t>
         </is>
       </c>
       <c r="B42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:41.505470Z</t>
+          <t>2026-08-02T18:08:55.998248Z</t>
         </is>
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T19:15:00Z</t>
+          <t>2026-08-03T10:30:00Z</t>
         </is>
       </c>
       <c r="D42" s="24" t="inlineStr">
         <is>
-          <t>67577</t>
+          <t>67514</t>
         </is>
       </c>
       <c r="E42" s="24" t="inlineStr">
@@ -12911,12 +12911,12 @@
       </c>
       <c r="F42" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="G42" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="H42" s="24" t="inlineStr">
@@ -12936,26 +12936,26 @@
         </is>
       </c>
       <c r="L42" s="26" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="M42" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.613497</v>
       </c>
       <c r="N42" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.619772</v>
       </c>
       <c r="O42" s="28" t="n">
-        <v>0.526938</v>
+        <v>0.639896</v>
       </c>
       <c r="P42" s="28" t="n"/>
       <c r="Q42" s="28" t="n">
-        <v>-0.082437</v>
+        <v>0.020124</v>
       </c>
       <c r="R42" s="26" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S42" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T42" s="24" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
       <c r="AD42" s="24" t="n"/>
       <c r="AE42" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
         </is>
       </c>
       <c r="AF42" s="31" t="inlineStr">
@@ -12996,7 +12996,7 @@
       <c r="AJ42" s="31" t="n"/>
       <c r="AK42" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL42" s="26" t="n">
@@ -13004,47 +13004,47 @@
       </c>
       <c r="AM42" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN42" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO42" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP42" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AQ42" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AR42" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Passion Academy</t>
         </is>
       </c>
       <c r="AS42" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AT42" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AU42" s="24" t="inlineStr">
         <is>
-          <t>Lixxx Club</t>
+          <t>EAC Rising</t>
         </is>
       </c>
       <c r="AV42" s="24" t="n"/>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="BA42" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BB42" s="24" t="inlineStr">
@@ -13077,7 +13077,7 @@
       </c>
       <c r="BD42" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BE42" s="24" t="inlineStr">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="BH42" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:29.080231Z</t>
+          <t>2026-08-02T18:08:48.789246Z</t>
         </is>
       </c>
       <c r="BI42" s="24" t="inlineStr">
@@ -13107,13 +13107,13 @@
       </c>
       <c r="BJ42" s="25" t="n"/>
       <c r="BK42" s="26" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="BL42" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.613497</v>
       </c>
       <c r="BM42" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.619772</v>
       </c>
       <c r="BN42" s="28" t="n"/>
       <c r="BO42" s="28" t="n"/>
@@ -13146,29 +13146,29 @@
       <c r="CP42" s="24" t="n"/>
       <c r="CQ42" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>648e1b3a3f924bfa</t>
+          <t>c4824d14c7554f93</t>
         </is>
       </c>
       <c r="B43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:41.505470Z</t>
+          <t>2026-08-02T18:08:55.998248Z</t>
         </is>
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T08:00:00Z</t>
+          <t>2026-08-03T11:00:00Z</t>
         </is>
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>68288</t>
+          <t>69135</t>
         </is>
       </c>
       <c r="E43" s="24" t="inlineStr">
@@ -13178,12 +13178,12 @@
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="G43" s="24" t="inlineStr">
         <is>
-          <t>WW Team</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="H43" s="24" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="I43" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J43" s="25" t="n"/>
@@ -13203,26 +13203,26 @@
         </is>
       </c>
       <c r="L43" s="26" t="n">
-        <v>186</v>
+        <v>-163</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>2.86</v>
+        <v>1.613497</v>
       </c>
       <c r="N43" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.619772</v>
       </c>
       <c r="O43" s="28" t="n">
-        <v>0.704209</v>
+        <v>0.527201</v>
       </c>
       <c r="P43" s="28" t="n"/>
       <c r="Q43" s="28" t="n">
-        <v>0.354559</v>
+        <v>-0.092571</v>
       </c>
       <c r="R43" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S43" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T43" s="24" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
       <c r="AD43" s="24" t="n"/>
       <c r="AE43" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=aec-cs2-ww-cshp-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-1win-exruby-2026-08-03).</t>
         </is>
       </c>
       <c r="AF43" s="31" t="inlineStr">
@@ -13281,37 +13281,37 @@
       </c>
       <c r="AO43" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP43" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AQ43" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AR43" s="24" t="inlineStr">
         <is>
-          <t>CYBERSHOKE Prospects</t>
+          <t>ex-RUBY</t>
         </is>
       </c>
       <c r="AS43" s="24" t="inlineStr">
         <is>
-          <t>WW Team</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="AT43" s="24" t="inlineStr">
         <is>
-          <t>WW Team</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="AU43" s="24" t="inlineStr">
         <is>
-          <t>WW Team</t>
+          <t>1WIN</t>
         </is>
       </c>
       <c r="AV43" s="24" t="n"/>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="BA43" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BB43" s="24" t="inlineStr">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="BD43" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BE43" s="24" t="inlineStr">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="BH43" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:30.555681Z</t>
+          <t>2026-08-02T18:08:49.284497Z</t>
         </is>
       </c>
       <c r="BI43" s="24" t="inlineStr">
@@ -13374,13 +13374,13 @@
       </c>
       <c r="BJ43" s="25" t="n"/>
       <c r="BK43" s="26" t="n">
-        <v>186</v>
+        <v>-163</v>
       </c>
       <c r="BL43" s="27" t="n">
-        <v>2.86</v>
+        <v>1.613497</v>
       </c>
       <c r="BM43" s="28" t="n">
-        <v>0.34965</v>
+        <v>0.619772</v>
       </c>
       <c r="BN43" s="28" t="n"/>
       <c r="BO43" s="28" t="n"/>
@@ -13413,29 +13413,29 @@
       <c r="CP43" s="24" t="n"/>
       <c r="CQ43" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="24" t="inlineStr">
         <is>
-          <t>c613fbc4bd254f6f</t>
+          <t>4344727d5776490e</t>
         </is>
       </c>
       <c r="B44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:41.505470Z</t>
+          <t>2026-08-02T18:08:55.998248Z</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-03T11:00:00Z</t>
         </is>
       </c>
       <c r="D44" s="24" t="inlineStr">
         <is>
-          <t>68289</t>
+          <t>69267</t>
         </is>
       </c>
       <c r="E44" s="24" t="inlineStr">
@@ -13445,12 +13445,12 @@
       </c>
       <c r="F44" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="G44" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="H44" s="24" t="inlineStr">
@@ -13470,26 +13470,26 @@
         </is>
       </c>
       <c r="L44" s="26" t="n">
-        <v>-138</v>
+        <v>-213</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.469484</v>
       </c>
       <c r="N44" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.680511</v>
       </c>
       <c r="O44" s="28" t="n">
-        <v>0.599199</v>
+        <v>0.628836</v>
       </c>
       <c r="P44" s="28" t="n"/>
       <c r="Q44" s="28" t="n">
-        <v>0.019367</v>
+        <v>-0.051675</v>
       </c>
       <c r="R44" s="26" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="S44" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T44" s="24" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
       <c r="AD44" s="24" t="n"/>
       <c r="AE44" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jpu-lk-2026-08-03).</t>
         </is>
       </c>
       <c r="AF44" s="31" t="inlineStr">
@@ -13530,7 +13530,7 @@
       <c r="AJ44" s="31" t="n"/>
       <c r="AK44" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL44" s="26" t="n">
@@ -13538,47 +13538,47 @@
       </c>
       <c r="AM44" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN44" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO44" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP44" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AQ44" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AR44" s="24" t="inlineStr">
         <is>
-          <t>FURY</t>
+          <t>los kogutos</t>
         </is>
       </c>
       <c r="AS44" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AT44" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AU44" s="24" t="inlineStr">
         <is>
-          <t>Mindfreak</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AV44" s="24" t="n"/>
@@ -13596,7 +13596,7 @@
       </c>
       <c r="BA44" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BB44" s="24" t="inlineStr">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="BD44" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BE44" s="24" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="BH44" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:31.821007Z</t>
+          <t>2026-08-02T18:08:49.833473Z</t>
         </is>
       </c>
       <c r="BI44" s="24" t="inlineStr">
@@ -13641,13 +13641,13 @@
       </c>
       <c r="BJ44" s="25" t="n"/>
       <c r="BK44" s="26" t="n">
-        <v>-138</v>
+        <v>-213</v>
       </c>
       <c r="BL44" s="27" t="n">
-        <v>1.724638</v>
+        <v>1.469484</v>
       </c>
       <c r="BM44" s="28" t="n">
-        <v>0.579832</v>
+        <v>0.680511</v>
       </c>
       <c r="BN44" s="28" t="n"/>
       <c r="BO44" s="28" t="n"/>
@@ -13680,29 +13680,29 @@
       <c r="CP44" s="24" t="n"/>
       <c r="CQ44" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>d88562aa425c4b48</t>
+          <t>fba4b18b41c4497d</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:41.505470Z</t>
+          <t>2026-08-02T18:08:55.998248Z</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T10:00:00Z</t>
+          <t>2026-08-03T11:00:00Z</t>
         </is>
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>67510</t>
+          <t>67578</t>
         </is>
       </c>
       <c r="E45" s="24" t="inlineStr">
@@ -13712,12 +13712,12 @@
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="G45" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="H45" s="24" t="inlineStr">
@@ -13737,20 +13737,20 @@
         </is>
       </c>
       <c r="L45" s="26" t="n">
-        <v>-223</v>
+        <v>-150</v>
       </c>
       <c r="M45" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.666667</v>
       </c>
       <c r="N45" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.6</v>
       </c>
       <c r="O45" s="28" t="n">
-        <v>0.563071</v>
+        <v>0.526938</v>
       </c>
       <c r="P45" s="28" t="n"/>
       <c r="Q45" s="28" t="n">
-        <v>-0.127331</v>
+        <v>-0.073062</v>
       </c>
       <c r="R45" s="26" t="n">
         <v>0</v>
@@ -13779,7 +13779,7 @@
       <c r="AD45" s="24" t="n"/>
       <c r="AE45" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
         </is>
       </c>
       <c r="AF45" s="31" t="inlineStr">
@@ -13815,37 +13815,37 @@
       </c>
       <c r="AO45" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP45" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AQ45" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AR45" s="24" t="inlineStr">
         <is>
-          <t>Johnny Speeds</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AS45" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AT45" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AU45" s="24" t="inlineStr">
         <is>
-          <t>Metizport</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AV45" s="24" t="n"/>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="BA45" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BB45" s="24" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="BD45" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BE45" s="24" t="inlineStr">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="BH45" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:33.313201Z</t>
+          <t>2026-08-02T18:08:50.485383Z</t>
         </is>
       </c>
       <c r="BI45" s="24" t="inlineStr">
@@ -13908,13 +13908,13 @@
       </c>
       <c r="BJ45" s="25" t="n"/>
       <c r="BK45" s="26" t="n">
-        <v>-223</v>
+        <v>-150</v>
       </c>
       <c r="BL45" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.666667</v>
       </c>
       <c r="BM45" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.6</v>
       </c>
       <c r="BN45" s="28" t="n"/>
       <c r="BO45" s="28" t="n"/>
@@ -13954,22 +13954,22 @@
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>9a50bb7a0c2d4b8a</t>
+          <t>206b74e1b5164c74</t>
         </is>
       </c>
       <c r="B46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:41.505470Z</t>
+          <t>2026-08-02T18:08:55.998248Z</t>
         </is>
       </c>
       <c r="C46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T11:00:00Z</t>
+          <t>2026-08-03T13:45:00Z</t>
         </is>
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>69135</t>
+          <t>67579</t>
         </is>
       </c>
       <c r="E46" s="24" t="inlineStr">
@@ -13979,12 +13979,12 @@
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
-          <t>ex-RUBY</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="G46" s="24" t="inlineStr">
         <is>
-          <t>1WIN</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="H46" s="24" t="inlineStr">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="I46" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J46" s="25" t="n"/>
@@ -14004,23 +14004,23 @@
         </is>
       </c>
       <c r="L46" s="26" t="n">
-        <v>-163</v>
+        <v>194</v>
       </c>
       <c r="M46" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.94</v>
       </c>
       <c r="N46" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.340136</v>
       </c>
       <c r="O46" s="28" t="n">
-        <v>0.527201</v>
+        <v>0.526281</v>
       </c>
       <c r="P46" s="28" t="n"/>
       <c r="Q46" s="28" t="n">
-        <v>-0.092571</v>
+        <v>0.186145</v>
       </c>
       <c r="R46" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S46" s="29" t="n">
         <v>1</v>
@@ -14046,7 +14046,7 @@
       <c r="AD46" s="24" t="n"/>
       <c r="AE46" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-1win-exruby-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
         </is>
       </c>
       <c r="AF46" s="31" t="inlineStr">
@@ -14082,37 +14082,37 @@
       </c>
       <c r="AO46" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP46" s="24" t="inlineStr">
         <is>
-          <t>ex-RUBY</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AQ46" s="24" t="inlineStr">
         <is>
-          <t>ex-RUBY</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AR46" s="24" t="inlineStr">
         <is>
-          <t>ex-RUBY</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AS46" s="24" t="inlineStr">
         <is>
-          <t>1WIN</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AT46" s="24" t="inlineStr">
         <is>
-          <t>1WIN</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AU46" s="24" t="inlineStr">
         <is>
-          <t>1WIN</t>
+          <t>Perfecto Club</t>
         </is>
       </c>
       <c r="AV46" s="24" t="n"/>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="BA46" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BB46" s="24" t="inlineStr">
@@ -14145,7 +14145,7 @@
       </c>
       <c r="BD46" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BE46" s="24" t="inlineStr">
@@ -14165,7 +14165,7 @@
       </c>
       <c r="BH46" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:34.765803Z</t>
+          <t>2026-08-02T18:08:50.962336Z</t>
         </is>
       </c>
       <c r="BI46" s="24" t="inlineStr">
@@ -14175,13 +14175,13 @@
       </c>
       <c r="BJ46" s="25" t="n"/>
       <c r="BK46" s="26" t="n">
-        <v>-163</v>
+        <v>194</v>
       </c>
       <c r="BL46" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.94</v>
       </c>
       <c r="BM46" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.340136</v>
       </c>
       <c r="BN46" s="28" t="n"/>
       <c r="BO46" s="28" t="n"/>
@@ -14214,29 +14214,29 @@
       <c r="CP46" s="24" t="n"/>
       <c r="CQ46" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>1ec174b7c2bb4a59</t>
+          <t>48449ab02faf40fc</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:41.505470Z</t>
+          <t>2026-08-02T18:08:55.998248Z</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T11:00:00Z</t>
+          <t>2026-08-03T14:00:00Z</t>
         </is>
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>69267</t>
+          <t>69268</t>
         </is>
       </c>
       <c r="E47" s="24" t="inlineStr">
@@ -14246,12 +14246,12 @@
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr">
@@ -14271,26 +14271,26 @@
         </is>
       </c>
       <c r="L47" s="26" t="n">
-        <v>-213</v>
+        <v>-178</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.561798</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.640288</v>
       </c>
       <c r="O47" s="28" t="n">
-        <v>0.628836</v>
+        <v>0.663041</v>
       </c>
       <c r="P47" s="28" t="n"/>
       <c r="Q47" s="28" t="n">
-        <v>-0.051675</v>
+        <v>0.022753</v>
       </c>
       <c r="R47" s="26" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="S47" s="29" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="T47" s="24" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
       <c r="AD47" s="24" t="n"/>
       <c r="AE47" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jpu-lk-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
         </is>
       </c>
       <c r="AF47" s="31" t="inlineStr">
@@ -14331,7 +14331,7 @@
       <c r="AJ47" s="31" t="n"/>
       <c r="AK47" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL47" s="26" t="n">
@@ -14339,47 +14339,47 @@
       </c>
       <c r="AM47" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN47" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO47" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP47" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AQ47" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AR47" s="24" t="inlineStr">
         <is>
-          <t>los kogutos</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AS47" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AT47" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AU47" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="AV47" s="24" t="n"/>
@@ -14397,7 +14397,7 @@
       </c>
       <c r="BA47" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BB47" s="24" t="inlineStr">
@@ -14412,7 +14412,7 @@
       </c>
       <c r="BD47" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BE47" s="24" t="inlineStr">
@@ -14432,7 +14432,7 @@
       </c>
       <c r="BH47" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:35.281516Z</t>
+          <t>2026-08-02T18:08:51.418739Z</t>
         </is>
       </c>
       <c r="BI47" s="24" t="inlineStr">
@@ -14442,13 +14442,13 @@
       </c>
       <c r="BJ47" s="25" t="n"/>
       <c r="BK47" s="26" t="n">
-        <v>-213</v>
+        <v>-178</v>
       </c>
       <c r="BL47" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.561798</v>
       </c>
       <c r="BM47" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.640288</v>
       </c>
       <c r="BN47" s="28" t="n"/>
       <c r="BO47" s="28" t="n"/>
@@ -14481,29 +14481,29 @@
       <c r="CP47" s="24" t="n"/>
       <c r="CQ47" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>6cf1e03d30cd49da</t>
+          <t>656a7ea1bc1f4276</t>
         </is>
       </c>
       <c r="B48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:41.505470Z</t>
+          <t>2026-08-02T18:08:55.998248Z</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T11:00:00Z</t>
+          <t>2026-08-03T14:00:00Z</t>
         </is>
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>67578</t>
+          <t>68292</t>
         </is>
       </c>
       <c r="E48" s="24" t="inlineStr">
@@ -14513,12 +14513,12 @@
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="G48" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>ARCRED</t>
         </is>
       </c>
       <c r="H48" s="24" t="inlineStr">
@@ -14538,26 +14538,26 @@
         </is>
       </c>
       <c r="L48" s="26" t="n">
-        <v>-150</v>
+        <v>-178</v>
       </c>
       <c r="M48" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.561798</v>
       </c>
       <c r="N48" s="28" t="n">
-        <v>0.6</v>
+        <v>0.640288</v>
       </c>
       <c r="O48" s="28" t="n">
-        <v>0.526938</v>
+        <v>0.613913</v>
       </c>
       <c r="P48" s="28" t="n"/>
       <c r="Q48" s="28" t="n">
-        <v>-0.073062</v>
+        <v>-0.026375</v>
       </c>
       <c r="R48" s="26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S48" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T48" s="24" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
       <c r="AD48" s="24" t="n"/>
       <c r="AE48" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-arc-btf-2026-08-03).</t>
         </is>
       </c>
       <c r="AF48" s="31" t="inlineStr">
@@ -14616,37 +14616,37 @@
       </c>
       <c r="AO48" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP48" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AQ48" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AR48" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="AS48" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>ARCRED</t>
         </is>
       </c>
       <c r="AT48" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>ARCRED</t>
         </is>
       </c>
       <c r="AU48" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>ARCRED</t>
         </is>
       </c>
       <c r="AV48" s="24" t="n"/>
@@ -14664,7 +14664,7 @@
       </c>
       <c r="BA48" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BB48" s="24" t="inlineStr">
@@ -14679,7 +14679,7 @@
       </c>
       <c r="BD48" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BE48" s="24" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="BH48" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:35.963959Z</t>
+          <t>2026-08-02T18:08:51.886373Z</t>
         </is>
       </c>
       <c r="BI48" s="24" t="inlineStr">
@@ -14709,13 +14709,13 @@
       </c>
       <c r="BJ48" s="25" t="n"/>
       <c r="BK48" s="26" t="n">
-        <v>-150</v>
+        <v>-178</v>
       </c>
       <c r="BL48" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.561798</v>
       </c>
       <c r="BM48" s="28" t="n">
-        <v>0.6</v>
+        <v>0.640288</v>
       </c>
       <c r="BN48" s="28" t="n"/>
       <c r="BO48" s="28" t="n"/>
@@ -14755,22 +14755,22 @@
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>620ff57fc7604013</t>
+          <t>f3976bb61d524a6f</t>
         </is>
       </c>
       <c r="B49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:41.505470Z</t>
+          <t>2026-08-02T18:08:55.998248Z</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T13:45:00Z</t>
+          <t>2026-08-03T23:00:00Z</t>
         </is>
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>67579</t>
+          <t>68043</t>
         </is>
       </c>
       <c r="E49" s="24" t="inlineStr">
@@ -14780,12 +14780,12 @@
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="G49" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="H49" s="24" t="inlineStr">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="I49" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J49" s="25" t="n"/>
@@ -14805,26 +14805,26 @@
         </is>
       </c>
       <c r="L49" s="26" t="n">
-        <v>194</v>
+        <v>122</v>
       </c>
       <c r="M49" s="27" t="n">
-        <v>2.94</v>
+        <v>2.22</v>
       </c>
       <c r="N49" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.45045</v>
       </c>
       <c r="O49" s="28" t="n">
-        <v>0.526281</v>
+        <v>0.569636</v>
       </c>
       <c r="P49" s="28" t="n"/>
       <c r="Q49" s="28" t="n">
-        <v>0.186145</v>
+        <v>0.119186</v>
       </c>
       <c r="R49" s="26" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="S49" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T49" s="24" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
       <c r="AD49" s="24" t="n"/>
       <c r="AE49" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
         </is>
       </c>
       <c r="AF49" s="31" t="inlineStr">
@@ -14888,32 +14888,32 @@
       </c>
       <c r="AP49" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="AQ49" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="AR49" s="24" t="inlineStr">
         <is>
-          <t>Morphilina Club</t>
+          <t>paiN Academy</t>
         </is>
       </c>
       <c r="AS49" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="AT49" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="AU49" s="24" t="inlineStr">
         <is>
-          <t>Perfecto Club</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="AV49" s="24" t="n"/>
@@ -14931,7 +14931,7 @@
       </c>
       <c r="BA49" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BB49" s="24" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="BD49" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
         </is>
       </c>
       <c r="BE49" s="24" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="BH49" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:36.441729Z</t>
+          <t>2026-08-02T18:08:55.995920Z</t>
         </is>
       </c>
       <c r="BI49" s="24" t="inlineStr">
@@ -14976,13 +14976,13 @@
       </c>
       <c r="BJ49" s="25" t="n"/>
       <c r="BK49" s="26" t="n">
-        <v>194</v>
+        <v>122</v>
       </c>
       <c r="BL49" s="27" t="n">
-        <v>2.94</v>
+        <v>2.22</v>
       </c>
       <c r="BM49" s="28" t="n">
-        <v>0.340136</v>
+        <v>0.45045</v>
       </c>
       <c r="BN49" s="28" t="n"/>
       <c r="BO49" s="28" t="n"/>
@@ -15022,22 +15022,22 @@
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="24" t="inlineStr">
         <is>
-          <t>705c32a5b0274406</t>
+          <t>e8dfdc43c69f4199</t>
         </is>
       </c>
       <c r="B50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:41.505470Z</t>
+          <t>2026-08-02T18:12:49.767554Z</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T14:00:00Z</t>
+          <t>2026-08-02T19:15:00Z</t>
         </is>
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>69268</t>
+          <t>67576</t>
         </is>
       </c>
       <c r="E50" s="24" t="inlineStr">
@@ -15047,12 +15047,12 @@
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="G50" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="H50" s="24" t="inlineStr">
@@ -15072,26 +15072,26 @@
         </is>
       </c>
       <c r="L50" s="26" t="n">
-        <v>-178</v>
+        <v>127</v>
       </c>
       <c r="M50" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.27</v>
       </c>
       <c r="N50" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.440529</v>
       </c>
       <c r="O50" s="28" t="n">
-        <v>0.663041</v>
+        <v>0.57961</v>
       </c>
       <c r="P50" s="28" t="n"/>
       <c r="Q50" s="28" t="n">
-        <v>0.022753</v>
+        <v>0.139081</v>
       </c>
       <c r="R50" s="26" t="n">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="S50" s="29" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="T50" s="24" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
       <c r="AD50" s="24" t="n"/>
       <c r="AE50" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
         </is>
       </c>
       <c r="AF50" s="31" t="inlineStr">
@@ -15132,7 +15132,7 @@
       <c r="AJ50" s="31" t="n"/>
       <c r="AK50" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL50" s="26" t="n">
@@ -15140,47 +15140,47 @@
       </c>
       <c r="AM50" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN50" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO50" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP50" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AQ50" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AR50" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>mokrivskiy Club</t>
         </is>
       </c>
       <c r="AS50" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AT50" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AU50" s="24" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>Morphilina Club</t>
         </is>
       </c>
       <c r="AV50" s="24" t="n"/>
@@ -15198,7 +15198,7 @@
       </c>
       <c r="BA50" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>97de5c5903ba33e53441b5088cf4e6c4cee4d2e8611df656dcf52f1b3af7f6f4</t>
         </is>
       </c>
       <c r="BB50" s="24" t="inlineStr">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="BD50" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>97de5c5903ba33e53441b5088cf4e6c4cee4d2e8611df656dcf52f1b3af7f6f4</t>
         </is>
       </c>
       <c r="BE50" s="24" t="inlineStr">
@@ -15233,7 +15233,7 @@
       </c>
       <c r="BH50" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:36.924167Z</t>
+          <t>2026-08-02T18:12:36.926594Z</t>
         </is>
       </c>
       <c r="BI50" s="24" t="inlineStr">
@@ -15243,13 +15243,13 @@
       </c>
       <c r="BJ50" s="25" t="n"/>
       <c r="BK50" s="26" t="n">
-        <v>-178</v>
+        <v>127</v>
       </c>
       <c r="BL50" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.27</v>
       </c>
       <c r="BM50" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.440529</v>
       </c>
       <c r="BN50" s="28" t="n"/>
       <c r="BO50" s="28" t="n"/>
@@ -15289,22 +15289,22 @@
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>8c5db8edc9b74634</t>
+          <t>fa6ef683221e4945</t>
         </is>
       </c>
       <c r="B51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:41.505470Z</t>
+          <t>2026-08-02T18:12:49.767554Z</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T14:00:00Z</t>
+          <t>2026-08-02T19:15:00Z</t>
         </is>
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>68292</t>
+          <t>67577</t>
         </is>
       </c>
       <c r="E51" s="24" t="inlineStr">
@@ -15314,12 +15314,12 @@
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="G51" s="24" t="inlineStr">
         <is>
-          <t>ARCRED</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="H51" s="24" t="inlineStr">
@@ -15339,26 +15339,26 @@
         </is>
       </c>
       <c r="L51" s="26" t="n">
-        <v>-178</v>
+        <v>-156</v>
       </c>
       <c r="M51" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.641026</v>
       </c>
       <c r="N51" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.609375</v>
       </c>
       <c r="O51" s="28" t="n">
-        <v>0.613913</v>
+        <v>0.52695</v>
       </c>
       <c r="P51" s="28" t="n"/>
       <c r="Q51" s="28" t="n">
-        <v>-0.026375</v>
+        <v>-0.082425</v>
       </c>
       <c r="R51" s="26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S51" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T51" s="24" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
       <c r="AD51" s="24" t="n"/>
       <c r="AE51" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-arc-btf-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
         </is>
       </c>
       <c r="AF51" s="31" t="inlineStr">
@@ -15417,37 +15417,37 @@
       </c>
       <c r="AO51" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP51" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AQ51" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AR51" s="24" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AS51" s="24" t="inlineStr">
         <is>
-          <t>ARCRED</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AT51" s="24" t="inlineStr">
         <is>
-          <t>ARCRED</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AU51" s="24" t="inlineStr">
         <is>
-          <t>ARCRED</t>
+          <t>Lixxx Club</t>
         </is>
       </c>
       <c r="AV51" s="24" t="n"/>
@@ -15465,7 +15465,7 @@
       </c>
       <c r="BA51" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>97de5c5903ba33e53441b5088cf4e6c4cee4d2e8611df656dcf52f1b3af7f6f4</t>
         </is>
       </c>
       <c r="BB51" s="24" t="inlineStr">
@@ -15480,7 +15480,7 @@
       </c>
       <c r="BD51" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>97de5c5903ba33e53441b5088cf4e6c4cee4d2e8611df656dcf52f1b3af7f6f4</t>
         </is>
       </c>
       <c r="BE51" s="24" t="inlineStr">
@@ -15500,7 +15500,7 @@
       </c>
       <c r="BH51" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:37.460336Z</t>
+          <t>2026-08-02T18:12:37.417895Z</t>
         </is>
       </c>
       <c r="BI51" s="24" t="inlineStr">
@@ -15510,13 +15510,13 @@
       </c>
       <c r="BJ51" s="25" t="n"/>
       <c r="BK51" s="26" t="n">
-        <v>-178</v>
+        <v>-156</v>
       </c>
       <c r="BL51" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.641026</v>
       </c>
       <c r="BM51" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.609375</v>
       </c>
       <c r="BN51" s="28" t="n"/>
       <c r="BO51" s="28" t="n"/>
@@ -15556,22 +15556,22 @@
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>a2a899947aa94a98</t>
+          <t>d6a8b2da702249d0</t>
         </is>
       </c>
       <c r="B52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:41.505470Z</t>
+          <t>2026-08-02T18:12:49.767554Z</t>
         </is>
       </c>
       <c r="C52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-03T23:00:00Z</t>
+          <t>2026-08-03T10:00:00Z</t>
         </is>
       </c>
       <c r="D52" s="24" t="inlineStr">
         <is>
-          <t>68043</t>
+          <t>68289</t>
         </is>
       </c>
       <c r="E52" s="24" t="inlineStr">
@@ -15581,12 +15581,12 @@
       </c>
       <c r="F52" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="G52" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="H52" s="24" t="inlineStr">
@@ -15606,23 +15606,23 @@
         </is>
       </c>
       <c r="L52" s="26" t="n">
-        <v>122</v>
+        <v>-138</v>
       </c>
       <c r="M52" s="27" t="n">
-        <v>2.22</v>
+        <v>1.724638</v>
       </c>
       <c r="N52" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.579832</v>
       </c>
       <c r="O52" s="28" t="n">
-        <v>0.569636</v>
+        <v>0.599274</v>
       </c>
       <c r="P52" s="28" t="n"/>
       <c r="Q52" s="28" t="n">
-        <v>0.119186</v>
+        <v>0.019442</v>
       </c>
       <c r="R52" s="26" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="S52" s="29" t="n">
         <v>1.25</v>
@@ -15648,7 +15648,7 @@
       <c r="AD52" s="24" t="n"/>
       <c r="AE52" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
         </is>
       </c>
       <c r="AF52" s="31" t="inlineStr">
@@ -15666,7 +15666,7 @@
       <c r="AJ52" s="31" t="n"/>
       <c r="AK52" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL52" s="26" t="n">
@@ -15674,47 +15674,47 @@
       </c>
       <c r="AM52" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN52" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO52" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP52" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="AQ52" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="AR52" s="24" t="inlineStr">
         <is>
-          <t>paiN Academy</t>
+          <t>FURY</t>
         </is>
       </c>
       <c r="AS52" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="AT52" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="AU52" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>Mindfreak</t>
         </is>
       </c>
       <c r="AV52" s="24" t="n"/>
@@ -15732,7 +15732,7 @@
       </c>
       <c r="BA52" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>97de5c5903ba33e53441b5088cf4e6c4cee4d2e8611df656dcf52f1b3af7f6f4</t>
         </is>
       </c>
       <c r="BB52" s="24" t="inlineStr">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="BD52" s="24" t="inlineStr">
         <is>
-          <t>a4e21a1af368f0354dc5f9a4308bc7027cac0942d4270c2251f9210a7793ef91</t>
+          <t>97de5c5903ba33e53441b5088cf4e6c4cee4d2e8611df656dcf52f1b3af7f6f4</t>
         </is>
       </c>
       <c r="BE52" s="24" t="inlineStr">
@@ -15767,7 +15767,7 @@
       </c>
       <c r="BH52" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T17:48:41.504632Z</t>
+          <t>2026-08-02T18:12:39.986059Z</t>
         </is>
       </c>
       <c r="BI52" s="24" t="inlineStr">
@@ -15777,13 +15777,13 @@
       </c>
       <c r="BJ52" s="25" t="n"/>
       <c r="BK52" s="26" t="n">
-        <v>122</v>
+        <v>-138</v>
       </c>
       <c r="BL52" s="27" t="n">
-        <v>2.22</v>
+        <v>1.724638</v>
       </c>
       <c r="BM52" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.579832</v>
       </c>
       <c r="BN52" s="28" t="n"/>
       <c r="BO52" s="28" t="n"/>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ52" headerRowCount="1">
-  <autoFilter ref="A1:CQ52"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ40" headerRowCount="1">
+  <autoFilter ref="A1:CQ40"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$52)</f>
+        <f>COUNTA('Picks'!$A$2:$A$40)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$52,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$40,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$52,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$40,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")+COUNTIFS('Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"win")+COUNTIFS('Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$52,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$40,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$40,"&gt;0",'Picks'!$V$2:$V$40,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$40,"&gt;0",'Picks'!$V$2:$V$40,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")/(COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")+COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$40,"&gt;0",'Picks'!$V$2:$V$40,"win")/(COUNTIFS('Picks'!$BX$2:$BX$40,"&gt;0",'Picks'!$V$2:$V$40,"win")+COUNTIFS('Picks'!$BX$2:$BX$40,"&gt;0",'Picks'!$V$2:$V$40,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$52)/SUM('Picks'!$BX$2:$BX$52),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$40)/SUM('Picks'!$BX$2:$BX$40),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$52)</f>
+        <f>SUM('Picks'!$BY$2:$BY$40)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$52,"&lt;&gt;",'Picks'!$AB$2:$AB$52),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$40,"&lt;&gt;",'Picks'!$AB$2:$AB$40),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$52,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$52,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$40,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$40,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$52,'Picks'!$AM$2:$AM$52,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$40,'Picks'!$AM$2:$AM$40,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A14,'Picks'!$U$2:$U$40,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A14,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A14,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$40,'Picks'!$H$2:$H$40,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$40,'Picks'!$H$2:$H$40,$A14,'Picks'!$U$2:$U$40,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A15,'Picks'!$U$2:$U$40,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A15,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A15,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$40,'Picks'!$H$2:$H$40,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$40,'Picks'!$H$2:$H$40,$A15,'Picks'!$U$2:$U$40,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A16,'Picks'!$U$2:$U$40,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A16,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$40,$A16,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$40,'Picks'!$H$2:$H$40,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$40,'Picks'!$H$2:$H$40,$A16,'Picks'!$U$2:$U$40,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ52"/>
+  <dimension ref="A1:CQ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12616,3210 +12616,6 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="24" t="inlineStr">
-        <is>
-          <t>7bc84868b2844b96</t>
-        </is>
-      </c>
-      <c r="B41" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:55.998248Z</t>
-        </is>
-      </c>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:00:00Z</t>
-        </is>
-      </c>
-      <c r="D41" s="24" t="inlineStr">
-        <is>
-          <t>67510</t>
-        </is>
-      </c>
-      <c r="E41" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F41" s="24" t="inlineStr">
-        <is>
-          <t>Johnny Speeds</t>
-        </is>
-      </c>
-      <c r="G41" s="24" t="inlineStr">
-        <is>
-          <t>Metizport</t>
-        </is>
-      </c>
-      <c r="H41" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I41" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J41" s="25" t="n"/>
-      <c r="K41" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L41" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="M41" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="N41" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="O41" s="28" t="n">
-        <v>0.563071</v>
-      </c>
-      <c r="P41" s="28" t="n"/>
-      <c r="Q41" s="28" t="n">
-        <v>-0.127331</v>
-      </c>
-      <c r="R41" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T41" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U41" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V41" s="24" t="n"/>
-      <c r="W41" s="26" t="n"/>
-      <c r="X41" s="26" t="n"/>
-      <c r="Y41" s="25" t="n"/>
-      <c r="Z41" s="26" t="n"/>
-      <c r="AA41" s="28" t="n"/>
-      <c r="AB41" s="28" t="n"/>
-      <c r="AC41" s="30" t="n"/>
-      <c r="AD41" s="24" t="n"/>
-      <c r="AE41" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF41" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG41" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH41" s="24" t="n"/>
-      <c r="AI41" s="31" t="n"/>
-      <c r="AJ41" s="31" t="n"/>
-      <c r="AK41" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL41" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM41" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN41" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO41" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP41" s="24" t="inlineStr">
-        <is>
-          <t>Johnny Speeds</t>
-        </is>
-      </c>
-      <c r="AQ41" s="24" t="inlineStr">
-        <is>
-          <t>Johnny Speeds</t>
-        </is>
-      </c>
-      <c r="AR41" s="24" t="inlineStr">
-        <is>
-          <t>Johnny Speeds</t>
-        </is>
-      </c>
-      <c r="AS41" s="24" t="inlineStr">
-        <is>
-          <t>Metizport</t>
-        </is>
-      </c>
-      <c r="AT41" s="24" t="inlineStr">
-        <is>
-          <t>Metizport</t>
-        </is>
-      </c>
-      <c r="AU41" s="24" t="inlineStr">
-        <is>
-          <t>Metizport</t>
-        </is>
-      </c>
-      <c r="AV41" s="24" t="n"/>
-      <c r="AW41" s="24" t="n"/>
-      <c r="AX41" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY41" s="24" t="n"/>
-      <c r="AZ41" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA41" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BB41" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC41" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD41" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BE41" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF41" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG41" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH41" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:47.796652Z</t>
-        </is>
-      </c>
-      <c r="BI41" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ41" s="25" t="n"/>
-      <c r="BK41" s="26" t="n">
-        <v>-223</v>
-      </c>
-      <c r="BL41" s="27" t="n">
-        <v>1.44843</v>
-      </c>
-      <c r="BM41" s="28" t="n">
-        <v>0.690402</v>
-      </c>
-      <c r="BN41" s="28" t="n"/>
-      <c r="BO41" s="28" t="n"/>
-      <c r="BP41" s="25" t="n"/>
-      <c r="BQ41" s="27" t="n"/>
-      <c r="BR41" s="28" t="n"/>
-      <c r="BS41" s="28" t="n"/>
-      <c r="BT41" s="28" t="n"/>
-      <c r="BU41" s="25" t="n"/>
-      <c r="BV41" s="29" t="n"/>
-      <c r="BW41" s="24" t="n"/>
-      <c r="BX41" s="30" t="n"/>
-      <c r="BY41" s="27" t="n"/>
-      <c r="BZ41" s="24" t="n"/>
-      <c r="CA41" s="31" t="n"/>
-      <c r="CB41" s="24" t="n"/>
-      <c r="CC41" s="24" t="n"/>
-      <c r="CD41" s="24" t="n"/>
-      <c r="CE41" s="24" t="n"/>
-      <c r="CF41" s="24" t="n"/>
-      <c r="CG41" s="24" t="n"/>
-      <c r="CH41" s="24" t="n"/>
-      <c r="CI41" s="24" t="n"/>
-      <c r="CJ41" s="24" t="n"/>
-      <c r="CK41" s="24" t="n"/>
-      <c r="CL41" s="24" t="n"/>
-      <c r="CM41" s="24" t="n"/>
-      <c r="CN41" s="24" t="n"/>
-      <c r="CO41" s="24" t="n"/>
-      <c r="CP41" s="24" t="n"/>
-      <c r="CQ41" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="24" t="inlineStr">
-        <is>
-          <t>e4703a062e3b4d09</t>
-        </is>
-      </c>
-      <c r="B42" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:55.998248Z</t>
-        </is>
-      </c>
-      <c r="C42" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:30:00Z</t>
-        </is>
-      </c>
-      <c r="D42" s="24" t="inlineStr">
-        <is>
-          <t>67514</t>
-        </is>
-      </c>
-      <c r="E42" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F42" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="G42" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="H42" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I42" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J42" s="25" t="n"/>
-      <c r="K42" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L42" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="M42" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="N42" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="O42" s="28" t="n">
-        <v>0.639896</v>
-      </c>
-      <c r="P42" s="28" t="n"/>
-      <c r="Q42" s="28" t="n">
-        <v>0.020124</v>
-      </c>
-      <c r="R42" s="26" t="n">
-        <v>30</v>
-      </c>
-      <c r="S42" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T42" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U42" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V42" s="24" t="n"/>
-      <c r="W42" s="26" t="n"/>
-      <c r="X42" s="26" t="n"/>
-      <c r="Y42" s="25" t="n"/>
-      <c r="Z42" s="26" t="n"/>
-      <c r="AA42" s="28" t="n"/>
-      <c r="AB42" s="28" t="n"/>
-      <c r="AC42" s="30" t="n"/>
-      <c r="AD42" s="24" t="n"/>
-      <c r="AE42" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF42" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG42" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH42" s="24" t="n"/>
-      <c r="AI42" s="31" t="n"/>
-      <c r="AJ42" s="31" t="n"/>
-      <c r="AK42" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL42" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM42" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN42" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO42" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP42" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AQ42" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AR42" s="24" t="inlineStr">
-        <is>
-          <t>Passion Academy</t>
-        </is>
-      </c>
-      <c r="AS42" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="AT42" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="AU42" s="24" t="inlineStr">
-        <is>
-          <t>EAC Rising</t>
-        </is>
-      </c>
-      <c r="AV42" s="24" t="n"/>
-      <c r="AW42" s="24" t="n"/>
-      <c r="AX42" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY42" s="24" t="n"/>
-      <c r="AZ42" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA42" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BB42" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC42" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD42" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BE42" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF42" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG42" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH42" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:48.789246Z</t>
-        </is>
-      </c>
-      <c r="BI42" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ42" s="25" t="n"/>
-      <c r="BK42" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="BL42" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="BM42" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="BN42" s="28" t="n"/>
-      <c r="BO42" s="28" t="n"/>
-      <c r="BP42" s="25" t="n"/>
-      <c r="BQ42" s="27" t="n"/>
-      <c r="BR42" s="28" t="n"/>
-      <c r="BS42" s="28" t="n"/>
-      <c r="BT42" s="28" t="n"/>
-      <c r="BU42" s="25" t="n"/>
-      <c r="BV42" s="29" t="n"/>
-      <c r="BW42" s="24" t="n"/>
-      <c r="BX42" s="30" t="n"/>
-      <c r="BY42" s="27" t="n"/>
-      <c r="BZ42" s="24" t="n"/>
-      <c r="CA42" s="31" t="n"/>
-      <c r="CB42" s="24" t="n"/>
-      <c r="CC42" s="24" t="n"/>
-      <c r="CD42" s="24" t="n"/>
-      <c r="CE42" s="24" t="n"/>
-      <c r="CF42" s="24" t="n"/>
-      <c r="CG42" s="24" t="n"/>
-      <c r="CH42" s="24" t="n"/>
-      <c r="CI42" s="24" t="n"/>
-      <c r="CJ42" s="24" t="n"/>
-      <c r="CK42" s="24" t="n"/>
-      <c r="CL42" s="24" t="n"/>
-      <c r="CM42" s="24" t="n"/>
-      <c r="CN42" s="24" t="n"/>
-      <c r="CO42" s="24" t="n"/>
-      <c r="CP42" s="24" t="n"/>
-      <c r="CQ42" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="24" t="inlineStr">
-        <is>
-          <t>c4824d14c7554f93</t>
-        </is>
-      </c>
-      <c r="B43" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:55.998248Z</t>
-        </is>
-      </c>
-      <c r="C43" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="D43" s="24" t="inlineStr">
-        <is>
-          <t>69135</t>
-        </is>
-      </c>
-      <c r="E43" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F43" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUBY</t>
-        </is>
-      </c>
-      <c r="G43" s="24" t="inlineStr">
-        <is>
-          <t>1WIN</t>
-        </is>
-      </c>
-      <c r="H43" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I43" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J43" s="25" t="n"/>
-      <c r="K43" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L43" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="M43" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="N43" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="O43" s="28" t="n">
-        <v>0.527201</v>
-      </c>
-      <c r="P43" s="28" t="n"/>
-      <c r="Q43" s="28" t="n">
-        <v>-0.092571</v>
-      </c>
-      <c r="R43" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T43" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U43" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V43" s="24" t="n"/>
-      <c r="W43" s="26" t="n"/>
-      <c r="X43" s="26" t="n"/>
-      <c r="Y43" s="25" t="n"/>
-      <c r="Z43" s="26" t="n"/>
-      <c r="AA43" s="28" t="n"/>
-      <c r="AB43" s="28" t="n"/>
-      <c r="AC43" s="30" t="n"/>
-      <c r="AD43" s="24" t="n"/>
-      <c r="AE43" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-1win-exruby-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF43" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG43" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH43" s="24" t="n"/>
-      <c r="AI43" s="31" t="n"/>
-      <c r="AJ43" s="31" t="n"/>
-      <c r="AK43" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL43" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM43" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN43" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO43" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP43" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUBY</t>
-        </is>
-      </c>
-      <c r="AQ43" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUBY</t>
-        </is>
-      </c>
-      <c r="AR43" s="24" t="inlineStr">
-        <is>
-          <t>ex-RUBY</t>
-        </is>
-      </c>
-      <c r="AS43" s="24" t="inlineStr">
-        <is>
-          <t>1WIN</t>
-        </is>
-      </c>
-      <c r="AT43" s="24" t="inlineStr">
-        <is>
-          <t>1WIN</t>
-        </is>
-      </c>
-      <c r="AU43" s="24" t="inlineStr">
-        <is>
-          <t>1WIN</t>
-        </is>
-      </c>
-      <c r="AV43" s="24" t="n"/>
-      <c r="AW43" s="24" t="n"/>
-      <c r="AX43" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY43" s="24" t="n"/>
-      <c r="AZ43" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA43" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BB43" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC43" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD43" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BE43" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF43" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG43" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH43" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:49.284497Z</t>
-        </is>
-      </c>
-      <c r="BI43" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ43" s="25" t="n"/>
-      <c r="BK43" s="26" t="n">
-        <v>-163</v>
-      </c>
-      <c r="BL43" s="27" t="n">
-        <v>1.613497</v>
-      </c>
-      <c r="BM43" s="28" t="n">
-        <v>0.619772</v>
-      </c>
-      <c r="BN43" s="28" t="n"/>
-      <c r="BO43" s="28" t="n"/>
-      <c r="BP43" s="25" t="n"/>
-      <c r="BQ43" s="27" t="n"/>
-      <c r="BR43" s="28" t="n"/>
-      <c r="BS43" s="28" t="n"/>
-      <c r="BT43" s="28" t="n"/>
-      <c r="BU43" s="25" t="n"/>
-      <c r="BV43" s="29" t="n"/>
-      <c r="BW43" s="24" t="n"/>
-      <c r="BX43" s="30" t="n"/>
-      <c r="BY43" s="27" t="n"/>
-      <c r="BZ43" s="24" t="n"/>
-      <c r="CA43" s="31" t="n"/>
-      <c r="CB43" s="24" t="n"/>
-      <c r="CC43" s="24" t="n"/>
-      <c r="CD43" s="24" t="n"/>
-      <c r="CE43" s="24" t="n"/>
-      <c r="CF43" s="24" t="n"/>
-      <c r="CG43" s="24" t="n"/>
-      <c r="CH43" s="24" t="n"/>
-      <c r="CI43" s="24" t="n"/>
-      <c r="CJ43" s="24" t="n"/>
-      <c r="CK43" s="24" t="n"/>
-      <c r="CL43" s="24" t="n"/>
-      <c r="CM43" s="24" t="n"/>
-      <c r="CN43" s="24" t="n"/>
-      <c r="CO43" s="24" t="n"/>
-      <c r="CP43" s="24" t="n"/>
-      <c r="CQ43" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="24" t="inlineStr">
-        <is>
-          <t>4344727d5776490e</t>
-        </is>
-      </c>
-      <c r="B44" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:55.998248Z</t>
-        </is>
-      </c>
-      <c r="C44" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="D44" s="24" t="inlineStr">
-        <is>
-          <t>69267</t>
-        </is>
-      </c>
-      <c r="E44" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F44" s="24" t="inlineStr">
-        <is>
-          <t>los kogutos</t>
-        </is>
-      </c>
-      <c r="G44" s="24" t="inlineStr">
-        <is>
-          <t>Just Players</t>
-        </is>
-      </c>
-      <c r="H44" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I44" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J44" s="25" t="n"/>
-      <c r="K44" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L44" s="26" t="n">
-        <v>-213</v>
-      </c>
-      <c r="M44" s="27" t="n">
-        <v>1.469484</v>
-      </c>
-      <c r="N44" s="28" t="n">
-        <v>0.680511</v>
-      </c>
-      <c r="O44" s="28" t="n">
-        <v>0.628836</v>
-      </c>
-      <c r="P44" s="28" t="n"/>
-      <c r="Q44" s="28" t="n">
-        <v>-0.051675</v>
-      </c>
-      <c r="R44" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T44" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U44" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V44" s="24" t="n"/>
-      <c r="W44" s="26" t="n"/>
-      <c r="X44" s="26" t="n"/>
-      <c r="Y44" s="25" t="n"/>
-      <c r="Z44" s="26" t="n"/>
-      <c r="AA44" s="28" t="n"/>
-      <c r="AB44" s="28" t="n"/>
-      <c r="AC44" s="30" t="n"/>
-      <c r="AD44" s="24" t="n"/>
-      <c r="AE44" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jpu-lk-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF44" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG44" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH44" s="24" t="n"/>
-      <c r="AI44" s="31" t="n"/>
-      <c r="AJ44" s="31" t="n"/>
-      <c r="AK44" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL44" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM44" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN44" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO44" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP44" s="24" t="inlineStr">
-        <is>
-          <t>los kogutos</t>
-        </is>
-      </c>
-      <c r="AQ44" s="24" t="inlineStr">
-        <is>
-          <t>los kogutos</t>
-        </is>
-      </c>
-      <c r="AR44" s="24" t="inlineStr">
-        <is>
-          <t>los kogutos</t>
-        </is>
-      </c>
-      <c r="AS44" s="24" t="inlineStr">
-        <is>
-          <t>Just Players</t>
-        </is>
-      </c>
-      <c r="AT44" s="24" t="inlineStr">
-        <is>
-          <t>Just Players</t>
-        </is>
-      </c>
-      <c r="AU44" s="24" t="inlineStr">
-        <is>
-          <t>Just Players</t>
-        </is>
-      </c>
-      <c r="AV44" s="24" t="n"/>
-      <c r="AW44" s="24" t="n"/>
-      <c r="AX44" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY44" s="24" t="n"/>
-      <c r="AZ44" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA44" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BB44" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC44" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD44" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BE44" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF44" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG44" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH44" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:49.833473Z</t>
-        </is>
-      </c>
-      <c r="BI44" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ44" s="25" t="n"/>
-      <c r="BK44" s="26" t="n">
-        <v>-213</v>
-      </c>
-      <c r="BL44" s="27" t="n">
-        <v>1.469484</v>
-      </c>
-      <c r="BM44" s="28" t="n">
-        <v>0.680511</v>
-      </c>
-      <c r="BN44" s="28" t="n"/>
-      <c r="BO44" s="28" t="n"/>
-      <c r="BP44" s="25" t="n"/>
-      <c r="BQ44" s="27" t="n"/>
-      <c r="BR44" s="28" t="n"/>
-      <c r="BS44" s="28" t="n"/>
-      <c r="BT44" s="28" t="n"/>
-      <c r="BU44" s="25" t="n"/>
-      <c r="BV44" s="29" t="n"/>
-      <c r="BW44" s="24" t="n"/>
-      <c r="BX44" s="30" t="n"/>
-      <c r="BY44" s="27" t="n"/>
-      <c r="BZ44" s="24" t="n"/>
-      <c r="CA44" s="31" t="n"/>
-      <c r="CB44" s="24" t="n"/>
-      <c r="CC44" s="24" t="n"/>
-      <c r="CD44" s="24" t="n"/>
-      <c r="CE44" s="24" t="n"/>
-      <c r="CF44" s="24" t="n"/>
-      <c r="CG44" s="24" t="n"/>
-      <c r="CH44" s="24" t="n"/>
-      <c r="CI44" s="24" t="n"/>
-      <c r="CJ44" s="24" t="n"/>
-      <c r="CK44" s="24" t="n"/>
-      <c r="CL44" s="24" t="n"/>
-      <c r="CM44" s="24" t="n"/>
-      <c r="CN44" s="24" t="n"/>
-      <c r="CO44" s="24" t="n"/>
-      <c r="CP44" s="24" t="n"/>
-      <c r="CQ44" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="36" customHeight="1">
-      <c r="A45" s="24" t="inlineStr">
-        <is>
-          <t>fba4b18b41c4497d</t>
-        </is>
-      </c>
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:55.998248Z</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T11:00:00Z</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="inlineStr">
-        <is>
-          <t>67578</t>
-        </is>
-      </c>
-      <c r="E45" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F45" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="G45" s="24" t="inlineStr">
-        <is>
-          <t>Recrent Club</t>
-        </is>
-      </c>
-      <c r="H45" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I45" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J45" s="25" t="n"/>
-      <c r="K45" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L45" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="M45" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="N45" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O45" s="28" t="n">
-        <v>0.526938</v>
-      </c>
-      <c r="P45" s="28" t="n"/>
-      <c r="Q45" s="28" t="n">
-        <v>-0.073062</v>
-      </c>
-      <c r="R45" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T45" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U45" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V45" s="24" t="n"/>
-      <c r="W45" s="26" t="n"/>
-      <c r="X45" s="26" t="n"/>
-      <c r="Y45" s="25" t="n"/>
-      <c r="Z45" s="26" t="n"/>
-      <c r="AA45" s="28" t="n"/>
-      <c r="AB45" s="28" t="n"/>
-      <c r="AC45" s="30" t="n"/>
-      <c r="AD45" s="24" t="n"/>
-      <c r="AE45" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF45" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG45" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH45" s="24" t="n"/>
-      <c r="AI45" s="31" t="n"/>
-      <c r="AJ45" s="31" t="n"/>
-      <c r="AK45" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL45" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM45" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN45" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO45" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP45" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AQ45" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AR45" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AS45" s="24" t="inlineStr">
-        <is>
-          <t>Recrent Club</t>
-        </is>
-      </c>
-      <c r="AT45" s="24" t="inlineStr">
-        <is>
-          <t>Recrent Club</t>
-        </is>
-      </c>
-      <c r="AU45" s="24" t="inlineStr">
-        <is>
-          <t>Recrent Club</t>
-        </is>
-      </c>
-      <c r="AV45" s="24" t="n"/>
-      <c r="AW45" s="24" t="n"/>
-      <c r="AX45" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY45" s="24" t="n"/>
-      <c r="AZ45" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA45" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BB45" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC45" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD45" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BE45" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF45" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG45" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH45" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:50.485383Z</t>
-        </is>
-      </c>
-      <c r="BI45" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ45" s="25" t="n"/>
-      <c r="BK45" s="26" t="n">
-        <v>-150</v>
-      </c>
-      <c r="BL45" s="27" t="n">
-        <v>1.666667</v>
-      </c>
-      <c r="BM45" s="28" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BN45" s="28" t="n"/>
-      <c r="BO45" s="28" t="n"/>
-      <c r="BP45" s="25" t="n"/>
-      <c r="BQ45" s="27" t="n"/>
-      <c r="BR45" s="28" t="n"/>
-      <c r="BS45" s="28" t="n"/>
-      <c r="BT45" s="28" t="n"/>
-      <c r="BU45" s="25" t="n"/>
-      <c r="BV45" s="29" t="n"/>
-      <c r="BW45" s="24" t="n"/>
-      <c r="BX45" s="30" t="n"/>
-      <c r="BY45" s="27" t="n"/>
-      <c r="BZ45" s="24" t="n"/>
-      <c r="CA45" s="31" t="n"/>
-      <c r="CB45" s="24" t="n"/>
-      <c r="CC45" s="24" t="n"/>
-      <c r="CD45" s="24" t="n"/>
-      <c r="CE45" s="24" t="n"/>
-      <c r="CF45" s="24" t="n"/>
-      <c r="CG45" s="24" t="n"/>
-      <c r="CH45" s="24" t="n"/>
-      <c r="CI45" s="24" t="n"/>
-      <c r="CJ45" s="24" t="n"/>
-      <c r="CK45" s="24" t="n"/>
-      <c r="CL45" s="24" t="n"/>
-      <c r="CM45" s="24" t="n"/>
-      <c r="CN45" s="24" t="n"/>
-      <c r="CO45" s="24" t="n"/>
-      <c r="CP45" s="24" t="n"/>
-      <c r="CQ45" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="36" customHeight="1">
-      <c r="A46" s="24" t="inlineStr">
-        <is>
-          <t>206b74e1b5164c74</t>
-        </is>
-      </c>
-      <c r="B46" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:55.998248Z</t>
-        </is>
-      </c>
-      <c r="C46" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T13:45:00Z</t>
-        </is>
-      </c>
-      <c r="D46" s="24" t="inlineStr">
-        <is>
-          <t>67579</t>
-        </is>
-      </c>
-      <c r="E46" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F46" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="G46" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="H46" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I46" s="24" t="inlineStr">
-        <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J46" s="25" t="n"/>
-      <c r="K46" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L46" s="26" t="n">
-        <v>194</v>
-      </c>
-      <c r="M46" s="27" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="N46" s="28" t="n">
-        <v>0.340136</v>
-      </c>
-      <c r="O46" s="28" t="n">
-        <v>0.526281</v>
-      </c>
-      <c r="P46" s="28" t="n"/>
-      <c r="Q46" s="28" t="n">
-        <v>0.186145</v>
-      </c>
-      <c r="R46" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S46" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T46" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U46" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V46" s="24" t="n"/>
-      <c r="W46" s="26" t="n"/>
-      <c r="X46" s="26" t="n"/>
-      <c r="Y46" s="25" t="n"/>
-      <c r="Z46" s="26" t="n"/>
-      <c r="AA46" s="28" t="n"/>
-      <c r="AB46" s="28" t="n"/>
-      <c r="AC46" s="30" t="n"/>
-      <c r="AD46" s="24" t="n"/>
-      <c r="AE46" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF46" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG46" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH46" s="24" t="n"/>
-      <c r="AI46" s="31" t="n"/>
-      <c r="AJ46" s="31" t="n"/>
-      <c r="AK46" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL46" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM46" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN46" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO46" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP46" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="AQ46" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="AR46" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="AS46" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AT46" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AU46" s="24" t="inlineStr">
-        <is>
-          <t>Perfecto Club</t>
-        </is>
-      </c>
-      <c r="AV46" s="24" t="n"/>
-      <c r="AW46" s="24" t="n"/>
-      <c r="AX46" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY46" s="24" t="n"/>
-      <c r="AZ46" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA46" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BB46" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC46" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD46" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BE46" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF46" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG46" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH46" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:50.962336Z</t>
-        </is>
-      </c>
-      <c r="BI46" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ46" s="25" t="n"/>
-      <c r="BK46" s="26" t="n">
-        <v>194</v>
-      </c>
-      <c r="BL46" s="27" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BM46" s="28" t="n">
-        <v>0.340136</v>
-      </c>
-      <c r="BN46" s="28" t="n"/>
-      <c r="BO46" s="28" t="n"/>
-      <c r="BP46" s="25" t="n"/>
-      <c r="BQ46" s="27" t="n"/>
-      <c r="BR46" s="28" t="n"/>
-      <c r="BS46" s="28" t="n"/>
-      <c r="BT46" s="28" t="n"/>
-      <c r="BU46" s="25" t="n"/>
-      <c r="BV46" s="29" t="n"/>
-      <c r="BW46" s="24" t="n"/>
-      <c r="BX46" s="30" t="n"/>
-      <c r="BY46" s="27" t="n"/>
-      <c r="BZ46" s="24" t="n"/>
-      <c r="CA46" s="31" t="n"/>
-      <c r="CB46" s="24" t="n"/>
-      <c r="CC46" s="24" t="n"/>
-      <c r="CD46" s="24" t="n"/>
-      <c r="CE46" s="24" t="n"/>
-      <c r="CF46" s="24" t="n"/>
-      <c r="CG46" s="24" t="n"/>
-      <c r="CH46" s="24" t="n"/>
-      <c r="CI46" s="24" t="n"/>
-      <c r="CJ46" s="24" t="n"/>
-      <c r="CK46" s="24" t="n"/>
-      <c r="CL46" s="24" t="n"/>
-      <c r="CM46" s="24" t="n"/>
-      <c r="CN46" s="24" t="n"/>
-      <c r="CO46" s="24" t="n"/>
-      <c r="CP46" s="24" t="n"/>
-      <c r="CQ46" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="36" customHeight="1">
-      <c r="A47" s="24" t="inlineStr">
-        <is>
-          <t>48449ab02faf40fc</t>
-        </is>
-      </c>
-      <c r="B47" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:55.998248Z</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="inlineStr">
-        <is>
-          <t>69268</t>
-        </is>
-      </c>
-      <c r="E47" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F47" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="G47" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="H47" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I47" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J47" s="25" t="n"/>
-      <c r="K47" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L47" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M47" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N47" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O47" s="28" t="n">
-        <v>0.663041</v>
-      </c>
-      <c r="P47" s="28" t="n"/>
-      <c r="Q47" s="28" t="n">
-        <v>0.022753</v>
-      </c>
-      <c r="R47" s="26" t="n">
-        <v>31</v>
-      </c>
-      <c r="S47" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T47" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U47" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V47" s="24" t="n"/>
-      <c r="W47" s="26" t="n"/>
-      <c r="X47" s="26" t="n"/>
-      <c r="Y47" s="25" t="n"/>
-      <c r="Z47" s="26" t="n"/>
-      <c r="AA47" s="28" t="n"/>
-      <c r="AB47" s="28" t="n"/>
-      <c r="AC47" s="30" t="n"/>
-      <c r="AD47" s="24" t="n"/>
-      <c r="AE47" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF47" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG47" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH47" s="24" t="n"/>
-      <c r="AI47" s="31" t="n"/>
-      <c r="AJ47" s="31" t="n"/>
-      <c r="AK47" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL47" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM47" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN47" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO47" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP47" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AQ47" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AR47" s="24" t="inlineStr">
-        <is>
-          <t>ex-Young Ninjas</t>
-        </is>
-      </c>
-      <c r="AS47" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AT47" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AU47" s="24" t="inlineStr">
-        <is>
-          <t>SPARTA</t>
-        </is>
-      </c>
-      <c r="AV47" s="24" t="n"/>
-      <c r="AW47" s="24" t="n"/>
-      <c r="AX47" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY47" s="24" t="n"/>
-      <c r="AZ47" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA47" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BB47" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC47" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD47" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BE47" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF47" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG47" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH47" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:51.418739Z</t>
-        </is>
-      </c>
-      <c r="BI47" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ47" s="25" t="n"/>
-      <c r="BK47" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL47" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM47" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN47" s="28" t="n"/>
-      <c r="BO47" s="28" t="n"/>
-      <c r="BP47" s="25" t="n"/>
-      <c r="BQ47" s="27" t="n"/>
-      <c r="BR47" s="28" t="n"/>
-      <c r="BS47" s="28" t="n"/>
-      <c r="BT47" s="28" t="n"/>
-      <c r="BU47" s="25" t="n"/>
-      <c r="BV47" s="29" t="n"/>
-      <c r="BW47" s="24" t="n"/>
-      <c r="BX47" s="30" t="n"/>
-      <c r="BY47" s="27" t="n"/>
-      <c r="BZ47" s="24" t="n"/>
-      <c r="CA47" s="31" t="n"/>
-      <c r="CB47" s="24" t="n"/>
-      <c r="CC47" s="24" t="n"/>
-      <c r="CD47" s="24" t="n"/>
-      <c r="CE47" s="24" t="n"/>
-      <c r="CF47" s="24" t="n"/>
-      <c r="CG47" s="24" t="n"/>
-      <c r="CH47" s="24" t="n"/>
-      <c r="CI47" s="24" t="n"/>
-      <c r="CJ47" s="24" t="n"/>
-      <c r="CK47" s="24" t="n"/>
-      <c r="CL47" s="24" t="n"/>
-      <c r="CM47" s="24" t="n"/>
-      <c r="CN47" s="24" t="n"/>
-      <c r="CO47" s="24" t="n"/>
-      <c r="CP47" s="24" t="n"/>
-      <c r="CQ47" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="36" customHeight="1">
-      <c r="A48" s="24" t="inlineStr">
-        <is>
-          <t>656a7ea1bc1f4276</t>
-        </is>
-      </c>
-      <c r="B48" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:55.998248Z</t>
-        </is>
-      </c>
-      <c r="C48" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T14:00:00Z</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="inlineStr">
-        <is>
-          <t>68292</t>
-        </is>
-      </c>
-      <c r="E48" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F48" s="24" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="G48" s="24" t="inlineStr">
-        <is>
-          <t>ARCRED</t>
-        </is>
-      </c>
-      <c r="H48" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I48" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J48" s="25" t="n"/>
-      <c r="K48" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L48" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="M48" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="N48" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="O48" s="28" t="n">
-        <v>0.613913</v>
-      </c>
-      <c r="P48" s="28" t="n"/>
-      <c r="Q48" s="28" t="n">
-        <v>-0.026375</v>
-      </c>
-      <c r="R48" s="26" t="n">
-        <v>7</v>
-      </c>
-      <c r="S48" s="29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T48" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U48" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V48" s="24" t="n"/>
-      <c r="W48" s="26" t="n"/>
-      <c r="X48" s="26" t="n"/>
-      <c r="Y48" s="25" t="n"/>
-      <c r="Z48" s="26" t="n"/>
-      <c r="AA48" s="28" t="n"/>
-      <c r="AB48" s="28" t="n"/>
-      <c r="AC48" s="30" t="n"/>
-      <c r="AD48" s="24" t="n"/>
-      <c r="AE48" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-arc-btf-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF48" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG48" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH48" s="24" t="n"/>
-      <c r="AI48" s="31" t="n"/>
-      <c r="AJ48" s="31" t="n"/>
-      <c r="AK48" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL48" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM48" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN48" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO48" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_LOW_EDGE</t>
-        </is>
-      </c>
-      <c r="AP48" s="24" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="AQ48" s="24" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="AR48" s="24" t="inlineStr">
-        <is>
-          <t>Butterfly</t>
-        </is>
-      </c>
-      <c r="AS48" s="24" t="inlineStr">
-        <is>
-          <t>ARCRED</t>
-        </is>
-      </c>
-      <c r="AT48" s="24" t="inlineStr">
-        <is>
-          <t>ARCRED</t>
-        </is>
-      </c>
-      <c r="AU48" s="24" t="inlineStr">
-        <is>
-          <t>ARCRED</t>
-        </is>
-      </c>
-      <c r="AV48" s="24" t="n"/>
-      <c r="AW48" s="24" t="n"/>
-      <c r="AX48" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY48" s="24" t="n"/>
-      <c r="AZ48" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA48" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BB48" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC48" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD48" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BE48" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF48" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG48" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH48" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:51.886373Z</t>
-        </is>
-      </c>
-      <c r="BI48" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ48" s="25" t="n"/>
-      <c r="BK48" s="26" t="n">
-        <v>-178</v>
-      </c>
-      <c r="BL48" s="27" t="n">
-        <v>1.561798</v>
-      </c>
-      <c r="BM48" s="28" t="n">
-        <v>0.640288</v>
-      </c>
-      <c r="BN48" s="28" t="n"/>
-      <c r="BO48" s="28" t="n"/>
-      <c r="BP48" s="25" t="n"/>
-      <c r="BQ48" s="27" t="n"/>
-      <c r="BR48" s="28" t="n"/>
-      <c r="BS48" s="28" t="n"/>
-      <c r="BT48" s="28" t="n"/>
-      <c r="BU48" s="25" t="n"/>
-      <c r="BV48" s="29" t="n"/>
-      <c r="BW48" s="24" t="n"/>
-      <c r="BX48" s="30" t="n"/>
-      <c r="BY48" s="27" t="n"/>
-      <c r="BZ48" s="24" t="n"/>
-      <c r="CA48" s="31" t="n"/>
-      <c r="CB48" s="24" t="n"/>
-      <c r="CC48" s="24" t="n"/>
-      <c r="CD48" s="24" t="n"/>
-      <c r="CE48" s="24" t="n"/>
-      <c r="CF48" s="24" t="n"/>
-      <c r="CG48" s="24" t="n"/>
-      <c r="CH48" s="24" t="n"/>
-      <c r="CI48" s="24" t="n"/>
-      <c r="CJ48" s="24" t="n"/>
-      <c r="CK48" s="24" t="n"/>
-      <c r="CL48" s="24" t="n"/>
-      <c r="CM48" s="24" t="n"/>
-      <c r="CN48" s="24" t="n"/>
-      <c r="CO48" s="24" t="n"/>
-      <c r="CP48" s="24" t="n"/>
-      <c r="CQ48" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="A49" s="24" t="inlineStr">
-        <is>
-          <t>f3976bb61d524a6f</t>
-        </is>
-      </c>
-      <c r="B49" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:55.998248Z</t>
-        </is>
-      </c>
-      <c r="C49" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T23:00:00Z</t>
-        </is>
-      </c>
-      <c r="D49" s="24" t="inlineStr">
-        <is>
-          <t>68043</t>
-        </is>
-      </c>
-      <c r="E49" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F49" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="G49" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="H49" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I49" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J49" s="25" t="n"/>
-      <c r="K49" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L49" s="26" t="n">
-        <v>122</v>
-      </c>
-      <c r="M49" s="27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="N49" s="28" t="n">
-        <v>0.45045</v>
-      </c>
-      <c r="O49" s="28" t="n">
-        <v>0.569636</v>
-      </c>
-      <c r="P49" s="28" t="n"/>
-      <c r="Q49" s="28" t="n">
-        <v>0.119186</v>
-      </c>
-      <c r="R49" s="26" t="n">
-        <v>80</v>
-      </c>
-      <c r="S49" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T49" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U49" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V49" s="24" t="n"/>
-      <c r="W49" s="26" t="n"/>
-      <c r="X49" s="26" t="n"/>
-      <c r="Y49" s="25" t="n"/>
-      <c r="Z49" s="26" t="n"/>
-      <c r="AA49" s="28" t="n"/>
-      <c r="AB49" s="28" t="n"/>
-      <c r="AC49" s="30" t="n"/>
-      <c r="AD49" s="24" t="n"/>
-      <c r="AE49" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF49" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG49" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH49" s="24" t="n"/>
-      <c r="AI49" s="31" t="n"/>
-      <c r="AJ49" s="31" t="n"/>
-      <c r="AK49" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL49" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM49" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN49" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO49" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP49" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AQ49" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AR49" s="24" t="inlineStr">
-        <is>
-          <t>paiN Academy</t>
-        </is>
-      </c>
-      <c r="AS49" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="AT49" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="AU49" s="24" t="inlineStr">
-        <is>
-          <t>Grêmio Esports</t>
-        </is>
-      </c>
-      <c r="AV49" s="24" t="n"/>
-      <c r="AW49" s="24" t="n"/>
-      <c r="AX49" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY49" s="24" t="n"/>
-      <c r="AZ49" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA49" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BB49" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC49" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD49" s="24" t="inlineStr">
-        <is>
-          <t>d5fa90971ced522e0070399e9eeaba0b323d1e6ef1030b6470d86e8cb482d801</t>
-        </is>
-      </c>
-      <c r="BE49" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF49" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG49" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH49" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:08:55.995920Z</t>
-        </is>
-      </c>
-      <c r="BI49" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ49" s="25" t="n"/>
-      <c r="BK49" s="26" t="n">
-        <v>122</v>
-      </c>
-      <c r="BL49" s="27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BM49" s="28" t="n">
-        <v>0.45045</v>
-      </c>
-      <c r="BN49" s="28" t="n"/>
-      <c r="BO49" s="28" t="n"/>
-      <c r="BP49" s="25" t="n"/>
-      <c r="BQ49" s="27" t="n"/>
-      <c r="BR49" s="28" t="n"/>
-      <c r="BS49" s="28" t="n"/>
-      <c r="BT49" s="28" t="n"/>
-      <c r="BU49" s="25" t="n"/>
-      <c r="BV49" s="29" t="n"/>
-      <c r="BW49" s="24" t="n"/>
-      <c r="BX49" s="30" t="n"/>
-      <c r="BY49" s="27" t="n"/>
-      <c r="BZ49" s="24" t="n"/>
-      <c r="CA49" s="31" t="n"/>
-      <c r="CB49" s="24" t="n"/>
-      <c r="CC49" s="24" t="n"/>
-      <c r="CD49" s="24" t="n"/>
-      <c r="CE49" s="24" t="n"/>
-      <c r="CF49" s="24" t="n"/>
-      <c r="CG49" s="24" t="n"/>
-      <c r="CH49" s="24" t="n"/>
-      <c r="CI49" s="24" t="n"/>
-      <c r="CJ49" s="24" t="n"/>
-      <c r="CK49" s="24" t="n"/>
-      <c r="CL49" s="24" t="n"/>
-      <c r="CM49" s="24" t="n"/>
-      <c r="CN49" s="24" t="n"/>
-      <c r="CO49" s="24" t="n"/>
-      <c r="CP49" s="24" t="n"/>
-      <c r="CQ49" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="A50" s="24" t="inlineStr">
-        <is>
-          <t>e8dfdc43c69f4199</t>
-        </is>
-      </c>
-      <c r="B50" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:49.767554Z</t>
-        </is>
-      </c>
-      <c r="C50" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T19:15:00Z</t>
-        </is>
-      </c>
-      <c r="D50" s="24" t="inlineStr">
-        <is>
-          <t>67576</t>
-        </is>
-      </c>
-      <c r="E50" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F50" s="24" t="inlineStr">
-        <is>
-          <t>mokrivskiy Club</t>
-        </is>
-      </c>
-      <c r="G50" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="H50" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I50" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J50" s="25" t="n"/>
-      <c r="K50" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L50" s="26" t="n">
-        <v>127</v>
-      </c>
-      <c r="M50" s="27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="N50" s="28" t="n">
-        <v>0.440529</v>
-      </c>
-      <c r="O50" s="28" t="n">
-        <v>0.57961</v>
-      </c>
-      <c r="P50" s="28" t="n"/>
-      <c r="Q50" s="28" t="n">
-        <v>0.139081</v>
-      </c>
-      <c r="R50" s="26" t="n">
-        <v>90</v>
-      </c>
-      <c r="S50" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T50" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U50" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V50" s="24" t="n"/>
-      <c r="W50" s="26" t="n"/>
-      <c r="X50" s="26" t="n"/>
-      <c r="Y50" s="25" t="n"/>
-      <c r="Z50" s="26" t="n"/>
-      <c r="AA50" s="28" t="n"/>
-      <c r="AB50" s="28" t="n"/>
-      <c r="AC50" s="30" t="n"/>
-      <c r="AD50" s="24" t="n"/>
-      <c r="AE50" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
-        </is>
-      </c>
-      <c r="AF50" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG50" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH50" s="24" t="n"/>
-      <c r="AI50" s="31" t="n"/>
-      <c r="AJ50" s="31" t="n"/>
-      <c r="AK50" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL50" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM50" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN50" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO50" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP50" s="24" t="inlineStr">
-        <is>
-          <t>mokrivskiy Club</t>
-        </is>
-      </c>
-      <c r="AQ50" s="24" t="inlineStr">
-        <is>
-          <t>mokrivskiy Club</t>
-        </is>
-      </c>
-      <c r="AR50" s="24" t="inlineStr">
-        <is>
-          <t>mokrivskiy Club</t>
-        </is>
-      </c>
-      <c r="AS50" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="AT50" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="AU50" s="24" t="inlineStr">
-        <is>
-          <t>Morphilina Club</t>
-        </is>
-      </c>
-      <c r="AV50" s="24" t="n"/>
-      <c r="AW50" s="24" t="n"/>
-      <c r="AX50" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY50" s="24" t="n"/>
-      <c r="AZ50" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA50" s="24" t="inlineStr">
-        <is>
-          <t>97de5c5903ba33e53441b5088cf4e6c4cee4d2e8611df656dcf52f1b3af7f6f4</t>
-        </is>
-      </c>
-      <c r="BB50" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC50" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD50" s="24" t="inlineStr">
-        <is>
-          <t>97de5c5903ba33e53441b5088cf4e6c4cee4d2e8611df656dcf52f1b3af7f6f4</t>
-        </is>
-      </c>
-      <c r="BE50" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF50" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG50" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH50" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:36.926594Z</t>
-        </is>
-      </c>
-      <c r="BI50" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ50" s="25" t="n"/>
-      <c r="BK50" s="26" t="n">
-        <v>127</v>
-      </c>
-      <c r="BL50" s="27" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BM50" s="28" t="n">
-        <v>0.440529</v>
-      </c>
-      <c r="BN50" s="28" t="n"/>
-      <c r="BO50" s="28" t="n"/>
-      <c r="BP50" s="25" t="n"/>
-      <c r="BQ50" s="27" t="n"/>
-      <c r="BR50" s="28" t="n"/>
-      <c r="BS50" s="28" t="n"/>
-      <c r="BT50" s="28" t="n"/>
-      <c r="BU50" s="25" t="n"/>
-      <c r="BV50" s="29" t="n"/>
-      <c r="BW50" s="24" t="n"/>
-      <c r="BX50" s="30" t="n"/>
-      <c r="BY50" s="27" t="n"/>
-      <c r="BZ50" s="24" t="n"/>
-      <c r="CA50" s="31" t="n"/>
-      <c r="CB50" s="24" t="n"/>
-      <c r="CC50" s="24" t="n"/>
-      <c r="CD50" s="24" t="n"/>
-      <c r="CE50" s="24" t="n"/>
-      <c r="CF50" s="24" t="n"/>
-      <c r="CG50" s="24" t="n"/>
-      <c r="CH50" s="24" t="n"/>
-      <c r="CI50" s="24" t="n"/>
-      <c r="CJ50" s="24" t="n"/>
-      <c r="CK50" s="24" t="n"/>
-      <c r="CL50" s="24" t="n"/>
-      <c r="CM50" s="24" t="n"/>
-      <c r="CN50" s="24" t="n"/>
-      <c r="CO50" s="24" t="n"/>
-      <c r="CP50" s="24" t="n"/>
-      <c r="CQ50" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="36" customHeight="1">
-      <c r="A51" s="24" t="inlineStr">
-        <is>
-          <t>fa6ef683221e4945</t>
-        </is>
-      </c>
-      <c r="B51" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:49.767554Z</t>
-        </is>
-      </c>
-      <c r="C51" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T19:15:00Z</t>
-        </is>
-      </c>
-      <c r="D51" s="24" t="inlineStr">
-        <is>
-          <t>67577</t>
-        </is>
-      </c>
-      <c r="E51" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F51" s="24" t="inlineStr">
-        <is>
-          <t>SNAILKICK Club</t>
-        </is>
-      </c>
-      <c r="G51" s="24" t="inlineStr">
-        <is>
-          <t>Lixxx Club</t>
-        </is>
-      </c>
-      <c r="H51" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I51" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J51" s="25" t="n"/>
-      <c r="K51" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L51" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="M51" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="N51" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="O51" s="28" t="n">
-        <v>0.52695</v>
-      </c>
-      <c r="P51" s="28" t="n"/>
-      <c r="Q51" s="28" t="n">
-        <v>-0.082425</v>
-      </c>
-      <c r="R51" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T51" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U51" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V51" s="24" t="n"/>
-      <c r="W51" s="26" t="n"/>
-      <c r="X51" s="26" t="n"/>
-      <c r="Y51" s="25" t="n"/>
-      <c r="Z51" s="26" t="n"/>
-      <c r="AA51" s="28" t="n"/>
-      <c r="AB51" s="28" t="n"/>
-      <c r="AC51" s="30" t="n"/>
-      <c r="AD51" s="24" t="n"/>
-      <c r="AE51" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
-        </is>
-      </c>
-      <c r="AF51" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG51" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH51" s="24" t="n"/>
-      <c r="AI51" s="31" t="n"/>
-      <c r="AJ51" s="31" t="n"/>
-      <c r="AK51" s="24" t="inlineStr">
-        <is>
-          <t>research_observation</t>
-        </is>
-      </c>
-      <c r="AL51" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM51" s="24" t="inlineStr">
-        <is>
-          <t>RESEARCH_OBSERVATION</t>
-        </is>
-      </c>
-      <c r="AN51" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL</t>
-        </is>
-      </c>
-      <c r="AO51" s="24" t="inlineStr">
-        <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
-        </is>
-      </c>
-      <c r="AP51" s="24" t="inlineStr">
-        <is>
-          <t>SNAILKICK Club</t>
-        </is>
-      </c>
-      <c r="AQ51" s="24" t="inlineStr">
-        <is>
-          <t>SNAILKICK Club</t>
-        </is>
-      </c>
-      <c r="AR51" s="24" t="inlineStr">
-        <is>
-          <t>SNAILKICK Club</t>
-        </is>
-      </c>
-      <c r="AS51" s="24" t="inlineStr">
-        <is>
-          <t>Lixxx Club</t>
-        </is>
-      </c>
-      <c r="AT51" s="24" t="inlineStr">
-        <is>
-          <t>Lixxx Club</t>
-        </is>
-      </c>
-      <c r="AU51" s="24" t="inlineStr">
-        <is>
-          <t>Lixxx Club</t>
-        </is>
-      </c>
-      <c r="AV51" s="24" t="n"/>
-      <c r="AW51" s="24" t="n"/>
-      <c r="AX51" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY51" s="24" t="n"/>
-      <c r="AZ51" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA51" s="24" t="inlineStr">
-        <is>
-          <t>97de5c5903ba33e53441b5088cf4e6c4cee4d2e8611df656dcf52f1b3af7f6f4</t>
-        </is>
-      </c>
-      <c r="BB51" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC51" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD51" s="24" t="inlineStr">
-        <is>
-          <t>97de5c5903ba33e53441b5088cf4e6c4cee4d2e8611df656dcf52f1b3af7f6f4</t>
-        </is>
-      </c>
-      <c r="BE51" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF51" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG51" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH51" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:37.417895Z</t>
-        </is>
-      </c>
-      <c r="BI51" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ51" s="25" t="n"/>
-      <c r="BK51" s="26" t="n">
-        <v>-156</v>
-      </c>
-      <c r="BL51" s="27" t="n">
-        <v>1.641026</v>
-      </c>
-      <c r="BM51" s="28" t="n">
-        <v>0.609375</v>
-      </c>
-      <c r="BN51" s="28" t="n"/>
-      <c r="BO51" s="28" t="n"/>
-      <c r="BP51" s="25" t="n"/>
-      <c r="BQ51" s="27" t="n"/>
-      <c r="BR51" s="28" t="n"/>
-      <c r="BS51" s="28" t="n"/>
-      <c r="BT51" s="28" t="n"/>
-      <c r="BU51" s="25" t="n"/>
-      <c r="BV51" s="29" t="n"/>
-      <c r="BW51" s="24" t="n"/>
-      <c r="BX51" s="30" t="n"/>
-      <c r="BY51" s="27" t="n"/>
-      <c r="BZ51" s="24" t="n"/>
-      <c r="CA51" s="31" t="n"/>
-      <c r="CB51" s="24" t="n"/>
-      <c r="CC51" s="24" t="n"/>
-      <c r="CD51" s="24" t="n"/>
-      <c r="CE51" s="24" t="n"/>
-      <c r="CF51" s="24" t="n"/>
-      <c r="CG51" s="24" t="n"/>
-      <c r="CH51" s="24" t="n"/>
-      <c r="CI51" s="24" t="n"/>
-      <c r="CJ51" s="24" t="n"/>
-      <c r="CK51" s="24" t="n"/>
-      <c r="CL51" s="24" t="n"/>
-      <c r="CM51" s="24" t="n"/>
-      <c r="CN51" s="24" t="n"/>
-      <c r="CO51" s="24" t="n"/>
-      <c r="CP51" s="24" t="n"/>
-      <c r="CQ51" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="24" t="inlineStr">
-        <is>
-          <t>d6a8b2da702249d0</t>
-        </is>
-      </c>
-      <c r="B52" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:49.767554Z</t>
-        </is>
-      </c>
-      <c r="C52" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-03T10:00:00Z</t>
-        </is>
-      </c>
-      <c r="D52" s="24" t="inlineStr">
-        <is>
-          <t>68289</t>
-        </is>
-      </c>
-      <c r="E52" s="24" t="inlineStr">
-        <is>
-          <t>CS2</t>
-        </is>
-      </c>
-      <c r="F52" s="24" t="inlineStr">
-        <is>
-          <t>FURY</t>
-        </is>
-      </c>
-      <c r="G52" s="24" t="inlineStr">
-        <is>
-          <t>Mindfreak</t>
-        </is>
-      </c>
-      <c r="H52" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I52" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J52" s="25" t="n"/>
-      <c r="K52" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L52" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="M52" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="N52" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="O52" s="28" t="n">
-        <v>0.599274</v>
-      </c>
-      <c r="P52" s="28" t="n"/>
-      <c r="Q52" s="28" t="n">
-        <v>0.019442</v>
-      </c>
-      <c r="R52" s="26" t="n">
-        <v>30</v>
-      </c>
-      <c r="S52" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T52" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U52" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V52" s="24" t="n"/>
-      <c r="W52" s="26" t="n"/>
-      <c r="X52" s="26" t="n"/>
-      <c r="Y52" s="25" t="n"/>
-      <c r="Z52" s="26" t="n"/>
-      <c r="AA52" s="28" t="n"/>
-      <c r="AB52" s="28" t="n"/>
-      <c r="AC52" s="30" t="n"/>
-      <c r="AD52" s="24" t="n"/>
-      <c r="AE52" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
-        </is>
-      </c>
-      <c r="AF52" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG52" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH52" s="24" t="n"/>
-      <c r="AI52" s="31" t="n"/>
-      <c r="AJ52" s="31" t="n"/>
-      <c r="AK52" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL52" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM52" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN52" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO52" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP52" s="24" t="inlineStr">
-        <is>
-          <t>FURY</t>
-        </is>
-      </c>
-      <c r="AQ52" s="24" t="inlineStr">
-        <is>
-          <t>FURY</t>
-        </is>
-      </c>
-      <c r="AR52" s="24" t="inlineStr">
-        <is>
-          <t>FURY</t>
-        </is>
-      </c>
-      <c r="AS52" s="24" t="inlineStr">
-        <is>
-          <t>Mindfreak</t>
-        </is>
-      </c>
-      <c r="AT52" s="24" t="inlineStr">
-        <is>
-          <t>Mindfreak</t>
-        </is>
-      </c>
-      <c r="AU52" s="24" t="inlineStr">
-        <is>
-          <t>Mindfreak</t>
-        </is>
-      </c>
-      <c r="AV52" s="24" t="n"/>
-      <c r="AW52" s="24" t="n"/>
-      <c r="AX52" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY52" s="24" t="n"/>
-      <c r="AZ52" s="24" t="inlineStr">
-        <is>
-          <t>shadow_qualified</t>
-        </is>
-      </c>
-      <c r="BA52" s="24" t="inlineStr">
-        <is>
-          <t>97de5c5903ba33e53441b5088cf4e6c4cee4d2e8611df656dcf52f1b3af7f6f4</t>
-        </is>
-      </c>
-      <c r="BB52" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC52" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD52" s="24" t="inlineStr">
-        <is>
-          <t>97de5c5903ba33e53441b5088cf4e6c4cee4d2e8611df656dcf52f1b3af7f6f4</t>
-        </is>
-      </c>
-      <c r="BE52" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF52" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG52" s="24" t="inlineStr">
-        <is>
-          <t>cs2-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH52" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-02T18:12:39.986059Z</t>
-        </is>
-      </c>
-      <c r="BI52" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ52" s="25" t="n"/>
-      <c r="BK52" s="26" t="n">
-        <v>-138</v>
-      </c>
-      <c r="BL52" s="27" t="n">
-        <v>1.724638</v>
-      </c>
-      <c r="BM52" s="28" t="n">
-        <v>0.579832</v>
-      </c>
-      <c r="BN52" s="28" t="n"/>
-      <c r="BO52" s="28" t="n"/>
-      <c r="BP52" s="25" t="n"/>
-      <c r="BQ52" s="27" t="n"/>
-      <c r="BR52" s="28" t="n"/>
-      <c r="BS52" s="28" t="n"/>
-      <c r="BT52" s="28" t="n"/>
-      <c r="BU52" s="25" t="n"/>
-      <c r="BV52" s="29" t="n"/>
-      <c r="BW52" s="24" t="n"/>
-      <c r="BX52" s="30" t="n"/>
-      <c r="BY52" s="27" t="n"/>
-      <c r="BZ52" s="24" t="n"/>
-      <c r="CA52" s="31" t="n"/>
-      <c r="CB52" s="24" t="n"/>
-      <c r="CC52" s="24" t="n"/>
-      <c r="CD52" s="24" t="n"/>
-      <c r="CE52" s="24" t="n"/>
-      <c r="CF52" s="24" t="n"/>
-      <c r="CG52" s="24" t="n"/>
-      <c r="CH52" s="24" t="n"/>
-      <c r="CI52" s="24" t="n"/>
-      <c r="CJ52" s="24" t="n"/>
-      <c r="CK52" s="24" t="n"/>
-      <c r="CL52" s="24" t="n"/>
-      <c r="CM52" s="24" t="n"/>
-      <c r="CN52" s="24" t="n"/>
-      <c r="CO52" s="24" t="n"/>
-      <c r="CP52" s="24" t="n"/>
-      <c r="CQ52" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ40" headerRowCount="1">
-  <autoFilter ref="A1:CQ40"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ52" headerRowCount="1">
+  <autoFilter ref="A1:CQ52"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$40)</f>
+        <f>COUNTA('Picks'!$A$2:$A$52)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$40,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$52,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$40,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$52,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"win")+COUNTIFS('Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")+COUNTIFS('Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$40,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$52,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$40,"&gt;0",'Picks'!$V$2:$V$40,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$40,"&gt;0",'Picks'!$V$2:$V$40,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$40,"&gt;0",'Picks'!$V$2:$V$40,"win")/(COUNTIFS('Picks'!$BX$2:$BX$40,"&gt;0",'Picks'!$V$2:$V$40,"win")+COUNTIFS('Picks'!$BX$2:$BX$40,"&gt;0",'Picks'!$V$2:$V$40,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")/(COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"win")+COUNTIFS('Picks'!$BX$2:$BX$52,"&gt;0",'Picks'!$V$2:$V$52,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$40)/SUM('Picks'!$BX$2:$BX$40),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$52)/SUM('Picks'!$BX$2:$BX$52),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$40)</f>
+        <f>SUM('Picks'!$BY$2:$BY$52)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$40,"&lt;&gt;",'Picks'!$AB$2:$AB$40),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$52,"&lt;&gt;",'Picks'!$AB$2:$AB$52),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$40,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$40,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$52,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$52,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$40,'Picks'!$AM$2:$AM$40,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$52,'Picks'!$AM$2:$AM$52,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$40,$A14,'Picks'!$U$2:$U$40,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$40,$A14,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$40,$A14,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$40,'Picks'!$H$2:$H$40,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$40,'Picks'!$H$2:$H$40,$A14,'Picks'!$U$2:$U$40,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A14,'Picks'!$U$2:$U$52,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$40,$A15,'Picks'!$U$2:$U$40,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$40,$A15,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$40,$A15,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$40,'Picks'!$H$2:$H$40,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$40,'Picks'!$H$2:$H$40,$A15,'Picks'!$U$2:$U$40,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A15,'Picks'!$U$2:$U$52,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$40,$A16,'Picks'!$U$2:$U$40,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$40,$A16,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$40,$A16,'Picks'!$U$2:$U$40,"settled",'Picks'!$V$2:$V$40,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled",'Picks'!$V$2:$V$52,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$40,'Picks'!$H$2:$H$40,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$52,'Picks'!$H$2:$H$52,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$40,'Picks'!$H$2:$H$40,$A16,'Picks'!$U$2:$U$40,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$52,'Picks'!$H$2:$H$52,$A16,'Picks'!$U$2:$U$52,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ40"/>
+  <dimension ref="A1:CQ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12616,6 +12616,3210 @@
         </is>
       </c>
     </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>40c0b4b277d143ad</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.992034Z</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>67576</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>mokrivskiy Club</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="H41" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I41" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J41" s="25" t="n"/>
+      <c r="K41" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M41" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N41" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O41" s="28" t="n">
+        <v>0.57961</v>
+      </c>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="28" t="n">
+        <v>0.139081</v>
+      </c>
+      <c r="R41" s="26" t="n">
+        <v>90</v>
+      </c>
+      <c r="S41" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T41" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U41" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V41" s="24" t="n"/>
+      <c r="W41" s="26" t="n"/>
+      <c r="X41" s="26" t="n"/>
+      <c r="Y41" s="25" t="n"/>
+      <c r="Z41" s="26" t="n"/>
+      <c r="AA41" s="28" t="n"/>
+      <c r="AB41" s="28" t="n"/>
+      <c r="AC41" s="30" t="n"/>
+      <c r="AD41" s="24" t="n"/>
+      <c r="AE41" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-mcor-mco-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF41" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG41" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH41" s="24" t="n"/>
+      <c r="AI41" s="31" t="n"/>
+      <c r="AJ41" s="31" t="n"/>
+      <c r="AK41" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL41" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM41" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN41" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO41" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP41" s="24" t="inlineStr">
+        <is>
+          <t>mokrivskiy Club</t>
+        </is>
+      </c>
+      <c r="AQ41" s="24" t="inlineStr">
+        <is>
+          <t>mokrivskiy Club</t>
+        </is>
+      </c>
+      <c r="AR41" s="24" t="inlineStr">
+        <is>
+          <t>mokrivskiy Club</t>
+        </is>
+      </c>
+      <c r="AS41" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AT41" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AU41" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AV41" s="24" t="n"/>
+      <c r="AW41" s="24" t="n"/>
+      <c r="AX41" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY41" s="24" t="n"/>
+      <c r="AZ41" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA41" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BB41" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC41" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD41" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BE41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG41" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:31.889837Z</t>
+        </is>
+      </c>
+      <c r="BI41" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ41" s="25" t="n"/>
+      <c r="BK41" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL41" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM41" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN41" s="28" t="n"/>
+      <c r="BO41" s="28" t="n"/>
+      <c r="BP41" s="25" t="n"/>
+      <c r="BQ41" s="27" t="n"/>
+      <c r="BR41" s="28" t="n"/>
+      <c r="BS41" s="28" t="n"/>
+      <c r="BT41" s="28" t="n"/>
+      <c r="BU41" s="25" t="n"/>
+      <c r="BV41" s="29" t="n"/>
+      <c r="BW41" s="24" t="n"/>
+      <c r="BX41" s="30" t="n"/>
+      <c r="BY41" s="27" t="n"/>
+      <c r="BZ41" s="24" t="n"/>
+      <c r="CA41" s="31" t="n"/>
+      <c r="CB41" s="24" t="n"/>
+      <c r="CC41" s="24" t="n"/>
+      <c r="CD41" s="24" t="n"/>
+      <c r="CE41" s="24" t="n"/>
+      <c r="CF41" s="24" t="n"/>
+      <c r="CG41" s="24" t="n"/>
+      <c r="CH41" s="24" t="n"/>
+      <c r="CI41" s="24" t="n"/>
+      <c r="CJ41" s="24" t="n"/>
+      <c r="CK41" s="24" t="n"/>
+      <c r="CL41" s="24" t="n"/>
+      <c r="CM41" s="24" t="n"/>
+      <c r="CN41" s="24" t="n"/>
+      <c r="CO41" s="24" t="n"/>
+      <c r="CP41" s="24" t="n"/>
+      <c r="CQ41" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>e942d73c1fb24422</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.992034Z</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:15:00Z</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>67577</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>SNAILKICK Club</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>Lixxx Club</t>
+        </is>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J42" s="25" t="n"/>
+      <c r="K42" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M42" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N42" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O42" s="28" t="n">
+        <v>0.52695</v>
+      </c>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="28" t="n">
+        <v>-0.082425</v>
+      </c>
+      <c r="R42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U42" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V42" s="24" t="n"/>
+      <c r="W42" s="26" t="n"/>
+      <c r="X42" s="26" t="n"/>
+      <c r="Y42" s="25" t="n"/>
+      <c r="Z42" s="26" t="n"/>
+      <c r="AA42" s="28" t="n"/>
+      <c r="AB42" s="28" t="n"/>
+      <c r="AC42" s="30" t="n"/>
+      <c r="AD42" s="24" t="n"/>
+      <c r="AE42" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-lci-scn-2026-08-02).</t>
+        </is>
+      </c>
+      <c r="AF42" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG42" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH42" s="24" t="n"/>
+      <c r="AI42" s="31" t="n"/>
+      <c r="AJ42" s="31" t="n"/>
+      <c r="AK42" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM42" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN42" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO42" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP42" s="24" t="inlineStr">
+        <is>
+          <t>SNAILKICK Club</t>
+        </is>
+      </c>
+      <c r="AQ42" s="24" t="inlineStr">
+        <is>
+          <t>SNAILKICK Club</t>
+        </is>
+      </c>
+      <c r="AR42" s="24" t="inlineStr">
+        <is>
+          <t>SNAILKICK Club</t>
+        </is>
+      </c>
+      <c r="AS42" s="24" t="inlineStr">
+        <is>
+          <t>Lixxx Club</t>
+        </is>
+      </c>
+      <c r="AT42" s="24" t="inlineStr">
+        <is>
+          <t>Lixxx Club</t>
+        </is>
+      </c>
+      <c r="AU42" s="24" t="inlineStr">
+        <is>
+          <t>Lixxx Club</t>
+        </is>
+      </c>
+      <c r="AV42" s="24" t="n"/>
+      <c r="AW42" s="24" t="n"/>
+      <c r="AX42" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY42" s="24" t="n"/>
+      <c r="AZ42" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA42" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BB42" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC42" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD42" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BE42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG42" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:32.462110Z</t>
+        </is>
+      </c>
+      <c r="BI42" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ42" s="25" t="n"/>
+      <c r="BK42" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL42" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM42" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN42" s="28" t="n"/>
+      <c r="BO42" s="28" t="n"/>
+      <c r="BP42" s="25" t="n"/>
+      <c r="BQ42" s="27" t="n"/>
+      <c r="BR42" s="28" t="n"/>
+      <c r="BS42" s="28" t="n"/>
+      <c r="BT42" s="28" t="n"/>
+      <c r="BU42" s="25" t="n"/>
+      <c r="BV42" s="29" t="n"/>
+      <c r="BW42" s="24" t="n"/>
+      <c r="BX42" s="30" t="n"/>
+      <c r="BY42" s="27" t="n"/>
+      <c r="BZ42" s="24" t="n"/>
+      <c r="CA42" s="31" t="n"/>
+      <c r="CB42" s="24" t="n"/>
+      <c r="CC42" s="24" t="n"/>
+      <c r="CD42" s="24" t="n"/>
+      <c r="CE42" s="24" t="n"/>
+      <c r="CF42" s="24" t="n"/>
+      <c r="CG42" s="24" t="n"/>
+      <c r="CH42" s="24" t="n"/>
+      <c r="CI42" s="24" t="n"/>
+      <c r="CJ42" s="24" t="n"/>
+      <c r="CK42" s="24" t="n"/>
+      <c r="CL42" s="24" t="n"/>
+      <c r="CM42" s="24" t="n"/>
+      <c r="CN42" s="24" t="n"/>
+      <c r="CO42" s="24" t="n"/>
+      <c r="CP42" s="24" t="n"/>
+      <c r="CQ42" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>225670c6c1e146c1</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.992034Z</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>68289</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I43" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J43" s="25" t="n"/>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L43" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="M43" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="N43" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="O43" s="28" t="n">
+        <v>0.599274</v>
+      </c>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="28" t="n">
+        <v>0.019442</v>
+      </c>
+      <c r="R43" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S43" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T43" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U43" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V43" s="24" t="n"/>
+      <c r="W43" s="26" t="n"/>
+      <c r="X43" s="26" t="n"/>
+      <c r="Y43" s="25" t="n"/>
+      <c r="Z43" s="26" t="n"/>
+      <c r="AA43" s="28" t="n"/>
+      <c r="AB43" s="28" t="n"/>
+      <c r="AC43" s="30" t="n"/>
+      <c r="AD43" s="24" t="n"/>
+      <c r="AE43" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-mf-fury-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF43" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG43" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH43" s="24" t="n"/>
+      <c r="AI43" s="31" t="n"/>
+      <c r="AJ43" s="31" t="n"/>
+      <c r="AK43" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL43" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM43" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN43" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO43" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP43" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="AQ43" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="AR43" s="24" t="inlineStr">
+        <is>
+          <t>FURY</t>
+        </is>
+      </c>
+      <c r="AS43" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="AT43" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="AU43" s="24" t="inlineStr">
+        <is>
+          <t>Mindfreak</t>
+        </is>
+      </c>
+      <c r="AV43" s="24" t="n"/>
+      <c r="AW43" s="24" t="n"/>
+      <c r="AX43" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY43" s="24" t="n"/>
+      <c r="AZ43" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA43" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BB43" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC43" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD43" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BE43" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF43" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG43" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:35.118991Z</t>
+        </is>
+      </c>
+      <c r="BI43" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ43" s="25" t="n"/>
+      <c r="BK43" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="BL43" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BM43" s="28" t="n">
+        <v>0.579832</v>
+      </c>
+      <c r="BN43" s="28" t="n"/>
+      <c r="BO43" s="28" t="n"/>
+      <c r="BP43" s="25" t="n"/>
+      <c r="BQ43" s="27" t="n"/>
+      <c r="BR43" s="28" t="n"/>
+      <c r="BS43" s="28" t="n"/>
+      <c r="BT43" s="28" t="n"/>
+      <c r="BU43" s="25" t="n"/>
+      <c r="BV43" s="29" t="n"/>
+      <c r="BW43" s="24" t="n"/>
+      <c r="BX43" s="30" t="n"/>
+      <c r="BY43" s="27" t="n"/>
+      <c r="BZ43" s="24" t="n"/>
+      <c r="CA43" s="31" t="n"/>
+      <c r="CB43" s="24" t="n"/>
+      <c r="CC43" s="24" t="n"/>
+      <c r="CD43" s="24" t="n"/>
+      <c r="CE43" s="24" t="n"/>
+      <c r="CF43" s="24" t="n"/>
+      <c r="CG43" s="24" t="n"/>
+      <c r="CH43" s="24" t="n"/>
+      <c r="CI43" s="24" t="n"/>
+      <c r="CJ43" s="24" t="n"/>
+      <c r="CK43" s="24" t="n"/>
+      <c r="CL43" s="24" t="n"/>
+      <c r="CM43" s="24" t="n"/>
+      <c r="CN43" s="24" t="n"/>
+      <c r="CO43" s="24" t="n"/>
+      <c r="CP43" s="24" t="n"/>
+      <c r="CQ43" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>93ed2943ccd7452a</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.992034Z</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>67510</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>Johnny Speeds</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="inlineStr">
+        <is>
+          <t>Metizport</t>
+        </is>
+      </c>
+      <c r="H44" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J44" s="25" t="n"/>
+      <c r="K44" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L44" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M44" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N44" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O44" s="28" t="n">
+        <v>0.563115</v>
+      </c>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="28" t="n">
+        <v>-0.127287</v>
+      </c>
+      <c r="R44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T44" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U44" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V44" s="24" t="n"/>
+      <c r="W44" s="26" t="n"/>
+      <c r="X44" s="26" t="n"/>
+      <c r="Y44" s="25" t="n"/>
+      <c r="Z44" s="26" t="n"/>
+      <c r="AA44" s="28" t="n"/>
+      <c r="AB44" s="28" t="n"/>
+      <c r="AC44" s="30" t="n"/>
+      <c r="AD44" s="24" t="n"/>
+      <c r="AE44" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-mzp-js-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF44" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG44" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH44" s="24" t="n"/>
+      <c r="AI44" s="31" t="n"/>
+      <c r="AJ44" s="31" t="n"/>
+      <c r="AK44" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL44" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM44" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN44" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO44" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP44" s="24" t="inlineStr">
+        <is>
+          <t>Johnny Speeds</t>
+        </is>
+      </c>
+      <c r="AQ44" s="24" t="inlineStr">
+        <is>
+          <t>Johnny Speeds</t>
+        </is>
+      </c>
+      <c r="AR44" s="24" t="inlineStr">
+        <is>
+          <t>Johnny Speeds</t>
+        </is>
+      </c>
+      <c r="AS44" s="24" t="inlineStr">
+        <is>
+          <t>Metizport</t>
+        </is>
+      </c>
+      <c r="AT44" s="24" t="inlineStr">
+        <is>
+          <t>Metizport</t>
+        </is>
+      </c>
+      <c r="AU44" s="24" t="inlineStr">
+        <is>
+          <t>Metizport</t>
+        </is>
+      </c>
+      <c r="AV44" s="24" t="n"/>
+      <c r="AW44" s="24" t="n"/>
+      <c r="AX44" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY44" s="24" t="n"/>
+      <c r="AZ44" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA44" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BB44" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC44" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD44" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BE44" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF44" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG44" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:36.680077Z</t>
+        </is>
+      </c>
+      <c r="BI44" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ44" s="25" t="n"/>
+      <c r="BK44" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL44" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM44" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN44" s="28" t="n"/>
+      <c r="BO44" s="28" t="n"/>
+      <c r="BP44" s="25" t="n"/>
+      <c r="BQ44" s="27" t="n"/>
+      <c r="BR44" s="28" t="n"/>
+      <c r="BS44" s="28" t="n"/>
+      <c r="BT44" s="28" t="n"/>
+      <c r="BU44" s="25" t="n"/>
+      <c r="BV44" s="29" t="n"/>
+      <c r="BW44" s="24" t="n"/>
+      <c r="BX44" s="30" t="n"/>
+      <c r="BY44" s="27" t="n"/>
+      <c r="BZ44" s="24" t="n"/>
+      <c r="CA44" s="31" t="n"/>
+      <c r="CB44" s="24" t="n"/>
+      <c r="CC44" s="24" t="n"/>
+      <c r="CD44" s="24" t="n"/>
+      <c r="CE44" s="24" t="n"/>
+      <c r="CF44" s="24" t="n"/>
+      <c r="CG44" s="24" t="n"/>
+      <c r="CH44" s="24" t="n"/>
+      <c r="CI44" s="24" t="n"/>
+      <c r="CJ44" s="24" t="n"/>
+      <c r="CK44" s="24" t="n"/>
+      <c r="CL44" s="24" t="n"/>
+      <c r="CM44" s="24" t="n"/>
+      <c r="CN44" s="24" t="n"/>
+      <c r="CO44" s="24" t="n"/>
+      <c r="CP44" s="24" t="n"/>
+      <c r="CQ44" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>412616da924148cc</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.992034Z</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:30:00Z</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>67514</t>
+        </is>
+      </c>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="G45" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="H45" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I45" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J45" s="25" t="n"/>
+      <c r="K45" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L45" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M45" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N45" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O45" s="28" t="n">
+        <v>0.640004</v>
+      </c>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="28" t="n">
+        <v>0.020232</v>
+      </c>
+      <c r="R45" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="S45" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T45" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U45" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V45" s="24" t="n"/>
+      <c r="W45" s="26" t="n"/>
+      <c r="X45" s="26" t="n"/>
+      <c r="Y45" s="25" t="n"/>
+      <c r="Z45" s="26" t="n"/>
+      <c r="AA45" s="28" t="n"/>
+      <c r="AB45" s="28" t="n"/>
+      <c r="AC45" s="30" t="n"/>
+      <c r="AD45" s="24" t="n"/>
+      <c r="AE45" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-era-psna-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF45" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG45" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH45" s="24" t="n"/>
+      <c r="AI45" s="31" t="n"/>
+      <c r="AJ45" s="31" t="n"/>
+      <c r="AK45" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL45" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM45" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN45" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO45" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP45" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="AQ45" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="AR45" s="24" t="inlineStr">
+        <is>
+          <t>Passion Academy</t>
+        </is>
+      </c>
+      <c r="AS45" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AT45" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AU45" s="24" t="inlineStr">
+        <is>
+          <t>EAC Rising</t>
+        </is>
+      </c>
+      <c r="AV45" s="24" t="n"/>
+      <c r="AW45" s="24" t="n"/>
+      <c r="AX45" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY45" s="24" t="n"/>
+      <c r="AZ45" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA45" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BB45" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC45" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD45" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BE45" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF45" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG45" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH45" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:37.624827Z</t>
+        </is>
+      </c>
+      <c r="BI45" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ45" s="25" t="n"/>
+      <c r="BK45" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL45" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM45" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN45" s="28" t="n"/>
+      <c r="BO45" s="28" t="n"/>
+      <c r="BP45" s="25" t="n"/>
+      <c r="BQ45" s="27" t="n"/>
+      <c r="BR45" s="28" t="n"/>
+      <c r="BS45" s="28" t="n"/>
+      <c r="BT45" s="28" t="n"/>
+      <c r="BU45" s="25" t="n"/>
+      <c r="BV45" s="29" t="n"/>
+      <c r="BW45" s="24" t="n"/>
+      <c r="BX45" s="30" t="n"/>
+      <c r="BY45" s="27" t="n"/>
+      <c r="BZ45" s="24" t="n"/>
+      <c r="CA45" s="31" t="n"/>
+      <c r="CB45" s="24" t="n"/>
+      <c r="CC45" s="24" t="n"/>
+      <c r="CD45" s="24" t="n"/>
+      <c r="CE45" s="24" t="n"/>
+      <c r="CF45" s="24" t="n"/>
+      <c r="CG45" s="24" t="n"/>
+      <c r="CH45" s="24" t="n"/>
+      <c r="CI45" s="24" t="n"/>
+      <c r="CJ45" s="24" t="n"/>
+      <c r="CK45" s="24" t="n"/>
+      <c r="CL45" s="24" t="n"/>
+      <c r="CM45" s="24" t="n"/>
+      <c r="CN45" s="24" t="n"/>
+      <c r="CO45" s="24" t="n"/>
+      <c r="CP45" s="24" t="n"/>
+      <c r="CQ45" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>a18c9bf9ab354be3</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.992034Z</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>69267</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="H46" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I46" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J46" s="25" t="n"/>
+      <c r="K46" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L46" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="M46" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="N46" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="O46" s="28" t="n">
+        <v>0.628935</v>
+      </c>
+      <c r="P46" s="28" t="n"/>
+      <c r="Q46" s="28" t="n">
+        <v>-0.051576</v>
+      </c>
+      <c r="R46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T46" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U46" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V46" s="24" t="n"/>
+      <c r="W46" s="26" t="n"/>
+      <c r="X46" s="26" t="n"/>
+      <c r="Y46" s="25" t="n"/>
+      <c r="Z46" s="26" t="n"/>
+      <c r="AA46" s="28" t="n"/>
+      <c r="AB46" s="28" t="n"/>
+      <c r="AC46" s="30" t="n"/>
+      <c r="AD46" s="24" t="n"/>
+      <c r="AE46" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-jpu-lk-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF46" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG46" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH46" s="24" t="n"/>
+      <c r="AI46" s="31" t="n"/>
+      <c r="AJ46" s="31" t="n"/>
+      <c r="AK46" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL46" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM46" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN46" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO46" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP46" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="AQ46" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="AR46" s="24" t="inlineStr">
+        <is>
+          <t>los kogutos</t>
+        </is>
+      </c>
+      <c r="AS46" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AT46" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AU46" s="24" t="inlineStr">
+        <is>
+          <t>Just Players</t>
+        </is>
+      </c>
+      <c r="AV46" s="24" t="n"/>
+      <c r="AW46" s="24" t="n"/>
+      <c r="AX46" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY46" s="24" t="n"/>
+      <c r="AZ46" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA46" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BB46" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC46" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD46" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BE46" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF46" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG46" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH46" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:38.106265Z</t>
+        </is>
+      </c>
+      <c r="BI46" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ46" s="25" t="n"/>
+      <c r="BK46" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="BL46" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BM46" s="28" t="n">
+        <v>0.680511</v>
+      </c>
+      <c r="BN46" s="28" t="n"/>
+      <c r="BO46" s="28" t="n"/>
+      <c r="BP46" s="25" t="n"/>
+      <c r="BQ46" s="27" t="n"/>
+      <c r="BR46" s="28" t="n"/>
+      <c r="BS46" s="28" t="n"/>
+      <c r="BT46" s="28" t="n"/>
+      <c r="BU46" s="25" t="n"/>
+      <c r="BV46" s="29" t="n"/>
+      <c r="BW46" s="24" t="n"/>
+      <c r="BX46" s="30" t="n"/>
+      <c r="BY46" s="27" t="n"/>
+      <c r="BZ46" s="24" t="n"/>
+      <c r="CA46" s="31" t="n"/>
+      <c r="CB46" s="24" t="n"/>
+      <c r="CC46" s="24" t="n"/>
+      <c r="CD46" s="24" t="n"/>
+      <c r="CE46" s="24" t="n"/>
+      <c r="CF46" s="24" t="n"/>
+      <c r="CG46" s="24" t="n"/>
+      <c r="CH46" s="24" t="n"/>
+      <c r="CI46" s="24" t="n"/>
+      <c r="CJ46" s="24" t="n"/>
+      <c r="CK46" s="24" t="n"/>
+      <c r="CL46" s="24" t="n"/>
+      <c r="CM46" s="24" t="n"/>
+      <c r="CN46" s="24" t="n"/>
+      <c r="CO46" s="24" t="n"/>
+      <c r="CP46" s="24" t="n"/>
+      <c r="CQ46" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>aaf28a4288ea44ae</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.992034Z</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>67578</t>
+        </is>
+      </c>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="inlineStr">
+        <is>
+          <t>Recrent Club</t>
+        </is>
+      </c>
+      <c r="H47" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I47" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J47" s="25" t="n"/>
+      <c r="K47" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L47" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M47" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N47" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O47" s="28" t="n">
+        <v>0.52695</v>
+      </c>
+      <c r="P47" s="28" t="n"/>
+      <c r="Q47" s="28" t="n">
+        <v>-0.07305</v>
+      </c>
+      <c r="R47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U47" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V47" s="24" t="n"/>
+      <c r="W47" s="26" t="n"/>
+      <c r="X47" s="26" t="n"/>
+      <c r="Y47" s="25" t="n"/>
+      <c r="Z47" s="26" t="n"/>
+      <c r="AA47" s="28" t="n"/>
+      <c r="AB47" s="28" t="n"/>
+      <c r="AC47" s="30" t="n"/>
+      <c r="AD47" s="24" t="n"/>
+      <c r="AE47" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-cs2-rce-pce-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF47" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG47" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH47" s="24" t="n"/>
+      <c r="AI47" s="31" t="n"/>
+      <c r="AJ47" s="31" t="n"/>
+      <c r="AK47" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL47" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM47" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN47" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO47" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP47" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AQ47" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AR47" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AS47" s="24" t="inlineStr">
+        <is>
+          <t>Recrent Club</t>
+        </is>
+      </c>
+      <c r="AT47" s="24" t="inlineStr">
+        <is>
+          <t>Recrent Club</t>
+        </is>
+      </c>
+      <c r="AU47" s="24" t="inlineStr">
+        <is>
+          <t>Recrent Club</t>
+        </is>
+      </c>
+      <c r="AV47" s="24" t="n"/>
+      <c r="AW47" s="24" t="n"/>
+      <c r="AX47" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY47" s="24" t="n"/>
+      <c r="AZ47" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA47" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BB47" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC47" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD47" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BE47" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF47" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG47" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH47" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:38.641492Z</t>
+        </is>
+      </c>
+      <c r="BI47" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ47" s="25" t="n"/>
+      <c r="BK47" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL47" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM47" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN47" s="28" t="n"/>
+      <c r="BO47" s="28" t="n"/>
+      <c r="BP47" s="25" t="n"/>
+      <c r="BQ47" s="27" t="n"/>
+      <c r="BR47" s="28" t="n"/>
+      <c r="BS47" s="28" t="n"/>
+      <c r="BT47" s="28" t="n"/>
+      <c r="BU47" s="25" t="n"/>
+      <c r="BV47" s="29" t="n"/>
+      <c r="BW47" s="24" t="n"/>
+      <c r="BX47" s="30" t="n"/>
+      <c r="BY47" s="27" t="n"/>
+      <c r="BZ47" s="24" t="n"/>
+      <c r="CA47" s="31" t="n"/>
+      <c r="CB47" s="24" t="n"/>
+      <c r="CC47" s="24" t="n"/>
+      <c r="CD47" s="24" t="n"/>
+      <c r="CE47" s="24" t="n"/>
+      <c r="CF47" s="24" t="n"/>
+      <c r="CG47" s="24" t="n"/>
+      <c r="CH47" s="24" t="n"/>
+      <c r="CI47" s="24" t="n"/>
+      <c r="CJ47" s="24" t="n"/>
+      <c r="CK47" s="24" t="n"/>
+      <c r="CL47" s="24" t="n"/>
+      <c r="CM47" s="24" t="n"/>
+      <c r="CN47" s="24" t="n"/>
+      <c r="CO47" s="24" t="n"/>
+      <c r="CP47" s="24" t="n"/>
+      <c r="CQ47" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>9c8db8d6e2834596</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.992034Z</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>69135</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUBY</t>
+        </is>
+      </c>
+      <c r="G48" s="24" t="inlineStr">
+        <is>
+          <t>1WIN</t>
+        </is>
+      </c>
+      <c r="H48" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I48" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J48" s="25" t="n"/>
+      <c r="K48" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L48" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M48" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N48" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O48" s="28" t="n">
+        <v>0.527213</v>
+      </c>
+      <c r="P48" s="28" t="n"/>
+      <c r="Q48" s="28" t="n">
+        <v>-0.102417</v>
+      </c>
+      <c r="R48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U48" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V48" s="24" t="n"/>
+      <c r="W48" s="26" t="n"/>
+      <c r="X48" s="26" t="n"/>
+      <c r="Y48" s="25" t="n"/>
+      <c r="Z48" s="26" t="n"/>
+      <c r="AA48" s="28" t="n"/>
+      <c r="AB48" s="28" t="n"/>
+      <c r="AC48" s="30" t="n"/>
+      <c r="AD48" s="24" t="n"/>
+      <c r="AE48" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-1win-exruby-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF48" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG48" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH48" s="24" t="n"/>
+      <c r="AI48" s="31" t="n"/>
+      <c r="AJ48" s="31" t="n"/>
+      <c r="AK48" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL48" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM48" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN48" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO48" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP48" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUBY</t>
+        </is>
+      </c>
+      <c r="AQ48" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUBY</t>
+        </is>
+      </c>
+      <c r="AR48" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUBY</t>
+        </is>
+      </c>
+      <c r="AS48" s="24" t="inlineStr">
+        <is>
+          <t>1WIN</t>
+        </is>
+      </c>
+      <c r="AT48" s="24" t="inlineStr">
+        <is>
+          <t>1WIN</t>
+        </is>
+      </c>
+      <c r="AU48" s="24" t="inlineStr">
+        <is>
+          <t>1WIN</t>
+        </is>
+      </c>
+      <c r="AV48" s="24" t="n"/>
+      <c r="AW48" s="24" t="n"/>
+      <c r="AX48" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY48" s="24" t="n"/>
+      <c r="AZ48" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA48" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BB48" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC48" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD48" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BE48" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF48" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG48" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH48" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:39.222086Z</t>
+        </is>
+      </c>
+      <c r="BI48" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ48" s="25" t="n"/>
+      <c r="BK48" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL48" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM48" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN48" s="28" t="n"/>
+      <c r="BO48" s="28" t="n"/>
+      <c r="BP48" s="25" t="n"/>
+      <c r="BQ48" s="27" t="n"/>
+      <c r="BR48" s="28" t="n"/>
+      <c r="BS48" s="28" t="n"/>
+      <c r="BT48" s="28" t="n"/>
+      <c r="BU48" s="25" t="n"/>
+      <c r="BV48" s="29" t="n"/>
+      <c r="BW48" s="24" t="n"/>
+      <c r="BX48" s="30" t="n"/>
+      <c r="BY48" s="27" t="n"/>
+      <c r="BZ48" s="24" t="n"/>
+      <c r="CA48" s="31" t="n"/>
+      <c r="CB48" s="24" t="n"/>
+      <c r="CC48" s="24" t="n"/>
+      <c r="CD48" s="24" t="n"/>
+      <c r="CE48" s="24" t="n"/>
+      <c r="CF48" s="24" t="n"/>
+      <c r="CG48" s="24" t="n"/>
+      <c r="CH48" s="24" t="n"/>
+      <c r="CI48" s="24" t="n"/>
+      <c r="CJ48" s="24" t="n"/>
+      <c r="CK48" s="24" t="n"/>
+      <c r="CL48" s="24" t="n"/>
+      <c r="CM48" s="24" t="n"/>
+      <c r="CN48" s="24" t="n"/>
+      <c r="CO48" s="24" t="n"/>
+      <c r="CP48" s="24" t="n"/>
+      <c r="CQ48" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>cdce12367ea0483b</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.992034Z</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:45:00Z</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>67579</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="H49" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I49" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J49" s="25" t="n"/>
+      <c r="K49" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L49" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="M49" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N49" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="O49" s="28" t="n">
+        <v>0.526317</v>
+      </c>
+      <c r="P49" s="28" t="n"/>
+      <c r="Q49" s="28" t="n">
+        <v>0.186181</v>
+      </c>
+      <c r="R49" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S49" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U49" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V49" s="24" t="n"/>
+      <c r="W49" s="26" t="n"/>
+      <c r="X49" s="26" t="n"/>
+      <c r="Y49" s="25" t="n"/>
+      <c r="Z49" s="26" t="n"/>
+      <c r="AA49" s="28" t="n"/>
+      <c r="AB49" s="28" t="n"/>
+      <c r="AC49" s="30" t="n"/>
+      <c r="AD49" s="24" t="n"/>
+      <c r="AE49" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3400 (market_slug=aec-cs2-pce-mcor-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF49" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG49" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH49" s="24" t="n"/>
+      <c r="AI49" s="31" t="n"/>
+      <c r="AJ49" s="31" t="n"/>
+      <c r="AK49" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL49" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM49" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN49" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO49" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP49" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AQ49" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AR49" s="24" t="inlineStr">
+        <is>
+          <t>Morphilina Club</t>
+        </is>
+      </c>
+      <c r="AS49" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AT49" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AU49" s="24" t="inlineStr">
+        <is>
+          <t>Perfecto Club</t>
+        </is>
+      </c>
+      <c r="AV49" s="24" t="n"/>
+      <c r="AW49" s="24" t="n"/>
+      <c r="AX49" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY49" s="24" t="n"/>
+      <c r="AZ49" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA49" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BB49" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC49" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD49" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BE49" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF49" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG49" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH49" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:39.764070Z</t>
+        </is>
+      </c>
+      <c r="BI49" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ49" s="25" t="n"/>
+      <c r="BK49" s="26" t="n">
+        <v>194</v>
+      </c>
+      <c r="BL49" s="27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BM49" s="28" t="n">
+        <v>0.340136</v>
+      </c>
+      <c r="BN49" s="28" t="n"/>
+      <c r="BO49" s="28" t="n"/>
+      <c r="BP49" s="25" t="n"/>
+      <c r="BQ49" s="27" t="n"/>
+      <c r="BR49" s="28" t="n"/>
+      <c r="BS49" s="28" t="n"/>
+      <c r="BT49" s="28" t="n"/>
+      <c r="BU49" s="25" t="n"/>
+      <c r="BV49" s="29" t="n"/>
+      <c r="BW49" s="24" t="n"/>
+      <c r="BX49" s="30" t="n"/>
+      <c r="BY49" s="27" t="n"/>
+      <c r="BZ49" s="24" t="n"/>
+      <c r="CA49" s="31" t="n"/>
+      <c r="CB49" s="24" t="n"/>
+      <c r="CC49" s="24" t="n"/>
+      <c r="CD49" s="24" t="n"/>
+      <c r="CE49" s="24" t="n"/>
+      <c r="CF49" s="24" t="n"/>
+      <c r="CG49" s="24" t="n"/>
+      <c r="CH49" s="24" t="n"/>
+      <c r="CI49" s="24" t="n"/>
+      <c r="CJ49" s="24" t="n"/>
+      <c r="CK49" s="24" t="n"/>
+      <c r="CL49" s="24" t="n"/>
+      <c r="CM49" s="24" t="n"/>
+      <c r="CN49" s="24" t="n"/>
+      <c r="CO49" s="24" t="n"/>
+      <c r="CP49" s="24" t="n"/>
+      <c r="CQ49" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>9ae4dc87df774f4c</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.992034Z</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>69268</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="G50" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="H50" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I50" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J50" s="25" t="n"/>
+      <c r="K50" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L50" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M50" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N50" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O50" s="28" t="n">
+        <v>0.663166</v>
+      </c>
+      <c r="P50" s="28" t="n"/>
+      <c r="Q50" s="28" t="n">
+        <v>0.022878</v>
+      </c>
+      <c r="R50" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S50" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T50" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U50" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V50" s="24" t="n"/>
+      <c r="W50" s="26" t="n"/>
+      <c r="X50" s="26" t="n"/>
+      <c r="Y50" s="25" t="n"/>
+      <c r="Z50" s="26" t="n"/>
+      <c r="AA50" s="28" t="n"/>
+      <c r="AB50" s="28" t="n"/>
+      <c r="AC50" s="30" t="n"/>
+      <c r="AD50" s="24" t="n"/>
+      <c r="AE50" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-sparta-eyn-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF50" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG50" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH50" s="24" t="n"/>
+      <c r="AI50" s="31" t="n"/>
+      <c r="AJ50" s="31" t="n"/>
+      <c r="AK50" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL50" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM50" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN50" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO50" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP50" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AQ50" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AR50" s="24" t="inlineStr">
+        <is>
+          <t>ex-Young Ninjas</t>
+        </is>
+      </c>
+      <c r="AS50" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AT50" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AU50" s="24" t="inlineStr">
+        <is>
+          <t>SPARTA</t>
+        </is>
+      </c>
+      <c r="AV50" s="24" t="n"/>
+      <c r="AW50" s="24" t="n"/>
+      <c r="AX50" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY50" s="24" t="n"/>
+      <c r="AZ50" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA50" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BB50" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC50" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD50" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BE50" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF50" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG50" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH50" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:40.237935Z</t>
+        </is>
+      </c>
+      <c r="BI50" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ50" s="25" t="n"/>
+      <c r="BK50" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL50" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM50" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN50" s="28" t="n"/>
+      <c r="BO50" s="28" t="n"/>
+      <c r="BP50" s="25" t="n"/>
+      <c r="BQ50" s="27" t="n"/>
+      <c r="BR50" s="28" t="n"/>
+      <c r="BS50" s="28" t="n"/>
+      <c r="BT50" s="28" t="n"/>
+      <c r="BU50" s="25" t="n"/>
+      <c r="BV50" s="29" t="n"/>
+      <c r="BW50" s="24" t="n"/>
+      <c r="BX50" s="30" t="n"/>
+      <c r="BY50" s="27" t="n"/>
+      <c r="BZ50" s="24" t="n"/>
+      <c r="CA50" s="31" t="n"/>
+      <c r="CB50" s="24" t="n"/>
+      <c r="CC50" s="24" t="n"/>
+      <c r="CD50" s="24" t="n"/>
+      <c r="CE50" s="24" t="n"/>
+      <c r="CF50" s="24" t="n"/>
+      <c r="CG50" s="24" t="n"/>
+      <c r="CH50" s="24" t="n"/>
+      <c r="CI50" s="24" t="n"/>
+      <c r="CJ50" s="24" t="n"/>
+      <c r="CK50" s="24" t="n"/>
+      <c r="CL50" s="24" t="n"/>
+      <c r="CM50" s="24" t="n"/>
+      <c r="CN50" s="24" t="n"/>
+      <c r="CO50" s="24" t="n"/>
+      <c r="CP50" s="24" t="n"/>
+      <c r="CQ50" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>c17d439ef8a6478f</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.992034Z</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>68292</t>
+        </is>
+      </c>
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>ARCRED</t>
+        </is>
+      </c>
+      <c r="H51" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I51" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J51" s="25" t="n"/>
+      <c r="K51" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L51" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M51" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N51" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O51" s="28" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="P51" s="28" t="n"/>
+      <c r="Q51" s="28" t="n">
+        <v>-0.026288</v>
+      </c>
+      <c r="R51" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="S51" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T51" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U51" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V51" s="24" t="n"/>
+      <c r="W51" s="26" t="n"/>
+      <c r="X51" s="26" t="n"/>
+      <c r="Y51" s="25" t="n"/>
+      <c r="Z51" s="26" t="n"/>
+      <c r="AA51" s="28" t="n"/>
+      <c r="AB51" s="28" t="n"/>
+      <c r="AC51" s="30" t="n"/>
+      <c r="AD51" s="24" t="n"/>
+      <c r="AE51" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-arc-btf-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF51" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG51" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH51" s="24" t="n"/>
+      <c r="AI51" s="31" t="n"/>
+      <c r="AJ51" s="31" t="n"/>
+      <c r="AK51" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL51" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM51" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN51" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO51" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP51" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AQ51" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AR51" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AS51" s="24" t="inlineStr">
+        <is>
+          <t>ARCRED</t>
+        </is>
+      </c>
+      <c r="AT51" s="24" t="inlineStr">
+        <is>
+          <t>ARCRED</t>
+        </is>
+      </c>
+      <c r="AU51" s="24" t="inlineStr">
+        <is>
+          <t>ARCRED</t>
+        </is>
+      </c>
+      <c r="AV51" s="24" t="n"/>
+      <c r="AW51" s="24" t="n"/>
+      <c r="AX51" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY51" s="24" t="n"/>
+      <c r="AZ51" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA51" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BB51" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC51" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD51" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BE51" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF51" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG51" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH51" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:40.707211Z</t>
+        </is>
+      </c>
+      <c r="BI51" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ51" s="25" t="n"/>
+      <c r="BK51" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL51" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM51" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN51" s="28" t="n"/>
+      <c r="BO51" s="28" t="n"/>
+      <c r="BP51" s="25" t="n"/>
+      <c r="BQ51" s="27" t="n"/>
+      <c r="BR51" s="28" t="n"/>
+      <c r="BS51" s="28" t="n"/>
+      <c r="BT51" s="28" t="n"/>
+      <c r="BU51" s="25" t="n"/>
+      <c r="BV51" s="29" t="n"/>
+      <c r="BW51" s="24" t="n"/>
+      <c r="BX51" s="30" t="n"/>
+      <c r="BY51" s="27" t="n"/>
+      <c r="BZ51" s="24" t="n"/>
+      <c r="CA51" s="31" t="n"/>
+      <c r="CB51" s="24" t="n"/>
+      <c r="CC51" s="24" t="n"/>
+      <c r="CD51" s="24" t="n"/>
+      <c r="CE51" s="24" t="n"/>
+      <c r="CF51" s="24" t="n"/>
+      <c r="CG51" s="24" t="n"/>
+      <c r="CH51" s="24" t="n"/>
+      <c r="CI51" s="24" t="n"/>
+      <c r="CJ51" s="24" t="n"/>
+      <c r="CK51" s="24" t="n"/>
+      <c r="CL51" s="24" t="n"/>
+      <c r="CM51" s="24" t="n"/>
+      <c r="CN51" s="24" t="n"/>
+      <c r="CO51" s="24" t="n"/>
+      <c r="CP51" s="24" t="n"/>
+      <c r="CQ51" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>142d7fccce1c4f93</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.992034Z</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>68043</t>
+        </is>
+      </c>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="H52" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J52" s="25" t="n"/>
+      <c r="K52" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L52" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M52" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N52" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O52" s="28" t="n">
+        <v>0.569685</v>
+      </c>
+      <c r="P52" s="28" t="n"/>
+      <c r="Q52" s="28" t="n">
+        <v>0.119235</v>
+      </c>
+      <c r="R52" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="S52" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T52" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U52" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V52" s="24" t="n"/>
+      <c r="W52" s="26" t="n"/>
+      <c r="X52" s="26" t="n"/>
+      <c r="Y52" s="25" t="n"/>
+      <c r="Z52" s="26" t="n"/>
+      <c r="AA52" s="28" t="n"/>
+      <c r="AB52" s="28" t="n"/>
+      <c r="AC52" s="30" t="n"/>
+      <c r="AD52" s="24" t="n"/>
+      <c r="AE52" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-ger-paina-2026-08-03).</t>
+        </is>
+      </c>
+      <c r="AF52" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG52" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH52" s="24" t="n"/>
+      <c r="AI52" s="31" t="n"/>
+      <c r="AJ52" s="31" t="n"/>
+      <c r="AK52" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL52" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM52" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN52" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO52" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP52" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AQ52" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AR52" s="24" t="inlineStr">
+        <is>
+          <t>paiN Academy</t>
+        </is>
+      </c>
+      <c r="AS52" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AT52" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AU52" s="24" t="inlineStr">
+        <is>
+          <t>Grêmio Esports</t>
+        </is>
+      </c>
+      <c r="AV52" s="24" t="n"/>
+      <c r="AW52" s="24" t="n"/>
+      <c r="AX52" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY52" s="24" t="n"/>
+      <c r="AZ52" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA52" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BB52" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC52" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD52" s="24" t="inlineStr">
+        <is>
+          <t>0393e290b17b4d34bf783a8173fb53c53aebc8558545e4c0778b6e017fd0a405</t>
+        </is>
+      </c>
+      <c r="BE52" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF52" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG52" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH52" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:24:44.989547Z</t>
+        </is>
+      </c>
+      <c r="BI52" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ52" s="25" t="n"/>
+      <c r="BK52" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL52" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM52" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN52" s="28" t="n"/>
+      <c r="BO52" s="28" t="n"/>
+      <c r="BP52" s="25" t="n"/>
+      <c r="BQ52" s="27" t="n"/>
+      <c r="BR52" s="28" t="n"/>
+      <c r="BS52" s="28" t="n"/>
+      <c r="BT52" s="28" t="n"/>
+      <c r="BU52" s="25" t="n"/>
+      <c r="BV52" s="29" t="n"/>
+      <c r="BW52" s="24" t="n"/>
+      <c r="BX52" s="30" t="n"/>
+      <c r="BY52" s="27" t="n"/>
+      <c r="BZ52" s="24" t="n"/>
+      <c r="CA52" s="31" t="n"/>
+      <c r="CB52" s="24" t="n"/>
+      <c r="CC52" s="24" t="n"/>
+      <c r="CD52" s="24" t="n"/>
+      <c r="CE52" s="24" t="n"/>
+      <c r="CF52" s="24" t="n"/>
+      <c r="CG52" s="24" t="n"/>
+      <c r="CH52" s="24" t="n"/>
+      <c r="CI52" s="24" t="n"/>
+      <c r="CJ52" s="24" t="n"/>
+      <c r="CK52" s="24" t="n"/>
+      <c r="CL52" s="24" t="n"/>
+      <c r="CM52" s="24" t="n"/>
+      <c r="CN52" s="24" t="n"/>
+      <c r="CO52" s="24" t="n"/>
+      <c r="CP52" s="24" t="n"/>
+      <c r="CQ52" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ78" headerRowCount="1">
-  <autoFilter ref="A1:CQ78"/>
-  <tableColumns count="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR87" headerRowCount="1">
+  <autoFilter ref="A1:CR87"/>
+  <tableColumns count="96">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -392,12 +392,13 @@
     <tableColumn id="87" name="unavailable_features"/>
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
-    <tableColumn id="90" name="rest_disparity"/>
-    <tableColumn id="91" name="back_to_back_gap"/>
-    <tableColumn id="92" name="games_last_7_gap"/>
-    <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="market_residual_probability"/>
-    <tableColumn id="95" name="trade_candidate"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="rest_disparity"/>
+    <tableColumn id="92" name="back_to_back_gap"/>
+    <tableColumn id="93" name="games_last_7_gap"/>
+    <tableColumn id="94" name="schedule_missingness"/>
+    <tableColumn id="95" name="market_residual_probability"/>
+    <tableColumn id="96" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -754,19 +755,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$78)</f>
+        <f>COUNTA('Picks'!$A$2:$A$87)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$78,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$87,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$78,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$87,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$78,"settled",'Picks'!$V$2:$V$78,"win")+COUNTIFS('Picks'!$U$2:$U$78,"settled",'Picks'!$V$2:$V$78,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$87,"settled",'Picks'!$V$2:$V$87,"win")+COUNTIFS('Picks'!$U$2:$U$87,"settled",'Picks'!$V$2:$V$87,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +795,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$78,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$87,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$78,"&gt;0",'Picks'!$V$2:$V$78,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$78,"&gt;0",'Picks'!$V$2:$V$78,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$87,"&gt;0",'Picks'!$V$2:$V$87,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$87,"&gt;0",'Picks'!$V$2:$V$87,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$78,"&gt;0",'Picks'!$V$2:$V$78,"win")/(COUNTIFS('Picks'!$BX$2:$BX$78,"&gt;0",'Picks'!$V$2:$V$78,"win")+COUNTIFS('Picks'!$BX$2:$BX$78,"&gt;0",'Picks'!$V$2:$V$78,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$87,"&gt;0",'Picks'!$V$2:$V$87,"win")/(COUNTIFS('Picks'!$BX$2:$BX$87,"&gt;0",'Picks'!$V$2:$V$87,"win")+COUNTIFS('Picks'!$BX$2:$BX$87,"&gt;0",'Picks'!$V$2:$V$87,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$78)/SUM('Picks'!$BX$2:$BX$78),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$87)/SUM('Picks'!$BX$2:$BX$87),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +835,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$78)</f>
+        <f>SUM('Picks'!$BY$2:$BY$87)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$78,"&lt;&gt;",'Picks'!$AB$2:$AB$78),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$87,"&lt;&gt;",'Picks'!$AB$2:$AB$87),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$78,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$78,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$87,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$87,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$78,'Picks'!$AM$2:$AM$78,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$87,'Picks'!$AM$2:$AM$87,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +902,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$78,$A14,'Picks'!$U$2:$U$78,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$87,$A14,'Picks'!$U$2:$U$87,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$78,$A14,'Picks'!$U$2:$U$78,"settled",'Picks'!$V$2:$V$78,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$87,$A14,'Picks'!$U$2:$U$87,"settled",'Picks'!$V$2:$V$87,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$78,$A14,'Picks'!$U$2:$U$78,"settled",'Picks'!$V$2:$V$78,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$87,$A14,'Picks'!$U$2:$U$87,"settled",'Picks'!$V$2:$V$87,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +918,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$78,'Picks'!$H$2:$H$78,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$87,'Picks'!$H$2:$H$87,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$78,'Picks'!$H$2:$H$78,$A14,'Picks'!$U$2:$U$78,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$87,'Picks'!$H$2:$H$87,$A14,'Picks'!$U$2:$U$87,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +933,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$78,$A15,'Picks'!$U$2:$U$78,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$87,$A15,'Picks'!$U$2:$U$87,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$78,$A15,'Picks'!$U$2:$U$78,"settled",'Picks'!$V$2:$V$78,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$87,$A15,'Picks'!$U$2:$U$87,"settled",'Picks'!$V$2:$V$87,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$78,$A15,'Picks'!$U$2:$U$78,"settled",'Picks'!$V$2:$V$78,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$87,$A15,'Picks'!$U$2:$U$87,"settled",'Picks'!$V$2:$V$87,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +949,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$78,'Picks'!$H$2:$H$78,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$87,'Picks'!$H$2:$H$87,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$78,'Picks'!$H$2:$H$78,$A15,'Picks'!$U$2:$U$78,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$87,'Picks'!$H$2:$H$87,$A15,'Picks'!$U$2:$U$87,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +964,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$78,$A16,'Picks'!$U$2:$U$78,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$87,$A16,'Picks'!$U$2:$U$87,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$78,$A16,'Picks'!$U$2:$U$78,"settled",'Picks'!$V$2:$V$78,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$87,$A16,'Picks'!$U$2:$U$87,"settled",'Picks'!$V$2:$V$87,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$78,$A16,'Picks'!$U$2:$U$78,"settled",'Picks'!$V$2:$V$78,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$87,$A16,'Picks'!$U$2:$U$87,"settled",'Picks'!$V$2:$V$87,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +980,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$78,'Picks'!$H$2:$H$78,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$87,'Picks'!$H$2:$H$87,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$78,'Picks'!$H$2:$H$78,$A16,'Picks'!$U$2:$U$78,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$87,'Picks'!$H$2:$H$87,$A16,'Picks'!$U$2:$U$87,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ78"/>
+  <dimension ref="A1:CR87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1105,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1560,30 +1562,35 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1875,6 +1882,7 @@
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2162,6 +2170,7 @@
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2449,6 +2458,7 @@
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
+      <c r="CR4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2736,6 +2746,7 @@
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
+      <c r="CR5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3023,6 +3034,7 @@
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
+      <c r="CR6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3286,6 +3298,7 @@
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
+      <c r="CR7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3573,6 +3586,7 @@
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
+      <c r="CR8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3860,6 +3874,7 @@
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
+      <c r="CR9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4147,6 +4162,7 @@
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
+      <c r="CR10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4434,6 +4450,7 @@
       <c r="CO11" s="24" t="n"/>
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4721,6 +4738,7 @@
       <c r="CO12" s="24" t="n"/>
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -5008,6 +5026,7 @@
       <c r="CO13" s="24" t="n"/>
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5295,6 +5314,7 @@
       <c r="CO14" s="24" t="n"/>
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5582,6 +5602,7 @@
       <c r="CO15" s="24" t="n"/>
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5869,6 +5890,7 @@
       <c r="CO16" s="24" t="n"/>
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6156,6 +6178,7 @@
       <c r="CO17" s="24" t="n"/>
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -6443,6 +6466,7 @@
       <c r="CO18" s="24" t="n"/>
       <c r="CP18" s="24" t="n"/>
       <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
@@ -6730,6 +6754,7 @@
       <c r="CO19" s="24" t="n"/>
       <c r="CP19" s="24" t="n"/>
       <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
@@ -7017,6 +7042,7 @@
       <c r="CO20" s="24" t="n"/>
       <c r="CP20" s="24" t="n"/>
       <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
@@ -7304,6 +7330,7 @@
       <c r="CO21" s="24" t="n"/>
       <c r="CP21" s="24" t="n"/>
       <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
@@ -7591,6 +7618,7 @@
       <c r="CO22" s="24" t="n"/>
       <c r="CP22" s="24" t="n"/>
       <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
@@ -7854,6 +7882,7 @@
       <c r="CO23" s="24" t="n"/>
       <c r="CP23" s="24" t="n"/>
       <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
@@ -8141,6 +8170,7 @@
       <c r="CO24" s="24" t="n"/>
       <c r="CP24" s="24" t="n"/>
       <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
@@ -8428,6 +8458,7 @@
       <c r="CO25" s="24" t="n"/>
       <c r="CP25" s="24" t="n"/>
       <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
@@ -8715,6 +8746,7 @@
       <c r="CO26" s="24" t="n"/>
       <c r="CP26" s="24" t="n"/>
       <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="n"/>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
@@ -9002,6 +9034,7 @@
       <c r="CO27" s="24" t="n"/>
       <c r="CP27" s="24" t="n"/>
       <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="n"/>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
@@ -9289,6 +9322,7 @@
       <c r="CO28" s="24" t="n"/>
       <c r="CP28" s="24" t="n"/>
       <c r="CQ28" s="24" t="n"/>
+      <c r="CR28" s="24" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
@@ -9566,6 +9600,7 @@
       <c r="CO29" s="24" t="n"/>
       <c r="CP29" s="24" t="n"/>
       <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="n"/>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
@@ -9853,6 +9888,7 @@
       <c r="CO30" s="24" t="n"/>
       <c r="CP30" s="24" t="n"/>
       <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="n"/>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
@@ -10140,6 +10176,7 @@
       <c r="CO31" s="24" t="n"/>
       <c r="CP31" s="24" t="n"/>
       <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="n"/>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
@@ -10427,6 +10464,7 @@
       <c r="CO32" s="24" t="n"/>
       <c r="CP32" s="24" t="n"/>
       <c r="CQ32" s="24" t="n"/>
+      <c r="CR32" s="24" t="n"/>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
@@ -10704,6 +10742,7 @@
       <c r="CO33" s="24" t="n"/>
       <c r="CP33" s="24" t="n"/>
       <c r="CQ33" s="24" t="n"/>
+      <c r="CR33" s="24" t="n"/>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
@@ -10991,6 +11030,7 @@
       <c r="CO34" s="24" t="n"/>
       <c r="CP34" s="24" t="n"/>
       <c r="CQ34" s="24" t="n"/>
+      <c r="CR34" s="24" t="n"/>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
@@ -11268,6 +11308,7 @@
       <c r="CO35" s="24" t="n"/>
       <c r="CP35" s="24" t="n"/>
       <c r="CQ35" s="24" t="n"/>
+      <c r="CR35" s="24" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
@@ -11555,6 +11596,7 @@
       <c r="CO36" s="24" t="n"/>
       <c r="CP36" s="24" t="n"/>
       <c r="CQ36" s="24" t="n"/>
+      <c r="CR36" s="24" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
@@ -11842,6 +11884,7 @@
       <c r="CO37" s="24" t="n"/>
       <c r="CP37" s="24" t="n"/>
       <c r="CQ37" s="24" t="n"/>
+      <c r="CR37" s="24" t="n"/>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
@@ -12128,7 +12171,8 @@
       <c r="CN38" s="24" t="n"/>
       <c r="CO38" s="24" t="n"/>
       <c r="CP38" s="24" t="n"/>
-      <c r="CQ38" s="24" t="inlineStr">
+      <c r="CQ38" s="24" t="n"/>
+      <c r="CR38" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -12409,7 +12453,8 @@
       <c r="CN39" s="24" t="n"/>
       <c r="CO39" s="24" t="n"/>
       <c r="CP39" s="24" t="n"/>
-      <c r="CQ39" s="24" t="inlineStr">
+      <c r="CQ39" s="24" t="n"/>
+      <c r="CR39" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -12700,7 +12745,8 @@
       <c r="CN40" s="24" t="n"/>
       <c r="CO40" s="24" t="n"/>
       <c r="CP40" s="24" t="n"/>
-      <c r="CQ40" s="24" t="inlineStr">
+      <c r="CQ40" s="24" t="n"/>
+      <c r="CR40" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -12991,7 +13037,8 @@
       <c r="CN41" s="24" t="n"/>
       <c r="CO41" s="24" t="n"/>
       <c r="CP41" s="24" t="n"/>
-      <c r="CQ41" s="24" t="inlineStr">
+      <c r="CQ41" s="24" t="n"/>
+      <c r="CR41" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -13282,7 +13329,8 @@
       <c r="CN42" s="24" t="n"/>
       <c r="CO42" s="24" t="n"/>
       <c r="CP42" s="24" t="n"/>
-      <c r="CQ42" s="24" t="inlineStr">
+      <c r="CQ42" s="24" t="n"/>
+      <c r="CR42" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -13573,7 +13621,8 @@
       <c r="CN43" s="24" t="n"/>
       <c r="CO43" s="24" t="n"/>
       <c r="CP43" s="24" t="n"/>
-      <c r="CQ43" s="24" t="inlineStr">
+      <c r="CQ43" s="24" t="n"/>
+      <c r="CR43" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -13864,7 +13913,8 @@
       <c r="CN44" s="24" t="n"/>
       <c r="CO44" s="24" t="n"/>
       <c r="CP44" s="24" t="n"/>
-      <c r="CQ44" s="24" t="inlineStr">
+      <c r="CQ44" s="24" t="n"/>
+      <c r="CR44" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -14155,7 +14205,8 @@
       <c r="CN45" s="24" t="n"/>
       <c r="CO45" s="24" t="n"/>
       <c r="CP45" s="24" t="n"/>
-      <c r="CQ45" s="24" t="inlineStr">
+      <c r="CQ45" s="24" t="n"/>
+      <c r="CR45" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -14446,7 +14497,8 @@
       <c r="CN46" s="24" t="n"/>
       <c r="CO46" s="24" t="n"/>
       <c r="CP46" s="24" t="n"/>
-      <c r="CQ46" s="24" t="inlineStr">
+      <c r="CQ46" s="24" t="n"/>
+      <c r="CR46" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -14737,7 +14789,8 @@
       <c r="CN47" s="24" t="n"/>
       <c r="CO47" s="24" t="n"/>
       <c r="CP47" s="24" t="n"/>
-      <c r="CQ47" s="24" t="inlineStr">
+      <c r="CQ47" s="24" t="n"/>
+      <c r="CR47" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -15028,7 +15081,8 @@
       <c r="CN48" s="24" t="n"/>
       <c r="CO48" s="24" t="n"/>
       <c r="CP48" s="24" t="n"/>
-      <c r="CQ48" s="24" t="inlineStr">
+      <c r="CQ48" s="24" t="n"/>
+      <c r="CR48" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -15319,7 +15373,8 @@
       <c r="CN49" s="24" t="n"/>
       <c r="CO49" s="24" t="n"/>
       <c r="CP49" s="24" t="n"/>
-      <c r="CQ49" s="24" t="inlineStr">
+      <c r="CQ49" s="24" t="n"/>
+      <c r="CR49" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -15610,7 +15665,8 @@
       <c r="CN50" s="24" t="n"/>
       <c r="CO50" s="24" t="n"/>
       <c r="CP50" s="24" t="n"/>
-      <c r="CQ50" s="24" t="inlineStr">
+      <c r="CQ50" s="24" t="n"/>
+      <c r="CR50" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -15901,7 +15957,8 @@
       <c r="CN51" s="24" t="n"/>
       <c r="CO51" s="24" t="n"/>
       <c r="CP51" s="24" t="n"/>
-      <c r="CQ51" s="24" t="inlineStr">
+      <c r="CQ51" s="24" t="n"/>
+      <c r="CR51" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -16192,7 +16249,8 @@
       <c r="CN52" s="24" t="n"/>
       <c r="CO52" s="24" t="n"/>
       <c r="CP52" s="24" t="n"/>
-      <c r="CQ52" s="24" t="inlineStr">
+      <c r="CQ52" s="24" t="n"/>
+      <c r="CR52" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -16483,7 +16541,8 @@
       <c r="CN53" s="24" t="n"/>
       <c r="CO53" s="24" t="n"/>
       <c r="CP53" s="24" t="n"/>
-      <c r="CQ53" s="24" t="inlineStr">
+      <c r="CQ53" s="24" t="n"/>
+      <c r="CR53" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -16774,7 +16833,8 @@
       <c r="CN54" s="24" t="n"/>
       <c r="CO54" s="24" t="n"/>
       <c r="CP54" s="24" t="n"/>
-      <c r="CQ54" s="24" t="inlineStr">
+      <c r="CQ54" s="24" t="n"/>
+      <c r="CR54" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -17065,7 +17125,8 @@
       <c r="CN55" s="24" t="n"/>
       <c r="CO55" s="24" t="n"/>
       <c r="CP55" s="24" t="n"/>
-      <c r="CQ55" s="24" t="inlineStr">
+      <c r="CQ55" s="24" t="n"/>
+      <c r="CR55" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -17332,7 +17393,8 @@
       <c r="CN56" s="24" t="n"/>
       <c r="CO56" s="24" t="n"/>
       <c r="CP56" s="24" t="n"/>
-      <c r="CQ56" s="24" t="inlineStr">
+      <c r="CQ56" s="24" t="n"/>
+      <c r="CR56" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -17623,7 +17685,8 @@
       <c r="CN57" s="24" t="n"/>
       <c r="CO57" s="24" t="n"/>
       <c r="CP57" s="24" t="n"/>
-      <c r="CQ57" s="24" t="inlineStr">
+      <c r="CQ57" s="24" t="n"/>
+      <c r="CR57" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -17632,12 +17695,12 @@
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>50b6b9d81afe49c5</t>
+          <t>bfe75fb7f86545b1</t>
         </is>
       </c>
       <c r="B58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T05:18:53.002097Z</t>
         </is>
       </c>
       <c r="C58" s="24" t="inlineStr">
@@ -17682,23 +17745,23 @@
         </is>
       </c>
       <c r="L58" s="26" t="n">
-        <v>-133</v>
+        <v>-122</v>
       </c>
       <c r="M58" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.819672</v>
       </c>
       <c r="N58" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.54955</v>
       </c>
       <c r="O58" s="28" t="n">
-        <v>0.527373</v>
+        <v>0.5273600000000001</v>
       </c>
       <c r="P58" s="28" t="n"/>
       <c r="Q58" s="28" t="n">
-        <v>-0.043442</v>
+        <v>-0.02219</v>
       </c>
       <c r="R58" s="26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S58" s="29" t="n">
         <v>1</v>
@@ -17724,7 +17787,7 @@
       <c r="AD58" s="24" t="n"/>
       <c r="AE58" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-g2a-js-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-g2a-js-2026-08-04).</t>
         </is>
       </c>
       <c r="AF58" s="31" t="inlineStr">
@@ -17808,7 +17871,7 @@
       </c>
       <c r="BA58" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
         </is>
       </c>
       <c r="BB58" s="24" t="inlineStr">
@@ -17823,7 +17886,7 @@
       </c>
       <c r="BD58" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
         </is>
       </c>
       <c r="BE58" s="24" t="inlineStr">
@@ -17843,7 +17906,7 @@
       </c>
       <c r="BH58" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:40.172587Z</t>
+          <t>2026-08-04T05:18:19.586314Z</t>
         </is>
       </c>
       <c r="BI58" s="24" t="inlineStr">
@@ -17853,13 +17916,13 @@
       </c>
       <c r="BJ58" s="25" t="n"/>
       <c r="BK58" s="26" t="n">
-        <v>-133</v>
+        <v>-122</v>
       </c>
       <c r="BL58" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.819672</v>
       </c>
       <c r="BM58" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.54955</v>
       </c>
       <c r="BN58" s="28" t="n"/>
       <c r="BO58" s="28" t="n"/>
@@ -17890,7 +17953,8 @@
       <c r="CN58" s="24" t="n"/>
       <c r="CO58" s="24" t="n"/>
       <c r="CP58" s="24" t="n"/>
-      <c r="CQ58" s="24" t="inlineStr">
+      <c r="CQ58" s="24" t="n"/>
+      <c r="CR58" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -17899,12 +17963,12 @@
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>06a10df2e46b4648</t>
+          <t>63db88fad55c495a</t>
         </is>
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T05:18:53.002097Z</t>
         </is>
       </c>
       <c r="C59" s="24" t="inlineStr">
@@ -17949,20 +18013,20 @@
         </is>
       </c>
       <c r="L59" s="26" t="n">
-        <v>-213</v>
+        <v>-223</v>
       </c>
       <c r="M59" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.44843</v>
       </c>
       <c r="N59" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.690402</v>
       </c>
       <c r="O59" s="28" t="n">
-        <v>0.5710730000000001</v>
+        <v>0.571054</v>
       </c>
       <c r="P59" s="28" t="n"/>
       <c r="Q59" s="28" t="n">
-        <v>-0.109438</v>
+        <v>-0.119348</v>
       </c>
       <c r="R59" s="26" t="n">
         <v>0</v>
@@ -17991,7 +18055,7 @@
       <c r="AD59" s="24" t="n"/>
       <c r="AE59" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-ign-sta-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-ign-sta-2026-08-04).</t>
         </is>
       </c>
       <c r="AF59" s="31" t="inlineStr">
@@ -18075,7 +18139,7 @@
       </c>
       <c r="BA59" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
         </is>
       </c>
       <c r="BB59" s="24" t="inlineStr">
@@ -18090,7 +18154,7 @@
       </c>
       <c r="BD59" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>83e1528a9bd51ea902d7704e0b3d24b0db02596c08a56e20e38f9385c7964710</t>
         </is>
       </c>
       <c r="BE59" s="24" t="inlineStr">
@@ -18110,7 +18174,7 @@
       </c>
       <c r="BH59" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:41.826436Z</t>
+          <t>2026-08-04T05:18:20.827862Z</t>
         </is>
       </c>
       <c r="BI59" s="24" t="inlineStr">
@@ -18120,13 +18184,13 @@
       </c>
       <c r="BJ59" s="25" t="n"/>
       <c r="BK59" s="26" t="n">
-        <v>-213</v>
+        <v>-223</v>
       </c>
       <c r="BL59" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.44843</v>
       </c>
       <c r="BM59" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.690402</v>
       </c>
       <c r="BN59" s="28" t="n"/>
       <c r="BO59" s="28" t="n"/>
@@ -18157,7 +18221,8 @@
       <c r="CN59" s="24" t="n"/>
       <c r="CO59" s="24" t="n"/>
       <c r="CP59" s="24" t="n"/>
-      <c r="CQ59" s="24" t="inlineStr">
+      <c r="CQ59" s="24" t="n"/>
+      <c r="CR59" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -18166,12 +18231,12 @@
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>981d1ecf929848d0</t>
+          <t>2a5ef31ba3d7448c</t>
         </is>
       </c>
       <c r="B60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C60" s="24" t="inlineStr">
@@ -18225,11 +18290,11 @@
         <v>0.5594710000000001</v>
       </c>
       <c r="O60" s="28" t="n">
-        <v>0.513213</v>
+        <v>0.513199</v>
       </c>
       <c r="P60" s="28" t="n"/>
       <c r="Q60" s="28" t="n">
-        <v>-0.046258</v>
+        <v>-0.046272</v>
       </c>
       <c r="R60" s="26" t="n">
         <v>0</v>
@@ -18342,7 +18407,7 @@
       </c>
       <c r="BA60" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB60" s="24" t="inlineStr">
@@ -18357,7 +18422,7 @@
       </c>
       <c r="BD60" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE60" s="24" t="inlineStr">
@@ -18377,7 +18442,7 @@
       </c>
       <c r="BH60" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:43.358031Z</t>
+          <t>2026-08-04T08:56:24.175897Z</t>
         </is>
       </c>
       <c r="BI60" s="24" t="inlineStr">
@@ -18424,7 +18489,8 @@
       <c r="CN60" s="24" t="n"/>
       <c r="CO60" s="24" t="n"/>
       <c r="CP60" s="24" t="n"/>
-      <c r="CQ60" s="24" t="inlineStr">
+      <c r="CQ60" s="24" t="n"/>
+      <c r="CR60" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -18433,12 +18499,12 @@
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>0f2a33e6c8d5405f</t>
+          <t>5a02f7db72834d1f</t>
         </is>
       </c>
       <c r="B61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C61" s="24" t="inlineStr">
@@ -18448,7 +18514,7 @@
       </c>
       <c r="D61" s="24" t="inlineStr">
         <is>
-          <t>68301</t>
+          <t>68302</t>
         </is>
       </c>
       <c r="E61" s="24" t="inlineStr">
@@ -18458,12 +18524,12 @@
       </c>
       <c r="F61" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Phantom</t>
         </is>
       </c>
       <c r="G61" s="24" t="inlineStr">
         <is>
-          <t>PCH3LK1N Club</t>
+          <t>Sashi Esport</t>
         </is>
       </c>
       <c r="H61" s="24" t="inlineStr">
@@ -18483,23 +18549,23 @@
         </is>
       </c>
       <c r="L61" s="26" t="n">
-        <v>-122</v>
+        <v>104</v>
       </c>
       <c r="M61" s="27" t="n">
-        <v>1.819672</v>
+        <v>2.04</v>
       </c>
       <c r="N61" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.490196</v>
       </c>
       <c r="O61" s="28" t="n">
-        <v>0.527048</v>
+        <v>0.551011</v>
       </c>
       <c r="P61" s="28" t="n"/>
       <c r="Q61" s="28" t="n">
-        <v>-0.022502</v>
+        <v>0.060815</v>
       </c>
       <c r="R61" s="26" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="S61" s="29" t="n">
         <v>1</v>
@@ -18525,7 +18591,7 @@
       <c r="AD61" s="24" t="n"/>
       <c r="AE61" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-plnc-scn-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-cs2-sashi-pha-2026-08-04).</t>
         </is>
       </c>
       <c r="AF61" s="31" t="inlineStr">
@@ -18543,7 +18609,7 @@
       <c r="AJ61" s="31" t="n"/>
       <c r="AK61" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL61" s="26" t="n">
@@ -18551,47 +18617,47 @@
       </c>
       <c r="AM61" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN61" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO61" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP61" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Phantom</t>
         </is>
       </c>
       <c r="AQ61" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Phantom</t>
         </is>
       </c>
       <c r="AR61" s="24" t="inlineStr">
         <is>
-          <t>SNAILKICK Club</t>
+          <t>Phantom</t>
         </is>
       </c>
       <c r="AS61" s="24" t="inlineStr">
         <is>
-          <t>PCH3LK1N Club</t>
+          <t>Sashi Esport</t>
         </is>
       </c>
       <c r="AT61" s="24" t="inlineStr">
         <is>
-          <t>PCH3LK1N Club</t>
+          <t>Sashi Esport</t>
         </is>
       </c>
       <c r="AU61" s="24" t="inlineStr">
         <is>
-          <t>PCH3LK1N Club</t>
+          <t>Sashi Esport</t>
         </is>
       </c>
       <c r="AV61" s="24" t="n"/>
@@ -18609,7 +18675,7 @@
       </c>
       <c r="BA61" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB61" s="24" t="inlineStr">
@@ -18624,7 +18690,7 @@
       </c>
       <c r="BD61" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE61" s="24" t="inlineStr">
@@ -18644,7 +18710,7 @@
       </c>
       <c r="BH61" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:44.338654Z</t>
+          <t>2026-08-04T08:56:24.737438Z</t>
         </is>
       </c>
       <c r="BI61" s="24" t="inlineStr">
@@ -18654,13 +18720,13 @@
       </c>
       <c r="BJ61" s="25" t="n"/>
       <c r="BK61" s="26" t="n">
-        <v>-122</v>
+        <v>104</v>
       </c>
       <c r="BL61" s="27" t="n">
-        <v>1.819672</v>
+        <v>2.04</v>
       </c>
       <c r="BM61" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.490196</v>
       </c>
       <c r="BN61" s="28" t="n"/>
       <c r="BO61" s="28" t="n"/>
@@ -18691,21 +18757,22 @@
       <c r="CN61" s="24" t="n"/>
       <c r="CO61" s="24" t="n"/>
       <c r="CP61" s="24" t="n"/>
-      <c r="CQ61" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CQ61" s="24" t="n"/>
+      <c r="CR61" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="24" t="inlineStr">
         <is>
-          <t>86667891fd994fee</t>
+          <t>cb7f1fae514b4028</t>
         </is>
       </c>
       <c r="B62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C62" s="24" t="inlineStr">
@@ -18715,7 +18782,7 @@
       </c>
       <c r="D62" s="24" t="inlineStr">
         <is>
-          <t>68302</t>
+          <t>68301</t>
         </is>
       </c>
       <c r="E62" s="24" t="inlineStr">
@@ -18725,12 +18792,12 @@
       </c>
       <c r="F62" s="24" t="inlineStr">
         <is>
-          <t>Phantom</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="G62" s="24" t="inlineStr">
         <is>
-          <t>Sashi Esport</t>
+          <t>PCH3LK1N Club</t>
         </is>
       </c>
       <c r="H62" s="24" t="inlineStr">
@@ -18750,23 +18817,23 @@
         </is>
       </c>
       <c r="L62" s="26" t="n">
-        <v>117</v>
+        <v>-113</v>
       </c>
       <c r="M62" s="27" t="n">
-        <v>2.17</v>
+        <v>1.884956</v>
       </c>
       <c r="N62" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.530516</v>
       </c>
       <c r="O62" s="28" t="n">
-        <v>0.551006</v>
+        <v>0.527057</v>
       </c>
       <c r="P62" s="28" t="n"/>
       <c r="Q62" s="28" t="n">
-        <v>0.09017699999999999</v>
+        <v>-0.003459</v>
       </c>
       <c r="R62" s="26" t="n">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="S62" s="29" t="n">
         <v>1</v>
@@ -18792,7 +18859,7 @@
       <c r="AD62" s="24" t="n"/>
       <c r="AE62" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-sashi-pha-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-cs2-plnc-scn-2026-08-04).</t>
         </is>
       </c>
       <c r="AF62" s="31" t="inlineStr">
@@ -18810,7 +18877,7 @@
       <c r="AJ62" s="31" t="n"/>
       <c r="AK62" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL62" s="26" t="n">
@@ -18818,47 +18885,47 @@
       </c>
       <c r="AM62" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN62" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO62" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP62" s="24" t="inlineStr">
         <is>
-          <t>Phantom</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AQ62" s="24" t="inlineStr">
         <is>
-          <t>Phantom</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AR62" s="24" t="inlineStr">
         <is>
-          <t>Phantom</t>
+          <t>SNAILKICK Club</t>
         </is>
       </c>
       <c r="AS62" s="24" t="inlineStr">
         <is>
-          <t>Sashi Esport</t>
+          <t>PCH3LK1N Club</t>
         </is>
       </c>
       <c r="AT62" s="24" t="inlineStr">
         <is>
-          <t>Sashi Esport</t>
+          <t>PCH3LK1N Club</t>
         </is>
       </c>
       <c r="AU62" s="24" t="inlineStr">
         <is>
-          <t>Sashi Esport</t>
+          <t>PCH3LK1N Club</t>
         </is>
       </c>
       <c r="AV62" s="24" t="n"/>
@@ -18876,7 +18943,7 @@
       </c>
       <c r="BA62" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB62" s="24" t="inlineStr">
@@ -18891,7 +18958,7 @@
       </c>
       <c r="BD62" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE62" s="24" t="inlineStr">
@@ -18911,7 +18978,7 @@
       </c>
       <c r="BH62" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:44.822978Z</t>
+          <t>2026-08-04T08:56:25.426369Z</t>
         </is>
       </c>
       <c r="BI62" s="24" t="inlineStr">
@@ -18921,13 +18988,13 @@
       </c>
       <c r="BJ62" s="25" t="n"/>
       <c r="BK62" s="26" t="n">
-        <v>117</v>
+        <v>-113</v>
       </c>
       <c r="BL62" s="27" t="n">
-        <v>2.17</v>
+        <v>1.884956</v>
       </c>
       <c r="BM62" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.530516</v>
       </c>
       <c r="BN62" s="28" t="n"/>
       <c r="BO62" s="28" t="n"/>
@@ -18958,21 +19025,22 @@
       <c r="CN62" s="24" t="n"/>
       <c r="CO62" s="24" t="n"/>
       <c r="CP62" s="24" t="n"/>
-      <c r="CQ62" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CQ62" s="24" t="n"/>
+      <c r="CR62" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>ed5311480f944717</t>
+          <t>fe5f1ab4ae674f3c</t>
         </is>
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
@@ -19026,11 +19094,11 @@
         <v>0.579832</v>
       </c>
       <c r="O63" s="28" t="n">
-        <v>0.691599</v>
+        <v>0.691594</v>
       </c>
       <c r="P63" s="28" t="n"/>
       <c r="Q63" s="28" t="n">
-        <v>0.111767</v>
+        <v>0.111762</v>
       </c>
       <c r="R63" s="26" t="n">
         <v>76</v>
@@ -19143,7 +19211,7 @@
       </c>
       <c r="BA63" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB63" s="24" t="inlineStr">
@@ -19158,7 +19226,7 @@
       </c>
       <c r="BD63" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE63" s="24" t="inlineStr">
@@ -19178,7 +19246,7 @@
       </c>
       <c r="BH63" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:45.360175Z</t>
+          <t>2026-08-04T08:56:25.971824Z</t>
         </is>
       </c>
       <c r="BI63" s="24" t="inlineStr">
@@ -19225,7 +19293,8 @@
       <c r="CN63" s="24" t="n"/>
       <c r="CO63" s="24" t="n"/>
       <c r="CP63" s="24" t="n"/>
-      <c r="CQ63" s="24" t="inlineStr">
+      <c r="CQ63" s="24" t="n"/>
+      <c r="CR63" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -19234,12 +19303,12 @@
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>7418210f9810457b</t>
+          <t>99b6896bb4514386</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
@@ -19284,20 +19353,20 @@
         </is>
       </c>
       <c r="L64" s="26" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="M64" s="27" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="N64" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.490196</v>
       </c>
       <c r="O64" s="28" t="n">
-        <v>0.7195859999999999</v>
+        <v>0.719577</v>
       </c>
       <c r="P64" s="28" t="n"/>
       <c r="Q64" s="28" t="n">
-        <v>0.258757</v>
+        <v>0.229381</v>
       </c>
       <c r="R64" s="26" t="n">
         <v>100</v>
@@ -19326,7 +19395,7 @@
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4600 (market_slug=aec-cs2-bw-leo-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-cs2-bw-leo-2026-08-04).</t>
         </is>
       </c>
       <c r="AF64" s="31" t="inlineStr">
@@ -19410,7 +19479,7 @@
       </c>
       <c r="BA64" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB64" s="24" t="inlineStr">
@@ -19425,7 +19494,7 @@
       </c>
       <c r="BD64" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE64" s="24" t="inlineStr">
@@ -19445,7 +19514,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:46.394598Z</t>
+          <t>2026-08-04T08:56:27.119976Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -19455,13 +19524,13 @@
       </c>
       <c r="BJ64" s="25" t="n"/>
       <c r="BK64" s="26" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="BL64" s="27" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="BM64" s="28" t="n">
-        <v>0.460829</v>
+        <v>0.490196</v>
       </c>
       <c r="BN64" s="28" t="n"/>
       <c r="BO64" s="28" t="n"/>
@@ -19492,7 +19561,8 @@
       <c r="CN64" s="24" t="n"/>
       <c r="CO64" s="24" t="n"/>
       <c r="CP64" s="24" t="n"/>
-      <c r="CQ64" s="24" t="inlineStr">
+      <c r="CQ64" s="24" t="n"/>
+      <c r="CR64" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -19501,12 +19571,12 @@
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>80a69293f56842c4</t>
+          <t>01b9fb5a4ee449d0</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
@@ -19551,23 +19621,23 @@
         </is>
       </c>
       <c r="L65" s="26" t="n">
-        <v>-186</v>
+        <v>-203</v>
       </c>
       <c r="M65" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.492611</v>
       </c>
       <c r="N65" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.669967</v>
       </c>
       <c r="O65" s="28" t="n">
-        <v>0.640949</v>
+        <v>0.640948</v>
       </c>
       <c r="P65" s="28" t="n"/>
       <c r="Q65" s="28" t="n">
-        <v>-0.009401</v>
+        <v>-0.029019</v>
       </c>
       <c r="R65" s="26" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="S65" s="29" t="n">
         <v>1.5</v>
@@ -19593,7 +19663,7 @@
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6500 (market_slug=aec-cs2-bmb-exmana-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-bmb-exmana-2026-08-04).</t>
         </is>
       </c>
       <c r="AF65" s="31" t="inlineStr">
@@ -19677,7 +19747,7 @@
       </c>
       <c r="BA65" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB65" s="24" t="inlineStr">
@@ -19692,7 +19762,7 @@
       </c>
       <c r="BD65" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE65" s="24" t="inlineStr">
@@ -19712,7 +19782,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:46.894304Z</t>
+          <t>2026-08-04T08:56:27.768400Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -19722,13 +19792,13 @@
       </c>
       <c r="BJ65" s="25" t="n"/>
       <c r="BK65" s="26" t="n">
-        <v>-186</v>
+        <v>-203</v>
       </c>
       <c r="BL65" s="27" t="n">
-        <v>1.537634</v>
+        <v>1.492611</v>
       </c>
       <c r="BM65" s="28" t="n">
-        <v>0.65035</v>
+        <v>0.669967</v>
       </c>
       <c r="BN65" s="28" t="n"/>
       <c r="BO65" s="28" t="n"/>
@@ -19759,7 +19829,8 @@
       <c r="CN65" s="24" t="n"/>
       <c r="CO65" s="24" t="n"/>
       <c r="CP65" s="24" t="n"/>
-      <c r="CQ65" s="24" t="inlineStr">
+      <c r="CQ65" s="24" t="n"/>
+      <c r="CR65" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -19768,12 +19839,12 @@
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>742f0bc43f68478d</t>
+          <t>5bf1ae41f31a473a</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
@@ -19818,23 +19889,23 @@
         </is>
       </c>
       <c r="L66" s="26" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="M66" s="27" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="N66" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.390625</v>
       </c>
       <c r="O66" s="28" t="n">
-        <v>0.527048</v>
+        <v>0.527057</v>
       </c>
       <c r="P66" s="28" t="n"/>
       <c r="Q66" s="28" t="n">
-        <v>0.076598</v>
+        <v>0.136432</v>
       </c>
       <c r="R66" s="26" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="S66" s="29" t="n">
         <v>1</v>
@@ -19860,7 +19931,7 @@
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-cs2-plnc-wco-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-cs2-plnc-wco-2026-08-04).</t>
         </is>
       </c>
       <c r="AF66" s="31" t="inlineStr">
@@ -19944,7 +20015,7 @@
       </c>
       <c r="BA66" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB66" s="24" t="inlineStr">
@@ -19959,7 +20030,7 @@
       </c>
       <c r="BD66" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE66" s="24" t="inlineStr">
@@ -19979,7 +20050,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:47.380226Z</t>
+          <t>2026-08-04T08:56:28.310332Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -19989,13 +20060,13 @@
       </c>
       <c r="BJ66" s="25" t="n"/>
       <c r="BK66" s="26" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="BL66" s="27" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="BM66" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.390625</v>
       </c>
       <c r="BN66" s="28" t="n"/>
       <c r="BO66" s="28" t="n"/>
@@ -20026,7 +20097,8 @@
       <c r="CN66" s="24" t="n"/>
       <c r="CO66" s="24" t="n"/>
       <c r="CP66" s="24" t="n"/>
-      <c r="CQ66" s="24" t="inlineStr">
+      <c r="CQ66" s="24" t="n"/>
+      <c r="CR66" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -20035,12 +20107,12 @@
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>5e479050a5c8466b</t>
+          <t>e2d0b33be84e4f12</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
@@ -20050,7 +20122,7 @@
       </c>
       <c r="D67" s="24" t="inlineStr">
         <is>
-          <t>68437</t>
+          <t>71318</t>
         </is>
       </c>
       <c r="E67" s="24" t="inlineStr">
@@ -20060,12 +20132,12 @@
       </c>
       <c r="F67" s="24" t="inlineStr">
         <is>
-          <t>GenOne</t>
+          <t>9INE</t>
         </is>
       </c>
       <c r="G67" s="24" t="inlineStr">
         <is>
-          <t>Nemiga</t>
+          <t>Liquid</t>
         </is>
       </c>
       <c r="H67" s="24" t="inlineStr">
@@ -20085,26 +20157,26 @@
         </is>
       </c>
       <c r="L67" s="26" t="n">
-        <v>-163</v>
+        <v>-233</v>
       </c>
       <c r="M67" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.429185</v>
       </c>
       <c r="N67" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.6997</v>
       </c>
       <c r="O67" s="28" t="n">
-        <v>0.518055</v>
+        <v>0.689596</v>
       </c>
       <c r="P67" s="28" t="n"/>
       <c r="Q67" s="28" t="n">
-        <v>-0.101717</v>
+        <v>-0.010104</v>
       </c>
       <c r="R67" s="26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S67" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T67" s="24" t="inlineStr">
         <is>
@@ -20127,7 +20199,7 @@
       <c r="AD67" s="24" t="n"/>
       <c r="AE67" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-nemi-g1-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-cs2-tl-9ine-2026-08-04).</t>
         </is>
       </c>
       <c r="AF67" s="31" t="inlineStr">
@@ -20168,32 +20240,32 @@
       </c>
       <c r="AP67" s="24" t="inlineStr">
         <is>
-          <t>GenOne</t>
+          <t>9INE</t>
         </is>
       </c>
       <c r="AQ67" s="24" t="inlineStr">
         <is>
-          <t>GenOne</t>
+          <t>9INE</t>
         </is>
       </c>
       <c r="AR67" s="24" t="inlineStr">
         <is>
-          <t>GenOne</t>
+          <t>9INE</t>
         </is>
       </c>
       <c r="AS67" s="24" t="inlineStr">
         <is>
-          <t>Nemiga</t>
+          <t>Liquid</t>
         </is>
       </c>
       <c r="AT67" s="24" t="inlineStr">
         <is>
-          <t>Nemiga</t>
+          <t>Liquid</t>
         </is>
       </c>
       <c r="AU67" s="24" t="inlineStr">
         <is>
-          <t>Nemiga</t>
+          <t>Liquid</t>
         </is>
       </c>
       <c r="AV67" s="24" t="n"/>
@@ -20211,7 +20283,7 @@
       </c>
       <c r="BA67" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB67" s="24" t="inlineStr">
@@ -20226,7 +20298,7 @@
       </c>
       <c r="BD67" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE67" s="24" t="inlineStr">
@@ -20246,7 +20318,7 @@
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:48.847552Z</t>
+          <t>2026-08-04T08:56:29.177358Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -20256,13 +20328,13 @@
       </c>
       <c r="BJ67" s="25" t="n"/>
       <c r="BK67" s="26" t="n">
-        <v>-163</v>
+        <v>-233</v>
       </c>
       <c r="BL67" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.429185</v>
       </c>
       <c r="BM67" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.6997</v>
       </c>
       <c r="BN67" s="28" t="n"/>
       <c r="BO67" s="28" t="n"/>
@@ -20293,7 +20365,8 @@
       <c r="CN67" s="24" t="n"/>
       <c r="CO67" s="24" t="n"/>
       <c r="CP67" s="24" t="n"/>
-      <c r="CQ67" s="24" t="inlineStr">
+      <c r="CQ67" s="24" t="n"/>
+      <c r="CR67" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -20302,12 +20375,12 @@
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
         <is>
-          <t>976705aa3abc4300</t>
+          <t>923a61f8a41e4ffa</t>
         </is>
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
@@ -20317,7 +20390,7 @@
       </c>
       <c r="D68" s="24" t="inlineStr">
         <is>
-          <t>71319</t>
+          <t>68437</t>
         </is>
       </c>
       <c r="E68" s="24" t="inlineStr">
@@ -20327,12 +20400,12 @@
       </c>
       <c r="F68" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>GenOne</t>
         </is>
       </c>
       <c r="G68" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>Nemiga</t>
         </is>
       </c>
       <c r="H68" s="24" t="inlineStr">
@@ -20352,20 +20425,20 @@
         </is>
       </c>
       <c r="L68" s="26" t="n">
-        <v>-178</v>
+        <v>-163</v>
       </c>
       <c r="M68" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.613497</v>
       </c>
       <c r="N68" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.619772</v>
       </c>
       <c r="O68" s="28" t="n">
-        <v>0.505162</v>
+        <v>0.518066</v>
       </c>
       <c r="P68" s="28" t="n"/>
       <c r="Q68" s="28" t="n">
-        <v>-0.135126</v>
+        <v>-0.101706</v>
       </c>
       <c r="R68" s="26" t="n">
         <v>0</v>
@@ -20394,7 +20467,7 @@
       <c r="AD68" s="24" t="n"/>
       <c r="AE68" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-cs2-jpu-enjoy-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-nemi-g1-2026-08-04).</t>
         </is>
       </c>
       <c r="AF68" s="31" t="inlineStr">
@@ -20435,32 +20508,32 @@
       </c>
       <c r="AP68" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>GenOne</t>
         </is>
       </c>
       <c r="AQ68" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>GenOne</t>
         </is>
       </c>
       <c r="AR68" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>GenOne</t>
         </is>
       </c>
       <c r="AS68" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>Nemiga</t>
         </is>
       </c>
       <c r="AT68" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>Nemiga</t>
         </is>
       </c>
       <c r="AU68" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>Nemiga</t>
         </is>
       </c>
       <c r="AV68" s="24" t="n"/>
@@ -20478,7 +20551,7 @@
       </c>
       <c r="BA68" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB68" s="24" t="inlineStr">
@@ -20493,7 +20566,7 @@
       </c>
       <c r="BD68" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE68" s="24" t="inlineStr">
@@ -20513,7 +20586,7 @@
       </c>
       <c r="BH68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:49.316034Z</t>
+          <t>2026-08-04T08:56:30.455227Z</t>
         </is>
       </c>
       <c r="BI68" s="24" t="inlineStr">
@@ -20523,13 +20596,13 @@
       </c>
       <c r="BJ68" s="25" t="n"/>
       <c r="BK68" s="26" t="n">
-        <v>-178</v>
+        <v>-163</v>
       </c>
       <c r="BL68" s="27" t="n">
-        <v>1.561798</v>
+        <v>1.613497</v>
       </c>
       <c r="BM68" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.619772</v>
       </c>
       <c r="BN68" s="28" t="n"/>
       <c r="BO68" s="28" t="n"/>
@@ -20560,7 +20633,8 @@
       <c r="CN68" s="24" t="n"/>
       <c r="CO68" s="24" t="n"/>
       <c r="CP68" s="24" t="n"/>
-      <c r="CQ68" s="24" t="inlineStr">
+      <c r="CQ68" s="24" t="n"/>
+      <c r="CR68" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -20569,22 +20643,22 @@
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>cb669fcd43774567</t>
+          <t>75a14d1764b04b86</t>
         </is>
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T16:30:00Z</t>
+          <t>2026-08-04T14:00:00Z</t>
         </is>
       </c>
       <c r="D69" s="24" t="inlineStr">
         <is>
-          <t>68562</t>
+          <t>71319</t>
         </is>
       </c>
       <c r="E69" s="24" t="inlineStr">
@@ -20594,12 +20668,12 @@
       </c>
       <c r="F69" s="24" t="inlineStr">
         <is>
-          <t>WorldEdit Club</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="G69" s="24" t="inlineStr">
         <is>
-          <t>shoke Club</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="H69" s="24" t="inlineStr">
@@ -20619,23 +20693,23 @@
         </is>
       </c>
       <c r="L69" s="26" t="n">
-        <v>133</v>
+        <v>-170</v>
       </c>
       <c r="M69" s="27" t="n">
-        <v>2.33</v>
+        <v>1.588235</v>
       </c>
       <c r="N69" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.62963</v>
       </c>
       <c r="O69" s="28" t="n">
-        <v>0.527048</v>
+        <v>0.505173</v>
       </c>
       <c r="P69" s="28" t="n"/>
       <c r="Q69" s="28" t="n">
-        <v>0.09786300000000001</v>
+        <v>-0.124457</v>
       </c>
       <c r="R69" s="26" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="S69" s="29" t="n">
         <v>1</v>
@@ -20661,7 +20735,7 @@
       <c r="AD69" s="24" t="n"/>
       <c r="AE69" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-cs2-sch-wco-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-jpu-enjoy-2026-08-04).</t>
         </is>
       </c>
       <c r="AF69" s="31" t="inlineStr">
@@ -20697,37 +20771,37 @@
       </c>
       <c r="AO69" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP69" s="24" t="inlineStr">
         <is>
-          <t>WorldEdit Club</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AQ69" s="24" t="inlineStr">
         <is>
-          <t>WorldEdit Club</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AR69" s="24" t="inlineStr">
         <is>
-          <t>WorldEdit Club</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AS69" s="24" t="inlineStr">
         <is>
-          <t>shoke Club</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AT69" s="24" t="inlineStr">
         <is>
-          <t>shoke Club</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AU69" s="24" t="inlineStr">
         <is>
-          <t>shoke Club</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AV69" s="24" t="n"/>
@@ -20745,7 +20819,7 @@
       </c>
       <c r="BA69" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB69" s="24" t="inlineStr">
@@ -20760,7 +20834,7 @@
       </c>
       <c r="BD69" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE69" s="24" t="inlineStr">
@@ -20780,7 +20854,7 @@
       </c>
       <c r="BH69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:49.840183Z</t>
+          <t>2026-08-04T08:56:31.204261Z</t>
         </is>
       </c>
       <c r="BI69" s="24" t="inlineStr">
@@ -20790,13 +20864,13 @@
       </c>
       <c r="BJ69" s="25" t="n"/>
       <c r="BK69" s="26" t="n">
-        <v>133</v>
+        <v>-170</v>
       </c>
       <c r="BL69" s="27" t="n">
-        <v>2.33</v>
+        <v>1.588235</v>
       </c>
       <c r="BM69" s="28" t="n">
-        <v>0.429185</v>
+        <v>0.62963</v>
       </c>
       <c r="BN69" s="28" t="n"/>
       <c r="BO69" s="28" t="n"/>
@@ -20827,21 +20901,22 @@
       <c r="CN69" s="24" t="n"/>
       <c r="CO69" s="24" t="n"/>
       <c r="CP69" s="24" t="n"/>
-      <c r="CQ69" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CQ69" s="24" t="n"/>
+      <c r="CR69" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>6058998addc64392</t>
+          <t>5403069b65de4474</t>
         </is>
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
@@ -20851,7 +20926,7 @@
       </c>
       <c r="D70" s="24" t="inlineStr">
         <is>
-          <t>68563</t>
+          <t>68562</t>
         </is>
       </c>
       <c r="E70" s="24" t="inlineStr">
@@ -20861,12 +20936,12 @@
       </c>
       <c r="F70" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>WorldEdit Club</t>
         </is>
       </c>
       <c r="G70" s="24" t="inlineStr">
         <is>
-          <t>Buster Club</t>
+          <t>shoke Club</t>
         </is>
       </c>
       <c r="H70" s="24" t="inlineStr">
@@ -20886,23 +20961,23 @@
         </is>
       </c>
       <c r="L70" s="26" t="n">
-        <v>144</v>
+        <v>-170</v>
       </c>
       <c r="M70" s="27" t="n">
-        <v>2.44</v>
+        <v>1.588235</v>
       </c>
       <c r="N70" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.62963</v>
       </c>
       <c r="O70" s="28" t="n">
-        <v>0.527048</v>
+        <v>0.527057</v>
       </c>
       <c r="P70" s="28" t="n"/>
       <c r="Q70" s="28" t="n">
-        <v>0.117212</v>
+        <v>-0.102573</v>
       </c>
       <c r="R70" s="26" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="S70" s="29" t="n">
         <v>1</v>
@@ -20928,7 +21003,7 @@
       <c r="AD70" s="24" t="n"/>
       <c r="AE70" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-cs2-bcu-rce-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-sch-wco-2026-08-04).</t>
         </is>
       </c>
       <c r="AF70" s="31" t="inlineStr">
@@ -20969,32 +21044,32 @@
       </c>
       <c r="AP70" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>WorldEdit Club</t>
         </is>
       </c>
       <c r="AQ70" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>WorldEdit Club</t>
         </is>
       </c>
       <c r="AR70" s="24" t="inlineStr">
         <is>
-          <t>Recrent Club</t>
+          <t>WorldEdit Club</t>
         </is>
       </c>
       <c r="AS70" s="24" t="inlineStr">
         <is>
-          <t>Buster Club</t>
+          <t>shoke Club</t>
         </is>
       </c>
       <c r="AT70" s="24" t="inlineStr">
         <is>
-          <t>Buster Club</t>
+          <t>shoke Club</t>
         </is>
       </c>
       <c r="AU70" s="24" t="inlineStr">
         <is>
-          <t>Buster Club</t>
+          <t>shoke Club</t>
         </is>
       </c>
       <c r="AV70" s="24" t="n"/>
@@ -21012,7 +21087,7 @@
       </c>
       <c r="BA70" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB70" s="24" t="inlineStr">
@@ -21027,7 +21102,7 @@
       </c>
       <c r="BD70" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE70" s="24" t="inlineStr">
@@ -21047,7 +21122,7 @@
       </c>
       <c r="BH70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:50.331445Z</t>
+          <t>2026-08-04T08:56:31.835843Z</t>
         </is>
       </c>
       <c r="BI70" s="24" t="inlineStr">
@@ -21057,13 +21132,13 @@
       </c>
       <c r="BJ70" s="25" t="n"/>
       <c r="BK70" s="26" t="n">
-        <v>144</v>
+        <v>-170</v>
       </c>
       <c r="BL70" s="27" t="n">
-        <v>2.44</v>
+        <v>1.588235</v>
       </c>
       <c r="BM70" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.62963</v>
       </c>
       <c r="BN70" s="28" t="n"/>
       <c r="BO70" s="28" t="n"/>
@@ -21094,31 +21169,32 @@
       <c r="CN70" s="24" t="n"/>
       <c r="CO70" s="24" t="n"/>
       <c r="CP70" s="24" t="n"/>
-      <c r="CQ70" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CQ70" s="24" t="n"/>
+      <c r="CR70" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>4c303a31b6a242a0</t>
+          <t>26906cebafaa4543</t>
         </is>
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T17:00:00Z</t>
+          <t>2026-08-04T16:30:00Z</t>
         </is>
       </c>
       <c r="D71" s="24" t="inlineStr">
         <is>
-          <t>68565</t>
+          <t>68563</t>
         </is>
       </c>
       <c r="E71" s="24" t="inlineStr">
@@ -21128,12 +21204,12 @@
       </c>
       <c r="F71" s="24" t="inlineStr">
         <is>
-          <t>ALKA GAMING</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="G71" s="24" t="inlineStr">
         <is>
-          <t>UNO MILLE</t>
+          <t>Buster Club</t>
         </is>
       </c>
       <c r="H71" s="24" t="inlineStr">
@@ -21153,26 +21229,26 @@
         </is>
       </c>
       <c r="L71" s="26" t="n">
-        <v>-213</v>
+        <v>-133</v>
       </c>
       <c r="M71" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.75188</v>
       </c>
       <c r="N71" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.570815</v>
       </c>
       <c r="O71" s="28" t="n">
-        <v>0.589568</v>
+        <v>0.527057</v>
       </c>
       <c r="P71" s="28" t="n"/>
       <c r="Q71" s="28" t="n">
-        <v>-0.090943</v>
+        <v>-0.043758</v>
       </c>
       <c r="R71" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S71" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T71" s="24" t="inlineStr">
         <is>
@@ -21195,7 +21271,7 @@
       <c r="AD71" s="24" t="n"/>
       <c r="AE71" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-uno-alka-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-bcu-rce-2026-08-04).</t>
         </is>
       </c>
       <c r="AF71" s="31" t="inlineStr">
@@ -21231,37 +21307,37 @@
       </c>
       <c r="AO71" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP71" s="24" t="inlineStr">
         <is>
-          <t>ALKA GAMING</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AQ71" s="24" t="inlineStr">
         <is>
-          <t>ALKA GAMING</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AR71" s="24" t="inlineStr">
         <is>
-          <t>ALKA GAMING</t>
+          <t>Recrent Club</t>
         </is>
       </c>
       <c r="AS71" s="24" t="inlineStr">
         <is>
-          <t>UNO MILLE</t>
+          <t>Buster Club</t>
         </is>
       </c>
       <c r="AT71" s="24" t="inlineStr">
         <is>
-          <t>UNO MILLE</t>
+          <t>Buster Club</t>
         </is>
       </c>
       <c r="AU71" s="24" t="inlineStr">
         <is>
-          <t>UNO MILLE</t>
+          <t>Buster Club</t>
         </is>
       </c>
       <c r="AV71" s="24" t="n"/>
@@ -21279,7 +21355,7 @@
       </c>
       <c r="BA71" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB71" s="24" t="inlineStr">
@@ -21294,7 +21370,7 @@
       </c>
       <c r="BD71" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE71" s="24" t="inlineStr">
@@ -21314,7 +21390,7 @@
       </c>
       <c r="BH71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:51.858945Z</t>
+          <t>2026-08-04T08:56:32.634716Z</t>
         </is>
       </c>
       <c r="BI71" s="24" t="inlineStr">
@@ -21324,13 +21400,13 @@
       </c>
       <c r="BJ71" s="25" t="n"/>
       <c r="BK71" s="26" t="n">
-        <v>-213</v>
+        <v>-133</v>
       </c>
       <c r="BL71" s="27" t="n">
-        <v>1.469484</v>
+        <v>1.75188</v>
       </c>
       <c r="BM71" s="28" t="n">
-        <v>0.680511</v>
+        <v>0.570815</v>
       </c>
       <c r="BN71" s="28" t="n"/>
       <c r="BO71" s="28" t="n"/>
@@ -21361,7 +21437,8 @@
       <c r="CN71" s="24" t="n"/>
       <c r="CO71" s="24" t="n"/>
       <c r="CP71" s="24" t="n"/>
-      <c r="CQ71" s="24" t="inlineStr">
+      <c r="CQ71" s="24" t="n"/>
+      <c r="CR71" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -21370,12 +21447,12 @@
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
         <is>
-          <t>4ec801effa1f4e1a</t>
+          <t>c81385dbdf9b4700</t>
         </is>
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C72" s="24" t="inlineStr">
@@ -21385,7 +21462,7 @@
       </c>
       <c r="D72" s="24" t="inlineStr">
         <is>
-          <t>68567</t>
+          <t>68565</t>
         </is>
       </c>
       <c r="E72" s="24" t="inlineStr">
@@ -21395,12 +21472,12 @@
       </c>
       <c r="F72" s="24" t="inlineStr">
         <is>
-          <t>INOX Division</t>
+          <t>ALKA GAMING</t>
         </is>
       </c>
       <c r="G72" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire</t>
+          <t>UNO MILLE</t>
         </is>
       </c>
       <c r="H72" s="24" t="inlineStr">
@@ -21420,26 +21497,26 @@
         </is>
       </c>
       <c r="L72" s="26" t="n">
-        <v>-133</v>
+        <v>-213</v>
       </c>
       <c r="M72" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.469484</v>
       </c>
       <c r="N72" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.680511</v>
       </c>
       <c r="O72" s="28" t="n">
-        <v>0.516514</v>
+        <v>0.589593</v>
       </c>
       <c r="P72" s="28" t="n"/>
       <c r="Q72" s="28" t="n">
-        <v>-0.054301</v>
+        <v>-0.090918</v>
       </c>
       <c r="R72" s="26" t="n">
         <v>0</v>
       </c>
       <c r="S72" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T72" s="24" t="inlineStr">
         <is>
@@ -21462,7 +21539,7 @@
       <c r="AD72" s="24" t="n"/>
       <c r="AE72" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-ef-inox-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-cs2-uno-alka-2026-08-04).</t>
         </is>
       </c>
       <c r="AF72" s="31" t="inlineStr">
@@ -21503,32 +21580,32 @@
       </c>
       <c r="AP72" s="24" t="inlineStr">
         <is>
-          <t>INOX Division</t>
+          <t>ALKA GAMING</t>
         </is>
       </c>
       <c r="AQ72" s="24" t="inlineStr">
         <is>
-          <t>INOX Division</t>
+          <t>ALKA GAMING</t>
         </is>
       </c>
       <c r="AR72" s="24" t="inlineStr">
         <is>
-          <t>INOX Division</t>
+          <t>ALKA GAMING</t>
         </is>
       </c>
       <c r="AS72" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire</t>
+          <t>UNO MILLE</t>
         </is>
       </c>
       <c r="AT72" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire</t>
+          <t>UNO MILLE</t>
         </is>
       </c>
       <c r="AU72" s="24" t="inlineStr">
         <is>
-          <t>Eternal Fire</t>
+          <t>UNO MILLE</t>
         </is>
       </c>
       <c r="AV72" s="24" t="n"/>
@@ -21546,7 +21623,7 @@
       </c>
       <c r="BA72" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB72" s="24" t="inlineStr">
@@ -21561,7 +21638,7 @@
       </c>
       <c r="BD72" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE72" s="24" t="inlineStr">
@@ -21581,7 +21658,7 @@
       </c>
       <c r="BH72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:52.328161Z</t>
+          <t>2026-08-04T08:56:34.585574Z</t>
         </is>
       </c>
       <c r="BI72" s="24" t="inlineStr">
@@ -21591,13 +21668,13 @@
       </c>
       <c r="BJ72" s="25" t="n"/>
       <c r="BK72" s="26" t="n">
-        <v>-133</v>
+        <v>-213</v>
       </c>
       <c r="BL72" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.469484</v>
       </c>
       <c r="BM72" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.680511</v>
       </c>
       <c r="BN72" s="28" t="n"/>
       <c r="BO72" s="28" t="n"/>
@@ -21628,7 +21705,8 @@
       <c r="CN72" s="24" t="n"/>
       <c r="CO72" s="24" t="n"/>
       <c r="CP72" s="24" t="n"/>
-      <c r="CQ72" s="24" t="inlineStr">
+      <c r="CQ72" s="24" t="n"/>
+      <c r="CR72" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -21637,12 +21715,12 @@
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>c08eea9848294cfc</t>
+          <t>64c05cb926774206</t>
         </is>
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C73" s="24" t="inlineStr">
@@ -21652,7 +21730,7 @@
       </c>
       <c r="D73" s="24" t="inlineStr">
         <is>
-          <t>71321</t>
+          <t>68567</t>
         </is>
       </c>
       <c r="E73" s="24" t="inlineStr">
@@ -21662,12 +21740,12 @@
       </c>
       <c r="F73" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>INOX Division</t>
         </is>
       </c>
       <c r="G73" s="24" t="inlineStr">
         <is>
-          <t>UNiTY esports</t>
+          <t>Eternal Fire</t>
         </is>
       </c>
       <c r="H73" s="24" t="inlineStr">
@@ -21677,7 +21755,7 @@
       </c>
       <c r="I73" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J73" s="25" t="n"/>
@@ -21687,20 +21765,20 @@
         </is>
       </c>
       <c r="L73" s="26" t="n">
-        <v>-122</v>
+        <v>-133</v>
       </c>
       <c r="M73" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.75188</v>
       </c>
       <c r="N73" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.570815</v>
       </c>
       <c r="O73" s="28" t="n">
-        <v>0.500412</v>
+        <v>0.516525</v>
       </c>
       <c r="P73" s="28" t="n"/>
       <c r="Q73" s="28" t="n">
-        <v>-0.049138</v>
+        <v>-0.05429</v>
       </c>
       <c r="R73" s="26" t="n">
         <v>0</v>
@@ -21729,7 +21807,7 @@
       <c r="AD73" s="24" t="n"/>
       <c r="AE73" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-unity-eyn-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-ef-inox-2026-08-04).</t>
         </is>
       </c>
       <c r="AF73" s="31" t="inlineStr">
@@ -21765,37 +21843,37 @@
       </c>
       <c r="AO73" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP73" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>INOX Division</t>
         </is>
       </c>
       <c r="AQ73" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>INOX Division</t>
         </is>
       </c>
       <c r="AR73" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>INOX Division</t>
         </is>
       </c>
       <c r="AS73" s="24" t="inlineStr">
         <is>
-          <t>UNiTY esports</t>
+          <t>Eternal Fire</t>
         </is>
       </c>
       <c r="AT73" s="24" t="inlineStr">
         <is>
-          <t>UNiTY esports</t>
+          <t>Eternal Fire</t>
         </is>
       </c>
       <c r="AU73" s="24" t="inlineStr">
         <is>
-          <t>UNiTY esports</t>
+          <t>Eternal Fire</t>
         </is>
       </c>
       <c r="AV73" s="24" t="n"/>
@@ -21813,7 +21891,7 @@
       </c>
       <c r="BA73" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB73" s="24" t="inlineStr">
@@ -21828,7 +21906,7 @@
       </c>
       <c r="BD73" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE73" s="24" t="inlineStr">
@@ -21848,7 +21926,7 @@
       </c>
       <c r="BH73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:52.848726Z</t>
+          <t>2026-08-04T08:56:35.266965Z</t>
         </is>
       </c>
       <c r="BI73" s="24" t="inlineStr">
@@ -21858,13 +21936,13 @@
       </c>
       <c r="BJ73" s="25" t="n"/>
       <c r="BK73" s="26" t="n">
-        <v>-122</v>
+        <v>-133</v>
       </c>
       <c r="BL73" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.75188</v>
       </c>
       <c r="BM73" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.570815</v>
       </c>
       <c r="BN73" s="28" t="n"/>
       <c r="BO73" s="28" t="n"/>
@@ -21895,7 +21973,8 @@
       <c r="CN73" s="24" t="n"/>
       <c r="CO73" s="24" t="n"/>
       <c r="CP73" s="24" t="n"/>
-      <c r="CQ73" s="24" t="inlineStr">
+      <c r="CQ73" s="24" t="n"/>
+      <c r="CR73" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -21904,22 +21983,22 @@
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
         <is>
-          <t>7f6de446b8c64daf</t>
+          <t>f2cec846a27b4cf1</t>
         </is>
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:30:00Z</t>
+          <t>2026-08-04T17:00:00Z</t>
         </is>
       </c>
       <c r="D74" s="24" t="inlineStr">
         <is>
-          <t>70533</t>
+          <t>71321</t>
         </is>
       </c>
       <c r="E74" s="24" t="inlineStr">
@@ -21929,12 +22008,12 @@
       </c>
       <c r="F74" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="G74" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="H74" s="24" t="inlineStr">
@@ -21944,7 +22023,7 @@
       </c>
       <c r="I74" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J74" s="25" t="n"/>
@@ -21954,23 +22033,23 @@
         </is>
       </c>
       <c r="L74" s="26" t="n">
-        <v>-156</v>
+        <v>-104</v>
       </c>
       <c r="M74" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.961538</v>
       </c>
       <c r="N74" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.509804</v>
       </c>
       <c r="O74" s="28" t="n">
-        <v>0.509286</v>
+        <v>0.500399</v>
       </c>
       <c r="P74" s="28" t="n"/>
       <c r="Q74" s="28" t="n">
-        <v>-0.100089</v>
+        <v>-0.009405</v>
       </c>
       <c r="R74" s="26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S74" s="29" t="n">
         <v>1</v>
@@ -21996,7 +22075,7 @@
       <c r="AD74" s="24" t="n"/>
       <c r="AE74" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-ger-rush-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-unity-eyn-2026-08-04).</t>
         </is>
       </c>
       <c r="AF74" s="31" t="inlineStr">
@@ -22037,32 +22116,32 @@
       </c>
       <c r="AP74" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AQ74" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AR74" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AS74" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="AT74" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="AU74" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="AV74" s="24" t="n"/>
@@ -22080,7 +22159,7 @@
       </c>
       <c r="BA74" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB74" s="24" t="inlineStr">
@@ -22095,7 +22174,7 @@
       </c>
       <c r="BD74" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE74" s="24" t="inlineStr">
@@ -22115,7 +22194,7 @@
       </c>
       <c r="BH74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:53.918772Z</t>
+          <t>2026-08-04T08:56:35.801312Z</t>
         </is>
       </c>
       <c r="BI74" s="24" t="inlineStr">
@@ -22125,13 +22204,13 @@
       </c>
       <c r="BJ74" s="25" t="n"/>
       <c r="BK74" s="26" t="n">
-        <v>-156</v>
+        <v>-104</v>
       </c>
       <c r="BL74" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.961538</v>
       </c>
       <c r="BM74" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.509804</v>
       </c>
       <c r="BN74" s="28" t="n"/>
       <c r="BO74" s="28" t="n"/>
@@ -22162,7 +22241,8 @@
       <c r="CN74" s="24" t="n"/>
       <c r="CO74" s="24" t="n"/>
       <c r="CP74" s="24" t="n"/>
-      <c r="CQ74" s="24" t="inlineStr">
+      <c r="CQ74" s="24" t="n"/>
+      <c r="CR74" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -22171,12 +22251,12 @@
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>e38196d0df884d85</t>
+          <t>1aa51a1f9b594394</t>
         </is>
       </c>
       <c r="B75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C75" s="24" t="inlineStr">
@@ -22186,7 +22266,7 @@
       </c>
       <c r="D75" s="24" t="inlineStr">
         <is>
-          <t>71385</t>
+          <t>70533</t>
         </is>
       </c>
       <c r="E75" s="24" t="inlineStr">
@@ -22196,12 +22276,12 @@
       </c>
       <c r="F75" s="24" t="inlineStr">
         <is>
-          <t>Drama eSports</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="G75" s="24" t="inlineStr">
         <is>
-          <t>KUUSAMO.gg</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="H75" s="24" t="inlineStr">
@@ -22221,26 +22301,26 @@
         </is>
       </c>
       <c r="L75" s="26" t="n">
-        <v>-104</v>
+        <v>-163</v>
       </c>
       <c r="M75" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.613497</v>
       </c>
       <c r="N75" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.619772</v>
       </c>
       <c r="O75" s="28" t="n">
-        <v>0.576412</v>
+        <v>0.509301</v>
       </c>
       <c r="P75" s="28" t="n"/>
       <c r="Q75" s="28" t="n">
-        <v>0.066608</v>
+        <v>-0.110471</v>
       </c>
       <c r="R75" s="26" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="S75" s="29" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="T75" s="24" t="inlineStr">
         <is>
@@ -22263,7 +22343,7 @@
       <c r="AD75" s="24" t="n"/>
       <c r="AE75" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-ksm-drama-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-ger-rush-2026-08-04).</t>
         </is>
       </c>
       <c r="AF75" s="31" t="inlineStr">
@@ -22281,7 +22361,7 @@
       <c r="AJ75" s="31" t="n"/>
       <c r="AK75" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL75" s="26" t="n">
@@ -22289,47 +22369,47 @@
       </c>
       <c r="AM75" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN75" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO75" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP75" s="24" t="inlineStr">
         <is>
-          <t>Drama eSports</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="AQ75" s="24" t="inlineStr">
         <is>
-          <t>Drama eSports</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="AR75" s="24" t="inlineStr">
         <is>
-          <t>Drama eSports</t>
+          <t>Rush</t>
         </is>
       </c>
       <c r="AS75" s="24" t="inlineStr">
         <is>
-          <t>KUUSAMO.gg</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="AT75" s="24" t="inlineStr">
         <is>
-          <t>KUUSAMO.gg</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="AU75" s="24" t="inlineStr">
         <is>
-          <t>KUUSAMO.gg</t>
+          <t>Grêmio Esports</t>
         </is>
       </c>
       <c r="AV75" s="24" t="n"/>
@@ -22347,7 +22427,7 @@
       </c>
       <c r="BA75" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB75" s="24" t="inlineStr">
@@ -22362,7 +22442,7 @@
       </c>
       <c r="BD75" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE75" s="24" t="inlineStr">
@@ -22382,7 +22462,7 @@
       </c>
       <c r="BH75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:54.911657Z</t>
+          <t>2026-08-04T08:56:37.172008Z</t>
         </is>
       </c>
       <c r="BI75" s="24" t="inlineStr">
@@ -22392,13 +22472,13 @@
       </c>
       <c r="BJ75" s="25" t="n"/>
       <c r="BK75" s="26" t="n">
-        <v>-104</v>
+        <v>-163</v>
       </c>
       <c r="BL75" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.613497</v>
       </c>
       <c r="BM75" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.619772</v>
       </c>
       <c r="BN75" s="28" t="n"/>
       <c r="BO75" s="28" t="n"/>
@@ -22429,21 +22509,22 @@
       <c r="CN75" s="24" t="n"/>
       <c r="CO75" s="24" t="n"/>
       <c r="CP75" s="24" t="n"/>
-      <c r="CQ75" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CQ75" s="24" t="n"/>
+      <c r="CR75" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
         <is>
-          <t>89e248c19cba49bf</t>
+          <t>97201e2fd9db43c2</t>
         </is>
       </c>
       <c r="B76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C76" s="24" t="inlineStr">
@@ -22453,7 +22534,7 @@
       </c>
       <c r="D76" s="24" t="inlineStr">
         <is>
-          <t>71390</t>
+          <t>71385</t>
         </is>
       </c>
       <c r="E76" s="24" t="inlineStr">
@@ -22463,12 +22544,12 @@
       </c>
       <c r="F76" s="24" t="inlineStr">
         <is>
-          <t>Subtop De France</t>
+          <t>Drama eSports</t>
         </is>
       </c>
       <c r="G76" s="24" t="inlineStr">
         <is>
-          <t>Glitchtech Esports</t>
+          <t>KUUSAMO.gg</t>
         </is>
       </c>
       <c r="H76" s="24" t="inlineStr">
@@ -22478,7 +22559,7 @@
       </c>
       <c r="I76" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J76" s="25" t="n"/>
@@ -22488,23 +22569,23 @@
         </is>
       </c>
       <c r="L76" s="26" t="n">
-        <v>-104</v>
+        <v>-170</v>
       </c>
       <c r="M76" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.588235</v>
       </c>
       <c r="N76" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.62963</v>
       </c>
       <c r="O76" s="28" t="n">
-        <v>0.598969</v>
+        <v>0.576417</v>
       </c>
       <c r="P76" s="28" t="n"/>
       <c r="Q76" s="28" t="n">
-        <v>0.08916499999999999</v>
+        <v>-0.053213</v>
       </c>
       <c r="R76" s="26" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="S76" s="29" t="n">
         <v>1.25</v>
@@ -22530,7 +22611,7 @@
       <c r="AD76" s="24" t="n"/>
       <c r="AE76" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-gel-sdf-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-ksm-drama-2026-08-04).</t>
         </is>
       </c>
       <c r="AF76" s="31" t="inlineStr">
@@ -22548,7 +22629,7 @@
       <c r="AJ76" s="31" t="n"/>
       <c r="AK76" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>research_observation</t>
         </is>
       </c>
       <c r="AL76" s="26" t="n">
@@ -22556,47 +22637,47 @@
       </c>
       <c r="AM76" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN76" s="24" t="inlineStr">
         <is>
-          <t>CALL</t>
+          <t>NO_CALL</t>
         </is>
       </c>
       <c r="AO76" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP76" s="24" t="inlineStr">
         <is>
-          <t>Subtop De France</t>
+          <t>Drama eSports</t>
         </is>
       </c>
       <c r="AQ76" s="24" t="inlineStr">
         <is>
-          <t>Subtop De France</t>
+          <t>Drama eSports</t>
         </is>
       </c>
       <c r="AR76" s="24" t="inlineStr">
         <is>
-          <t>Subtop De France</t>
+          <t>Drama eSports</t>
         </is>
       </c>
       <c r="AS76" s="24" t="inlineStr">
         <is>
-          <t>Glitchtech Esports</t>
+          <t>KUUSAMO.gg</t>
         </is>
       </c>
       <c r="AT76" s="24" t="inlineStr">
         <is>
-          <t>Glitchtech Esports</t>
+          <t>KUUSAMO.gg</t>
         </is>
       </c>
       <c r="AU76" s="24" t="inlineStr">
         <is>
-          <t>Glitchtech Esports</t>
+          <t>KUUSAMO.gg</t>
         </is>
       </c>
       <c r="AV76" s="24" t="n"/>
@@ -22614,7 +22695,7 @@
       </c>
       <c r="BA76" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB76" s="24" t="inlineStr">
@@ -22629,7 +22710,7 @@
       </c>
       <c r="BD76" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE76" s="24" t="inlineStr">
@@ -22649,7 +22730,7 @@
       </c>
       <c r="BH76" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:57.015430Z</t>
+          <t>2026-08-04T08:56:38.676055Z</t>
         </is>
       </c>
       <c r="BI76" s="24" t="inlineStr">
@@ -22659,13 +22740,13 @@
       </c>
       <c r="BJ76" s="25" t="n"/>
       <c r="BK76" s="26" t="n">
-        <v>-104</v>
+        <v>-170</v>
       </c>
       <c r="BL76" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.588235</v>
       </c>
       <c r="BM76" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.62963</v>
       </c>
       <c r="BN76" s="28" t="n"/>
       <c r="BO76" s="28" t="n"/>
@@ -22696,21 +22777,22 @@
       <c r="CN76" s="24" t="n"/>
       <c r="CO76" s="24" t="n"/>
       <c r="CP76" s="24" t="n"/>
-      <c r="CQ76" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CQ76" s="24" t="n"/>
+      <c r="CR76" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="24" t="inlineStr">
         <is>
-          <t>bbfdec782ec846f5</t>
+          <t>abd4344563f249df</t>
         </is>
       </c>
       <c r="B77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:01:00.694416Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C77" s="24" t="inlineStr">
@@ -22720,7 +22802,7 @@
       </c>
       <c r="D77" s="24" t="inlineStr">
         <is>
-          <t>71388</t>
+          <t>71390</t>
         </is>
       </c>
       <c r="E77" s="24" t="inlineStr">
@@ -22730,12 +22812,12 @@
       </c>
       <c r="F77" s="24" t="inlineStr">
         <is>
-          <t>Fraternity</t>
+          <t>Subtop De France</t>
         </is>
       </c>
       <c r="G77" s="24" t="inlineStr">
         <is>
-          <t>PURE</t>
+          <t>Glitchtech Esports</t>
         </is>
       </c>
       <c r="H77" s="24" t="inlineStr">
@@ -22745,7 +22827,7 @@
       </c>
       <c r="I77" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J77" s="25" t="n"/>
@@ -22755,26 +22837,26 @@
         </is>
       </c>
       <c r="L77" s="26" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="M77" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.613497</v>
       </c>
       <c r="N77" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.619772</v>
       </c>
       <c r="O77" s="28" t="n">
-        <v>0.556215</v>
+        <v>0.598949</v>
       </c>
       <c r="P77" s="28" t="n"/>
       <c r="Q77" s="28" t="n">
-        <v>-0.05316</v>
+        <v>-0.020823</v>
       </c>
       <c r="R77" s="26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S77" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T77" s="24" t="inlineStr">
         <is>
@@ -22797,7 +22879,7 @@
       <c r="AD77" s="24" t="n"/>
       <c r="AE77" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-pure-frt-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-gel-sdf-2026-08-04).</t>
         </is>
       </c>
       <c r="AF77" s="31" t="inlineStr">
@@ -22838,32 +22920,32 @@
       </c>
       <c r="AP77" s="24" t="inlineStr">
         <is>
-          <t>Fraternity</t>
+          <t>Subtop De France</t>
         </is>
       </c>
       <c r="AQ77" s="24" t="inlineStr">
         <is>
-          <t>Fraternity</t>
+          <t>Subtop De France</t>
         </is>
       </c>
       <c r="AR77" s="24" t="inlineStr">
         <is>
-          <t>Fraternity</t>
+          <t>Subtop De France</t>
         </is>
       </c>
       <c r="AS77" s="24" t="inlineStr">
         <is>
-          <t>PURE</t>
+          <t>Glitchtech Esports</t>
         </is>
       </c>
       <c r="AT77" s="24" t="inlineStr">
         <is>
-          <t>PURE</t>
+          <t>Glitchtech Esports</t>
         </is>
       </c>
       <c r="AU77" s="24" t="inlineStr">
         <is>
-          <t>PURE</t>
+          <t>Glitchtech Esports</t>
         </is>
       </c>
       <c r="AV77" s="24" t="n"/>
@@ -22881,7 +22963,7 @@
       </c>
       <c r="BA77" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB77" s="24" t="inlineStr">
@@ -22896,7 +22978,7 @@
       </c>
       <c r="BD77" s="24" t="inlineStr">
         <is>
-          <t>09a1290618ceeeb656e117e9f9dc9002fa1c96576b62b6ccc86887cf39cea65f</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE77" s="24" t="inlineStr">
@@ -22916,7 +22998,7 @@
       </c>
       <c r="BH77" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T02:00:58.048624Z</t>
+          <t>2026-08-04T08:56:40.911181Z</t>
         </is>
       </c>
       <c r="BI77" s="24" t="inlineStr">
@@ -22926,13 +23008,13 @@
       </c>
       <c r="BJ77" s="25" t="n"/>
       <c r="BK77" s="26" t="n">
-        <v>-156</v>
+        <v>-163</v>
       </c>
       <c r="BL77" s="27" t="n">
-        <v>1.641026</v>
+        <v>1.613497</v>
       </c>
       <c r="BM77" s="28" t="n">
-        <v>0.609375</v>
+        <v>0.619772</v>
       </c>
       <c r="BN77" s="28" t="n"/>
       <c r="BO77" s="28" t="n"/>
@@ -22963,7 +23045,8 @@
       <c r="CN77" s="24" t="n"/>
       <c r="CO77" s="24" t="n"/>
       <c r="CP77" s="24" t="n"/>
-      <c r="CQ77" s="24" t="inlineStr">
+      <c r="CQ77" s="24" t="n"/>
+      <c r="CR77" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -22972,12 +23055,12 @@
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="24" t="inlineStr">
         <is>
-          <t>c68584aba0394add</t>
+          <t>ab579008b3794a96</t>
         </is>
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T04:00:12.475882Z</t>
+          <t>2026-08-04T08:56:55.041466Z</t>
         </is>
       </c>
       <c r="C78" s="24" t="inlineStr">
@@ -22987,7 +23070,7 @@
       </c>
       <c r="D78" s="24" t="inlineStr">
         <is>
-          <t>71382</t>
+          <t>71389</t>
         </is>
       </c>
       <c r="E78" s="24" t="inlineStr">
@@ -22997,12 +23080,12 @@
       </c>
       <c r="F78" s="24" t="inlineStr">
         <is>
-          <t>JUMBO TEAM</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="G78" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>Arch</t>
         </is>
       </c>
       <c r="H78" s="24" t="inlineStr">
@@ -23022,26 +23105,26 @@
         </is>
       </c>
       <c r="L78" s="26" t="n">
-        <v>-163</v>
+        <v>-104</v>
       </c>
       <c r="M78" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.961538</v>
       </c>
       <c r="N78" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.509804</v>
       </c>
       <c r="O78" s="28" t="n">
-        <v>0.67501</v>
+        <v>0.698419</v>
       </c>
       <c r="P78" s="28" t="n"/>
       <c r="Q78" s="28" t="n">
-        <v>0.055238</v>
+        <v>0.188615</v>
       </c>
       <c r="R78" s="26" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="S78" s="29" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T78" s="24" t="inlineStr">
         <is>
@@ -23064,7 +23147,7 @@
       <c r="AD78" s="24" t="n"/>
       <c r="AE78" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-bge-jumbo-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-arch-bg-2026-08-04).</t>
         </is>
       </c>
       <c r="AF78" s="31" t="inlineStr">
@@ -23105,32 +23188,32 @@
       </c>
       <c r="AP78" s="24" t="inlineStr">
         <is>
-          <t>JUMBO TEAM</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AQ78" s="24" t="inlineStr">
         <is>
-          <t>JUMBO TEAM</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AR78" s="24" t="inlineStr">
         <is>
-          <t>JUMBO TEAM</t>
+          <t>Banger Gang</t>
         </is>
       </c>
       <c r="AS78" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>Arch</t>
         </is>
       </c>
       <c r="AT78" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>Arch</t>
         </is>
       </c>
       <c r="AU78" s="24" t="inlineStr">
         <is>
-          <t>Benched gods</t>
+          <t>Arch</t>
         </is>
       </c>
       <c r="AV78" s="24" t="n"/>
@@ -23148,7 +23231,7 @@
       </c>
       <c r="BA78" s="24" t="inlineStr">
         <is>
-          <t>15c4c90af7c7e70d96e71add7b9cc8fbed98352fcea88c83a1a27ed966f78c49</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BB78" s="24" t="inlineStr">
@@ -23163,7 +23246,7 @@
       </c>
       <c r="BD78" s="24" t="inlineStr">
         <is>
-          <t>15c4c90af7c7e70d96e71add7b9cc8fbed98352fcea88c83a1a27ed966f78c49</t>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
         </is>
       </c>
       <c r="BE78" s="24" t="inlineStr">
@@ -23183,7 +23266,7 @@
       </c>
       <c r="BH78" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T04:00:07.463015Z</t>
+          <t>2026-08-04T08:56:41.500495Z</t>
         </is>
       </c>
       <c r="BI78" s="24" t="inlineStr">
@@ -23193,13 +23276,13 @@
       </c>
       <c r="BJ78" s="25" t="n"/>
       <c r="BK78" s="26" t="n">
-        <v>-163</v>
+        <v>-104</v>
       </c>
       <c r="BL78" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.961538</v>
       </c>
       <c r="BM78" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.509804</v>
       </c>
       <c r="BN78" s="28" t="n"/>
       <c r="BO78" s="28" t="n"/>
@@ -23230,7 +23313,2420 @@
       <c r="CN78" s="24" t="n"/>
       <c r="CO78" s="24" t="n"/>
       <c r="CP78" s="24" t="n"/>
-      <c r="CQ78" s="24" t="inlineStr">
+      <c r="CQ78" s="24" t="n"/>
+      <c r="CR78" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="36" customHeight="1">
+      <c r="A79" s="24" t="inlineStr">
+        <is>
+          <t>f429197b3d334a5c</t>
+        </is>
+      </c>
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:55.041466Z</t>
+        </is>
+      </c>
+      <c r="C79" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr">
+        <is>
+          <t>71388</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F79" s="24" t="inlineStr">
+        <is>
+          <t>Fraternity</t>
+        </is>
+      </c>
+      <c r="G79" s="24" t="inlineStr">
+        <is>
+          <t>PURE</t>
+        </is>
+      </c>
+      <c r="H79" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I79" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J79" s="25" t="n"/>
+      <c r="K79" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L79" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M79" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N79" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O79" s="28" t="n">
+        <v>0.556222</v>
+      </c>
+      <c r="P79" s="28" t="n"/>
+      <c r="Q79" s="28" t="n">
+        <v>0.025706</v>
+      </c>
+      <c r="R79" s="26" t="n">
+        <v>33</v>
+      </c>
+      <c r="S79" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U79" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V79" s="24" t="n"/>
+      <c r="W79" s="26" t="n"/>
+      <c r="X79" s="26" t="n"/>
+      <c r="Y79" s="25" t="n"/>
+      <c r="Z79" s="26" t="n"/>
+      <c r="AA79" s="28" t="n"/>
+      <c r="AB79" s="28" t="n"/>
+      <c r="AC79" s="30" t="n"/>
+      <c r="AD79" s="24" t="n"/>
+      <c r="AE79" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-cs2-pure-frt-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF79" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG79" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH79" s="24" t="n"/>
+      <c r="AI79" s="31" t="n"/>
+      <c r="AJ79" s="31" t="n"/>
+      <c r="AK79" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL79" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM79" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN79" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO79" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP79" s="24" t="inlineStr">
+        <is>
+          <t>Fraternity</t>
+        </is>
+      </c>
+      <c r="AQ79" s="24" t="inlineStr">
+        <is>
+          <t>Fraternity</t>
+        </is>
+      </c>
+      <c r="AR79" s="24" t="inlineStr">
+        <is>
+          <t>Fraternity</t>
+        </is>
+      </c>
+      <c r="AS79" s="24" t="inlineStr">
+        <is>
+          <t>PURE</t>
+        </is>
+      </c>
+      <c r="AT79" s="24" t="inlineStr">
+        <is>
+          <t>PURE</t>
+        </is>
+      </c>
+      <c r="AU79" s="24" t="inlineStr">
+        <is>
+          <t>PURE</t>
+        </is>
+      </c>
+      <c r="AV79" s="24" t="n"/>
+      <c r="AW79" s="24" t="n"/>
+      <c r="AX79" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY79" s="24" t="n"/>
+      <c r="AZ79" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA79" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BB79" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC79" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD79" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BE79" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF79" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG79" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH79" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:42.051951Z</t>
+        </is>
+      </c>
+      <c r="BI79" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ79" s="25" t="n"/>
+      <c r="BK79" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL79" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM79" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN79" s="28" t="n"/>
+      <c r="BO79" s="28" t="n"/>
+      <c r="BP79" s="25" t="n"/>
+      <c r="BQ79" s="27" t="n"/>
+      <c r="BR79" s="28" t="n"/>
+      <c r="BS79" s="28" t="n"/>
+      <c r="BT79" s="28" t="n"/>
+      <c r="BU79" s="25" t="n"/>
+      <c r="BV79" s="29" t="n"/>
+      <c r="BW79" s="24" t="n"/>
+      <c r="BX79" s="30" t="n"/>
+      <c r="BY79" s="27" t="n"/>
+      <c r="BZ79" s="24" t="n"/>
+      <c r="CA79" s="31" t="n"/>
+      <c r="CB79" s="24" t="n"/>
+      <c r="CC79" s="24" t="n"/>
+      <c r="CD79" s="24" t="n"/>
+      <c r="CE79" s="24" t="n"/>
+      <c r="CF79" s="24" t="n"/>
+      <c r="CG79" s="24" t="n"/>
+      <c r="CH79" s="24" t="n"/>
+      <c r="CI79" s="24" t="n"/>
+      <c r="CJ79" s="24" t="n"/>
+      <c r="CK79" s="24" t="n"/>
+      <c r="CL79" s="24" t="n"/>
+      <c r="CM79" s="24" t="n"/>
+      <c r="CN79" s="24" t="n"/>
+      <c r="CO79" s="24" t="n"/>
+      <c r="CP79" s="24" t="n"/>
+      <c r="CQ79" s="24" t="n"/>
+      <c r="CR79" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="36" customHeight="1">
+      <c r="A80" s="24" t="inlineStr">
+        <is>
+          <t>7d45b8cf85224177</t>
+        </is>
+      </c>
+      <c r="B80" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:55.041466Z</t>
+        </is>
+      </c>
+      <c r="C80" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D80" s="24" t="inlineStr">
+        <is>
+          <t>71387</t>
+        </is>
+      </c>
+      <c r="E80" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F80" s="24" t="inlineStr">
+        <is>
+          <t>OLDBOYS PL</t>
+        </is>
+      </c>
+      <c r="G80" s="24" t="inlineStr">
+        <is>
+          <t>eSuba</t>
+        </is>
+      </c>
+      <c r="H80" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I80" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J80" s="25" t="n"/>
+      <c r="K80" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L80" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M80" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N80" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O80" s="28" t="n">
+        <v>0.6138</v>
+      </c>
+      <c r="P80" s="28" t="n"/>
+      <c r="Q80" s="28" t="n">
+        <v>0.023636</v>
+      </c>
+      <c r="R80" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="S80" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T80" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U80" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V80" s="24" t="n"/>
+      <c r="W80" s="26" t="n"/>
+      <c r="X80" s="26" t="n"/>
+      <c r="Y80" s="25" t="n"/>
+      <c r="Z80" s="26" t="n"/>
+      <c r="AA80" s="28" t="n"/>
+      <c r="AB80" s="28" t="n"/>
+      <c r="AC80" s="30" t="n"/>
+      <c r="AD80" s="24" t="n"/>
+      <c r="AE80" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-esb-oldboyspl-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF80" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG80" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH80" s="24" t="n"/>
+      <c r="AI80" s="31" t="n"/>
+      <c r="AJ80" s="31" t="n"/>
+      <c r="AK80" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL80" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM80" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN80" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO80" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP80" s="24" t="inlineStr">
+        <is>
+          <t>OLDBOYS PL</t>
+        </is>
+      </c>
+      <c r="AQ80" s="24" t="inlineStr">
+        <is>
+          <t>OLDBOYS PL</t>
+        </is>
+      </c>
+      <c r="AR80" s="24" t="inlineStr">
+        <is>
+          <t>OLDBOYS PL</t>
+        </is>
+      </c>
+      <c r="AS80" s="24" t="inlineStr">
+        <is>
+          <t>eSuba</t>
+        </is>
+      </c>
+      <c r="AT80" s="24" t="inlineStr">
+        <is>
+          <t>eSuba</t>
+        </is>
+      </c>
+      <c r="AU80" s="24" t="inlineStr">
+        <is>
+          <t>eSuba</t>
+        </is>
+      </c>
+      <c r="AV80" s="24" t="n"/>
+      <c r="AW80" s="24" t="n"/>
+      <c r="AX80" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY80" s="24" t="n"/>
+      <c r="AZ80" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA80" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BB80" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC80" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD80" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BE80" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF80" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG80" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH80" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:42.609865Z</t>
+        </is>
+      </c>
+      <c r="BI80" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ80" s="25" t="n"/>
+      <c r="BK80" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL80" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM80" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN80" s="28" t="n"/>
+      <c r="BO80" s="28" t="n"/>
+      <c r="BP80" s="25" t="n"/>
+      <c r="BQ80" s="27" t="n"/>
+      <c r="BR80" s="28" t="n"/>
+      <c r="BS80" s="28" t="n"/>
+      <c r="BT80" s="28" t="n"/>
+      <c r="BU80" s="25" t="n"/>
+      <c r="BV80" s="29" t="n"/>
+      <c r="BW80" s="24" t="n"/>
+      <c r="BX80" s="30" t="n"/>
+      <c r="BY80" s="27" t="n"/>
+      <c r="BZ80" s="24" t="n"/>
+      <c r="CA80" s="31" t="n"/>
+      <c r="CB80" s="24" t="n"/>
+      <c r="CC80" s="24" t="n"/>
+      <c r="CD80" s="24" t="n"/>
+      <c r="CE80" s="24" t="n"/>
+      <c r="CF80" s="24" t="n"/>
+      <c r="CG80" s="24" t="n"/>
+      <c r="CH80" s="24" t="n"/>
+      <c r="CI80" s="24" t="n"/>
+      <c r="CJ80" s="24" t="n"/>
+      <c r="CK80" s="24" t="n"/>
+      <c r="CL80" s="24" t="n"/>
+      <c r="CM80" s="24" t="n"/>
+      <c r="CN80" s="24" t="n"/>
+      <c r="CO80" s="24" t="n"/>
+      <c r="CP80" s="24" t="n"/>
+      <c r="CQ80" s="24" t="n"/>
+      <c r="CR80" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="36" customHeight="1">
+      <c r="A81" s="24" t="inlineStr">
+        <is>
+          <t>691e8e639def4075</t>
+        </is>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:55.041466Z</t>
+        </is>
+      </c>
+      <c r="C81" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:30:00Z</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>71382</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F81" s="24" t="inlineStr">
+        <is>
+          <t>JUMBO TEAM</t>
+        </is>
+      </c>
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>Benched gods</t>
+        </is>
+      </c>
+      <c r="H81" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I81" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J81" s="25" t="n"/>
+      <c r="K81" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L81" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M81" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N81" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O81" s="28" t="n">
+        <v>0.67501</v>
+      </c>
+      <c r="P81" s="28" t="n"/>
+      <c r="Q81" s="28" t="n">
+        <v>0.084846</v>
+      </c>
+      <c r="R81" s="26" t="n">
+        <v>62</v>
+      </c>
+      <c r="S81" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T81" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U81" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V81" s="24" t="n"/>
+      <c r="W81" s="26" t="n"/>
+      <c r="X81" s="26" t="n"/>
+      <c r="Y81" s="25" t="n"/>
+      <c r="Z81" s="26" t="n"/>
+      <c r="AA81" s="28" t="n"/>
+      <c r="AB81" s="28" t="n"/>
+      <c r="AC81" s="30" t="n"/>
+      <c r="AD81" s="24" t="n"/>
+      <c r="AE81" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-cs2-bge-jumbo-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF81" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG81" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH81" s="24" t="n"/>
+      <c r="AI81" s="31" t="n"/>
+      <c r="AJ81" s="31" t="n"/>
+      <c r="AK81" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL81" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM81" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN81" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO81" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP81" s="24" t="inlineStr">
+        <is>
+          <t>JUMBO TEAM</t>
+        </is>
+      </c>
+      <c r="AQ81" s="24" t="inlineStr">
+        <is>
+          <t>JUMBO TEAM</t>
+        </is>
+      </c>
+      <c r="AR81" s="24" t="inlineStr">
+        <is>
+          <t>JUMBO TEAM</t>
+        </is>
+      </c>
+      <c r="AS81" s="24" t="inlineStr">
+        <is>
+          <t>Benched gods</t>
+        </is>
+      </c>
+      <c r="AT81" s="24" t="inlineStr">
+        <is>
+          <t>Benched gods</t>
+        </is>
+      </c>
+      <c r="AU81" s="24" t="inlineStr">
+        <is>
+          <t>Benched gods</t>
+        </is>
+      </c>
+      <c r="AV81" s="24" t="n"/>
+      <c r="AW81" s="24" t="n"/>
+      <c r="AX81" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY81" s="24" t="n"/>
+      <c r="AZ81" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA81" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BB81" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC81" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD81" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BE81" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF81" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG81" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH81" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:43.095313Z</t>
+        </is>
+      </c>
+      <c r="BI81" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ81" s="25" t="n"/>
+      <c r="BK81" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL81" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM81" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN81" s="28" t="n"/>
+      <c r="BO81" s="28" t="n"/>
+      <c r="BP81" s="25" t="n"/>
+      <c r="BQ81" s="27" t="n"/>
+      <c r="BR81" s="28" t="n"/>
+      <c r="BS81" s="28" t="n"/>
+      <c r="BT81" s="28" t="n"/>
+      <c r="BU81" s="25" t="n"/>
+      <c r="BV81" s="29" t="n"/>
+      <c r="BW81" s="24" t="n"/>
+      <c r="BX81" s="30" t="n"/>
+      <c r="BY81" s="27" t="n"/>
+      <c r="BZ81" s="24" t="n"/>
+      <c r="CA81" s="31" t="n"/>
+      <c r="CB81" s="24" t="n"/>
+      <c r="CC81" s="24" t="n"/>
+      <c r="CD81" s="24" t="n"/>
+      <c r="CE81" s="24" t="n"/>
+      <c r="CF81" s="24" t="n"/>
+      <c r="CG81" s="24" t="n"/>
+      <c r="CH81" s="24" t="n"/>
+      <c r="CI81" s="24" t="n"/>
+      <c r="CJ81" s="24" t="n"/>
+      <c r="CK81" s="24" t="n"/>
+      <c r="CL81" s="24" t="n"/>
+      <c r="CM81" s="24" t="n"/>
+      <c r="CN81" s="24" t="n"/>
+      <c r="CO81" s="24" t="n"/>
+      <c r="CP81" s="24" t="n"/>
+      <c r="CQ81" s="24" t="n"/>
+      <c r="CR81" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="A82" s="24" t="inlineStr">
+        <is>
+          <t>63371c71ca844c34</t>
+        </is>
+      </c>
+      <c r="B82" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:55.041466Z</t>
+        </is>
+      </c>
+      <c r="C82" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D82" s="24" t="inlineStr">
+        <is>
+          <t>69510</t>
+        </is>
+      </c>
+      <c r="E82" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F82" s="24" t="inlineStr">
+        <is>
+          <t>FaZe Up Next</t>
+        </is>
+      </c>
+      <c r="G82" s="24" t="inlineStr">
+        <is>
+          <t>Dynamo Eclot Phoenix</t>
+        </is>
+      </c>
+      <c r="H82" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I82" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J82" s="25" t="n"/>
+      <c r="K82" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L82" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="M82" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N82" s="28" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="O82" s="28" t="n">
+        <v>0.512967</v>
+      </c>
+      <c r="P82" s="28" t="n"/>
+      <c r="Q82" s="28" t="n">
+        <v>0.203369</v>
+      </c>
+      <c r="R82" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S82" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T82" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U82" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V82" s="24" t="n"/>
+      <c r="W82" s="26" t="n"/>
+      <c r="X82" s="26" t="n"/>
+      <c r="Y82" s="25" t="n"/>
+      <c r="Z82" s="26" t="n"/>
+      <c r="AA82" s="28" t="n"/>
+      <c r="AB82" s="28" t="n"/>
+      <c r="AC82" s="30" t="n"/>
+      <c r="AD82" s="24" t="n"/>
+      <c r="AE82" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3100 (market_slug=aec-cs2-dep-fazeun-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF82" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG82" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH82" s="24" t="n"/>
+      <c r="AI82" s="31" t="n"/>
+      <c r="AJ82" s="31" t="n"/>
+      <c r="AK82" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL82" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM82" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN82" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO82" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP82" s="24" t="inlineStr">
+        <is>
+          <t>FaZe Up Next</t>
+        </is>
+      </c>
+      <c r="AQ82" s="24" t="inlineStr">
+        <is>
+          <t>FaZe Up Next</t>
+        </is>
+      </c>
+      <c r="AR82" s="24" t="inlineStr">
+        <is>
+          <t>FaZe Up Next</t>
+        </is>
+      </c>
+      <c r="AS82" s="24" t="inlineStr">
+        <is>
+          <t>Dynamo Eclot Phoenix</t>
+        </is>
+      </c>
+      <c r="AT82" s="24" t="inlineStr">
+        <is>
+          <t>Dynamo Eclot Phoenix</t>
+        </is>
+      </c>
+      <c r="AU82" s="24" t="inlineStr">
+        <is>
+          <t>Dynamo Eclot Phoenix</t>
+        </is>
+      </c>
+      <c r="AV82" s="24" t="n"/>
+      <c r="AW82" s="24" t="n"/>
+      <c r="AX82" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY82" s="24" t="n"/>
+      <c r="AZ82" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA82" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BB82" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC82" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD82" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BE82" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF82" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG82" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH82" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:46.237997Z</t>
+        </is>
+      </c>
+      <c r="BI82" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ82" s="25" t="n"/>
+      <c r="BK82" s="26" t="n">
+        <v>223</v>
+      </c>
+      <c r="BL82" s="27" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BM82" s="28" t="n">
+        <v>0.309598</v>
+      </c>
+      <c r="BN82" s="28" t="n"/>
+      <c r="BO82" s="28" t="n"/>
+      <c r="BP82" s="25" t="n"/>
+      <c r="BQ82" s="27" t="n"/>
+      <c r="BR82" s="28" t="n"/>
+      <c r="BS82" s="28" t="n"/>
+      <c r="BT82" s="28" t="n"/>
+      <c r="BU82" s="25" t="n"/>
+      <c r="BV82" s="29" t="n"/>
+      <c r="BW82" s="24" t="n"/>
+      <c r="BX82" s="30" t="n"/>
+      <c r="BY82" s="27" t="n"/>
+      <c r="BZ82" s="24" t="n"/>
+      <c r="CA82" s="31" t="n"/>
+      <c r="CB82" s="24" t="n"/>
+      <c r="CC82" s="24" t="n"/>
+      <c r="CD82" s="24" t="n"/>
+      <c r="CE82" s="24" t="n"/>
+      <c r="CF82" s="24" t="n"/>
+      <c r="CG82" s="24" t="n"/>
+      <c r="CH82" s="24" t="n"/>
+      <c r="CI82" s="24" t="n"/>
+      <c r="CJ82" s="24" t="n"/>
+      <c r="CK82" s="24" t="n"/>
+      <c r="CL82" s="24" t="n"/>
+      <c r="CM82" s="24" t="n"/>
+      <c r="CN82" s="24" t="n"/>
+      <c r="CO82" s="24" t="n"/>
+      <c r="CP82" s="24" t="n"/>
+      <c r="CQ82" s="24" t="n"/>
+      <c r="CR82" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="36" customHeight="1">
+      <c r="A83" s="24" t="inlineStr">
+        <is>
+          <t>b0fd4e3cad94478e</t>
+        </is>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:55.041466Z</t>
+        </is>
+      </c>
+      <c r="C83" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>69537</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F83" s="24" t="inlineStr">
+        <is>
+          <t>Abyssal</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>Arcade Esports</t>
+        </is>
+      </c>
+      <c r="H83" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I83" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J83" s="25" t="n"/>
+      <c r="K83" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L83" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="M83" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N83" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="O83" s="28" t="n">
+        <v>0.536892</v>
+      </c>
+      <c r="P83" s="28" t="n"/>
+      <c r="Q83" s="28" t="n">
+        <v>0.107707</v>
+      </c>
+      <c r="R83" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="S83" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U83" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V83" s="24" t="n"/>
+      <c r="W83" s="26" t="n"/>
+      <c r="X83" s="26" t="n"/>
+      <c r="Y83" s="25" t="n"/>
+      <c r="Z83" s="26" t="n"/>
+      <c r="AA83" s="28" t="n"/>
+      <c r="AB83" s="28" t="n"/>
+      <c r="AC83" s="30" t="n"/>
+      <c r="AD83" s="24" t="n"/>
+      <c r="AE83" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4300 (market_slug=aec-cs2-aer-aby-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF83" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG83" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH83" s="24" t="n"/>
+      <c r="AI83" s="31" t="n"/>
+      <c r="AJ83" s="31" t="n"/>
+      <c r="AK83" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL83" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM83" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN83" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO83" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP83" s="24" t="inlineStr">
+        <is>
+          <t>Abyssal</t>
+        </is>
+      </c>
+      <c r="AQ83" s="24" t="inlineStr">
+        <is>
+          <t>Abyssal</t>
+        </is>
+      </c>
+      <c r="AR83" s="24" t="inlineStr">
+        <is>
+          <t>Abyssal</t>
+        </is>
+      </c>
+      <c r="AS83" s="24" t="inlineStr">
+        <is>
+          <t>Arcade Esports</t>
+        </is>
+      </c>
+      <c r="AT83" s="24" t="inlineStr">
+        <is>
+          <t>Arcade Esports</t>
+        </is>
+      </c>
+      <c r="AU83" s="24" t="inlineStr">
+        <is>
+          <t>Arcade Esports</t>
+        </is>
+      </c>
+      <c r="AV83" s="24" t="n"/>
+      <c r="AW83" s="24" t="n"/>
+      <c r="AX83" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY83" s="24" t="n"/>
+      <c r="AZ83" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA83" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BB83" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC83" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD83" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BE83" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF83" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG83" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH83" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:46.758046Z</t>
+        </is>
+      </c>
+      <c r="BI83" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ83" s="25" t="n"/>
+      <c r="BK83" s="26" t="n">
+        <v>133</v>
+      </c>
+      <c r="BL83" s="27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BM83" s="28" t="n">
+        <v>0.429185</v>
+      </c>
+      <c r="BN83" s="28" t="n"/>
+      <c r="BO83" s="28" t="n"/>
+      <c r="BP83" s="25" t="n"/>
+      <c r="BQ83" s="27" t="n"/>
+      <c r="BR83" s="28" t="n"/>
+      <c r="BS83" s="28" t="n"/>
+      <c r="BT83" s="28" t="n"/>
+      <c r="BU83" s="25" t="n"/>
+      <c r="BV83" s="29" t="n"/>
+      <c r="BW83" s="24" t="n"/>
+      <c r="BX83" s="30" t="n"/>
+      <c r="BY83" s="27" t="n"/>
+      <c r="BZ83" s="24" t="n"/>
+      <c r="CA83" s="31" t="n"/>
+      <c r="CB83" s="24" t="n"/>
+      <c r="CC83" s="24" t="n"/>
+      <c r="CD83" s="24" t="n"/>
+      <c r="CE83" s="24" t="n"/>
+      <c r="CF83" s="24" t="n"/>
+      <c r="CG83" s="24" t="n"/>
+      <c r="CH83" s="24" t="n"/>
+      <c r="CI83" s="24" t="n"/>
+      <c r="CJ83" s="24" t="n"/>
+      <c r="CK83" s="24" t="n"/>
+      <c r="CL83" s="24" t="n"/>
+      <c r="CM83" s="24" t="n"/>
+      <c r="CN83" s="24" t="n"/>
+      <c r="CO83" s="24" t="n"/>
+      <c r="CP83" s="24" t="n"/>
+      <c r="CQ83" s="24" t="n"/>
+      <c r="CR83" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="36" customHeight="1">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>e15d757a9ca0484d</t>
+        </is>
+      </c>
+      <c r="B84" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:55.041466Z</t>
+        </is>
+      </c>
+      <c r="C84" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D84" s="24" t="inlineStr">
+        <is>
+          <t>71199</t>
+        </is>
+      </c>
+      <c r="E84" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F84" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="G84" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="H84" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I84" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J84" s="25" t="n"/>
+      <c r="K84" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L84" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M84" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N84" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O84" s="28" t="n">
+        <v>0.505972</v>
+      </c>
+      <c r="P84" s="28" t="n"/>
+      <c r="Q84" s="28" t="n">
+        <v>0.065443</v>
+      </c>
+      <c r="R84" s="26" t="n">
+        <v>53</v>
+      </c>
+      <c r="S84" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T84" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U84" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V84" s="24" t="n"/>
+      <c r="W84" s="26" t="n"/>
+      <c r="X84" s="26" t="n"/>
+      <c r="Y84" s="25" t="n"/>
+      <c r="Z84" s="26" t="n"/>
+      <c r="AA84" s="28" t="n"/>
+      <c r="AB84" s="28" t="n"/>
+      <c r="AC84" s="30" t="n"/>
+      <c r="AD84" s="24" t="n"/>
+      <c r="AE84" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4400 (market_slug=aec-cs2-btf-erx-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF84" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG84" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH84" s="24" t="n"/>
+      <c r="AI84" s="31" t="n"/>
+      <c r="AJ84" s="31" t="n"/>
+      <c r="AK84" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL84" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM84" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN84" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO84" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP84" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AQ84" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AR84" s="24" t="inlineStr">
+        <is>
+          <t>ex-RUSTEC</t>
+        </is>
+      </c>
+      <c r="AS84" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AT84" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AU84" s="24" t="inlineStr">
+        <is>
+          <t>Butterfly</t>
+        </is>
+      </c>
+      <c r="AV84" s="24" t="n"/>
+      <c r="AW84" s="24" t="n"/>
+      <c r="AX84" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY84" s="24" t="n"/>
+      <c r="AZ84" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA84" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BB84" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC84" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD84" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BE84" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF84" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG84" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH84" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:48.910262Z</t>
+        </is>
+      </c>
+      <c r="BI84" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ84" s="25" t="n"/>
+      <c r="BK84" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL84" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM84" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN84" s="28" t="n"/>
+      <c r="BO84" s="28" t="n"/>
+      <c r="BP84" s="25" t="n"/>
+      <c r="BQ84" s="27" t="n"/>
+      <c r="BR84" s="28" t="n"/>
+      <c r="BS84" s="28" t="n"/>
+      <c r="BT84" s="28" t="n"/>
+      <c r="BU84" s="25" t="n"/>
+      <c r="BV84" s="29" t="n"/>
+      <c r="BW84" s="24" t="n"/>
+      <c r="BX84" s="30" t="n"/>
+      <c r="BY84" s="27" t="n"/>
+      <c r="BZ84" s="24" t="n"/>
+      <c r="CA84" s="31" t="n"/>
+      <c r="CB84" s="24" t="n"/>
+      <c r="CC84" s="24" t="n"/>
+      <c r="CD84" s="24" t="n"/>
+      <c r="CE84" s="24" t="n"/>
+      <c r="CF84" s="24" t="n"/>
+      <c r="CG84" s="24" t="n"/>
+      <c r="CH84" s="24" t="n"/>
+      <c r="CI84" s="24" t="n"/>
+      <c r="CJ84" s="24" t="n"/>
+      <c r="CK84" s="24" t="n"/>
+      <c r="CL84" s="24" t="n"/>
+      <c r="CM84" s="24" t="n"/>
+      <c r="CN84" s="24" t="n"/>
+      <c r="CO84" s="24" t="n"/>
+      <c r="CP84" s="24" t="n"/>
+      <c r="CQ84" s="24" t="n"/>
+      <c r="CR84" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="36" customHeight="1">
+      <c r="A85" s="24" t="inlineStr">
+        <is>
+          <t>a01f472f33cc4852</t>
+        </is>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:55.041466Z</t>
+        </is>
+      </c>
+      <c r="C85" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>69555</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F85" s="24" t="inlineStr">
+        <is>
+          <t>PCH3LK1N Club</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>Lixxx Club</t>
+        </is>
+      </c>
+      <c r="H85" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I85" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J85" s="25" t="n"/>
+      <c r="K85" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L85" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M85" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N85" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O85" s="28" t="n">
+        <v>0.527057</v>
+      </c>
+      <c r="P85" s="28" t="n"/>
+      <c r="Q85" s="28" t="n">
+        <v>-0.032414</v>
+      </c>
+      <c r="R85" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="S85" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U85" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V85" s="24" t="n"/>
+      <c r="W85" s="26" t="n"/>
+      <c r="X85" s="26" t="n"/>
+      <c r="Y85" s="25" t="n"/>
+      <c r="Z85" s="26" t="n"/>
+      <c r="AA85" s="28" t="n"/>
+      <c r="AB85" s="28" t="n"/>
+      <c r="AC85" s="30" t="n"/>
+      <c r="AD85" s="24" t="n"/>
+      <c r="AE85" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-cs2-lci-plnc-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF85" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG85" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH85" s="24" t="n"/>
+      <c r="AI85" s="31" t="n"/>
+      <c r="AJ85" s="31" t="n"/>
+      <c r="AK85" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL85" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM85" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN85" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO85" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP85" s="24" t="inlineStr">
+        <is>
+          <t>PCH3LK1N Club</t>
+        </is>
+      </c>
+      <c r="AQ85" s="24" t="inlineStr">
+        <is>
+          <t>PCH3LK1N Club</t>
+        </is>
+      </c>
+      <c r="AR85" s="24" t="inlineStr">
+        <is>
+          <t>PCH3LK1N Club</t>
+        </is>
+      </c>
+      <c r="AS85" s="24" t="inlineStr">
+        <is>
+          <t>Lixxx Club</t>
+        </is>
+      </c>
+      <c r="AT85" s="24" t="inlineStr">
+        <is>
+          <t>Lixxx Club</t>
+        </is>
+      </c>
+      <c r="AU85" s="24" t="inlineStr">
+        <is>
+          <t>Lixxx Club</t>
+        </is>
+      </c>
+      <c r="AV85" s="24" t="n"/>
+      <c r="AW85" s="24" t="n"/>
+      <c r="AX85" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY85" s="24" t="n"/>
+      <c r="AZ85" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA85" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BB85" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC85" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD85" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BE85" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF85" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG85" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH85" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:50.632049Z</t>
+        </is>
+      </c>
+      <c r="BI85" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ85" s="25" t="n"/>
+      <c r="BK85" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL85" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM85" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN85" s="28" t="n"/>
+      <c r="BO85" s="28" t="n"/>
+      <c r="BP85" s="25" t="n"/>
+      <c r="BQ85" s="27" t="n"/>
+      <c r="BR85" s="28" t="n"/>
+      <c r="BS85" s="28" t="n"/>
+      <c r="BT85" s="28" t="n"/>
+      <c r="BU85" s="25" t="n"/>
+      <c r="BV85" s="29" t="n"/>
+      <c r="BW85" s="24" t="n"/>
+      <c r="BX85" s="30" t="n"/>
+      <c r="BY85" s="27" t="n"/>
+      <c r="BZ85" s="24" t="n"/>
+      <c r="CA85" s="31" t="n"/>
+      <c r="CB85" s="24" t="n"/>
+      <c r="CC85" s="24" t="n"/>
+      <c r="CD85" s="24" t="n"/>
+      <c r="CE85" s="24" t="n"/>
+      <c r="CF85" s="24" t="n"/>
+      <c r="CG85" s="24" t="n"/>
+      <c r="CH85" s="24" t="n"/>
+      <c r="CI85" s="24" t="n"/>
+      <c r="CJ85" s="24" t="n"/>
+      <c r="CK85" s="24" t="n"/>
+      <c r="CL85" s="24" t="n"/>
+      <c r="CM85" s="24" t="n"/>
+      <c r="CN85" s="24" t="n"/>
+      <c r="CO85" s="24" t="n"/>
+      <c r="CP85" s="24" t="n"/>
+      <c r="CQ85" s="24" t="n"/>
+      <c r="CR85" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="36" customHeight="1">
+      <c r="A86" s="24" t="inlineStr">
+        <is>
+          <t>3bc5c6e37c554a78</t>
+        </is>
+      </c>
+      <c r="B86" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:55.041466Z</t>
+        </is>
+      </c>
+      <c r="C86" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D86" s="24" t="inlineStr">
+        <is>
+          <t>69616</t>
+        </is>
+      </c>
+      <c r="E86" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F86" s="24" t="inlineStr">
+        <is>
+          <t>eSuba</t>
+        </is>
+      </c>
+      <c r="G86" s="24" t="inlineStr">
+        <is>
+          <t>JAM</t>
+        </is>
+      </c>
+      <c r="H86" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I86" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J86" s="25" t="n"/>
+      <c r="K86" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L86" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M86" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N86" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O86" s="28" t="n">
+        <v>0.537618</v>
+      </c>
+      <c r="P86" s="28" t="n"/>
+      <c r="Q86" s="28" t="n">
+        <v>-0.033197</v>
+      </c>
+      <c r="R86" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="S86" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T86" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U86" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V86" s="24" t="n"/>
+      <c r="W86" s="26" t="n"/>
+      <c r="X86" s="26" t="n"/>
+      <c r="Y86" s="25" t="n"/>
+      <c r="Z86" s="26" t="n"/>
+      <c r="AA86" s="28" t="n"/>
+      <c r="AB86" s="28" t="n"/>
+      <c r="AC86" s="30" t="n"/>
+      <c r="AD86" s="24" t="n"/>
+      <c r="AE86" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-jam-esb-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF86" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG86" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH86" s="24" t="n"/>
+      <c r="AI86" s="31" t="n"/>
+      <c r="AJ86" s="31" t="n"/>
+      <c r="AK86" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL86" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM86" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN86" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO86" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP86" s="24" t="inlineStr">
+        <is>
+          <t>eSuba</t>
+        </is>
+      </c>
+      <c r="AQ86" s="24" t="inlineStr">
+        <is>
+          <t>eSuba</t>
+        </is>
+      </c>
+      <c r="AR86" s="24" t="inlineStr">
+        <is>
+          <t>eSuba</t>
+        </is>
+      </c>
+      <c r="AS86" s="24" t="inlineStr">
+        <is>
+          <t>JAM</t>
+        </is>
+      </c>
+      <c r="AT86" s="24" t="inlineStr">
+        <is>
+          <t>JAM</t>
+        </is>
+      </c>
+      <c r="AU86" s="24" t="inlineStr">
+        <is>
+          <t>JAM</t>
+        </is>
+      </c>
+      <c r="AV86" s="24" t="n"/>
+      <c r="AW86" s="24" t="n"/>
+      <c r="AX86" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY86" s="24" t="n"/>
+      <c r="AZ86" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA86" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BB86" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC86" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD86" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BE86" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF86" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG86" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH86" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:52.334320Z</t>
+        </is>
+      </c>
+      <c r="BI86" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ86" s="25" t="n"/>
+      <c r="BK86" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL86" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM86" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN86" s="28" t="n"/>
+      <c r="BO86" s="28" t="n"/>
+      <c r="BP86" s="25" t="n"/>
+      <c r="BQ86" s="27" t="n"/>
+      <c r="BR86" s="28" t="n"/>
+      <c r="BS86" s="28" t="n"/>
+      <c r="BT86" s="28" t="n"/>
+      <c r="BU86" s="25" t="n"/>
+      <c r="BV86" s="29" t="n"/>
+      <c r="BW86" s="24" t="n"/>
+      <c r="BX86" s="30" t="n"/>
+      <c r="BY86" s="27" t="n"/>
+      <c r="BZ86" s="24" t="n"/>
+      <c r="CA86" s="31" t="n"/>
+      <c r="CB86" s="24" t="n"/>
+      <c r="CC86" s="24" t="n"/>
+      <c r="CD86" s="24" t="n"/>
+      <c r="CE86" s="24" t="n"/>
+      <c r="CF86" s="24" t="n"/>
+      <c r="CG86" s="24" t="n"/>
+      <c r="CH86" s="24" t="n"/>
+      <c r="CI86" s="24" t="n"/>
+      <c r="CJ86" s="24" t="n"/>
+      <c r="CK86" s="24" t="n"/>
+      <c r="CL86" s="24" t="n"/>
+      <c r="CM86" s="24" t="n"/>
+      <c r="CN86" s="24" t="n"/>
+      <c r="CO86" s="24" t="n"/>
+      <c r="CP86" s="24" t="n"/>
+      <c r="CQ86" s="24" t="n"/>
+      <c r="CR86" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="24" t="inlineStr">
+        <is>
+          <t>8a0cd6c0d2d04e41</t>
+        </is>
+      </c>
+      <c r="B87" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:55.041466Z</t>
+        </is>
+      </c>
+      <c r="C87" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr">
+        <is>
+          <t>69617</t>
+        </is>
+      </c>
+      <c r="E87" s="24" t="inlineStr">
+        <is>
+          <t>CS2</t>
+        </is>
+      </c>
+      <c r="F87" s="24" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="G87" s="24" t="inlineStr">
+        <is>
+          <t>GamersLab Esports</t>
+        </is>
+      </c>
+      <c r="H87" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I87" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J87" s="25" t="n"/>
+      <c r="K87" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L87" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M87" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N87" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O87" s="28" t="n">
+        <v>0.6268860000000001</v>
+      </c>
+      <c r="P87" s="28" t="n"/>
+      <c r="Q87" s="28" t="n">
+        <v>0.017511</v>
+      </c>
+      <c r="R87" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="S87" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T87" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U87" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V87" s="24" t="n"/>
+      <c r="W87" s="26" t="n"/>
+      <c r="X87" s="26" t="n"/>
+      <c r="Y87" s="25" t="n"/>
+      <c r="Z87" s="26" t="n"/>
+      <c r="AA87" s="28" t="n"/>
+      <c r="AB87" s="28" t="n"/>
+      <c r="AC87" s="30" t="n"/>
+      <c r="AD87" s="24" t="n"/>
+      <c r="AE87" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-cs2-gea-navij-2026-08-05).</t>
+        </is>
+      </c>
+      <c r="AF87" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG87" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH87" s="24" t="n"/>
+      <c r="AI87" s="31" t="n"/>
+      <c r="AJ87" s="31" t="n"/>
+      <c r="AK87" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL87" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM87" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN87" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO87" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP87" s="24" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="AQ87" s="24" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="AR87" s="24" t="inlineStr">
+        <is>
+          <t>NAVI Junior</t>
+        </is>
+      </c>
+      <c r="AS87" s="24" t="inlineStr">
+        <is>
+          <t>GamersLab Esports</t>
+        </is>
+      </c>
+      <c r="AT87" s="24" t="inlineStr">
+        <is>
+          <t>GamersLab Esports</t>
+        </is>
+      </c>
+      <c r="AU87" s="24" t="inlineStr">
+        <is>
+          <t>GamersLab Esports</t>
+        </is>
+      </c>
+      <c r="AV87" s="24" t="n"/>
+      <c r="AW87" s="24" t="n"/>
+      <c r="AX87" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY87" s="24" t="n"/>
+      <c r="AZ87" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA87" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BB87" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC87" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD87" s="24" t="inlineStr">
+        <is>
+          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+        </is>
+      </c>
+      <c r="BE87" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF87" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG87" s="24" t="inlineStr">
+        <is>
+          <t>cs2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH87" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:52.829078Z</t>
+        </is>
+      </c>
+      <c r="BI87" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ87" s="25" t="n"/>
+      <c r="BK87" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL87" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM87" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN87" s="28" t="n"/>
+      <c r="BO87" s="28" t="n"/>
+      <c r="BP87" s="25" t="n"/>
+      <c r="BQ87" s="27" t="n"/>
+      <c r="BR87" s="28" t="n"/>
+      <c r="BS87" s="28" t="n"/>
+      <c r="BT87" s="28" t="n"/>
+      <c r="BU87" s="25" t="n"/>
+      <c r="BV87" s="29" t="n"/>
+      <c r="BW87" s="24" t="n"/>
+      <c r="BX87" s="30" t="n"/>
+      <c r="BY87" s="27" t="n"/>
+      <c r="BZ87" s="24" t="n"/>
+      <c r="CA87" s="31" t="n"/>
+      <c r="CB87" s="24" t="n"/>
+      <c r="CC87" s="24" t="n"/>
+      <c r="CD87" s="24" t="n"/>
+      <c r="CE87" s="24" t="n"/>
+      <c r="CF87" s="24" t="n"/>
+      <c r="CG87" s="24" t="n"/>
+      <c r="CH87" s="24" t="n"/>
+      <c r="CI87" s="24" t="n"/>
+      <c r="CJ87" s="24" t="n"/>
+      <c r="CK87" s="24" t="n"/>
+      <c r="CL87" s="24" t="n"/>
+      <c r="CM87" s="24" t="n"/>
+      <c r="CN87" s="24" t="n"/>
+      <c r="CO87" s="24" t="n"/>
+      <c r="CP87" s="24" t="n"/>
+      <c r="CQ87" s="24" t="n"/>
+      <c r="CR87" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>

--- a/data/research/cs2.xlsx
+++ b/data/research/cs2.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR87" headerRowCount="1">
-  <autoFilter ref="A1:CR87"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS91" headerRowCount="1">
+  <autoFilter ref="A1:CS91"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -755,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$87)</f>
+        <f>COUNTA('Picks'!$A$2:$A$91)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$87,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$91,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$87,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$91,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$87,"settled",'Picks'!$V$2:$V$87,"win")+COUNTIFS('Picks'!$U$2:$U$87,"settled",'Picks'!$V$2:$V$87,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$91,"settled",'Picks'!$V$2:$V$91,"win")+COUNTIFS('Picks'!$U$2:$U$91,"settled",'Picks'!$V$2:$V$91,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -795,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$87,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$91,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$87,"&gt;0",'Picks'!$V$2:$V$87,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$87,"&gt;0",'Picks'!$V$2:$V$87,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$91,"&gt;0",'Picks'!$V$2:$V$91,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$91,"&gt;0",'Picks'!$V$2:$V$91,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$87,"&gt;0",'Picks'!$V$2:$V$87,"win")/(COUNTIFS('Picks'!$BX$2:$BX$87,"&gt;0",'Picks'!$V$2:$V$87,"win")+COUNTIFS('Picks'!$BX$2:$BX$87,"&gt;0",'Picks'!$V$2:$V$87,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$91,"&gt;0",'Picks'!$V$2:$V$91,"win")/(COUNTIFS('Picks'!$BX$2:$BX$91,"&gt;0",'Picks'!$V$2:$V$91,"win")+COUNTIFS('Picks'!$BX$2:$BX$91,"&gt;0",'Picks'!$V$2:$V$91,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$87)/SUM('Picks'!$BX$2:$BX$87),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$91)/SUM('Picks'!$BX$2:$BX$91),0)</f>
         <v/>
       </c>
     </row>
@@ -835,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$87)</f>
+        <f>SUM('Picks'!$BY$2:$BY$91)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$87,"&lt;&gt;",'Picks'!$AB$2:$AB$87),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$91,"&lt;&gt;",'Picks'!$AB$2:$AB$91),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$87,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$87,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$91,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$91,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$87,'Picks'!$AM$2:$AM$87,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$91,'Picks'!$AM$2:$AM$91,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -902,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$87,$A14,'Picks'!$U$2:$U$87,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$91,$A14,'Picks'!$U$2:$U$91,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$87,$A14,'Picks'!$U$2:$U$87,"settled",'Picks'!$V$2:$V$87,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$91,$A14,'Picks'!$U$2:$U$91,"settled",'Picks'!$V$2:$V$91,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$87,$A14,'Picks'!$U$2:$U$87,"settled",'Picks'!$V$2:$V$87,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$91,$A14,'Picks'!$U$2:$U$91,"settled",'Picks'!$V$2:$V$91,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -918,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$87,'Picks'!$H$2:$H$87,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$91,'Picks'!$H$2:$H$91,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$87,'Picks'!$H$2:$H$87,$A14,'Picks'!$U$2:$U$87,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$91,'Picks'!$H$2:$H$91,$A14,'Picks'!$U$2:$U$91,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -933,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$87,$A15,'Picks'!$U$2:$U$87,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$91,$A15,'Picks'!$U$2:$U$91,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$87,$A15,'Picks'!$U$2:$U$87,"settled",'Picks'!$V$2:$V$87,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$91,$A15,'Picks'!$U$2:$U$91,"settled",'Picks'!$V$2:$V$91,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$87,$A15,'Picks'!$U$2:$U$87,"settled",'Picks'!$V$2:$V$87,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$91,$A15,'Picks'!$U$2:$U$91,"settled",'Picks'!$V$2:$V$91,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -949,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$87,'Picks'!$H$2:$H$87,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$91,'Picks'!$H$2:$H$91,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$87,'Picks'!$H$2:$H$87,$A15,'Picks'!$U$2:$U$87,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$91,'Picks'!$H$2:$H$91,$A15,'Picks'!$U$2:$U$91,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -964,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$87,$A16,'Picks'!$U$2:$U$87,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$91,$A16,'Picks'!$U$2:$U$91,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$87,$A16,'Picks'!$U$2:$U$87,"settled",'Picks'!$V$2:$V$87,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$91,$A16,'Picks'!$U$2:$U$91,"settled",'Picks'!$V$2:$V$91,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$87,$A16,'Picks'!$U$2:$U$87,"settled",'Picks'!$V$2:$V$87,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$91,$A16,'Picks'!$U$2:$U$91,"settled",'Picks'!$V$2:$V$91,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -980,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$87,'Picks'!$H$2:$H$87,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$91,'Picks'!$H$2:$H$91,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$87,'Picks'!$H$2:$H$87,$A16,'Picks'!$U$2:$U$87,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$91,'Picks'!$H$2:$H$91,$A16,'Picks'!$U$2:$U$91,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR87"/>
+  <dimension ref="A1:CS91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1883,6 +1890,7 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2171,6 +2179,7 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2459,6 +2468,7 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2747,6 +2757,7 @@
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
       <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="24" t="inlineStr">
@@ -3035,6 +3046,7 @@
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
       <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="n"/>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
@@ -3299,6 +3311,7 @@
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
       <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="24" t="inlineStr">
@@ -3587,6 +3600,7 @@
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
       <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="n"/>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
@@ -3875,6 +3889,7 @@
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
       <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="n"/>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
@@ -4163,6 +4178,7 @@
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
       <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="24" t="inlineStr">
@@ -4451,6 +4467,7 @@
       <c r="CP11" s="24" t="n"/>
       <c r="CQ11" s="24" t="n"/>
       <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="n"/>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
@@ -4739,6 +4756,7 @@
       <c r="CP12" s="24" t="n"/>
       <c r="CQ12" s="24" t="n"/>
       <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
@@ -5027,6 +5045,7 @@
       <c r="CP13" s="24" t="n"/>
       <c r="CQ13" s="24" t="n"/>
       <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="24" t="inlineStr">
@@ -5315,6 +5334,7 @@
       <c r="CP14" s="24" t="n"/>
       <c r="CQ14" s="24" t="n"/>
       <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
@@ -5603,6 +5623,7 @@
       <c r="CP15" s="24" t="n"/>
       <c r="CQ15" s="24" t="n"/>
       <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
@@ -5891,6 +5912,7 @@
       <c r="CP16" s="24" t="n"/>
       <c r="CQ16" s="24" t="n"/>
       <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="24" t="inlineStr">
@@ -6179,6 +6201,7 @@
       <c r="CP17" s="24" t="n"/>
       <c r="CQ17" s="24" t="n"/>
       <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
@@ -6467,6 +6490,7 @@
       <c r="CP18" s="24" t="n"/>
       <c r="CQ18" s="24" t="n"/>
       <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
@@ -6755,6 +6779,7 @@
       <c r="CP19" s="24" t="n"/>
       <c r="CQ19" s="24" t="n"/>
       <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="24" t="inlineStr">
@@ -7043,6 +7068,7 @@
       <c r="CP20" s="24" t="n"/>
       <c r="CQ20" s="24" t="n"/>
       <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
@@ -7331,6 +7357,7 @@
       <c r="CP21" s="24" t="n"/>
       <c r="CQ21" s="24" t="n"/>
       <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
@@ -7619,6 +7646,7 @@
       <c r="CP22" s="24" t="n"/>
       <c r="CQ22" s="24" t="n"/>
       <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
@@ -7883,6 +7911,7 @@
       <c r="CP23" s="24" t="n"/>
       <c r="CQ23" s="24" t="n"/>
       <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
@@ -8171,6 +8200,7 @@
       <c r="CP24" s="24" t="n"/>
       <c r="CQ24" s="24" t="n"/>
       <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
@@ -8459,6 +8489,7 @@
       <c r="CP25" s="24" t="n"/>
       <c r="CQ25" s="24" t="n"/>
       <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
@@ -8747,6 +8778,7 @@
       <c r="CP26" s="24" t="n"/>
       <c r="CQ26" s="24" t="n"/>
       <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="n"/>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
@@ -9035,6 +9067,7 @@
       <c r="CP27" s="24" t="n"/>
       <c r="CQ27" s="24" t="n"/>
       <c r="CR27" s="24" t="n"/>
+      <c r="CS27" s="24" t="n"/>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
@@ -9323,6 +9356,7 @@
       <c r="CP28" s="24" t="n"/>
       <c r="CQ28" s="24" t="n"/>
       <c r="CR28" s="24" t="n"/>
+      <c r="CS28" s="24" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
@@ -9601,6 +9635,7 @@
       <c r="CP29" s="24" t="n"/>
       <c r="CQ29" s="24" t="n"/>
       <c r="CR29" s="24" t="n"/>
+      <c r="CS29" s="24" t="n"/>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
@@ -9889,6 +9924,7 @@
       <c r="CP30" s="24" t="n"/>
       <c r="CQ30" s="24" t="n"/>
       <c r="CR30" s="24" t="n"/>
+      <c r="CS30" s="24" t="n"/>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
@@ -10177,6 +10213,7 @@
       <c r="CP31" s="24" t="n"/>
       <c r="CQ31" s="24" t="n"/>
       <c r="CR31" s="24" t="n"/>
+      <c r="CS31" s="24" t="n"/>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="24" t="inlineStr">
@@ -10465,6 +10502,7 @@
       <c r="CP32" s="24" t="n"/>
       <c r="CQ32" s="24" t="n"/>
       <c r="CR32" s="24" t="n"/>
+      <c r="CS32" s="24" t="n"/>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
@@ -10743,6 +10781,7 @@
       <c r="CP33" s="24" t="n"/>
       <c r="CQ33" s="24" t="n"/>
       <c r="CR33" s="24" t="n"/>
+      <c r="CS33" s="24" t="n"/>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
@@ -11031,6 +11070,7 @@
       <c r="CP34" s="24" t="n"/>
       <c r="CQ34" s="24" t="n"/>
       <c r="CR34" s="24" t="n"/>
+      <c r="CS34" s="24" t="n"/>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
@@ -11309,6 +11349,7 @@
       <c r="CP35" s="24" t="n"/>
       <c r="CQ35" s="24" t="n"/>
       <c r="CR35" s="24" t="n"/>
+      <c r="CS35" s="24" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
@@ -11597,6 +11638,7 @@
       <c r="CP36" s="24" t="n"/>
       <c r="CQ36" s="24" t="n"/>
       <c r="CR36" s="24" t="n"/>
+      <c r="CS36" s="24" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
@@ -11885,6 +11927,7 @@
       <c r="CP37" s="24" t="n"/>
       <c r="CQ37" s="24" t="n"/>
       <c r="CR37" s="24" t="n"/>
+      <c r="CS37" s="24" t="n"/>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="24" t="inlineStr">
@@ -12172,7 +12215,8 @@
       <c r="CO38" s="24" t="n"/>
       <c r="CP38" s="24" t="n"/>
       <c r="CQ38" s="24" t="n"/>
-      <c r="CR38" s="24" t="inlineStr">
+      <c r="CR38" s="24" t="n"/>
+      <c r="CS38" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -12454,7 +12498,8 @@
       <c r="CO39" s="24" t="n"/>
       <c r="CP39" s="24" t="n"/>
       <c r="CQ39" s="24" t="n"/>
-      <c r="CR39" s="24" t="inlineStr">
+      <c r="CR39" s="24" t="n"/>
+      <c r="CS39" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -12746,7 +12791,8 @@
       <c r="CO40" s="24" t="n"/>
       <c r="CP40" s="24" t="n"/>
       <c r="CQ40" s="24" t="n"/>
-      <c r="CR40" s="24" t="inlineStr">
+      <c r="CR40" s="24" t="n"/>
+      <c r="CS40" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -13038,7 +13084,8 @@
       <c r="CO41" s="24" t="n"/>
       <c r="CP41" s="24" t="n"/>
       <c r="CQ41" s="24" t="n"/>
-      <c r="CR41" s="24" t="inlineStr">
+      <c r="CR41" s="24" t="n"/>
+      <c r="CS41" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -13330,7 +13377,8 @@
       <c r="CO42" s="24" t="n"/>
       <c r="CP42" s="24" t="n"/>
       <c r="CQ42" s="24" t="n"/>
-      <c r="CR42" s="24" t="inlineStr">
+      <c r="CR42" s="24" t="n"/>
+      <c r="CS42" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -13622,7 +13670,8 @@
       <c r="CO43" s="24" t="n"/>
       <c r="CP43" s="24" t="n"/>
       <c r="CQ43" s="24" t="n"/>
-      <c r="CR43" s="24" t="inlineStr">
+      <c r="CR43" s="24" t="n"/>
+      <c r="CS43" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -13914,7 +13963,8 @@
       <c r="CO44" s="24" t="n"/>
       <c r="CP44" s="24" t="n"/>
       <c r="CQ44" s="24" t="n"/>
-      <c r="CR44" s="24" t="inlineStr">
+      <c r="CR44" s="24" t="n"/>
+      <c r="CS44" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -14206,7 +14256,8 @@
       <c r="CO45" s="24" t="n"/>
       <c r="CP45" s="24" t="n"/>
       <c r="CQ45" s="24" t="n"/>
-      <c r="CR45" s="24" t="inlineStr">
+      <c r="CR45" s="24" t="n"/>
+      <c r="CS45" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -14498,7 +14549,8 @@
       <c r="CO46" s="24" t="n"/>
       <c r="CP46" s="24" t="n"/>
       <c r="CQ46" s="24" t="n"/>
-      <c r="CR46" s="24" t="inlineStr">
+      <c r="CR46" s="24" t="n"/>
+      <c r="CS46" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -14790,7 +14842,8 @@
       <c r="CO47" s="24" t="n"/>
       <c r="CP47" s="24" t="n"/>
       <c r="CQ47" s="24" t="n"/>
-      <c r="CR47" s="24" t="inlineStr">
+      <c r="CR47" s="24" t="n"/>
+      <c r="CS47" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -15082,7 +15135,8 @@
       <c r="CO48" s="24" t="n"/>
       <c r="CP48" s="24" t="n"/>
       <c r="CQ48" s="24" t="n"/>
-      <c r="CR48" s="24" t="inlineStr">
+      <c r="CR48" s="24" t="n"/>
+      <c r="CS48" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -15374,7 +15428,8 @@
       <c r="CO49" s="24" t="n"/>
       <c r="CP49" s="24" t="n"/>
       <c r="CQ49" s="24" t="n"/>
-      <c r="CR49" s="24" t="inlineStr">
+      <c r="CR49" s="24" t="n"/>
+      <c r="CS49" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -15666,7 +15721,8 @@
       <c r="CO50" s="24" t="n"/>
       <c r="CP50" s="24" t="n"/>
       <c r="CQ50" s="24" t="n"/>
-      <c r="CR50" s="24" t="inlineStr">
+      <c r="CR50" s="24" t="n"/>
+      <c r="CS50" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -15958,7 +16014,8 @@
       <c r="CO51" s="24" t="n"/>
       <c r="CP51" s="24" t="n"/>
       <c r="CQ51" s="24" t="n"/>
-      <c r="CR51" s="24" t="inlineStr">
+      <c r="CR51" s="24" t="n"/>
+      <c r="CS51" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -16250,7 +16307,8 @@
       <c r="CO52" s="24" t="n"/>
       <c r="CP52" s="24" t="n"/>
       <c r="CQ52" s="24" t="n"/>
-      <c r="CR52" s="24" t="inlineStr">
+      <c r="CR52" s="24" t="n"/>
+      <c r="CS52" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -16542,7 +16600,8 @@
       <c r="CO53" s="24" t="n"/>
       <c r="CP53" s="24" t="n"/>
       <c r="CQ53" s="24" t="n"/>
-      <c r="CR53" s="24" t="inlineStr">
+      <c r="CR53" s="24" t="n"/>
+      <c r="CS53" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -16834,7 +16893,8 @@
       <c r="CO54" s="24" t="n"/>
       <c r="CP54" s="24" t="n"/>
       <c r="CQ54" s="24" t="n"/>
-      <c r="CR54" s="24" t="inlineStr">
+      <c r="CR54" s="24" t="n"/>
+      <c r="CS54" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -17126,7 +17186,8 @@
       <c r="CO55" s="24" t="n"/>
       <c r="CP55" s="24" t="n"/>
       <c r="CQ55" s="24" t="n"/>
-      <c r="CR55" s="24" t="inlineStr">
+      <c r="CR55" s="24" t="n"/>
+      <c r="CS55" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -17394,7 +17455,8 @@
       <c r="CO56" s="24" t="n"/>
       <c r="CP56" s="24" t="n"/>
       <c r="CQ56" s="24" t="n"/>
-      <c r="CR56" s="24" t="inlineStr">
+      <c r="CR56" s="24" t="n"/>
+      <c r="CS56" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -17686,7 +17748,8 @@
       <c r="CO57" s="24" t="n"/>
       <c r="CP57" s="24" t="n"/>
       <c r="CQ57" s="24" t="n"/>
-      <c r="CR57" s="24" t="inlineStr">
+      <c r="CR57" s="24" t="n"/>
+      <c r="CS57" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -17773,18 +17836,38 @@
       </c>
       <c r="U58" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V58" s="24" t="n"/>
-      <c r="W58" s="26" t="n"/>
-      <c r="X58" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V58" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W58" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X58" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y58" s="25" t="n"/>
-      <c r="Z58" s="26" t="n"/>
-      <c r="AA58" s="28" t="n"/>
-      <c r="AB58" s="28" t="n"/>
-      <c r="AC58" s="30" t="n"/>
-      <c r="AD58" s="24" t="n"/>
+      <c r="Z58" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="AA58" s="28" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AB58" s="28" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AC58" s="30" t="n">
+        <v>0.8197</v>
+      </c>
+      <c r="AD58" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:57:38.643502Z</t>
+        </is>
+      </c>
       <c r="AE58" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-g2a-js-2026-08-04).</t>
@@ -17927,8 +18010,12 @@
       <c r="BN58" s="28" t="n"/>
       <c r="BO58" s="28" t="n"/>
       <c r="BP58" s="25" t="n"/>
-      <c r="BQ58" s="27" t="n"/>
-      <c r="BR58" s="28" t="n"/>
+      <c r="BQ58" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BR58" s="28" t="n">
+        <v>0.55</v>
+      </c>
       <c r="BS58" s="28" t="n"/>
       <c r="BT58" s="28" t="n"/>
       <c r="BU58" s="25" t="n"/>
@@ -17954,7 +18041,8 @@
       <c r="CO58" s="24" t="n"/>
       <c r="CP58" s="24" t="n"/>
       <c r="CQ58" s="24" t="n"/>
-      <c r="CR58" s="24" t="inlineStr">
+      <c r="CR58" s="24" t="n"/>
+      <c r="CS58" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -18041,18 +18129,38 @@
       </c>
       <c r="U59" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V59" s="24" t="n"/>
-      <c r="W59" s="26" t="n"/>
-      <c r="X59" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V59" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y59" s="25" t="n"/>
-      <c r="Z59" s="26" t="n"/>
-      <c r="AA59" s="28" t="n"/>
-      <c r="AB59" s="28" t="n"/>
-      <c r="AC59" s="30" t="n"/>
-      <c r="AD59" s="24" t="n"/>
+      <c r="Z59" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="AA59" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB59" s="28" t="n">
+        <v>-0.000402</v>
+      </c>
+      <c r="AC59" s="30" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD59" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T11:57:40.271226Z</t>
+        </is>
+      </c>
       <c r="AE59" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-cs2-ign-sta-2026-08-04).</t>
@@ -18065,7 +18173,7 @@
       </c>
       <c r="AG59" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH59" s="24" t="n"/>
@@ -18195,8 +18303,12 @@
       <c r="BN59" s="28" t="n"/>
       <c r="BO59" s="28" t="n"/>
       <c r="BP59" s="25" t="n"/>
-      <c r="BQ59" s="27" t="n"/>
-      <c r="BR59" s="28" t="n"/>
+      <c r="BQ59" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BR59" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="BS59" s="28" t="n"/>
       <c r="BT59" s="28" t="n"/>
       <c r="BU59" s="25" t="n"/>
@@ -18222,7 +18334,8 @@
       <c r="CO59" s="24" t="n"/>
       <c r="CP59" s="24" t="n"/>
       <c r="CQ59" s="24" t="n"/>
-      <c r="CR59" s="24" t="inlineStr">
+      <c r="CR59" s="24" t="n"/>
+      <c r="CS59" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -18309,18 +18422,38 @@
       </c>
       <c r="U60" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V60" s="24" t="n"/>
-      <c r="W60" s="26" t="n"/>
-      <c r="X60" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V60" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W60" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X60" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y60" s="25" t="n"/>
-      <c r="Z60" s="26" t="n"/>
-      <c r="AA60" s="28" t="n"/>
-      <c r="AB60" s="28" t="n"/>
-      <c r="AC60" s="30" t="n"/>
-      <c r="AD60" s="24" t="n"/>
+      <c r="Z60" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA60" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB60" s="28" t="n">
+        <v>0.000529</v>
+      </c>
+      <c r="AC60" s="30" t="n">
+        <v>0.7874</v>
+      </c>
+      <c r="AD60" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:03:06.444544Z</t>
+        </is>
+      </c>
       <c r="AE60" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-cs2-encep-icp-2026-08-04).</t>
@@ -18463,8 +18596,12 @@
       <c r="BN60" s="28" t="n"/>
       <c r="BO60" s="28" t="n"/>
       <c r="BP60" s="25" t="n"/>
-      <c r="BQ60" s="27" t="n"/>
-      <c r="BR60" s="28" t="n"/>
+      <c r="BQ60" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR60" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="BS60" s="28" t="n"/>
       <c r="BT60" s="28" t="n"/>
       <c r="BU60" s="25" t="n"/>
@@ -18490,7 +18627,8 @@
       <c r="CO60" s="24" t="n"/>
       <c r="CP60" s="24" t="n"/>
       <c r="CQ60" s="24" t="n"/>
-      <c r="CR60" s="24" t="inlineStr">
+      <c r="CR60" s="24" t="n"/>
+      <c r="CS60" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -18577,18 +18715,38 @@
       </c>
       <c r="U61" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V61" s="24" t="n"/>
-      <c r="W61" s="26" t="n"/>
-      <c r="X61" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V61" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W61" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y61" s="25" t="n"/>
-      <c r="Z61" s="26" t="n"/>
-      <c r="AA61" s="28" t="n"/>
-      <c r="AB61" s="28" t="n"/>
-      <c r="AC61" s="30" t="n"/>
-      <c r="AD61" s="24" t="n"/>
+      <c r="Z61" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="AA61" s="28" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AB61" s="28" t="n">
+        <v>-0.000196</v>
+      </c>
+      <c r="AC61" s="30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD61" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:03:08.153056Z</t>
+        </is>
+      </c>
       <c r="AE61" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-cs2-sashi-pha-2026-08-04).</t>
@@ -18731,8 +18889,12 @@
       <c r="BN61" s="28" t="n"/>
       <c r="BO61" s="28" t="n"/>
       <c r="BP61" s="25" t="n"/>
-      <c r="BQ61" s="27" t="n"/>
-      <c r="BR61" s="28" t="n"/>
+      <c r="BQ61" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BR61" s="28" t="n">
+        <v>0.49</v>
+      </c>
       <c r="BS61" s="28" t="n"/>
       <c r="BT61" s="28" t="n"/>
       <c r="BU61" s="25" t="n"/>
@@ -18758,7 +18920,8 @@
       <c r="CO61" s="24" t="n"/>
       <c r="CP61" s="24" t="n"/>
       <c r="CQ61" s="24" t="n"/>
-      <c r="CR61" s="24" t="inlineStr">
+      <c r="CR61" s="24" t="n"/>
+      <c r="CS61" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -18845,18 +19008,38 @@
       </c>
       <c r="U62" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V62" s="24" t="n"/>
-      <c r="W62" s="26" t="n"/>
-      <c r="X62" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V62" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W62" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X62" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y62" s="25" t="n"/>
-      <c r="Z62" s="26" t="n"/>
-      <c r="AA62" s="28" t="n"/>
-      <c r="AB62" s="28" t="n"/>
-      <c r="AC62" s="30" t="n"/>
-      <c r="AD62" s="24" t="n"/>
+      <c r="Z62" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA62" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB62" s="28" t="n">
+        <v>-0.000516</v>
+      </c>
+      <c r="AC62" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD62" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:03:09.721402Z</t>
+        </is>
+      </c>
       <c r="AE62" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=aec-cs2-plnc-scn-2026-08-04).</t>
@@ -18869,7 +19052,7 @@
       </c>
       <c r="AG62" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH62" s="24" t="n"/>
@@ -18999,8 +19182,12 @@
       <c r="BN62" s="28" t="n"/>
       <c r="BO62" s="28" t="n"/>
       <c r="BP62" s="25" t="n"/>
-      <c r="BQ62" s="27" t="n"/>
-      <c r="BR62" s="28" t="n"/>
+      <c r="BQ62" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR62" s="28" t="n">
+        <v>0.53</v>
+      </c>
       <c r="BS62" s="28" t="n"/>
       <c r="BT62" s="28" t="n"/>
       <c r="BU62" s="25" t="n"/>
@@ -19026,7 +19213,8 @@
       <c r="CO62" s="24" t="n"/>
       <c r="CP62" s="24" t="n"/>
       <c r="CQ62" s="24" t="n"/>
-      <c r="CR62" s="24" t="inlineStr">
+      <c r="CR62" s="24" t="n"/>
+      <c r="CS62" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -19113,18 +19301,38 @@
       </c>
       <c r="U63" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V63" s="24" t="n"/>
-      <c r="W63" s="26" t="n"/>
-      <c r="X63" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V63" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W63" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X63" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y63" s="25" t="n"/>
-      <c r="Z63" s="26" t="n"/>
-      <c r="AA63" s="28" t="n"/>
-      <c r="AB63" s="28" t="n"/>
-      <c r="AC63" s="30" t="n"/>
-      <c r="AD63" s="24" t="n"/>
+      <c r="Z63" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="AA63" s="28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB63" s="28" t="n">
+        <v>0.000168</v>
+      </c>
+      <c r="AC63" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD63" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T14:03:11.366824Z</t>
+        </is>
+      </c>
       <c r="AE63" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5800 (market_slug=aec-cs2-ace-bca-2026-08-04).</t>
@@ -19137,7 +19345,7 @@
       </c>
       <c r="AG63" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH63" s="24" t="n"/>
@@ -19267,8 +19475,12 @@
       <c r="BN63" s="28" t="n"/>
       <c r="BO63" s="28" t="n"/>
       <c r="BP63" s="25" t="n"/>
-      <c r="BQ63" s="27" t="n"/>
-      <c r="BR63" s="28" t="n"/>
+      <c r="BQ63" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BR63" s="28" t="n">
+        <v>0.58</v>
+      </c>
       <c r="BS63" s="28" t="n"/>
       <c r="BT63" s="28" t="n"/>
       <c r="BU63" s="25" t="n"/>
@@ -19294,7 +19506,8 @@
       <c r="CO63" s="24" t="n"/>
       <c r="CP63" s="24" t="n"/>
       <c r="CQ63" s="24" t="n"/>
-      <c r="CR63" s="24" t="inlineStr">
+      <c r="CR63" s="24" t="n"/>
+      <c r="CS63" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -19303,12 +19516,12 @@
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>99b6896bb4514386</t>
+          <t>71253e3d5d7f47e2</t>
         </is>
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T12:02:30.114508Z</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
@@ -19318,7 +19531,7 @@
       </c>
       <c r="D64" s="24" t="inlineStr">
         <is>
-          <t>71213</t>
+          <t>71280</t>
         </is>
       </c>
       <c r="E64" s="24" t="inlineStr">
@@ -19328,12 +19541,12 @@
       </c>
       <c r="F64" s="24" t="inlineStr">
         <is>
-          <t>Leo Team</t>
+          <t>ex-MANA eSports</t>
         </is>
       </c>
       <c r="G64" s="24" t="inlineStr">
         <is>
-          <t>Bushido Wildcats</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="H64" s="24" t="inlineStr">
@@ -19353,26 +19566,26 @@
         </is>
       </c>
       <c r="L64" s="26" t="n">
-        <v>104</v>
+        <v>-203</v>
       </c>
       <c r="M64" s="27" t="n">
-        <v>2.04</v>
+        <v>1.492611</v>
       </c>
       <c r="N64" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.669967</v>
       </c>
       <c r="O64" s="28" t="n">
-        <v>0.719577</v>
+        <v>0.640787</v>
       </c>
       <c r="P64" s="28" t="n"/>
       <c r="Q64" s="28" t="n">
-        <v>0.229381</v>
+        <v>-0.02918</v>
       </c>
       <c r="R64" s="26" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="S64" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T64" s="24" t="inlineStr">
         <is>
@@ -19395,7 +19608,7 @@
       <c r="AD64" s="24" t="n"/>
       <c r="AE64" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4900 (market_slug=aec-cs2-bw-leo-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-bmb-exmana-2026-08-04).</t>
         </is>
       </c>
       <c r="AF64" s="31" t="inlineStr">
@@ -19431,37 +19644,37 @@
       </c>
       <c r="AO64" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>NO_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP64" s="24" t="inlineStr">
         <is>
-          <t>Leo Team</t>
+          <t>ex-MANA eSports</t>
         </is>
       </c>
       <c r="AQ64" s="24" t="inlineStr">
         <is>
-          <t>Leo Team</t>
+          <t>ex-MANA eSports</t>
         </is>
       </c>
       <c r="AR64" s="24" t="inlineStr">
         <is>
-          <t>Leo Team</t>
+          <t>ex-MANA eSports</t>
         </is>
       </c>
       <c r="AS64" s="24" t="inlineStr">
         <is>
-          <t>Bushido Wildcats</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AT64" s="24" t="inlineStr">
         <is>
-          <t>Bushido Wildcats</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AU64" s="24" t="inlineStr">
         <is>
-          <t>Bushido Wildcats</t>
+          <t>BASEMENT BOYS</t>
         </is>
       </c>
       <c r="AV64" s="24" t="n"/>
@@ -19479,7 +19692,7 @@
       </c>
       <c r="BA64" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
         </is>
       </c>
       <c r="BB64" s="24" t="inlineStr">
@@ -19494,7 +19707,7 @@
       </c>
       <c r="BD64" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
         </is>
       </c>
       <c r="BE64" s="24" t="inlineStr">
@@ -19514,7 +19727,7 @@
       </c>
       <c r="BH64" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:27.119976Z</t>
+          <t>2026-08-04T12:01:37.143655Z</t>
         </is>
       </c>
       <c r="BI64" s="24" t="inlineStr">
@@ -19524,13 +19737,13 @@
       </c>
       <c r="BJ64" s="25" t="n"/>
       <c r="BK64" s="26" t="n">
-        <v>104</v>
+        <v>-203</v>
       </c>
       <c r="BL64" s="27" t="n">
-        <v>2.04</v>
+        <v>1.492611</v>
       </c>
       <c r="BM64" s="28" t="n">
-        <v>0.490196</v>
+        <v>0.669967</v>
       </c>
       <c r="BN64" s="28" t="n"/>
       <c r="BO64" s="28" t="n"/>
@@ -19562,21 +19775,22 @@
       <c r="CO64" s="24" t="n"/>
       <c r="CP64" s="24" t="n"/>
       <c r="CQ64" s="24" t="n"/>
-      <c r="CR64" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
+      <c r="CR64" s="24" t="n"/>
+      <c r="CS64" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>01b9fb5a4ee449d0</t>
+          <t>04bf6223d1074ca1</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T12:02:30.114508Z</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
@@ -19586,7 +19800,7 @@
       </c>
       <c r="D65" s="24" t="inlineStr">
         <is>
-          <t>71280</t>
+          <t>71213</t>
         </is>
       </c>
       <c r="E65" s="24" t="inlineStr">
@@ -19596,12 +19810,12 @@
       </c>
       <c r="F65" s="24" t="inlineStr">
         <is>
-          <t>ex-MANA eSports</t>
+          <t>Leo Team</t>
         </is>
       </c>
       <c r="G65" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="H65" s="24" t="inlineStr">
@@ -19621,26 +19835,26 @@
         </is>
       </c>
       <c r="L65" s="26" t="n">
-        <v>-203</v>
+        <v>-104</v>
       </c>
       <c r="M65" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.961538</v>
       </c>
       <c r="N65" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.509804</v>
       </c>
       <c r="O65" s="28" t="n">
-        <v>0.640948</v>
+        <v>0.719395</v>
       </c>
       <c r="P65" s="28" t="n"/>
       <c r="Q65" s="28" t="n">
-        <v>-0.029019</v>
+        <v>0.209591</v>
       </c>
       <c r="R65" s="26" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="S65" s="29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="T65" s="24" t="inlineStr">
         <is>
@@ -19663,7 +19877,7 @@
       <c r="AD65" s="24" t="n"/>
       <c r="AE65" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6700 (market_slug=aec-cs2-bmb-exmana-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-bw-leo-2026-08-04).</t>
         </is>
       </c>
       <c r="AF65" s="31" t="inlineStr">
@@ -19699,37 +19913,37 @@
       </c>
       <c r="AO65" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_LOW_EDGE</t>
+          <t>NO_CALL_MODEL_UNVALIDATED</t>
         </is>
       </c>
       <c r="AP65" s="24" t="inlineStr">
         <is>
-          <t>ex-MANA eSports</t>
+          <t>Leo Team</t>
         </is>
       </c>
       <c r="AQ65" s="24" t="inlineStr">
         <is>
-          <t>ex-MANA eSports</t>
+          <t>Leo Team</t>
         </is>
       </c>
       <c r="AR65" s="24" t="inlineStr">
         <is>
-          <t>ex-MANA eSports</t>
+          <t>Leo Team</t>
         </is>
       </c>
       <c r="AS65" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="AT65" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="AU65" s="24" t="inlineStr">
         <is>
-          <t>BASEMENT BOYS</t>
+          <t>Bushido Wildcats</t>
         </is>
       </c>
       <c r="AV65" s="24" t="n"/>
@@ -19747,7 +19961,7 @@
       </c>
       <c r="BA65" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
         </is>
       </c>
       <c r="BB65" s="24" t="inlineStr">
@@ -19762,7 +19976,7 @@
       </c>
       <c r="BD65" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
         </is>
       </c>
       <c r="BE65" s="24" t="inlineStr">
@@ -19782,7 +19996,7 @@
       </c>
       <c r="BH65" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:27.768400Z</t>
+          <t>2026-08-04T12:01:38.137077Z</t>
         </is>
       </c>
       <c r="BI65" s="24" t="inlineStr">
@@ -19792,13 +20006,13 @@
       </c>
       <c r="BJ65" s="25" t="n"/>
       <c r="BK65" s="26" t="n">
-        <v>-203</v>
+        <v>-104</v>
       </c>
       <c r="BL65" s="27" t="n">
-        <v>1.492611</v>
+        <v>1.961538</v>
       </c>
       <c r="BM65" s="28" t="n">
-        <v>0.669967</v>
+        <v>0.509804</v>
       </c>
       <c r="BN65" s="28" t="n"/>
       <c r="BO65" s="28" t="n"/>
@@ -19830,21 +20044,22 @@
       <c r="CO65" s="24" t="n"/>
       <c r="CP65" s="24" t="n"/>
       <c r="CQ65" s="24" t="n"/>
-      <c r="CR65" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR65" s="24" t="n"/>
+      <c r="CS65" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="24" t="inlineStr">
         <is>
-          <t>5bf1ae41f31a473a</t>
+          <t>8bb216674c4240bc</t>
         </is>
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T12:02:30.114508Z</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
@@ -19889,23 +20104,23 @@
         </is>
       </c>
       <c r="L66" s="26" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="M66" s="27" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="N66" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.380228</v>
       </c>
       <c r="O66" s="28" t="n">
-        <v>0.527057</v>
+        <v>0.526874</v>
       </c>
       <c r="P66" s="28" t="n"/>
       <c r="Q66" s="28" t="n">
-        <v>0.136432</v>
+        <v>0.146646</v>
       </c>
       <c r="R66" s="26" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="S66" s="29" t="n">
         <v>1</v>
@@ -19931,7 +20146,7 @@
       <c r="AD66" s="24" t="n"/>
       <c r="AE66" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-cs2-plnc-wco-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-cs2-plnc-wco-2026-08-04).</t>
         </is>
       </c>
       <c r="AF66" s="31" t="inlineStr">
@@ -20015,7 +20230,7 @@
       </c>
       <c r="BA66" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
         </is>
       </c>
       <c r="BB66" s="24" t="inlineStr">
@@ -20030,7 +20245,7 @@
       </c>
       <c r="BD66" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
         </is>
       </c>
       <c r="BE66" s="24" t="inlineStr">
@@ -20050,7 +20265,7 @@
       </c>
       <c r="BH66" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:28.310332Z</t>
+          <t>2026-08-04T12:01:39.296037Z</t>
         </is>
       </c>
       <c r="BI66" s="24" t="inlineStr">
@@ -20060,13 +20275,13 @@
       </c>
       <c r="BJ66" s="25" t="n"/>
       <c r="BK66" s="26" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="BL66" s="27" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="BM66" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.380228</v>
       </c>
       <c r="BN66" s="28" t="n"/>
       <c r="BO66" s="28" t="n"/>
@@ -20098,7 +20313,8 @@
       <c r="CO66" s="24" t="n"/>
       <c r="CP66" s="24" t="n"/>
       <c r="CQ66" s="24" t="n"/>
-      <c r="CR66" s="24" t="inlineStr">
+      <c r="CR66" s="24" t="n"/>
+      <c r="CS66" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -20107,12 +20323,12 @@
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>e2d0b33be84e4f12</t>
+          <t>96126276e7a74d7e</t>
         </is>
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T12:02:30.114508Z</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
@@ -20122,7 +20338,7 @@
       </c>
       <c r="D67" s="24" t="inlineStr">
         <is>
-          <t>71318</t>
+          <t>68437</t>
         </is>
       </c>
       <c r="E67" s="24" t="inlineStr">
@@ -20132,12 +20348,12 @@
       </c>
       <c r="F67" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>GenOne</t>
         </is>
       </c>
       <c r="G67" s="24" t="inlineStr">
         <is>
-          <t>Liquid</t>
+          <t>Nemiga</t>
         </is>
       </c>
       <c r="H67" s="24" t="inlineStr">
@@ -20157,26 +20373,26 @@
         </is>
       </c>
       <c r="L67" s="26" t="n">
-        <v>-233</v>
+        <v>-163</v>
       </c>
       <c r="M67" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.613497</v>
       </c>
       <c r="N67" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.619772</v>
       </c>
       <c r="O67" s="28" t="n">
-        <v>0.689596</v>
+        <v>0.5179</v>
       </c>
       <c r="P67" s="28" t="n"/>
       <c r="Q67" s="28" t="n">
-        <v>-0.010104</v>
+        <v>-0.101872</v>
       </c>
       <c r="R67" s="26" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S67" s="29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T67" s="24" t="inlineStr">
         <is>
@@ -20199,7 +20415,7 @@
       <c r="AD67" s="24" t="n"/>
       <c r="AE67" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-cs2-tl-9ine-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-nemi-g1-2026-08-04).</t>
         </is>
       </c>
       <c r="AF67" s="31" t="inlineStr">
@@ -20240,32 +20456,32 @@
       </c>
       <c r="AP67" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>GenOne</t>
         </is>
       </c>
       <c r="AQ67" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>GenOne</t>
         </is>
       </c>
       <c r="AR67" s="24" t="inlineStr">
         <is>
-          <t>9INE</t>
+          <t>GenOne</t>
         </is>
       </c>
       <c r="AS67" s="24" t="inlineStr">
         <is>
-          <t>Liquid</t>
+          <t>Nemiga</t>
         </is>
       </c>
       <c r="AT67" s="24" t="inlineStr">
         <is>
-          <t>Liquid</t>
+          <t>Nemiga</t>
         </is>
       </c>
       <c r="AU67" s="24" t="inlineStr">
         <is>
-          <t>Liquid</t>
+          <t>Nemiga</t>
         </is>
       </c>
       <c r="AV67" s="24" t="n"/>
@@ -20283,7 +20499,7 @@
       </c>
       <c r="BA67" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
         </is>
       </c>
       <c r="BB67" s="24" t="inlineStr">
@@ -20298,7 +20514,7 @@
       </c>
       <c r="BD67" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
         </is>
       </c>
       <c r="BE67" s="24" t="inlineStr">
@@ -20318,7 +20534,7 @@
       </c>
       <c r="BH67" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:29.177358Z</t>
+          <t>2026-08-04T12:01:41.460173Z</t>
         </is>
       </c>
       <c r="BI67" s="24" t="inlineStr">
@@ -20328,13 +20544,13 @@
       </c>
       <c r="BJ67" s="25" t="n"/>
       <c r="BK67" s="26" t="n">
-        <v>-233</v>
+        <v>-163</v>
       </c>
       <c r="BL67" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.613497</v>
       </c>
       <c r="BM67" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.619772</v>
       </c>
       <c r="BN67" s="28" t="n"/>
       <c r="BO67" s="28" t="n"/>
@@ -20366,7 +20582,8 @@
       <c r="CO67" s="24" t="n"/>
       <c r="CP67" s="24" t="n"/>
       <c r="CQ67" s="24" t="n"/>
-      <c r="CR67" s="24" t="inlineStr">
+      <c r="CR67" s="24" t="n"/>
+      <c r="CS67" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -20375,12 +20592,12 @@
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="24" t="inlineStr">
         <is>
-          <t>923a61f8a41e4ffa</t>
+          <t>66b3a1ade0a04bd3</t>
         </is>
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T12:02:30.114508Z</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
@@ -20390,7 +20607,7 @@
       </c>
       <c r="D68" s="24" t="inlineStr">
         <is>
-          <t>68437</t>
+          <t>71319</t>
         </is>
       </c>
       <c r="E68" s="24" t="inlineStr">
@@ -20400,12 +20617,12 @@
       </c>
       <c r="F68" s="24" t="inlineStr">
         <is>
-          <t>GenOne</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="G68" s="24" t="inlineStr">
         <is>
-          <t>Nemiga</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="H68" s="24" t="inlineStr">
@@ -20415,7 +20632,7 @@
       </c>
       <c r="I68" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J68" s="25" t="n"/>
@@ -20425,23 +20642,23 @@
         </is>
       </c>
       <c r="L68" s="26" t="n">
-        <v>-163</v>
+        <v>163</v>
       </c>
       <c r="M68" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.63</v>
       </c>
       <c r="N68" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.380228</v>
       </c>
       <c r="O68" s="28" t="n">
-        <v>0.518066</v>
+        <v>0.509432</v>
       </c>
       <c r="P68" s="28" t="n"/>
       <c r="Q68" s="28" t="n">
-        <v>-0.101706</v>
+        <v>0.129204</v>
       </c>
       <c r="R68" s="26" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S68" s="29" t="n">
         <v>1</v>
@@ -20467,7 +20684,7 @@
       <c r="AD68" s="24" t="n"/>
       <c r="AE68" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-nemi-g1-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-cs2-jpu-enjoy-2026-08-04).</t>
         </is>
       </c>
       <c r="AF68" s="31" t="inlineStr">
@@ -20508,32 +20725,32 @@
       </c>
       <c r="AP68" s="24" t="inlineStr">
         <is>
-          <t>GenOne</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AQ68" s="24" t="inlineStr">
         <is>
-          <t>GenOne</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AR68" s="24" t="inlineStr">
         <is>
-          <t>GenOne</t>
+          <t>ENJOY</t>
         </is>
       </c>
       <c r="AS68" s="24" t="inlineStr">
         <is>
-          <t>Nemiga</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AT68" s="24" t="inlineStr">
         <is>
-          <t>Nemiga</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AU68" s="24" t="inlineStr">
         <is>
-          <t>Nemiga</t>
+          <t>Just Players</t>
         </is>
       </c>
       <c r="AV68" s="24" t="n"/>
@@ -20551,7 +20768,7 @@
       </c>
       <c r="BA68" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
         </is>
       </c>
       <c r="BB68" s="24" t="inlineStr">
@@ -20566,7 +20783,7 @@
       </c>
       <c r="BD68" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
         </is>
       </c>
       <c r="BE68" s="24" t="inlineStr">
@@ -20586,7 +20803,7 @@
       </c>
       <c r="BH68" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:30.455227Z</t>
+          <t>2026-08-04T12:01:42.547114Z</t>
         </is>
       </c>
       <c r="BI68" s="24" t="inlineStr">
@@ -20596,13 +20813,13 @@
       </c>
       <c r="BJ68" s="25" t="n"/>
       <c r="BK68" s="26" t="n">
-        <v>-163</v>
+        <v>163</v>
       </c>
       <c r="BL68" s="27" t="n">
-        <v>1.613497</v>
+        <v>2.63</v>
       </c>
       <c r="BM68" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.380228</v>
       </c>
       <c r="BN68" s="28" t="n"/>
       <c r="BO68" s="28" t="n"/>
@@ -20634,21 +20851,22 @@
       <c r="CO68" s="24" t="n"/>
       <c r="CP68" s="24" t="n"/>
       <c r="CQ68" s="24" t="n"/>
-      <c r="CR68" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR68" s="24" t="n"/>
+      <c r="CS68" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>75a14d1764b04b86</t>
+          <t>6d604382a0a344f2</t>
         </is>
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T12:02:30.114508Z</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
@@ -20658,7 +20876,7 @@
       </c>
       <c r="D69" s="24" t="inlineStr">
         <is>
-          <t>71319</t>
+          <t>71318</t>
         </is>
       </c>
       <c r="E69" s="24" t="inlineStr">
@@ -20668,12 +20886,12 @@
       </c>
       <c r="F69" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>9INE</t>
         </is>
       </c>
       <c r="G69" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>Liquid</t>
         </is>
       </c>
       <c r="H69" s="24" t="inlineStr">
@@ -20693,26 +20911,26 @@
         </is>
       </c>
       <c r="L69" s="26" t="n">
-        <v>-170</v>
+        <v>-233</v>
       </c>
       <c r="M69" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.429185</v>
       </c>
       <c r="N69" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.6997</v>
       </c>
       <c r="O69" s="28" t="n">
-        <v>0.505173</v>
+        <v>0.689352</v>
       </c>
       <c r="P69" s="28" t="n"/>
       <c r="Q69" s="28" t="n">
-        <v>-0.124457</v>
+        <v>-0.010348</v>
       </c>
       <c r="R69" s="26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S69" s="29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T69" s="24" t="inlineStr">
         <is>
@@ -20735,7 +20953,7 @@
       <c r="AD69" s="24" t="n"/>
       <c r="AE69" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-cs2-jpu-enjoy-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-cs2-tl-9ine-2026-08-04).</t>
         </is>
       </c>
       <c r="AF69" s="31" t="inlineStr">
@@ -20776,32 +20994,32 @@
       </c>
       <c r="AP69" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>9INE</t>
         </is>
       </c>
       <c r="AQ69" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>9INE</t>
         </is>
       </c>
       <c r="AR69" s="24" t="inlineStr">
         <is>
-          <t>ENJOY</t>
+          <t>9INE</t>
         </is>
       </c>
       <c r="AS69" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>Liquid</t>
         </is>
       </c>
       <c r="AT69" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>Liquid</t>
         </is>
       </c>
       <c r="AU69" s="24" t="inlineStr">
         <is>
-          <t>Just Players</t>
+          <t>Liquid</t>
         </is>
       </c>
       <c r="AV69" s="24" t="n"/>
@@ -20819,7 +21037,7 @@
       </c>
       <c r="BA69" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
         </is>
       </c>
       <c r="BB69" s="24" t="inlineStr">
@@ -20834,7 +21052,7 @@
       </c>
       <c r="BD69" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>c721353818b949592e0d9143f94caccefc04915eac71c58a5983a137fbf32d77</t>
         </is>
       </c>
       <c r="BE69" s="24" t="inlineStr">
@@ -20854,7 +21072,7 @@
       </c>
       <c r="BH69" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:31.204261Z</t>
+          <t>2026-08-04T12:01:43.680044Z</t>
         </is>
       </c>
       <c r="BI69" s="24" t="inlineStr">
@@ -20864,13 +21082,13 @@
       </c>
       <c r="BJ69" s="25" t="n"/>
       <c r="BK69" s="26" t="n">
-        <v>-170</v>
+        <v>-233</v>
       </c>
       <c r="BL69" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.429185</v>
       </c>
       <c r="BM69" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.6997</v>
       </c>
       <c r="BN69" s="28" t="n"/>
       <c r="BO69" s="28" t="n"/>
@@ -20902,7 +21120,8 @@
       <c r="CO69" s="24" t="n"/>
       <c r="CP69" s="24" t="n"/>
       <c r="CQ69" s="24" t="n"/>
-      <c r="CR69" s="24" t="inlineStr">
+      <c r="CR69" s="24" t="n"/>
+      <c r="CS69" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -20911,12 +21130,12 @@
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>5403069b65de4474</t>
+          <t>93292ab1c226496e</t>
         </is>
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T14:27:03.198804Z</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
@@ -20970,11 +21189,11 @@
         <v>0.62963</v>
       </c>
       <c r="O70" s="28" t="n">
-        <v>0.527057</v>
+        <v>0.526798</v>
       </c>
       <c r="P70" s="28" t="n"/>
       <c r="Q70" s="28" t="n">
-        <v>-0.102573</v>
+        <v>-0.102832</v>
       </c>
       <c r="R70" s="26" t="n">
         <v>0</v>
@@ -21087,7 +21306,7 @@
       </c>
       <c r="BA70" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BB70" s="24" t="inlineStr">
@@ -21102,7 +21321,7 @@
       </c>
       <c r="BD70" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BE70" s="24" t="inlineStr">
@@ -21122,7 +21341,7 @@
       </c>
       <c r="BH70" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:31.835843Z</t>
+          <t>2026-08-04T14:26:40.094577Z</t>
         </is>
       </c>
       <c r="BI70" s="24" t="inlineStr">
@@ -21170,7 +21389,8 @@
       <c r="CO70" s="24" t="n"/>
       <c r="CP70" s="24" t="n"/>
       <c r="CQ70" s="24" t="n"/>
-      <c r="CR70" s="24" t="inlineStr">
+      <c r="CR70" s="24" t="n"/>
+      <c r="CS70" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -21179,12 +21399,12 @@
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>26906cebafaa4543</t>
+          <t>f088b35924894980</t>
         </is>
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T14:27:03.198804Z</t>
         </is>
       </c>
       <c r="C71" s="24" t="inlineStr">
@@ -21238,11 +21458,11 @@
         <v>0.570815</v>
       </c>
       <c r="O71" s="28" t="n">
-        <v>0.527057</v>
+        <v>0.526798</v>
       </c>
       <c r="P71" s="28" t="n"/>
       <c r="Q71" s="28" t="n">
-        <v>-0.043758</v>
+        <v>-0.044017</v>
       </c>
       <c r="R71" s="26" t="n">
         <v>0</v>
@@ -21355,7 +21575,7 @@
       </c>
       <c r="BA71" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BB71" s="24" t="inlineStr">
@@ -21370,7 +21590,7 @@
       </c>
       <c r="BD71" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BE71" s="24" t="inlineStr">
@@ -21390,7 +21610,7 @@
       </c>
       <c r="BH71" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:32.634716Z</t>
+          <t>2026-08-04T14:26:40.578112Z</t>
         </is>
       </c>
       <c r="BI71" s="24" t="inlineStr">
@@ -21438,7 +21658,8 @@
       <c r="CO71" s="24" t="n"/>
       <c r="CP71" s="24" t="n"/>
       <c r="CQ71" s="24" t="n"/>
-      <c r="CR71" s="24" t="inlineStr">
+      <c r="CR71" s="24" t="n"/>
+      <c r="CS71" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -21447,12 +21668,12 @@
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="24" t="inlineStr">
         <is>
-          <t>c81385dbdf9b4700</t>
+          <t>cea59b111d1947d6</t>
         </is>
       </c>
       <c r="B72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T14:27:03.198804Z</t>
         </is>
       </c>
       <c r="C72" s="24" t="inlineStr">
@@ -21506,11 +21727,11 @@
         <v>0.680511</v>
       </c>
       <c r="O72" s="28" t="n">
-        <v>0.589593</v>
+        <v>0.589329</v>
       </c>
       <c r="P72" s="28" t="n"/>
       <c r="Q72" s="28" t="n">
-        <v>-0.090918</v>
+        <v>-0.091182</v>
       </c>
       <c r="R72" s="26" t="n">
         <v>0</v>
@@ -21623,7 +21844,7 @@
       </c>
       <c r="BA72" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BB72" s="24" t="inlineStr">
@@ -21638,7 +21859,7 @@
       </c>
       <c r="BD72" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BE72" s="24" t="inlineStr">
@@ -21658,7 +21879,7 @@
       </c>
       <c r="BH72" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:34.585574Z</t>
+          <t>2026-08-04T14:26:41.052332Z</t>
         </is>
       </c>
       <c r="BI72" s="24" t="inlineStr">
@@ -21706,7 +21927,8 @@
       <c r="CO72" s="24" t="n"/>
       <c r="CP72" s="24" t="n"/>
       <c r="CQ72" s="24" t="n"/>
-      <c r="CR72" s="24" t="inlineStr">
+      <c r="CR72" s="24" t="n"/>
+      <c r="CS72" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -21715,12 +21937,12 @@
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>64c05cb926774206</t>
+          <t>b7b5d837c0cd4942</t>
         </is>
       </c>
       <c r="B73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T14:27:03.198804Z</t>
         </is>
       </c>
       <c r="C73" s="24" t="inlineStr">
@@ -21765,20 +21987,20 @@
         </is>
       </c>
       <c r="L73" s="26" t="n">
-        <v>-133</v>
+        <v>-127</v>
       </c>
       <c r="M73" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.787402</v>
       </c>
       <c r="N73" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O73" s="28" t="n">
-        <v>0.516525</v>
+        <v>0.516198</v>
       </c>
       <c r="P73" s="28" t="n"/>
       <c r="Q73" s="28" t="n">
-        <v>-0.05429</v>
+        <v>-0.043273</v>
       </c>
       <c r="R73" s="26" t="n">
         <v>0</v>
@@ -21807,7 +22029,7 @@
       <c r="AD73" s="24" t="n"/>
       <c r="AE73" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-cs2-ef-inox-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5600 (market_slug=aec-cs2-ef-inox-2026-08-04).</t>
         </is>
       </c>
       <c r="AF73" s="31" t="inlineStr">
@@ -21891,7 +22113,7 @@
       </c>
       <c r="BA73" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BB73" s="24" t="inlineStr">
@@ -21906,7 +22128,7 @@
       </c>
       <c r="BD73" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BE73" s="24" t="inlineStr">
@@ -21926,7 +22148,7 @@
       </c>
       <c r="BH73" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:35.266965Z</t>
+          <t>2026-08-04T14:26:41.781184Z</t>
         </is>
       </c>
       <c r="BI73" s="24" t="inlineStr">
@@ -21936,13 +22158,13 @@
       </c>
       <c r="BJ73" s="25" t="n"/>
       <c r="BK73" s="26" t="n">
-        <v>-133</v>
+        <v>-127</v>
       </c>
       <c r="BL73" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.787402</v>
       </c>
       <c r="BM73" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN73" s="28" t="n"/>
       <c r="BO73" s="28" t="n"/>
@@ -21974,7 +22196,8 @@
       <c r="CO73" s="24" t="n"/>
       <c r="CP73" s="24" t="n"/>
       <c r="CQ73" s="24" t="n"/>
-      <c r="CR73" s="24" t="inlineStr">
+      <c r="CR73" s="24" t="n"/>
+      <c r="CS73" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -21983,12 +22206,12 @@
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="24" t="inlineStr">
         <is>
-          <t>f2cec846a27b4cf1</t>
+          <t>e3630e6d84d1436f</t>
         </is>
       </c>
       <c r="B74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T14:27:03.198804Z</t>
         </is>
       </c>
       <c r="C74" s="24" t="inlineStr">
@@ -21998,7 +22221,7 @@
       </c>
       <c r="D74" s="24" t="inlineStr">
         <is>
-          <t>71321</t>
+          <t>71337</t>
         </is>
       </c>
       <c r="E74" s="24" t="inlineStr">
@@ -22008,12 +22231,12 @@
       </c>
       <c r="F74" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="G74" s="24" t="inlineStr">
         <is>
-          <t>UNiTY esports</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="H74" s="24" t="inlineStr">
@@ -22023,7 +22246,7 @@
       </c>
       <c r="I74" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J74" s="25" t="n"/>
@@ -22033,26 +22256,26 @@
         </is>
       </c>
       <c r="L74" s="26" t="n">
-        <v>-104</v>
+        <v>-122</v>
       </c>
       <c r="M74" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.819672</v>
       </c>
       <c r="N74" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.54955</v>
       </c>
       <c r="O74" s="28" t="n">
-        <v>0.500399</v>
+        <v>0.571449</v>
       </c>
       <c r="P74" s="28" t="n"/>
       <c r="Q74" s="28" t="n">
-        <v>-0.009405</v>
+        <v>0.021899</v>
       </c>
       <c r="R74" s="26" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="S74" s="29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T74" s="24" t="inlineStr">
         <is>
@@ -22075,7 +22298,7 @@
       <c r="AD74" s="24" t="n"/>
       <c r="AE74" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.5100 (market_slug=aec-cs2-unity-eyn-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5500 (market_slug=aec-cs2-for-agc-2026-08-04).</t>
         </is>
       </c>
       <c r="AF74" s="31" t="inlineStr">
@@ -22093,7 +22316,7 @@
       <c r="AJ74" s="31" t="n"/>
       <c r="AK74" s="24" t="inlineStr">
         <is>
-          <t>research_observation</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL74" s="26" t="n">
@@ -22101,47 +22324,47 @@
       </c>
       <c r="AM74" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN74" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL</t>
+          <t>CALL</t>
         </is>
       </c>
       <c r="AO74" s="24" t="inlineStr">
         <is>
-          <t>NO_CALL_MODEL_UNVALIDATED</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP74" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="AQ74" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="AR74" s="24" t="inlineStr">
         <is>
-          <t>ex-Young Ninjas</t>
+          <t>A Great Chaos</t>
         </is>
       </c>
       <c r="AS74" s="24" t="inlineStr">
         <is>
-          <t>UNiTY esports</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AT74" s="24" t="inlineStr">
         <is>
-          <t>UNiTY esports</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AU74" s="24" t="inlineStr">
         <is>
-          <t>UNiTY esports</t>
+          <t>Fortress</t>
         </is>
       </c>
       <c r="AV74" s="24" t="n"/>
@@ -22159,7 +22382,7 @@
       </c>
       <c r="BA74" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BB74" s="24" t="inlineStr">
@@ -22174,7 +22397,7 @@
       </c>
       <c r="BD74" s="24" t="inlineStr">
         <is>
-          <t>2e5d465a17379306940528ff103c7508aad908ecb9a4879bb8031bb88a86443c</t>
+          <t>00cdf82f3d57942970af15209b096125d6c9c414d900ca7bc63b9b6d0234f3e3</t>
         </is>
       </c>
       <c r="BE74" s="24" t="inlineStr">
@@ -22194,7 +22417,7 @@
       </c>
       <c r="BH74" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:35.801312Z</t>
+          <t>2026-08-04T14:26:42.351782Z</t>
         </is>
       </c>
       <c r="BI74" s="24" t="inlineStr">
@@ -22204,13 +22427,13 @@
       </c>
       <c r="BJ74" s="25" t="n"/>
       <c r="BK74" s="26" t="n">
-        <v>-104</v>
+        <v>-122</v>
       </c>
       <c r="BL74" s="27" t="n">
-        <v>1.961538</v>
+        <v>1.819672</v>
       </c>
       <c r="BM74" s="28" t="n">
-        <v>0.509804</v>
+        <v>0.54955</v>
       </c>
       <c r="BN74" s="28" t="n"/>
       <c r="BO74" s="28" t="n"/>
@@ -22242,31 +22465,32 @@
       <c r="CO74" s="24" t="n"/>
       <c r="CP74" s="24" t="n"/>
       <c r="CQ74" s="24" t="n"/>
-      <c r="CR74" s="24" t="inlineStr">
-        <is>
-          <t>False</t>
+      <c r="CR74" s="24" t="n"/>
+      <c r="CS74" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>1aa51a1f9b594394</t>
+          <t>1ee97222632244dc</t>
         </is>
       </c>
       <c r="B75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T08:56:55.041466Z</t>
+          <t>2026-08-04T14:27:03.198804Z</t>
         </is>
       </c>
       <c r="C75" s="24" t="inlineStr">
         <is>
-          <t>2026-08-04T18:30:00Z</t>
+          <t>2026-08-04T17:00:00Z</t>
         </is>
       </c>
       <c r="D75" s="24" t="inlineStr">
         <is>
-          <t>70533</t>
+          <t>71321</t>
         </is>
       </c>
       <c r="E75" s="24" t="inlineStr">
@@ -22276,12 +22500,12 @@
       </c>
       <c r="F75" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="G75" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="H75" s="24" t="inlineStr">
@@ -22291,7 +22515,7 @@
       </c>
       <c r="I75" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J75" s="25" t="n"/>
@@ -22301,23 +22525,23 @@
         </is>
       </c>
       <c r="L75" s="26" t="n">
-        <v>-163</v>
+        <v>100</v>
       </c>
       <c r="M75" s="27" t="n">
-        <v>1.613497</v>
+        <v>2</v>
       </c>
       <c r="N75" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.5</v>
       </c>
       <c r="O75" s="28" t="n">
-        <v>0.509301</v>
+        <v>0.5006660000000001</v>
       </c>
       <c r="P75" s="28" t="n"/>
       <c r="Q75" s="28" t="n">
-        <v>-0.110471</v>
+        <v>0.000666</v>
       </c>
       <c r="R75" s="26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S75" s="29" t="n">
         <v>1</v>
@@ -22343,7 +22567,7 @@
       <c r="AD75" s="24" t="n"/>
       <c r="AE75" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-cs2-ger-rush-2026-08-04).</t>
+          <t>Neutral Elo baseline; executable ask 0.5000 (market_slug=aec-cs2-unity-eyn-2026-08-04).</t>
         </is>
       </c>
       <c r="AF75" s="31" t="inlineStr">
@@ -22384,32 +22608,32 @@
       </c>
       <c r="AP75" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AQ75" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AR75" s="24" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>ex-Young Ninjas</t>
         </is>
       </c>
       <c r="AS75" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="AT75" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="AU75" s="24" t="inlineStr">
         <is>
-          <t>Grêmio Esports</t>
+          <t>UNiTY esports</t>
         </is>
       </c>
       <c r="AV75" s="24" t="n"/>
@@ -22427,7 +22651,7 @@
       </c>
       <c r="BA75" s="24" t="inlineStr">
         <is>
-     